--- a/Solicitacoes.xlsx
+++ b/Solicitacoes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="243">
   <si>
     <t>Protocolo</t>
   </si>
@@ -59,133 +59,175 @@
     <t>Prazo desejado</t>
   </si>
   <si>
+    <t>ANA.GOLDIM</t>
+  </si>
+  <si>
+    <t>HELPDESK - CUIDAR</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>Agendamentos</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- AG- AGENDAMENTO com erro Módulo de Regulação: Enviar mensagens Lean e Integracao Iris</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Suporte nível II</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>CORRECAO</t>
+  </si>
+  <si>
+    <t>BCON</t>
+  </si>
+  <si>
+    <t>Autorização</t>
+  </si>
+  <si>
+    <t>COMPESAPREV-CONECTA- Eventos negados, com recibo autorizado</t>
+  </si>
+  <si>
+    <t>Verificando</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- AG- PROD- Agendamento Regulacao travado</t>
+  </si>
+  <si>
+    <t>Liberado para cliente</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Compesaprev- Conecta- Erro na autorização</t>
+  </si>
+  <si>
     <t>COMPESAPREV.JULIA</t>
   </si>
   <si>
-    <t>CORRECAO</t>
-  </si>
-  <si>
-    <t>AG</t>
+    <t>Julia Albertim</t>
+  </si>
+  <si>
+    <t>Adm Operadora</t>
+  </si>
+  <si>
+    <t>Impossibilidade de Auditoria Geral de Biometria na Execução de Eventos (Exigência de Filtro por Prestador)</t>
+  </si>
+  <si>
+    <t>Homologando</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>MARIANA.HILA</t>
+  </si>
+  <si>
+    <t>SAAS</t>
+  </si>
+  <si>
+    <t>CompesaPrev - criar usuario WTS para Niecia</t>
+  </si>
+  <si>
+    <t>LUCAS.FIRMAN</t>
+  </si>
+  <si>
+    <t>Lista de Credenciados Ativos Conecta Compesa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPESAPREV- CONECTA- PROD:  Prestadores nao conseguem buscar o evento proprio</t>
+  </si>
+  <si>
+    <t>COMPESAPREV - CONECTA- PROD: Erro no arquivo excel relatorio</t>
+  </si>
+  <si>
+    <t>Plataforma Lean</t>
+  </si>
+  <si>
+    <t>Processos</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- LEAN- PROD- Agendamento travado</t>
   </si>
   <si>
     <t>ADM</t>
   </si>
   <si>
-    <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
-  </si>
-  <si>
-    <t>Pendente</t>
-  </si>
-  <si>
-    <t>Suporte nível II</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Julia Albertim</t>
-  </si>
-  <si>
-    <t>HELPDESK - CUIDAR</t>
-  </si>
-  <si>
-    <t>BCON</t>
-  </si>
-  <si>
-    <t>Faturamento</t>
-  </si>
-  <si>
-    <t>CONECTA - XML não sai do estado de "Em Processamento"</t>
-  </si>
-  <si>
-    <t>Resolvido</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>ANA.GOLDIM</t>
-  </si>
-  <si>
-    <t>Autorização</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- Conecta- Erro na solicitação dos procedimentos.</t>
-  </si>
-  <si>
-    <t>Homologando</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Agendamentos</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- AG- AGENDAMENTO com erro Módulo de Regulação: Enviar mensagens Lean e Integracao Iris</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>CONECTA - Erro na execução de guias | pop-up e bloqueio por biometria</t>
-  </si>
-  <si>
-    <t>Adm Operadora</t>
-  </si>
-  <si>
-    <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
-  </si>
-  <si>
-    <t>Verificando</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Prestadores</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO NOME PRESTADOR</t>
-  </si>
-  <si>
-    <t>Liberado para cliente</t>
-  </si>
-  <si>
-    <t>Plataforma Lean</t>
+    <t>COMPESAPREV- CONECTA- PROD -Publicação Webservices 4.02.00</t>
+  </si>
+  <si>
+    <t>NATALYA.GONCALVES</t>
+  </si>
+  <si>
+    <t>PORTAL</t>
+  </si>
+  <si>
+    <t>Gestor</t>
+  </si>
+  <si>
+    <t>Erro apresentado na sincronização "Dados rede de Atendimento"</t>
+  </si>
+  <si>
+    <t>Critica Conecta- Evento TGE</t>
+  </si>
+  <si>
+    <t>ANA.BRASILEIRO</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Erro ao enviar e-mail pelo Portal.</t>
   </si>
   <si>
     <t>Configurações do Sistema</t>
   </si>
   <si>
-    <t>Ajuste no tempo de sessão ativa (timeout) do sistema Lean.</t>
-  </si>
-  <si>
-    <t>ALEXIA.SANTOS</t>
-  </si>
-  <si>
-    <t>Controle Financeiro</t>
-  </si>
-  <si>
-    <t>Correção – CompesaPrev – Erro de Geração do Código de Barras e Linha Digitável</t>
-  </si>
-  <si>
-    <t>COMPESAPREV-CONECTA- Eventos negados, com recibo autorizado</t>
-  </si>
-  <si>
-    <t>COMPESAPREV.NIECIA</t>
-  </si>
-  <si>
-    <t>Niécia Morais</t>
-  </si>
-  <si>
-    <t>Processamento de Contas</t>
-  </si>
-  <si>
-    <t>Erro no faturamento de pagamentos prestadores</t>
-  </si>
-  <si>
-    <t>Dúvida sobre o local para salvar/exportar a Guia Executada no Portal do Prestador</t>
+    <t>Erro Lean Compesaprev</t>
+  </si>
+  <si>
+    <t>Mariana Hila</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Solicito configuração dos dados SMTP Servidor: smtp.office365.comPorta: 587Usuário: portalcompesas</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Solicito atualização do ambiente de homologação e produção para release 94</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_ Configuração de ServerManager</t>
+  </si>
+  <si>
+    <t>PRESTADOR.RAFAEL.P</t>
+  </si>
+  <si>
+    <t>Beneficiários</t>
+  </si>
+  <si>
+    <t>Erro na visualização de endereços do sistema web</t>
+  </si>
+  <si>
+    <t>CONFIGURAÇÃO</t>
+  </si>
+  <si>
+    <t>Atendimento</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Central de Atendimento</t>
+  </si>
+  <si>
+    <t>alexandre.gomes</t>
+  </si>
+  <si>
+    <t>Alexandre Machado de Souza Gomes</t>
+  </si>
+  <si>
+    <t>CRIAÇÃO DE AMBIENTE SAAS PARA O CLIENTE COMPESAPREV</t>
   </si>
   <si>
     <t>MOBE</t>
@@ -194,466 +236,61 @@
     <t>APP</t>
   </si>
   <si>
-    <t>Histórico financeiro sem a informação individual de todos os beneficiários</t>
-  </si>
-  <si>
-    <t>PORTAL</t>
-  </si>
-  <si>
-    <t>Portal não envia e-mails, recuperação de senha e processos parados desde 04/09</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- AG- PROD- Agendamento Regulacao travado</t>
-  </si>
-  <si>
-    <t>Processos</t>
-  </si>
-  <si>
-    <t>Lean / AG (Integração e guias travadas)</t>
-  </si>
-  <si>
-    <t>Beneficiários</t>
-  </si>
-  <si>
-    <t>Erro de divergência de cadastro entre o AG e o LEAN</t>
-  </si>
-  <si>
-    <t>MOBE | Erro no servidor ao tentar logar.</t>
-  </si>
-  <si>
-    <t>Extrato de Utilização com valores de coparticipações sem a limitação de PF e antes do faturamento ser concluído</t>
-  </si>
-  <si>
     <t>Erro ao buscar documento/relatório na Consulta de Autorizações (App)</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>Compesaprev- Conecta- Erro na autorização</t>
-  </si>
-  <si>
-    <t>CENTRAL ATENDIMENTO</t>
-  </si>
-  <si>
-    <t>Transações</t>
-  </si>
-  <si>
-    <t>Falha na integração entre AG Web e Central de Atendimento</t>
-  </si>
-  <si>
     <t>Ajuste de permissões e perfis de acesso no AG - Papel de Desenvolvedor aplicado a todos os usuários</t>
   </si>
   <si>
-    <t>Inconsistência no cálculo do prazo em horas úteis</t>
-  </si>
-  <si>
-    <t>Alinhamento sobre parametrização de críticas/motivos de negação automáticos (AG / Conecta)</t>
-  </si>
-  <si>
-    <t>APOIO DE NEGÓCIO</t>
-  </si>
-  <si>
-    <t>Erro na de geração do “Nosso Número” no boleto</t>
-  </si>
-  <si>
-    <t>Versão futura</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>EVIDENCIAS DO PROBLEMA NO RELATORIO DE PREVIA DE PAGAMENTO</t>
-  </si>
-  <si>
-    <t>COMPESAPREV – AG: Duplicidade dos eventos solicitados no e-mail do Beneficiario</t>
-  </si>
-  <si>
-    <t>Impossibilidade de Auditoria Geral de Biometria na Execução de Eventos (Exigência de Filtro por Prestador)</t>
-  </si>
-  <si>
-    <t>Atualização do AG em Produção - Release 3.65.19 (Ambiente e WTS)</t>
+    <t>COMPESAPREV.DANIEL</t>
+  </si>
+  <si>
+    <t>Daniel Serafim</t>
+  </si>
+  <si>
+    <t>BuilderCli para HML está solicitante atualizar para versão 25.0.94.4 ou superior</t>
+  </si>
+  <si>
+    <t>Lean Compesaprev- Sistema não realiza a busca da operadora no monitor de regulação</t>
+  </si>
+  <si>
+    <t>Instalação do Task worker para o cliente TRT3 base do LEAN</t>
+  </si>
+  <si>
+    <t>Parametrização de processos de agendamento no sistema Lean Compesaprev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPESAPREV_  sem retorno ao solicitar sincronização de parâmetros</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Replicação dos dados de produção em homologação</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Liberação de licenças desktop</t>
+  </si>
+  <si>
+    <t>FERNANDO.CARENO</t>
   </si>
   <si>
     <t>Regulação Médica</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- LEAN- RELATORIO- Regulações Vencidas</t>
-  </si>
-  <si>
-    <t>Esqueci minha senha APP</t>
-  </si>
-  <si>
-    <t>MELHORIA</t>
-  </si>
-  <si>
-    <t>CompesaPrev – Erro na Emissão de Boleto</t>
-  </si>
-  <si>
-    <t>Aguardando análise (negócio)</t>
-  </si>
-  <si>
-    <t>IMPL NAO COBRADA</t>
-  </si>
-  <si>
-    <t>Compesaprev - Complemento II SMS 2531696 – Regra para cálculo de coparticipação</t>
-  </si>
-  <si>
-    <t>Analisando (negócio)</t>
-  </si>
-  <si>
-    <t>ANA.BRASILEIRO</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Painel de sincronização - PLANOS</t>
-  </si>
-  <si>
-    <t>Históricos Atendimentos</t>
-  </si>
-  <si>
-    <t>Não está sendo possível SOLUCIONAR DEMANDAS</t>
-  </si>
-  <si>
-    <t>Compesaprev- Lean- Erro log integração</t>
-  </si>
-  <si>
-    <t>Daniel Serafim</t>
-  </si>
-  <si>
-    <t>COMPESAPREV - SISTEMA NÃO ESTÁ CONSIDERANDO LIMITADOR PF PARA REEMBOLSO</t>
-  </si>
-  <si>
-    <t>COMPESAPREV.DANIEL</t>
-  </si>
-  <si>
-    <t>COMPESPREV - Arquivo retorno com erro na importação</t>
-  </si>
-  <si>
-    <t>Julia Flora Ferreira de Albertim</t>
-  </si>
-  <si>
-    <t>Não consigo vizualizar o que estão pedindo para ALTERAR quando solicitam alteração cadastral de E-MAIL</t>
-  </si>
-  <si>
-    <t>Os detalhes da CARTEIRINHA não está aparecendo para alguns beneficiários</t>
-  </si>
-  <si>
-    <t>Acesso rede credenciada com perfil de DEPENDENTE não traz resultados.</t>
-  </si>
-  <si>
-    <t>MARIANA.HILA</t>
-  </si>
-  <si>
-    <t>SAAS</t>
-  </si>
-  <si>
-    <t>CompesaPrev - criar usuario WTS para Niecia</t>
-  </si>
-  <si>
-    <t>Liberação de Relatório Geral de Execução e Biometria / Correção de Bloqueios</t>
-  </si>
-  <si>
-    <t>Compesaprev-Lean- Erro na inclusão de procedimento- OPME</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Solicito atualização do Portal para release 2.2.22 para PRODUÇÃO</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Solicito atualização do Portal para release 2.2.22 para HOMOLOGAÇÃO</t>
-  </si>
-  <si>
-    <t>Acesso e busca na rede credenciada</t>
-  </si>
-  <si>
-    <t>LUCAS.FIRMAN</t>
-  </si>
-  <si>
-    <t>Falha ao utilizar o campo Ignorar críticas de XML no Conecta</t>
-  </si>
-  <si>
-    <t>COMPREPREV_ PROBLEMA RELACIONADO A REDE DE ATENDIMENTO</t>
-  </si>
-  <si>
-    <t>Atendimento</t>
-  </si>
-  <si>
-    <t>Compesaprev- AG-Produção: Erro na autorização</t>
-  </si>
-  <si>
-    <t>Compesaprev | AG TGE – Duplicidade de procedimento com o mesmo código</t>
-  </si>
-  <si>
-    <t>Valor Autorizado Não Exibido no Recibo de Atendimento</t>
-  </si>
-  <si>
-    <t>Lista de Credenciados Ativos Conecta Compesa</t>
-  </si>
-  <si>
-    <t>Falha ao ativar/desativar críticas de XML no Conecta</t>
-  </si>
-  <si>
-    <t>EDITAL NEGOCIACAO</t>
-  </si>
-  <si>
-    <t>MOBILE IRIS</t>
-  </si>
-  <si>
-    <t>App</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Implantação Mobile Íris</t>
-  </si>
-  <si>
-    <t>COMPESAPREV – AG - Produção: Falha na Integração das Guias para o Lean</t>
-  </si>
-  <si>
-    <t>COMPESAPREV – Lean Produção: Falha no Agendamento da Tarefa de Finalização</t>
-  </si>
-  <si>
-    <t>COMPESAPREV – Conecta Produção: Eventos não são localizados para inclusão em guia</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- AG- REGULAÇÃO- Agendamento travado</t>
-  </si>
-  <si>
-    <t>COMPESAPREV - Solicitação de atualização cadastral pelo Portal</t>
-  </si>
-  <si>
-    <t>Integrações</t>
-  </si>
-  <si>
-    <t>Compesaprev- Prod- Erro na fila de integraçao guias de prorrogação</t>
-  </si>
-  <si>
-    <t>Legal</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Rede de Atendimento - MOBILE</t>
-  </si>
-  <si>
-    <t>SERVIÇOS PONTUAIS</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- IRIS-Produção</t>
-  </si>
-  <si>
-    <t>COMPESAPREV-LEAN-PROD- Erro ao substituir diária — Enum inválido (TissTabelaProcedimentos)</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Cadastro de Cooperados</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- LEAN- PROD- Erro na finalização das regulacoes</t>
-  </si>
-  <si>
-    <t>Cancelado</t>
-  </si>
-  <si>
-    <t>Compesaprev- Lean- Produção- Erro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPESAPREV- CONECTA- PROD:  Prestadores nao conseguem buscar o evento proprio</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Alteração de logo para Mobile</t>
-  </si>
-  <si>
-    <t>COMPESAPREV - CONECTA- PROD: Erro no arquivo excel relatorio</t>
-  </si>
-  <si>
-    <t>QUALIDADE</t>
-  </si>
-  <si>
-    <t>COMPESAPREV-AG-PROD- Erro na inclusão de eventos no sistema AG</t>
-  </si>
-  <si>
-    <t>Aguardando detalhamento</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- LEAN- PROD- Agendamento travado</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- CONECTA- PROD -Publicação Webservices 4.02.00</t>
-  </si>
-  <si>
-    <t>VINICIUS.GENEROSO</t>
-  </si>
-  <si>
-    <t>Alteração da busca de limite de PF mensal por faixa salarial exclusivamente do titular</t>
-  </si>
-  <si>
-    <t>Complemento SMS 2531696 – Regra para cálculo de coparticipação</t>
-  </si>
-  <si>
-    <t>Complemento SMS 2470122 – Regra para cálculo de mensalidade</t>
-  </si>
-  <si>
-    <t>NATALYA.GONCALVES</t>
-  </si>
-  <si>
-    <t>Gestor</t>
-  </si>
-  <si>
-    <t>Erro apresentado na sincronização "Dados rede de Atendimento"</t>
-  </si>
-  <si>
-    <t>MONICA.SILVA</t>
-  </si>
-  <si>
-    <t>COMPLEMENTAR - SMS 2531696 - Cálculo de coparticipação por faixa salarial</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Apoio em rotina FTP</t>
-  </si>
-  <si>
-    <t>Erro de execução de query (NHibernate) ao enviar lote de pagamento</t>
-  </si>
-  <si>
-    <t>Web</t>
-  </si>
-  <si>
-    <t>Atualização da BuilderCli</t>
-  </si>
-  <si>
-    <t>Erro no envio de nota fiscal anexada no lote do Conecta para o AG</t>
-  </si>
-  <si>
-    <t>Status “Negada” não refletido no Conecta</t>
-  </si>
-  <si>
-    <t>WebServices da TISS 4.01 com Falha</t>
-  </si>
-  <si>
-    <t>BuilderCli para HML está solicitante atualizar para versão 25.0.94.4 ou superior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agendamentos do Conecta no Ambiente AG Não Estão Sendo  Processados</t>
-  </si>
-  <si>
-    <t>Cálculo de coparticipação por faixa salarial</t>
-  </si>
-  <si>
-    <t>PRESTADOR.RAFAEL.P</t>
-  </si>
-  <si>
-    <t>Mariana Hila</t>
-  </si>
-  <si>
-    <t>Erro para o cadastro das Qualificações</t>
-  </si>
-  <si>
-    <t>Atualização Versao TISS Conecta</t>
-  </si>
-  <si>
-    <t>Critica Conecta- Evento TGE</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Erro ao enviar e-mail pelo Portal.</t>
-  </si>
-  <si>
-    <t>Erro Lean Compesaprev Log de Finalização</t>
-  </si>
-  <si>
-    <t>RUI.KOEPSEL</t>
-  </si>
-  <si>
-    <t>CONSULTORIA</t>
-  </si>
-  <si>
-    <t>Consultoria a COMPESAPREV</t>
-  </si>
-  <si>
-    <t>Erro de sincronização entre AG e Central de Atendimento – Atendimento a Prestador</t>
-  </si>
-  <si>
-    <t>Aguardando testes internos</t>
-  </si>
-  <si>
-    <t>Lean Compesaprev- Sistema não realiza a busca da operadora no monitor de regulação</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Portal de Beneficiários</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_ Erro ao realizar sincronizações</t>
-  </si>
-  <si>
-    <t>Erro Lean Compesaprev</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Tombamento AG Produção na Homologação</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_ Portal de Beneficiários</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Solicito liberação do Conecta em produção. Segue dados do AG: https://compesaprev.bennercloud.com.br/AgWeb</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Solicito configuração dos dados SMTP Servidor: smtp.office365.comPorta: 587Usuário: portalcompesas</t>
-  </si>
-  <si>
-    <t>Instalação do Task worker para o cliente TRT3 base do LEAN</t>
-  </si>
-  <si>
-    <t>Parametrização de processos de agendamento no sistema Lean Compesaprev</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Solicito atualização do ambiente de homologação e produção para release 94</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_ Atualização AG (homologação)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPESAPREV_ erro na  sincronização</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_ Habilitar a rede credenciada ao Portal (tela de login).</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Atualização do Portal (homologação)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPESAPREV_  sem retorno ao solicitar sincronização de parâmetros</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Replicação dos dados de produção em homologação</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Liberação de licenças desktop</t>
-  </si>
-  <si>
-    <t>PEDRO.ALMEIDA</t>
-  </si>
-  <si>
-    <t>tombamento de base</t>
-  </si>
-  <si>
-    <t>Integração OPMENexo - Gestão de Cotações</t>
-  </si>
-  <si>
-    <t>FERNANDO.CARENO</t>
   </si>
   <si>
     <t xml:space="preserve">Erro ao abrir monitor de regulação do LEAN.
 Mesmo problema sendo tratado na SMS 2499740.</t>
   </si>
   <si>
-    <t>COMPESAPREV_ Configuração de ServerManager</t>
-  </si>
-  <si>
-    <t>Erro na visualização de endereços do sistema web</t>
-  </si>
-  <si>
     <t>Erro de sincronização entre AG e Central de Atendimento – Exportar Dados Beneficiário</t>
   </si>
   <si>
+    <t>QUALIDADE</t>
+  </si>
+  <si>
     <t>Legenda de campos sobrepostas</t>
   </si>
   <si>
-    <t>CONFIGURAÇÃO</t>
-  </si>
-  <si>
     <t xml:space="preserve">CompesaPrev  - Liberação da ferramenta Central de Atendimento no ambiente de produção</t>
   </si>
   <si>
@@ -666,6 +303,396 @@
     <t>CompesaPrev - Solicito criação da operadora CompesaPrev para a plataforma do Íris</t>
   </si>
   <si>
+    <t>CompesaPrev - Liberação de acesso ao Conecta</t>
+  </si>
+  <si>
+    <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Prestadores</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO NOME PRESTADOR</t>
+  </si>
+  <si>
+    <t>Ajuste no tempo de sessão ativa (timeout) do sistema Lean.</t>
+  </si>
+  <si>
+    <t>Dúvida sobre o local para salvar/exportar a Guia Executada no Portal do Prestador</t>
+  </si>
+  <si>
+    <t>Inconsistência no cálculo do prazo em horas úteis</t>
+  </si>
+  <si>
+    <t>Alinhamento sobre parametrização de críticas/motivos de negação automáticos (AG / Conecta)</t>
+  </si>
+  <si>
+    <t>CENTRAL ATENDIMENTO</t>
+  </si>
+  <si>
+    <t>Históricos Atendimentos</t>
+  </si>
+  <si>
+    <t>Não está sendo possível SOLUCIONAR DEMANDAS</t>
+  </si>
+  <si>
+    <t>Compesaprev- Lean- Erro log integração</t>
+  </si>
+  <si>
+    <t>Cancelado</t>
+  </si>
+  <si>
+    <t>Controle Financeiro</t>
+  </si>
+  <si>
+    <t>COMPESPREV - Arquivo retorno com erro na importação</t>
+  </si>
+  <si>
+    <t>Julia Flora Ferreira de Albertim</t>
+  </si>
+  <si>
+    <t>Liberação de Relatório Geral de Execução e Biometria / Correção de Bloqueios</t>
+  </si>
+  <si>
+    <t>Compesaprev-Lean- Erro na inclusão de procedimento- OPME</t>
+  </si>
+  <si>
+    <t>Falha ao utilizar o campo Ignorar críticas de XML no Conecta</t>
+  </si>
+  <si>
+    <t>Compesaprev- AG-Produção: Erro na autorização</t>
+  </si>
+  <si>
+    <t>Valor Autorizado Não Exibido no Recibo de Atendimento</t>
+  </si>
+  <si>
+    <t>Falha ao ativar/desativar críticas de XML no Conecta</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Cadastro de Cooperados</t>
+  </si>
+  <si>
+    <t>Faturamento</t>
+  </si>
+  <si>
+    <t>Erro no envio de nota fiscal anexada no lote do Conecta para o AG</t>
+  </si>
+  <si>
+    <t>Status “Negada” não refletido no Conecta</t>
+  </si>
+  <si>
+    <t>Atualização Versao TISS Conecta</t>
+  </si>
+  <si>
+    <t>Erro Lean Compesaprev Log de Finalização</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Tombamento AG Produção na Homologação</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Solicito liberação do Conecta em produção. Segue dados do AG: https://compesaprev.bennercloud.com.br/AgWeb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPESAPREV_ erro na  sincronização</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_ Habilitar a rede credenciada ao Portal (tela de login).</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Atualização do Portal (homologação)</t>
+  </si>
+  <si>
+    <t>PEDRO.ALMEIDA</t>
+  </si>
+  <si>
+    <t>tombamento de base</t>
+  </si>
+  <si>
+    <t>luciano.hering</t>
+  </si>
+  <si>
+    <t>[CRIAÇÃO DE BASE PARA CLIENTE COMPESAPREV OCI265 - SAUDE 10.220.0.38 - BASE PORTAL</t>
+  </si>
+  <si>
+    <t>[CRIAÇÃO DE BASE PARA CLIENTE COMPESAPREV OCI265 - SAUDE 10.220.0.38</t>
+  </si>
+  <si>
+    <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- Conecta- Erro na solicitação dos procedimentos.</t>
+  </si>
+  <si>
+    <t>ALEXIA.SANTOS</t>
+  </si>
+  <si>
+    <t>Correção – CompesaPrev – Erro de Geração do Código de Barras e Linha Digitável</t>
+  </si>
+  <si>
+    <t>COMPESAPREV.NIECIA</t>
+  </si>
+  <si>
+    <t>Niécia Morais</t>
+  </si>
+  <si>
+    <t>Processamento de Contas</t>
+  </si>
+  <si>
+    <t>Erro no faturamento de pagamentos prestadores</t>
+  </si>
+  <si>
+    <t>Histórico financeiro sem a informação individual de todos os beneficiários</t>
+  </si>
+  <si>
+    <t>Erro de divergência de cadastro entre o AG e o LEAN</t>
+  </si>
+  <si>
+    <t>MOBE | Erro no servidor ao tentar logar.</t>
+  </si>
+  <si>
+    <t>Extrato de Utilização com valores de coparticipações sem a limitação de PF e antes do faturamento ser concluído</t>
+  </si>
+  <si>
+    <t>Transações</t>
+  </si>
+  <si>
+    <t>Falha na integração entre AG Web e Central de Atendimento</t>
+  </si>
+  <si>
+    <t>EVIDENCIAS DO PROBLEMA NO RELATORIO DE PREVIA DE PAGAMENTO</t>
+  </si>
+  <si>
+    <t>COMPESAPREV – AG: Duplicidade dos eventos solicitados no e-mail do Beneficiario</t>
+  </si>
+  <si>
+    <t>Atualização do AG em Produção - Release 3.65.19 (Ambiente e WTS)</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- LEAN- RELATORIO- Regulações Vencidas</t>
+  </si>
+  <si>
+    <t>Esqueci minha senha APP</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Painel de sincronização - PLANOS</t>
+  </si>
+  <si>
+    <t>COMPESAPREV - SISTEMA NÃO ESTÁ CONSIDERANDO LIMITADOR PF PARA REEMBOLSO</t>
+  </si>
+  <si>
+    <t>Não consigo vizualizar o que estão pedindo para ALTERAR quando solicitam alteração cadastral de E-MAIL</t>
+  </si>
+  <si>
+    <t>Acesso rede credenciada com perfil de DEPENDENTE não traz resultados.</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Solicito atualização do Portal para release 2.2.22 para PRODUÇÃO</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Solicito atualização do Portal para release 2.2.22 para HOMOLOGAÇÃO</t>
+  </si>
+  <si>
+    <t>Acesso e busca na rede credenciada</t>
+  </si>
+  <si>
+    <t>Compesaprev | AG TGE – Duplicidade de procedimento com o mesmo código</t>
+  </si>
+  <si>
+    <t>COMPESAPREV – AG - Produção: Falha na Integração das Guias para o Lean</t>
+  </si>
+  <si>
+    <t>COMPESAPREV – Conecta Produção: Eventos não são localizados para inclusão em guia</t>
+  </si>
+  <si>
+    <t>COMPESAPREV - Solicitação de atualização cadastral pelo Portal</t>
+  </si>
+  <si>
+    <t>Legal</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Rede de Atendimento - MOBILE</t>
+  </si>
+  <si>
+    <t>Integrações</t>
+  </si>
+  <si>
+    <t>COMPESAPREV-LEAN-PROD- Erro ao substituir diária — Enum inválido (TissTabelaProcedimentos)</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- LEAN- PROD- Erro na finalização das regulacoes</t>
+  </si>
+  <si>
+    <t>Compesaprev- Lean- Produção- Erro</t>
+  </si>
+  <si>
+    <t>Erro de execução de query (NHibernate) ao enviar lote de pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agendamentos do Conecta no Ambiente AG Não Estão Sendo  Processados</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_ Erro ao realizar sincronizações</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_ Portal de Beneficiários</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_ Atualização AG (homologação)</t>
+  </si>
+  <si>
+    <t>CONECTA - XML não sai do estado de "Em Processamento"</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>CONECTA - Erro na execução de guias | pop-up e bloqueio por biometria</t>
+  </si>
+  <si>
+    <t>Portal não envia e-mails, recuperação de senha e processos parados desde 04/09</t>
+  </si>
+  <si>
+    <t>Lean / AG (Integração e guias travadas)</t>
+  </si>
+  <si>
+    <t>COMPESAPREV – Lean Produção: Falha no Agendamento da Tarefa de Finalização</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- AG- REGULAÇÃO- Agendamento travado</t>
+  </si>
+  <si>
+    <t>Compesaprev- Prod- Erro na fila de integraçao guias de prorrogação</t>
+  </si>
+  <si>
+    <t>Atualização da BuilderCli</t>
+  </si>
+  <si>
+    <t>WebServices da TISS 4.01 com Falha</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Portal de Beneficiários</t>
+  </si>
+  <si>
+    <t>APOIO DE NEGÓCIO</t>
+  </si>
+  <si>
+    <t>Erro na de geração do “Nosso Número” no boleto</t>
+  </si>
+  <si>
+    <t>Versão futura</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>MELHORIA</t>
+  </si>
+  <si>
+    <t>CompesaPrev – Erro na Emissão de Boleto</t>
+  </si>
+  <si>
+    <t>Aguardando análise (negócio)</t>
+  </si>
+  <si>
+    <t>IMPL NAO COBRADA</t>
+  </si>
+  <si>
+    <t>Compesaprev - Complemento II SMS 2531696 – Regra para cálculo de coparticipação</t>
+  </si>
+  <si>
+    <t>Analisando (negócio)</t>
+  </si>
+  <si>
+    <t>Os detalhes da CARTEIRINHA não está aparecendo para alguns beneficiários</t>
+  </si>
+  <si>
+    <t>COMPREPREV_ PROBLEMA RELACIONADO A REDE DE ATENDIMENTO</t>
+  </si>
+  <si>
+    <t>EDITAL NEGOCIACAO</t>
+  </si>
+  <si>
+    <t>MOBILE IRIS</t>
+  </si>
+  <si>
+    <t>App</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Implantação Mobile Íris</t>
+  </si>
+  <si>
+    <t>SERVIÇOS PONTUAIS</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- IRIS-Produção</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Alteração de logo para Mobile</t>
+  </si>
+  <si>
+    <t>COMPESAPREV-AG-PROD- Erro na inclusão de eventos no sistema AG</t>
+  </si>
+  <si>
+    <t>Aguardando detalhamento</t>
+  </si>
+  <si>
+    <t>VINICIUS.GENEROSO</t>
+  </si>
+  <si>
+    <t>Alteração da busca de limite de PF mensal por faixa salarial exclusivamente do titular</t>
+  </si>
+  <si>
+    <t>Complemento SMS 2531696 – Regra para cálculo de coparticipação</t>
+  </si>
+  <si>
+    <t>Complemento SMS 2470122 – Regra para cálculo de mensalidade</t>
+  </si>
+  <si>
+    <t>MONICA.SILVA</t>
+  </si>
+  <si>
+    <t>COMPLEMENTAR - SMS 2531696 - Cálculo de coparticipação por faixa salarial</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Apoio em rotina FTP</t>
+  </si>
+  <si>
+    <t>Cálculo de coparticipação por faixa salarial</t>
+  </si>
+  <si>
+    <t>Erro para o cadastro das Qualificações</t>
+  </si>
+  <si>
+    <t>RUI.KOEPSEL</t>
+  </si>
+  <si>
+    <t>CONSULTORIA</t>
+  </si>
+  <si>
+    <t>Consultoria a COMPESAPREV</t>
+  </si>
+  <si>
+    <t>Erro de sincronização entre AG e Central de Atendimento – Atendimento a Prestador</t>
+  </si>
+  <si>
+    <t>Aguardando testes internos</t>
+  </si>
+  <si>
+    <t>Integração OPMENexo - Gestão de Cotações</t>
+  </si>
+  <si>
     <t>IMPLEMENTACAO</t>
   </si>
   <si>
@@ -687,9 +714,6 @@
     <t>DV_Envio automático de comunicados aos beneficiários</t>
   </si>
   <si>
-    <t>CompesaPrev - Central de Atendimento</t>
-  </si>
-  <si>
     <t>PRESTADOR.PRISCILA.S</t>
   </si>
   <si>
@@ -714,31 +738,10 @@
     <t>CompesaPrev |Informações adicionais para migração de dados de beneficiários</t>
   </si>
   <si>
-    <t>luciano.hering</t>
-  </si>
-  <si>
-    <t>[CRIAÇÃO DE BASE PARA CLIENTE COMPESAPREV OCI265 - SAUDE 10.220.0.38 - BASE PORTAL</t>
-  </si>
-  <si>
     <t>Fernando.Soncin</t>
   </si>
   <si>
     <t>Avaliação de documentação de aderência módulo de Beneficiários</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Liberação de acesso ao Conecta</t>
-  </si>
-  <si>
-    <t>alexandre.gomes</t>
-  </si>
-  <si>
-    <t>Alexandre Machado de Souza Gomes</t>
-  </si>
-  <si>
-    <t>CRIAÇÃO DE AMBIENTE SAAS PARA O CLIENTE COMPESAPREV</t>
-  </si>
-  <si>
-    <t>[CRIAÇÃO DE BASE PARA CLIENTE COMPESAPREV OCI265 - SAUDE 10.220.0.38</t>
   </si>
 </sst>
 </file>
@@ -794,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O141"/>
+  <dimension ref="A1:O142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1506990705218" customWidth="1"/>
@@ -863,7 +866,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2615970</v>
+        <v>2614686</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>15</v>
@@ -887,10 +890,10 @@
         <v>20</v>
       </c>
       <c r="I2" s="3">
-        <v>46288.4166666667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="J2" s="3">
-        <v>46282.5089930556</v>
+        <v>46282.4296635764</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>21</v>
@@ -899,208 +902,208 @@
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>46282.5089930556</v>
+        <v>46280.4450115741</v>
       </c>
       <c r="N2" s="3">
-        <v>46288.4166666667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2615871</v>
+        <v>2612720</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="E3" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="F3" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="G3" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="H3" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="I3" s="3">
-        <v>46286.4024189815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="J3" s="3">
-        <v>46286.3450115741</v>
+        <v>46279.4816203704</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M3" s="3">
-        <v>46282.4440856481</v>
+        <v>46275.4553356481</v>
       </c>
       <c r="N3" s="3">
-        <v>46286.4024189815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2615590</v>
+        <v>2611551</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3">
-        <v>46287.5805092593</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="J4" s="3">
-        <v>46281.7496990741</v>
+        <v>46274.3603356481</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L4" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M4" s="3">
-        <v>46281.6638425926</v>
+        <v>46273.4725115741</v>
       </c>
       <c r="N4" s="3">
-        <v>46287.5805092593</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>2614686</v>
+        <v>2609883</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F5" s="0" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I5" s="3">
-        <v>46321.5908449074</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="J5" s="3">
-        <v>46282.4296635764</v>
+        <v>46280.4030439815</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="M5" s="3">
-        <v>46280.4450115741</v>
+        <v>46267.6217013889</v>
       </c>
       <c r="N5" s="3">
-        <v>46321.5908449074</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="O5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>2614334</v>
+        <v>2604815</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D6" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="0" t="s">
-        <v>25</v>
-      </c>
       <c r="F6" s="0" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I6" s="3">
-        <v>46283.5629166667</v>
+        <v>46296.563587963</v>
       </c>
       <c r="J6" s="3">
-        <v>46283.4291666667</v>
+        <v>46268.6781365741</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M6" s="3">
-        <v>46279.6749305556</v>
+        <v>46255.4177546296</v>
       </c>
       <c r="N6" s="3">
-        <v>46283.5629166667</v>
+        <v>46296.563587963</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>2614135</v>
+        <v>2596882</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F7" s="0" t="s">
         <v>39</v>
@@ -1109,76 +1112,76 @@
         <v>40</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3">
-        <v>46289.7291666667</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="J7" s="3">
-        <v>46279.6123263889</v>
+        <v>46267.6170023148</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="M7" s="3">
-        <v>46279.5169097222</v>
+        <v>46238.7108912037</v>
       </c>
       <c r="N7" s="3">
-        <v>46289.7291666667</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>2613646</v>
+        <v>2591284</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C8" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="E8" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F8" s="0" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3">
-        <v>46289.3876041667</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="J8" s="3">
-        <v>46283.4346064815</v>
+        <v>46225.7002398495</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="M8" s="3">
-        <v>46276.6376041667</v>
+        <v>46225.6718171296</v>
       </c>
       <c r="N8" s="3">
-        <v>46289.3876041667</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2613202</v>
+        <v>2584167</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>15</v>
@@ -1187,667 +1190,667 @@
         <v>15</v>
       </c>
       <c r="D9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="F9" s="0" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I9" s="3">
-        <v>46288.6119212963</v>
+        <v>46246.7216435185</v>
       </c>
       <c r="J9" s="3">
-        <v>46283.4707657407</v>
+        <v>46247.4396759259</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="M9" s="3">
-        <v>46276.3827546296</v>
+        <v>46206.6383101852</v>
       </c>
       <c r="N9" s="3">
-        <v>46288.6119212963</v>
+        <v>46246.7216435185</v>
       </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>2613026</v>
+        <v>2583447</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D10" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F10" s="0" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I10" s="3">
-        <v>46281.6747800926</v>
+        <v>46245.6724189815</v>
       </c>
       <c r="J10" s="3">
-        <v>46280.356624456</v>
+        <v>46265.3645138889</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L10" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M10" s="3">
-        <v>46275.6895601852</v>
+        <v>46205.5752083333</v>
       </c>
       <c r="N10" s="3">
-        <v>46281.6747800926</v>
+        <v>46245.6724189815</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>2612720</v>
+        <v>2582452</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="I11" s="3">
-        <v>46316.6011689815</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="J11" s="3">
-        <v>46279.4816203704</v>
+        <v>46204.7763078704</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="M11" s="3">
-        <v>46275.4553356481</v>
+        <v>46203.8250810185</v>
       </c>
       <c r="N11" s="3">
-        <v>46316.6011689815</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>2611881</v>
+        <v>2582352</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I12" s="3">
-        <v>46279.6652314815</v>
+        <v>46244.340775463</v>
       </c>
       <c r="J12" s="3">
-        <v>46274.7389930556</v>
+        <v>46204.7761805556</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L12" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M12" s="3">
-        <v>46273.7485648148</v>
+        <v>46203.6741087963</v>
       </c>
       <c r="N12" s="3">
-        <v>46279.6652314815</v>
+        <v>46244.340775463</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>2611848</v>
+        <v>2572707</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I13" s="3">
-        <v>46287.4094675926</v>
+        <v>46219.3964814815</v>
       </c>
       <c r="J13" s="3">
-        <v>46276.5914583333</v>
+        <v>46188.4629166667</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="M13" s="3">
-        <v>46273.7127546296</v>
+        <v>46178.7298148148</v>
       </c>
       <c r="N13" s="3">
-        <v>46287.4094675926</v>
+        <v>46219.3964814815</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>2611692</v>
+        <v>2529591</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D14" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="0" t="s">
-        <v>58</v>
-      </c>
       <c r="F14" s="0" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I14" s="3">
-        <v>46279.4554861111</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="J14" s="3">
-        <v>46273.637278588</v>
+        <v>46126.6875</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L14" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M14" s="3">
-        <v>46273.6013194444</v>
+        <v>46069.4509722222</v>
       </c>
       <c r="N14" s="3">
-        <v>46279.4554861111</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2611552</v>
+        <v>2528858</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I15" s="3">
-        <v>46275.4327083333</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="J15" s="3">
-        <v>46273.5743171296</v>
+        <v>46087.6277662037</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M15" s="3">
-        <v>46273.474375</v>
+        <v>46065.7194791667</v>
       </c>
       <c r="N15" s="3">
-        <v>46275.4327083333</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>2611551</v>
+        <v>2523602</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I16" s="3">
-        <v>46314.6183449074</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="J16" s="3">
-        <v>46274.3603356481</v>
+        <v>46056.5784027778</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="M16" s="3">
-        <v>46273.4725115741</v>
+        <v>46055.4788310185</v>
       </c>
       <c r="N16" s="3">
-        <v>46314.6183449074</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>2611539</v>
+        <v>2519904</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I17" s="3">
-        <v>46275.4227083333</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="J17" s="3">
-        <v>46274.3607986111</v>
+        <v>46044.7413888889</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M17" s="3">
-        <v>46273.464375</v>
+        <v>46044.6384606482</v>
       </c>
       <c r="N17" s="3">
-        <v>46275.4227083333</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>2611521</v>
+        <v>2518650</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I18" s="3">
-        <v>46279.3705439815</v>
+        <v>46072.3536921296</v>
       </c>
       <c r="J18" s="3">
-        <v>46273.7182003819</v>
+        <v>46043.8185648148</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L18" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M18" s="3">
-        <v>46273.4538773148</v>
+        <v>46042.3536921296</v>
       </c>
       <c r="N18" s="3">
-        <v>46279.3705439815</v>
+        <v>46080.437025463</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>2610876</v>
+        <v>2502438</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I19" s="3">
-        <v>46276.3367592593</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="J19" s="3">
-        <v>46269.4406376505</v>
+        <v>45996.4823032407</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L19" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M19" s="3">
-        <v>46269.4200925926</v>
+        <v>45992.7134722222</v>
       </c>
       <c r="N19" s="3">
-        <v>46276.3367592593</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>2610030</v>
+        <v>2501349</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I20" s="3">
-        <v>46274.6271990741</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="J20" s="3">
-        <v>46268.3853071412</v>
+        <v>46069.3651388889</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L20" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M20" s="3">
-        <v>46267.7105324074</v>
+        <v>45989.0365856482</v>
       </c>
       <c r="N20" s="3">
-        <v>46274.6271990741</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>2609985</v>
+        <v>2474606</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I21" s="3">
-        <v>46301.4629166667</v>
+        <v>45952.4506944444</v>
       </c>
       <c r="J21" s="3">
-        <v>46267.6774134606</v>
+        <v>45966.4450925926</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="M21" s="3">
-        <v>46267.67125</v>
+        <v>45924.4486921296</v>
       </c>
       <c r="N21" s="3">
-        <v>46301.4629166667</v>
+        <v>45952.4506944444</v>
       </c>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2609883</v>
+        <v>2437239</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I22" s="3">
-        <v>46309.7050347222</v>
+        <v>45870.3600462963</v>
       </c>
       <c r="J22" s="3">
-        <v>46280.4030439815</v>
+        <v>45841.7026091435</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="M22" s="3">
-        <v>46267.6217013889</v>
+        <v>45831.6933796296</v>
       </c>
       <c r="N22" s="3">
-        <v>46309.7050347222</v>
+        <v>45870.3600462963</v>
       </c>
       <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>2609551</v>
+        <v>2609985</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="G23" s="0" t="s">
         <v>74</v>
-      </c>
-      <c r="G23" s="0" t="s">
-        <v>75</v>
       </c>
       <c r="H23" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I23" s="3">
-        <v>46273.6887962963</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="J23" s="3">
-        <v>46267.355462963</v>
+        <v>46267.6774134606</v>
       </c>
       <c r="K23" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="M23" s="3">
-        <v>46267.355462963</v>
+        <v>46267.67125</v>
       </c>
       <c r="N23" s="3">
-        <v>46273.6887962963</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="O23" s="3"/>
     </row>
@@ -1856,19 +1859,19 @@
         <v>2609107</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>76</v>
@@ -1886,7 +1889,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M24" s="3">
         <v>46266.4797916667</v>
@@ -1898,52 +1901,52 @@
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>2608731</v>
+        <v>2547638</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I25" s="3">
-        <v>46279.4280671296</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="J25" s="3">
-        <v>46273.3513888889</v>
+        <v>46119.5010069444</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="M25" s="3">
-        <v>46265.6780671296</v>
+        <v>46114.4931944444</v>
       </c>
       <c r="N25" s="3">
-        <v>46279.4280671296</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>2608637</v>
+        <v>2524373</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>15</v>
@@ -1952,276 +1955,280 @@
         <v>15</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I26" s="3">
-        <v>46279.3644444444</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="J26" s="3">
-        <v>46266.3667347222</v>
+        <v>46056.6543865741</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="M26" s="3">
-        <v>46265.6144444444</v>
+        <v>46056.5937847222</v>
       </c>
       <c r="N26" s="3">
-        <v>46279.3644444444</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>2607413</v>
+        <v>2519523</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="I27" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="I27" s="3">
+        <v>46076.5902777778</v>
+      </c>
       <c r="J27" s="3">
-        <v>46266.569212963</v>
+        <v>46048.4589814815</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M27" s="3">
-        <v>46261.6163888889</v>
-      </c>
-      <c r="N27" s="3"/>
+        <v>46043.7362847222</v>
+      </c>
+      <c r="N27" s="3">
+        <v>46077.380775463</v>
+      </c>
       <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>2607198</v>
+        <v>2519383</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I28" s="3">
-        <v>46267.3546643518</v>
+        <v>46076.399224537</v>
       </c>
       <c r="J28" s="3">
-        <v>46273.6204976852</v>
+        <v>46048.4599305556</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="M28" s="3">
-        <v>46261.4379976852</v>
+        <v>46043.6075578704</v>
       </c>
       <c r="N28" s="3">
-        <v>46267.3546643518</v>
+        <v>46076.399224537</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>2606003</v>
+        <v>2509014</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I29" s="3">
-        <v>46265.3599537037</v>
+        <v>46044.7250578704</v>
       </c>
       <c r="J29" s="3">
-        <v>46259.4993506944</v>
+        <v>46022.6138541667</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="M29" s="3">
-        <v>46259.443287037</v>
+        <v>46008.454224537</v>
       </c>
       <c r="N29" s="3">
-        <v>46290.75</v>
+        <v>46045.4708564815</v>
       </c>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>2604815</v>
+        <v>2506714</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F30" s="0" t="s">
         <v>39</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I30" s="3">
-        <v>46296.563587963</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="J30" s="3">
-        <v>46268.6781365741</v>
+        <v>46044.7372337963</v>
       </c>
       <c r="K30" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="M30" s="3">
-        <v>46255.4177546296</v>
+        <v>46002.4364699074</v>
       </c>
       <c r="N30" s="3">
-        <v>46296.563587963</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>2604500</v>
+        <v>2506599</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I31" s="3">
-        <v>46260.4812268519</v>
+        <v>46037.61375</v>
       </c>
       <c r="J31" s="3">
-        <v>46258.3485416667</v>
+        <v>46052.3252083333</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="M31" s="3">
-        <v>46254.6270601852</v>
+        <v>46002.3429166667</v>
       </c>
       <c r="N31" s="3">
-        <v>46260.4812268519</v>
+        <v>46037.61375</v>
       </c>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>2603668</v>
+        <v>2502589</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F32" s="0" t="s">
         <v>87</v>
@@ -2230,82 +2237,82 @@
         <v>88</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I32" s="3">
-        <v>46259.3446296296</v>
+        <v>46029.6634375</v>
       </c>
       <c r="J32" s="3">
-        <v>46258.6426851852</v>
+        <v>46014.6931018519</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="M32" s="3">
-        <v>46253.427962963</v>
+        <v>45993.3791087963</v>
       </c>
       <c r="N32" s="3">
-        <v>46290.75</v>
+        <v>46029.6634375</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>2602388</v>
+        <v>2500635</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>89</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I33" s="3">
-        <v>46255.4166666667</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="J33" s="3">
-        <v>46253.4900231482</v>
+        <v>46027.3611111111</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="M33" s="3">
-        <v>46251.5527777778</v>
+        <v>45987.671712963</v>
       </c>
       <c r="N33" s="3">
-        <v>46255.4166666667</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>2601999</v>
+        <v>2498066</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>90</v>
@@ -2314,875 +2321,878 @@
         <v>17</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>91</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="I34" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="I34" s="3">
+        <v>46073.7916666667</v>
+      </c>
       <c r="J34" s="3">
-        <v>46266.6188194444</v>
+        <v>46126.6953240741</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M34" s="3">
-        <v>46248.7351273148</v>
+        <v>45979.750162037</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>2600778</v>
+        <v>2494282</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="I35" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="I35" s="3">
+        <v>45986.48125</v>
+      </c>
       <c r="J35" s="3">
-        <v>46274.3780324074</v>
+        <v>45988.567025463</v>
       </c>
       <c r="K35" s="0" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M35" s="3">
-        <v>46246.7171759259</v>
-      </c>
-      <c r="N35" s="3"/>
+        <v>45971.4792824074</v>
+      </c>
+      <c r="N35" s="3">
+        <v>45986.4815625</v>
+      </c>
       <c r="O35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>2599732</v>
+        <v>2494179</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I36" s="3">
-        <v>46251.4016203704</v>
+        <v>46002.675775463</v>
       </c>
       <c r="J36" s="3">
-        <v>46248.3419117245</v>
+        <v>46044.7370486111</v>
       </c>
       <c r="K36" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="M36" s="3">
-        <v>46245.4849537037</v>
+        <v>45971.4049421296</v>
       </c>
       <c r="N36" s="3">
-        <v>46251.4016203704</v>
+        <v>46002.675775463</v>
       </c>
       <c r="O36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>2598987</v>
+        <v>2439691</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D37" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="F37" s="0" t="s">
-        <v>98</v>
-      </c>
       <c r="G37" s="0" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I37" s="3">
-        <v>46254.6856134259</v>
+        <v>45852.3770833333</v>
       </c>
       <c r="J37" s="3">
-        <v>46251.536875</v>
+        <v>45838.6211342593</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="M37" s="3">
-        <v>46244.4564467593</v>
+        <v>45838.3761921296</v>
       </c>
       <c r="N37" s="3">
-        <v>46254.6856134259</v>
+        <v>45852.3770833333</v>
       </c>
       <c r="O37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>2598910</v>
+        <v>2614135</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D38" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E38" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="F38" s="0" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I38" s="3">
-        <v>46254.6386574074</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="J38" s="3">
-        <v>46248.4760674769</v>
+        <v>46279.6123263889</v>
       </c>
       <c r="K38" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M38" s="3">
-        <v>46244.4094907407</v>
+        <v>46279.5169097222</v>
       </c>
       <c r="N38" s="3">
-        <v>46261.6103125</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="O38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2598767</v>
+        <v>2613646</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I39" s="3">
-        <v>46247.6666666667</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="J39" s="3">
-        <v>46245.6608564815</v>
+        <v>46283.4346064815</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M39" s="3">
-        <v>46241.757962963</v>
+        <v>46276.6376041667</v>
       </c>
       <c r="N39" s="3">
-        <v>46247.6666666667</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="O39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>2597798</v>
+        <v>2613202</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="C40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="D40" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="G40" s="0" t="s">
-        <v>104</v>
-      </c>
       <c r="H40" s="0" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I40" s="3">
-        <v>46290.75</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="J40" s="3">
-        <v>46273.4412384259</v>
+        <v>46283.4707657407</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M40" s="3">
-        <v>46240.4508912037</v>
+        <v>46276.3827546296</v>
       </c>
       <c r="N40" s="3">
-        <v>46290.75</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="O40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>2597524</v>
+        <v>2611848</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="D41" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E41" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F41" s="0" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I41" s="3">
-        <v>46267.0453356481</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="J41" s="3">
-        <v>46259.4158333333</v>
+        <v>46276.5914583333</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M41" s="3">
-        <v>46239.6925347222</v>
+        <v>46273.7127546296</v>
       </c>
       <c r="N41" s="3">
-        <v>46267.0453356481</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="O41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>2597515</v>
+        <v>2608731</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H42" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I42" s="3">
-        <v>46266.4759953704</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="J42" s="3">
-        <v>46261.4097453704</v>
+        <v>46273.3513888889</v>
       </c>
       <c r="K42" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="M42" s="3">
-        <v>46239.6856134259</v>
+        <v>46265.6780671296</v>
       </c>
       <c r="N42" s="3">
-        <v>46266.4759953704</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="O42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>2597495</v>
+        <v>2608637</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H43" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I43" s="3">
-        <v>46252.3333333333</v>
+        <v>46279.3644444444</v>
       </c>
       <c r="J43" s="3">
-        <v>46241.6523302083</v>
+        <v>46266.3667347222</v>
       </c>
       <c r="K43" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M43" s="3">
-        <v>46239.6802199074</v>
+        <v>46265.6144444444</v>
       </c>
       <c r="N43" s="3">
-        <v>46245.5968865741</v>
-      </c>
-      <c r="O43" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>46279.3644444444</v>
+      </c>
+      <c r="O43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>2596882</v>
+        <v>2598987</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I44" s="3">
-        <v>46280.3775578704</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="J44" s="3">
-        <v>46267.6170023148</v>
+        <v>46251.536875</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="M44" s="3">
-        <v>46238.7108912037</v>
+        <v>46244.4564467593</v>
       </c>
       <c r="N44" s="3">
-        <v>46280.3775578704</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="O44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>2596538</v>
+        <v>2598910</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="I45" s="3">
-        <v>46268.6668865741</v>
+        <v>46254.6386574074</v>
       </c>
       <c r="J45" s="3">
-        <v>46269.3797800926</v>
+        <v>46248.4760674769</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M45" s="3">
-        <v>46238.4644791667</v>
+        <v>46244.4094907407</v>
       </c>
       <c r="N45" s="3">
-        <v>46273.960787037</v>
+        <v>46261.6103125</v>
       </c>
       <c r="O45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>2596407</v>
+        <v>2597798</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I46" s="3">
-        <v>46248.6072106482</v>
+        <v>46290.75</v>
       </c>
       <c r="J46" s="3">
-        <v>46267.6164814815</v>
+        <v>46273.4412384259</v>
       </c>
       <c r="K46" s="0" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M46" s="3">
-        <v>46238.3780439815</v>
+        <v>46240.4508912037</v>
       </c>
       <c r="N46" s="3">
-        <v>46248.6072106482</v>
+        <v>46290.75</v>
       </c>
       <c r="O46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>2595510</v>
+        <v>2596538</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D47" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E47" s="0" t="s">
-        <v>61</v>
-      </c>
       <c r="F47" s="0" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I47" s="3">
-        <v>46240.4984606481</v>
+        <v>46273.960787037</v>
       </c>
       <c r="J47" s="3">
-        <v>46245.3667592593</v>
+        <v>46286.3521412037</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M47" s="3">
-        <v>46234.6442939815</v>
+        <v>46238.4644791667</v>
       </c>
       <c r="N47" s="3">
-        <v>46240.4984606481</v>
+        <v>46273.960787037</v>
       </c>
       <c r="O47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>2595497</v>
+        <v>2596407</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I48" s="3">
-        <v>46240.4978240741</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="J48" s="3">
-        <v>46245.3669444444</v>
+        <v>46267.6164814815</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M48" s="3">
-        <v>46234.6436574074</v>
+        <v>46238.3780439815</v>
       </c>
       <c r="N48" s="3">
-        <v>46240.4978240741</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="O48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>2593529</v>
+        <v>2593260</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D49" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E49" s="0" t="s">
-        <v>58</v>
-      </c>
       <c r="F49" s="0" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I49" s="3">
-        <v>46237.5806597222</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="J49" s="3">
-        <v>46233.4404570255</v>
+        <v>46267.614525463</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M49" s="3">
-        <v>46231.6639930556</v>
+        <v>46231.435150463</v>
       </c>
       <c r="N49" s="3">
-        <v>46237.5806597222</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="O49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>2593490</v>
+        <v>2592878</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I50" s="3">
-        <v>46239.6748032407</v>
+        <v>46241.3504282407</v>
       </c>
       <c r="J50" s="3">
-        <v>46253.4905324074</v>
+        <v>46230.6675740741</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="M50" s="3">
-        <v>46231.6518865741</v>
+        <v>46230.6004282407</v>
       </c>
       <c r="N50" s="3">
-        <v>46239.6748032407</v>
-      </c>
-      <c r="O50" s="3">
-        <v>46234.48125</v>
-      </c>
+        <v>46290.75</v>
+      </c>
+      <c r="O50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>2593260</v>
+        <v>2591596</v>
       </c>
       <c r="B51" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G51" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="C51" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="D51" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E51" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="G51" s="0" t="s">
-        <v>118</v>
-      </c>
       <c r="H51" s="0" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I51" s="3">
-        <v>46241.6638888889</v>
+        <v>46238.7083333333</v>
       </c>
       <c r="J51" s="3">
-        <v>46267.614525463</v>
+        <v>46267.3444803241</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M51" s="3">
-        <v>46231.435150463</v>
+        <v>46226.4797916667</v>
       </c>
       <c r="N51" s="3">
-        <v>46241.6638888889</v>
+        <v>46282.6141435185</v>
       </c>
       <c r="O51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>2593216</v>
+        <v>2588490</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I52" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="I52" s="3">
+        <v>46230.722037037</v>
+      </c>
       <c r="J52" s="3">
-        <v>46231.4047453704</v>
+        <v>46231.4339699074</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="M52" s="3">
-        <v>46231.4011111111</v>
-      </c>
-      <c r="N52" s="3"/>
+        <v>46218.4928703704</v>
+      </c>
+      <c r="N52" s="3">
+        <v>46230.722037037</v>
+      </c>
       <c r="O52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>2592878</v>
+        <v>2585424</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="D53" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E53" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F53" s="0" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I53" s="3">
-        <v>46241.3504282407</v>
+        <v>46223.3927199074</v>
       </c>
       <c r="J53" s="3">
-        <v>46230.6675740741</v>
+        <v>46234.4964930556</v>
       </c>
       <c r="K53" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M53" s="3">
-        <v>46230.6004282407</v>
+        <v>46210.6427199074</v>
       </c>
       <c r="N53" s="3">
         <v>46290.75</v>
@@ -3191,3650 +3201,3660 @@
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>2592468</v>
+        <v>2556211</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D54" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E54" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="F54" s="0" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I54" s="3">
-        <v>46237.6038657407</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="J54" s="3">
-        <v>46240.6136738773</v>
+        <v>46146.3663773148</v>
       </c>
       <c r="K54" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M54" s="3">
-        <v>46227.7107060185</v>
+        <v>46139.4325810185</v>
       </c>
       <c r="N54" s="3">
-        <v>46293.6033680556</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="O54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>2591596</v>
+        <v>2556029</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="D55" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E55" s="0" t="s">
+      <c r="F55" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="F55" s="0" t="s">
-        <v>31</v>
-      </c>
       <c r="G55" s="0" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I55" s="3">
-        <v>46238.7083333333</v>
+        <v>46150.5</v>
       </c>
       <c r="J55" s="3">
-        <v>46267.3444803241</v>
+        <v>46146.401875</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M55" s="3">
-        <v>46226.4797916667</v>
+        <v>46138.757337963</v>
       </c>
       <c r="N55" s="3">
-        <v>46282.6141435185</v>
+        <v>46154.6616087963</v>
       </c>
       <c r="O55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>2591284</v>
+        <v>2529639</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I56" s="3">
-        <v>46266.3384837963</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="J56" s="3">
-        <v>46225.7002398495</v>
+        <v>46072.6891666667</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="M56" s="3">
-        <v>46225.6718171296</v>
+        <v>46069.5930902778</v>
       </c>
       <c r="N56" s="3">
-        <v>46266.3384837963</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="O56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>2588490</v>
+        <v>2525312</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I57" s="3">
-        <v>46230.722037037</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="J57" s="3">
-        <v>46231.4339699074</v>
+        <v>46062.7587037037</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="M57" s="3">
-        <v>46218.4928703704</v>
+        <v>46058.3585648148</v>
       </c>
       <c r="N57" s="3">
-        <v>46230.722037037</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="O57" s="3"/>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>2588025</v>
+        <v>2521645</v>
       </c>
       <c r="B58" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="H58" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="C58" s="0" t="s">
+      <c r="I58" s="3">
+        <v>46062.5</v>
+      </c>
+      <c r="J58" s="3">
+        <v>46050.3426763542</v>
+      </c>
+      <c r="K58" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="D58" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="E58" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="F58" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="G58" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="H58" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3">
-        <v>46267.5903356482</v>
-      </c>
-      <c r="K58" s="0" t="s">
-        <v>81</v>
-      </c>
       <c r="L58" s="0" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="M58" s="3">
-        <v>46217.612962963</v>
+        <v>46049.7714236111</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>2587849</v>
+        <v>2520048</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D59" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F59" s="0" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I59" s="3">
-        <v>46226.6083796296</v>
+        <v>46057.5</v>
       </c>
       <c r="J59" s="3">
-        <v>46237.9144806713</v>
+        <v>46052.5774305556</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M59" s="3">
-        <v>46217.4506597222</v>
+        <v>46045.3325578704</v>
       </c>
       <c r="N59" s="3">
-        <v>46226.6083796296</v>
+        <v>46057.5</v>
       </c>
       <c r="O59" s="3"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2587713</v>
+        <v>2512883</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I60" s="3">
-        <v>46218.7408680556</v>
+        <v>46037.6340972222</v>
       </c>
       <c r="J60" s="3">
-        <v>46230.4199074074</v>
+        <v>46129.4199421296</v>
       </c>
       <c r="K60" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="M60" s="3">
-        <v>46217.3658680556</v>
+        <v>46027.4049305556</v>
       </c>
       <c r="N60" s="3">
-        <v>46218.7408680556</v>
+        <v>46141.6335300926</v>
       </c>
       <c r="O60" s="3"/>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>2587585</v>
+        <v>2512542</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I61" s="3">
-        <v>46220.6264583333</v>
+        <v>46036.5</v>
       </c>
       <c r="J61" s="3">
-        <v>46259.4474884259</v>
+        <v>46024.5900925926</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M61" s="3">
-        <v>46216.7097916667</v>
+        <v>46022.6836342593</v>
       </c>
       <c r="N61" s="3">
-        <v>46220.6264583333</v>
+        <v>46036.5</v>
       </c>
       <c r="O61" s="3"/>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>2587006</v>
+        <v>2512541</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I62" s="3">
-        <v>46217.7289699074</v>
+        <v>46036.5</v>
       </c>
       <c r="J62" s="3">
-        <v>46227.4549884259</v>
+        <v>46022.7128356481</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="M62" s="3">
-        <v>46213.7239236111</v>
+        <v>46022.6762615741</v>
       </c>
       <c r="N62" s="3">
-        <v>46217.7289699074</v>
+        <v>46036.5</v>
       </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>2586984</v>
+        <v>2506311</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I63" s="3">
-        <v>46295.7416550926</v>
+        <v>46013.7291666667</v>
       </c>
       <c r="J63" s="3">
-        <v>46273.4946180556</v>
+        <v>46013.461875</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M63" s="3">
-        <v>46213.6971527778</v>
+        <v>46001.5219328704</v>
       </c>
       <c r="N63" s="3">
-        <v>46295.7416550926</v>
+        <v>46013.7291666667</v>
       </c>
       <c r="O63" s="3"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2586910</v>
+        <v>2449811</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I64" s="3">
-        <v>46226.5833333333</v>
+        <v>45875.3688888889</v>
       </c>
       <c r="J64" s="3">
-        <v>46230.4194212963</v>
+        <v>45870.3628819444</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="M64" s="3">
-        <v>46213.6245833333</v>
+        <v>45862.6188888889</v>
       </c>
       <c r="N64" s="3">
-        <v>46226.5833333333</v>
+        <v>45875.3688888889</v>
       </c>
       <c r="O64" s="3"/>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2586651</v>
+        <v>2436707</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I65" s="3">
-        <v>46218.7157407407</v>
+        <v>45835.7284722222</v>
       </c>
       <c r="J65" s="3">
-        <v>46213.3824074074</v>
+        <v>46126.7436921296</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="M65" s="3">
-        <v>46213.3824074074</v>
+        <v>45828.8276273148</v>
       </c>
       <c r="N65" s="3">
-        <v>46218.7157407407</v>
+        <v>45835.7288773148</v>
       </c>
       <c r="O65" s="3"/>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>2586187</v>
+        <v>2617057</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="I66" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I66" s="3">
+        <v>46290.4043865741</v>
+      </c>
       <c r="J66" s="3">
-        <v>46219.3850231481</v>
+        <v>46286.4877199074</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M66" s="3">
-        <v>46211.7697337963</v>
-      </c>
-      <c r="N66" s="3"/>
+        <v>46286.4877199074</v>
+      </c>
+      <c r="N66" s="3">
+        <v>46290.4043865741</v>
+      </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>2585888</v>
+        <v>2615970</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H67" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I67" s="3">
-        <v>46217.4119907407</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="J67" s="3">
-        <v>46217.5003587963</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="K67" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="M67" s="3">
-        <v>46211.4953240741</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="N67" s="3">
-        <v>46290.75</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="O67" s="3"/>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>2585424</v>
+        <v>2615590</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E68" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="F68" s="0" t="s">
-        <v>39</v>
-      </c>
       <c r="G68" s="0" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I68" s="3">
-        <v>46223.3927199074</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="J68" s="3">
-        <v>46234.4964930556</v>
+        <v>46281.7496990741</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="M68" s="3">
-        <v>46210.6427199074</v>
+        <v>46281.6638425926</v>
       </c>
       <c r="N68" s="3">
-        <v>46290.75</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="O68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>2584638</v>
+        <v>2613026</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="I69" s="3">
-        <v>46213.4171527778</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="J69" s="3">
-        <v>46213.4090859607</v>
+        <v>46280.356624456</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="M69" s="3">
-        <v>46209.5016203704</v>
+        <v>46275.6895601852</v>
       </c>
       <c r="N69" s="3">
-        <v>46232.3874884259</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="O69" s="3"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>2584397</v>
+        <v>2611881</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I70" s="3">
-        <v>46212.6757175926</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="J70" s="3">
-        <v>46213.3741550926</v>
+        <v>46274.7389930556</v>
       </c>
       <c r="K70" s="0" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="M70" s="3">
-        <v>46209.3423842593</v>
+        <v>46273.7485648148</v>
       </c>
       <c r="N70" s="3">
-        <v>46212.6757175926</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="O70" s="3"/>
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>2584167</v>
+        <v>2611692</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I71" s="3">
-        <v>46246.7216435185</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="J71" s="3">
-        <v>46247.4396759259</v>
+        <v>46273.637278588</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="M71" s="3">
-        <v>46206.6383101852</v>
+        <v>46273.6013194444</v>
       </c>
       <c r="N71" s="3">
-        <v>46246.7216435185</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="O71" s="3"/>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>2583950</v>
+        <v>2611521</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I72" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I72" s="3">
+        <v>46279.3705439815</v>
+      </c>
       <c r="J72" s="3">
-        <v>46273.4100925926</v>
+        <v>46273.7182003819</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M72" s="3">
-        <v>46206.4623148148</v>
-      </c>
-      <c r="N72" s="3"/>
+        <v>46273.4538773148</v>
+      </c>
+      <c r="N72" s="3">
+        <v>46279.3705439815</v>
+      </c>
       <c r="O72" s="3"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>2583447</v>
+        <v>2610876</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D73" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I73" s="3">
-        <v>46245.6724189815</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="J73" s="3">
-        <v>46265.3645138889</v>
+        <v>46269.4406376505</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="M73" s="3">
-        <v>46205.5752083333</v>
+        <v>46269.4200925926</v>
       </c>
       <c r="N73" s="3">
-        <v>46245.6724189815</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="O73" s="3"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2583382</v>
+        <v>2610030</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>149</v>
+        <v>16</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I74" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I74" s="3">
+        <v>46274.6271990741</v>
+      </c>
       <c r="J74" s="3">
-        <v>46279.4689699074</v>
+        <v>46268.3853071412</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M74" s="3">
-        <v>46205.4905092593</v>
-      </c>
-      <c r="N74" s="3"/>
+        <v>46267.7105324074</v>
+      </c>
+      <c r="N74" s="3">
+        <v>46274.6271990741</v>
+      </c>
       <c r="O74" s="3"/>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2582452</v>
+        <v>2609551</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I75" s="3">
-        <v>46244.4166666667</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="J75" s="3">
-        <v>46204.7763078704</v>
+        <v>46267.355462963</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="M75" s="3">
-        <v>46203.8250810185</v>
+        <v>46267.355462963</v>
       </c>
       <c r="N75" s="3">
-        <v>46244.4166666667</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="O75" s="3"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>2582352</v>
+        <v>2607198</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E76" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I76" s="3">
-        <v>46244.340775463</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="J76" s="3">
-        <v>46204.7761805556</v>
+        <v>46273.6204976852</v>
       </c>
       <c r="K76" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="M76" s="3">
-        <v>46203.6741087963</v>
+        <v>46261.4379976852</v>
       </c>
       <c r="N76" s="3">
-        <v>46244.340775463</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="O76" s="3"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>2579299</v>
+        <v>2606003</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="E77" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I77" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I77" s="3">
+        <v>46265.3599537037</v>
+      </c>
       <c r="J77" s="3">
-        <v>46204.3277777778</v>
+        <v>46259.4993506944</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M77" s="3">
-        <v>46196.4165162037</v>
-      </c>
-      <c r="N77" s="3"/>
+        <v>46259.443287037</v>
+      </c>
+      <c r="N77" s="3">
+        <v>46290.75</v>
+      </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>2576326</v>
+        <v>2604500</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="E78" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I78" s="3">
-        <v>46192.7916666667</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="J78" s="3">
-        <v>46230.6812731481</v>
+        <v>46258.3485416667</v>
       </c>
       <c r="K78" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M78" s="3">
-        <v>46189.3995833333</v>
-      </c>
-      <c r="N78" s="3"/>
+        <v>46254.6270601852</v>
+      </c>
+      <c r="N78" s="3">
+        <v>46260.4812268519</v>
+      </c>
       <c r="O78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2574153</v>
+        <v>2603668</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I79" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I79" s="3">
+        <v>46259.3446296296</v>
+      </c>
       <c r="J79" s="3">
-        <v>46204.3218402778</v>
+        <v>46258.6426851852</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M79" s="3">
-        <v>46183.4711226852</v>
-      </c>
-      <c r="N79" s="3"/>
+        <v>46253.427962963</v>
+      </c>
+      <c r="N79" s="3">
+        <v>46290.75</v>
+      </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>2572707</v>
+        <v>2602388</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>158</v>
+        <v>32</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I80" s="3">
-        <v>46219.3964814815</v>
+        <v>46255.4166666667</v>
       </c>
       <c r="J80" s="3">
-        <v>46188.4629166667</v>
+        <v>46253.4900231482</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="M80" s="3">
-        <v>46178.7298148148</v>
+        <v>46251.5527777778</v>
       </c>
       <c r="N80" s="3">
-        <v>46219.3964814815</v>
+        <v>46255.4166666667</v>
       </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>2570274</v>
+        <v>2599732</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I81" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="I81" s="3">
+        <v>46251.4016203704</v>
+      </c>
       <c r="J81" s="3">
-        <v>46204.3220138889</v>
+        <v>46248.3419117245</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M81" s="3">
-        <v>46171.6563773148</v>
-      </c>
-      <c r="N81" s="3"/>
+        <v>46245.4849537037</v>
+      </c>
+      <c r="N81" s="3">
+        <v>46251.4016203704</v>
+      </c>
       <c r="O81" s="3"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>2562116</v>
+        <v>2598767</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="E82" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I82" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I82" s="3">
+        <v>46247.6666666667</v>
+      </c>
       <c r="J82" s="3">
-        <v>46160.7191666667</v>
+        <v>46245.6608564815</v>
       </c>
       <c r="K82" s="0" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M82" s="3">
-        <v>46154.3432638889</v>
-      </c>
-      <c r="N82" s="3"/>
+        <v>46241.757962963</v>
+      </c>
+      <c r="N82" s="3">
+        <v>46247.6666666667</v>
+      </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>2558553</v>
+        <v>2597524</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I83" s="3">
-        <v>46149.6895138889</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="J83" s="3">
-        <v>46154.5888773148</v>
+        <v>46259.4158333333</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="M83" s="3">
-        <v>46146.3561805556</v>
+        <v>46239.6925347222</v>
       </c>
       <c r="N83" s="3">
-        <v>46149.6895138889</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="O83" s="3"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>2556271</v>
+        <v>2597495</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I84" s="3">
-        <v>46141.4297453704</v>
+        <v>46252.3333333333</v>
       </c>
       <c r="J84" s="3">
-        <v>46139.9871412037</v>
+        <v>46241.6523302083</v>
       </c>
       <c r="K84" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="M84" s="3">
-        <v>46139.471412037</v>
+        <v>46239.6802199074</v>
       </c>
       <c r="N84" s="3">
-        <v>46141.4901157407</v>
-      </c>
-      <c r="O84" s="3"/>
+        <v>46245.5968865741</v>
+      </c>
+      <c r="O84" s="3">
+        <v>46252.3333333333</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>2556211</v>
+        <v>2595510</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I85" s="3">
-        <v>46150.6617476852</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="J85" s="3">
-        <v>46146.3663773148</v>
+        <v>46245.3667592593</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="M85" s="3">
-        <v>46139.4325810185</v>
+        <v>46234.6442939815</v>
       </c>
       <c r="N85" s="3">
-        <v>46150.6617476852</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="O85" s="3"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>2556029</v>
+        <v>2595497</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I86" s="3">
-        <v>46150.5</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="J86" s="3">
-        <v>46146.401875</v>
+        <v>46245.3669444444</v>
       </c>
       <c r="K86" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L86" s="0" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="M86" s="3">
-        <v>46138.757337963</v>
+        <v>46234.6436574074</v>
       </c>
       <c r="N86" s="3">
-        <v>46154.6616087963</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="O86" s="3"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>2554341</v>
+        <v>2593529</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I87" s="3">
-        <v>46136.3599768519</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="J87" s="3">
-        <v>46135.6585185185</v>
+        <v>46233.4404570255</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="M87" s="3">
-        <v>46134.4016435185</v>
+        <v>46231.6639930556</v>
       </c>
       <c r="N87" s="3">
-        <v>46136.3599768519</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>2547638</v>
+        <v>2592468</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I88" s="3">
-        <v>46150.3473611111</v>
+        <v>46237.6038657407</v>
       </c>
       <c r="J88" s="3">
-        <v>46119.5010069444</v>
+        <v>46240.6136738773</v>
       </c>
       <c r="K88" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="M88" s="3">
-        <v>46114.4931944444</v>
+        <v>46227.7107060185</v>
       </c>
       <c r="N88" s="3">
-        <v>46150.3473611111</v>
+        <v>46293.6033680556</v>
       </c>
       <c r="O88" s="3"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>2537054</v>
+        <v>2587849</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E89" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I89" s="3">
-        <v>46093.4339236111</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="J89" s="3">
-        <v>46090.3698263889</v>
+        <v>46237.9144806713</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="M89" s="3">
-        <v>46087.5797569444</v>
+        <v>46217.4506597222</v>
       </c>
       <c r="N89" s="3">
-        <v>46093.4339236111</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="O89" s="3"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2531696</v>
+        <v>2587585</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I90" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="I90" s="3">
+        <v>46220.6264583333</v>
+      </c>
       <c r="J90" s="3">
-        <v>46204.3216782407</v>
+        <v>46259.4474884259</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M90" s="3">
-        <v>46076.5833912037</v>
-      </c>
-      <c r="N90" s="3"/>
+        <v>46216.7097916667</v>
+      </c>
+      <c r="N90" s="3">
+        <v>46220.6264583333</v>
+      </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>2530739</v>
+        <v>2586984</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>174</v>
+        <v>55</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="I91" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="I91" s="3">
+        <v>46295.7416550926</v>
+      </c>
       <c r="J91" s="3">
-        <v>46218.6914940625</v>
+        <v>46273.4946180556</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M91" s="3">
-        <v>46072.6973148148</v>
-      </c>
-      <c r="N91" s="3"/>
+        <v>46213.6971527778</v>
+      </c>
+      <c r="N91" s="3">
+        <v>46295.7416550926</v>
+      </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>2529639</v>
+        <v>2586651</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>39</v>
+        <v>167</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I92" s="3">
-        <v>46083.3430902778</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="J92" s="3">
-        <v>46072.6891666667</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="M92" s="3">
-        <v>46069.5930902778</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="N92" s="3">
-        <v>46083.3430902778</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="O92" s="3"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>2529591</v>
+        <v>2585888</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I93" s="3">
-        <v>46108.5968055556</v>
+        <v>46217.4119907407</v>
       </c>
       <c r="J93" s="3">
-        <v>46126.6875</v>
+        <v>46217.5003587963</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="M93" s="3">
-        <v>46069.4509722222</v>
+        <v>46211.4953240741</v>
       </c>
       <c r="N93" s="3">
-        <v>46108.5968055556</v>
+        <v>46290.75</v>
       </c>
       <c r="O93" s="3"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>2528858</v>
+        <v>2584638</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="I94" s="3">
-        <v>46107.3861458333</v>
+        <v>46213.4171527778</v>
       </c>
       <c r="J94" s="3">
-        <v>46087.6277662037</v>
+        <v>46213.4090859607</v>
       </c>
       <c r="K94" s="0" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L94" s="0" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="M94" s="3">
-        <v>46065.7194791667</v>
+        <v>46209.5016203704</v>
       </c>
       <c r="N94" s="3">
-        <v>46107.3861458333</v>
+        <v>46232.3874884259</v>
       </c>
       <c r="O94" s="3"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>2525312</v>
+        <v>2584397</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I95" s="3">
-        <v>46070.5877314815</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="J95" s="3">
-        <v>46062.7587037037</v>
+        <v>46213.3741550926</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="M95" s="3">
-        <v>46058.3585648148</v>
+        <v>46209.3423842593</v>
       </c>
       <c r="N95" s="3">
-        <v>46070.5877314815</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="O95" s="3"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>2525272</v>
+        <v>2558553</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I96" s="3">
-        <v>46203.7916666667</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="J96" s="3">
-        <v>46126.7441782407</v>
+        <v>46154.5888773148</v>
       </c>
       <c r="K96" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L96" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M96" s="3">
-        <v>46058.2883101852</v>
-      </c>
-      <c r="N96" s="3"/>
+        <v>46146.3561805556</v>
+      </c>
+      <c r="N96" s="3">
+        <v>46149.6895138889</v>
+      </c>
       <c r="O96" s="3"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>2524577</v>
+        <v>2537054</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="I97" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="I97" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="J97" s="3">
-        <v>46267.4298180903</v>
+        <v>46090.3698263889</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="M97" s="3">
-        <v>46056.697349537</v>
-      </c>
-      <c r="N97" s="3"/>
+        <v>46087.5797569444</v>
+      </c>
+      <c r="N97" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="O97" s="3"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>2524373</v>
+        <v>2523635</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I98" s="3">
-        <v>46087.3854513889</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="J98" s="3">
-        <v>46056.6543865741</v>
+        <v>46055.6034837963</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="M98" s="3">
-        <v>46056.5937847222</v>
+        <v>46055.4997569444</v>
       </c>
       <c r="N98" s="3">
-        <v>46087.3854513889</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="O98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>2524062</v>
+        <v>2521079</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I99" s="3">
-        <v>46057.7412615741</v>
+        <v>46052.6666666667</v>
       </c>
       <c r="J99" s="3">
-        <v>46056.6210300926</v>
+        <v>46056.6197800926</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="M99" s="3">
-        <v>46056.3662615741</v>
+        <v>46048.7684490741</v>
       </c>
       <c r="N99" s="3">
-        <v>46057.7412615741</v>
+        <v>46061.6309722222</v>
       </c>
       <c r="O99" s="3"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>2523635</v>
+        <v>2519284</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I100" s="3">
-        <v>46059.4164236111</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="J100" s="3">
-        <v>46055.6034837963</v>
+        <v>46043.742337963</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L100" s="0" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="M100" s="3">
-        <v>46055.4997569444</v>
+        <v>46043.4816319444</v>
       </c>
       <c r="N100" s="3">
-        <v>46059.4164236111</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>2523602</v>
+        <v>2513117</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>47</v>
+        <v>177</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I101" s="3">
-        <v>46093.6246643519</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="J101" s="3">
-        <v>46056.5784027778</v>
+        <v>46028.3500347222</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="M101" s="3">
-        <v>46055.4788310185</v>
+        <v>46027.6381134259</v>
       </c>
       <c r="N101" s="3">
-        <v>46093.6246643519</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>2521645</v>
+        <v>2615871</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="D102" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E102" s="0" t="s">
-        <v>110</v>
-      </c>
       <c r="F102" s="0" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="I102" s="3">
-        <v>46062.5</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="J102" s="3">
-        <v>46050.3426763542</v>
+        <v>46286.3450115741</v>
       </c>
       <c r="K102" s="0" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="L102" s="0" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="M102" s="3">
-        <v>46049.7714236111</v>
-      </c>
-      <c r="N102" s="3"/>
+        <v>46282.4440856481</v>
+      </c>
+      <c r="N102" s="3">
+        <v>46286.4024189815</v>
+      </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>2521079</v>
+        <v>2614334</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="D103" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E103" s="0" t="s">
-        <v>61</v>
-      </c>
       <c r="F103" s="0" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I103" s="3">
-        <v>46052.6666666667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="J103" s="3">
-        <v>46056.6197800926</v>
+        <v>46283.4291666667</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="M103" s="3">
-        <v>46048.7684490741</v>
+        <v>46279.6749305556</v>
       </c>
       <c r="N103" s="3">
-        <v>46061.6309722222</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>2520048</v>
+        <v>2611552</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>174</v>
+        <v>33</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I104" s="3">
-        <v>46057.5</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="J104" s="3">
-        <v>46052.5774305556</v>
+        <v>46273.5743171296</v>
       </c>
       <c r="K104" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="M104" s="3">
-        <v>46045.3325578704</v>
+        <v>46273.474375</v>
       </c>
       <c r="N104" s="3">
-        <v>46057.5</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="O104" s="3"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>2519904</v>
+        <v>2611539</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>174</v>
+        <v>33</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I105" s="3">
-        <v>46084.7217939815</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="J105" s="3">
-        <v>46044.7413888889</v>
+        <v>46274.3607986111</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="M105" s="3">
-        <v>46044.6384606482</v>
+        <v>46273.464375</v>
       </c>
       <c r="N105" s="3">
-        <v>46084.7217939815</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="O105" s="3"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>2519523</v>
+        <v>2593490</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I106" s="3">
-        <v>46076.5902777778</v>
+        <v>46239.6748032407</v>
       </c>
       <c r="J106" s="3">
-        <v>46048.4589814815</v>
+        <v>46253.4905324074</v>
       </c>
       <c r="K106" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L106" s="0" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="M106" s="3">
-        <v>46043.7362847222</v>
+        <v>46231.6518865741</v>
       </c>
       <c r="N106" s="3">
-        <v>46077.380775463</v>
-      </c>
-      <c r="O106" s="3"/>
+        <v>46239.6748032407</v>
+      </c>
+      <c r="O106" s="3">
+        <v>46234.48125</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>2519383</v>
+        <v>2587713</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E107" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="F107" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F107" s="0" t="s">
-        <v>47</v>
-      </c>
       <c r="G107" s="0" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I107" s="3">
-        <v>46076.399224537</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="J107" s="3">
-        <v>46048.4599305556</v>
+        <v>46230.4199074074</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="M107" s="3">
-        <v>46043.6075578704</v>
+        <v>46217.3658680556</v>
       </c>
       <c r="N107" s="3">
-        <v>46076.399224537</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="O107" s="3"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>2519284</v>
+        <v>2587006</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F108" s="0" t="s">
         <v>18</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I108" s="3">
-        <v>46049.3982986111</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="J108" s="3">
-        <v>46043.742337963</v>
+        <v>46227.4549884259</v>
       </c>
       <c r="K108" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L108" s="0" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="M108" s="3">
-        <v>46043.4816319444</v>
+        <v>46213.7239236111</v>
       </c>
       <c r="N108" s="3">
-        <v>46049.3982986111</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>2518650</v>
+        <v>2586910</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>18</v>
+        <v>169</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I109" s="3">
-        <v>46072.3536921296</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="J109" s="3">
-        <v>46043.8185648148</v>
+        <v>46230.4194212963</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="M109" s="3">
-        <v>46042.3536921296</v>
+        <v>46213.6245833333</v>
       </c>
       <c r="N109" s="3">
-        <v>46080.437025463</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="O109" s="3"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>2513117</v>
+        <v>2556271</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E110" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I110" s="3">
-        <v>46031.4922800926</v>
+        <v>46141.4297453704</v>
       </c>
       <c r="J110" s="3">
-        <v>46028.3500347222</v>
+        <v>46139.9871412037</v>
       </c>
       <c r="K110" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L110" s="0" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="M110" s="3">
-        <v>46027.6381134259</v>
+        <v>46139.471412037</v>
       </c>
       <c r="N110" s="3">
-        <v>46031.4922800926</v>
+        <v>46141.4901157407</v>
       </c>
       <c r="O110" s="3"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>2512883</v>
+        <v>2554341</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="D111" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E111" s="0" t="s">
-        <v>61</v>
-      </c>
       <c r="F111" s="0" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I111" s="3">
-        <v>46037.6340972222</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="J111" s="3">
-        <v>46129.4199421296</v>
+        <v>46135.6585185185</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="M111" s="3">
-        <v>46027.4049305556</v>
+        <v>46134.4016435185</v>
       </c>
       <c r="N111" s="3">
-        <v>46141.6335300926</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="O111" s="3"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>2512542</v>
+        <v>2524062</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I112" s="3">
-        <v>46036.5</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="J112" s="3">
-        <v>46024.5900925926</v>
+        <v>46056.6210300926</v>
       </c>
       <c r="K112" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="M112" s="3">
-        <v>46022.6836342593</v>
+        <v>46056.3662615741</v>
       </c>
       <c r="N112" s="3">
-        <v>46036.5</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="O112" s="3"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>2512541</v>
+        <v>2607413</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>24</v>
+        <v>190</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I113" s="3">
-        <v>46036.5</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="I113" s="3"/>
       <c r="J113" s="3">
-        <v>46022.7128356481</v>
+        <v>46266.569212963</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>42</v>
+        <v>193</v>
       </c>
       <c r="M113" s="3">
-        <v>46022.6762615741</v>
-      </c>
-      <c r="N113" s="3">
-        <v>46036.5</v>
-      </c>
+        <v>46261.6163888889</v>
+      </c>
+      <c r="N113" s="3"/>
       <c r="O113" s="3"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>2509014</v>
+        <v>2601999</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I114" s="3">
-        <v>46044.7250578704</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="I114" s="3"/>
       <c r="J114" s="3">
-        <v>46022.6138541667</v>
+        <v>46266.6188194444</v>
       </c>
       <c r="K114" s="0" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="L114" s="0" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="M114" s="3">
-        <v>46008.454224537</v>
-      </c>
-      <c r="N114" s="3">
-        <v>46045.4708564815</v>
-      </c>
+        <v>46248.7351273148</v>
+      </c>
+      <c r="N114" s="3"/>
       <c r="O114" s="3"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>2506714</v>
+        <v>2600778</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="F115" s="0" t="s">
         <v>110</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I115" s="3">
-        <v>46038.7073032407</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="I115" s="3"/>
       <c r="J115" s="3">
-        <v>46044.7372337963</v>
+        <v>46274.3780324074</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="M115" s="3">
-        <v>46002.4364699074</v>
-      </c>
-      <c r="N115" s="3">
-        <v>46038.7073032407</v>
-      </c>
+        <v>46246.7171759259</v>
+      </c>
+      <c r="N115" s="3"/>
       <c r="O115" s="3"/>
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>2506599</v>
+        <v>2597515</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I116" s="3">
-        <v>46037.61375</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="J116" s="3">
-        <v>46052.3252083333</v>
+        <v>46261.4097453704</v>
       </c>
       <c r="K116" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L116" s="0" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="M116" s="3">
-        <v>46002.3429166667</v>
+        <v>46239.6856134259</v>
       </c>
       <c r="N116" s="3">
-        <v>46037.61375</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="O116" s="3"/>
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>2506311</v>
+        <v>2593216</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>203</v>
+        <v>55</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>203</v>
+        <v>55</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I117" s="3">
-        <v>46013.7291666667</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I117" s="3"/>
       <c r="J117" s="3">
-        <v>46013.461875</v>
+        <v>46231.4047453704</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>42</v>
+        <v>193</v>
       </c>
       <c r="M117" s="3">
-        <v>46001.5219328704</v>
-      </c>
-      <c r="N117" s="3">
-        <v>46013.7291666667</v>
-      </c>
+        <v>46231.4011111111</v>
+      </c>
+      <c r="N117" s="3"/>
       <c r="O117" s="3"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>2506102</v>
+        <v>2588025</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>46</v>
+        <v>203</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>205</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="I118" s="3"/>
       <c r="J118" s="3">
-        <v>46241.5032638889</v>
+        <v>46267.5903356482</v>
       </c>
       <c r="K118" s="0" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="L118" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M118" s="3">
-        <v>46001.3800578704</v>
+        <v>46217.612962963</v>
       </c>
       <c r="N118" s="3"/>
       <c r="O118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>2502589</v>
+        <v>2586187</v>
       </c>
       <c r="B119" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D119" s="0" t="s">
         <v>206</v>
       </c>
-      <c r="C119" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="D119" s="0" t="s">
-        <v>24</v>
-      </c>
       <c r="E119" s="0" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>207</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I119" s="3">
-        <v>46029.6634375</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="I119" s="3"/>
       <c r="J119" s="3">
-        <v>46014.6931018519</v>
+        <v>46219.3850231481</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="M119" s="3">
-        <v>45993.3791087963</v>
-      </c>
-      <c r="N119" s="3">
-        <v>46029.6634375</v>
-      </c>
+        <v>46211.7697337963</v>
+      </c>
+      <c r="N119" s="3"/>
       <c r="O119" s="3"/>
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <v>2502438</v>
+        <v>2583950</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>174</v>
+        <v>38</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>24</v>
+        <v>197</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>208</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I120" s="3">
-        <v>46037.3801388889</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I120" s="3"/>
       <c r="J120" s="3">
-        <v>45996.4823032407</v>
+        <v>46273.4100925926</v>
       </c>
       <c r="K120" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L120" s="0" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="M120" s="3">
-        <v>45992.7134722222</v>
-      </c>
-      <c r="N120" s="3">
-        <v>46037.3801388889</v>
-      </c>
+        <v>46206.4623148148</v>
+      </c>
+      <c r="N120" s="3"/>
       <c r="O120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <v>2501349</v>
+        <v>2583382</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>173</v>
+        <v>15</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="E121" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>209</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I121" s="3">
-        <v>46069.7381944444</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="I121" s="3"/>
       <c r="J121" s="3">
-        <v>46069.3651388889</v>
+        <v>46279.4689699074</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="M121" s="3">
-        <v>45989.0365856482</v>
-      </c>
-      <c r="N121" s="3">
-        <v>46069.7381944444</v>
-      </c>
+        <v>46205.4905092593</v>
+      </c>
+      <c r="N121" s="3"/>
       <c r="O121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <v>2500635</v>
+        <v>2579299</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>24</v>
+        <v>197</v>
       </c>
       <c r="E122" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I122" s="3">
-        <v>46024.4633796296</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I122" s="3"/>
       <c r="J122" s="3">
-        <v>46027.3611111111</v>
+        <v>46204.3277777778</v>
       </c>
       <c r="K122" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L122" s="0" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="M122" s="3">
-        <v>45987.671712963</v>
-      </c>
-      <c r="N122" s="3">
-        <v>46024.4633796296</v>
-      </c>
+        <v>46196.4165162037</v>
+      </c>
+      <c r="N122" s="3"/>
       <c r="O122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <v>2498066</v>
+        <v>2576326</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="E123" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I123" s="3">
-        <v>46073.7916666667</v>
+        <v>46192.7916666667</v>
       </c>
       <c r="J123" s="3">
-        <v>46126.6953240741</v>
+        <v>46230.6812731481</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="M123" s="3">
-        <v>45979.750162037</v>
+        <v>46189.3995833333</v>
       </c>
       <c r="N123" s="3"/>
       <c r="O123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <v>2494282</v>
+        <v>2574153</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="E124" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I124" s="3">
-        <v>45986.48125</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I124" s="3"/>
       <c r="J124" s="3">
-        <v>45988.567025463</v>
+        <v>46204.3218402778</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L124" s="0" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="M124" s="3">
-        <v>45971.4792824074</v>
-      </c>
-      <c r="N124" s="3">
-        <v>45986.4815625</v>
-      </c>
+        <v>46183.4711226852</v>
+      </c>
+      <c r="N124" s="3"/>
       <c r="O124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <v>2494179</v>
+        <v>2570274</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>109</v>
+        <v>215</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="D125" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="E125" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F125" s="0" t="s">
         <v>110</v>
-      </c>
-      <c r="E125" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="F125" s="0" t="s">
-        <v>215</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>216</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="I125" s="3">
-        <v>46002.675775463</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I125" s="3"/>
       <c r="J125" s="3">
-        <v>46044.7370486111</v>
+        <v>46204.3220138889</v>
       </c>
       <c r="K125" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="M125" s="3">
-        <v>45971.4049421296</v>
-      </c>
-      <c r="N125" s="3">
-        <v>46002.675775463</v>
-      </c>
+        <v>46171.6563773148</v>
+      </c>
+      <c r="N125" s="3"/>
       <c r="O125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <v>2490911</v>
+        <v>2562116</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E126" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="I126" s="3"/>
       <c r="J126" s="3">
-        <v>46182.7633796296</v>
+        <v>46160.7191666667</v>
       </c>
       <c r="K126" s="0" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M126" s="3">
-        <v>45961.5760300926</v>
+        <v>46154.3432638889</v>
       </c>
       <c r="N126" s="3"/>
       <c r="O126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <v>2490185</v>
+        <v>2531696</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="E127" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I127" s="3">
-        <v>46203.7916666667</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I127" s="3"/>
       <c r="J127" s="3">
-        <v>46051.4836111111</v>
+        <v>46204.3216782407</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M127" s="3">
-        <v>45960.3928819444</v>
+        <v>46076.5833912037</v>
       </c>
       <c r="N127" s="3"/>
       <c r="O127" s="3"/>
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <v>2489016</v>
+        <v>2530739</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>220</v>
+        <v>17</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>215</v>
+        <v>99</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="I128" s="3"/>
       <c r="J128" s="3">
-        <v>45958.3906481481</v>
+        <v>46218.6914940625</v>
       </c>
       <c r="K128" s="0" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="L128" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M128" s="3">
-        <v>45957.7253009259</v>
+        <v>46072.6973148148</v>
       </c>
       <c r="N128" s="3"/>
       <c r="O128" s="3"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <v>2485386</v>
+        <v>2525272</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>96</v>
+        <v>220</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>96</v>
+        <v>220</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E129" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>222</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="I129" s="3">
-        <v>46386.7916666667</v>
+        <v>46203.7916666667</v>
       </c>
       <c r="J129" s="3">
-        <v>46182.7639236111</v>
+        <v>46126.7441782407</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M129" s="3">
-        <v>45947.7000115741</v>
+        <v>46058.2883101852</v>
       </c>
       <c r="N129" s="3"/>
       <c r="O129" s="3"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <v>2483420</v>
+        <v>2524577</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>223</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="I130" s="3"/>
       <c r="J130" s="3">
-        <v>46140.3843518519</v>
+        <v>46267.4298180903</v>
       </c>
       <c r="K130" s="0" t="s">
-        <v>144</v>
+        <v>192</v>
       </c>
       <c r="L130" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M130" s="3">
-        <v>45944.6603819444</v>
+        <v>46056.697349537</v>
       </c>
       <c r="N130" s="3"/>
       <c r="O130" s="3"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <v>2474606</v>
+        <v>2506102</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I131" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I131" s="3"/>
       <c r="J131" s="3">
-        <v>45966.4450925926</v>
+        <v>46241.5032638889</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="M131" s="3">
-        <v>45924.4486921296</v>
-      </c>
-      <c r="N131" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>46001.3800578704</v>
+      </c>
+      <c r="N131" s="3"/>
       <c r="O131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <v>2470122</v>
+        <v>2490911</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>225</v>
+        <v>55</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>225</v>
+        <v>55</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E132" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>227</v>
+        <v>109</v>
       </c>
       <c r="I132" s="3"/>
       <c r="J132" s="3">
-        <v>46204.3270601852</v>
+        <v>46182.7633796296</v>
       </c>
       <c r="K132" s="0" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L132" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M132" s="3">
-        <v>45912.5572222222</v>
+        <v>45961.5760300926</v>
       </c>
       <c r="N132" s="3"/>
       <c r="O132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <v>2463515</v>
+        <v>2490185</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E133" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I133" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="I133" s="3">
+        <v>46203.7916666667</v>
+      </c>
       <c r="J133" s="3">
-        <v>45910.4755555556</v>
+        <v>46051.4836111111</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M133" s="3">
-        <v>45897.4218865741</v>
+        <v>45960.3928819444</v>
       </c>
       <c r="N133" s="3"/>
       <c r="O133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <v>2461703</v>
+        <v>2489016</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>230</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>227</v>
+        <v>29</v>
       </c>
       <c r="I134" s="3"/>
       <c r="J134" s="3">
-        <v>46003.3706828704</v>
+        <v>45958.3906481481</v>
       </c>
       <c r="K134" s="0" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="L134" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M134" s="3">
-        <v>45894.4525347222</v>
+        <v>45957.7253009259</v>
       </c>
       <c r="N134" s="3"/>
       <c r="O134" s="3"/>
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <v>2459339</v>
+        <v>2485386</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E135" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>231</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="I135" s="3"/>
+        <v>109</v>
+      </c>
+      <c r="I135" s="3">
+        <v>46386.7916666667</v>
+      </c>
       <c r="J135" s="3">
-        <v>46140.3839930556</v>
+        <v>46182.7639236111</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M135" s="3">
-        <v>45887.7442361111</v>
+        <v>45947.7000115741</v>
       </c>
       <c r="N135" s="3"/>
       <c r="O135" s="3"/>
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <v>2456538</v>
+        <v>2483420</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>79</v>
+        <v>226</v>
       </c>
       <c r="E136" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>232</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="I136" s="3"/>
       <c r="J136" s="3">
-        <v>46126.7428356481</v>
+        <v>46140.3843518519</v>
       </c>
       <c r="K136" s="0" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L136" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M136" s="3">
-        <v>45880.6643055556</v>
+        <v>45944.6603819444</v>
       </c>
       <c r="N136" s="3"/>
       <c r="O136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <v>2449811</v>
+        <v>2470122</v>
       </c>
       <c r="B137" s="0" t="s">
         <v>233</v>
@@ -6843,10 +6863,10 @@
         <v>233</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>110</v>
+        <v>226</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="F137" s="0" t="s">
         <v>110</v>
@@ -6855,200 +6875,228 @@
         <v>234</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I137" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="I137" s="3"/>
       <c r="J137" s="3">
-        <v>45870.3628819444</v>
+        <v>46204.3270601852</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>42</v>
+        <v>193</v>
       </c>
       <c r="M137" s="3">
-        <v>45862.6188888889</v>
-      </c>
-      <c r="N137" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>45912.5572222222</v>
+      </c>
+      <c r="N137" s="3"/>
       <c r="O137" s="3"/>
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <v>2442028</v>
+        <v>2463515</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>235</v>
+        <v>38</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>235</v>
+        <v>38</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E138" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I138" s="3"/>
       <c r="J138" s="3">
-        <v>46126.7431134259</v>
+        <v>45910.4755555556</v>
       </c>
       <c r="K138" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L138" s="0" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="M138" s="3">
-        <v>45842.317025463</v>
+        <v>45897.4218865741</v>
       </c>
       <c r="N138" s="3"/>
       <c r="O138" s="3"/>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>2439691</v>
+        <v>2461703</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>25</v>
+        <v>72</v>
+      </c>
+      <c r="F139" s="0" t="s">
+        <v>73</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I139" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="I139" s="3"/>
       <c r="J139" s="3">
-        <v>45838.6211342593</v>
+        <v>46003.3706828704</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="M139" s="3">
-        <v>45838.3761921296</v>
-      </c>
-      <c r="N139" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>45894.4525347222</v>
+      </c>
+      <c r="N139" s="3"/>
       <c r="O139" s="3"/>
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>2437239</v>
+        <v>2459339</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>238</v>
+        <v>38</v>
       </c>
       <c r="C140" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D140" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="E140" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F140" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="G140" s="0" t="s">
         <v>239</v>
       </c>
-      <c r="D140" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E140" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="F140" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="G140" s="0" t="s">
-        <v>240</v>
-      </c>
       <c r="H140" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I140" s="3">
-        <v>45870.3600462963</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="I140" s="3"/>
       <c r="J140" s="3">
-        <v>45841.7026091435</v>
+        <v>46140.3839930556</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L140" s="0" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="M140" s="3">
-        <v>45831.6933796296</v>
-      </c>
-      <c r="N140" s="3">
-        <v>45870.3600462963</v>
-      </c>
+        <v>45887.7442361111</v>
+      </c>
+      <c r="N140" s="3"/>
       <c r="O140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>2436707</v>
+        <v>2456538</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>233</v>
+        <v>38</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>233</v>
+        <v>38</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="E141" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="G141" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="H141" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="I141" s="3"/>
+      <c r="J141" s="3">
+        <v>46126.7428356481</v>
+      </c>
+      <c r="K141" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="L141" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="M141" s="3">
+        <v>45880.6643055556</v>
+      </c>
+      <c r="N141" s="3"/>
+      <c r="O141" s="3"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2">
+        <v>2442028</v>
+      </c>
+      <c r="B142" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="H141" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I141" s="3">
-        <v>45835.7284722222</v>
-      </c>
-      <c r="J141" s="3">
-        <v>46126.7436921296</v>
-      </c>
-      <c r="K141" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="L141" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="M141" s="3">
-        <v>45828.8276273148</v>
-      </c>
-      <c r="N141" s="3">
-        <v>45835.7288773148</v>
-      </c>
-      <c r="O141" s="3"/>
+      <c r="C142" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="D142" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F142" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="G142" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="H142" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="I142" s="3"/>
+      <c r="J142" s="3">
+        <v>46126.7431134259</v>
+      </c>
+      <c r="K142" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="L142" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="M142" s="3">
+        <v>45842.317025463</v>
+      </c>
+      <c r="N142" s="3"/>
+      <c r="O142" s="3"/>
     </row>
   </sheetData>
   <headerFooter/>

--- a/Solicitacoes.xlsx
+++ b/Solicitacoes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
   <si>
     <t>Protocolo</t>
   </si>
@@ -59,13 +59,73 @@
     <t>Prazo desejado</t>
   </si>
   <si>
+    <t>COMPESAPREV.JULIA</t>
+  </si>
+  <si>
+    <t>CORRECAO</t>
+  </si>
+  <si>
+    <t>BCON</t>
+  </si>
+  <si>
+    <t>Faturamento</t>
+  </si>
+  <si>
+    <t>Guia não disponível para execução de eventos por outros prestadores</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Suporte nível II</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Plataforma Lean</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
+    <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
+  </si>
+  <si>
+    <t>HELPDESK - CUIDAR</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
+  </si>
+  <si>
+    <t>Julia Albertim</t>
+  </si>
+  <si>
+    <t>CONECTA - XML não sai do estado de "Em Processamento"</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>ANA.GOLDIM</t>
   </si>
   <si>
-    <t>HELPDESK - CUIDAR</t>
-  </si>
-  <si>
-    <t>AG</t>
+    <t>Autorização</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- Conecta- Erro na solicitação dos procedimentos.</t>
+  </si>
+  <si>
+    <t>Homologando</t>
+  </si>
+  <si>
+    <t>Cliente</t>
   </si>
   <si>
     <t>Agendamentos</t>
@@ -74,58 +134,220 @@
     <t>COMPESAPREV- AG- AGENDAMENTO com erro Módulo de Regulação: Enviar mensagens Lean e Integracao Iris</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
-    <t>Suporte nível II</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
-    <t>CORRECAO</t>
-  </si>
-  <si>
-    <t>BCON</t>
-  </si>
-  <si>
-    <t>Autorização</t>
+    <t>CONECTA - Erro na execução de guias | pop-up e bloqueio por biometria</t>
+  </si>
+  <si>
+    <t>Adm Operadora</t>
+  </si>
+  <si>
+    <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
+  </si>
+  <si>
+    <t>Verificando</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Prestadores</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO NOME PRESTADOR</t>
+  </si>
+  <si>
+    <t>Liberado para cliente</t>
+  </si>
+  <si>
+    <t>Configurações do Sistema</t>
+  </si>
+  <si>
+    <t>Ajuste no tempo de sessão ativa (timeout) do sistema Lean.</t>
+  </si>
+  <si>
+    <t>ALEXIA.SANTOS</t>
+  </si>
+  <si>
+    <t>Controle Financeiro</t>
+  </si>
+  <si>
+    <t>Correção – CompesaPrev – Erro de Geração do Código de Barras e Linha Digitável</t>
   </si>
   <si>
     <t>COMPESAPREV-CONECTA- Eventos negados, com recibo autorizado</t>
   </si>
   <si>
-    <t>Verificando</t>
+    <t>COMPESAPREV.NIECIA</t>
+  </si>
+  <si>
+    <t>Niécia Morais</t>
+  </si>
+  <si>
+    <t>Processamento de Contas</t>
+  </si>
+  <si>
+    <t>Erro no faturamento de pagamentos prestadores</t>
+  </si>
+  <si>
+    <t>Dúvida sobre o local para salvar/exportar a Guia Executada no Portal do Prestador</t>
+  </si>
+  <si>
+    <t>MOBE</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>Histórico financeiro sem a informação individual de todos os beneficiários</t>
+  </si>
+  <si>
+    <t>PORTAL</t>
+  </si>
+  <si>
+    <t>Portal não envia e-mails, recuperação de senha e processos parados desde 04/09</t>
   </si>
   <si>
     <t>COMPESAPREV- AG- PROD- Agendamento Regulacao travado</t>
   </si>
   <si>
-    <t>Liberado para cliente</t>
-  </si>
-  <si>
-    <t>Resolvido</t>
+    <t>Processos</t>
+  </si>
+  <si>
+    <t>Lean / AG (Integração e guias travadas)</t>
+  </si>
+  <si>
+    <t>Beneficiários</t>
+  </si>
+  <si>
+    <t>Erro de divergência de cadastro entre o AG e o LEAN</t>
+  </si>
+  <si>
+    <t>MOBE | Erro no servidor ao tentar logar.</t>
+  </si>
+  <si>
+    <t>Extrato de Utilização com valores de coparticipações sem a limitação de PF e antes do faturamento ser concluído</t>
+  </si>
+  <si>
+    <t>Erro ao buscar documento/relatório na Consulta de Autorizações (App)</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>Compesaprev- Conecta- Erro na autorização</t>
   </si>
   <si>
-    <t>COMPESAPREV.JULIA</t>
-  </si>
-  <si>
-    <t>Julia Albertim</t>
-  </si>
-  <si>
-    <t>Adm Operadora</t>
+    <t>CENTRAL ATENDIMENTO</t>
+  </si>
+  <si>
+    <t>Transações</t>
+  </si>
+  <si>
+    <t>Falha na integração entre AG Web e Central de Atendimento</t>
+  </si>
+  <si>
+    <t>Ajuste de permissões e perfis de acesso no AG - Papel de Desenvolvedor aplicado a todos os usuários</t>
+  </si>
+  <si>
+    <t>Inconsistência no cálculo do prazo em horas úteis</t>
+  </si>
+  <si>
+    <t>Alinhamento sobre parametrização de críticas/motivos de negação automáticos (AG / Conecta)</t>
+  </si>
+  <si>
+    <t>APOIO DE NEGÓCIO</t>
+  </si>
+  <si>
+    <t>Erro na de geração do “Nosso Número” no boleto</t>
+  </si>
+  <si>
+    <t>Versão futura</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>EVIDENCIAS DO PROBLEMA NO RELATORIO DE PREVIA DE PAGAMENTO</t>
+  </si>
+  <si>
+    <t>COMPESAPREV – AG: Duplicidade dos eventos solicitados no e-mail do Beneficiario</t>
   </si>
   <si>
     <t>Impossibilidade de Auditoria Geral de Biometria na Execução de Eventos (Exigência de Filtro por Prestador)</t>
   </si>
   <si>
-    <t>Homologando</t>
-  </si>
-  <si>
-    <t>Cliente</t>
+    <t>Atualização do AG em Produção - Release 3.65.19 (Ambiente e WTS)</t>
+  </si>
+  <si>
+    <t>Regulação Médica</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- LEAN- RELATORIO- Regulações Vencidas</t>
+  </si>
+  <si>
+    <t>Esqueci minha senha APP</t>
+  </si>
+  <si>
+    <t>MELHORIA</t>
+  </si>
+  <si>
+    <t>CompesaPrev – Erro na Emissão de Boleto</t>
+  </si>
+  <si>
+    <t>Aguardando análise (negócio)</t>
+  </si>
+  <si>
+    <t>IMPL NAO COBRADA</t>
+  </si>
+  <si>
+    <t>Compesaprev - Complemento II SMS 2531696 – Regra para cálculo de coparticipação</t>
+  </si>
+  <si>
+    <t>Analisando (negócio)</t>
+  </si>
+  <si>
+    <t>ANA.BRASILEIRO</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Painel de sincronização - PLANOS</t>
+  </si>
+  <si>
+    <t>Históricos Atendimentos</t>
+  </si>
+  <si>
+    <t>Não está sendo possível SOLUCIONAR DEMANDAS</t>
+  </si>
+  <si>
+    <t>Compesaprev- Lean- Erro log integração</t>
+  </si>
+  <si>
+    <t>Cancelado</t>
+  </si>
+  <si>
+    <t>Daniel Serafim</t>
+  </si>
+  <si>
+    <t>COMPESAPREV - SISTEMA NÃO ESTÁ CONSIDERANDO LIMITADOR PF PARA REEMBOLSO</t>
+  </si>
+  <si>
+    <t>COMPESAPREV.DANIEL</t>
+  </si>
+  <si>
+    <t>COMPESPREV - Arquivo retorno com erro na importação</t>
+  </si>
+  <si>
+    <t>Julia Flora Ferreira de Albertim</t>
+  </si>
+  <si>
+    <t>Não consigo vizualizar o que estão pedindo para ALTERAR quando solicitam alteração cadastral de E-MAIL</t>
+  </si>
+  <si>
+    <t>Os detalhes da CARTEIRINHA não está aparecendo para alguns beneficiários</t>
+  </si>
+  <si>
+    <t>Acesso rede credenciada com perfil de DEPENDENTE não traz resultados.</t>
   </si>
   <si>
     <t>MARIANA.HILA</t>
@@ -137,130 +359,265 @@
     <t>CompesaPrev - criar usuario WTS para Niecia</t>
   </si>
   <si>
+    <t>Liberação de Relatório Geral de Execução e Biometria / Correção de Bloqueios</t>
+  </si>
+  <si>
+    <t>Compesaprev-Lean- Erro na inclusão de procedimento- OPME</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Solicito atualização do Portal para release 2.2.22 para PRODUÇÃO</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Solicito atualização do Portal para release 2.2.22 para HOMOLOGAÇÃO</t>
+  </si>
+  <si>
+    <t>Acesso e busca na rede credenciada</t>
+  </si>
+  <si>
     <t>LUCAS.FIRMAN</t>
   </si>
   <si>
+    <t>Falha ao utilizar o campo Ignorar críticas de XML no Conecta</t>
+  </si>
+  <si>
+    <t>COMPREPREV_ PROBLEMA RELACIONADO A REDE DE ATENDIMENTO</t>
+  </si>
+  <si>
+    <t>Atendimento</t>
+  </si>
+  <si>
+    <t>Compesaprev- AG-Produção: Erro na autorização</t>
+  </si>
+  <si>
+    <t>Compesaprev | AG TGE – Duplicidade de procedimento com o mesmo código</t>
+  </si>
+  <si>
+    <t>Valor Autorizado Não Exibido no Recibo de Atendimento</t>
+  </si>
+  <si>
     <t>Lista de Credenciados Ativos Conecta Compesa</t>
   </si>
   <si>
+    <t>Falha ao ativar/desativar críticas de XML no Conecta</t>
+  </si>
+  <si>
+    <t>EDITAL NEGOCIACAO</t>
+  </si>
+  <si>
+    <t>MOBILE IRIS</t>
+  </si>
+  <si>
+    <t>App</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Implantação Mobile Íris</t>
+  </si>
+  <si>
+    <t>COMPESAPREV – AG - Produção: Falha na Integração das Guias para o Lean</t>
+  </si>
+  <si>
+    <t>COMPESAPREV – Lean Produção: Falha no Agendamento da Tarefa de Finalização</t>
+  </si>
+  <si>
+    <t>COMPESAPREV – Conecta Produção: Eventos não são localizados para inclusão em guia</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- AG- REGULAÇÃO- Agendamento travado</t>
+  </si>
+  <si>
+    <t>COMPESAPREV - Solicitação de atualização cadastral pelo Portal</t>
+  </si>
+  <si>
+    <t>Integrações</t>
+  </si>
+  <si>
+    <t>Compesaprev- Prod- Erro na fila de integraçao guias de prorrogação</t>
+  </si>
+  <si>
+    <t>Legal</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Rede de Atendimento - MOBILE</t>
+  </si>
+  <si>
+    <t>SERVIÇOS PONTUAIS</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- IRIS-Produção</t>
+  </si>
+  <si>
+    <t>COMPESAPREV-LEAN-PROD- Erro ao substituir diária — Enum inválido (TissTabelaProcedimentos)</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Cadastro de Cooperados</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- LEAN- PROD- Erro na finalização das regulacoes</t>
+  </si>
+  <si>
+    <t>Compesaprev- Lean- Produção- Erro</t>
+  </si>
+  <si>
     <t xml:space="preserve">COMPESAPREV- CONECTA- PROD:  Prestadores nao conseguem buscar o evento proprio</t>
   </si>
   <si>
+    <t>CompesaPrev - Alteração de logo para Mobile</t>
+  </si>
+  <si>
     <t>COMPESAPREV - CONECTA- PROD: Erro no arquivo excel relatorio</t>
   </si>
   <si>
-    <t>Plataforma Lean</t>
-  </si>
-  <si>
-    <t>Processos</t>
+    <t>QUALIDADE</t>
+  </si>
+  <si>
+    <t>COMPESAPREV-AG-PROD- Erro na inclusão de eventos no sistema AG</t>
+  </si>
+  <si>
+    <t>Aguardando detalhamento</t>
   </si>
   <si>
     <t>COMPESAPREV- LEAN- PROD- Agendamento travado</t>
   </si>
   <si>
-    <t>ADM</t>
-  </si>
-  <si>
     <t>COMPESAPREV- CONECTA- PROD -Publicação Webservices 4.02.00</t>
   </si>
   <si>
+    <t>VINICIUS.GENEROSO</t>
+  </si>
+  <si>
+    <t>Alteração da busca de limite de PF mensal por faixa salarial exclusivamente do titular</t>
+  </si>
+  <si>
+    <t>Complemento SMS 2531696 – Regra para cálculo de coparticipação</t>
+  </si>
+  <si>
+    <t>Complemento SMS 2470122 – Regra para cálculo de mensalidade</t>
+  </si>
+  <si>
     <t>NATALYA.GONCALVES</t>
   </si>
   <si>
-    <t>PORTAL</t>
-  </si>
-  <si>
     <t>Gestor</t>
   </si>
   <si>
     <t>Erro apresentado na sincronização "Dados rede de Atendimento"</t>
   </si>
   <si>
+    <t>MONICA.SILVA</t>
+  </si>
+  <si>
+    <t>COMPLEMENTAR - SMS 2531696 - Cálculo de coparticipação por faixa salarial</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Apoio em rotina FTP</t>
+  </si>
+  <si>
+    <t>Erro de execução de query (NHibernate) ao enviar lote de pagamento</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>Atualização da BuilderCli</t>
+  </si>
+  <si>
+    <t>Erro no envio de nota fiscal anexada no lote do Conecta para o AG</t>
+  </si>
+  <si>
+    <t>Status “Negada” não refletido no Conecta</t>
+  </si>
+  <si>
+    <t>WebServices da TISS 4.01 com Falha</t>
+  </si>
+  <si>
+    <t>BuilderCli para HML está solicitante atualizar para versão 25.0.94.4 ou superior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agendamentos do Conecta no Ambiente AG Não Estão Sendo  Processados</t>
+  </si>
+  <si>
+    <t>Cálculo de coparticipação por faixa salarial</t>
+  </si>
+  <si>
+    <t>PRESTADOR.RAFAEL.P</t>
+  </si>
+  <si>
+    <t>Mariana Hila</t>
+  </si>
+  <si>
+    <t>Erro para o cadastro das Qualificações</t>
+  </si>
+  <si>
+    <t>Atualização Versao TISS Conecta</t>
+  </si>
+  <si>
     <t>Critica Conecta- Evento TGE</t>
   </si>
   <si>
-    <t>ANA.BRASILEIRO</t>
-  </si>
-  <si>
     <t>COMPESAPREV_Erro ao enviar e-mail pelo Portal.</t>
   </si>
   <si>
-    <t>Configurações do Sistema</t>
+    <t>Erro Lean Compesaprev Log de Finalização</t>
+  </si>
+  <si>
+    <t>RUI.KOEPSEL</t>
+  </si>
+  <si>
+    <t>CONSULTORIA</t>
+  </si>
+  <si>
+    <t>Consultoria a COMPESAPREV</t>
+  </si>
+  <si>
+    <t>Erro de sincronização entre AG e Central de Atendimento – Atendimento a Prestador</t>
+  </si>
+  <si>
+    <t>Aguardando testes internos</t>
+  </si>
+  <si>
+    <t>Lean Compesaprev- Sistema não realiza a busca da operadora no monitor de regulação</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Portal de Beneficiários</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_ Erro ao realizar sincronizações</t>
   </si>
   <si>
     <t>Erro Lean Compesaprev</t>
   </si>
   <si>
-    <t>Mariana Hila</t>
+    <t>CompesaPrev - Tombamento AG Produção na Homologação</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_ Portal de Beneficiários</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Solicito liberação do Conecta em produção. Segue dados do AG: https://compesaprev.bennercloud.com.br/AgWeb</t>
   </si>
   <si>
     <t>CompesaPrev - Solicito configuração dos dados SMTP Servidor: smtp.office365.comPorta: 587Usuário: portalcompesas</t>
   </si>
   <si>
+    <t>Instalação do Task worker para o cliente TRT3 base do LEAN</t>
+  </si>
+  <si>
+    <t>Parametrização de processos de agendamento no sistema Lean Compesaprev</t>
+  </si>
+  <si>
     <t>CompesaPrev - Solicito atualização do ambiente de homologação e produção para release 94</t>
   </si>
   <si>
-    <t>COMPESAPREV_ Configuração de ServerManager</t>
-  </si>
-  <si>
-    <t>PRESTADOR.RAFAEL.P</t>
-  </si>
-  <si>
-    <t>Beneficiários</t>
-  </si>
-  <si>
-    <t>Erro na visualização de endereços do sistema web</t>
-  </si>
-  <si>
-    <t>CONFIGURAÇÃO</t>
-  </si>
-  <si>
-    <t>Atendimento</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Central de Atendimento</t>
-  </si>
-  <si>
-    <t>alexandre.gomes</t>
-  </si>
-  <si>
-    <t>Alexandre Machado de Souza Gomes</t>
-  </si>
-  <si>
-    <t>CRIAÇÃO DE AMBIENTE SAAS PARA O CLIENTE COMPESAPREV</t>
-  </si>
-  <si>
-    <t>MOBE</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>Erro ao buscar documento/relatório na Consulta de Autorizações (App)</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Ajuste de permissões e perfis de acesso no AG - Papel de Desenvolvedor aplicado a todos os usuários</t>
-  </si>
-  <si>
-    <t>COMPESAPREV.DANIEL</t>
-  </si>
-  <si>
-    <t>Daniel Serafim</t>
-  </si>
-  <si>
-    <t>BuilderCli para HML está solicitante atualizar para versão 25.0.94.4 ou superior</t>
-  </si>
-  <si>
-    <t>Lean Compesaprev- Sistema não realiza a busca da operadora no monitor de regulação</t>
-  </si>
-  <si>
-    <t>Instalação do Task worker para o cliente TRT3 base do LEAN</t>
-  </si>
-  <si>
-    <t>Parametrização de processos de agendamento no sistema Lean Compesaprev</t>
+    <t>COMPESAPREV_ Atualização AG (homologação)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPESAPREV_ erro na  sincronização</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_ Habilitar a rede credenciada ao Portal (tela de login).</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Atualização do Portal (homologação)</t>
   </si>
   <si>
     <t xml:space="preserve">COMPESAPREV_  sem retorno ao solicitar sincronização de parâmetros</t>
@@ -272,25 +629,37 @@
     <t>CompesaPrev - Liberação de licenças desktop</t>
   </si>
   <si>
+    <t>PEDRO.ALMEIDA</t>
+  </si>
+  <si>
+    <t>tombamento de base</t>
+  </si>
+  <si>
+    <t>Integração OPMENexo - Gestão de Cotações</t>
+  </si>
+  <si>
     <t>FERNANDO.CARENO</t>
-  </si>
-  <si>
-    <t>Regulação Médica</t>
   </si>
   <si>
     <t xml:space="preserve">Erro ao abrir monitor de regulação do LEAN.
 Mesmo problema sendo tratado na SMS 2499740.</t>
   </si>
   <si>
+    <t>COMPESAPREV_ Configuração de ServerManager</t>
+  </si>
+  <si>
+    <t>Erro na visualização de endereços do sistema web</t>
+  </si>
+  <si>
     <t>Erro de sincronização entre AG e Central de Atendimento – Exportar Dados Beneficiário</t>
   </si>
   <si>
-    <t>QUALIDADE</t>
-  </si>
-  <si>
     <t>Legenda de campos sobrepostas</t>
   </si>
   <si>
+    <t>CONFIGURAÇÃO</t>
+  </si>
+  <si>
     <t xml:space="preserve">CompesaPrev  - Liberação da ferramenta Central de Atendimento no ambiente de produção</t>
   </si>
   <si>
@@ -303,445 +672,79 @@
     <t>CompesaPrev - Solicito criação da operadora CompesaPrev para a plataforma do Íris</t>
   </si>
   <si>
+    <t>IMPLEMENTACAO</t>
+  </si>
+  <si>
+    <t>DV_Detalhamento de boletos</t>
+  </si>
+  <si>
+    <t>Consultoria para CompesaPRev</t>
+  </si>
+  <si>
+    <t>RESSARCIMENTO SUS</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Ressarcimento SUS</t>
+  </si>
+  <si>
+    <t>DV_ISS geração de arquivo TXT ISS prestador</t>
+  </si>
+  <si>
+    <t>DV_Envio automático de comunicados aos beneficiários</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Central de Atendimento</t>
+  </si>
+  <si>
+    <t>PRESTADOR.PRISCILA.S</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_DV_CALCULO DE MENSALIDADE</t>
+  </si>
+  <si>
+    <t>Faturado</t>
+  </si>
+  <si>
+    <t>APOIO TÉCNICO</t>
+  </si>
+  <si>
+    <t>CompesaPrev | Migração de beneficiários e prestadores ativos</t>
+  </si>
+  <si>
+    <t>Implementar app CompesaPrev</t>
+  </si>
+  <si>
+    <t>CompesaPrev - Permissão e Acesso para dependentes maiores de 18 anos no Portal e Mobile</t>
+  </si>
+  <si>
+    <t>CompesaPrev |Informações adicionais para migração de dados de beneficiários</t>
+  </si>
+  <si>
+    <t>luciano.hering</t>
+  </si>
+  <si>
+    <t>[CRIAÇÃO DE BASE PARA CLIENTE COMPESAPREV OCI265 - SAUDE 10.220.0.38 - BASE PORTAL</t>
+  </si>
+  <si>
+    <t>Fernando.Soncin</t>
+  </si>
+  <si>
+    <t>Avaliação de documentação de aderência módulo de Beneficiários</t>
+  </si>
+  <si>
     <t>CompesaPrev - Liberação de acesso ao Conecta</t>
   </si>
   <si>
-    <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Prestadores</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO NOME PRESTADOR</t>
-  </si>
-  <si>
-    <t>Ajuste no tempo de sessão ativa (timeout) do sistema Lean.</t>
-  </si>
-  <si>
-    <t>Dúvida sobre o local para salvar/exportar a Guia Executada no Portal do Prestador</t>
-  </si>
-  <si>
-    <t>Inconsistência no cálculo do prazo em horas úteis</t>
-  </si>
-  <si>
-    <t>Alinhamento sobre parametrização de críticas/motivos de negação automáticos (AG / Conecta)</t>
-  </si>
-  <si>
-    <t>CENTRAL ATENDIMENTO</t>
-  </si>
-  <si>
-    <t>Históricos Atendimentos</t>
-  </si>
-  <si>
-    <t>Não está sendo possível SOLUCIONAR DEMANDAS</t>
-  </si>
-  <si>
-    <t>Compesaprev- Lean- Erro log integração</t>
-  </si>
-  <si>
-    <t>Cancelado</t>
-  </si>
-  <si>
-    <t>Controle Financeiro</t>
-  </si>
-  <si>
-    <t>COMPESPREV - Arquivo retorno com erro na importação</t>
-  </si>
-  <si>
-    <t>Julia Flora Ferreira de Albertim</t>
-  </si>
-  <si>
-    <t>Liberação de Relatório Geral de Execução e Biometria / Correção de Bloqueios</t>
-  </si>
-  <si>
-    <t>Compesaprev-Lean- Erro na inclusão de procedimento- OPME</t>
-  </si>
-  <si>
-    <t>Falha ao utilizar o campo Ignorar críticas de XML no Conecta</t>
-  </si>
-  <si>
-    <t>Compesaprev- AG-Produção: Erro na autorização</t>
-  </si>
-  <si>
-    <t>Valor Autorizado Não Exibido no Recibo de Atendimento</t>
-  </si>
-  <si>
-    <t>Falha ao ativar/desativar críticas de XML no Conecta</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Cadastro de Cooperados</t>
-  </si>
-  <si>
-    <t>Faturamento</t>
-  </si>
-  <si>
-    <t>Erro no envio de nota fiscal anexada no lote do Conecta para o AG</t>
-  </si>
-  <si>
-    <t>Status “Negada” não refletido no Conecta</t>
-  </si>
-  <si>
-    <t>Atualização Versao TISS Conecta</t>
-  </si>
-  <si>
-    <t>Erro Lean Compesaprev Log de Finalização</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Tombamento AG Produção na Homologação</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Solicito liberação do Conecta em produção. Segue dados do AG: https://compesaprev.bennercloud.com.br/AgWeb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPESAPREV_ erro na  sincronização</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_ Habilitar a rede credenciada ao Portal (tela de login).</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Atualização do Portal (homologação)</t>
-  </si>
-  <si>
-    <t>PEDRO.ALMEIDA</t>
-  </si>
-  <si>
-    <t>tombamento de base</t>
-  </si>
-  <si>
-    <t>luciano.hering</t>
-  </si>
-  <si>
-    <t>[CRIAÇÃO DE BASE PARA CLIENTE COMPESAPREV OCI265 - SAUDE 10.220.0.38 - BASE PORTAL</t>
+    <t>alexandre.gomes</t>
+  </si>
+  <si>
+    <t>Alexandre Machado de Souza Gomes</t>
+  </si>
+  <si>
+    <t>CRIAÇÃO DE AMBIENTE SAAS PARA O CLIENTE COMPESAPREV</t>
   </si>
   <si>
     <t>[CRIAÇÃO DE BASE PARA CLIENTE COMPESAPREV OCI265 - SAUDE 10.220.0.38</t>
-  </si>
-  <si>
-    <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- Conecta- Erro na solicitação dos procedimentos.</t>
-  </si>
-  <si>
-    <t>ALEXIA.SANTOS</t>
-  </si>
-  <si>
-    <t>Correção – CompesaPrev – Erro de Geração do Código de Barras e Linha Digitável</t>
-  </si>
-  <si>
-    <t>COMPESAPREV.NIECIA</t>
-  </si>
-  <si>
-    <t>Niécia Morais</t>
-  </si>
-  <si>
-    <t>Processamento de Contas</t>
-  </si>
-  <si>
-    <t>Erro no faturamento de pagamentos prestadores</t>
-  </si>
-  <si>
-    <t>Histórico financeiro sem a informação individual de todos os beneficiários</t>
-  </si>
-  <si>
-    <t>Erro de divergência de cadastro entre o AG e o LEAN</t>
-  </si>
-  <si>
-    <t>MOBE | Erro no servidor ao tentar logar.</t>
-  </si>
-  <si>
-    <t>Extrato de Utilização com valores de coparticipações sem a limitação de PF e antes do faturamento ser concluído</t>
-  </si>
-  <si>
-    <t>Transações</t>
-  </si>
-  <si>
-    <t>Falha na integração entre AG Web e Central de Atendimento</t>
-  </si>
-  <si>
-    <t>EVIDENCIAS DO PROBLEMA NO RELATORIO DE PREVIA DE PAGAMENTO</t>
-  </si>
-  <si>
-    <t>COMPESAPREV – AG: Duplicidade dos eventos solicitados no e-mail do Beneficiario</t>
-  </si>
-  <si>
-    <t>Atualização do AG em Produção - Release 3.65.19 (Ambiente e WTS)</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- LEAN- RELATORIO- Regulações Vencidas</t>
-  </si>
-  <si>
-    <t>Esqueci minha senha APP</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Painel de sincronização - PLANOS</t>
-  </si>
-  <si>
-    <t>COMPESAPREV - SISTEMA NÃO ESTÁ CONSIDERANDO LIMITADOR PF PARA REEMBOLSO</t>
-  </si>
-  <si>
-    <t>Não consigo vizualizar o que estão pedindo para ALTERAR quando solicitam alteração cadastral de E-MAIL</t>
-  </si>
-  <si>
-    <t>Acesso rede credenciada com perfil de DEPENDENTE não traz resultados.</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Solicito atualização do Portal para release 2.2.22 para PRODUÇÃO</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Solicito atualização do Portal para release 2.2.22 para HOMOLOGAÇÃO</t>
-  </si>
-  <si>
-    <t>Acesso e busca na rede credenciada</t>
-  </si>
-  <si>
-    <t>Compesaprev | AG TGE – Duplicidade de procedimento com o mesmo código</t>
-  </si>
-  <si>
-    <t>COMPESAPREV – AG - Produção: Falha na Integração das Guias para o Lean</t>
-  </si>
-  <si>
-    <t>COMPESAPREV – Conecta Produção: Eventos não são localizados para inclusão em guia</t>
-  </si>
-  <si>
-    <t>COMPESAPREV - Solicitação de atualização cadastral pelo Portal</t>
-  </si>
-  <si>
-    <t>Legal</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Rede de Atendimento - MOBILE</t>
-  </si>
-  <si>
-    <t>Integrações</t>
-  </si>
-  <si>
-    <t>COMPESAPREV-LEAN-PROD- Erro ao substituir diária — Enum inválido (TissTabelaProcedimentos)</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- LEAN- PROD- Erro na finalização das regulacoes</t>
-  </si>
-  <si>
-    <t>Compesaprev- Lean- Produção- Erro</t>
-  </si>
-  <si>
-    <t>Erro de execução de query (NHibernate) ao enviar lote de pagamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agendamentos do Conecta no Ambiente AG Não Estão Sendo  Processados</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_ Erro ao realizar sincronizações</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_ Portal de Beneficiários</t>
-  </si>
-  <si>
-    <t>Web</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_ Atualização AG (homologação)</t>
-  </si>
-  <si>
-    <t>CONECTA - XML não sai do estado de "Em Processamento"</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>CONECTA - Erro na execução de guias | pop-up e bloqueio por biometria</t>
-  </si>
-  <si>
-    <t>Portal não envia e-mails, recuperação de senha e processos parados desde 04/09</t>
-  </si>
-  <si>
-    <t>Lean / AG (Integração e guias travadas)</t>
-  </si>
-  <si>
-    <t>COMPESAPREV – Lean Produção: Falha no Agendamento da Tarefa de Finalização</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- AG- REGULAÇÃO- Agendamento travado</t>
-  </si>
-  <si>
-    <t>Compesaprev- Prod- Erro na fila de integraçao guias de prorrogação</t>
-  </si>
-  <si>
-    <t>Atualização da BuilderCli</t>
-  </si>
-  <si>
-    <t>WebServices da TISS 4.01 com Falha</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Portal de Beneficiários</t>
-  </si>
-  <si>
-    <t>APOIO DE NEGÓCIO</t>
-  </si>
-  <si>
-    <t>Erro na de geração do “Nosso Número” no boleto</t>
-  </si>
-  <si>
-    <t>Versão futura</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>MELHORIA</t>
-  </si>
-  <si>
-    <t>CompesaPrev – Erro na Emissão de Boleto</t>
-  </si>
-  <si>
-    <t>Aguardando análise (negócio)</t>
-  </si>
-  <si>
-    <t>IMPL NAO COBRADA</t>
-  </si>
-  <si>
-    <t>Compesaprev - Complemento II SMS 2531696 – Regra para cálculo de coparticipação</t>
-  </si>
-  <si>
-    <t>Analisando (negócio)</t>
-  </si>
-  <si>
-    <t>Os detalhes da CARTEIRINHA não está aparecendo para alguns beneficiários</t>
-  </si>
-  <si>
-    <t>COMPREPREV_ PROBLEMA RELACIONADO A REDE DE ATENDIMENTO</t>
-  </si>
-  <si>
-    <t>EDITAL NEGOCIACAO</t>
-  </si>
-  <si>
-    <t>MOBILE IRIS</t>
-  </si>
-  <si>
-    <t>App</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Implantação Mobile Íris</t>
-  </si>
-  <si>
-    <t>SERVIÇOS PONTUAIS</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- IRIS-Produção</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Alteração de logo para Mobile</t>
-  </si>
-  <si>
-    <t>COMPESAPREV-AG-PROD- Erro na inclusão de eventos no sistema AG</t>
-  </si>
-  <si>
-    <t>Aguardando detalhamento</t>
-  </si>
-  <si>
-    <t>VINICIUS.GENEROSO</t>
-  </si>
-  <si>
-    <t>Alteração da busca de limite de PF mensal por faixa salarial exclusivamente do titular</t>
-  </si>
-  <si>
-    <t>Complemento SMS 2531696 – Regra para cálculo de coparticipação</t>
-  </si>
-  <si>
-    <t>Complemento SMS 2470122 – Regra para cálculo de mensalidade</t>
-  </si>
-  <si>
-    <t>MONICA.SILVA</t>
-  </si>
-  <si>
-    <t>COMPLEMENTAR - SMS 2531696 - Cálculo de coparticipação por faixa salarial</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Apoio em rotina FTP</t>
-  </si>
-  <si>
-    <t>Cálculo de coparticipação por faixa salarial</t>
-  </si>
-  <si>
-    <t>Erro para o cadastro das Qualificações</t>
-  </si>
-  <si>
-    <t>RUI.KOEPSEL</t>
-  </si>
-  <si>
-    <t>CONSULTORIA</t>
-  </si>
-  <si>
-    <t>Consultoria a COMPESAPREV</t>
-  </si>
-  <si>
-    <t>Erro de sincronização entre AG e Central de Atendimento – Atendimento a Prestador</t>
-  </si>
-  <si>
-    <t>Aguardando testes internos</t>
-  </si>
-  <si>
-    <t>Integração OPMENexo - Gestão de Cotações</t>
-  </si>
-  <si>
-    <t>IMPLEMENTACAO</t>
-  </si>
-  <si>
-    <t>DV_Detalhamento de boletos</t>
-  </si>
-  <si>
-    <t>Consultoria para CompesaPRev</t>
-  </si>
-  <si>
-    <t>RESSARCIMENTO SUS</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Ressarcimento SUS</t>
-  </si>
-  <si>
-    <t>DV_ISS geração de arquivo TXT ISS prestador</t>
-  </si>
-  <si>
-    <t>DV_Envio automático de comunicados aos beneficiários</t>
-  </si>
-  <si>
-    <t>PRESTADOR.PRISCILA.S</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_DV_CALCULO DE MENSALIDADE</t>
-  </si>
-  <si>
-    <t>Faturado</t>
-  </si>
-  <si>
-    <t>APOIO TÉCNICO</t>
-  </si>
-  <si>
-    <t>CompesaPrev | Migração de beneficiários e prestadores ativos</t>
-  </si>
-  <si>
-    <t>Implementar app CompesaPrev</t>
-  </si>
-  <si>
-    <t>CompesaPrev - Permissão e Acesso para dependentes maiores de 18 anos no Portal e Mobile</t>
-  </si>
-  <si>
-    <t>CompesaPrev |Informações adicionais para migração de dados de beneficiários</t>
-  </si>
-  <si>
-    <t>Fernando.Soncin</t>
-  </si>
-  <si>
-    <t>Avaliação de documentação de aderência módulo de Beneficiários</t>
   </si>
 </sst>
 </file>
@@ -797,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O142"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1506990705218" customWidth="1"/>
@@ -866,7 +869,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2614686</v>
+        <v>2617170</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>15</v>
@@ -890,10 +893,10 @@
         <v>20</v>
       </c>
       <c r="I2" s="3">
-        <v>46321.5908449074</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="J2" s="3">
-        <v>46282.4296635764</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>21</v>
@@ -902,16 +905,16 @@
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>46280.4450115741</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="N2" s="3">
-        <v>46321.5908449074</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2612720</v>
+        <v>2617057</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>15</v>
@@ -920,25 +923,25 @@
         <v>15</v>
       </c>
       <c r="D3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="F3" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="G3" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="0" t="s">
-        <v>26</v>
-      </c>
       <c r="H3" s="0" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I3" s="3">
-        <v>46316.6011689815</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="J3" s="3">
-        <v>46279.4816203704</v>
+        <v>46286.5879513889</v>
       </c>
       <c r="K3" s="0" t="s">
         <v>21</v>
@@ -947,16 +950,16 @@
         <v>22</v>
       </c>
       <c r="M3" s="3">
-        <v>46275.4553356481</v>
+        <v>46286.4877199074</v>
       </c>
       <c r="N3" s="3">
-        <v>46316.6011689815</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2611551</v>
+        <v>2615970</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>15</v>
@@ -965,100 +968,100 @@
         <v>15</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I4" s="3">
-        <v>46314.6183449074</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="J4" s="3">
-        <v>46274.3603356481</v>
+        <v>46287.3554017708</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L4" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M4" s="3">
-        <v>46273.4725115741</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="N4" s="3">
-        <v>46314.6183449074</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>2609883</v>
+        <v>2615871</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3">
-        <v>46309.7050347222</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="J5" s="3">
-        <v>46280.4030439815</v>
+        <v>46286.3450115741</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M5" s="3">
-        <v>46267.6217013889</v>
+        <v>46282.4440856481</v>
       </c>
       <c r="N5" s="3">
-        <v>46309.7050347222</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="O5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>2604815</v>
+        <v>2615590</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>33</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>34</v>
@@ -1070,10 +1073,10 @@
         <v>36</v>
       </c>
       <c r="I6" s="3">
-        <v>46296.563587963</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="J6" s="3">
-        <v>46268.6781365741</v>
+        <v>46281.7496990741</v>
       </c>
       <c r="K6" s="0" t="s">
         <v>37</v>
@@ -1082,196 +1085,196 @@
         <v>22</v>
       </c>
       <c r="M6" s="3">
-        <v>46255.4177546296</v>
+        <v>46281.6638425926</v>
       </c>
       <c r="N6" s="3">
-        <v>46296.563587963</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>2596882</v>
+        <v>2614686</v>
       </c>
       <c r="B7" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="G7" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="0" t="s">
+      <c r="H7" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3">
+        <v>46321.5908449074</v>
+      </c>
+      <c r="J7" s="3">
+        <v>46282.4296635764</v>
+      </c>
+      <c r="K7" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="3">
-        <v>46280.3775578704</v>
-      </c>
-      <c r="J7" s="3">
-        <v>46267.6170023148</v>
-      </c>
-      <c r="K7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M7" s="3">
-        <v>46238.7108912037</v>
+        <v>46280.4450115741</v>
       </c>
       <c r="N7" s="3">
-        <v>46280.3775578704</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>2591284</v>
+        <v>2614334</v>
       </c>
       <c r="B8" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>42</v>
-      </c>
       <c r="H8" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3">
-        <v>46266.3384837963</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="J8" s="3">
-        <v>46225.7002398495</v>
+        <v>46283.4291666667</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M8" s="3">
-        <v>46225.6718171296</v>
+        <v>46279.6749305556</v>
       </c>
       <c r="N8" s="3">
-        <v>46266.3384837963</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2584167</v>
+        <v>2614135</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="I9" s="3">
-        <v>46246.7216435185</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="J9" s="3">
-        <v>46247.4396759259</v>
+        <v>46279.6123263889</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="M9" s="3">
-        <v>46206.6383101852</v>
+        <v>46279.5169097222</v>
       </c>
       <c r="N9" s="3">
-        <v>46246.7216435185</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>2583447</v>
+        <v>2613646</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I10" s="3">
-        <v>46245.6724189815</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="J10" s="3">
-        <v>46265.3645138889</v>
+        <v>46283.4346064815</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="M10" s="3">
-        <v>46205.5752083333</v>
+        <v>46276.6376041667</v>
       </c>
       <c r="N10" s="3">
-        <v>46245.6724189815</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>2582452</v>
+        <v>2613202</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>15</v>
@@ -1280,532 +1283,532 @@
         <v>15</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E11" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="3">
+        <v>46288.6119212963</v>
+      </c>
+      <c r="J11" s="3">
+        <v>46283.4707657407</v>
+      </c>
+      <c r="K11" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="3">
-        <v>46244.4166666667</v>
-      </c>
-      <c r="J11" s="3">
-        <v>46204.7763078704</v>
-      </c>
-      <c r="K11" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M11" s="3">
-        <v>46203.8250810185</v>
+        <v>46276.3827546296</v>
       </c>
       <c r="N11" s="3">
-        <v>46244.4166666667</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>2582352</v>
+        <v>2613026</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I12" s="3">
-        <v>46244.340775463</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="J12" s="3">
-        <v>46204.7761805556</v>
+        <v>46280.356624456</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L12" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M12" s="3">
-        <v>46203.6741087963</v>
+        <v>46275.6895601852</v>
       </c>
       <c r="N12" s="3">
-        <v>46244.340775463</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>2572707</v>
+        <v>2612720</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="I13" s="3">
-        <v>46219.3964814815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="J13" s="3">
-        <v>46188.4629166667</v>
+        <v>46279.4816203704</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="M13" s="3">
-        <v>46178.7298148148</v>
+        <v>46275.4553356481</v>
       </c>
       <c r="N13" s="3">
-        <v>46219.3964814815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>2529591</v>
+        <v>2611881</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I14" s="3">
-        <v>46108.5968055556</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="J14" s="3">
-        <v>46126.6875</v>
+        <v>46274.7389930556</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L14" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M14" s="3">
-        <v>46069.4509722222</v>
+        <v>46273.7485648148</v>
       </c>
       <c r="N14" s="3">
-        <v>46108.5968055556</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2528858</v>
+        <v>2611848</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I15" s="3">
-        <v>46107.3861458333</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="J15" s="3">
-        <v>46087.6277662037</v>
+        <v>46276.5914583333</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="M15" s="3">
-        <v>46065.7194791667</v>
+        <v>46273.7127546296</v>
       </c>
       <c r="N15" s="3">
-        <v>46107.3861458333</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>2523602</v>
+        <v>2611692</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I16" s="3">
-        <v>46093.6246643519</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="J16" s="3">
-        <v>46056.5784027778</v>
+        <v>46273.637278588</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L16" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M16" s="3">
-        <v>46055.4788310185</v>
+        <v>46273.6013194444</v>
       </c>
       <c r="N16" s="3">
-        <v>46093.6246643519</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>2519904</v>
+        <v>2611552</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I17" s="3">
-        <v>46084.7217939815</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="J17" s="3">
-        <v>46044.7413888889</v>
+        <v>46273.5743171296</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M17" s="3">
-        <v>46044.6384606482</v>
+        <v>46273.474375</v>
       </c>
       <c r="N17" s="3">
-        <v>46084.7217939815</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>2518650</v>
+        <v>2611551</v>
       </c>
       <c r="B18" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>48</v>
-      </c>
       <c r="G18" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I18" s="3">
-        <v>46072.3536921296</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="J18" s="3">
-        <v>46043.8185648148</v>
+        <v>46274.3603356481</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="M18" s="3">
-        <v>46042.3536921296</v>
+        <v>46273.4725115741</v>
       </c>
       <c r="N18" s="3">
-        <v>46080.437025463</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>2502438</v>
+        <v>2611539</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I19" s="3">
-        <v>46037.3801388889</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="J19" s="3">
-        <v>45996.4823032407</v>
+        <v>46274.3607986111</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M19" s="3">
-        <v>45992.7134722222</v>
+        <v>46273.464375</v>
       </c>
       <c r="N19" s="3">
-        <v>46037.3801388889</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>2501349</v>
+        <v>2611521</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I20" s="3">
-        <v>46069.7381944444</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="J20" s="3">
-        <v>46069.3651388889</v>
+        <v>46273.7182003819</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L20" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M20" s="3">
-        <v>45989.0365856482</v>
+        <v>46273.4538773148</v>
       </c>
       <c r="N20" s="3">
-        <v>46069.7381944444</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>2474606</v>
+        <v>2610876</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I21" s="3">
-        <v>45952.4506944444</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="J21" s="3">
-        <v>45966.4450925926</v>
+        <v>46269.4406376505</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L21" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M21" s="3">
-        <v>45924.4486921296</v>
+        <v>46269.4200925926</v>
       </c>
       <c r="N21" s="3">
-        <v>45952.4506944444</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2437239</v>
+        <v>2610030</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>71</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I22" s="3">
-        <v>45870.3600462963</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="J22" s="3">
-        <v>45841.7026091435</v>
+        <v>46268.3853071412</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L22" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M22" s="3">
-        <v>45831.6933796296</v>
+        <v>46267.7105324074</v>
       </c>
       <c r="N22" s="3">
-        <v>45870.3600462963</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="O22" s="3"/>
     </row>
@@ -1814,22 +1817,22 @@
         <v>2609985</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E23" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="0" t="s">
         <v>72</v>
-      </c>
-      <c r="F23" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="0" t="s">
-        <v>74</v>
       </c>
       <c r="H23" s="0" t="s">
         <v>20</v>
@@ -1844,7 +1847,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M23" s="3">
         <v>46267.67125</v>
@@ -1856,97 +1859,97 @@
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>2609107</v>
+        <v>2609883</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3">
-        <v>46300.3339583333</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="J24" s="3">
-        <v>46268.4380070255</v>
+        <v>46280.4030439815</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M24" s="3">
-        <v>46266.4797916667</v>
+        <v>46267.6217013889</v>
       </c>
       <c r="N24" s="3">
-        <v>46300.3339583333</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>2547638</v>
+        <v>2609551</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I25" s="3">
-        <v>46150.3473611111</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="J25" s="3">
-        <v>46119.5010069444</v>
+        <v>46267.355462963</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="M25" s="3">
-        <v>46114.4931944444</v>
+        <v>46267.355462963</v>
       </c>
       <c r="N25" s="3">
-        <v>46150.3473611111</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>2524373</v>
+        <v>2609107</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>15</v>
@@ -1955,43 +1958,43 @@
         <v>15</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I26" s="3">
-        <v>46087.3854513889</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="J26" s="3">
-        <v>46056.6543865741</v>
+        <v>46268.4380070255</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M26" s="3">
-        <v>46056.5937847222</v>
+        <v>46266.4797916667</v>
       </c>
       <c r="N26" s="3">
-        <v>46087.3854513889</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>2519523</v>
+        <v>2608731</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>15</v>
@@ -2000,43 +2003,43 @@
         <v>15</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E27" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="3">
+        <v>46279.4280671296</v>
+      </c>
+      <c r="J27" s="3">
+        <v>46273.3513888889</v>
+      </c>
+      <c r="K27" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F27" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="H27" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I27" s="3">
-        <v>46076.5902777778</v>
-      </c>
-      <c r="J27" s="3">
-        <v>46048.4589814815</v>
-      </c>
-      <c r="K27" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="0" t="s">
-        <v>75</v>
-      </c>
       <c r="M27" s="3">
-        <v>46043.7362847222</v>
+        <v>46265.6780671296</v>
       </c>
       <c r="N27" s="3">
-        <v>46077.380775463</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>2519383</v>
+        <v>2608637</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>15</v>
@@ -2045,758 +2048,751 @@
         <v>15</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" s="3">
+        <v>46279.3644444444</v>
+      </c>
+      <c r="J28" s="3">
+        <v>46266.3667347222</v>
+      </c>
+      <c r="K28" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F28" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="H28" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I28" s="3">
-        <v>46076.399224537</v>
-      </c>
-      <c r="J28" s="3">
-        <v>46048.4599305556</v>
-      </c>
-      <c r="K28" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" s="0" t="s">
-        <v>75</v>
-      </c>
       <c r="M28" s="3">
-        <v>46043.6075578704</v>
+        <v>46265.6144444444</v>
       </c>
       <c r="N28" s="3">
-        <v>46076.399224537</v>
+        <v>46279.3644444444</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>2509014</v>
+        <v>2607413</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G29" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3">
+        <v>46266.569212963</v>
+      </c>
+      <c r="K29" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="H29" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I29" s="3">
-        <v>46044.7250578704</v>
-      </c>
-      <c r="J29" s="3">
-        <v>46022.6138541667</v>
-      </c>
-      <c r="K29" s="0" t="s">
-        <v>30</v>
-      </c>
       <c r="L29" s="0" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="M29" s="3">
-        <v>46008.454224537</v>
-      </c>
-      <c r="N29" s="3">
-        <v>46045.4708564815</v>
-      </c>
+        <v>46261.6163888889</v>
+      </c>
+      <c r="N29" s="3"/>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>2506714</v>
+        <v>2607198</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I30" s="3">
-        <v>46038.7073032407</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="J30" s="3">
-        <v>46044.7372337963</v>
+        <v>46273.6204976852</v>
       </c>
       <c r="K30" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="M30" s="3">
-        <v>46002.4364699074</v>
+        <v>46261.4379976852</v>
       </c>
       <c r="N30" s="3">
-        <v>46038.7073032407</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>2506599</v>
+        <v>2606003</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I31" s="3">
-        <v>46037.61375</v>
+        <v>46265.3599537037</v>
       </c>
       <c r="J31" s="3">
-        <v>46052.3252083333</v>
+        <v>46259.4993506944</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="M31" s="3">
-        <v>46002.3429166667</v>
+        <v>46259.443287037</v>
       </c>
       <c r="N31" s="3">
-        <v>46037.61375</v>
+        <v>46290.75</v>
       </c>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>2502589</v>
+        <v>2604815</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F32" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="0" t="s">
-        <v>88</v>
-      </c>
       <c r="H32" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I32" s="3">
-        <v>46029.6634375</v>
+        <v>46296.563587963</v>
       </c>
       <c r="J32" s="3">
-        <v>46014.6931018519</v>
+        <v>46268.6781365741</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M32" s="3">
-        <v>45993.3791087963</v>
+        <v>46255.4177546296</v>
       </c>
       <c r="N32" s="3">
-        <v>46029.6634375</v>
+        <v>46296.563587963</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>2500635</v>
+        <v>2604500</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I33" s="3">
-        <v>46024.4633796296</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="J33" s="3">
-        <v>46027.3611111111</v>
+        <v>46258.3485416667</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="M33" s="3">
-        <v>45987.671712963</v>
+        <v>46254.6270601852</v>
       </c>
       <c r="N33" s="3">
-        <v>46024.4633796296</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>2498066</v>
+        <v>2603668</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="D34" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="G34" s="0" t="s">
-        <v>91</v>
-      </c>
       <c r="H34" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I34" s="3">
-        <v>46073.7916666667</v>
+        <v>46259.3446296296</v>
       </c>
       <c r="J34" s="3">
-        <v>46126.6953240741</v>
+        <v>46258.6426851852</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="M34" s="3">
-        <v>45979.750162037</v>
-      </c>
-      <c r="N34" s="3"/>
+        <v>46253.427962963</v>
+      </c>
+      <c r="N34" s="3">
+        <v>46290.75</v>
+      </c>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>2494282</v>
+        <v>2602388</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I35" s="3">
-        <v>45986.48125</v>
+        <v>46255.4166666667</v>
       </c>
       <c r="J35" s="3">
-        <v>45988.567025463</v>
+        <v>46253.4900231482</v>
       </c>
       <c r="K35" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="M35" s="3">
-        <v>45971.4792824074</v>
+        <v>46251.5527777778</v>
       </c>
       <c r="N35" s="3">
-        <v>45986.4815625</v>
+        <v>46255.4166666667</v>
       </c>
       <c r="O35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>2494179</v>
+        <v>2601999</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E36" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="G36" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="H36" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="G36" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="H36" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="3">
-        <v>46002.675775463</v>
-      </c>
+      <c r="I36" s="3"/>
       <c r="J36" s="3">
-        <v>46044.7370486111</v>
+        <v>46266.6188194444</v>
       </c>
       <c r="K36" s="0" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="M36" s="3">
-        <v>45971.4049421296</v>
-      </c>
-      <c r="N36" s="3">
-        <v>46002.675775463</v>
-      </c>
+        <v>46248.7351273148</v>
+      </c>
+      <c r="N36" s="3"/>
       <c r="O36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>2439691</v>
+        <v>2600778</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>52</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>96</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I37" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="I37" s="3"/>
       <c r="J37" s="3">
-        <v>45838.6211342593</v>
+        <v>46274.3780324074</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="M37" s="3">
-        <v>45838.3761921296</v>
-      </c>
-      <c r="N37" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>46246.7171759259</v>
+      </c>
+      <c r="N37" s="3"/>
       <c r="O37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>2614135</v>
+        <v>2599732</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E38" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="F38" s="0" t="s">
-        <v>34</v>
-      </c>
       <c r="G38" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I38" s="3">
-        <v>46289.7291666667</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="J38" s="3">
-        <v>46279.6123263889</v>
+        <v>46248.3419117245</v>
       </c>
       <c r="K38" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M38" s="3">
-        <v>46279.5169097222</v>
+        <v>46245.4849537037</v>
       </c>
       <c r="N38" s="3">
-        <v>46289.7291666667</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="O38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2613646</v>
+        <v>2598987</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I39" s="3">
-        <v>46289.3876041667</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="J39" s="3">
-        <v>46283.4346064815</v>
+        <v>46251.536875</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="M39" s="3">
-        <v>46276.6376041667</v>
+        <v>46244.4564467593</v>
       </c>
       <c r="N39" s="3">
-        <v>46289.3876041667</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="O39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>2613202</v>
+        <v>2598910</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E40" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="H40" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="I40" s="3">
+        <v>46254.6386574074</v>
+      </c>
+      <c r="J40" s="3">
+        <v>46248.4760674769</v>
+      </c>
+      <c r="K40" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="L40" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F40" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G40" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="H40" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I40" s="3">
-        <v>46288.6119212963</v>
-      </c>
-      <c r="J40" s="3">
-        <v>46283.4707657407</v>
-      </c>
-      <c r="K40" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="L40" s="0" t="s">
-        <v>98</v>
-      </c>
       <c r="M40" s="3">
-        <v>46276.3827546296</v>
+        <v>46244.4094907407</v>
       </c>
       <c r="N40" s="3">
-        <v>46288.6119212963</v>
+        <v>46261.6103125</v>
       </c>
       <c r="O40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>2611848</v>
+        <v>2598767</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H41" s="0" t="s">
         <v>36</v>
       </c>
       <c r="I41" s="3">
-        <v>46287.4094675926</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="J41" s="3">
-        <v>46276.5914583333</v>
+        <v>46245.6608564815</v>
       </c>
       <c r="K41" s="0" t="s">
         <v>37</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M41" s="3">
-        <v>46273.7127546296</v>
+        <v>46241.757962963</v>
       </c>
       <c r="N41" s="3">
-        <v>46287.4094675926</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="O41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>2608731</v>
+        <v>2597798</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E42" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="H42" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="3">
+        <v>46290.75</v>
+      </c>
+      <c r="J42" s="3">
+        <v>46273.4412384259</v>
+      </c>
+      <c r="K42" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="L42" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F42" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G42" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="H42" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42" s="3">
-        <v>46279.4280671296</v>
-      </c>
-      <c r="J42" s="3">
-        <v>46273.3513888889</v>
-      </c>
-      <c r="K42" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="L42" s="0" t="s">
-        <v>98</v>
-      </c>
       <c r="M42" s="3">
-        <v>46265.6780671296</v>
+        <v>46240.4508912037</v>
       </c>
       <c r="N42" s="3">
-        <v>46279.4280671296</v>
+        <v>46290.75</v>
       </c>
       <c r="O42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>2608637</v>
+        <v>2597524</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I43" s="3">
-        <v>46279.3644444444</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="J43" s="3">
-        <v>46266.3667347222</v>
+        <v>46259.4158333333</v>
       </c>
       <c r="K43" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M43" s="3">
-        <v>46265.6144444444</v>
+        <v>46239.6925347222</v>
       </c>
       <c r="N43" s="3">
-        <v>46279.3644444444</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="O43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>2598987</v>
+        <v>2597515</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I44" s="3">
-        <v>46254.6856134259</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="J44" s="3">
-        <v>46251.536875</v>
+        <v>46261.4097453704</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="M44" s="3">
-        <v>46244.4564467593</v>
+        <v>46239.6856134259</v>
       </c>
       <c r="N44" s="3">
-        <v>46254.6856134259</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="O44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>2598910</v>
+        <v>2597495</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>15</v>
@@ -2805,82 +2801,84 @@
         <v>15</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="I45" s="3">
-        <v>46254.6386574074</v>
+        <v>46252.3333333333</v>
       </c>
       <c r="J45" s="3">
-        <v>46248.4760674769</v>
+        <v>46241.6523302083</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M45" s="3">
-        <v>46244.4094907407</v>
+        <v>46239.6802199074</v>
       </c>
       <c r="N45" s="3">
-        <v>46261.6103125</v>
-      </c>
-      <c r="O45" s="3"/>
+        <v>46245.5968865741</v>
+      </c>
+      <c r="O45" s="3">
+        <v>46252.3333333333</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>2597798</v>
+        <v>2596882</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I46" s="3">
-        <v>46290.75</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="J46" s="3">
-        <v>46273.4412384259</v>
+        <v>46267.6170023148</v>
       </c>
       <c r="K46" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="M46" s="3">
-        <v>46240.4508912037</v>
+        <v>46238.7108912037</v>
       </c>
       <c r="N46" s="3">
-        <v>46290.75</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="O46" s="3"/>
     </row>
@@ -2889,25 +2887,25 @@
         <v>2596538</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I47" s="3">
         <v>46273.960787037</v>
@@ -2916,10 +2914,10 @@
         <v>46286.3521412037</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="M47" s="3">
         <v>46238.4644791667</v>
@@ -2934,25 +2932,25 @@
         <v>2596407</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I48" s="3">
         <v>46248.6072106482</v>
@@ -2961,10 +2959,10 @@
         <v>46267.6164814815</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="M48" s="3">
         <v>46238.3780439815</v>
@@ -2976,956 +2974,948 @@
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>2593260</v>
+        <v>2595510</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E49" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="F49" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="F49" s="0" t="s">
-        <v>34</v>
-      </c>
       <c r="G49" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I49" s="3">
-        <v>46241.6638888889</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="J49" s="3">
-        <v>46267.614525463</v>
+        <v>46245.3667592593</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M49" s="3">
-        <v>46231.435150463</v>
+        <v>46234.6442939815</v>
       </c>
       <c r="N49" s="3">
-        <v>46241.6638888889</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="O49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>2592878</v>
+        <v>2595497</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I50" s="3">
-        <v>46241.3504282407</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="J50" s="3">
-        <v>46230.6675740741</v>
+        <v>46245.3669444444</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M50" s="3">
-        <v>46230.6004282407</v>
+        <v>46234.6436574074</v>
       </c>
       <c r="N50" s="3">
-        <v>46290.75</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="O50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>2591596</v>
+        <v>2593529</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H51" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I51" s="3">
-        <v>46238.7083333333</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="J51" s="3">
-        <v>46267.3444803241</v>
+        <v>46233.4404570255</v>
       </c>
       <c r="K51" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M51" s="3">
-        <v>46226.4797916667</v>
+        <v>46231.6639930556</v>
       </c>
       <c r="N51" s="3">
-        <v>46282.6141435185</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="O51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>2588490</v>
+        <v>2593490</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I52" s="3">
-        <v>46230.722037037</v>
+        <v>46239.6748032407</v>
       </c>
       <c r="J52" s="3">
-        <v>46231.4339699074</v>
+        <v>46253.4905324074</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="M52" s="3">
-        <v>46218.4928703704</v>
+        <v>46231.6518865741</v>
       </c>
       <c r="N52" s="3">
-        <v>46230.722037037</v>
-      </c>
-      <c r="O52" s="3"/>
+        <v>46239.6748032407</v>
+      </c>
+      <c r="O52" s="3">
+        <v>46234.48125</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>2585424</v>
+        <v>2593260</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I53" s="3">
-        <v>46223.3927199074</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="J53" s="3">
-        <v>46234.4964930556</v>
+        <v>46267.614525463</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="M53" s="3">
-        <v>46210.6427199074</v>
+        <v>46231.435150463</v>
       </c>
       <c r="N53" s="3">
-        <v>46290.75</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="O53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>2556211</v>
+        <v>2593216</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="E54" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="0" t="s">
-        <v>120</v>
-      </c>
       <c r="G54" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="I54" s="3">
-        <v>46150.6617476852</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="I54" s="3"/>
       <c r="J54" s="3">
-        <v>46146.3663773148</v>
+        <v>46231.4047453704</v>
       </c>
       <c r="K54" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="M54" s="3">
-        <v>46139.4325810185</v>
-      </c>
-      <c r="N54" s="3">
-        <v>46150.6617476852</v>
-      </c>
+        <v>46231.4011111111</v>
+      </c>
+      <c r="N54" s="3"/>
       <c r="O54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>2556029</v>
+        <v>2592878</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I55" s="3">
-        <v>46150.5</v>
+        <v>46241.3504282407</v>
       </c>
       <c r="J55" s="3">
-        <v>46146.401875</v>
+        <v>46230.6675740741</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="M55" s="3">
-        <v>46138.757337963</v>
+        <v>46230.6004282407</v>
       </c>
       <c r="N55" s="3">
-        <v>46154.6616087963</v>
+        <v>46290.75</v>
       </c>
       <c r="O55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>2529639</v>
+        <v>2592468</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I56" s="3">
-        <v>46083.3430902778</v>
+        <v>46237.6038657407</v>
       </c>
       <c r="J56" s="3">
-        <v>46072.6891666667</v>
+        <v>46240.6136738773</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M56" s="3">
-        <v>46069.5930902778</v>
+        <v>46227.7107060185</v>
       </c>
       <c r="N56" s="3">
-        <v>46083.3430902778</v>
+        <v>46293.6033680556</v>
       </c>
       <c r="O56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>2525312</v>
+        <v>2591596</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E57" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G57" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="H57" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="3">
+        <v>46238.7083333333</v>
+      </c>
+      <c r="J57" s="3">
+        <v>46267.3444803241</v>
+      </c>
+      <c r="K57" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F57" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="G57" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="H57" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I57" s="3">
-        <v>46070.5877314815</v>
-      </c>
-      <c r="J57" s="3">
-        <v>46062.7587037037</v>
-      </c>
-      <c r="K57" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="L57" s="0" t="s">
-        <v>98</v>
-      </c>
       <c r="M57" s="3">
-        <v>46058.3585648148</v>
+        <v>46226.4797916667</v>
       </c>
       <c r="N57" s="3">
-        <v>46070.5877314815</v>
+        <v>46282.6141435185</v>
       </c>
       <c r="O57" s="3"/>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>2521645</v>
+        <v>2591284</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="I58" s="3">
-        <v>46062.5</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="J58" s="3">
-        <v>46050.3426763542</v>
+        <v>46225.7002398495</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="M58" s="3">
-        <v>46049.7714236111</v>
-      </c>
-      <c r="N58" s="3"/>
+        <v>46225.6718171296</v>
+      </c>
+      <c r="N58" s="3">
+        <v>46266.3384837963</v>
+      </c>
       <c r="O58" s="3"/>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>2520048</v>
+        <v>2588490</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I59" s="3">
-        <v>46057.5</v>
+        <v>46230.722037037</v>
       </c>
       <c r="J59" s="3">
-        <v>46052.5774305556</v>
+        <v>46231.4339699074</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="M59" s="3">
-        <v>46045.3325578704</v>
+        <v>46218.4928703704</v>
       </c>
       <c r="N59" s="3">
-        <v>46057.5</v>
+        <v>46230.722037037</v>
       </c>
       <c r="O59" s="3"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2512883</v>
+        <v>2588025</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I60" s="3">
-        <v>46037.6340972222</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="I60" s="3"/>
       <c r="J60" s="3">
-        <v>46129.4199421296</v>
+        <v>46267.5903356482</v>
       </c>
       <c r="K60" s="0" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="M60" s="3">
-        <v>46027.4049305556</v>
-      </c>
-      <c r="N60" s="3">
-        <v>46141.6335300926</v>
-      </c>
+        <v>46217.612962963</v>
+      </c>
+      <c r="N60" s="3"/>
       <c r="O60" s="3"/>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>2512542</v>
+        <v>2587849</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I61" s="3">
-        <v>46036.5</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="J61" s="3">
-        <v>46024.5900925926</v>
+        <v>46237.9144806713</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M61" s="3">
-        <v>46022.6836342593</v>
+        <v>46217.4506597222</v>
       </c>
       <c r="N61" s="3">
-        <v>46036.5</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="O61" s="3"/>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>2512541</v>
+        <v>2587713</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I62" s="3">
-        <v>46036.5</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="J62" s="3">
-        <v>46022.7128356481</v>
+        <v>46230.4199074074</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="M62" s="3">
-        <v>46022.6762615741</v>
+        <v>46217.3658680556</v>
       </c>
       <c r="N62" s="3">
-        <v>46036.5</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>2506311</v>
+        <v>2587585</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I63" s="3">
-        <v>46013.7291666667</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="J63" s="3">
-        <v>46013.461875</v>
+        <v>46259.4474884259</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M63" s="3">
-        <v>46001.5219328704</v>
+        <v>46216.7097916667</v>
       </c>
       <c r="N63" s="3">
-        <v>46013.7291666667</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="O63" s="3"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2449811</v>
+        <v>2587006</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I64" s="3">
-        <v>45875.3688888889</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="J64" s="3">
-        <v>45870.3628819444</v>
+        <v>46227.4549884259</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="M64" s="3">
-        <v>45862.6188888889</v>
+        <v>46213.7239236111</v>
       </c>
       <c r="N64" s="3">
-        <v>45875.3688888889</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="O64" s="3"/>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2436707</v>
+        <v>2586984</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I65" s="3">
-        <v>45835.7284722222</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="J65" s="3">
-        <v>46126.7436921296</v>
+        <v>46273.4946180556</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="M65" s="3">
-        <v>45828.8276273148</v>
+        <v>46213.6971527778</v>
       </c>
       <c r="N65" s="3">
-        <v>45835.7288773148</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="O65" s="3"/>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>2617057</v>
+        <v>2586910</v>
       </c>
       <c r="B66" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="G66" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="H66" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="I66" s="3">
+        <v>46226.5833333333</v>
+      </c>
+      <c r="J66" s="3">
+        <v>46230.4194212963</v>
+      </c>
+      <c r="K66" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L66" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C66" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D66" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E66" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F66" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="G66" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="H66" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I66" s="3">
-        <v>46290.4043865741</v>
-      </c>
-      <c r="J66" s="3">
-        <v>46286.4877199074</v>
-      </c>
-      <c r="K66" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="L66" s="0" t="s">
-        <v>136</v>
-      </c>
       <c r="M66" s="3">
-        <v>46286.4877199074</v>
+        <v>46213.6245833333</v>
       </c>
       <c r="N66" s="3">
-        <v>46290.4043865741</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>2615970</v>
+        <v>2586651</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H67" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I67" s="3">
-        <v>46288.4166666667</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="J67" s="3">
-        <v>46282.5089930556</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="K67" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="M67" s="3">
-        <v>46282.5089930556</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="N67" s="3">
-        <v>46288.4166666667</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="O67" s="3"/>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>2615590</v>
+        <v>2586187</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>16</v>
+        <v>142</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I68" s="3">
-        <v>46287.5805092593</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I68" s="3"/>
       <c r="J68" s="3">
-        <v>46281.7496990741</v>
+        <v>46219.3850231481</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M68" s="3">
-        <v>46281.6638425926</v>
-      </c>
-      <c r="N68" s="3">
-        <v>46287.5805092593</v>
-      </c>
+        <v>46211.7697337963</v>
+      </c>
+      <c r="N68" s="3"/>
       <c r="O68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>2613026</v>
+        <v>2585888</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H69" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I69" s="3">
-        <v>46281.6747800926</v>
+        <v>46217.4119907407</v>
       </c>
       <c r="J69" s="3">
-        <v>46280.356624456</v>
+        <v>46217.5003587963</v>
       </c>
       <c r="K69" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="M69" s="3">
-        <v>46275.6895601852</v>
+        <v>46211.4953240741</v>
       </c>
       <c r="N69" s="3">
-        <v>46281.6747800926</v>
+        <v>46290.75</v>
       </c>
       <c r="O69" s="3"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>2611881</v>
+        <v>2585424</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>16</v>
@@ -3934,3169 +3924,3227 @@
         <v>17</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I70" s="3">
-        <v>46279.6652314815</v>
+        <v>46223.3927199074</v>
       </c>
       <c r="J70" s="3">
-        <v>46274.7389930556</v>
+        <v>46234.4964930556</v>
       </c>
       <c r="K70" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="M70" s="3">
-        <v>46273.7485648148</v>
+        <v>46210.6427199074</v>
       </c>
       <c r="N70" s="3">
-        <v>46279.6652314815</v>
+        <v>46290.75</v>
       </c>
       <c r="O70" s="3"/>
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>2611692</v>
+        <v>2584638</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="I71" s="3">
-        <v>46279.4554861111</v>
+        <v>46213.4171527778</v>
       </c>
       <c r="J71" s="3">
-        <v>46273.637278588</v>
+        <v>46213.4090859607</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="M71" s="3">
-        <v>46273.6013194444</v>
+        <v>46209.5016203704</v>
       </c>
       <c r="N71" s="3">
-        <v>46279.4554861111</v>
+        <v>46232.3874884259</v>
       </c>
       <c r="O71" s="3"/>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>2611521</v>
+        <v>2584397</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I72" s="3">
-        <v>46279.3705439815</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="J72" s="3">
-        <v>46273.7182003819</v>
+        <v>46213.3741550926</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="M72" s="3">
-        <v>46273.4538773148</v>
+        <v>46209.3423842593</v>
       </c>
       <c r="N72" s="3">
-        <v>46279.3705439815</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="O72" s="3"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>2610876</v>
+        <v>2584167</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I73" s="3">
-        <v>46276.3367592593</v>
+        <v>46246.7216435185</v>
       </c>
       <c r="J73" s="3">
-        <v>46269.4406376505</v>
+        <v>46247.4396759259</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="M73" s="3">
-        <v>46269.4200925926</v>
+        <v>46206.6383101852</v>
       </c>
       <c r="N73" s="3">
-        <v>46276.3367592593</v>
+        <v>46246.7216435185</v>
       </c>
       <c r="O73" s="3"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2610030</v>
+        <v>2583950</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I74" s="3">
-        <v>46274.6271990741</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="I74" s="3"/>
       <c r="J74" s="3">
-        <v>46268.3853071412</v>
+        <v>46273.4100925926</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M74" s="3">
-        <v>46267.7105324074</v>
-      </c>
-      <c r="N74" s="3">
-        <v>46274.6271990741</v>
-      </c>
+        <v>46206.4623148148</v>
+      </c>
+      <c r="N74" s="3"/>
       <c r="O74" s="3"/>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2609551</v>
+        <v>2583447</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>150</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I75" s="3">
-        <v>46273.6887962963</v>
+        <v>46245.6724189815</v>
       </c>
       <c r="J75" s="3">
-        <v>46267.355462963</v>
+        <v>46265.3645138889</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="M75" s="3">
-        <v>46267.355462963</v>
+        <v>46205.5752083333</v>
       </c>
       <c r="N75" s="3">
-        <v>46273.6887962963</v>
+        <v>46245.6724189815</v>
       </c>
       <c r="O75" s="3"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>2607198</v>
+        <v>2583382</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I76" s="3">
-        <v>46267.3546643518</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="I76" s="3"/>
       <c r="J76" s="3">
-        <v>46273.6204976852</v>
+        <v>46279.4689699074</v>
       </c>
       <c r="K76" s="0" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M76" s="3">
-        <v>46261.4379976852</v>
-      </c>
-      <c r="N76" s="3">
-        <v>46267.3546643518</v>
-      </c>
+        <v>46205.4905092593</v>
+      </c>
+      <c r="N76" s="3"/>
       <c r="O76" s="3"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>2606003</v>
+        <v>2582452</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I77" s="3">
-        <v>46265.3599537037</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="J77" s="3">
-        <v>46259.4993506944</v>
+        <v>46204.7763078704</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="M77" s="3">
-        <v>46259.443287037</v>
+        <v>46203.8250810185</v>
       </c>
       <c r="N77" s="3">
-        <v>46290.75</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>2604500</v>
+        <v>2582352</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C78" s="0" t="s">
         <v>33</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I78" s="3">
-        <v>46260.4812268519</v>
+        <v>46244.340775463</v>
       </c>
       <c r="J78" s="3">
-        <v>46258.3485416667</v>
+        <v>46204.7761805556</v>
       </c>
       <c r="K78" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="M78" s="3">
-        <v>46254.6270601852</v>
+        <v>46203.6741087963</v>
       </c>
       <c r="N78" s="3">
-        <v>46260.4812268519</v>
+        <v>46244.340775463</v>
       </c>
       <c r="O78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2603668</v>
+        <v>2579299</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I79" s="3">
-        <v>46259.3446296296</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="I79" s="3"/>
       <c r="J79" s="3">
-        <v>46258.6426851852</v>
+        <v>46204.3277777778</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M79" s="3">
-        <v>46253.427962963</v>
-      </c>
-      <c r="N79" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46196.4165162037</v>
+      </c>
+      <c r="N79" s="3"/>
       <c r="O79" s="3"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>2602388</v>
+        <v>2576326</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I80" s="3">
-        <v>46255.4166666667</v>
+        <v>46192.7916666667</v>
       </c>
       <c r="J80" s="3">
-        <v>46253.4900231482</v>
+        <v>46230.6812731481</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M80" s="3">
-        <v>46251.5527777778</v>
-      </c>
-      <c r="N80" s="3">
-        <v>46255.4166666667</v>
-      </c>
+        <v>46189.3995833333</v>
+      </c>
+      <c r="N80" s="3"/>
       <c r="O80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>2599732</v>
+        <v>2574153</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I81" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="I81" s="3"/>
       <c r="J81" s="3">
-        <v>46248.3419117245</v>
+        <v>46204.3218402778</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M81" s="3">
-        <v>46245.4849537037</v>
-      </c>
-      <c r="N81" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>46183.4711226852</v>
+      </c>
+      <c r="N81" s="3"/>
       <c r="O81" s="3"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>2598767</v>
+        <v>2572707</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I82" s="3">
-        <v>46247.6666666667</v>
+        <v>46219.3964814815</v>
       </c>
       <c r="J82" s="3">
-        <v>46245.6608564815</v>
+        <v>46188.4629166667</v>
       </c>
       <c r="K82" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="M82" s="3">
-        <v>46241.757962963</v>
+        <v>46178.7298148148</v>
       </c>
       <c r="N82" s="3">
-        <v>46247.6666666667</v>
+        <v>46219.3964814815</v>
       </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>2597524</v>
+        <v>2570274</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I83" s="3">
-        <v>46267.0453356481</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="I83" s="3"/>
       <c r="J83" s="3">
-        <v>46259.4158333333</v>
+        <v>46204.3220138889</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M83" s="3">
-        <v>46239.6925347222</v>
-      </c>
-      <c r="N83" s="3">
-        <v>46267.0453356481</v>
-      </c>
+        <v>46171.6563773148</v>
+      </c>
+      <c r="N83" s="3"/>
       <c r="O83" s="3"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>2597495</v>
+        <v>2562116</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I84" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="I84" s="3"/>
       <c r="J84" s="3">
-        <v>46241.6523302083</v>
+        <v>46160.7191666667</v>
       </c>
       <c r="K84" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M84" s="3">
-        <v>46239.6802199074</v>
-      </c>
-      <c r="N84" s="3">
-        <v>46245.5968865741</v>
-      </c>
-      <c r="O84" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>46154.3432638889</v>
+      </c>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>2595510</v>
+        <v>2558553</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I85" s="3">
-        <v>46240.4984606481</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="J85" s="3">
-        <v>46245.3667592593</v>
+        <v>46154.5888773148</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="M85" s="3">
-        <v>46234.6442939815</v>
+        <v>46146.3561805556</v>
       </c>
       <c r="N85" s="3">
-        <v>46240.4984606481</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="O85" s="3"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>2595497</v>
+        <v>2556271</v>
       </c>
       <c r="B86" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="G86" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="H86" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="I86" s="3">
+        <v>46141.4297453704</v>
+      </c>
+      <c r="J86" s="3">
+        <v>46139.9871412037</v>
+      </c>
+      <c r="K86" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L86" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C86" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="D86" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E86" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="F86" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="G86" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="H86" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I86" s="3">
-        <v>46240.4978240741</v>
-      </c>
-      <c r="J86" s="3">
-        <v>46245.3669444444</v>
-      </c>
-      <c r="K86" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="L86" s="0" t="s">
-        <v>136</v>
-      </c>
       <c r="M86" s="3">
-        <v>46234.6436574074</v>
+        <v>46139.471412037</v>
       </c>
       <c r="N86" s="3">
-        <v>46240.4978240741</v>
+        <v>46141.4901157407</v>
       </c>
       <c r="O86" s="3"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>2593529</v>
+        <v>2556211</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="I87" s="3">
-        <v>46237.5806597222</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="J87" s="3">
-        <v>46233.4404570255</v>
+        <v>46146.3663773148</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="M87" s="3">
-        <v>46231.6639930556</v>
+        <v>46139.4325810185</v>
       </c>
       <c r="N87" s="3">
-        <v>46237.5806597222</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>2592468</v>
+        <v>2556029</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E88" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G88" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="H88" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="I88" s="3">
+        <v>46150.5</v>
+      </c>
+      <c r="J88" s="3">
+        <v>46146.401875</v>
+      </c>
+      <c r="K88" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L88" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F88" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G88" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="H88" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I88" s="3">
-        <v>46237.6038657407</v>
-      </c>
-      <c r="J88" s="3">
-        <v>46240.6136738773</v>
-      </c>
-      <c r="K88" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="L88" s="0" t="s">
-        <v>136</v>
-      </c>
       <c r="M88" s="3">
-        <v>46227.7107060185</v>
+        <v>46138.757337963</v>
       </c>
       <c r="N88" s="3">
-        <v>46293.6033680556</v>
+        <v>46154.6616087963</v>
       </c>
       <c r="O88" s="3"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>2587849</v>
+        <v>2554341</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E89" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I89" s="3">
-        <v>46226.6083796296</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="J89" s="3">
-        <v>46237.9144806713</v>
+        <v>46135.6585185185</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="M89" s="3">
-        <v>46217.4506597222</v>
+        <v>46134.4016435185</v>
       </c>
       <c r="N89" s="3">
-        <v>46226.6083796296</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="O89" s="3"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2587585</v>
+        <v>2547638</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E90" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F90" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="F90" s="0" t="s">
-        <v>25</v>
-      </c>
       <c r="G90" s="0" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I90" s="3">
-        <v>46220.6264583333</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="J90" s="3">
-        <v>46259.4474884259</v>
+        <v>46119.5010069444</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="M90" s="3">
-        <v>46216.7097916667</v>
+        <v>46114.4931944444</v>
       </c>
       <c r="N90" s="3">
-        <v>46220.6264583333</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>2586984</v>
+        <v>2537054</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I91" s="3">
-        <v>46295.7416550926</v>
+        <v>46093.4339236111</v>
       </c>
       <c r="J91" s="3">
-        <v>46273.4946180556</v>
+        <v>46090.3698263889</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="M91" s="3">
-        <v>46213.6971527778</v>
+        <v>46087.5797569444</v>
       </c>
       <c r="N91" s="3">
-        <v>46295.7416550926</v>
+        <v>46093.4339236111</v>
       </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>2586651</v>
+        <v>2531696</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>167</v>
+        <v>52</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I92" s="3">
-        <v>46218.7157407407</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="I92" s="3"/>
       <c r="J92" s="3">
-        <v>46213.3824074074</v>
+        <v>46204.3216782407</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M92" s="3">
-        <v>46213.3824074074</v>
-      </c>
-      <c r="N92" s="3">
-        <v>46218.7157407407</v>
-      </c>
+        <v>46076.5833912037</v>
+      </c>
+      <c r="N92" s="3"/>
       <c r="O92" s="3"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>2585888</v>
+        <v>2530739</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>169</v>
+        <v>46</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I93" s="3">
-        <v>46217.4119907407</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="I93" s="3"/>
       <c r="J93" s="3">
-        <v>46217.5003587963</v>
+        <v>46218.6914940625</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M93" s="3">
-        <v>46211.4953240741</v>
-      </c>
-      <c r="N93" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46072.6973148148</v>
+      </c>
+      <c r="N93" s="3"/>
       <c r="O93" s="3"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>2584638</v>
+        <v>2529639</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E94" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="G94" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="H94" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="I94" s="3">
+        <v>46083.3430902778</v>
+      </c>
+      <c r="J94" s="3">
+        <v>46072.6891666667</v>
+      </c>
+      <c r="K94" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L94" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F94" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="G94" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="H94" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="I94" s="3">
-        <v>46213.4171527778</v>
-      </c>
-      <c r="J94" s="3">
-        <v>46213.4090859607</v>
-      </c>
-      <c r="K94" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="L94" s="0" t="s">
-        <v>136</v>
-      </c>
       <c r="M94" s="3">
-        <v>46209.5016203704</v>
+        <v>46069.5930902778</v>
       </c>
       <c r="N94" s="3">
-        <v>46232.3874884259</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="O94" s="3"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>2584397</v>
+        <v>2529591</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I95" s="3">
-        <v>46212.6757175926</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="J95" s="3">
-        <v>46213.3741550926</v>
+        <v>46126.6875</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="M95" s="3">
-        <v>46209.3423842593</v>
+        <v>46069.4509722222</v>
       </c>
       <c r="N95" s="3">
-        <v>46212.6757175926</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="O95" s="3"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>2558553</v>
+        <v>2528858</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E96" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="F96" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="F96" s="0" t="s">
-        <v>120</v>
-      </c>
       <c r="G96" s="0" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I96" s="3">
-        <v>46149.6895138889</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="J96" s="3">
-        <v>46154.5888773148</v>
+        <v>46087.6277662037</v>
       </c>
       <c r="K96" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L96" s="0" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="M96" s="3">
-        <v>46146.3561805556</v>
+        <v>46065.7194791667</v>
       </c>
       <c r="N96" s="3">
-        <v>46149.6895138889</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="O96" s="3"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>2537054</v>
+        <v>2525312</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I97" s="3">
-        <v>46093.4339236111</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="J97" s="3">
-        <v>46090.3698263889</v>
+        <v>46062.7587037037</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="M97" s="3">
-        <v>46087.5797569444</v>
+        <v>46058.3585648148</v>
       </c>
       <c r="N97" s="3">
-        <v>46093.4339236111</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="O97" s="3"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>2523635</v>
+        <v>2525272</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>16</v>
+        <v>183</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I98" s="3">
-        <v>46059.4164236111</v>
+        <v>46203.7916666667</v>
       </c>
       <c r="J98" s="3">
-        <v>46055.6034837963</v>
+        <v>46126.7441782407</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M98" s="3">
-        <v>46055.4997569444</v>
-      </c>
-      <c r="N98" s="3">
-        <v>46059.4164236111</v>
-      </c>
+        <v>46058.2883101852</v>
+      </c>
+      <c r="N98" s="3"/>
       <c r="O98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>2521079</v>
+        <v>2524577</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I99" s="3">
-        <v>46052.6666666667</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="I99" s="3"/>
       <c r="J99" s="3">
-        <v>46056.6197800926</v>
+        <v>46267.4298180903</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="M99" s="3">
-        <v>46048.7684490741</v>
-      </c>
-      <c r="N99" s="3">
-        <v>46061.6309722222</v>
-      </c>
+        <v>46056.697349537</v>
+      </c>
+      <c r="N99" s="3"/>
       <c r="O99" s="3"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>2519284</v>
+        <v>2524373</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I100" s="3">
-        <v>46049.3982986111</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="J100" s="3">
-        <v>46043.742337963</v>
+        <v>46056.6543865741</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L100" s="0" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="M100" s="3">
-        <v>46043.4816319444</v>
+        <v>46056.5937847222</v>
       </c>
       <c r="N100" s="3">
-        <v>46049.3982986111</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>2513117</v>
+        <v>2524062</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>177</v>
+        <v>24</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I101" s="3">
-        <v>46031.4922800926</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="J101" s="3">
-        <v>46028.3500347222</v>
+        <v>46056.6210300926</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="M101" s="3">
-        <v>46027.6381134259</v>
+        <v>46056.3662615741</v>
       </c>
       <c r="N101" s="3">
-        <v>46031.4922800926</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>2615871</v>
+        <v>2523635</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E102" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="F102" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="F102" s="0" t="s">
-        <v>120</v>
-      </c>
       <c r="G102" s="0" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I102" s="3">
-        <v>46286.4024189815</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="J102" s="3">
-        <v>46286.3450115741</v>
+        <v>46055.6034837963</v>
       </c>
       <c r="K102" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L102" s="0" t="s">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="M102" s="3">
-        <v>46282.4440856481</v>
+        <v>46055.4997569444</v>
       </c>
       <c r="N102" s="3">
-        <v>46286.4024189815</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>2614334</v>
+        <v>2523602</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C103" s="0" t="s">
         <v>33</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I103" s="3">
-        <v>46283.5629166667</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="J103" s="3">
-        <v>46283.4291666667</v>
+        <v>46056.5784027778</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="M103" s="3">
-        <v>46279.6749305556</v>
+        <v>46055.4788310185</v>
       </c>
       <c r="N103" s="3">
-        <v>46283.5629166667</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>2611552</v>
+        <v>2521645</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="I104" s="3">
-        <v>46275.4327083333</v>
+        <v>46062.5</v>
       </c>
       <c r="J104" s="3">
-        <v>46273.5743171296</v>
+        <v>46050.3426763542</v>
       </c>
       <c r="K104" s="0" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="M104" s="3">
-        <v>46273.474375</v>
-      </c>
-      <c r="N104" s="3">
-        <v>46275.4327083333</v>
-      </c>
+        <v>46049.7714236111</v>
+      </c>
+      <c r="N104" s="3"/>
       <c r="O104" s="3"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>2611539</v>
+        <v>2521079</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I105" s="3">
-        <v>46275.4227083333</v>
+        <v>46052.6666666667</v>
       </c>
       <c r="J105" s="3">
-        <v>46274.3607986111</v>
+        <v>46056.6197800926</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="M105" s="3">
-        <v>46273.464375</v>
+        <v>46048.7684490741</v>
       </c>
       <c r="N105" s="3">
-        <v>46275.4227083333</v>
+        <v>46061.6309722222</v>
       </c>
       <c r="O105" s="3"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>2593490</v>
+        <v>2520048</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I106" s="3">
-        <v>46239.6748032407</v>
+        <v>46057.5</v>
       </c>
       <c r="J106" s="3">
-        <v>46253.4905324074</v>
+        <v>46052.5774305556</v>
       </c>
       <c r="K106" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L106" s="0" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="M106" s="3">
-        <v>46231.6518865741</v>
+        <v>46045.3325578704</v>
       </c>
       <c r="N106" s="3">
-        <v>46239.6748032407</v>
-      </c>
-      <c r="O106" s="3">
-        <v>46234.48125</v>
-      </c>
+        <v>46057.5</v>
+      </c>
+      <c r="O106" s="3"/>
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>2587713</v>
+        <v>2519904</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I107" s="3">
-        <v>46218.7408680556</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="J107" s="3">
-        <v>46230.4199074074</v>
+        <v>46044.7413888889</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="M107" s="3">
-        <v>46217.3658680556</v>
+        <v>46044.6384606482</v>
       </c>
       <c r="N107" s="3">
-        <v>46218.7408680556</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="O107" s="3"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>2587006</v>
+        <v>2519523</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I108" s="3">
-        <v>46217.7289699074</v>
+        <v>46076.5902777778</v>
       </c>
       <c r="J108" s="3">
-        <v>46227.4549884259</v>
+        <v>46048.4589814815</v>
       </c>
       <c r="K108" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L108" s="0" t="s">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="M108" s="3">
-        <v>46213.7239236111</v>
+        <v>46043.7362847222</v>
       </c>
       <c r="N108" s="3">
-        <v>46217.7289699074</v>
+        <v>46077.380775463</v>
       </c>
       <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>2586910</v>
+        <v>2519383</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I109" s="3">
-        <v>46226.5833333333</v>
+        <v>46076.399224537</v>
       </c>
       <c r="J109" s="3">
-        <v>46230.4194212963</v>
+        <v>46048.4599305556</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="M109" s="3">
-        <v>46213.6245833333</v>
+        <v>46043.6075578704</v>
       </c>
       <c r="N109" s="3">
-        <v>46226.5833333333</v>
+        <v>46076.399224537</v>
       </c>
       <c r="O109" s="3"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>2556271</v>
+        <v>2519284</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>177</v>
+        <v>24</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I110" s="3">
-        <v>46141.4297453704</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="J110" s="3">
-        <v>46139.9871412037</v>
+        <v>46043.742337963</v>
       </c>
       <c r="K110" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L110" s="0" t="s">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="M110" s="3">
-        <v>46139.471412037</v>
+        <v>46043.4816319444</v>
       </c>
       <c r="N110" s="3">
-        <v>46141.4901157407</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="O110" s="3"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>2554341</v>
+        <v>2518650</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E111" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F111" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="F111" s="0" t="s">
-        <v>34</v>
-      </c>
       <c r="G111" s="0" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I111" s="3">
-        <v>46136.3599768519</v>
+        <v>46072.3536921296</v>
       </c>
       <c r="J111" s="3">
-        <v>46135.6585185185</v>
+        <v>46043.8185648148</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="M111" s="3">
-        <v>46134.4016435185</v>
+        <v>46042.3536921296</v>
       </c>
       <c r="N111" s="3">
-        <v>46136.3599768519</v>
+        <v>46080.437025463</v>
       </c>
       <c r="O111" s="3"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>2524062</v>
+        <v>2513117</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>48</v>
+        <v>167</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I112" s="3">
-        <v>46057.7412615741</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="J112" s="3">
-        <v>46056.6210300926</v>
+        <v>46028.3500347222</v>
       </c>
       <c r="K112" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="M112" s="3">
-        <v>46056.3662615741</v>
+        <v>46027.6381134259</v>
       </c>
       <c r="N112" s="3">
-        <v>46057.7412615741</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="O112" s="3"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>2607413</v>
+        <v>2512883</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="I113" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I113" s="3">
+        <v>46037.6340972222</v>
+      </c>
       <c r="J113" s="3">
-        <v>46266.569212963</v>
+        <v>46129.4199421296</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>193</v>
+        <v>45</v>
       </c>
       <c r="M113" s="3">
-        <v>46261.6163888889</v>
-      </c>
-      <c r="N113" s="3"/>
+        <v>46027.4049305556</v>
+      </c>
+      <c r="N113" s="3">
+        <v>46141.6335300926</v>
+      </c>
       <c r="O113" s="3"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>2601999</v>
+        <v>2512542</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>194</v>
+        <v>26</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="I114" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I114" s="3">
+        <v>46036.5</v>
+      </c>
       <c r="J114" s="3">
-        <v>46266.6188194444</v>
+        <v>46024.5900925926</v>
       </c>
       <c r="K114" s="0" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="L114" s="0" t="s">
-        <v>193</v>
+        <v>45</v>
       </c>
       <c r="M114" s="3">
-        <v>46248.7351273148</v>
-      </c>
-      <c r="N114" s="3"/>
+        <v>46022.6836342593</v>
+      </c>
+      <c r="N114" s="3">
+        <v>46036.5</v>
+      </c>
       <c r="O114" s="3"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>2600778</v>
+        <v>2512541</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="I115" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I115" s="3">
+        <v>46036.5</v>
+      </c>
       <c r="J115" s="3">
-        <v>46274.3780324074</v>
+        <v>46022.7128356481</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>193</v>
+        <v>45</v>
       </c>
       <c r="M115" s="3">
-        <v>46246.7171759259</v>
-      </c>
-      <c r="N115" s="3"/>
+        <v>46022.6762615741</v>
+      </c>
+      <c r="N115" s="3">
+        <v>46036.5</v>
+      </c>
       <c r="O115" s="3"/>
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>2597515</v>
+        <v>2509014</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I116" s="3">
-        <v>46266.4759953704</v>
+        <v>46044.7250578704</v>
       </c>
       <c r="J116" s="3">
-        <v>46261.4097453704</v>
+        <v>46022.6138541667</v>
       </c>
       <c r="K116" s="0" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L116" s="0" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="M116" s="3">
-        <v>46239.6856134259</v>
+        <v>46008.454224537</v>
       </c>
       <c r="N116" s="3">
-        <v>46266.4759953704</v>
+        <v>46045.4708564815</v>
       </c>
       <c r="O116" s="3"/>
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>2593216</v>
+        <v>2506714</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>190</v>
+        <v>113</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I117" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I117" s="3">
+        <v>46038.7073032407</v>
+      </c>
       <c r="J117" s="3">
-        <v>46231.4047453704</v>
+        <v>46044.7372337963</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="M117" s="3">
-        <v>46231.4011111111</v>
-      </c>
-      <c r="N117" s="3"/>
+        <v>46002.4364699074</v>
+      </c>
+      <c r="N117" s="3">
+        <v>46038.7073032407</v>
+      </c>
       <c r="O117" s="3"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>2588025</v>
+        <v>2506599</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>202</v>
+        <v>26</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>203</v>
+        <v>113</v>
       </c>
       <c r="F118" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="G118" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="G118" s="0" t="s">
-        <v>205</v>
-      </c>
       <c r="H118" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="I118" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I118" s="3">
+        <v>46037.61375</v>
+      </c>
       <c r="J118" s="3">
-        <v>46267.5903356482</v>
+        <v>46052.3252083333</v>
       </c>
       <c r="K118" s="0" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="L118" s="0" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="M118" s="3">
-        <v>46217.612962963</v>
-      </c>
-      <c r="N118" s="3"/>
+        <v>46002.3429166667</v>
+      </c>
+      <c r="N118" s="3">
+        <v>46037.61375</v>
+      </c>
       <c r="O118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>2586187</v>
+        <v>2506311</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="D119" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="F119" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="G119" s="0" t="s">
         <v>206</v>
       </c>
-      <c r="E119" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F119" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G119" s="0" t="s">
-        <v>207</v>
-      </c>
       <c r="H119" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="I119" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I119" s="3">
+        <v>46013.7291666667</v>
+      </c>
       <c r="J119" s="3">
-        <v>46219.3850231481</v>
+        <v>46013.461875</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>193</v>
+        <v>45</v>
       </c>
       <c r="M119" s="3">
-        <v>46211.7697337963</v>
-      </c>
-      <c r="N119" s="3"/>
+        <v>46001.5219328704</v>
+      </c>
+      <c r="N119" s="3">
+        <v>46013.7291666667</v>
+      </c>
       <c r="O119" s="3"/>
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <v>2583950</v>
+        <v>2506102</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I120" s="3"/>
       <c r="J120" s="3">
-        <v>46273.4100925926</v>
+        <v>46241.5032638889</v>
       </c>
       <c r="K120" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L120" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M120" s="3">
-        <v>46206.4623148148</v>
+        <v>46001.3800578704</v>
       </c>
       <c r="N120" s="3"/>
       <c r="O120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <v>2583382</v>
+        <v>2502589</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>15</v>
+        <v>208</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>15</v>
+        <v>208</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>209</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="I121" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I121" s="3">
+        <v>46029.6634375</v>
+      </c>
       <c r="J121" s="3">
-        <v>46279.4689699074</v>
+        <v>46014.6931018519</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="M121" s="3">
-        <v>46205.4905092593</v>
-      </c>
-      <c r="N121" s="3"/>
+        <v>45993.3791087963</v>
+      </c>
+      <c r="N121" s="3">
+        <v>46029.6634375</v>
+      </c>
       <c r="O121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <v>2579299</v>
+        <v>2502438</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>211</v>
+        <v>98</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I122" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I122" s="3">
+        <v>46037.3801388889</v>
+      </c>
       <c r="J122" s="3">
-        <v>46204.3277777778</v>
+        <v>45996.4823032407</v>
       </c>
       <c r="K122" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L122" s="0" t="s">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="M122" s="3">
-        <v>46196.4165162037</v>
-      </c>
-      <c r="N122" s="3"/>
+        <v>45992.7134722222</v>
+      </c>
+      <c r="N122" s="3">
+        <v>46037.3801388889</v>
+      </c>
       <c r="O122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <v>2576326</v>
+        <v>2501349</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I123" s="3">
-        <v>46192.7916666667</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="J123" s="3">
-        <v>46230.6812731481</v>
+        <v>46069.3651388889</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="M123" s="3">
-        <v>46189.3995833333</v>
-      </c>
-      <c r="N123" s="3"/>
+        <v>45989.0365856482</v>
+      </c>
+      <c r="N123" s="3">
+        <v>46069.7381944444</v>
+      </c>
       <c r="O123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <v>2574153</v>
+        <v>2500635</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I124" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I124" s="3">
+        <v>46024.4633796296</v>
+      </c>
       <c r="J124" s="3">
-        <v>46204.3218402778</v>
+        <v>46027.3611111111</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L124" s="0" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="M124" s="3">
-        <v>46183.4711226852</v>
-      </c>
-      <c r="N124" s="3"/>
+        <v>45987.671712963</v>
+      </c>
+      <c r="N124" s="3">
+        <v>46024.4633796296</v>
+      </c>
       <c r="O124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <v>2570274</v>
+        <v>2498066</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>215</v>
+        <v>176</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I125" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I125" s="3">
+        <v>46073.7916666667</v>
+      </c>
       <c r="J125" s="3">
-        <v>46204.3220138889</v>
+        <v>46126.6953240741</v>
       </c>
       <c r="K125" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="M125" s="3">
-        <v>46171.6563773148</v>
+        <v>45979.750162037</v>
       </c>
       <c r="N125" s="3"/>
       <c r="O125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <v>2562116</v>
+        <v>2494282</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I126" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I126" s="3">
+        <v>45986.48125</v>
+      </c>
       <c r="J126" s="3">
-        <v>46160.7191666667</v>
+        <v>45988.567025463</v>
       </c>
       <c r="K126" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="M126" s="3">
-        <v>46154.3432638889</v>
-      </c>
-      <c r="N126" s="3"/>
+        <v>45971.4792824074</v>
+      </c>
+      <c r="N126" s="3">
+        <v>45986.4815625</v>
+      </c>
       <c r="O126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <v>2531696</v>
+        <v>2494179</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>197</v>
+        <v>113</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>110</v>
+        <v>217</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>218</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I127" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="I127" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="J127" s="3">
-        <v>46204.3216782407</v>
+        <v>46044.7370486111</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="M127" s="3">
-        <v>46076.5833912037</v>
-      </c>
-      <c r="N127" s="3"/>
+        <v>45971.4049421296</v>
+      </c>
+      <c r="N127" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="O127" s="3"/>
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <v>2530739</v>
+        <v>2490911</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>196</v>
+        <v>103</v>
       </c>
       <c r="I128" s="3"/>
       <c r="J128" s="3">
-        <v>46218.6914940625</v>
+        <v>46182.7633796296</v>
       </c>
       <c r="K128" s="0" t="s">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="L128" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M128" s="3">
-        <v>46072.6973148148</v>
+        <v>45961.5760300926</v>
       </c>
       <c r="N128" s="3"/>
       <c r="O128" s="3"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <v>2525272</v>
+        <v>2490185</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="D129" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="E129" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F129" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="G129" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="E129" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F129" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="G129" s="0" t="s">
-        <v>222</v>
-      </c>
       <c r="H129" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I129" s="3">
         <v>46203.7916666667</v>
       </c>
       <c r="J129" s="3">
-        <v>46126.7441782407</v>
+        <v>46051.4836111111</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M129" s="3">
-        <v>46058.2883101852</v>
+        <v>45960.3928819444</v>
       </c>
       <c r="N129" s="3"/>
       <c r="O129" s="3"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <v>2524577</v>
+        <v>2489016</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>194</v>
+        <v>81</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>223</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>224</v>
+        <v>48</v>
       </c>
       <c r="I130" s="3"/>
       <c r="J130" s="3">
-        <v>46267.4298180903</v>
+        <v>45958.3906481481</v>
       </c>
       <c r="K130" s="0" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="L130" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M130" s="3">
-        <v>46056.697349537</v>
+        <v>45957.7253009259</v>
       </c>
       <c r="N130" s="3"/>
       <c r="O130" s="3"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <v>2506102</v>
+        <v>2485386</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I131" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="I131" s="3">
+        <v>46386.7916666667</v>
+      </c>
       <c r="J131" s="3">
-        <v>46241.5032638889</v>
+        <v>46182.7639236111</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M131" s="3">
-        <v>46001.3800578704</v>
+        <v>45947.7000115741</v>
       </c>
       <c r="N131" s="3"/>
       <c r="O131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <v>2490911</v>
+        <v>2483420</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I132" s="3"/>
       <c r="J132" s="3">
-        <v>46182.7633796296</v>
+        <v>46140.3843518519</v>
       </c>
       <c r="K132" s="0" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L132" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M132" s="3">
-        <v>45961.5760300926</v>
+        <v>45944.6603819444</v>
       </c>
       <c r="N132" s="3"/>
       <c r="O132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <v>2490185</v>
+        <v>2474606</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>220</v>
+        <v>112</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>220</v>
+        <v>112</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I133" s="3">
-        <v>46203.7916666667</v>
+        <v>45952.4506944444</v>
       </c>
       <c r="J133" s="3">
-        <v>46051.4836111111</v>
+        <v>45966.4450925926</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="M133" s="3">
-        <v>45960.3928819444</v>
-      </c>
-      <c r="N133" s="3"/>
+        <v>45924.4486921296</v>
+      </c>
+      <c r="N133" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="O133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <v>2489016</v>
+        <v>2470122</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>38</v>
+        <v>227</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>38</v>
+        <v>227</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="E134" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F134" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="G134" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="H134" s="0" t="s">
         <v>229</v>
-      </c>
-      <c r="F134" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="G134" s="0" t="s">
-        <v>230</v>
-      </c>
-      <c r="H134" s="0" t="s">
-        <v>29</v>
       </c>
       <c r="I134" s="3"/>
       <c r="J134" s="3">
-        <v>45958.3906481481</v>
+        <v>46204.3270601852</v>
       </c>
       <c r="K134" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L134" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M134" s="3">
-        <v>45957.7253009259</v>
+        <v>45912.5572222222</v>
       </c>
       <c r="N134" s="3"/>
       <c r="O134" s="3"/>
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <v>2485386</v>
+        <v>2463515</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>231</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="I135" s="3">
-        <v>46386.7916666667</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="I135" s="3"/>
       <c r="J135" s="3">
-        <v>46182.7639236111</v>
+        <v>45910.4755555556</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M135" s="3">
-        <v>45947.7000115741</v>
+        <v>45897.4218865741</v>
       </c>
       <c r="N135" s="3"/>
       <c r="O135" s="3"/>
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <v>2483420</v>
+        <v>2461703</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>232</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="I136" s="3"/>
       <c r="J136" s="3">
-        <v>46140.3843518519</v>
+        <v>46003.3706828704</v>
       </c>
       <c r="K136" s="0" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="L136" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M136" s="3">
-        <v>45944.6603819444</v>
+        <v>45894.4525347222</v>
       </c>
       <c r="N136" s="3"/>
       <c r="O136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <v>2470122</v>
+        <v>2459339</v>
       </c>
       <c r="B137" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="C137" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D137" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="E137" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F137" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G137" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="C137" s="0" t="s">
-        <v>233</v>
-      </c>
-      <c r="D137" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="E137" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F137" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="G137" s="0" t="s">
-        <v>234</v>
-      </c>
       <c r="H137" s="0" t="s">
-        <v>235</v>
+        <v>103</v>
       </c>
       <c r="I137" s="3"/>
       <c r="J137" s="3">
-        <v>46204.3270601852</v>
+        <v>46140.3839930556</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M137" s="3">
-        <v>45912.5572222222</v>
+        <v>45887.7442361111</v>
       </c>
       <c r="N137" s="3"/>
       <c r="O137" s="3"/>
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <v>2463515</v>
+        <v>2456538</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I138" s="3"/>
       <c r="J138" s="3">
-        <v>45910.4755555556</v>
+        <v>46126.7428356481</v>
       </c>
       <c r="K138" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L138" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M138" s="3">
-        <v>45897.4218865741</v>
+        <v>45880.6643055556</v>
       </c>
       <c r="N138" s="3"/>
       <c r="O138" s="3"/>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>2461703</v>
+        <v>2449811</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>50</v>
+        <v>235</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>50</v>
+        <v>235</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>226</v>
+        <v>113</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="I139" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I139" s="3">
+        <v>45875.3688888889</v>
+      </c>
       <c r="J139" s="3">
-        <v>46003.3706828704</v>
+        <v>45870.3628819444</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>193</v>
+        <v>45</v>
       </c>
       <c r="M139" s="3">
-        <v>45894.4525347222</v>
-      </c>
-      <c r="N139" s="3"/>
+        <v>45862.6188888889</v>
+      </c>
+      <c r="N139" s="3">
+        <v>45875.3688888889</v>
+      </c>
       <c r="O139" s="3"/>
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>2459339</v>
+        <v>2442028</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>38</v>
+        <v>237</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>38</v>
+        <v>237</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="I140" s="3"/>
       <c r="J140" s="3">
-        <v>46140.3839930556</v>
+        <v>46126.7431134259</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="L140" s="0" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="M140" s="3">
-        <v>45887.7442361111</v>
+        <v>45842.317025463</v>
       </c>
       <c r="N140" s="3"/>
       <c r="O140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>2456538</v>
+        <v>2439691</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="E141" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="F141" s="0" t="s">
-        <v>64</v>
-      </c>
       <c r="G141" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I141" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I141" s="3">
+        <v>45852.3770833333</v>
+      </c>
       <c r="J141" s="3">
-        <v>46126.7428356481</v>
+        <v>45838.6211342593</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="M141" s="3">
-        <v>45880.6643055556</v>
-      </c>
-      <c r="N141" s="3"/>
+        <v>45838.3761921296</v>
+      </c>
+      <c r="N141" s="3">
+        <v>45852.3770833333</v>
+      </c>
       <c r="O141" s="3"/>
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <v>2442028</v>
+        <v>2437239</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C142" s="0" t="s">
         <v>241</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>242</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I142" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I142" s="3">
+        <v>45870.3600462963</v>
+      </c>
       <c r="J142" s="3">
-        <v>46126.7431134259</v>
+        <v>45841.7026091435</v>
       </c>
       <c r="K142" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L142" s="0" t="s">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="M142" s="3">
-        <v>45842.317025463</v>
-      </c>
-      <c r="N142" s="3"/>
+        <v>45831.6933796296</v>
+      </c>
+      <c r="N142" s="3">
+        <v>45870.3600462963</v>
+      </c>
       <c r="O142" s="3"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2">
+        <v>2436707</v>
+      </c>
+      <c r="B143" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="C143" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="D143" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E143" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F143" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G143" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="H143" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="I143" s="3">
+        <v>45835.7284722222</v>
+      </c>
+      <c r="J143" s="3">
+        <v>46126.7436921296</v>
+      </c>
+      <c r="K143" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L143" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="M143" s="3">
+        <v>45828.8276273148</v>
+      </c>
+      <c r="N143" s="3">
+        <v>45835.7288773148</v>
+      </c>
+      <c r="O143" s="3"/>
     </row>
   </sheetData>
   <headerFooter/>

--- a/Solicitacoes.xlsx
+++ b/Solicitacoes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
   <si>
     <t>Protocolo</t>
   </si>
@@ -65,6 +65,24 @@
     <t>CORRECAO</t>
   </si>
   <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
+    <t>INSTABILIDADE MÓDULOS</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Suporte nível II</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>BCON</t>
   </si>
   <si>
@@ -74,28 +92,13 @@
     <t>Guia não disponível para execução de eventos por outros prestadores</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
-    <t>Suporte nível II</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Plataforma Lean</t>
   </si>
   <si>
-    <t>ADM</t>
-  </si>
-  <si>
     <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
   </si>
   <si>
     <t>HELPDESK - CUIDAR</t>
-  </si>
-  <si>
-    <t>AG</t>
   </si>
   <si>
     <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
@@ -800,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1506990705218" customWidth="1"/>
@@ -869,7 +872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2617170</v>
+        <v>2617538</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>15</v>
@@ -893,10 +896,10 @@
         <v>20</v>
       </c>
       <c r="I2" s="3">
-        <v>46290.4403703704</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="J2" s="3">
-        <v>46286.5862037037</v>
+        <v>46287.4164930556</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>21</v>
@@ -905,16 +908,16 @@
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>46286.5862037037</v>
+        <v>46287.4164930556</v>
       </c>
       <c r="N2" s="3">
-        <v>46290.4403703704</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2617057</v>
+        <v>2617170</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>15</v>
@@ -938,10 +941,10 @@
         <v>20</v>
       </c>
       <c r="I3" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="J3" s="3">
-        <v>46286.5879513889</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="K3" s="0" t="s">
         <v>21</v>
@@ -950,16 +953,16 @@
         <v>22</v>
       </c>
       <c r="M3" s="3">
-        <v>46286.4877199074</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="N3" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2615970</v>
+        <v>2617057</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>15</v>
@@ -968,25 +971,25 @@
         <v>15</v>
       </c>
       <c r="D4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="F4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="0" t="s">
         <v>27</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>28</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="J4" s="3">
-        <v>46287.3554017708</v>
+        <v>46286.5879513889</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>21</v>
@@ -995,25 +998,25 @@
         <v>22</v>
       </c>
       <c r="M4" s="3">
-        <v>46282.5089930556</v>
+        <v>46286.4877199074</v>
       </c>
       <c r="N4" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>2615871</v>
+        <v>2615970</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>17</v>
@@ -1022,724 +1025,724 @@
         <v>18</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="I5" s="3">
-        <v>46286.4024189815</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="J5" s="3">
-        <v>46286.3450115741</v>
+        <v>46287.3554017708</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M5" s="3">
-        <v>46282.4440856481</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="N5" s="3">
-        <v>46286.4024189815</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="O5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>2615590</v>
+        <v>2615871</v>
       </c>
       <c r="B6" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3">
+        <v>46286.4024189815</v>
+      </c>
+      <c r="J6" s="3">
+        <v>46286.3450115741</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="3">
-        <v>46287.5805092593</v>
-      </c>
-      <c r="J6" s="3">
-        <v>46281.7496990741</v>
-      </c>
-      <c r="K6" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M6" s="3">
-        <v>46281.6638425926</v>
+        <v>46282.4440856481</v>
       </c>
       <c r="N6" s="3">
-        <v>46287.5805092593</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>2614686</v>
+        <v>2615590</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F7" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="3">
+        <v>46287.5805092593</v>
+      </c>
+      <c r="J7" s="3">
+        <v>46281.7496990741</v>
+      </c>
+      <c r="K7" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="3">
-        <v>46321.5908449074</v>
-      </c>
-      <c r="J7" s="3">
-        <v>46282.4296635764</v>
-      </c>
-      <c r="K7" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="L7" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M7" s="3">
-        <v>46280.4450115741</v>
+        <v>46281.6638425926</v>
       </c>
       <c r="N7" s="3">
-        <v>46321.5908449074</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>2614334</v>
+        <v>2614686</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G8" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="3">
+        <v>46321.5908449074</v>
+      </c>
+      <c r="J8" s="3">
+        <v>46282.4296635764</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3">
-        <v>46283.5629166667</v>
-      </c>
-      <c r="J8" s="3">
-        <v>46283.4291666667</v>
-      </c>
-      <c r="K8" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="0" t="s">
-        <v>32</v>
-      </c>
       <c r="M8" s="3">
-        <v>46279.6749305556</v>
+        <v>46280.4450115741</v>
       </c>
       <c r="N8" s="3">
-        <v>46283.5629166667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2614135</v>
+        <v>2614334</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F9" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="0" t="s">
-        <v>43</v>
-      </c>
       <c r="H9" s="0" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3">
-        <v>46289.7291666667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="J9" s="3">
-        <v>46279.6123263889</v>
+        <v>46283.4291666667</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="M9" s="3">
-        <v>46279.5169097222</v>
+        <v>46279.6749305556</v>
       </c>
       <c r="N9" s="3">
-        <v>46289.7291666667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>2613646</v>
+        <v>2614135</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F10" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="3">
+        <v>46289.7291666667</v>
+      </c>
+      <c r="J10" s="3">
+        <v>46279.6123263889</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="3">
-        <v>46289.3876041667</v>
-      </c>
-      <c r="J10" s="3">
-        <v>46283.4346064815</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>45</v>
-      </c>
       <c r="M10" s="3">
-        <v>46276.6376041667</v>
+        <v>46279.5169097222</v>
       </c>
       <c r="N10" s="3">
-        <v>46289.3876041667</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>2613202</v>
+        <v>2613646</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I11" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="J11" s="3">
-        <v>46283.4707657407</v>
+        <v>46283.4346064815</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M11" s="3">
-        <v>46276.3827546296</v>
+        <v>46276.6376041667</v>
       </c>
       <c r="N11" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>2613026</v>
+        <v>2613202</v>
       </c>
       <c r="B12" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="0" t="s">
         <v>51</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="0" t="s">
-        <v>53</v>
       </c>
       <c r="H12" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="3">
-        <v>46281.6747800926</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="J12" s="3">
-        <v>46280.356624456</v>
+        <v>46283.4707657407</v>
       </c>
       <c r="K12" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M12" s="3">
-        <v>46275.6895601852</v>
+        <v>46276.3827546296</v>
       </c>
       <c r="N12" s="3">
-        <v>46281.6747800926</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>2612720</v>
+        <v>2613026</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>54</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I13" s="3">
-        <v>46316.6011689815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="J13" s="3">
-        <v>46279.4816203704</v>
+        <v>46287.6117592593</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M13" s="3">
-        <v>46275.4553356481</v>
+        <v>46275.6895601852</v>
       </c>
       <c r="N13" s="3">
-        <v>46316.6011689815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>2611881</v>
+        <v>2612720</v>
       </c>
       <c r="B14" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>58</v>
-      </c>
       <c r="H14" s="0" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I14" s="3">
-        <v>46279.6652314815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="J14" s="3">
-        <v>46274.7389930556</v>
+        <v>46279.4816203704</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="M14" s="3">
-        <v>46273.7485648148</v>
+        <v>46275.4553356481</v>
       </c>
       <c r="N14" s="3">
-        <v>46279.6652314815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2611848</v>
+        <v>2611881</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>59</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I15" s="3">
-        <v>46287.4094675926</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="J15" s="3">
-        <v>46276.5914583333</v>
+        <v>46274.7389930556</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="M15" s="3">
-        <v>46273.7127546296</v>
+        <v>46273.7485648148</v>
       </c>
       <c r="N15" s="3">
-        <v>46287.4094675926</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>2611692</v>
+        <v>2611848</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E16" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="0" t="s">
-        <v>62</v>
-      </c>
       <c r="H16" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I16" s="3">
-        <v>46279.4554861111</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="J16" s="3">
-        <v>46273.637278588</v>
+        <v>46276.5914583333</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M16" s="3">
-        <v>46273.6013194444</v>
+        <v>46273.7127546296</v>
       </c>
       <c r="N16" s="3">
-        <v>46279.4554861111</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>2611552</v>
+        <v>2611692</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E17" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="0" t="s">
-        <v>64</v>
-      </c>
       <c r="H17" s="0" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I17" s="3">
-        <v>46275.4327083333</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="J17" s="3">
-        <v>46273.5743171296</v>
+        <v>46273.637278588</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M17" s="3">
-        <v>46273.474375</v>
+        <v>46273.6013194444</v>
       </c>
       <c r="N17" s="3">
-        <v>46275.4327083333</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>2611551</v>
+        <v>2611552</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>65</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I18" s="3">
-        <v>46314.6183449074</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="J18" s="3">
-        <v>46274.3603356481</v>
+        <v>46273.5743171296</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="M18" s="3">
-        <v>46273.4725115741</v>
+        <v>46273.474375</v>
       </c>
       <c r="N18" s="3">
-        <v>46314.6183449074</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>2611539</v>
+        <v>2611551</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F19" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="0" t="s">
-        <v>67</v>
-      </c>
       <c r="H19" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I19" s="3">
-        <v>46275.4227083333</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="J19" s="3">
-        <v>46274.3607986111</v>
+        <v>46274.3603356481</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="M19" s="3">
-        <v>46273.464375</v>
+        <v>46273.4725115741</v>
       </c>
       <c r="N19" s="3">
-        <v>46275.4227083333</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>2611521</v>
+        <v>2611539</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D20" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="0" t="s">
-        <v>27</v>
-      </c>
       <c r="F20" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="G20" s="0" t="s">
-        <v>69</v>
-      </c>
       <c r="H20" s="0" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I20" s="3">
-        <v>46279.3705439815</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="J20" s="3">
-        <v>46273.7182003819</v>
+        <v>46274.3607986111</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M20" s="3">
-        <v>46273.4538773148</v>
+        <v>46273.464375</v>
       </c>
       <c r="N20" s="3">
-        <v>46279.3705439815</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>2610876</v>
+        <v>2611521</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G21" s="0" t="s">
         <v>70</v>
@@ -1748,10 +1751,10 @@
         <v>20</v>
       </c>
       <c r="I21" s="3">
-        <v>46276.3367592593</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="J21" s="3">
-        <v>46269.4406376505</v>
+        <v>46273.7182003819</v>
       </c>
       <c r="K21" s="0" t="s">
         <v>21</v>
@@ -1760,31 +1763,31 @@
         <v>22</v>
       </c>
       <c r="M21" s="3">
-        <v>46269.4200925926</v>
+        <v>46273.4538773148</v>
       </c>
       <c r="N21" s="3">
-        <v>46276.3367592593</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2610030</v>
+        <v>2610876</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>71</v>
@@ -1793,10 +1796,10 @@
         <v>20</v>
       </c>
       <c r="I22" s="3">
-        <v>46274.6271990741</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="J22" s="3">
-        <v>46268.3853071412</v>
+        <v>46269.4406376505</v>
       </c>
       <c r="K22" s="0" t="s">
         <v>21</v>
@@ -1805,31 +1808,31 @@
         <v>22</v>
       </c>
       <c r="M22" s="3">
-        <v>46267.7105324074</v>
+        <v>46269.4200925926</v>
       </c>
       <c r="N22" s="3">
-        <v>46274.6271990741</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>2609985</v>
+        <v>2610030</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G23" s="0" t="s">
         <v>72</v>
@@ -1838,118 +1841,118 @@
         <v>20</v>
       </c>
       <c r="I23" s="3">
-        <v>46301.4629166667</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="J23" s="3">
-        <v>46267.6774134606</v>
+        <v>46268.3853071412</v>
       </c>
       <c r="K23" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="M23" s="3">
-        <v>46267.67125</v>
+        <v>46267.7105324074</v>
       </c>
       <c r="N23" s="3">
-        <v>46301.4629166667</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>2609883</v>
+        <v>2609985</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="G24" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="3">
+        <v>46301.4629166667</v>
+      </c>
+      <c r="J24" s="3">
+        <v>46267.6774134606</v>
+      </c>
+      <c r="K24" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3">
-        <v>46309.7050347222</v>
-      </c>
-      <c r="J24" s="3">
-        <v>46280.4030439815</v>
-      </c>
-      <c r="K24" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="L24" s="0" t="s">
-        <v>40</v>
-      </c>
       <c r="M24" s="3">
-        <v>46267.6217013889</v>
+        <v>46267.67125</v>
       </c>
       <c r="N24" s="3">
-        <v>46309.7050347222</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>2609551</v>
+        <v>2609883</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E25" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="F25" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="0" t="s">
-        <v>77</v>
-      </c>
       <c r="H25" s="0" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3">
-        <v>46273.6887962963</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="J25" s="3">
-        <v>46267.355462963</v>
+        <v>46280.4030439815</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="M25" s="3">
-        <v>46267.355462963</v>
+        <v>46267.6217013889</v>
       </c>
       <c r="N25" s="3">
-        <v>46273.6887962963</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>2609107</v>
+        <v>2609551</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>15</v>
@@ -1958,13 +1961,13 @@
         <v>15</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>78</v>
@@ -1973,28 +1976,28 @@
         <v>20</v>
       </c>
       <c r="I26" s="3">
-        <v>46300.3339583333</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="J26" s="3">
-        <v>46268.4380070255</v>
+        <v>46267.355462963</v>
       </c>
       <c r="K26" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="M26" s="3">
-        <v>46266.4797916667</v>
+        <v>46267.355462963</v>
       </c>
       <c r="N26" s="3">
-        <v>46300.3339583333</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>2608731</v>
+        <v>2609107</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>15</v>
@@ -2003,13 +2006,13 @@
         <v>15</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G27" s="0" t="s">
         <v>79</v>
@@ -2018,28 +2021,28 @@
         <v>20</v>
       </c>
       <c r="I27" s="3">
-        <v>46279.4280671296</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="J27" s="3">
-        <v>46273.3513888889</v>
+        <v>46268.4380070255</v>
       </c>
       <c r="K27" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="M27" s="3">
-        <v>46265.6780671296</v>
+        <v>46266.4797916667</v>
       </c>
       <c r="N27" s="3">
-        <v>46279.4280671296</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>2608637</v>
+        <v>2608731</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>15</v>
@@ -2048,13 +2051,13 @@
         <v>15</v>
       </c>
       <c r="D28" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="0" t="s">
-        <v>27</v>
-      </c>
       <c r="F28" s="0" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>80</v>
@@ -2063,736 +2066,736 @@
         <v>20</v>
       </c>
       <c r="I28" s="3">
-        <v>46279.3644444444</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="J28" s="3">
-        <v>46266.3667347222</v>
+        <v>46273.3513888889</v>
       </c>
       <c r="K28" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M28" s="3">
-        <v>46265.6144444444</v>
+        <v>46265.6780671296</v>
       </c>
       <c r="N28" s="3">
-        <v>46279.3644444444</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>2607413</v>
+        <v>2608637</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="D29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="E29" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" s="0" t="s">
-        <v>82</v>
-      </c>
       <c r="H29" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I29" s="3">
+        <v>46304.6977777778</v>
+      </c>
       <c r="J29" s="3">
-        <v>46266.569212963</v>
+        <v>46287.4125274653</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="M29" s="3">
-        <v>46261.6163888889</v>
-      </c>
-      <c r="N29" s="3"/>
+        <v>46265.6144444444</v>
+      </c>
+      <c r="N29" s="3">
+        <v>46304.6977777778</v>
+      </c>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>2607198</v>
+        <v>2607413</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G30" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3">
+        <v>46266.569212963</v>
+      </c>
+      <c r="K30" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="L30" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="H30" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I30" s="3">
-        <v>46267.3546643518</v>
-      </c>
-      <c r="J30" s="3">
-        <v>46273.6204976852</v>
-      </c>
-      <c r="K30" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="L30" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M30" s="3">
-        <v>46261.4379976852</v>
-      </c>
-      <c r="N30" s="3">
-        <v>46267.3546643518</v>
-      </c>
+        <v>46261.6163888889</v>
+      </c>
+      <c r="N30" s="3"/>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>2606003</v>
+        <v>2607198</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>86</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I31" s="3">
-        <v>46265.3599537037</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="J31" s="3">
-        <v>46259.4993506944</v>
+        <v>46273.6204976852</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L31" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M31" s="3">
-        <v>46259.443287037</v>
+        <v>46261.4379976852</v>
       </c>
       <c r="N31" s="3">
-        <v>46290.75</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>2604815</v>
+        <v>2606003</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>87</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I32" s="3">
-        <v>46296.563587963</v>
+        <v>46265.3599537037</v>
       </c>
       <c r="J32" s="3">
-        <v>46268.6781365741</v>
+        <v>46259.4993506944</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M32" s="3">
-        <v>46255.4177546296</v>
+        <v>46259.443287037</v>
       </c>
       <c r="N32" s="3">
-        <v>46296.563587963</v>
+        <v>46290.75</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>2604500</v>
+        <v>2604815</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>88</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I33" s="3">
-        <v>46260.4812268519</v>
+        <v>46296.563587963</v>
       </c>
       <c r="J33" s="3">
-        <v>46258.3485416667</v>
+        <v>46268.6781365741</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="M33" s="3">
-        <v>46254.6270601852</v>
+        <v>46255.4177546296</v>
       </c>
       <c r="N33" s="3">
-        <v>46260.4812268519</v>
+        <v>46296.563587963</v>
       </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>2603668</v>
+        <v>2604500</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F34" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="G34" s="0" t="s">
-        <v>90</v>
-      </c>
       <c r="H34" s="0" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I34" s="3">
-        <v>46259.3446296296</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="J34" s="3">
-        <v>46258.6426851852</v>
+        <v>46258.3485416667</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L34" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M34" s="3">
-        <v>46253.427962963</v>
+        <v>46254.6270601852</v>
       </c>
       <c r="N34" s="3">
-        <v>46290.75</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>2602388</v>
+        <v>2603668</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D35" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E35" s="0" t="s">
-        <v>60</v>
-      </c>
       <c r="F35" s="0" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>91</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I35" s="3">
-        <v>46255.4166666667</v>
+        <v>46259.3446296296</v>
       </c>
       <c r="J35" s="3">
-        <v>46253.4900231482</v>
+        <v>46258.6426851852</v>
       </c>
       <c r="K35" s="0" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L35" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M35" s="3">
-        <v>46251.5527777778</v>
+        <v>46253.427962963</v>
       </c>
       <c r="N35" s="3">
-        <v>46255.4166666667</v>
+        <v>46290.75</v>
       </c>
       <c r="O35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>2601999</v>
+        <v>2602388</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D36" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="E36" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F36" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="G36" s="0" t="s">
-        <v>93</v>
-      </c>
       <c r="H36" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="I36" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I36" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="J36" s="3">
-        <v>46266.6188194444</v>
+        <v>46253.4900231482</v>
       </c>
       <c r="K36" s="0" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="M36" s="3">
-        <v>46248.7351273148</v>
-      </c>
-      <c r="N36" s="3"/>
+        <v>46251.5527777778</v>
+      </c>
+      <c r="N36" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="O36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>2600778</v>
+        <v>2601999</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D37" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="H37" s="0" t="s">
         <v>95</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="G37" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="H37" s="0" t="s">
-        <v>97</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3">
-        <v>46274.3780324074</v>
+        <v>46266.6188194444</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M37" s="3">
-        <v>46246.7171759259</v>
+        <v>46248.7351273148</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>2599732</v>
+        <v>2600778</v>
       </c>
       <c r="B38" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G38" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="H38" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="F38" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="H38" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I38" s="3">
-        <v>46251.4016203704</v>
-      </c>
+      <c r="I38" s="3"/>
       <c r="J38" s="3">
-        <v>46248.3419117245</v>
+        <v>46274.3780324074</v>
       </c>
       <c r="K38" s="0" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="M38" s="3">
-        <v>46245.4849537037</v>
-      </c>
-      <c r="N38" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>46246.7171759259</v>
+      </c>
+      <c r="N38" s="3"/>
       <c r="O38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2598987</v>
+        <v>2599732</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F39" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="G39" s="0" t="s">
-        <v>101</v>
-      </c>
       <c r="H39" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I39" s="3">
-        <v>46254.6856134259</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="J39" s="3">
-        <v>46251.536875</v>
+        <v>46248.3419117245</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="M39" s="3">
-        <v>46244.4564467593</v>
+        <v>46245.4849537037</v>
       </c>
       <c r="N39" s="3">
-        <v>46254.6856134259</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="O39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>2598910</v>
+        <v>2598987</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>102</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="I40" s="3">
-        <v>46254.6386574074</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="J40" s="3">
-        <v>46248.4760674769</v>
+        <v>46251.536875</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M40" s="3">
-        <v>46244.4094907407</v>
+        <v>46244.4564467593</v>
       </c>
       <c r="N40" s="3">
-        <v>46261.6103125</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="O40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>2598767</v>
+        <v>2598910</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C41" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="G41" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="H41" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="D41" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G41" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="H41" s="0" t="s">
-        <v>36</v>
-      </c>
       <c r="I41" s="3">
-        <v>46247.6666666667</v>
+        <v>46254.6386574074</v>
       </c>
       <c r="J41" s="3">
-        <v>46245.6608564815</v>
+        <v>46248.4760674769</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M41" s="3">
-        <v>46241.757962963</v>
+        <v>46244.4094907407</v>
       </c>
       <c r="N41" s="3">
-        <v>46247.6666666667</v>
+        <v>46261.6103125</v>
       </c>
       <c r="O41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>2597798</v>
+        <v>2598767</v>
       </c>
       <c r="B42" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="C42" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="G42" s="0" t="s">
-        <v>107</v>
-      </c>
       <c r="H42" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I42" s="3">
-        <v>46290.75</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="J42" s="3">
-        <v>46273.4412384259</v>
+        <v>46245.6608564815</v>
       </c>
       <c r="K42" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="M42" s="3">
-        <v>46240.4508912037</v>
+        <v>46241.757962963</v>
       </c>
       <c r="N42" s="3">
-        <v>46290.75</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="O42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>2597524</v>
+        <v>2597798</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C43" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="D43" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F43" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="G43" s="0" t="s">
-        <v>109</v>
-      </c>
       <c r="H43" s="0" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I43" s="3">
-        <v>46267.0453356481</v>
+        <v>46290.75</v>
       </c>
       <c r="J43" s="3">
-        <v>46259.4158333333</v>
+        <v>46273.4412384259</v>
       </c>
       <c r="K43" s="0" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M43" s="3">
-        <v>46239.6925347222</v>
+        <v>46240.4508912037</v>
       </c>
       <c r="N43" s="3">
-        <v>46267.0453356481</v>
+        <v>46290.75</v>
       </c>
       <c r="O43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>2597515</v>
+        <v>2597524</v>
       </c>
       <c r="B44" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>110</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I44" s="3">
-        <v>46266.4759953704</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="J44" s="3">
-        <v>46261.4097453704</v>
+        <v>46259.4158333333</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="M44" s="3">
-        <v>46239.6856134259</v>
+        <v>46239.6925347222</v>
       </c>
       <c r="N44" s="3">
-        <v>46266.4759953704</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="O44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>2597495</v>
+        <v>2597515</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>15</v>
@@ -2801,13 +2804,13 @@
         <v>15</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>111</v>
@@ -2816,493 +2819,493 @@
         <v>20</v>
       </c>
       <c r="I45" s="3">
-        <v>46252.3333333333</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="J45" s="3">
-        <v>46241.6523302083</v>
+        <v>46261.4097453704</v>
       </c>
       <c r="K45" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="M45" s="3">
-        <v>46239.6802199074</v>
+        <v>46239.6856134259</v>
       </c>
       <c r="N45" s="3">
-        <v>46245.5968865741</v>
-      </c>
-      <c r="O45" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>46266.4759953704</v>
+      </c>
+      <c r="O45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>2596882</v>
+        <v>2597495</v>
       </c>
       <c r="B46" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="F46" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="C46" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="F46" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="G46" s="0" t="s">
-        <v>114</v>
-      </c>
       <c r="H46" s="0" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I46" s="3">
-        <v>46280.3775578704</v>
+        <v>46252.3333333333</v>
       </c>
       <c r="J46" s="3">
-        <v>46267.6170023148</v>
+        <v>46241.6523302083</v>
       </c>
       <c r="K46" s="0" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M46" s="3">
-        <v>46238.7108912037</v>
+        <v>46239.6802199074</v>
       </c>
       <c r="N46" s="3">
-        <v>46280.3775578704</v>
-      </c>
-      <c r="O46" s="3"/>
+        <v>46245.5968865741</v>
+      </c>
+      <c r="O46" s="3">
+        <v>46252.3333333333</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>2596538</v>
+        <v>2596882</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>115</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I47" s="3">
-        <v>46273.960787037</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="J47" s="3">
-        <v>46286.3521412037</v>
+        <v>46267.6170023148</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M47" s="3">
-        <v>46238.4644791667</v>
+        <v>46238.7108912037</v>
       </c>
       <c r="N47" s="3">
-        <v>46273.960787037</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="O47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>2596407</v>
+        <v>2596538</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E48" s="0" t="s">
         <v>23</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>116</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I48" s="3">
-        <v>46248.6072106482</v>
+        <v>46273.960787037</v>
       </c>
       <c r="J48" s="3">
-        <v>46267.6164814815</v>
+        <v>46286.3521412037</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M48" s="3">
-        <v>46238.3780439815</v>
+        <v>46238.4644791667</v>
       </c>
       <c r="N48" s="3">
-        <v>46248.6072106482</v>
+        <v>46273.960787037</v>
       </c>
       <c r="O48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>2595510</v>
+        <v>2596407</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="D49" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E49" s="0" t="s">
-        <v>63</v>
-      </c>
       <c r="F49" s="0" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="G49" s="0" t="s">
         <v>117</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I49" s="3">
-        <v>46240.4984606481</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="J49" s="3">
-        <v>46245.3667592593</v>
+        <v>46267.6164814815</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M49" s="3">
-        <v>46234.6442939815</v>
+        <v>46238.3780439815</v>
       </c>
       <c r="N49" s="3">
-        <v>46240.4984606481</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="O49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>2595497</v>
+        <v>2595510</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>118</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I50" s="3">
-        <v>46240.4978240741</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="J50" s="3">
-        <v>46245.3669444444</v>
+        <v>46245.3667592593</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L50" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M50" s="3">
-        <v>46234.6436574074</v>
+        <v>46234.6442939815</v>
       </c>
       <c r="N50" s="3">
-        <v>46240.4978240741</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="O50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>2593529</v>
+        <v>2595497</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>119</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I51" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="J51" s="3">
-        <v>46233.4404570255</v>
+        <v>46245.3669444444</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L51" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M51" s="3">
-        <v>46231.6639930556</v>
+        <v>46234.6436574074</v>
       </c>
       <c r="N51" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="O51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>2593490</v>
+        <v>2593529</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I52" s="3">
-        <v>46239.6748032407</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="J52" s="3">
-        <v>46253.4905324074</v>
+        <v>46233.4404570255</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M52" s="3">
-        <v>46231.6518865741</v>
+        <v>46231.6639930556</v>
       </c>
       <c r="N52" s="3">
-        <v>46239.6748032407</v>
-      </c>
-      <c r="O52" s="3">
-        <v>46234.48125</v>
-      </c>
+        <v>46237.5806597222</v>
+      </c>
+      <c r="O52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>2593260</v>
+        <v>2593490</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I53" s="3">
-        <v>46241.6638888889</v>
+        <v>46239.6748032407</v>
       </c>
       <c r="J53" s="3">
-        <v>46267.614525463</v>
+        <v>46253.4905324074</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="M53" s="3">
-        <v>46231.435150463</v>
+        <v>46231.6518865741</v>
       </c>
       <c r="N53" s="3">
-        <v>46241.6638888889</v>
-      </c>
-      <c r="O53" s="3"/>
+        <v>46239.6748032407</v>
+      </c>
+      <c r="O53" s="3">
+        <v>46234.48125</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>2593216</v>
+        <v>2593260</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>122</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I54" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="I54" s="3">
+        <v>46241.6638888889</v>
+      </c>
       <c r="J54" s="3">
-        <v>46231.4047453704</v>
+        <v>46267.614525463</v>
       </c>
       <c r="K54" s="0" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="M54" s="3">
-        <v>46231.4011111111</v>
-      </c>
-      <c r="N54" s="3"/>
+        <v>46231.435150463</v>
+      </c>
+      <c r="N54" s="3">
+        <v>46241.6638888889</v>
+      </c>
       <c r="O54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>2592878</v>
+        <v>2593216</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="F55" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="G55" s="0" t="s">
-        <v>124</v>
-      </c>
       <c r="H55" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I55" s="3">
-        <v>46241.3504282407</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I55" s="3"/>
       <c r="J55" s="3">
-        <v>46230.6675740741</v>
+        <v>46231.4047453704</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="M55" s="3">
-        <v>46230.6004282407</v>
-      </c>
-      <c r="N55" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46231.4011111111</v>
+      </c>
+      <c r="N55" s="3"/>
       <c r="O55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>2592468</v>
+        <v>2592878</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>125</v>
@@ -3311,43 +3314,43 @@
         <v>20</v>
       </c>
       <c r="I56" s="3">
-        <v>46237.6038657407</v>
+        <v>46241.3504282407</v>
       </c>
       <c r="J56" s="3">
-        <v>46240.6136738773</v>
+        <v>46230.6675740741</v>
       </c>
       <c r="K56" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M56" s="3">
-        <v>46227.7107060185</v>
+        <v>46230.6004282407</v>
       </c>
       <c r="N56" s="3">
-        <v>46293.6033680556</v>
+        <v>46290.75</v>
       </c>
       <c r="O56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>2591596</v>
+        <v>2592468</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="D57" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E57" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F57" s="0" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G57" s="0" t="s">
         <v>126</v>
@@ -3356,596 +3359,596 @@
         <v>20</v>
       </c>
       <c r="I57" s="3">
-        <v>46238.7083333333</v>
+        <v>46237.6038657407</v>
       </c>
       <c r="J57" s="3">
-        <v>46267.3444803241</v>
+        <v>46240.6136738773</v>
       </c>
       <c r="K57" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="M57" s="3">
-        <v>46226.4797916667</v>
+        <v>46227.7107060185</v>
       </c>
       <c r="N57" s="3">
-        <v>46282.6141435185</v>
+        <v>46293.6033680556</v>
       </c>
       <c r="O57" s="3"/>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>2591284</v>
+        <v>2591596</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>127</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="I58" s="3">
-        <v>46266.3384837963</v>
+        <v>46238.7083333333</v>
       </c>
       <c r="J58" s="3">
-        <v>46225.7002398495</v>
+        <v>46267.3444803241</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M58" s="3">
-        <v>46225.6718171296</v>
+        <v>46226.4797916667</v>
       </c>
       <c r="N58" s="3">
-        <v>46266.3384837963</v>
+        <v>46282.6141435185</v>
       </c>
       <c r="O58" s="3"/>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>2588490</v>
+        <v>2591284</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>128</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I59" s="3">
-        <v>46230.722037037</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="J59" s="3">
-        <v>46231.4339699074</v>
+        <v>46225.7002398495</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M59" s="3">
-        <v>46218.4928703704</v>
+        <v>46225.6718171296</v>
       </c>
       <c r="N59" s="3">
-        <v>46230.722037037</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="O59" s="3"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2588025</v>
+        <v>2588490</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D60" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="E60" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="F60" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="G60" s="0" t="s">
-        <v>132</v>
-      </c>
       <c r="H60" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="I60" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="I60" s="3">
+        <v>46230.722037037</v>
+      </c>
       <c r="J60" s="3">
-        <v>46267.5903356482</v>
+        <v>46231.4339699074</v>
       </c>
       <c r="K60" s="0" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="M60" s="3">
-        <v>46217.612962963</v>
-      </c>
-      <c r="N60" s="3"/>
+        <v>46218.4928703704</v>
+      </c>
+      <c r="N60" s="3">
+        <v>46230.722037037</v>
+      </c>
       <c r="O60" s="3"/>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>2587849</v>
+        <v>2588025</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>133</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I61" s="3">
-        <v>46226.6083796296</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="I61" s="3"/>
       <c r="J61" s="3">
-        <v>46237.9144806713</v>
+        <v>46267.5903356482</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="M61" s="3">
-        <v>46217.4506597222</v>
-      </c>
-      <c r="N61" s="3">
-        <v>46226.6083796296</v>
-      </c>
+        <v>46217.612962963</v>
+      </c>
+      <c r="N61" s="3"/>
       <c r="O61" s="3"/>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>2587713</v>
+        <v>2587849</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>134</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I62" s="3">
-        <v>46218.7408680556</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="J62" s="3">
-        <v>46230.4199074074</v>
+        <v>46237.9144806713</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M62" s="3">
-        <v>46217.3658680556</v>
+        <v>46217.4506597222</v>
       </c>
       <c r="N62" s="3">
-        <v>46218.7408680556</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>2587585</v>
+        <v>2587713</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D63" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E63" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F63" s="0" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>135</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I63" s="3">
-        <v>46220.6264583333</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="J63" s="3">
-        <v>46259.4474884259</v>
+        <v>46230.4199074074</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M63" s="3">
-        <v>46216.7097916667</v>
+        <v>46217.3658680556</v>
       </c>
       <c r="N63" s="3">
-        <v>46220.6264583333</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="O63" s="3"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2587006</v>
+        <v>2587585</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>136</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I64" s="3">
-        <v>46217.7289699074</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="J64" s="3">
-        <v>46227.4549884259</v>
+        <v>46259.4474884259</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M64" s="3">
-        <v>46213.7239236111</v>
+        <v>46216.7097916667</v>
       </c>
       <c r="N64" s="3">
-        <v>46217.7289699074</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="O64" s="3"/>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2586984</v>
+        <v>2587006</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>137</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I65" s="3">
-        <v>46295.7416550926</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="J65" s="3">
-        <v>46273.4946180556</v>
+        <v>46227.4549884259</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M65" s="3">
-        <v>46213.6971527778</v>
+        <v>46213.7239236111</v>
       </c>
       <c r="N65" s="3">
-        <v>46295.7416550926</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="O65" s="3"/>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>2586910</v>
+        <v>2586984</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="F66" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" s="0" t="s">
         <v>138</v>
       </c>
-      <c r="G66" s="0" t="s">
-        <v>139</v>
-      </c>
       <c r="H66" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I66" s="3">
-        <v>46226.5833333333</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="J66" s="3">
-        <v>46230.4194212963</v>
+        <v>46273.4946180556</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M66" s="3">
-        <v>46213.6245833333</v>
+        <v>46213.6971527778</v>
       </c>
       <c r="N66" s="3">
-        <v>46226.5833333333</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>2586651</v>
+        <v>2586910</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="D67" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E67" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E67" s="0" t="s">
-        <v>60</v>
-      </c>
       <c r="F67" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="G67" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="G67" s="0" t="s">
-        <v>141</v>
-      </c>
       <c r="H67" s="0" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I67" s="3">
-        <v>46218.7157407407</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="J67" s="3">
-        <v>46213.3824074074</v>
+        <v>46230.4194212963</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M67" s="3">
-        <v>46213.3824074074</v>
+        <v>46213.6245833333</v>
       </c>
       <c r="N67" s="3">
-        <v>46218.7157407407</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="O67" s="3"/>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>2586187</v>
+        <v>2586651</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D68" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="F68" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="G68" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="E68" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="G68" s="0" t="s">
-        <v>143</v>
-      </c>
       <c r="H68" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="I68" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I68" s="3">
+        <v>46218.7157407407</v>
+      </c>
       <c r="J68" s="3">
-        <v>46219.3850231481</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="M68" s="3">
-        <v>46211.7697337963</v>
-      </c>
-      <c r="N68" s="3"/>
+        <v>46213.3824074074</v>
+      </c>
+      <c r="N68" s="3">
+        <v>46218.7157407407</v>
+      </c>
       <c r="O68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>2585888</v>
+        <v>2586187</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>144</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I69" s="3">
-        <v>46217.4119907407</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="I69" s="3"/>
       <c r="J69" s="3">
-        <v>46217.5003587963</v>
+        <v>46219.3850231481</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="M69" s="3">
-        <v>46211.4953240741</v>
-      </c>
-      <c r="N69" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46211.7697337963</v>
+      </c>
+      <c r="N69" s="3"/>
       <c r="O69" s="3"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>2585424</v>
+        <v>2585888</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="G70" s="0" t="s">
         <v>145</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="I70" s="3">
-        <v>46223.3927199074</v>
+        <v>46217.4119907407</v>
       </c>
       <c r="J70" s="3">
-        <v>46234.4964930556</v>
+        <v>46217.5003587963</v>
       </c>
       <c r="K70" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="M70" s="3">
-        <v>46210.6427199074</v>
+        <v>46211.4953240741</v>
       </c>
       <c r="N70" s="3">
         <v>46290.75</v>
@@ -3954,1981 +3957,1981 @@
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>2584638</v>
+        <v>2585424</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E71" s="0" t="s">
         <v>23</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="G71" s="0" t="s">
         <v>146</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I71" s="3">
-        <v>46213.4171527778</v>
+        <v>46223.3927199074</v>
       </c>
       <c r="J71" s="3">
-        <v>46213.4090859607</v>
+        <v>46234.4964930556</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M71" s="3">
-        <v>46209.5016203704</v>
+        <v>46210.6427199074</v>
       </c>
       <c r="N71" s="3">
-        <v>46232.3874884259</v>
+        <v>46290.75</v>
       </c>
       <c r="O71" s="3"/>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>2584397</v>
+        <v>2584638</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D72" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E72" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="F72" s="0" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>147</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="I72" s="3">
-        <v>46212.6757175926</v>
+        <v>46213.4171527778</v>
       </c>
       <c r="J72" s="3">
-        <v>46213.3741550926</v>
+        <v>46213.4090859607</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="L72" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M72" s="3">
-        <v>46209.3423842593</v>
+        <v>46209.5016203704</v>
       </c>
       <c r="N72" s="3">
-        <v>46212.6757175926</v>
+        <v>46232.3874884259</v>
       </c>
       <c r="O72" s="3"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>2584167</v>
+        <v>2584397</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D73" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E73" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F73" s="0" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>148</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I73" s="3">
-        <v>46246.7216435185</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="J73" s="3">
-        <v>46247.4396759259</v>
+        <v>46213.3741550926</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M73" s="3">
-        <v>46206.6383101852</v>
+        <v>46209.3423842593</v>
       </c>
       <c r="N73" s="3">
-        <v>46246.7216435185</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="O73" s="3"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2583950</v>
+        <v>2584167</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>149</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I74" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I74" s="3">
+        <v>46246.7216435185</v>
+      </c>
       <c r="J74" s="3">
-        <v>46273.4100925926</v>
+        <v>46247.4396759259</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="M74" s="3">
-        <v>46206.4623148148</v>
-      </c>
-      <c r="N74" s="3"/>
+        <v>46206.6383101852</v>
+      </c>
+      <c r="N74" s="3">
+        <v>46246.7216435185</v>
+      </c>
       <c r="O74" s="3"/>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2583447</v>
+        <v>2583950</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>150</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I75" s="3">
-        <v>46245.6724189815</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I75" s="3"/>
       <c r="J75" s="3">
-        <v>46265.3645138889</v>
+        <v>46273.4100925926</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="M75" s="3">
-        <v>46205.5752083333</v>
-      </c>
-      <c r="N75" s="3">
-        <v>46245.6724189815</v>
-      </c>
+        <v>46206.4623148148</v>
+      </c>
+      <c r="N75" s="3"/>
       <c r="O75" s="3"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>2583382</v>
+        <v>2583447</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D76" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="E76" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F76" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="G76" s="0" t="s">
-        <v>152</v>
-      </c>
       <c r="H76" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="I76" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I76" s="3">
+        <v>46205.7916666667</v>
+      </c>
       <c r="J76" s="3">
-        <v>46279.4689699074</v>
+        <v>46265.3645138889</v>
       </c>
       <c r="K76" s="0" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="M76" s="3">
-        <v>46205.4905092593</v>
-      </c>
-      <c r="N76" s="3"/>
+        <v>46205.5752083333</v>
+      </c>
+      <c r="N76" s="3">
+        <v>46245.6724189815</v>
+      </c>
       <c r="O76" s="3"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>2582452</v>
+        <v>2583382</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>26</v>
+        <v>152</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="G77" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="H77" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="H77" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I77" s="3">
-        <v>46244.4166666667</v>
-      </c>
+      <c r="I77" s="3"/>
       <c r="J77" s="3">
-        <v>46204.7763078704</v>
+        <v>46279.4689699074</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="M77" s="3">
-        <v>46203.8250810185</v>
-      </c>
-      <c r="N77" s="3">
-        <v>46244.4166666667</v>
-      </c>
+        <v>46205.4905092593</v>
+      </c>
+      <c r="N77" s="3"/>
       <c r="O77" s="3"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>2582352</v>
+        <v>2582452</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D78" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E78" s="0" t="s">
-        <v>27</v>
-      </c>
       <c r="F78" s="0" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>155</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I78" s="3">
-        <v>46244.340775463</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="J78" s="3">
-        <v>46204.7761805556</v>
+        <v>46204.7763078704</v>
       </c>
       <c r="K78" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M78" s="3">
-        <v>46203.6741087963</v>
+        <v>46203.8250810185</v>
       </c>
       <c r="N78" s="3">
-        <v>46244.340775463</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="O78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2579299</v>
+        <v>2582352</v>
       </c>
       <c r="B79" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" s="0" t="s">
         <v>156</v>
       </c>
-      <c r="C79" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="D79" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="E79" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F79" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="G79" s="0" t="s">
-        <v>157</v>
-      </c>
       <c r="H79" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I79" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I79" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="J79" s="3">
-        <v>46204.3277777778</v>
+        <v>46204.7761805556</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="M79" s="3">
-        <v>46196.4165162037</v>
-      </c>
-      <c r="N79" s="3"/>
+        <v>46203.6741087963</v>
+      </c>
+      <c r="N79" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>2576326</v>
+        <v>2579299</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>158</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I80" s="3">
-        <v>46192.7916666667</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I80" s="3"/>
       <c r="J80" s="3">
-        <v>46230.6812731481</v>
+        <v>46204.3277777778</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M80" s="3">
-        <v>46189.3995833333</v>
+        <v>46196.4165162037</v>
       </c>
       <c r="N80" s="3"/>
       <c r="O80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>2574153</v>
+        <v>2576326</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>159</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I81" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I81" s="3">
+        <v>46192.7916666667</v>
+      </c>
       <c r="J81" s="3">
-        <v>46204.3218402778</v>
+        <v>46230.6812731481</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M81" s="3">
-        <v>46183.4711226852</v>
+        <v>46189.3995833333</v>
       </c>
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>2572707</v>
+        <v>2574153</v>
       </c>
       <c r="B82" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G82" s="0" t="s">
         <v>160</v>
       </c>
-      <c r="C82" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="D82" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E82" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="F82" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="G82" s="0" t="s">
-        <v>162</v>
-      </c>
       <c r="H82" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I82" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I82" s="3"/>
       <c r="J82" s="3">
-        <v>46188.4629166667</v>
+        <v>46204.3218402778</v>
       </c>
       <c r="K82" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="M82" s="3">
-        <v>46178.7298148148</v>
-      </c>
-      <c r="N82" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>46183.4711226852</v>
+      </c>
+      <c r="N82" s="3"/>
       <c r="O82" s="3"/>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>2570274</v>
+        <v>2572707</v>
       </c>
       <c r="B83" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="F83" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="G83" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="C83" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="D83" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="E83" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F83" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="G83" s="0" t="s">
-        <v>164</v>
-      </c>
       <c r="H83" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I83" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I83" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="J83" s="3">
-        <v>46204.3220138889</v>
+        <v>46188.4629166667</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="M83" s="3">
-        <v>46171.6563773148</v>
-      </c>
-      <c r="N83" s="3"/>
+        <v>46178.7298148148</v>
+      </c>
+      <c r="N83" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="O83" s="3"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>2562116</v>
+        <v>2570274</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>165</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I84" s="3"/>
       <c r="J84" s="3">
-        <v>46160.7191666667</v>
+        <v>46204.3220138889</v>
       </c>
       <c r="K84" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M84" s="3">
-        <v>46154.3432638889</v>
+        <v>46171.6563773148</v>
       </c>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>2558553</v>
+        <v>2562116</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="E85" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>166</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I85" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I85" s="3"/>
       <c r="J85" s="3">
-        <v>46154.5888773148</v>
+        <v>46160.7191666667</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="M85" s="3">
-        <v>46146.3561805556</v>
-      </c>
-      <c r="N85" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>46154.3432638889</v>
+      </c>
+      <c r="N85" s="3"/>
       <c r="O85" s="3"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>2556271</v>
+        <v>2558553</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F86" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G86" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="G86" s="0" t="s">
-        <v>168</v>
-      </c>
       <c r="H86" s="0" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I86" s="3">
-        <v>46141.4297453704</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="J86" s="3">
-        <v>46139.9871412037</v>
+        <v>46154.5888773148</v>
       </c>
       <c r="K86" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L86" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M86" s="3">
-        <v>46139.471412037</v>
+        <v>46146.3561805556</v>
       </c>
       <c r="N86" s="3">
-        <v>46141.4901157407</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="O86" s="3"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>2556211</v>
+        <v>2556271</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E87" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>169</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I87" s="3">
-        <v>46150.6617476852</v>
+        <v>46141.4297453704</v>
       </c>
       <c r="J87" s="3">
-        <v>46146.3663773148</v>
+        <v>46139.9871412037</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="M87" s="3">
-        <v>46139.4325810185</v>
+        <v>46139.471412037</v>
       </c>
       <c r="N87" s="3">
-        <v>46150.6617476852</v>
+        <v>46141.4901157407</v>
       </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>2556029</v>
+        <v>2556211</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G88" s="0" t="s">
         <v>170</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I88" s="3">
-        <v>46150.5</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="J88" s="3">
-        <v>46146.401875</v>
+        <v>46146.3663773148</v>
       </c>
       <c r="K88" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M88" s="3">
-        <v>46138.757337963</v>
+        <v>46139.4325810185</v>
       </c>
       <c r="N88" s="3">
-        <v>46154.6616087963</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="O88" s="3"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>2554341</v>
+        <v>2556029</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>171</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I89" s="3">
-        <v>46136.3599768519</v>
+        <v>46150.5</v>
       </c>
       <c r="J89" s="3">
-        <v>46135.6585185185</v>
+        <v>46146.401875</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="M89" s="3">
-        <v>46134.4016435185</v>
+        <v>46138.757337963</v>
       </c>
       <c r="N89" s="3">
-        <v>46136.3599768519</v>
+        <v>46154.6616087963</v>
       </c>
       <c r="O89" s="3"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2547638</v>
+        <v>2554341</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>172</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I90" s="3">
-        <v>46150.3473611111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="J90" s="3">
-        <v>46119.5010069444</v>
+        <v>46135.6585185185</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="M90" s="3">
-        <v>46114.4931944444</v>
+        <v>46134.4016435185</v>
       </c>
       <c r="N90" s="3">
-        <v>46150.3473611111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>2537054</v>
+        <v>2547638</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>173</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I91" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="J91" s="3">
-        <v>46090.3698263889</v>
+        <v>46119.5010069444</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="M91" s="3">
-        <v>46087.5797569444</v>
+        <v>46114.4931944444</v>
       </c>
       <c r="N91" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>2531696</v>
+        <v>2537054</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>174</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I92" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I92" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="J92" s="3">
-        <v>46204.3216782407</v>
+        <v>46090.3698263889</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="M92" s="3">
-        <v>46076.5833912037</v>
-      </c>
-      <c r="N92" s="3"/>
+        <v>46087.5797569444</v>
+      </c>
+      <c r="N92" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="O92" s="3"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>2530739</v>
+        <v>2531696</v>
       </c>
       <c r="B93" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C93" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G93" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="C93" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="D93" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="E93" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F93" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="G93" s="0" t="s">
-        <v>177</v>
-      </c>
       <c r="H93" s="0" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="I93" s="3"/>
       <c r="J93" s="3">
-        <v>46218.6914940625</v>
+        <v>46204.3216782407</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M93" s="3">
-        <v>46072.6973148148</v>
+        <v>46076.5833912037</v>
       </c>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>2529639</v>
+        <v>2530739</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>33</v>
+        <v>177</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="E94" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>178</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I94" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="I94" s="3"/>
       <c r="J94" s="3">
-        <v>46072.6891666667</v>
+        <v>46218.6914940625</v>
       </c>
       <c r="K94" s="0" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="L94" s="0" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="M94" s="3">
-        <v>46069.5930902778</v>
-      </c>
-      <c r="N94" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>46072.6973148148</v>
+      </c>
+      <c r="N94" s="3"/>
       <c r="O94" s="3"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>2529591</v>
+        <v>2529639</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>179</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I95" s="3">
-        <v>46108.5968055556</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="J95" s="3">
-        <v>46126.6875</v>
+        <v>46072.6891666667</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M95" s="3">
-        <v>46069.4509722222</v>
+        <v>46069.5930902778</v>
       </c>
       <c r="N95" s="3">
-        <v>46108.5968055556</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="O95" s="3"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>2528858</v>
+        <v>2529591</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>180</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I96" s="3">
-        <v>46107.3861458333</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="J96" s="3">
-        <v>46087.6277662037</v>
+        <v>46126.6875</v>
       </c>
       <c r="K96" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L96" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M96" s="3">
-        <v>46065.7194791667</v>
+        <v>46069.4509722222</v>
       </c>
       <c r="N96" s="3">
-        <v>46107.3861458333</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="O96" s="3"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>2525312</v>
+        <v>2528858</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>181</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I97" s="3">
-        <v>46070.5877314815</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="J97" s="3">
-        <v>46062.7587037037</v>
+        <v>46087.6277662037</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M97" s="3">
-        <v>46058.3585648148</v>
+        <v>46065.7194791667</v>
       </c>
       <c r="N97" s="3">
-        <v>46070.5877314815</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="O97" s="3"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>2525272</v>
+        <v>2525312</v>
       </c>
       <c r="B98" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F98" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="G98" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="C98" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="D98" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="E98" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F98" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="G98" s="0" t="s">
-        <v>184</v>
-      </c>
       <c r="H98" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I98" s="3">
-        <v>46203.7916666667</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="J98" s="3">
-        <v>46126.7441782407</v>
+        <v>46062.7587037037</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="M98" s="3">
-        <v>46058.2883101852</v>
-      </c>
-      <c r="N98" s="3"/>
+        <v>46058.3585648148</v>
+      </c>
+      <c r="N98" s="3">
+        <v>46070.5877314815</v>
+      </c>
       <c r="O98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>2524577</v>
+        <v>2525272</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>185</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="I99" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I99" s="3">
+        <v>46203.7916666667</v>
+      </c>
       <c r="J99" s="3">
-        <v>46267.4298180903</v>
+        <v>46126.7441782407</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M99" s="3">
-        <v>46056.697349537</v>
+        <v>46058.2883101852</v>
       </c>
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>2524373</v>
+        <v>2524577</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G100" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="H100" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="H100" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I100" s="3">
-        <v>46087.3854513889</v>
-      </c>
+      <c r="I100" s="3"/>
       <c r="J100" s="3">
-        <v>46056.6543865741</v>
+        <v>46267.4298180903</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="L100" s="0" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M100" s="3">
-        <v>46056.5937847222</v>
-      </c>
-      <c r="N100" s="3">
-        <v>46087.3854513889</v>
-      </c>
+        <v>46056.697349537</v>
+      </c>
+      <c r="N100" s="3"/>
       <c r="O100" s="3"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>2524062</v>
+        <v>2524373</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="D101" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E101" s="0" t="s">
-        <v>63</v>
-      </c>
       <c r="F101" s="0" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>188</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I101" s="3">
-        <v>46057.7412615741</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="J101" s="3">
-        <v>46056.6210300926</v>
+        <v>46056.6543865741</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="M101" s="3">
-        <v>46056.3662615741</v>
+        <v>46056.5937847222</v>
       </c>
       <c r="N101" s="3">
-        <v>46057.7412615741</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>2523635</v>
+        <v>2524062</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>189</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I102" s="3">
-        <v>46059.4164236111</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="J102" s="3">
-        <v>46055.6034837963</v>
+        <v>46056.6210300926</v>
       </c>
       <c r="K102" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L102" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M102" s="3">
-        <v>46055.4997569444</v>
+        <v>46056.3662615741</v>
       </c>
       <c r="N102" s="3">
-        <v>46059.4164236111</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>2523602</v>
+        <v>2523635</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>190</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I103" s="3">
-        <v>46093.6246643519</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="J103" s="3">
-        <v>46056.5784027778</v>
+        <v>46055.6034837963</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M103" s="3">
-        <v>46055.4788310185</v>
+        <v>46055.4997569444</v>
       </c>
       <c r="N103" s="3">
-        <v>46093.6246643519</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>2521645</v>
+        <v>2523602</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="D104" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E104" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E104" s="0" t="s">
-        <v>113</v>
-      </c>
       <c r="F104" s="0" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>191</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="I104" s="3">
-        <v>46062.5</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="J104" s="3">
-        <v>46050.3426763542</v>
+        <v>46056.5784027778</v>
       </c>
       <c r="K104" s="0" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M104" s="3">
-        <v>46049.7714236111</v>
-      </c>
-      <c r="N104" s="3"/>
+        <v>46055.4788310185</v>
+      </c>
+      <c r="N104" s="3">
+        <v>46093.6246643519</v>
+      </c>
       <c r="O104" s="3"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>2521079</v>
+        <v>2521645</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>192</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="I105" s="3">
-        <v>46052.6666666667</v>
+        <v>46062.5</v>
       </c>
       <c r="J105" s="3">
-        <v>46056.6197800926</v>
+        <v>46050.3426763542</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M105" s="3">
-        <v>46048.7684490741</v>
-      </c>
-      <c r="N105" s="3">
-        <v>46061.6309722222</v>
-      </c>
+        <v>46049.7714236111</v>
+      </c>
+      <c r="N105" s="3"/>
       <c r="O105" s="3"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>2520048</v>
+        <v>2521079</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>176</v>
+        <v>99</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>193</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I106" s="3">
-        <v>46057.5</v>
+        <v>46052.6666666667</v>
       </c>
       <c r="J106" s="3">
-        <v>46052.5774305556</v>
+        <v>46056.6197800926</v>
       </c>
       <c r="K106" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L106" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="M106" s="3">
-        <v>46045.3325578704</v>
+        <v>46048.7684490741</v>
       </c>
       <c r="N106" s="3">
-        <v>46057.5</v>
+        <v>46061.6309722222</v>
       </c>
       <c r="O106" s="3"/>
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>2519904</v>
+        <v>2520048</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>194</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I107" s="3">
-        <v>46084.7217939815</v>
+        <v>46057.5</v>
       </c>
       <c r="J107" s="3">
-        <v>46044.7413888889</v>
+        <v>46052.5774305556</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M107" s="3">
-        <v>46044.6384606482</v>
+        <v>46045.3325578704</v>
       </c>
       <c r="N107" s="3">
-        <v>46084.7217939815</v>
+        <v>46057.5</v>
       </c>
       <c r="O107" s="3"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>2519523</v>
+        <v>2519904</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>33</v>
+        <v>177</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>195</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I108" s="3">
-        <v>46076.5902777778</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="J108" s="3">
-        <v>46048.4589814815</v>
+        <v>46044.7413888889</v>
       </c>
       <c r="K108" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L108" s="0" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M108" s="3">
-        <v>46043.7362847222</v>
+        <v>46044.6384606482</v>
       </c>
       <c r="N108" s="3">
-        <v>46077.380775463</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>2519383</v>
+        <v>2519523</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D109" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E109" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E109" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="F109" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>196</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I109" s="3">
-        <v>46076.399224537</v>
+        <v>46076.5902777778</v>
       </c>
       <c r="J109" s="3">
-        <v>46048.4599305556</v>
+        <v>46048.4589814815</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M109" s="3">
-        <v>46043.6075578704</v>
+        <v>46043.7362847222</v>
       </c>
       <c r="N109" s="3">
-        <v>46076.399224537</v>
+        <v>46077.380775463</v>
       </c>
       <c r="O109" s="3"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>2519284</v>
+        <v>2519383</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="D110" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E110" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E110" s="0" t="s">
-        <v>63</v>
-      </c>
       <c r="F110" s="0" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I110" s="3">
-        <v>46049.3982986111</v>
+        <v>46076.399224537</v>
       </c>
       <c r="J110" s="3">
-        <v>46043.742337963</v>
+        <v>46048.4599305556</v>
       </c>
       <c r="K110" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L110" s="0" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="M110" s="3">
-        <v>46043.4816319444</v>
+        <v>46043.6075578704</v>
       </c>
       <c r="N110" s="3">
-        <v>46049.3982986111</v>
+        <v>46076.399224537</v>
       </c>
       <c r="O110" s="3"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>2518650</v>
+        <v>2519284</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>176</v>
+        <v>99</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I111" s="3">
-        <v>46072.3536921296</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="J111" s="3">
-        <v>46043.8185648148</v>
+        <v>46043.742337963</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M111" s="3">
-        <v>46042.3536921296</v>
+        <v>46043.4816319444</v>
       </c>
       <c r="N111" s="3">
-        <v>46080.437025463</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="O111" s="3"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>2513117</v>
+        <v>2518650</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>98</v>
+        <v>177</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>198</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I112" s="3">
-        <v>46031.4922800926</v>
+        <v>46072.3536921296</v>
       </c>
       <c r="J112" s="3">
-        <v>46028.3500347222</v>
+        <v>46043.8185648148</v>
       </c>
       <c r="K112" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="M112" s="3">
-        <v>46027.6381134259</v>
+        <v>46042.3536921296</v>
       </c>
       <c r="N112" s="3">
-        <v>46031.4922800926</v>
+        <v>46080.437025463</v>
       </c>
       <c r="O112" s="3"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>2512883</v>
+        <v>2513117</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>24</v>
+        <v>168</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>199</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I113" s="3">
-        <v>46037.6340972222</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="J113" s="3">
-        <v>46129.4199421296</v>
+        <v>46028.3500347222</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="M113" s="3">
-        <v>46027.4049305556</v>
+        <v>46027.6381134259</v>
       </c>
       <c r="N113" s="3">
-        <v>46141.6335300926</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="O113" s="3"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>2512542</v>
+        <v>2512883</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>200</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I114" s="3">
-        <v>46036.5</v>
+        <v>46037.6340972222</v>
       </c>
       <c r="J114" s="3">
-        <v>46024.5900925926</v>
+        <v>46129.4199421296</v>
       </c>
       <c r="K114" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L114" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M114" s="3">
-        <v>46022.6836342593</v>
+        <v>46027.4049305556</v>
       </c>
       <c r="N114" s="3">
-        <v>46036.5</v>
+        <v>46141.6335300926</v>
       </c>
       <c r="O114" s="3"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>2512541</v>
+        <v>2512542</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>201</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I115" s="3">
         <v>46036.5</v>
       </c>
       <c r="J115" s="3">
-        <v>46022.7128356481</v>
+        <v>46024.5900925926</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M115" s="3">
-        <v>46022.6762615741</v>
+        <v>46022.6836342593</v>
       </c>
       <c r="N115" s="3">
         <v>46036.5</v>
@@ -5937,1214 +5940,1259 @@
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>2509014</v>
+        <v>2512541</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>202</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I116" s="3">
-        <v>46044.7250578704</v>
+        <v>46036.5</v>
       </c>
       <c r="J116" s="3">
-        <v>46022.6138541667</v>
+        <v>46022.7128356481</v>
       </c>
       <c r="K116" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L116" s="0" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="M116" s="3">
-        <v>46008.454224537</v>
+        <v>46022.6762615741</v>
       </c>
       <c r="N116" s="3">
-        <v>46045.4708564815</v>
+        <v>46036.5</v>
       </c>
       <c r="O116" s="3"/>
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>2506714</v>
+        <v>2509014</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>203</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I117" s="3">
-        <v>46038.7073032407</v>
+        <v>46044.7250578704</v>
       </c>
       <c r="J117" s="3">
-        <v>46044.7372337963</v>
+        <v>46022.6138541667</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M117" s="3">
-        <v>46002.4364699074</v>
+        <v>46008.454224537</v>
       </c>
       <c r="N117" s="3">
-        <v>46038.7073032407</v>
+        <v>46045.4708564815</v>
       </c>
       <c r="O117" s="3"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>2506599</v>
+        <v>2506714</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>204</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I118" s="3">
-        <v>46037.61375</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="J118" s="3">
-        <v>46052.3252083333</v>
+        <v>46044.7372337963</v>
       </c>
       <c r="K118" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L118" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M118" s="3">
-        <v>46002.3429166667</v>
+        <v>46002.4364699074</v>
       </c>
       <c r="N118" s="3">
-        <v>46037.61375</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="O118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>2506311</v>
+        <v>2506599</v>
       </c>
       <c r="B119" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="C119" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D119" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="F119" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="G119" s="0" t="s">
         <v>205</v>
       </c>
-      <c r="C119" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="D119" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="E119" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="F119" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="G119" s="0" t="s">
-        <v>206</v>
-      </c>
       <c r="H119" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I119" s="3">
-        <v>46013.7291666667</v>
+        <v>46037.61375</v>
       </c>
       <c r="J119" s="3">
-        <v>46013.461875</v>
+        <v>46052.3252083333</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="M119" s="3">
-        <v>46001.5219328704</v>
+        <v>46002.3429166667</v>
       </c>
       <c r="N119" s="3">
-        <v>46013.7291666667</v>
+        <v>46037.61375</v>
       </c>
       <c r="O119" s="3"/>
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <v>2506102</v>
+        <v>2506311</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>207</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I120" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I120" s="3">
+        <v>46013.7291666667</v>
+      </c>
       <c r="J120" s="3">
-        <v>46241.5032638889</v>
+        <v>46013.461875</v>
       </c>
       <c r="K120" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L120" s="0" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="M120" s="3">
-        <v>46001.3800578704</v>
-      </c>
-      <c r="N120" s="3"/>
+        <v>46001.5219328704</v>
+      </c>
+      <c r="N120" s="3">
+        <v>46013.7291666667</v>
+      </c>
       <c r="O120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <v>2502589</v>
+        <v>2506102</v>
       </c>
       <c r="B121" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="C121" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="D121" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F121" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="G121" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="C121" s="0" t="s">
-        <v>208</v>
-      </c>
-      <c r="D121" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E121" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="F121" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="G121" s="0" t="s">
-        <v>209</v>
-      </c>
       <c r="H121" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I121" s="3">
-        <v>46029.6634375</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I121" s="3"/>
       <c r="J121" s="3">
-        <v>46014.6931018519</v>
+        <v>46241.5032638889</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M121" s="3">
-        <v>45993.3791087963</v>
-      </c>
-      <c r="N121" s="3">
-        <v>46029.6634375</v>
-      </c>
+        <v>46001.3800578704</v>
+      </c>
+      <c r="N121" s="3"/>
       <c r="O121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <v>2502438</v>
+        <v>2502589</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>98</v>
+        <v>209</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="D122" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E122" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E122" s="0" t="s">
-        <v>63</v>
-      </c>
       <c r="F122" s="0" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>210</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I122" s="3">
-        <v>46037.3801388889</v>
+        <v>46029.6634375</v>
       </c>
       <c r="J122" s="3">
-        <v>45996.4823032407</v>
+        <v>46014.6931018519</v>
       </c>
       <c r="K122" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L122" s="0" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="M122" s="3">
-        <v>45992.7134722222</v>
+        <v>45993.3791087963</v>
       </c>
       <c r="N122" s="3">
-        <v>46037.3801388889</v>
+        <v>46029.6634375</v>
       </c>
       <c r="O122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <v>2501349</v>
+        <v>2502438</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>175</v>
+        <v>99</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>211</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I123" s="3">
-        <v>46069.7381944444</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="J123" s="3">
-        <v>46069.3651388889</v>
+        <v>45996.4823032407</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M123" s="3">
-        <v>45989.0365856482</v>
+        <v>45992.7134722222</v>
       </c>
       <c r="N123" s="3">
-        <v>46069.7381944444</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="O123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <v>2500635</v>
+        <v>2501349</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>212</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I124" s="3">
-        <v>46024.4633796296</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="J124" s="3">
-        <v>46027.3611111111</v>
+        <v>46069.3651388889</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L124" s="0" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="M124" s="3">
-        <v>45987.671712963</v>
+        <v>45989.0365856482</v>
       </c>
       <c r="N124" s="3">
-        <v>46024.4633796296</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="O124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <v>2498066</v>
+        <v>2500635</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>151</v>
+        <v>28</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>213</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I125" s="3">
-        <v>46073.7916666667</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="J125" s="3">
-        <v>46126.6953240741</v>
+        <v>46027.3611111111</v>
       </c>
       <c r="K125" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M125" s="3">
-        <v>45979.750162037</v>
-      </c>
-      <c r="N125" s="3"/>
+        <v>45987.671712963</v>
+      </c>
+      <c r="N125" s="3">
+        <v>46024.4633796296</v>
+      </c>
       <c r="O125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <v>2494282</v>
+        <v>2498066</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="D126" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="E126" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F126" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="G126" s="0" t="s">
         <v>214</v>
       </c>
-      <c r="E126" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F126" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="G126" s="0" t="s">
-        <v>215</v>
-      </c>
       <c r="H126" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I126" s="3">
-        <v>45986.48125</v>
+        <v>46073.7916666667</v>
       </c>
       <c r="J126" s="3">
-        <v>45988.567025463</v>
+        <v>46126.6953240741</v>
       </c>
       <c r="K126" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M126" s="3">
-        <v>45971.4792824074</v>
-      </c>
-      <c r="N126" s="3">
-        <v>45986.4815625</v>
-      </c>
+        <v>45979.750162037</v>
+      </c>
+      <c r="N126" s="3"/>
       <c r="O126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <v>2494179</v>
+        <v>2494282</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>113</v>
+        <v>215</v>
       </c>
       <c r="E127" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F127" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="G127" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="F127" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="G127" s="0" t="s">
-        <v>218</v>
-      </c>
       <c r="H127" s="0" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I127" s="3">
-        <v>46002.675775463</v>
+        <v>45986.48125</v>
       </c>
       <c r="J127" s="3">
-        <v>46044.7370486111</v>
+        <v>45988.567025463</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M127" s="3">
-        <v>45971.4049421296</v>
+        <v>45971.4792824074</v>
       </c>
       <c r="N127" s="3">
-        <v>46002.675775463</v>
+        <v>45986.4815625</v>
       </c>
       <c r="O127" s="3"/>
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <v>2490911</v>
+        <v>2494179</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>98</v>
+        <v>177</v>
       </c>
       <c r="D128" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="E128" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="F128" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="G128" s="0" t="s">
         <v>219</v>
       </c>
-      <c r="E128" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F128" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="G128" s="0" t="s">
-        <v>220</v>
-      </c>
       <c r="H128" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="I128" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="I128" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="J128" s="3">
-        <v>46182.7633796296</v>
+        <v>46044.7370486111</v>
       </c>
       <c r="K128" s="0" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="L128" s="0" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="M128" s="3">
-        <v>45961.5760300926</v>
-      </c>
-      <c r="N128" s="3"/>
+        <v>45971.4049421296</v>
+      </c>
+      <c r="N128" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="O128" s="3"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <v>2490185</v>
+        <v>2490911</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>221</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I129" s="3">
-        <v>46203.7916666667</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="I129" s="3"/>
       <c r="J129" s="3">
-        <v>46051.4836111111</v>
+        <v>46182.7633796296</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M129" s="3">
-        <v>45960.3928819444</v>
+        <v>45961.5760300926</v>
       </c>
       <c r="N129" s="3"/>
       <c r="O129" s="3"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <v>2489016</v>
+        <v>2490185</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="E130" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F130" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G130" s="0" t="s">
         <v>222</v>
       </c>
-      <c r="F130" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="G130" s="0" t="s">
-        <v>223</v>
-      </c>
       <c r="H130" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I130" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I130" s="3">
+        <v>46203.7916666667</v>
+      </c>
       <c r="J130" s="3">
-        <v>45958.3906481481</v>
+        <v>46051.4836111111</v>
       </c>
       <c r="K130" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L130" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M130" s="3">
-        <v>45957.7253009259</v>
+        <v>45960.3928819444</v>
       </c>
       <c r="N130" s="3"/>
       <c r="O130" s="3"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <v>2485386</v>
+        <v>2489016</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>52</v>
+        <v>218</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>224</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="I131" s="3">
-        <v>46386.7916666667</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I131" s="3"/>
       <c r="J131" s="3">
-        <v>46182.7639236111</v>
+        <v>45958.3906481481</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M131" s="3">
-        <v>45947.7000115741</v>
+        <v>45957.7253009259</v>
       </c>
       <c r="N131" s="3"/>
       <c r="O131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <v>2483420</v>
+        <v>2485386</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>225</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="I132" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="I132" s="3">
+        <v>46386.7916666667</v>
+      </c>
       <c r="J132" s="3">
-        <v>46140.3843518519</v>
+        <v>46182.7639236111</v>
       </c>
       <c r="K132" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L132" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M132" s="3">
-        <v>45944.6603819444</v>
+        <v>45947.7000115741</v>
       </c>
       <c r="N132" s="3"/>
       <c r="O132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <v>2474606</v>
+        <v>2483420</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>226</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I133" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="I133" s="3"/>
       <c r="J133" s="3">
-        <v>45966.4450925926</v>
+        <v>46140.3843518519</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="M133" s="3">
-        <v>45924.4486921296</v>
-      </c>
-      <c r="N133" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>45944.6603819444</v>
+      </c>
+      <c r="N133" s="3"/>
       <c r="O133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <v>2470122</v>
+        <v>2474606</v>
       </c>
       <c r="B134" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="C134" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D134" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="E134" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F134" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="G134" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="C134" s="0" t="s">
-        <v>227</v>
-      </c>
-      <c r="D134" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E134" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F134" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="G134" s="0" t="s">
-        <v>228</v>
-      </c>
       <c r="H134" s="0" t="s">
-        <v>229</v>
-      </c>
-      <c r="I134" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I134" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="J134" s="3">
-        <v>46204.3270601852</v>
+        <v>45966.4450925926</v>
       </c>
       <c r="K134" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L134" s="0" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="M134" s="3">
-        <v>45912.5572222222</v>
-      </c>
-      <c r="N134" s="3"/>
+        <v>45924.4486921296</v>
+      </c>
+      <c r="N134" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="O134" s="3"/>
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <v>2463515</v>
+        <v>2470122</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="D135" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="E135" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F135" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G135" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="H135" s="0" t="s">
         <v>230</v>
-      </c>
-      <c r="E135" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F135" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G135" s="0" t="s">
-        <v>231</v>
-      </c>
-      <c r="H135" s="0" t="s">
-        <v>48</v>
       </c>
       <c r="I135" s="3"/>
       <c r="J135" s="3">
-        <v>45910.4755555556</v>
+        <v>46204.3270601852</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M135" s="3">
-        <v>45897.4218865741</v>
+        <v>45912.5572222222</v>
       </c>
       <c r="N135" s="3"/>
       <c r="O135" s="3"/>
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <v>2461703</v>
+        <v>2463515</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>232</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>229</v>
+        <v>49</v>
       </c>
       <c r="I136" s="3"/>
       <c r="J136" s="3">
-        <v>46003.3706828704</v>
+        <v>45910.4755555556</v>
       </c>
       <c r="K136" s="0" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="L136" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M136" s="3">
-        <v>45894.4525347222</v>
+        <v>45897.4218865741</v>
       </c>
       <c r="N136" s="3"/>
       <c r="O136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <v>2459339</v>
+        <v>2461703</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>233</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="I137" s="3"/>
       <c r="J137" s="3">
-        <v>46140.3839930556</v>
+        <v>46003.3706828704</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M137" s="3">
-        <v>45887.7442361111</v>
+        <v>45894.4525347222</v>
       </c>
       <c r="N137" s="3"/>
       <c r="O137" s="3"/>
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <v>2456538</v>
+        <v>2459339</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>234</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="I138" s="3"/>
       <c r="J138" s="3">
-        <v>46126.7428356481</v>
+        <v>46140.3839930556</v>
       </c>
       <c r="K138" s="0" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="L138" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M138" s="3">
-        <v>45880.6643055556</v>
+        <v>45887.7442361111</v>
       </c>
       <c r="N138" s="3"/>
       <c r="O138" s="3"/>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>2449811</v>
+        <v>2456538</v>
       </c>
       <c r="B139" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D139" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="E139" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F139" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="G139" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="C139" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="D139" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="E139" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="F139" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="G139" s="0" t="s">
-        <v>236</v>
-      </c>
       <c r="H139" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I139" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I139" s="3"/>
       <c r="J139" s="3">
-        <v>45870.3628819444</v>
+        <v>46126.7428356481</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="M139" s="3">
-        <v>45862.6188888889</v>
-      </c>
-      <c r="N139" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>45880.6643055556</v>
+      </c>
+      <c r="N139" s="3"/>
       <c r="O139" s="3"/>
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>2442028</v>
+        <v>2449811</v>
       </c>
       <c r="B140" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="C140" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="D140" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="E140" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="F140" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="G140" s="0" t="s">
         <v>237</v>
       </c>
-      <c r="C140" s="0" t="s">
-        <v>237</v>
-      </c>
-      <c r="D140" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="E140" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F140" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G140" s="0" t="s">
-        <v>238</v>
-      </c>
       <c r="H140" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I140" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I140" s="3">
+        <v>45875.3688888889</v>
+      </c>
       <c r="J140" s="3">
-        <v>46126.7431134259</v>
+        <v>45870.3628819444</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L140" s="0" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="M140" s="3">
-        <v>45842.317025463</v>
-      </c>
-      <c r="N140" s="3"/>
+        <v>45862.6188888889</v>
+      </c>
+      <c r="N140" s="3">
+        <v>45875.3688888889</v>
+      </c>
       <c r="O140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>2439691</v>
+        <v>2442028</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="E141" s="0" t="s">
         <v>17</v>
       </c>
+      <c r="F141" s="0" t="s">
+        <v>18</v>
+      </c>
       <c r="G141" s="0" t="s">
         <v>239</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I141" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I141" s="3"/>
       <c r="J141" s="3">
-        <v>45838.6211342593</v>
+        <v>46126.7431134259</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M141" s="3">
-        <v>45838.3761921296</v>
-      </c>
-      <c r="N141" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>45842.317025463</v>
+      </c>
+      <c r="N141" s="3"/>
       <c r="O141" s="3"/>
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <v>2437239</v>
+        <v>2439691</v>
       </c>
       <c r="B142" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="C142" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D142" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G142" s="0" t="s">
         <v>240</v>
       </c>
-      <c r="C142" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="D142" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E142" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="F142" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="G142" s="0" t="s">
-        <v>242</v>
-      </c>
       <c r="H142" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I142" s="3">
-        <v>45870.3600462963</v>
+        <v>45852.3770833333</v>
       </c>
       <c r="J142" s="3">
-        <v>45841.7026091435</v>
+        <v>45838.6211342593</v>
       </c>
       <c r="K142" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L142" s="0" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="M142" s="3">
-        <v>45831.6933796296</v>
+        <v>45838.3761921296</v>
       </c>
       <c r="N142" s="3">
-        <v>45870.3600462963</v>
+        <v>45852.3770833333</v>
       </c>
       <c r="O142" s="3"/>
     </row>
     <row r="143">
       <c r="A143" s="2">
-        <v>2436707</v>
+        <v>2437239</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>214</v>
+        <v>28</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>243</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I143" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="J143" s="3">
+        <v>45841.7026091435</v>
+      </c>
+      <c r="K143" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="L143" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="M143" s="3">
+        <v>45831.6933796296</v>
+      </c>
+      <c r="N143" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="O143" s="3"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2">
+        <v>2436707</v>
+      </c>
+      <c r="B144" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="D144" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F144" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G144" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="H144" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="I144" s="3">
         <v>45835.7284722222</v>
       </c>
-      <c r="J143" s="3">
+      <c r="J144" s="3">
         <v>46126.7436921296</v>
       </c>
-      <c r="K143" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="L143" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="M143" s="3">
+      <c r="K144" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="L144" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="M144" s="3">
         <v>45828.8276273148</v>
       </c>
-      <c r="N143" s="3">
+      <c r="N144" s="3">
         <v>45835.7288773148</v>
       </c>
-      <c r="O143" s="3"/>
+      <c r="O144" s="3"/>
     </row>
   </sheetData>
   <headerFooter/>

--- a/Solicitacoes.xlsx
+++ b/Solicitacoes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="248">
   <si>
     <t>Protocolo</t>
   </si>
@@ -59,13 +59,37 @@
     <t>Prazo desejado</t>
   </si>
   <si>
+    <t>ROGERIO.ALMEIDA</t>
+  </si>
+  <si>
+    <t>CORRECAO</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>ANS</t>
+  </si>
+  <si>
+    <t>Critica para gerar XML na Rotina Monitoramento TISS</t>
+  </si>
+  <si>
+    <t>Verificando</t>
+  </si>
+  <si>
+    <t>Suporte nível II</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>COMPESAPREV.JULIA</t>
   </si>
   <si>
-    <t>CORRECAO</t>
-  </si>
-  <si>
-    <t>AG</t>
+    <t>Julia Albertim</t>
+  </si>
+  <si>
+    <t>HELPDESK - CUIDAR</t>
   </si>
   <si>
     <t>ADM</t>
@@ -74,39 +98,36 @@
     <t>INSTABILIDADE MÓDULOS</t>
   </si>
   <si>
+    <t>Homologando</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>BCON</t>
+  </si>
+  <si>
+    <t>Faturamento</t>
+  </si>
+  <si>
+    <t>Guia não disponível para execução de eventos por outros prestadores</t>
+  </si>
+  <si>
     <t>Pendente</t>
   </si>
   <si>
-    <t>Suporte nível II</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>BCON</t>
-  </si>
-  <si>
-    <t>Faturamento</t>
-  </si>
-  <si>
-    <t>Guia não disponível para execução de eventos por outros prestadores</t>
-  </si>
-  <si>
     <t>Plataforma Lean</t>
   </si>
   <si>
     <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
   </si>
   <si>
-    <t>HELPDESK - CUIDAR</t>
-  </si>
-  <si>
     <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
   </si>
   <si>
-    <t>Julia Albertim</t>
-  </si>
-  <si>
     <t>CONECTA - XML não sai do estado de "Em Processamento"</t>
   </si>
   <si>
@@ -125,12 +146,6 @@
     <t>COMPESAPREV- Conecta- Erro na solicitação dos procedimentos.</t>
   </si>
   <si>
-    <t>Homologando</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
     <t>Agendamentos</t>
   </si>
   <si>
@@ -149,9 +164,6 @@
     <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
   </si>
   <si>
-    <t>Verificando</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -267,9 +279,6 @@
   </si>
   <si>
     <t>Versão futura</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
   <si>
     <t>EVIDENCIAS DO PROBLEMA NO RELATORIO DE PREVIA DE PAGAMENTO</t>
@@ -803,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O144"/>
+  <dimension ref="A1:O145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1506990705218" customWidth="1"/>
@@ -872,7 +881,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2617538</v>
+        <v>2617933</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>15</v>
@@ -895,11 +904,9 @@
       <c r="H2" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="3">
-        <v>46290.7498263889</v>
-      </c>
+      <c r="I2" s="3"/>
       <c r="J2" s="3">
-        <v>46287.4164930556</v>
+        <v>46288.4902662037</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>21</v>
@@ -908,1589 +915,1591 @@
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>46287.4164930556</v>
-      </c>
-      <c r="N2" s="3">
-        <v>46290.7498263889</v>
-      </c>
+        <v>46287.7594097222</v>
+      </c>
+      <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2617170</v>
+        <v>2617538</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I3" s="3">
-        <v>46290.4403703704</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="J3" s="3">
-        <v>46286.5862037037</v>
+        <v>46288.4440509259</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M3" s="3">
-        <v>46286.5862037037</v>
+        <v>46287.4164930556</v>
       </c>
       <c r="N3" s="3">
-        <v>46290.4403703704</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2617057</v>
+        <v>2617170</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I4" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="J4" s="3">
-        <v>46286.5879513889</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M4" s="3">
-        <v>46286.4877199074</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="N4" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>2615970</v>
+        <v>2617057</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I5" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="J5" s="3">
-        <v>46287.3554017708</v>
+        <v>46286.5879513889</v>
       </c>
       <c r="K5" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M5" s="3">
-        <v>46282.5089930556</v>
+        <v>46286.4877199074</v>
       </c>
       <c r="N5" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="O5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>2615871</v>
+        <v>2615970</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3">
+        <v>46288.4166666667</v>
+      </c>
+      <c r="J6" s="3">
+        <v>46287.3554017708</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3">
-        <v>46286.4024189815</v>
-      </c>
-      <c r="J6" s="3">
-        <v>46286.3450115741</v>
-      </c>
-      <c r="K6" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="M6" s="3">
-        <v>46282.4440856481</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="N6" s="3">
-        <v>46286.4024189815</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>2615590</v>
+        <v>2615871</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I7" s="3">
-        <v>46287.5805092593</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="J7" s="3">
-        <v>46281.7496990741</v>
+        <v>46286.3450115741</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="M7" s="3">
-        <v>46281.6638425926</v>
+        <v>46282.4440856481</v>
       </c>
       <c r="N7" s="3">
-        <v>46287.5805092593</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>2614686</v>
+        <v>2615590</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D8" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="I8" s="3">
-        <v>46321.5908449074</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="J8" s="3">
-        <v>46282.4296635764</v>
+        <v>46281.7496990741</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M8" s="3">
-        <v>46280.4450115741</v>
+        <v>46281.6638425926</v>
       </c>
       <c r="N8" s="3">
-        <v>46321.5908449074</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2614334</v>
+        <v>2614686</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3">
-        <v>46283.5629166667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="J9" s="3">
-        <v>46283.4291666667</v>
+        <v>46282.4296635764</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="M9" s="3">
-        <v>46279.6749305556</v>
+        <v>46280.4450115741</v>
       </c>
       <c r="N9" s="3">
-        <v>46283.5629166667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>2614135</v>
+        <v>2614334</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I10" s="3">
-        <v>46289.7291666667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="J10" s="3">
-        <v>46279.6123263889</v>
+        <v>46283.4291666667</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M10" s="3">
-        <v>46279.5169097222</v>
+        <v>46279.6749305556</v>
       </c>
       <c r="N10" s="3">
-        <v>46289.7291666667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>2613646</v>
+        <v>2614135</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I11" s="3">
-        <v>46289.3876041667</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="J11" s="3">
-        <v>46283.4346064815</v>
+        <v>46279.6123263889</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M11" s="3">
-        <v>46276.6376041667</v>
+        <v>46279.5169097222</v>
       </c>
       <c r="N11" s="3">
-        <v>46289.3876041667</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>2613202</v>
+        <v>2613646</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F12" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="3">
+        <v>46289.3876041667</v>
+      </c>
+      <c r="J12" s="3">
+        <v>46283.4346064815</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="3">
-        <v>46288.6119212963</v>
-      </c>
-      <c r="J12" s="3">
-        <v>46283.4707657407</v>
-      </c>
-      <c r="K12" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="M12" s="3">
-        <v>46276.3827546296</v>
+        <v>46276.6376041667</v>
       </c>
       <c r="N12" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>2613026</v>
+        <v>2613202</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I13" s="3">
-        <v>46281.6747800926</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="J13" s="3">
-        <v>46287.6117592593</v>
+        <v>46283.4707657407</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="M13" s="3">
-        <v>46275.6895601852</v>
+        <v>46276.3827546296</v>
       </c>
       <c r="N13" s="3">
-        <v>46281.6747800926</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>2612720</v>
+        <v>2613026</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I14" s="3">
-        <v>46316.6011689815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="J14" s="3">
-        <v>46279.4816203704</v>
+        <v>46287.6117592593</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M14" s="3">
-        <v>46275.4553356481</v>
+        <v>46275.6895601852</v>
       </c>
       <c r="N14" s="3">
-        <v>46316.6011689815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2611881</v>
+        <v>2612720</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>59</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I15" s="3">
-        <v>46279.6652314815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="J15" s="3">
-        <v>46274.7389930556</v>
+        <v>46279.4816203704</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M15" s="3">
-        <v>46273.7485648148</v>
+        <v>46275.4553356481</v>
       </c>
       <c r="N15" s="3">
-        <v>46279.6652314815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>2611848</v>
+        <v>2611881</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C16" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="3">
+        <v>46279.6652314815</v>
+      </c>
+      <c r="J16" s="3">
+        <v>46274.7389930556</v>
+      </c>
+      <c r="K16" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="3">
-        <v>46287.4094675926</v>
-      </c>
-      <c r="J16" s="3">
-        <v>46276.5914583333</v>
-      </c>
-      <c r="K16" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="M16" s="3">
-        <v>46273.7127546296</v>
+        <v>46273.7485648148</v>
       </c>
       <c r="N16" s="3">
-        <v>46287.4094675926</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>2611692</v>
+        <v>2611848</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D17" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="I17" s="3">
-        <v>46279.4554861111</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="J17" s="3">
-        <v>46273.637278588</v>
+        <v>46276.5914583333</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="M17" s="3">
-        <v>46273.6013194444</v>
+        <v>46273.7127546296</v>
       </c>
       <c r="N17" s="3">
-        <v>46279.4554861111</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>2611552</v>
+        <v>2611692</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C18" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="3">
+        <v>46279.4554861111</v>
+      </c>
+      <c r="J18" s="3">
+        <v>46273.637278588</v>
+      </c>
+      <c r="K18" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" s="3">
-        <v>46275.4327083333</v>
-      </c>
-      <c r="J18" s="3">
-        <v>46273.5743171296</v>
-      </c>
-      <c r="K18" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="M18" s="3">
-        <v>46273.474375</v>
+        <v>46273.6013194444</v>
       </c>
       <c r="N18" s="3">
-        <v>46275.4327083333</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>2611551</v>
+        <v>2611552</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I19" s="3">
-        <v>46314.6183449074</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="J19" s="3">
-        <v>46274.3603356481</v>
+        <v>46273.5743171296</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M19" s="3">
-        <v>46273.4725115741</v>
+        <v>46273.474375</v>
       </c>
       <c r="N19" s="3">
-        <v>46314.6183449074</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>2611539</v>
+        <v>2611551</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I20" s="3">
-        <v>46275.4227083333</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="J20" s="3">
-        <v>46274.3607986111</v>
+        <v>46274.3603356481</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="M20" s="3">
-        <v>46273.464375</v>
+        <v>46273.4725115741</v>
       </c>
       <c r="N20" s="3">
-        <v>46275.4227083333</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>2611521</v>
+        <v>2611539</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I21" s="3">
-        <v>46279.3705439815</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="J21" s="3">
-        <v>46273.7182003819</v>
+        <v>46274.3607986111</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="M21" s="3">
-        <v>46273.4538773148</v>
+        <v>46273.464375</v>
       </c>
       <c r="N21" s="3">
-        <v>46279.3705439815</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2610876</v>
+        <v>2611521</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I22" s="3">
-        <v>46276.3367592593</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="J22" s="3">
-        <v>46269.4406376505</v>
+        <v>46273.7182003819</v>
       </c>
       <c r="K22" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M22" s="3">
-        <v>46269.4200925926</v>
+        <v>46273.4538773148</v>
       </c>
       <c r="N22" s="3">
-        <v>46276.3367592593</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>2610030</v>
+        <v>2610876</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I23" s="3">
-        <v>46274.6271990741</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="J23" s="3">
-        <v>46268.3853071412</v>
+        <v>46269.4406376505</v>
       </c>
       <c r="K23" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M23" s="3">
-        <v>46267.7105324074</v>
+        <v>46269.4200925926</v>
       </c>
       <c r="N23" s="3">
-        <v>46274.6271990741</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>2609985</v>
+        <v>2610030</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I24" s="3">
-        <v>46301.4629166667</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="J24" s="3">
-        <v>46267.6774134606</v>
+        <v>46268.3853071412</v>
       </c>
       <c r="K24" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="M24" s="3">
-        <v>46267.67125</v>
+        <v>46267.7105324074</v>
       </c>
       <c r="N24" s="3">
-        <v>46301.4629166667</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>2609883</v>
+        <v>2609985</v>
       </c>
       <c r="B25" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>32</v>
-      </c>
       <c r="I25" s="3">
-        <v>46309.7050347222</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="J25" s="3">
-        <v>46280.4030439815</v>
+        <v>46267.6774134606</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="M25" s="3">
-        <v>46267.6217013889</v>
+        <v>46267.67125</v>
       </c>
       <c r="N25" s="3">
-        <v>46309.7050347222</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>2609551</v>
+        <v>2609883</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I26" s="3">
-        <v>46273.6887962963</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="J26" s="3">
-        <v>46267.355462963</v>
+        <v>46280.4030439815</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M26" s="3">
-        <v>46267.355462963</v>
+        <v>46267.6217013889</v>
       </c>
       <c r="N26" s="3">
-        <v>46273.6887962963</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>2609107</v>
+        <v>2609551</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I27" s="3">
-        <v>46300.3339583333</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="J27" s="3">
-        <v>46268.4380070255</v>
+        <v>46267.355462963</v>
       </c>
       <c r="K27" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="M27" s="3">
-        <v>46266.4797916667</v>
+        <v>46267.355462963</v>
       </c>
       <c r="N27" s="3">
-        <v>46300.3339583333</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>2608731</v>
+        <v>2609107</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E28" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="F28" s="0" t="s">
-        <v>50</v>
-      </c>
       <c r="G28" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I28" s="3">
-        <v>46279.4280671296</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="J28" s="3">
-        <v>46273.3513888889</v>
+        <v>46268.4380070255</v>
       </c>
       <c r="K28" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="M28" s="3">
-        <v>46265.6780671296</v>
+        <v>46266.4797916667</v>
       </c>
       <c r="N28" s="3">
-        <v>46279.4280671296</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>2608637</v>
+        <v>2608731</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I29" s="3">
-        <v>46304.6977777778</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="J29" s="3">
-        <v>46287.4125274653</v>
+        <v>46273.3513888889</v>
       </c>
       <c r="K29" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M29" s="3">
-        <v>46265.6144444444</v>
+        <v>46265.6780671296</v>
       </c>
       <c r="N29" s="3">
-        <v>46304.6977777778</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>2607413</v>
+        <v>2608637</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="E30" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I30" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="I30" s="3">
+        <v>46304.6977777778</v>
+      </c>
       <c r="J30" s="3">
-        <v>46266.569212963</v>
+        <v>46287.4125274653</v>
       </c>
       <c r="K30" s="0" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="M30" s="3">
-        <v>46261.6163888889</v>
-      </c>
-      <c r="N30" s="3"/>
+        <v>46265.6144444444</v>
+      </c>
+      <c r="N30" s="3">
+        <v>46304.6977777778</v>
+      </c>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>2607198</v>
+        <v>2607413</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>56</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I31" s="3">
-        <v>46267.3546643518</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I31" s="3"/>
       <c r="J31" s="3">
-        <v>46273.6204976852</v>
+        <v>46266.569212963</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="L31" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M31" s="3">
-        <v>46261.4379976852</v>
-      </c>
-      <c r="N31" s="3">
-        <v>46267.3546643518</v>
-      </c>
+        <v>46261.6163888889</v>
+      </c>
+      <c r="N31" s="3"/>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>2606003</v>
+        <v>2607198</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I32" s="3">
-        <v>46265.3599537037</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="J32" s="3">
-        <v>46259.4993506944</v>
+        <v>46273.6204976852</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M32" s="3">
-        <v>46259.443287037</v>
+        <v>46261.4379976852</v>
       </c>
       <c r="N32" s="3">
-        <v>46290.75</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>2604815</v>
+        <v>2606003</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C33" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G33" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="H33" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I33" s="3">
+        <v>46265.3599537037</v>
+      </c>
+      <c r="J33" s="3">
+        <v>46259.4993506944</v>
+      </c>
+      <c r="K33" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="G33" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="H33" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I33" s="3">
-        <v>46296.563587963</v>
-      </c>
-      <c r="J33" s="3">
-        <v>46268.6781365741</v>
-      </c>
-      <c r="K33" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="L33" s="0" t="s">
-        <v>41</v>
-      </c>
       <c r="M33" s="3">
-        <v>46255.4177546296</v>
+        <v>46259.443287037</v>
       </c>
       <c r="N33" s="3">
-        <v>46296.563587963</v>
+        <v>46290.75</v>
       </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>2604500</v>
+        <v>2604815</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D34" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="G34" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="E34" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G34" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="H34" s="0" t="s">
-        <v>49</v>
-      </c>
       <c r="I34" s="3">
-        <v>46260.4812268519</v>
+        <v>46296.563587963</v>
       </c>
       <c r="J34" s="3">
-        <v>46258.3485416667</v>
+        <v>46268.6781365741</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M34" s="3">
-        <v>46254.6270601852</v>
+        <v>46255.4177546296</v>
       </c>
       <c r="N34" s="3">
-        <v>46260.4812268519</v>
+        <v>46296.563587963</v>
       </c>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>2603668</v>
+        <v>2604500</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E35" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="F35" s="0" t="s">
-        <v>90</v>
-      </c>
       <c r="G35" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I35" s="3">
-        <v>46259.3446296296</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="J35" s="3">
-        <v>46258.6426851852</v>
+        <v>46258.3485416667</v>
       </c>
       <c r="K35" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M35" s="3">
-        <v>46253.427962963</v>
+        <v>46254.6270601852</v>
       </c>
       <c r="N35" s="3">
-        <v>46290.75</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="O35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>2602388</v>
+        <v>2603668</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C36" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" s="3">
+        <v>46259.3446296296</v>
+      </c>
+      <c r="J36" s="3">
+        <v>46258.6426851852</v>
+      </c>
+      <c r="K36" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E36" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="F36" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="H36" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I36" s="3">
-        <v>46255.4166666667</v>
-      </c>
-      <c r="J36" s="3">
-        <v>46253.4900231482</v>
-      </c>
-      <c r="K36" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="L36" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M36" s="3">
-        <v>46251.5527777778</v>
+        <v>46253.427962963</v>
       </c>
       <c r="N36" s="3">
-        <v>46255.4166666667</v>
+        <v>46290.75</v>
       </c>
       <c r="O36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>2601999</v>
+        <v>2602388</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="I37" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I37" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="J37" s="3">
-        <v>46266.6188194444</v>
+        <v>46253.4900231482</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="M37" s="3">
-        <v>46248.7351273148</v>
-      </c>
-      <c r="N37" s="3"/>
+        <v>46251.5527777778</v>
+      </c>
+      <c r="N37" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="O37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>2600778</v>
+        <v>2601999</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>96</v>
@@ -2499,7 +2508,7 @@
         <v>17</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>97</v>
@@ -2509,365 +2518,361 @@
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3">
-        <v>46274.3780324074</v>
+        <v>46266.6188194444</v>
       </c>
       <c r="K38" s="0" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M38" s="3">
-        <v>46246.7171759259</v>
+        <v>46248.7351273148</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2599732</v>
+        <v>2600778</v>
       </c>
       <c r="B39" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="D39" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="E39" s="0" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>100</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I39" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="I39" s="3"/>
       <c r="J39" s="3">
-        <v>46248.3419117245</v>
+        <v>46274.3780324074</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="L39" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M39" s="3">
-        <v>46245.4849537037</v>
-      </c>
-      <c r="N39" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>46246.7171759259</v>
+      </c>
+      <c r="N39" s="3"/>
       <c r="O39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>2598987</v>
+        <v>2599732</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="C40" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="H40" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="I40" s="3">
+        <v>46251.4016203704</v>
+      </c>
+      <c r="J40" s="3">
+        <v>46248.3419117245</v>
+      </c>
+      <c r="K40" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="L40" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="G40" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="H40" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I40" s="3">
-        <v>46254.6856134259</v>
-      </c>
-      <c r="J40" s="3">
-        <v>46251.536875</v>
-      </c>
-      <c r="K40" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="L40" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="M40" s="3">
-        <v>46244.4564467593</v>
+        <v>46245.4849537037</v>
       </c>
       <c r="N40" s="3">
-        <v>46254.6856134259</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="O40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>2598910</v>
+        <v>2598987</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="I41" s="3">
-        <v>46254.6386574074</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="J41" s="3">
-        <v>46248.4760674769</v>
+        <v>46251.536875</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M41" s="3">
-        <v>46244.4094907407</v>
+        <v>46244.4564467593</v>
       </c>
       <c r="N41" s="3">
-        <v>46261.6103125</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="O41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>2598767</v>
+        <v>2598910</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>106</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="I42" s="3">
-        <v>46247.6666666667</v>
+        <v>46254.6386574074</v>
       </c>
       <c r="J42" s="3">
-        <v>46245.6608564815</v>
+        <v>46248.4760674769</v>
       </c>
       <c r="K42" s="0" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="M42" s="3">
-        <v>46241.757962963</v>
+        <v>46244.4094907407</v>
       </c>
       <c r="N42" s="3">
-        <v>46247.6666666667</v>
+        <v>46261.6103125</v>
       </c>
       <c r="O42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>2597798</v>
+        <v>2598767</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E43" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I43" s="3">
-        <v>46290.75</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="J43" s="3">
-        <v>46273.4412384259</v>
+        <v>46245.6608564815</v>
       </c>
       <c r="K43" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="M43" s="3">
-        <v>46240.4508912037</v>
+        <v>46241.757962963</v>
       </c>
       <c r="N43" s="3">
-        <v>46290.75</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="O43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>2597524</v>
+        <v>2597798</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E44" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="I44" s="3">
-        <v>46267.0453356481</v>
+        <v>46290.75</v>
       </c>
       <c r="J44" s="3">
-        <v>46259.4158333333</v>
+        <v>46273.4412384259</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="M44" s="3">
-        <v>46239.6925347222</v>
+        <v>46240.4508912037</v>
       </c>
       <c r="N44" s="3">
-        <v>46267.0453356481</v>
+        <v>46290.75</v>
       </c>
       <c r="O44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>2597515</v>
+        <v>2597524</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I45" s="3">
-        <v>46266.4759953704</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="J45" s="3">
-        <v>46261.4097453704</v>
+        <v>46259.4158333333</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="M45" s="3">
-        <v>46239.6856134259</v>
+        <v>46239.6925347222</v>
       </c>
       <c r="N45" s="3">
-        <v>46266.4759953704</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="O45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>2597495</v>
+        <v>2597515</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I46" s="3">
-        <v>46252.3333333333</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="J46" s="3">
-        <v>46241.6523302083</v>
+        <v>46261.4097453704</v>
       </c>
       <c r="K46" s="0" t="s">
         <v>21</v>
@@ -2876,1124 +2881,1124 @@
         <v>22</v>
       </c>
       <c r="M46" s="3">
-        <v>46239.6802199074</v>
+        <v>46239.6856134259</v>
       </c>
       <c r="N46" s="3">
-        <v>46245.5968865741</v>
-      </c>
-      <c r="O46" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>46266.4759953704</v>
+      </c>
+      <c r="O46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>2596882</v>
+        <v>2597495</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>115</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I47" s="3">
-        <v>46280.3775578704</v>
+        <v>46252.3333333333</v>
       </c>
       <c r="J47" s="3">
-        <v>46267.6170023148</v>
+        <v>46241.6523302083</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M47" s="3">
-        <v>46238.7108912037</v>
+        <v>46239.6802199074</v>
       </c>
       <c r="N47" s="3">
-        <v>46280.3775578704</v>
-      </c>
-      <c r="O47" s="3"/>
+        <v>46245.5968865741</v>
+      </c>
+      <c r="O47" s="3">
+        <v>46252.3333333333</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>2596538</v>
+        <v>2596882</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="I48" s="3">
-        <v>46273.960787037</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="J48" s="3">
-        <v>46286.3521412037</v>
+        <v>46267.6170023148</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L48" s="0" t="s">
         <v>46</v>
       </c>
       <c r="M48" s="3">
-        <v>46238.4644791667</v>
+        <v>46238.7108912037</v>
       </c>
       <c r="N48" s="3">
-        <v>46273.960787037</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="O48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>2596407</v>
+        <v>2596538</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I49" s="3">
-        <v>46248.6072106482</v>
+        <v>46273.960787037</v>
       </c>
       <c r="J49" s="3">
-        <v>46267.6164814815</v>
+        <v>46286.3521412037</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M49" s="3">
-        <v>46238.3780439815</v>
+        <v>46238.4644791667</v>
       </c>
       <c r="N49" s="3">
-        <v>46248.6072106482</v>
+        <v>46273.960787037</v>
       </c>
       <c r="O49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>2595510</v>
+        <v>2596407</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I50" s="3">
-        <v>46240.4984606481</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="J50" s="3">
-        <v>46245.3667592593</v>
+        <v>46267.6164814815</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="M50" s="3">
-        <v>46234.6442939815</v>
+        <v>46238.3780439815</v>
       </c>
       <c r="N50" s="3">
-        <v>46240.4984606481</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="O50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>2595497</v>
+        <v>2595510</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I51" s="3">
-        <v>46240.4978240741</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="J51" s="3">
-        <v>46245.3669444444</v>
+        <v>46245.3667592593</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M51" s="3">
-        <v>46234.6436574074</v>
+        <v>46234.6442939815</v>
       </c>
       <c r="N51" s="3">
-        <v>46240.4978240741</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="O51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>2593529</v>
+        <v>2595497</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I52" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="J52" s="3">
-        <v>46233.4404570255</v>
+        <v>46245.3669444444</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M52" s="3">
-        <v>46231.6639930556</v>
+        <v>46234.6436574074</v>
       </c>
       <c r="N52" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="O52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>2593490</v>
+        <v>2593529</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I53" s="3">
-        <v>46239.6748032407</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="J53" s="3">
-        <v>46253.4905324074</v>
+        <v>46233.4404570255</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M53" s="3">
-        <v>46231.6518865741</v>
+        <v>46231.6639930556</v>
       </c>
       <c r="N53" s="3">
-        <v>46239.6748032407</v>
-      </c>
-      <c r="O53" s="3">
-        <v>46234.48125</v>
-      </c>
+        <v>46237.5806597222</v>
+      </c>
+      <c r="O53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>2593260</v>
+        <v>2593490</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I54" s="3">
-        <v>46241.6638888889</v>
+        <v>46239.6748032407</v>
       </c>
       <c r="J54" s="3">
-        <v>46267.614525463</v>
+        <v>46253.4905324074</v>
       </c>
       <c r="K54" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M54" s="3">
-        <v>46231.435150463</v>
+        <v>46231.6518865741</v>
       </c>
       <c r="N54" s="3">
-        <v>46241.6638888889</v>
-      </c>
-      <c r="O54" s="3"/>
+        <v>46239.6748032407</v>
+      </c>
+      <c r="O54" s="3">
+        <v>46234.48125</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>2593216</v>
+        <v>2593260</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I55" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="I55" s="3">
+        <v>46241.6638888889</v>
+      </c>
       <c r="J55" s="3">
-        <v>46231.4047453704</v>
+        <v>46267.614525463</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="M55" s="3">
-        <v>46231.4011111111</v>
-      </c>
-      <c r="N55" s="3"/>
+        <v>46231.435150463</v>
+      </c>
+      <c r="N55" s="3">
+        <v>46241.6638888889</v>
+      </c>
       <c r="O55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>2592878</v>
+        <v>2593216</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I56" s="3">
-        <v>46241.3504282407</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I56" s="3"/>
       <c r="J56" s="3">
-        <v>46230.6675740741</v>
+        <v>46231.4047453704</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M56" s="3">
-        <v>46230.6004282407</v>
-      </c>
-      <c r="N56" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46231.4011111111</v>
+      </c>
+      <c r="N56" s="3"/>
       <c r="O56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>2592468</v>
+        <v>2592878</v>
       </c>
       <c r="B57" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="G57" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="H57" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D57" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E57" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F57" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="G57" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="H57" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="I57" s="3">
-        <v>46237.6038657407</v>
+        <v>46241.3504282407</v>
       </c>
       <c r="J57" s="3">
-        <v>46240.6136738773</v>
+        <v>46230.6675740741</v>
       </c>
       <c r="K57" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="M57" s="3">
-        <v>46227.7107060185</v>
+        <v>46230.6004282407</v>
       </c>
       <c r="N57" s="3">
-        <v>46293.6033680556</v>
+        <v>46290.75</v>
       </c>
       <c r="O57" s="3"/>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>2591596</v>
+        <v>2592468</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I58" s="3">
-        <v>46238.7083333333</v>
+        <v>46237.6038657407</v>
       </c>
       <c r="J58" s="3">
-        <v>46267.3444803241</v>
+        <v>46240.6136738773</v>
       </c>
       <c r="K58" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="M58" s="3">
-        <v>46226.4797916667</v>
+        <v>46227.7107060185</v>
       </c>
       <c r="N58" s="3">
-        <v>46282.6141435185</v>
+        <v>46293.6033680556</v>
       </c>
       <c r="O58" s="3"/>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>2591284</v>
+        <v>2591596</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I59" s="3">
-        <v>46266.3384837963</v>
+        <v>46238.7083333333</v>
       </c>
       <c r="J59" s="3">
-        <v>46225.7002398495</v>
+        <v>46267.3444803241</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M59" s="3">
-        <v>46225.6718171296</v>
+        <v>46226.4797916667</v>
       </c>
       <c r="N59" s="3">
-        <v>46266.3384837963</v>
+        <v>46282.6141435185</v>
       </c>
       <c r="O59" s="3"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2588490</v>
+        <v>2591284</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I60" s="3">
-        <v>46230.722037037</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="J60" s="3">
-        <v>46231.4339699074</v>
+        <v>46225.7002398495</v>
       </c>
       <c r="K60" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L60" s="0" t="s">
         <v>46</v>
       </c>
       <c r="M60" s="3">
-        <v>46218.4928703704</v>
+        <v>46225.6718171296</v>
       </c>
       <c r="N60" s="3">
-        <v>46230.722037037</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="O60" s="3"/>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>2588025</v>
+        <v>2588490</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="F61" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="G61" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="G61" s="0" t="s">
-        <v>133</v>
-      </c>
       <c r="H61" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="I61" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="I61" s="3">
+        <v>46230.722037037</v>
+      </c>
       <c r="J61" s="3">
-        <v>46267.5903356482</v>
+        <v>46231.4339699074</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="M61" s="3">
-        <v>46217.612962963</v>
-      </c>
-      <c r="N61" s="3"/>
+        <v>46218.4928703704</v>
+      </c>
+      <c r="N61" s="3">
+        <v>46230.722037037</v>
+      </c>
       <c r="O61" s="3"/>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>2587849</v>
+        <v>2588025</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I62" s="3">
-        <v>46226.6083796296</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="I62" s="3"/>
       <c r="J62" s="3">
-        <v>46237.9144806713</v>
+        <v>46267.5903356482</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="L62" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M62" s="3">
-        <v>46217.4506597222</v>
-      </c>
-      <c r="N62" s="3">
-        <v>46226.6083796296</v>
-      </c>
+        <v>46217.612962963</v>
+      </c>
+      <c r="N62" s="3"/>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>2587713</v>
+        <v>2587849</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E63" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="F63" s="0" t="s">
-        <v>67</v>
-      </c>
       <c r="G63" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I63" s="3">
-        <v>46218.7408680556</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="J63" s="3">
-        <v>46230.4199074074</v>
+        <v>46237.9144806713</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M63" s="3">
-        <v>46217.3658680556</v>
+        <v>46217.4506597222</v>
       </c>
       <c r="N63" s="3">
-        <v>46218.7408680556</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="O63" s="3"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2587585</v>
+        <v>2587713</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I64" s="3">
-        <v>46220.6264583333</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="J64" s="3">
-        <v>46259.4474884259</v>
+        <v>46230.4199074074</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="M64" s="3">
-        <v>46216.7097916667</v>
+        <v>46217.3658680556</v>
       </c>
       <c r="N64" s="3">
-        <v>46220.6264583333</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="O64" s="3"/>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2587006</v>
+        <v>2587585</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I65" s="3">
-        <v>46217.7289699074</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="J65" s="3">
-        <v>46227.4549884259</v>
+        <v>46259.4474884259</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M65" s="3">
-        <v>46213.7239236111</v>
+        <v>46216.7097916667</v>
       </c>
       <c r="N65" s="3">
-        <v>46217.7289699074</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="O65" s="3"/>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>2586984</v>
+        <v>2587006</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I66" s="3">
-        <v>46295.7416550926</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="J66" s="3">
-        <v>46273.4946180556</v>
+        <v>46227.4549884259</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="M66" s="3">
-        <v>46213.6971527778</v>
+        <v>46213.7239236111</v>
       </c>
       <c r="N66" s="3">
-        <v>46295.7416550926</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>2586910</v>
+        <v>2586984</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E67" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F67" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="0" t="s">
-        <v>139</v>
-      </c>
       <c r="G67" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I67" s="3">
-        <v>46226.5833333333</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="J67" s="3">
-        <v>46230.4194212963</v>
+        <v>46273.4946180556</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M67" s="3">
-        <v>46213.6245833333</v>
+        <v>46213.6971527778</v>
       </c>
       <c r="N67" s="3">
-        <v>46226.5833333333</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="O67" s="3"/>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>2586651</v>
+        <v>2586910</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I68" s="3">
-        <v>46218.7157407407</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="J68" s="3">
-        <v>46213.3824074074</v>
+        <v>46230.4194212963</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="M68" s="3">
-        <v>46213.3824074074</v>
+        <v>46213.6245833333</v>
       </c>
       <c r="N68" s="3">
-        <v>46218.7157407407</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="O68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>2586187</v>
+        <v>2586651</v>
       </c>
       <c r="B69" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F69" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="G69" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="H69" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="C69" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D69" s="0" t="s">
-        <v>143</v>
-      </c>
-      <c r="E69" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F69" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="G69" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="H69" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I69" s="3"/>
+      <c r="I69" s="3">
+        <v>46218.7157407407</v>
+      </c>
       <c r="J69" s="3">
-        <v>46219.3850231481</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="M69" s="3">
-        <v>46211.7697337963</v>
-      </c>
-      <c r="N69" s="3"/>
+        <v>46213.3824074074</v>
+      </c>
+      <c r="N69" s="3">
+        <v>46218.7157407407</v>
+      </c>
       <c r="O69" s="3"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>2585888</v>
+        <v>2586187</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H70" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="I70" s="3">
-        <v>46217.4119907407</v>
-      </c>
+      <c r="I70" s="3"/>
       <c r="J70" s="3">
-        <v>46217.5003587963</v>
+        <v>46219.3850231481</v>
       </c>
       <c r="K70" s="0" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="L70" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M70" s="3">
-        <v>46211.4953240741</v>
-      </c>
-      <c r="N70" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46211.7697337963</v>
+      </c>
+      <c r="N70" s="3"/>
       <c r="O70" s="3"/>
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>2585424</v>
+        <v>2585888</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="I71" s="3">
-        <v>46223.3927199074</v>
+        <v>46217.4119907407</v>
       </c>
       <c r="J71" s="3">
-        <v>46234.4964930556</v>
+        <v>46217.5003587963</v>
       </c>
       <c r="K71" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="M71" s="3">
-        <v>46210.6427199074</v>
+        <v>46211.4953240741</v>
       </c>
       <c r="N71" s="3">
         <v>46290.75</v>
@@ -4002,529 +4007,529 @@
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>2584638</v>
+        <v>2585424</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="I72" s="3">
-        <v>46213.4171527778</v>
+        <v>46223.3927199074</v>
       </c>
       <c r="J72" s="3">
-        <v>46213.4090859607</v>
+        <v>46234.4964930556</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="M72" s="3">
-        <v>46209.5016203704</v>
+        <v>46210.6427199074</v>
       </c>
       <c r="N72" s="3">
-        <v>46232.3874884259</v>
+        <v>46290.75</v>
       </c>
       <c r="O72" s="3"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>2584397</v>
+        <v>2584638</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="I73" s="3">
-        <v>46212.6757175926</v>
+        <v>46213.4171527778</v>
       </c>
       <c r="J73" s="3">
-        <v>46213.3741550926</v>
+        <v>46213.4090859607</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M73" s="3">
-        <v>46209.3423842593</v>
+        <v>46209.5016203704</v>
       </c>
       <c r="N73" s="3">
-        <v>46212.6757175926</v>
+        <v>46232.3874884259</v>
       </c>
       <c r="O73" s="3"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2584167</v>
+        <v>2584397</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I74" s="3">
-        <v>46246.7216435185</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="J74" s="3">
-        <v>46247.4396759259</v>
+        <v>46213.3741550926</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M74" s="3">
-        <v>46206.6383101852</v>
+        <v>46209.3423842593</v>
       </c>
       <c r="N74" s="3">
-        <v>46246.7216435185</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="O74" s="3"/>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2583950</v>
+        <v>2584167</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I75" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I75" s="3">
+        <v>46246.7216435185</v>
+      </c>
       <c r="J75" s="3">
-        <v>46273.4100925926</v>
+        <v>46247.4396759259</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="M75" s="3">
-        <v>46206.4623148148</v>
-      </c>
-      <c r="N75" s="3"/>
+        <v>46206.6383101852</v>
+      </c>
+      <c r="N75" s="3">
+        <v>46246.7216435185</v>
+      </c>
       <c r="O75" s="3"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>2583447</v>
+        <v>2583950</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I76" s="3">
-        <v>46205.7916666667</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I76" s="3"/>
       <c r="J76" s="3">
-        <v>46265.3645138889</v>
+        <v>46273.4100925926</v>
       </c>
       <c r="K76" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="M76" s="3">
-        <v>46205.5752083333</v>
-      </c>
-      <c r="N76" s="3">
-        <v>46245.6724189815</v>
-      </c>
+        <v>46206.4623148148</v>
+      </c>
+      <c r="N76" s="3"/>
       <c r="O76" s="3"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>2583382</v>
+        <v>2583447</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="I77" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I77" s="3">
+        <v>46205.7916666667</v>
+      </c>
       <c r="J77" s="3">
-        <v>46279.4689699074</v>
+        <v>46265.3645138889</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="M77" s="3">
-        <v>46205.4905092593</v>
-      </c>
-      <c r="N77" s="3"/>
+        <v>46205.5752083333</v>
+      </c>
+      <c r="N77" s="3">
+        <v>46245.6724189815</v>
+      </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>2582452</v>
+        <v>2583382</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I78" s="3">
-        <v>46244.4166666667</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="I78" s="3"/>
       <c r="J78" s="3">
-        <v>46204.7763078704</v>
+        <v>46279.4689699074</v>
       </c>
       <c r="K78" s="0" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="M78" s="3">
-        <v>46203.8250810185</v>
-      </c>
-      <c r="N78" s="3">
-        <v>46244.4166666667</v>
-      </c>
+        <v>46205.4905092593</v>
+      </c>
+      <c r="N78" s="3"/>
       <c r="O78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2582352</v>
+        <v>2582452</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I79" s="3">
-        <v>46244.340775463</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="J79" s="3">
-        <v>46204.7761805556</v>
+        <v>46204.7763078704</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M79" s="3">
-        <v>46203.6741087963</v>
+        <v>46203.8250810185</v>
       </c>
       <c r="N79" s="3">
-        <v>46244.340775463</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>2579299</v>
+        <v>2582352</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="E80" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I80" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I80" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="J80" s="3">
-        <v>46204.3277777778</v>
+        <v>46204.7761805556</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="M80" s="3">
-        <v>46196.4165162037</v>
-      </c>
-      <c r="N80" s="3"/>
+        <v>46203.6741087963</v>
+      </c>
+      <c r="N80" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>2576326</v>
+        <v>2579299</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E81" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I81" s="3">
-        <v>46192.7916666667</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I81" s="3"/>
       <c r="J81" s="3">
-        <v>46230.6812731481</v>
+        <v>46204.3277777778</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M81" s="3">
-        <v>46189.3995833333</v>
+        <v>46196.4165162037</v>
       </c>
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>2574153</v>
+        <v>2576326</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E82" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I82" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I82" s="3">
+        <v>46192.7916666667</v>
+      </c>
       <c r="J82" s="3">
-        <v>46204.3218402778</v>
+        <v>46230.6812731481</v>
       </c>
       <c r="K82" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M82" s="3">
-        <v>46183.4711226852</v>
+        <v>46189.3995833333</v>
       </c>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>2572707</v>
+        <v>2574153</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>163</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I83" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I83" s="3"/>
       <c r="J83" s="3">
-        <v>46188.4629166667</v>
+        <v>46204.3218402778</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="M83" s="3">
-        <v>46178.7298148148</v>
-      </c>
-      <c r="N83" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>46183.4711226852</v>
+      </c>
+      <c r="N83" s="3"/>
       <c r="O83" s="3"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>2570274</v>
+        <v>2572707</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>164</v>
@@ -4533,1450 +4538,1450 @@
         <v>164</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I84" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I84" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="J84" s="3">
-        <v>46204.3220138889</v>
+        <v>46188.4629166667</v>
       </c>
       <c r="K84" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="M84" s="3">
-        <v>46171.6563773148</v>
-      </c>
-      <c r="N84" s="3"/>
+        <v>46178.7298148148</v>
+      </c>
+      <c r="N84" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="O84" s="3"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>2562116</v>
+        <v>2570274</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E85" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I85" s="3"/>
       <c r="J85" s="3">
-        <v>46160.7191666667</v>
+        <v>46204.3220138889</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M85" s="3">
-        <v>46154.3432638889</v>
+        <v>46171.6563773148</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>2558553</v>
+        <v>2562116</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I86" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I86" s="3"/>
       <c r="J86" s="3">
-        <v>46154.5888773148</v>
+        <v>46160.7191666667</v>
       </c>
       <c r="K86" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L86" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M86" s="3">
-        <v>46146.3561805556</v>
-      </c>
-      <c r="N86" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>46154.3432638889</v>
+      </c>
+      <c r="N86" s="3"/>
       <c r="O86" s="3"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>2556271</v>
+        <v>2558553</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>168</v>
+        <v>32</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I87" s="3">
-        <v>46141.4297453704</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="J87" s="3">
-        <v>46139.9871412037</v>
+        <v>46154.5888773148</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M87" s="3">
-        <v>46139.471412037</v>
+        <v>46146.3561805556</v>
       </c>
       <c r="N87" s="3">
-        <v>46141.4901157407</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>2556211</v>
+        <v>2556271</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="I88" s="3">
-        <v>46150.6617476852</v>
+        <v>46141.4297453704</v>
       </c>
       <c r="J88" s="3">
-        <v>46146.3663773148</v>
+        <v>46139.9871412037</v>
       </c>
       <c r="K88" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M88" s="3">
-        <v>46139.4325810185</v>
+        <v>46139.471412037</v>
       </c>
       <c r="N88" s="3">
-        <v>46150.6617476852</v>
+        <v>46141.4901157407</v>
       </c>
       <c r="O88" s="3"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>2556029</v>
+        <v>2556211</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I89" s="3">
-        <v>46150.5</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="J89" s="3">
-        <v>46146.401875</v>
+        <v>46146.3663773148</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M89" s="3">
-        <v>46138.757337963</v>
+        <v>46139.4325810185</v>
       </c>
       <c r="N89" s="3">
-        <v>46154.6616087963</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="O89" s="3"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2554341</v>
+        <v>2556029</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I90" s="3">
-        <v>46136.3599768519</v>
+        <v>46150.5</v>
       </c>
       <c r="J90" s="3">
-        <v>46135.6585185185</v>
+        <v>46146.401875</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="M90" s="3">
-        <v>46134.4016435185</v>
+        <v>46138.757337963</v>
       </c>
       <c r="N90" s="3">
-        <v>46136.3599768519</v>
+        <v>46154.6616087963</v>
       </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>2547638</v>
+        <v>2554341</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I91" s="3">
-        <v>46150.3473611111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="J91" s="3">
-        <v>46119.5010069444</v>
+        <v>46135.6585185185</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="M91" s="3">
-        <v>46114.4931944444</v>
+        <v>46134.4016435185</v>
       </c>
       <c r="N91" s="3">
-        <v>46150.3473611111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>2537054</v>
+        <v>2547638</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E92" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I92" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="J92" s="3">
-        <v>46090.3698263889</v>
+        <v>46119.5010069444</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="M92" s="3">
-        <v>46087.5797569444</v>
+        <v>46114.4931944444</v>
       </c>
       <c r="N92" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="O92" s="3"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>2531696</v>
+        <v>2537054</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="E93" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I93" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I93" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="J93" s="3">
-        <v>46204.3216782407</v>
+        <v>46090.3698263889</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="M93" s="3">
-        <v>46076.5833912037</v>
-      </c>
-      <c r="N93" s="3"/>
+        <v>46087.5797569444</v>
+      </c>
+      <c r="N93" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="O93" s="3"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>2530739</v>
+        <v>2531696</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E94" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>178</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="I94" s="3"/>
       <c r="J94" s="3">
-        <v>46218.6914940625</v>
+        <v>46204.3216782407</v>
       </c>
       <c r="K94" s="0" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="L94" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M94" s="3">
-        <v>46072.6973148148</v>
+        <v>46076.5833912037</v>
       </c>
       <c r="N94" s="3"/>
       <c r="O94" s="3"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>2529639</v>
+        <v>2530739</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>34</v>
+        <v>179</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I95" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="I95" s="3"/>
       <c r="J95" s="3">
-        <v>46072.6891666667</v>
+        <v>46218.6914940625</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M95" s="3">
-        <v>46069.5930902778</v>
-      </c>
-      <c r="N95" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>46072.6973148148</v>
+      </c>
+      <c r="N95" s="3"/>
       <c r="O95" s="3"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>2529591</v>
+        <v>2529639</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I96" s="3">
-        <v>46108.5968055556</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="J96" s="3">
-        <v>46126.6875</v>
+        <v>46072.6891666667</v>
       </c>
       <c r="K96" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L96" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M96" s="3">
-        <v>46069.4509722222</v>
+        <v>46069.5930902778</v>
       </c>
       <c r="N96" s="3">
-        <v>46108.5968055556</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="O96" s="3"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>2528858</v>
+        <v>2529591</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I97" s="3">
-        <v>46107.3861458333</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="J97" s="3">
-        <v>46087.6277662037</v>
+        <v>46126.6875</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M97" s="3">
-        <v>46065.7194791667</v>
+        <v>46069.4509722222</v>
       </c>
       <c r="N97" s="3">
-        <v>46107.3861458333</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="O97" s="3"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>2525312</v>
+        <v>2528858</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E98" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F98" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="F98" s="0" t="s">
-        <v>90</v>
-      </c>
       <c r="G98" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I98" s="3">
-        <v>46070.5877314815</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="J98" s="3">
-        <v>46062.7587037037</v>
+        <v>46087.6277662037</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L98" s="0" t="s">
         <v>46</v>
       </c>
       <c r="M98" s="3">
-        <v>46058.3585648148</v>
+        <v>46065.7194791667</v>
       </c>
       <c r="N98" s="3">
-        <v>46070.5877314815</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="O98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>2525272</v>
+        <v>2525312</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>184</v>
+        <v>25</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>185</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I99" s="3">
-        <v>46203.7916666667</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="J99" s="3">
-        <v>46126.7441782407</v>
+        <v>46062.7587037037</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="M99" s="3">
-        <v>46058.2883101852</v>
-      </c>
-      <c r="N99" s="3"/>
+        <v>46058.3585648148</v>
+      </c>
+      <c r="N99" s="3">
+        <v>46070.5877314815</v>
+      </c>
       <c r="O99" s="3"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>2524577</v>
+        <v>2525272</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="I100" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I100" s="3">
+        <v>46203.7916666667</v>
+      </c>
       <c r="J100" s="3">
-        <v>46267.4298180903</v>
+        <v>46126.7441782407</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="L100" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M100" s="3">
-        <v>46056.697349537</v>
+        <v>46058.2883101852</v>
       </c>
       <c r="N100" s="3"/>
       <c r="O100" s="3"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>2524373</v>
+        <v>2524577</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I101" s="3">
-        <v>46087.3854513889</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="I101" s="3"/>
       <c r="J101" s="3">
-        <v>46056.6543865741</v>
+        <v>46267.4298180903</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="M101" s="3">
-        <v>46056.5937847222</v>
-      </c>
-      <c r="N101" s="3">
-        <v>46087.3854513889</v>
-      </c>
+        <v>46056.697349537</v>
+      </c>
+      <c r="N101" s="3"/>
       <c r="O101" s="3"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>2524062</v>
+        <v>2524373</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I102" s="3">
-        <v>46057.7412615741</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="J102" s="3">
-        <v>46056.6210300926</v>
+        <v>46056.6543865741</v>
       </c>
       <c r="K102" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L102" s="0" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="M102" s="3">
-        <v>46056.3662615741</v>
+        <v>46056.5937847222</v>
       </c>
       <c r="N102" s="3">
-        <v>46057.7412615741</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>2523635</v>
+        <v>2524062</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I103" s="3">
-        <v>46059.4164236111</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="J103" s="3">
-        <v>46055.6034837963</v>
+        <v>46056.6210300926</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="M103" s="3">
-        <v>46055.4997569444</v>
+        <v>46056.3662615741</v>
       </c>
       <c r="N103" s="3">
-        <v>46059.4164236111</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>2523602</v>
+        <v>2523635</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E104" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F104" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="F104" s="0" t="s">
-        <v>50</v>
-      </c>
       <c r="G104" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I104" s="3">
-        <v>46093.6246643519</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="J104" s="3">
-        <v>46056.5784027778</v>
+        <v>46055.6034837963</v>
       </c>
       <c r="K104" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M104" s="3">
-        <v>46055.4788310185</v>
+        <v>46055.4997569444</v>
       </c>
       <c r="N104" s="3">
-        <v>46093.6246643519</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="O104" s="3"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>2521645</v>
+        <v>2523602</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="I105" s="3">
-        <v>46062.5</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="J105" s="3">
-        <v>46050.3426763542</v>
+        <v>46056.5784027778</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="L105" s="0" t="s">
         <v>46</v>
       </c>
       <c r="M105" s="3">
-        <v>46049.7714236111</v>
-      </c>
-      <c r="N105" s="3"/>
+        <v>46055.4788310185</v>
+      </c>
+      <c r="N105" s="3">
+        <v>46093.6246643519</v>
+      </c>
       <c r="O105" s="3"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>2521079</v>
+        <v>2521645</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="I106" s="3">
-        <v>46052.6666666667</v>
+        <v>46062.5</v>
       </c>
       <c r="J106" s="3">
-        <v>46056.6197800926</v>
+        <v>46050.3426763542</v>
       </c>
       <c r="K106" s="0" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="L106" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="M106" s="3">
-        <v>46048.7684490741</v>
-      </c>
-      <c r="N106" s="3">
-        <v>46061.6309722222</v>
-      </c>
+        <v>46049.7714236111</v>
+      </c>
+      <c r="N106" s="3"/>
       <c r="O106" s="3"/>
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>2520048</v>
+        <v>2521079</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="I107" s="3">
-        <v>46057.5</v>
+        <v>46052.6666666667</v>
       </c>
       <c r="J107" s="3">
-        <v>46052.5774305556</v>
+        <v>46056.6197800926</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="M107" s="3">
-        <v>46045.3325578704</v>
+        <v>46048.7684490741</v>
       </c>
       <c r="N107" s="3">
-        <v>46057.5</v>
+        <v>46061.6309722222</v>
       </c>
       <c r="O107" s="3"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>2519904</v>
+        <v>2520048</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I108" s="3">
-        <v>46084.7217939815</v>
+        <v>46057.5</v>
       </c>
       <c r="J108" s="3">
-        <v>46044.7413888889</v>
+        <v>46052.5774305556</v>
       </c>
       <c r="K108" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L108" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M108" s="3">
-        <v>46044.6384606482</v>
+        <v>46045.3325578704</v>
       </c>
       <c r="N108" s="3">
-        <v>46084.7217939815</v>
+        <v>46057.5</v>
       </c>
       <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>2519523</v>
+        <v>2519904</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E109" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F109" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="F109" s="0" t="s">
-        <v>50</v>
-      </c>
       <c r="G109" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I109" s="3">
-        <v>46076.5902777778</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="J109" s="3">
-        <v>46048.4589814815</v>
+        <v>46044.7413888889</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="M109" s="3">
-        <v>46043.7362847222</v>
+        <v>46044.6384606482</v>
       </c>
       <c r="N109" s="3">
-        <v>46077.380775463</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="O109" s="3"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>2519383</v>
+        <v>2519523</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I110" s="3">
-        <v>46076.399224537</v>
+        <v>46076.5902777778</v>
       </c>
       <c r="J110" s="3">
-        <v>46048.4599305556</v>
+        <v>46048.4589814815</v>
       </c>
       <c r="K110" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L110" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="M110" s="3">
-        <v>46043.6075578704</v>
+        <v>46043.7362847222</v>
       </c>
       <c r="N110" s="3">
-        <v>46076.399224537</v>
+        <v>46077.380775463</v>
       </c>
       <c r="O110" s="3"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>2519284</v>
+        <v>2519383</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I111" s="3">
-        <v>46049.3982986111</v>
+        <v>46076.399224537</v>
       </c>
       <c r="J111" s="3">
-        <v>46043.742337963</v>
+        <v>46048.4599305556</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="M111" s="3">
-        <v>46043.4816319444</v>
+        <v>46043.6075578704</v>
       </c>
       <c r="N111" s="3">
-        <v>46049.3982986111</v>
+        <v>46076.399224537</v>
       </c>
       <c r="O111" s="3"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>2518650</v>
+        <v>2519284</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I112" s="3">
-        <v>46072.3536921296</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="J112" s="3">
-        <v>46043.8185648148</v>
+        <v>46043.742337963</v>
       </c>
       <c r="K112" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M112" s="3">
-        <v>46042.3536921296</v>
+        <v>46043.4816319444</v>
       </c>
       <c r="N112" s="3">
-        <v>46080.437025463</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="O112" s="3"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>2513117</v>
+        <v>2518650</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>99</v>
+        <v>180</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E113" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I113" s="3">
-        <v>46031.4922800926</v>
+        <v>46072.3536921296</v>
       </c>
       <c r="J113" s="3">
-        <v>46028.3500347222</v>
+        <v>46043.8185648148</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M113" s="3">
-        <v>46027.6381134259</v>
+        <v>46042.3536921296</v>
       </c>
       <c r="N113" s="3">
-        <v>46031.4922800926</v>
+        <v>46080.437025463</v>
       </c>
       <c r="O113" s="3"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>2512883</v>
+        <v>2513117</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I114" s="3">
-        <v>46037.6340972222</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="J114" s="3">
-        <v>46129.4199421296</v>
+        <v>46028.3500347222</v>
       </c>
       <c r="K114" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L114" s="0" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="M114" s="3">
-        <v>46027.4049305556</v>
+        <v>46027.6381134259</v>
       </c>
       <c r="N114" s="3">
-        <v>46141.6335300926</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="O114" s="3"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>2512542</v>
+        <v>2512883</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I115" s="3">
-        <v>46036.5</v>
+        <v>46037.6340972222</v>
       </c>
       <c r="J115" s="3">
-        <v>46024.5900925926</v>
+        <v>46129.4199421296</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M115" s="3">
-        <v>46022.6836342593</v>
+        <v>46027.4049305556</v>
       </c>
       <c r="N115" s="3">
-        <v>46036.5</v>
+        <v>46141.6335300926</v>
       </c>
       <c r="O115" s="3"/>
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>2512541</v>
+        <v>2512542</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I116" s="3">
         <v>46036.5</v>
       </c>
       <c r="J116" s="3">
-        <v>46022.7128356481</v>
+        <v>46024.5900925926</v>
       </c>
       <c r="K116" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L116" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M116" s="3">
-        <v>46022.6762615741</v>
+        <v>46022.6836342593</v>
       </c>
       <c r="N116" s="3">
         <v>46036.5</v>
@@ -5985,1214 +5990,1259 @@
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>2509014</v>
+        <v>2512541</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I117" s="3">
-        <v>46044.7250578704</v>
+        <v>46036.5</v>
       </c>
       <c r="J117" s="3">
-        <v>46022.6138541667</v>
+        <v>46022.7128356481</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="M117" s="3">
-        <v>46008.454224537</v>
+        <v>46022.6762615741</v>
       </c>
       <c r="N117" s="3">
-        <v>46045.4708564815</v>
+        <v>46036.5</v>
       </c>
       <c r="O117" s="3"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>2506714</v>
+        <v>2509014</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I118" s="3">
-        <v>46038.7073032407</v>
+        <v>46044.7250578704</v>
       </c>
       <c r="J118" s="3">
-        <v>46044.7372337963</v>
+        <v>46022.6138541667</v>
       </c>
       <c r="K118" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L118" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="M118" s="3">
-        <v>46002.4364699074</v>
+        <v>46008.454224537</v>
       </c>
       <c r="N118" s="3">
-        <v>46038.7073032407</v>
+        <v>46045.4708564815</v>
       </c>
       <c r="O118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>2506599</v>
+        <v>2506714</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I119" s="3">
-        <v>46037.61375</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="J119" s="3">
-        <v>46052.3252083333</v>
+        <v>46044.7372337963</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="M119" s="3">
-        <v>46002.3429166667</v>
+        <v>46002.4364699074</v>
       </c>
       <c r="N119" s="3">
-        <v>46037.61375</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="O119" s="3"/>
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <v>2506311</v>
+        <v>2506599</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>206</v>
+        <v>116</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>206</v>
+        <v>116</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I120" s="3">
-        <v>46013.7291666667</v>
+        <v>46037.61375</v>
       </c>
       <c r="J120" s="3">
-        <v>46013.461875</v>
+        <v>46052.3252083333</v>
       </c>
       <c r="K120" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L120" s="0" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="M120" s="3">
-        <v>46001.5219328704</v>
+        <v>46002.3429166667</v>
       </c>
       <c r="N120" s="3">
-        <v>46013.7291666667</v>
+        <v>46037.61375</v>
       </c>
       <c r="O120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <v>2506102</v>
+        <v>2506311</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I121" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I121" s="3">
+        <v>46013.7291666667</v>
+      </c>
       <c r="J121" s="3">
-        <v>46241.5032638889</v>
+        <v>46013.461875</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="M121" s="3">
-        <v>46001.3800578704</v>
-      </c>
-      <c r="N121" s="3"/>
+        <v>46001.5219328704</v>
+      </c>
+      <c r="N121" s="3">
+        <v>46013.7291666667</v>
+      </c>
       <c r="O121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <v>2502589</v>
+        <v>2506102</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>209</v>
+        <v>124</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>209</v>
+        <v>124</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I122" s="3">
-        <v>46029.6634375</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I122" s="3"/>
       <c r="J122" s="3">
-        <v>46014.6931018519</v>
+        <v>46241.5032638889</v>
       </c>
       <c r="K122" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L122" s="0" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="M122" s="3">
-        <v>45993.3791087963</v>
-      </c>
-      <c r="N122" s="3">
-        <v>46029.6634375</v>
-      </c>
+        <v>46001.3800578704</v>
+      </c>
+      <c r="N122" s="3"/>
       <c r="O122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <v>2502438</v>
+        <v>2502589</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>99</v>
+        <v>212</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I123" s="3">
-        <v>46037.3801388889</v>
+        <v>46029.6634375</v>
       </c>
       <c r="J123" s="3">
-        <v>45996.4823032407</v>
+        <v>46014.6931018519</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="M123" s="3">
-        <v>45992.7134722222</v>
+        <v>45993.3791087963</v>
       </c>
       <c r="N123" s="3">
-        <v>46037.3801388889</v>
+        <v>46029.6634375</v>
       </c>
       <c r="O123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <v>2501349</v>
+        <v>2502438</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I124" s="3">
-        <v>46069.7381944444</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="J124" s="3">
-        <v>46069.3651388889</v>
+        <v>45996.4823032407</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L124" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M124" s="3">
-        <v>45989.0365856482</v>
+        <v>45992.7134722222</v>
       </c>
       <c r="N124" s="3">
-        <v>46069.7381944444</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="O124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <v>2500635</v>
+        <v>2501349</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E125" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I125" s="3">
-        <v>46024.4633796296</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="J125" s="3">
-        <v>46027.3611111111</v>
+        <v>46069.3651388889</v>
       </c>
       <c r="K125" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="M125" s="3">
-        <v>45987.671712963</v>
+        <v>45989.0365856482</v>
       </c>
       <c r="N125" s="3">
-        <v>46024.4633796296</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="O125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <v>2498066</v>
+        <v>2500635</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="E126" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I126" s="3">
-        <v>46073.7916666667</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="J126" s="3">
-        <v>46126.6953240741</v>
+        <v>46027.3611111111</v>
       </c>
       <c r="K126" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="M126" s="3">
-        <v>45979.750162037</v>
-      </c>
-      <c r="N126" s="3"/>
+        <v>45987.671712963</v>
+      </c>
+      <c r="N126" s="3">
+        <v>46024.4633796296</v>
+      </c>
       <c r="O126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <v>2494282</v>
+        <v>2498066</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="E127" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I127" s="3">
-        <v>45986.48125</v>
+        <v>46073.7916666667</v>
       </c>
       <c r="J127" s="3">
-        <v>45988.567025463</v>
+        <v>46126.6953240741</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="M127" s="3">
-        <v>45971.4792824074</v>
-      </c>
-      <c r="N127" s="3">
-        <v>45986.4815625</v>
-      </c>
+        <v>45979.750162037</v>
+      </c>
+      <c r="N127" s="3"/>
       <c r="O127" s="3"/>
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <v>2494179</v>
+        <v>2494282</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>114</v>
+        <v>218</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>219</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="I128" s="3">
-        <v>46002.675775463</v>
+        <v>45986.48125</v>
       </c>
       <c r="J128" s="3">
-        <v>46044.7370486111</v>
+        <v>45988.567025463</v>
       </c>
       <c r="K128" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L128" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="M128" s="3">
-        <v>45971.4049421296</v>
+        <v>45971.4792824074</v>
       </c>
       <c r="N128" s="3">
-        <v>46002.675775463</v>
+        <v>45986.4815625</v>
       </c>
       <c r="O128" s="3"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <v>2490911</v>
+        <v>2494179</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>99</v>
+        <v>180</v>
       </c>
       <c r="D129" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="E129" s="0" t="s">
         <v>220</v>
       </c>
-      <c r="E129" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F129" s="0" t="s">
-        <v>53</v>
+        <v>221</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="I129" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="I129" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="J129" s="3">
-        <v>46182.7633796296</v>
+        <v>46044.7370486111</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M129" s="3">
-        <v>45961.5760300926</v>
-      </c>
-      <c r="N129" s="3"/>
+        <v>45971.4049421296</v>
+      </c>
+      <c r="N129" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="O129" s="3"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <v>2490185</v>
+        <v>2490911</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="E130" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I130" s="3">
-        <v>46203.7916666667</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="I130" s="3"/>
       <c r="J130" s="3">
-        <v>46051.4836111111</v>
+        <v>46182.7633796296</v>
       </c>
       <c r="K130" s="0" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="L130" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M130" s="3">
-        <v>45960.3928819444</v>
+        <v>45961.5760300926</v>
       </c>
       <c r="N130" s="3"/>
       <c r="O130" s="3"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <v>2489016</v>
+        <v>2490185</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>113</v>
+        <v>186</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>113</v>
+        <v>186</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>223</v>
+        <v>17</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>218</v>
+        <v>57</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I131" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I131" s="3">
+        <v>46203.7916666667</v>
+      </c>
       <c r="J131" s="3">
-        <v>45958.3906481481</v>
+        <v>46051.4836111111</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M131" s="3">
-        <v>45957.7253009259</v>
+        <v>45960.3928819444</v>
       </c>
       <c r="N131" s="3"/>
       <c r="O131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <v>2485386</v>
+        <v>2489016</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>220</v>
+        <v>86</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>17</v>
+        <v>226</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>53</v>
+        <v>221</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="I132" s="3">
-        <v>46386.7916666667</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I132" s="3"/>
       <c r="J132" s="3">
-        <v>46182.7639236111</v>
+        <v>45958.3906481481</v>
       </c>
       <c r="K132" s="0" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="L132" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M132" s="3">
-        <v>45947.7000115741</v>
+        <v>45957.7253009259</v>
       </c>
       <c r="N132" s="3"/>
       <c r="O132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <v>2483420</v>
+        <v>2485386</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E133" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="I133" s="3"/>
+        <v>107</v>
+      </c>
+      <c r="I133" s="3">
+        <v>46386.7916666667</v>
+      </c>
       <c r="J133" s="3">
-        <v>46140.3843518519</v>
+        <v>46182.7639236111</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M133" s="3">
-        <v>45944.6603819444</v>
+        <v>45947.7000115741</v>
       </c>
       <c r="N133" s="3"/>
       <c r="O133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <v>2474606</v>
+        <v>2483420</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E134" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I134" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="I134" s="3"/>
       <c r="J134" s="3">
-        <v>45966.4450925926</v>
+        <v>46140.3843518519</v>
       </c>
       <c r="K134" s="0" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="L134" s="0" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="M134" s="3">
-        <v>45924.4486921296</v>
-      </c>
-      <c r="N134" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>45944.6603819444</v>
+      </c>
+      <c r="N134" s="3"/>
       <c r="O134" s="3"/>
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <v>2470122</v>
+        <v>2474606</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E135" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>230</v>
-      </c>
-      <c r="I135" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I135" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="J135" s="3">
-        <v>46204.3270601852</v>
+        <v>45966.4450925926</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="M135" s="3">
-        <v>45912.5572222222</v>
-      </c>
-      <c r="N135" s="3"/>
+        <v>45924.4486921296</v>
+      </c>
+      <c r="N135" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="O135" s="3"/>
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <v>2463515</v>
+        <v>2470122</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>113</v>
+        <v>231</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>113</v>
+        <v>231</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E136" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>232</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>49</v>
+        <v>233</v>
       </c>
       <c r="I136" s="3"/>
       <c r="J136" s="3">
-        <v>45910.4755555556</v>
+        <v>46204.3270601852</v>
       </c>
       <c r="K136" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L136" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M136" s="3">
-        <v>45897.4218865741</v>
+        <v>45912.5572222222</v>
       </c>
       <c r="N136" s="3"/>
       <c r="O136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <v>2461703</v>
+        <v>2463515</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>230</v>
+        <v>53</v>
       </c>
       <c r="I137" s="3"/>
       <c r="J137" s="3">
-        <v>46003.3706828704</v>
+        <v>45910.4755555556</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M137" s="3">
-        <v>45894.4525347222</v>
+        <v>45897.4218865741</v>
       </c>
       <c r="N137" s="3"/>
       <c r="O137" s="3"/>
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <v>2459339</v>
+        <v>2461703</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>104</v>
+        <v>233</v>
       </c>
       <c r="I138" s="3"/>
       <c r="J138" s="3">
-        <v>46140.3839930556</v>
+        <v>46003.3706828704</v>
       </c>
       <c r="K138" s="0" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="L138" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M138" s="3">
-        <v>45887.7442361111</v>
+        <v>45894.4525347222</v>
       </c>
       <c r="N138" s="3"/>
       <c r="O138" s="3"/>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>2456538</v>
+        <v>2459339</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="E139" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="I139" s="3"/>
       <c r="J139" s="3">
-        <v>46126.7428356481</v>
+        <v>46140.3839930556</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M139" s="3">
-        <v>45880.6643055556</v>
+        <v>45887.7442361111</v>
       </c>
       <c r="N139" s="3"/>
       <c r="O139" s="3"/>
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>2449811</v>
+        <v>2456538</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I140" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I140" s="3"/>
       <c r="J140" s="3">
-        <v>45870.3628819444</v>
+        <v>46126.7428356481</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L140" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M140" s="3">
-        <v>45862.6188888889</v>
-      </c>
-      <c r="N140" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>45880.6643055556</v>
+      </c>
+      <c r="N140" s="3"/>
       <c r="O140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>2442028</v>
+        <v>2449811</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I141" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I141" s="3">
+        <v>45875.3688888889</v>
+      </c>
       <c r="J141" s="3">
-        <v>46126.7431134259</v>
+        <v>45870.3628819444</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="M141" s="3">
-        <v>45842.317025463</v>
-      </c>
-      <c r="N141" s="3"/>
+        <v>45862.6188888889</v>
+      </c>
+      <c r="N141" s="3">
+        <v>45875.3688888889</v>
+      </c>
       <c r="O141" s="3"/>
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <v>2439691</v>
+        <v>2442028</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>113</v>
+        <v>241</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>113</v>
+        <v>241</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="F142" s="0" t="s">
+        <v>26</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="I142" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I142" s="3"/>
       <c r="J142" s="3">
-        <v>45838.6211342593</v>
+        <v>46126.7431134259</v>
       </c>
       <c r="K142" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L142" s="0" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="M142" s="3">
-        <v>45838.3761921296</v>
-      </c>
-      <c r="N142" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>45842.317025463</v>
+      </c>
+      <c r="N142" s="3"/>
       <c r="O142" s="3"/>
     </row>
     <row r="143">
       <c r="A143" s="2">
-        <v>2437239</v>
+        <v>2439691</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>241</v>
+        <v>116</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>242</v>
+        <v>116</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>28</v>
+        <v>218</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="F143" s="0" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>243</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I143" s="3">
-        <v>45870.3600462963</v>
+        <v>45852.3770833333</v>
       </c>
       <c r="J143" s="3">
-        <v>45841.7026091435</v>
+        <v>45838.6211342593</v>
       </c>
       <c r="K143" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L143" s="0" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="M143" s="3">
-        <v>45831.6933796296</v>
+        <v>45838.3761921296</v>
       </c>
       <c r="N143" s="3">
-        <v>45870.3600462963</v>
+        <v>45852.3770833333</v>
       </c>
       <c r="O143" s="3"/>
     </row>
     <row r="144">
       <c r="A144" s="2">
-        <v>2436707</v>
+        <v>2437239</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>215</v>
+        <v>25</v>
       </c>
       <c r="E144" s="0" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I144" s="3">
-        <v>45835.7284722222</v>
+        <v>45870.3600462963</v>
       </c>
       <c r="J144" s="3">
-        <v>46126.7436921296</v>
+        <v>45841.7026091435</v>
       </c>
       <c r="K144" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L144" s="0" t="s">
         <v>46</v>
       </c>
       <c r="M144" s="3">
+        <v>45831.6933796296</v>
+      </c>
+      <c r="N144" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="O144" s="3"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2">
+        <v>2436707</v>
+      </c>
+      <c r="B145" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="C145" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="D145" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="E145" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F145" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G145" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="H145" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="I145" s="3">
+        <v>45835.7284722222</v>
+      </c>
+      <c r="J145" s="3">
+        <v>46126.7436921296</v>
+      </c>
+      <c r="K145" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="L145" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="M145" s="3">
         <v>45828.8276273148</v>
       </c>
-      <c r="N144" s="3">
+      <c r="N145" s="3">
         <v>45835.7288773148</v>
       </c>
-      <c r="O144" s="3"/>
+      <c r="O145" s="3"/>
     </row>
   </sheetData>
   <headerFooter/>

--- a/Solicitacoes.xlsx
+++ b/Solicitacoes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
   <si>
     <t>Protocolo</t>
   </si>
@@ -59,12 +59,45 @@
     <t>Prazo desejado</t>
   </si>
   <si>
+    <t>COMPESAPREV.JULIA</t>
+  </si>
+  <si>
+    <t>CORRECAO</t>
+  </si>
+  <si>
+    <t>BCON</t>
+  </si>
+  <si>
+    <t>Adm Operadora</t>
+  </si>
+  <si>
+    <t>CON - Impossibilidade adiconar corpo clínico</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Suporte nível II</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>MOBE</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APP -  Erro no servidor / buscar dados</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>ROGERIO.ALMEIDA</t>
   </si>
   <si>
-    <t>CORRECAO</t>
-  </si>
-  <si>
     <t>AG</t>
   </si>
   <si>
@@ -77,15 +110,9 @@
     <t>Verificando</t>
   </si>
   <si>
-    <t>Suporte nível II</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
-    <t>COMPESAPREV.JULIA</t>
-  </si>
-  <si>
     <t>Julia Albertim</t>
   </si>
   <si>
@@ -104,21 +131,12 @@
     <t>Cliente</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>BCON</t>
-  </si>
-  <si>
     <t>Faturamento</t>
   </si>
   <si>
     <t>Guia não disponível para execução de eventos por outros prestadores</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
     <t>Plataforma Lean</t>
   </si>
   <si>
@@ -134,9 +152,6 @@
     <t>Resolvido</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>ANA.GOLDIM</t>
   </si>
   <si>
@@ -158,9 +173,6 @@
     <t>CONECTA - Erro na execução de guias | pop-up e bloqueio por biometria</t>
   </si>
   <si>
-    <t>Adm Operadora</t>
-  </si>
-  <si>
     <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
   </si>
   <si>
@@ -207,12 +219,6 @@
   </si>
   <si>
     <t>Dúvida sobre o local para salvar/exportar a Guia Executada no Portal do Prestador</t>
-  </si>
-  <si>
-    <t>MOBE</t>
-  </si>
-  <si>
-    <t>APP</t>
   </si>
   <si>
     <t>Histórico financeiro sem a informação individual de todos os beneficiários</t>
@@ -812,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O145"/>
+  <dimension ref="A1:O147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1506990705218" customWidth="1"/>
@@ -881,7 +887,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2617933</v>
+        <v>2618403</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>15</v>
@@ -904,9 +910,11 @@
       <c r="H2" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="3"/>
+      <c r="I2" s="3">
+        <v>46294.5634259259</v>
+      </c>
       <c r="J2" s="3">
-        <v>46288.4902662037</v>
+        <v>46288.6467592593</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>21</v>
@@ -915,569 +923,567 @@
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>46287.7594097222</v>
-      </c>
-      <c r="N2" s="3"/>
+        <v>46288.6467592593</v>
+      </c>
+      <c r="N2" s="3">
+        <v>46294.5634259259</v>
+      </c>
       <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2617538</v>
+        <v>2618370</v>
       </c>
       <c r="B3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="F3" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="G3" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="0" t="s">
+      <c r="H3" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3">
+        <v>46290.5871296296</v>
+      </c>
+      <c r="J3" s="3">
+        <v>46288.6287962963</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="3">
-        <v>46290.7498263889</v>
-      </c>
-      <c r="J3" s="3">
-        <v>46288.4440509259</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>30</v>
-      </c>
       <c r="M3" s="3">
-        <v>46287.4164930556</v>
+        <v>46288.6287962963</v>
       </c>
       <c r="N3" s="3">
-        <v>46290.7498263889</v>
+        <v>46290.5871296296</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2617170</v>
+        <v>2617933</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="3">
-        <v>46290.4403703704</v>
-      </c>
+      <c r="I4" s="3"/>
       <c r="J4" s="3">
-        <v>46286.5862037037</v>
+        <v>46288.4902662037</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M4" s="3">
-        <v>46286.5862037037</v>
-      </c>
-      <c r="N4" s="3">
-        <v>46290.4403703704</v>
-      </c>
+        <v>46287.7594097222</v>
+      </c>
+      <c r="N4" s="3"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>2617057</v>
+        <v>2617538</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="0" t="s">
         <v>35</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>26</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>36</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I5" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="J5" s="3">
-        <v>46286.5879513889</v>
+        <v>46288.4440509259</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M5" s="3">
-        <v>46286.4877199074</v>
+        <v>46287.4164930556</v>
       </c>
       <c r="N5" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="O5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>2615970</v>
+        <v>2617170</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I6" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="J6" s="3">
-        <v>46287.3554017708</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="K6" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M6" s="3">
-        <v>46282.5089930556</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="N6" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>2615871</v>
+        <v>2617057</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I7" s="3">
-        <v>46286.4024189815</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="J7" s="3">
-        <v>46286.3450115741</v>
+        <v>46286.5879513889</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M7" s="3">
-        <v>46282.4440856481</v>
+        <v>46286.4877199074</v>
       </c>
       <c r="N7" s="3">
-        <v>46286.4024189815</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>2615590</v>
+        <v>2615970</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I8" s="3">
-        <v>46287.5805092593</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="J8" s="3">
-        <v>46281.7496990741</v>
+        <v>46287.3554017708</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M8" s="3">
-        <v>46281.6638425926</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="N8" s="3">
-        <v>46287.5805092593</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2614686</v>
+        <v>2615871</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="0" t="s">
-        <v>45</v>
-      </c>
       <c r="H9" s="0" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I9" s="3">
-        <v>46321.5908449074</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="J9" s="3">
-        <v>46282.4296635764</v>
+        <v>46286.3450115741</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="M9" s="3">
-        <v>46280.4450115741</v>
+        <v>46282.4440856481</v>
       </c>
       <c r="N9" s="3">
-        <v>46321.5908449074</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>2614334</v>
+        <v>2615590</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I10" s="3">
-        <v>46283.5629166667</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="J10" s="3">
-        <v>46283.4291666667</v>
+        <v>46281.7496990741</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M10" s="3">
-        <v>46279.6749305556</v>
+        <v>46281.6638425926</v>
       </c>
       <c r="N10" s="3">
-        <v>46283.5629166667</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>2614135</v>
+        <v>2614686</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I11" s="3">
-        <v>46289.7291666667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="J11" s="3">
-        <v>46279.6123263889</v>
+        <v>46282.4296635764</v>
       </c>
       <c r="K11" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M11" s="3">
-        <v>46279.5169097222</v>
+        <v>46280.4450115741</v>
       </c>
       <c r="N11" s="3">
-        <v>46289.7291666667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>2613646</v>
+        <v>2614334</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I12" s="3">
-        <v>46289.3876041667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="J12" s="3">
-        <v>46283.4346064815</v>
+        <v>46283.4291666667</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="M12" s="3">
-        <v>46276.6376041667</v>
+        <v>46279.6749305556</v>
       </c>
       <c r="N12" s="3">
-        <v>46289.3876041667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>2613202</v>
+        <v>2614135</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="J13" s="3">
-        <v>46283.4707657407</v>
+        <v>46279.6123263889</v>
       </c>
       <c r="K13" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M13" s="3">
-        <v>46276.3827546296</v>
+        <v>46279.5169097222</v>
       </c>
       <c r="N13" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>2613026</v>
+        <v>2613646</v>
       </c>
       <c r="B14" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>58</v>
-      </c>
       <c r="H14" s="0" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="I14" s="3">
-        <v>46281.6747800926</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="J14" s="3">
-        <v>46287.6117592593</v>
+        <v>46283.4346064815</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="M14" s="3">
-        <v>46275.6895601852</v>
+        <v>46276.6376041667</v>
       </c>
       <c r="N14" s="3">
-        <v>46281.6747800926</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2612720</v>
+        <v>2613202</v>
       </c>
       <c r="B15" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>31</v>
-      </c>
       <c r="F15" s="0" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>59</v>
@@ -1486,130 +1492,130 @@
         <v>20</v>
       </c>
       <c r="I15" s="3">
-        <v>46316.6011689815</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="J15" s="3">
-        <v>46279.4816203704</v>
+        <v>46283.4707657407</v>
       </c>
       <c r="K15" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M15" s="3">
-        <v>46275.4553356481</v>
+        <v>46276.3827546296</v>
       </c>
       <c r="N15" s="3">
-        <v>46316.6011689815</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>2611881</v>
+        <v>2613026</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>60</v>
       </c>
       <c r="C16" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="0" t="s">
+      <c r="G16" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="0" t="s">
-        <v>63</v>
-      </c>
       <c r="H16" s="0" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I16" s="3">
-        <v>46279.6652314815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="J16" s="3">
-        <v>46274.7389930556</v>
+        <v>46287.6117592593</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M16" s="3">
-        <v>46273.7485648148</v>
+        <v>46275.6895601852</v>
       </c>
       <c r="N16" s="3">
-        <v>46279.6652314815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>2611848</v>
+        <v>2612720</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E17" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="I17" s="3">
-        <v>46287.4094675926</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="J17" s="3">
-        <v>46276.5914583333</v>
+        <v>46279.4816203704</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M17" s="3">
-        <v>46273.7127546296</v>
+        <v>46275.4553356481</v>
       </c>
       <c r="N17" s="3">
-        <v>46287.4094675926</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>2611692</v>
+        <v>2611881</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>66</v>
@@ -1618,5631 +1624,5721 @@
         <v>67</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I18" s="3">
-        <v>46279.4554861111</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="J18" s="3">
-        <v>46273.637278588</v>
+        <v>46274.7389930556</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M18" s="3">
-        <v>46273.6013194444</v>
+        <v>46273.7485648148</v>
       </c>
       <c r="N18" s="3">
-        <v>46279.4554861111</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>2611552</v>
+        <v>2611848</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E19" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="0" t="s">
-        <v>69</v>
-      </c>
       <c r="H19" s="0" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="I19" s="3">
-        <v>46275.4327083333</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="J19" s="3">
-        <v>46273.5743171296</v>
+        <v>46276.5914583333</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="M19" s="3">
-        <v>46273.474375</v>
+        <v>46273.7127546296</v>
       </c>
       <c r="N19" s="3">
-        <v>46275.4327083333</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>2611551</v>
+        <v>2611692</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="I20" s="3">
-        <v>46314.6183449074</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="J20" s="3">
-        <v>46274.3603356481</v>
+        <v>46273.637278588</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M20" s="3">
-        <v>46273.4725115741</v>
+        <v>46273.6013194444</v>
       </c>
       <c r="N20" s="3">
-        <v>46314.6183449074</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>2611539</v>
+        <v>2611552</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E21" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="G21" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="0" t="s">
-        <v>72</v>
-      </c>
       <c r="H21" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I21" s="3">
-        <v>46275.4227083333</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="J21" s="3">
-        <v>46274.3607986111</v>
+        <v>46273.5743171296</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="M21" s="3">
-        <v>46273.464375</v>
+        <v>46273.474375</v>
       </c>
       <c r="N21" s="3">
-        <v>46275.4227083333</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2611521</v>
+        <v>2611551</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I22" s="3">
-        <v>46279.3705439815</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="J22" s="3">
-        <v>46273.7182003819</v>
+        <v>46274.3603356481</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="M22" s="3">
-        <v>46273.4538773148</v>
+        <v>46273.4725115741</v>
       </c>
       <c r="N22" s="3">
-        <v>46279.3705439815</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>2610876</v>
+        <v>2611539</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I23" s="3">
-        <v>46276.3367592593</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="J23" s="3">
-        <v>46269.4406376505</v>
+        <v>46274.3607986111</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M23" s="3">
-        <v>46269.4200925926</v>
+        <v>46273.464375</v>
       </c>
       <c r="N23" s="3">
-        <v>46276.3367592593</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>2610030</v>
+        <v>2611521</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>76</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I24" s="3">
-        <v>46274.6271990741</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="J24" s="3">
-        <v>46268.3853071412</v>
+        <v>46273.7182003819</v>
       </c>
       <c r="K24" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M24" s="3">
-        <v>46267.7105324074</v>
+        <v>46273.4538773148</v>
       </c>
       <c r="N24" s="3">
-        <v>46274.6271990741</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>2609985</v>
+        <v>2610876</v>
       </c>
       <c r="B25" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>65</v>
-      </c>
       <c r="F25" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="G25" s="0" t="s">
         <v>77</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I25" s="3">
-        <v>46301.4629166667</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="J25" s="3">
-        <v>46267.6774134606</v>
+        <v>46269.4406376505</v>
       </c>
       <c r="K25" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="M25" s="3">
-        <v>46267.67125</v>
+        <v>46269.4200925926</v>
       </c>
       <c r="N25" s="3">
-        <v>46301.4629166667</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>2609883</v>
+        <v>2610030</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I26" s="3">
-        <v>46309.7050347222</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="J26" s="3">
-        <v>46280.4030439815</v>
+        <v>46268.3853071412</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M26" s="3">
-        <v>46267.6217013889</v>
+        <v>46267.7105324074</v>
       </c>
       <c r="N26" s="3">
-        <v>46309.7050347222</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>2609551</v>
+        <v>2609985</v>
       </c>
       <c r="B27" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>80</v>
-      </c>
       <c r="F27" s="0" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I27" s="3">
-        <v>46273.6887962963</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="J27" s="3">
-        <v>46267.355462963</v>
+        <v>46267.6774134606</v>
       </c>
       <c r="K27" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="M27" s="3">
-        <v>46267.355462963</v>
+        <v>46267.67125</v>
       </c>
       <c r="N27" s="3">
-        <v>46273.6887962963</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>2609107</v>
+        <v>2609883</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I28" s="3">
-        <v>46300.3339583333</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="J28" s="3">
-        <v>46268.4380070255</v>
+        <v>46280.4030439815</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="M28" s="3">
-        <v>46266.4797916667</v>
+        <v>46267.6217013889</v>
       </c>
       <c r="N28" s="3">
-        <v>46300.3339583333</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>2608731</v>
+        <v>2609551</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>84</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I29" s="3">
-        <v>46279.4280671296</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="J29" s="3">
-        <v>46273.3513888889</v>
+        <v>46267.355462963</v>
       </c>
       <c r="K29" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="M29" s="3">
-        <v>46265.6780671296</v>
+        <v>46267.355462963</v>
       </c>
       <c r="N29" s="3">
-        <v>46279.4280671296</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>2608637</v>
+        <v>2609107</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>85</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I30" s="3">
-        <v>46304.6977777778</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="J30" s="3">
-        <v>46287.4125274653</v>
+        <v>46268.4380070255</v>
       </c>
       <c r="K30" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="M30" s="3">
-        <v>46265.6144444444</v>
+        <v>46266.4797916667</v>
       </c>
       <c r="N30" s="3">
-        <v>46304.6977777778</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>2607413</v>
+        <v>2608731</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="D31" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" s="0" t="s">
         <v>86</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G31" s="0" t="s">
-        <v>87</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="3"/>
+      <c r="I31" s="3">
+        <v>46279.4280671296</v>
+      </c>
       <c r="J31" s="3">
-        <v>46266.569212963</v>
+        <v>46273.3513888889</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="M31" s="3">
-        <v>46261.6163888889</v>
-      </c>
-      <c r="N31" s="3"/>
+        <v>46265.6780671296</v>
+      </c>
+      <c r="N31" s="3">
+        <v>46279.4280671296</v>
+      </c>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>2607198</v>
+        <v>2608637</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="I32" s="3">
-        <v>46267.3546643518</v>
+        <v>46304.6977777778</v>
       </c>
       <c r="J32" s="3">
-        <v>46273.6204976852</v>
+        <v>46287.4125274653</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="M32" s="3">
-        <v>46261.4379976852</v>
+        <v>46265.6144444444</v>
       </c>
       <c r="N32" s="3">
-        <v>46267.3546643518</v>
+        <v>46304.6977777778</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>2606003</v>
+        <v>2607413</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G33" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="H33" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3">
+        <v>46266.569212963</v>
+      </c>
+      <c r="K33" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="H33" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="I33" s="3">
-        <v>46265.3599537037</v>
-      </c>
-      <c r="J33" s="3">
-        <v>46259.4993506944</v>
-      </c>
-      <c r="K33" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="L33" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M33" s="3">
-        <v>46259.443287037</v>
-      </c>
-      <c r="N33" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46261.6163888889</v>
+      </c>
+      <c r="N33" s="3"/>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>2604815</v>
+        <v>2607198</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>91</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="I34" s="3">
-        <v>46296.563587963</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="J34" s="3">
-        <v>46268.6781365741</v>
+        <v>46273.6204976852</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M34" s="3">
-        <v>46255.4177546296</v>
+        <v>46261.4379976852</v>
       </c>
       <c r="N34" s="3">
-        <v>46296.563587963</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>2604500</v>
+        <v>2606003</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>92</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="I35" s="3">
-        <v>46260.4812268519</v>
+        <v>46265.3599537037</v>
       </c>
       <c r="J35" s="3">
-        <v>46258.3485416667</v>
+        <v>46259.4993506944</v>
       </c>
       <c r="K35" s="0" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M35" s="3">
-        <v>46254.6270601852</v>
+        <v>46259.443287037</v>
       </c>
       <c r="N35" s="3">
-        <v>46260.4812268519</v>
+        <v>46290.75</v>
       </c>
       <c r="O35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>2603668</v>
+        <v>2604815</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F36" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="G36" s="0" t="s">
-        <v>94</v>
-      </c>
       <c r="H36" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I36" s="3">
-        <v>46259.3446296296</v>
+        <v>46296.563587963</v>
       </c>
       <c r="J36" s="3">
-        <v>46258.6426851852</v>
+        <v>46268.6781365741</v>
       </c>
       <c r="K36" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="M36" s="3">
-        <v>46253.427962963</v>
+        <v>46255.4177546296</v>
       </c>
       <c r="N36" s="3">
-        <v>46290.75</v>
+        <v>46296.563587963</v>
       </c>
       <c r="O36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>2602388</v>
+        <v>2604500</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I37" s="3">
-        <v>46255.4166666667</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="J37" s="3">
-        <v>46253.4900231482</v>
+        <v>46258.3485416667</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M37" s="3">
-        <v>46251.5527777778</v>
+        <v>46254.6270601852</v>
       </c>
       <c r="N37" s="3">
-        <v>46255.4166666667</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="O37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>2601999</v>
+        <v>2603668</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D38" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="G38" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="E38" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G38" s="0" t="s">
-        <v>97</v>
-      </c>
       <c r="H38" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="I38" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I38" s="3">
+        <v>46259.3446296296</v>
+      </c>
       <c r="J38" s="3">
-        <v>46266.6188194444</v>
+        <v>46258.6426851852</v>
       </c>
       <c r="K38" s="0" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="L38" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M38" s="3">
-        <v>46248.7351273148</v>
-      </c>
-      <c r="N38" s="3"/>
+        <v>46253.427962963</v>
+      </c>
+      <c r="N38" s="3">
+        <v>46290.75</v>
+      </c>
       <c r="O38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2600778</v>
+        <v>2602388</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="I39" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I39" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="J39" s="3">
-        <v>46274.3780324074</v>
+        <v>46253.4900231482</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="L39" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M39" s="3">
-        <v>46246.7171759259</v>
-      </c>
-      <c r="N39" s="3"/>
+        <v>46251.5527777778</v>
+      </c>
+      <c r="N39" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="O39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>2599732</v>
+        <v>2601999</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I40" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I40" s="3"/>
       <c r="J40" s="3">
-        <v>46248.3419117245</v>
+        <v>46266.6188194444</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M40" s="3">
-        <v>46245.4849537037</v>
-      </c>
-      <c r="N40" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>46248.7351273148</v>
+      </c>
+      <c r="N40" s="3"/>
       <c r="O40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>2598987</v>
+        <v>2600778</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I41" s="3">
-        <v>46254.6856134259</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="I41" s="3"/>
       <c r="J41" s="3">
-        <v>46251.536875</v>
+        <v>46274.3780324074</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="M41" s="3">
-        <v>46244.4564467593</v>
-      </c>
-      <c r="N41" s="3">
-        <v>46254.6856134259</v>
-      </c>
+        <v>46246.7171759259</v>
+      </c>
+      <c r="N41" s="3"/>
       <c r="O41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>2598910</v>
+        <v>2599732</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E42" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="F42" s="0" t="s">
-        <v>71</v>
-      </c>
       <c r="G42" s="0" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="I42" s="3">
-        <v>46254.6386574074</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="J42" s="3">
-        <v>46248.4760674769</v>
+        <v>46248.3419117245</v>
       </c>
       <c r="K42" s="0" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="M42" s="3">
-        <v>46244.4094907407</v>
+        <v>46245.4849537037</v>
       </c>
       <c r="N42" s="3">
-        <v>46261.6103125</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="O42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>2598767</v>
+        <v>2598987</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="I43" s="3">
-        <v>46247.6666666667</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="J43" s="3">
-        <v>46245.6608564815</v>
+        <v>46251.536875</v>
       </c>
       <c r="K43" s="0" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="M43" s="3">
-        <v>46241.757962963</v>
+        <v>46244.4564467593</v>
       </c>
       <c r="N43" s="3">
-        <v>46247.6666666667</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="O43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>2597798</v>
+        <v>2598910</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="C44" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G44" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G44" s="0" t="s">
-        <v>111</v>
-      </c>
       <c r="H44" s="0" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="I44" s="3">
-        <v>46290.75</v>
+        <v>46254.6386574074</v>
       </c>
       <c r="J44" s="3">
-        <v>46273.4412384259</v>
+        <v>46248.4760674769</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M44" s="3">
-        <v>46240.4508912037</v>
+        <v>46244.4094907407</v>
       </c>
       <c r="N44" s="3">
-        <v>46290.75</v>
+        <v>46261.6103125</v>
       </c>
       <c r="O44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>2597524</v>
+        <v>2598767</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="I45" s="3">
-        <v>46267.0453356481</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="J45" s="3">
-        <v>46259.4158333333</v>
+        <v>46245.6608564815</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M45" s="3">
-        <v>46239.6925347222</v>
+        <v>46241.757962963</v>
       </c>
       <c r="N45" s="3">
-        <v>46267.0453356481</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="O45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>2597515</v>
+        <v>2597798</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I46" s="3">
-        <v>46266.4759953704</v>
+        <v>46290.75</v>
       </c>
       <c r="J46" s="3">
-        <v>46261.4097453704</v>
+        <v>46273.4412384259</v>
       </c>
       <c r="K46" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="M46" s="3">
-        <v>46239.6856134259</v>
+        <v>46240.4508912037</v>
       </c>
       <c r="N46" s="3">
-        <v>46266.4759953704</v>
+        <v>46290.75</v>
       </c>
       <c r="O46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>2597495</v>
+        <v>2597524</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>115</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I47" s="3">
-        <v>46252.3333333333</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="J47" s="3">
-        <v>46241.6523302083</v>
+        <v>46259.4158333333</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M47" s="3">
-        <v>46239.6802199074</v>
+        <v>46239.6925347222</v>
       </c>
       <c r="N47" s="3">
-        <v>46245.5968865741</v>
-      </c>
-      <c r="O47" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>46267.0453356481</v>
+      </c>
+      <c r="O47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>2596882</v>
+        <v>2597515</v>
       </c>
       <c r="B48" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="G48" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="C48" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="D48" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="F48" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="G48" s="0" t="s">
-        <v>118</v>
-      </c>
       <c r="H48" s="0" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="I48" s="3">
-        <v>46280.3775578704</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="J48" s="3">
-        <v>46267.6170023148</v>
+        <v>46261.4097453704</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="M48" s="3">
-        <v>46238.7108912037</v>
+        <v>46239.6856134259</v>
       </c>
       <c r="N48" s="3">
-        <v>46280.3775578704</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="O48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>2596538</v>
+        <v>2597495</v>
       </c>
       <c r="B49" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E49" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="0" t="s">
-        <v>31</v>
-      </c>
       <c r="F49" s="0" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I49" s="3">
-        <v>46273.960787037</v>
+        <v>46252.3333333333</v>
       </c>
       <c r="J49" s="3">
-        <v>46286.3521412037</v>
+        <v>46241.6523302083</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="M49" s="3">
-        <v>46238.4644791667</v>
+        <v>46239.6802199074</v>
       </c>
       <c r="N49" s="3">
-        <v>46273.960787037</v>
-      </c>
-      <c r="O49" s="3"/>
+        <v>46245.5968865741</v>
+      </c>
+      <c r="O49" s="3">
+        <v>46252.3333333333</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>2596407</v>
+        <v>2596882</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>120</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I50" s="3">
-        <v>46248.6072106482</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="J50" s="3">
-        <v>46267.6164814815</v>
+        <v>46267.6170023148</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M50" s="3">
-        <v>46238.3780439815</v>
+        <v>46238.7108912037</v>
       </c>
       <c r="N50" s="3">
-        <v>46248.6072106482</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="O50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>2595510</v>
+        <v>2596538</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>121</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I51" s="3">
-        <v>46240.4984606481</v>
+        <v>46273.960787037</v>
       </c>
       <c r="J51" s="3">
-        <v>46245.3667592593</v>
+        <v>46286.3521412037</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="M51" s="3">
-        <v>46234.6442939815</v>
+        <v>46238.4644791667</v>
       </c>
       <c r="N51" s="3">
-        <v>46240.4984606481</v>
+        <v>46273.960787037</v>
       </c>
       <c r="O51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>2595497</v>
+        <v>2596407</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>122</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I52" s="3">
-        <v>46240.4978240741</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="J52" s="3">
-        <v>46245.3669444444</v>
+        <v>46267.6164814815</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="M52" s="3">
-        <v>46234.6436574074</v>
+        <v>46238.3780439815</v>
       </c>
       <c r="N52" s="3">
-        <v>46240.4978240741</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="O52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>2593529</v>
+        <v>2595510</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>123</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I53" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="J53" s="3">
-        <v>46233.4404570255</v>
+        <v>46245.3667592593</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M53" s="3">
-        <v>46231.6639930556</v>
+        <v>46234.6442939815</v>
       </c>
       <c r="N53" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="O53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>2593490</v>
+        <v>2595497</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I54" s="3">
-        <v>46239.6748032407</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="J54" s="3">
-        <v>46253.4905324074</v>
+        <v>46245.3669444444</v>
       </c>
       <c r="K54" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M54" s="3">
-        <v>46231.6518865741</v>
+        <v>46234.6436574074</v>
       </c>
       <c r="N54" s="3">
-        <v>46239.6748032407</v>
-      </c>
-      <c r="O54" s="3">
-        <v>46234.48125</v>
-      </c>
+        <v>46240.4978240741</v>
+      </c>
+      <c r="O54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>2593260</v>
+        <v>2593529</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>125</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I55" s="3">
-        <v>46241.6638888889</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="J55" s="3">
-        <v>46267.614525463</v>
+        <v>46233.4404570255</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="M55" s="3">
-        <v>46231.435150463</v>
+        <v>46231.6639930556</v>
       </c>
       <c r="N55" s="3">
-        <v>46241.6638888889</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="O55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>2593216</v>
+        <v>2593490</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F56" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="H56" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="I56" s="3">
+        <v>46239.6748032407</v>
+      </c>
+      <c r="J56" s="3">
+        <v>46253.4905324074</v>
+      </c>
+      <c r="K56" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="L56" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="G56" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="H56" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3">
-        <v>46231.4047453704</v>
-      </c>
-      <c r="K56" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="L56" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M56" s="3">
-        <v>46231.4011111111</v>
-      </c>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
+        <v>46231.6518865741</v>
+      </c>
+      <c r="N56" s="3">
+        <v>46239.6748032407</v>
+      </c>
+      <c r="O56" s="3">
+        <v>46234.48125</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>2592878</v>
+        <v>2593260</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E57" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F57" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="G57" s="0" t="s">
-        <v>128</v>
-      </c>
       <c r="H57" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I57" s="3">
-        <v>46241.3504282407</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="J57" s="3">
-        <v>46230.6675740741</v>
+        <v>46267.614525463</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M57" s="3">
-        <v>46230.6004282407</v>
+        <v>46231.435150463</v>
       </c>
       <c r="N57" s="3">
-        <v>46290.75</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="O57" s="3"/>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>2592468</v>
+        <v>2593216</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E58" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F58" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="F58" s="0" t="s">
-        <v>54</v>
-      </c>
       <c r="G58" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="I58" s="3">
-        <v>46237.6038657407</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="I58" s="3"/>
       <c r="J58" s="3">
-        <v>46240.6136738773</v>
+        <v>46231.4047453704</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M58" s="3">
-        <v>46227.7107060185</v>
-      </c>
-      <c r="N58" s="3">
-        <v>46293.6033680556</v>
-      </c>
+        <v>46231.4011111111</v>
+      </c>
+      <c r="N58" s="3"/>
       <c r="O58" s="3"/>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>2591596</v>
+        <v>2592878</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>130</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I59" s="3">
-        <v>46238.7083333333</v>
+        <v>46241.3504282407</v>
       </c>
       <c r="J59" s="3">
-        <v>46267.3444803241</v>
+        <v>46230.6675740741</v>
       </c>
       <c r="K59" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M59" s="3">
-        <v>46226.4797916667</v>
+        <v>46230.6004282407</v>
       </c>
       <c r="N59" s="3">
-        <v>46282.6141435185</v>
+        <v>46290.75</v>
       </c>
       <c r="O59" s="3"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2591284</v>
+        <v>2592468</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G60" s="0" t="s">
         <v>131</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I60" s="3">
-        <v>46266.3384837963</v>
+        <v>46237.6038657407</v>
       </c>
       <c r="J60" s="3">
-        <v>46225.7002398495</v>
+        <v>46240.6136738773</v>
       </c>
       <c r="K60" s="0" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M60" s="3">
-        <v>46225.6718171296</v>
+        <v>46227.7107060185</v>
       </c>
       <c r="N60" s="3">
-        <v>46266.3384837963</v>
+        <v>46293.6033680556</v>
       </c>
       <c r="O60" s="3"/>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>2588490</v>
+        <v>2591596</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>132</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I61" s="3">
-        <v>46230.722037037</v>
+        <v>46238.7083333333</v>
       </c>
       <c r="J61" s="3">
-        <v>46231.4339699074</v>
+        <v>46267.3444803241</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M61" s="3">
-        <v>46218.4928703704</v>
+        <v>46226.4797916667</v>
       </c>
       <c r="N61" s="3">
-        <v>46230.722037037</v>
+        <v>46282.6141435185</v>
       </c>
       <c r="O61" s="3"/>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>2588025</v>
+        <v>2591284</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D62" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="E62" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="F62" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="G62" s="0" t="s">
-        <v>136</v>
-      </c>
       <c r="H62" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="I62" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="I62" s="3">
+        <v>46266.3384837963</v>
+      </c>
       <c r="J62" s="3">
-        <v>46267.5903356482</v>
+        <v>46225.7002398495</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="M62" s="3">
-        <v>46217.612962963</v>
-      </c>
-      <c r="N62" s="3"/>
+        <v>46225.6718171296</v>
+      </c>
+      <c r="N62" s="3">
+        <v>46266.3384837963</v>
+      </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>2587849</v>
+        <v>2588490</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E63" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I63" s="3">
-        <v>46226.6083796296</v>
+        <v>46230.722037037</v>
       </c>
       <c r="J63" s="3">
-        <v>46237.9144806713</v>
+        <v>46231.4339699074</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="M63" s="3">
-        <v>46217.4506597222</v>
+        <v>46218.4928703704</v>
       </c>
       <c r="N63" s="3">
-        <v>46226.6083796296</v>
+        <v>46230.722037037</v>
       </c>
       <c r="O63" s="3"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2587713</v>
+        <v>2588025</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>138</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I64" s="3">
-        <v>46218.7408680556</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I64" s="3"/>
       <c r="J64" s="3">
-        <v>46230.4199074074</v>
+        <v>46267.5903356482</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M64" s="3">
-        <v>46217.3658680556</v>
-      </c>
-      <c r="N64" s="3">
-        <v>46218.7408680556</v>
-      </c>
+        <v>46217.612962963</v>
+      </c>
+      <c r="N64" s="3"/>
       <c r="O64" s="3"/>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2587585</v>
+        <v>2587849</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>139</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I65" s="3">
-        <v>46220.6264583333</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="J65" s="3">
-        <v>46259.4474884259</v>
+        <v>46237.9144806713</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M65" s="3">
-        <v>46216.7097916667</v>
+        <v>46217.4506597222</v>
       </c>
       <c r="N65" s="3">
-        <v>46220.6264583333</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="O65" s="3"/>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>2587006</v>
+        <v>2587713</v>
       </c>
       <c r="B66" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E66" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C66" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D66" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F66" s="0" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>140</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I66" s="3">
-        <v>46217.7289699074</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="J66" s="3">
-        <v>46227.4549884259</v>
+        <v>46230.4199074074</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="M66" s="3">
-        <v>46213.7239236111</v>
+        <v>46217.3658680556</v>
       </c>
       <c r="N66" s="3">
-        <v>46217.7289699074</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>2586984</v>
+        <v>2587585</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>141</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I67" s="3">
-        <v>46295.7416550926</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="J67" s="3">
-        <v>46273.4946180556</v>
+        <v>46259.4474884259</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M67" s="3">
-        <v>46213.6971527778</v>
+        <v>46216.7097916667</v>
       </c>
       <c r="N67" s="3">
-        <v>46295.7416550926</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="O67" s="3"/>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>2586910</v>
+        <v>2587006</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F68" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="G68" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="G68" s="0" t="s">
-        <v>143</v>
-      </c>
       <c r="H68" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I68" s="3">
-        <v>46226.5833333333</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="J68" s="3">
-        <v>46230.4194212963</v>
+        <v>46227.4549884259</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="M68" s="3">
-        <v>46213.6245833333</v>
+        <v>46213.7239236111</v>
       </c>
       <c r="N68" s="3">
-        <v>46226.5833333333</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="O68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>2586651</v>
+        <v>2586984</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>144</v>
+        <v>35</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I69" s="3">
-        <v>46218.7157407407</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="J69" s="3">
-        <v>46213.3824074074</v>
+        <v>46273.4946180556</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M69" s="3">
-        <v>46213.3824074074</v>
+        <v>46213.6971527778</v>
       </c>
       <c r="N69" s="3">
-        <v>46218.7157407407</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="O69" s="3"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>2586187</v>
+        <v>2586910</v>
       </c>
       <c r="B70" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E70" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C70" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D70" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="E70" s="0" t="s">
-        <v>17</v>
-      </c>
       <c r="F70" s="0" t="s">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I70" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I70" s="3">
+        <v>46226.5833333333</v>
+      </c>
       <c r="J70" s="3">
-        <v>46219.3850231481</v>
+        <v>46230.4194212963</v>
       </c>
       <c r="K70" s="0" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M70" s="3">
-        <v>46211.7697337963</v>
-      </c>
-      <c r="N70" s="3"/>
+        <v>46213.6245833333</v>
+      </c>
+      <c r="N70" s="3">
+        <v>46226.5833333333</v>
+      </c>
       <c r="O70" s="3"/>
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>2585888</v>
+        <v>2586651</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I71" s="3">
-        <v>46217.4119907407</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="J71" s="3">
-        <v>46217.5003587963</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="K71" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M71" s="3">
-        <v>46211.4953240741</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="N71" s="3">
-        <v>46290.75</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="O71" s="3"/>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>2585424</v>
+        <v>2586187</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>149</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I72" s="3">
-        <v>46223.3927199074</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I72" s="3"/>
       <c r="J72" s="3">
-        <v>46234.4964930556</v>
+        <v>46219.3850231481</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="M72" s="3">
-        <v>46210.6427199074</v>
-      </c>
-      <c r="N72" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46211.7697337963</v>
+      </c>
+      <c r="N72" s="3"/>
       <c r="O72" s="3"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>2584638</v>
+        <v>2585888</v>
       </c>
       <c r="B73" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E73" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C73" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D73" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="0" t="s">
-        <v>35</v>
-      </c>
       <c r="F73" s="0" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>150</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="I73" s="3">
-        <v>46213.4171527778</v>
+        <v>46217.4119907407</v>
       </c>
       <c r="J73" s="3">
-        <v>46213.4090859607</v>
+        <v>46217.5003587963</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M73" s="3">
-        <v>46209.5016203704</v>
+        <v>46211.4953240741</v>
       </c>
       <c r="N73" s="3">
-        <v>46232.3874884259</v>
+        <v>46290.75</v>
       </c>
       <c r="O73" s="3"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2584397</v>
+        <v>2585424</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>151</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I74" s="3">
-        <v>46212.6757175926</v>
+        <v>46223.3927199074</v>
       </c>
       <c r="J74" s="3">
-        <v>46213.3741550926</v>
+        <v>46234.4964930556</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="M74" s="3">
-        <v>46209.3423842593</v>
+        <v>46210.6427199074</v>
       </c>
       <c r="N74" s="3">
-        <v>46212.6757175926</v>
+        <v>46290.75</v>
       </c>
       <c r="O74" s="3"/>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2584167</v>
+        <v>2584638</v>
       </c>
       <c r="B75" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E75" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C75" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D75" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E75" s="0" t="s">
-        <v>31</v>
-      </c>
       <c r="F75" s="0" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>152</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="I75" s="3">
-        <v>46246.7216435185</v>
+        <v>46213.4171527778</v>
       </c>
       <c r="J75" s="3">
-        <v>46247.4396759259</v>
+        <v>46213.4090859607</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M75" s="3">
-        <v>46206.6383101852</v>
+        <v>46209.5016203704</v>
       </c>
       <c r="N75" s="3">
-        <v>46246.7216435185</v>
+        <v>46232.3874884259</v>
       </c>
       <c r="O75" s="3"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>2583950</v>
+        <v>2584397</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>153</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I76" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I76" s="3">
+        <v>46212.6757175926</v>
+      </c>
       <c r="J76" s="3">
-        <v>46273.4100925926</v>
+        <v>46213.3741550926</v>
       </c>
       <c r="K76" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L76" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M76" s="3">
-        <v>46206.4623148148</v>
-      </c>
-      <c r="N76" s="3"/>
+        <v>46209.3423842593</v>
+      </c>
+      <c r="N76" s="3">
+        <v>46212.6757175926</v>
+      </c>
       <c r="O76" s="3"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>2583447</v>
+        <v>2584167</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>154</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I77" s="3">
-        <v>46205.7916666667</v>
+        <v>46246.7216435185</v>
       </c>
       <c r="J77" s="3">
-        <v>46265.3645138889</v>
+        <v>46247.4396759259</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M77" s="3">
-        <v>46205.5752083333</v>
+        <v>46206.6383101852</v>
       </c>
       <c r="N77" s="3">
-        <v>46245.6724189815</v>
+        <v>46246.7216435185</v>
       </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>2583382</v>
+        <v>2583950</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="D78" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G78" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="E78" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F78" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="G78" s="0" t="s">
-        <v>156</v>
-      </c>
       <c r="H78" s="0" t="s">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="3">
-        <v>46279.4689699074</v>
+        <v>46273.4100925926</v>
       </c>
       <c r="K78" s="0" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M78" s="3">
-        <v>46205.4905092593</v>
+        <v>46206.4623148148</v>
       </c>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2582452</v>
+        <v>2583447</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I79" s="3">
-        <v>46244.4166666667</v>
+        <v>46205.7916666667</v>
       </c>
       <c r="J79" s="3">
-        <v>46204.7763078704</v>
+        <v>46265.3645138889</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M79" s="3">
-        <v>46203.8250810185</v>
+        <v>46205.5752083333</v>
       </c>
       <c r="N79" s="3">
-        <v>46244.4166666667</v>
+        <v>46245.6724189815</v>
       </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>2582352</v>
+        <v>2583382</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="G80" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="H80" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="H80" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I80" s="3">
-        <v>46244.340775463</v>
-      </c>
+      <c r="I80" s="3"/>
       <c r="J80" s="3">
-        <v>46204.7761805556</v>
+        <v>46279.4689699074</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="M80" s="3">
-        <v>46203.6741087963</v>
-      </c>
-      <c r="N80" s="3">
-        <v>46244.340775463</v>
-      </c>
+        <v>46205.4905092593</v>
+      </c>
+      <c r="N80" s="3"/>
       <c r="O80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>2579299</v>
+        <v>2582452</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F81" s="0" t="s">
         <v>73</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I81" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I81" s="3">
+        <v>46244.4166666667</v>
+      </c>
       <c r="J81" s="3">
-        <v>46204.3277777778</v>
+        <v>46204.7763078704</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="M81" s="3">
-        <v>46196.4165162037</v>
-      </c>
-      <c r="N81" s="3"/>
+        <v>46203.8250810185</v>
+      </c>
+      <c r="N81" s="3">
+        <v>46244.4166666667</v>
+      </c>
       <c r="O81" s="3"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>2576326</v>
+        <v>2582352</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I82" s="3">
-        <v>46192.7916666667</v>
+        <v>46244.340775463</v>
       </c>
       <c r="J82" s="3">
-        <v>46230.6812731481</v>
+        <v>46204.7761805556</v>
       </c>
       <c r="K82" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="M82" s="3">
-        <v>46189.3995833333</v>
-      </c>
-      <c r="N82" s="3"/>
+        <v>46203.6741087963</v>
+      </c>
+      <c r="N82" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>2574153</v>
+        <v>2579299</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>163</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I83" s="3"/>
       <c r="J83" s="3">
-        <v>46204.3218402778</v>
+        <v>46204.3277777778</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M83" s="3">
-        <v>46183.4711226852</v>
+        <v>46196.4165162037</v>
       </c>
       <c r="N83" s="3"/>
       <c r="O83" s="3"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>2572707</v>
+        <v>2576326</v>
       </c>
       <c r="B84" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C84" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="E84" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F84" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="G84" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="C84" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="D84" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E84" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="F84" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="G84" s="0" t="s">
-        <v>166</v>
-      </c>
       <c r="H84" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I84" s="3">
-        <v>46219.3964814815</v>
+        <v>46192.7916666667</v>
       </c>
       <c r="J84" s="3">
-        <v>46188.4629166667</v>
+        <v>46230.6812731481</v>
       </c>
       <c r="K84" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="M84" s="3">
-        <v>46178.7298148148</v>
-      </c>
-      <c r="N84" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>46189.3995833333</v>
+      </c>
+      <c r="N84" s="3"/>
       <c r="O84" s="3"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>2570274</v>
+        <v>2574153</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I85" s="3"/>
       <c r="J85" s="3">
-        <v>46204.3220138889</v>
+        <v>46204.3218402778</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M85" s="3">
-        <v>46171.6563773148</v>
+        <v>46183.4711226852</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>2562116</v>
+        <v>2572707</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I86" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I86" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="J86" s="3">
-        <v>46160.7191666667</v>
+        <v>46188.4629166667</v>
       </c>
       <c r="K86" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L86" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="M86" s="3">
-        <v>46154.3432638889</v>
-      </c>
-      <c r="N86" s="3"/>
+        <v>46178.7298148148</v>
+      </c>
+      <c r="N86" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="O86" s="3"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>2558553</v>
+        <v>2570274</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>170</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="I87" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="I87" s="3"/>
       <c r="J87" s="3">
-        <v>46154.5888773148</v>
+        <v>46204.3220138889</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M87" s="3">
-        <v>46146.3561805556</v>
-      </c>
-      <c r="N87" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>46171.6563773148</v>
+      </c>
+      <c r="N87" s="3"/>
       <c r="O87" s="3"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>2556271</v>
+        <v>2562116</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F88" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="G88" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="G88" s="0" t="s">
-        <v>172</v>
-      </c>
       <c r="H88" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I88" s="3">
-        <v>46141.4297453704</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="I88" s="3"/>
       <c r="J88" s="3">
-        <v>46139.9871412037</v>
+        <v>46160.7191666667</v>
       </c>
       <c r="K88" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M88" s="3">
-        <v>46139.471412037</v>
-      </c>
-      <c r="N88" s="3">
-        <v>46141.4901157407</v>
-      </c>
+        <v>46154.3432638889</v>
+      </c>
+      <c r="N88" s="3"/>
       <c r="O88" s="3"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>2556211</v>
+        <v>2558553</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I89" s="3">
-        <v>46150.6617476852</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="J89" s="3">
-        <v>46146.3663773148</v>
+        <v>46154.5888773148</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="M89" s="3">
-        <v>46139.4325810185</v>
+        <v>46146.3561805556</v>
       </c>
       <c r="N89" s="3">
-        <v>46150.6617476852</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="O89" s="3"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2556029</v>
+        <v>2556271</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>174</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I90" s="3">
-        <v>46150.5</v>
+        <v>46141.4297453704</v>
       </c>
       <c r="J90" s="3">
-        <v>46146.401875</v>
+        <v>46139.9871412037</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="M90" s="3">
-        <v>46138.757337963</v>
+        <v>46139.471412037</v>
       </c>
       <c r="N90" s="3">
-        <v>46154.6616087963</v>
+        <v>46141.4901157407</v>
       </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>2554341</v>
+        <v>2556211</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>175</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I91" s="3">
-        <v>46136.3599768519</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="J91" s="3">
-        <v>46135.6585185185</v>
+        <v>46146.3663773148</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="M91" s="3">
-        <v>46134.4016435185</v>
+        <v>46139.4325810185</v>
       </c>
       <c r="N91" s="3">
-        <v>46136.3599768519</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>2547638</v>
+        <v>2556029</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E92" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>176</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I92" s="3">
-        <v>46150.3473611111</v>
+        <v>46150.5</v>
       </c>
       <c r="J92" s="3">
-        <v>46119.5010069444</v>
+        <v>46146.401875</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="M92" s="3">
-        <v>46114.4931944444</v>
+        <v>46138.757337963</v>
       </c>
       <c r="N92" s="3">
-        <v>46150.3473611111</v>
+        <v>46154.6616087963</v>
       </c>
       <c r="O92" s="3"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>2537054</v>
+        <v>2554341</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E93" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>177</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I93" s="3">
-        <v>46093.4339236111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="J93" s="3">
-        <v>46090.3698263889</v>
+        <v>46135.6585185185</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M93" s="3">
-        <v>46087.5797569444</v>
+        <v>46134.4016435185</v>
       </c>
       <c r="N93" s="3">
-        <v>46093.4339236111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="O93" s="3"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>2531696</v>
+        <v>2547638</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>178</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I94" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I94" s="3">
+        <v>46150.3473611111</v>
+      </c>
       <c r="J94" s="3">
-        <v>46204.3216782407</v>
+        <v>46119.5010069444</v>
       </c>
       <c r="K94" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L94" s="0" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="M94" s="3">
-        <v>46076.5833912037</v>
-      </c>
-      <c r="N94" s="3"/>
+        <v>46114.4931944444</v>
+      </c>
+      <c r="N94" s="3">
+        <v>46150.3473611111</v>
+      </c>
       <c r="O94" s="3"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>2530739</v>
+        <v>2537054</v>
       </c>
       <c r="B95" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="C95" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E95" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F95" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G95" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="C95" s="0" t="s">
-        <v>180</v>
-      </c>
-      <c r="D95" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="E95" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F95" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="G95" s="0" t="s">
-        <v>181</v>
-      </c>
       <c r="H95" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="I95" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I95" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="J95" s="3">
-        <v>46218.6914940625</v>
+        <v>46090.3698263889</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="L95" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M95" s="3">
-        <v>46072.6973148148</v>
-      </c>
-      <c r="N95" s="3"/>
+        <v>46087.5797569444</v>
+      </c>
+      <c r="N95" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="O95" s="3"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>2529639</v>
+        <v>2531696</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I96" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="I96" s="3"/>
       <c r="J96" s="3">
-        <v>46072.6891666667</v>
+        <v>46204.3216782407</v>
       </c>
       <c r="K96" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L96" s="0" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="M96" s="3">
-        <v>46069.5930902778</v>
-      </c>
-      <c r="N96" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>46076.5833912037</v>
+      </c>
+      <c r="N96" s="3"/>
       <c r="O96" s="3"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>2529591</v>
+        <v>2530739</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>41</v>
+        <v>181</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>183</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I97" s="3">
-        <v>46108.5968055556</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I97" s="3"/>
       <c r="J97" s="3">
-        <v>46126.6875</v>
+        <v>46218.6914940625</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="M97" s="3">
-        <v>46069.4509722222</v>
-      </c>
-      <c r="N97" s="3">
-        <v>46108.5968055556</v>
-      </c>
+        <v>46072.6973148148</v>
+      </c>
+      <c r="N97" s="3"/>
       <c r="O97" s="3"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>2528858</v>
+        <v>2529639</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G98" s="0" t="s">
         <v>184</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I98" s="3">
-        <v>46107.3861458333</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="J98" s="3">
-        <v>46087.6277662037</v>
+        <v>46072.6891666667</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M98" s="3">
-        <v>46065.7194791667</v>
+        <v>46069.5930902778</v>
       </c>
       <c r="N98" s="3">
-        <v>46107.3861458333</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="O98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>2525312</v>
+        <v>2529591</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>185</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I99" s="3">
-        <v>46070.5877314815</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="J99" s="3">
-        <v>46062.7587037037</v>
+        <v>46126.6875</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M99" s="3">
-        <v>46058.3585648148</v>
+        <v>46069.4509722222</v>
       </c>
       <c r="N99" s="3">
-        <v>46070.5877314815</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="O99" s="3"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>2525272</v>
+        <v>2528858</v>
       </c>
       <c r="B100" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E100" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F100" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G100" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="C100" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="D100" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="E100" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F100" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G100" s="0" t="s">
-        <v>188</v>
-      </c>
       <c r="H100" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I100" s="3">
-        <v>46203.7916666667</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="J100" s="3">
-        <v>46126.7441782407</v>
+        <v>46087.6277662037</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L100" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="M100" s="3">
-        <v>46058.2883101852</v>
-      </c>
-      <c r="N100" s="3"/>
+        <v>46065.7194791667</v>
+      </c>
+      <c r="N100" s="3">
+        <v>46107.3861458333</v>
+      </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>2524577</v>
+        <v>2525312</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="I101" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I101" s="3">
+        <v>46070.5877314815</v>
+      </c>
       <c r="J101" s="3">
-        <v>46267.4298180903</v>
+        <v>46062.7587037037</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="M101" s="3">
-        <v>46056.697349537</v>
-      </c>
-      <c r="N101" s="3"/>
+        <v>46058.3585648148</v>
+      </c>
+      <c r="N101" s="3">
+        <v>46070.5877314815</v>
+      </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>2524373</v>
+        <v>2525272</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I102" s="3">
-        <v>46087.3854513889</v>
+        <v>46203.7916666667</v>
       </c>
       <c r="J102" s="3">
-        <v>46056.6543865741</v>
+        <v>46126.7441782407</v>
       </c>
       <c r="K102" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L102" s="0" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="M102" s="3">
-        <v>46056.5937847222</v>
-      </c>
-      <c r="N102" s="3">
-        <v>46087.3854513889</v>
-      </c>
+        <v>46058.2883101852</v>
+      </c>
+      <c r="N102" s="3"/>
       <c r="O102" s="3"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>2524062</v>
+        <v>2524577</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G103" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="H103" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="H103" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I103" s="3">
-        <v>46057.7412615741</v>
-      </c>
+      <c r="I103" s="3"/>
       <c r="J103" s="3">
-        <v>46056.6210300926</v>
+        <v>46267.4298180903</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M103" s="3">
-        <v>46056.3662615741</v>
-      </c>
-      <c r="N103" s="3">
-        <v>46057.7412615741</v>
-      </c>
+        <v>46056.697349537</v>
+      </c>
+      <c r="N103" s="3"/>
       <c r="O103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>2523635</v>
+        <v>2524373</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>193</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I104" s="3">
-        <v>46059.4164236111</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="J104" s="3">
-        <v>46055.6034837963</v>
+        <v>46056.6543865741</v>
       </c>
       <c r="K104" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="M104" s="3">
-        <v>46055.4997569444</v>
+        <v>46056.5937847222</v>
       </c>
       <c r="N104" s="3">
-        <v>46059.4164236111</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="O104" s="3"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>2523602</v>
+        <v>2524062</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E105" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F105" s="0" t="s">
         <v>35</v>
-      </c>
-      <c r="F105" s="0" t="s">
-        <v>54</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>194</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I105" s="3">
-        <v>46093.6246643519</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="J105" s="3">
-        <v>46056.5784027778</v>
+        <v>46056.6210300926</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="M105" s="3">
-        <v>46055.4788310185</v>
+        <v>46056.3662615741</v>
       </c>
       <c r="N105" s="3">
-        <v>46093.6246643519</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="O105" s="3"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>2521645</v>
+        <v>2523635</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>195</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="I106" s="3">
-        <v>46062.5</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="J106" s="3">
-        <v>46050.3426763542</v>
+        <v>46055.6034837963</v>
       </c>
       <c r="K106" s="0" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="L106" s="0" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="M106" s="3">
-        <v>46049.7714236111</v>
-      </c>
-      <c r="N106" s="3"/>
+        <v>46055.4997569444</v>
+      </c>
+      <c r="N106" s="3">
+        <v>46059.4164236111</v>
+      </c>
       <c r="O106" s="3"/>
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>2521079</v>
+        <v>2523602</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>196</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I107" s="3">
-        <v>46052.6666666667</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="J107" s="3">
-        <v>46056.6197800926</v>
+        <v>46056.5784027778</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="M107" s="3">
-        <v>46048.7684490741</v>
+        <v>46055.4788310185</v>
       </c>
       <c r="N107" s="3">
-        <v>46061.6309722222</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="O107" s="3"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>2520048</v>
+        <v>2521645</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>180</v>
+        <v>118</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>197</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="I108" s="3">
-        <v>46057.5</v>
+        <v>46062.5</v>
       </c>
       <c r="J108" s="3">
-        <v>46052.5774305556</v>
+        <v>46050.3426763542</v>
       </c>
       <c r="K108" s="0" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="L108" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M108" s="3">
-        <v>46045.3325578704</v>
-      </c>
-      <c r="N108" s="3">
-        <v>46057.5</v>
-      </c>
+        <v>46049.7714236111</v>
+      </c>
+      <c r="N108" s="3"/>
       <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>2519904</v>
+        <v>2521079</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>198</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I109" s="3">
-        <v>46084.7217939815</v>
+        <v>46052.6666666667</v>
       </c>
       <c r="J109" s="3">
-        <v>46044.7413888889</v>
+        <v>46056.6197800926</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M109" s="3">
-        <v>46044.6384606482</v>
+        <v>46048.7684490741</v>
       </c>
       <c r="N109" s="3">
-        <v>46084.7217939815</v>
+        <v>46061.6309722222</v>
       </c>
       <c r="O109" s="3"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>2519523</v>
+        <v>2520048</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>199</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I110" s="3">
-        <v>46076.5902777778</v>
+        <v>46057.5</v>
       </c>
       <c r="J110" s="3">
-        <v>46048.4589814815</v>
+        <v>46052.5774305556</v>
       </c>
       <c r="K110" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L110" s="0" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="M110" s="3">
-        <v>46043.7362847222</v>
+        <v>46045.3325578704</v>
       </c>
       <c r="N110" s="3">
-        <v>46077.380775463</v>
+        <v>46057.5</v>
       </c>
       <c r="O110" s="3"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>2519383</v>
+        <v>2519904</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E111" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F111" s="0" t="s">
         <v>35</v>
-      </c>
-      <c r="F111" s="0" t="s">
-        <v>54</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>200</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I111" s="3">
-        <v>46076.399224537</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="J111" s="3">
-        <v>46048.4599305556</v>
+        <v>46044.7413888889</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="M111" s="3">
-        <v>46043.6075578704</v>
+        <v>46044.6384606482</v>
       </c>
       <c r="N111" s="3">
-        <v>46076.399224537</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="O111" s="3"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>2519284</v>
+        <v>2519523</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I112" s="3">
-        <v>46049.3982986111</v>
+        <v>46076.5902777778</v>
       </c>
       <c r="J112" s="3">
-        <v>46043.742337963</v>
+        <v>46048.4589814815</v>
       </c>
       <c r="K112" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="M112" s="3">
-        <v>46043.4816319444</v>
+        <v>46043.7362847222</v>
       </c>
       <c r="N112" s="3">
-        <v>46049.3982986111</v>
+        <v>46077.380775463</v>
       </c>
       <c r="O112" s="3"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>2518650</v>
+        <v>2519383</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I113" s="3">
-        <v>46072.3536921296</v>
+        <v>46076.399224537</v>
       </c>
       <c r="J113" s="3">
-        <v>46043.8185648148</v>
+        <v>46048.4599305556</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="M113" s="3">
-        <v>46042.3536921296</v>
+        <v>46043.6075578704</v>
       </c>
       <c r="N113" s="3">
-        <v>46080.437025463</v>
+        <v>46076.399224537</v>
       </c>
       <c r="O113" s="3"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>2513117</v>
+        <v>2519284</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I114" s="3">
-        <v>46031.4922800926</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="J114" s="3">
-        <v>46028.3500347222</v>
+        <v>46043.742337963</v>
       </c>
       <c r="K114" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L114" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M114" s="3">
-        <v>46027.6381134259</v>
+        <v>46043.4816319444</v>
       </c>
       <c r="N114" s="3">
-        <v>46031.4922800926</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="O114" s="3"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>2512883</v>
+        <v>2518650</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>203</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I115" s="3">
-        <v>46037.6340972222</v>
+        <v>46072.3536921296</v>
       </c>
       <c r="J115" s="3">
-        <v>46129.4199421296</v>
+        <v>46043.8185648148</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M115" s="3">
-        <v>46027.4049305556</v>
+        <v>46042.3536921296</v>
       </c>
       <c r="N115" s="3">
-        <v>46141.6335300926</v>
+        <v>46080.437025463</v>
       </c>
       <c r="O115" s="3"/>
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>2512542</v>
+        <v>2513117</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>204</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I116" s="3">
-        <v>46036.5</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="J116" s="3">
-        <v>46024.5900925926</v>
+        <v>46028.3500347222</v>
       </c>
       <c r="K116" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L116" s="0" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="M116" s="3">
-        <v>46022.6836342593</v>
+        <v>46027.6381134259</v>
       </c>
       <c r="N116" s="3">
-        <v>46036.5</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="O116" s="3"/>
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>2512541</v>
+        <v>2512883</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>205</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I117" s="3">
-        <v>46036.5</v>
+        <v>46037.6340972222</v>
       </c>
       <c r="J117" s="3">
-        <v>46022.7128356481</v>
+        <v>46129.4199421296</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M117" s="3">
-        <v>46022.6762615741</v>
+        <v>46027.4049305556</v>
       </c>
       <c r="N117" s="3">
-        <v>46036.5</v>
+        <v>46141.6335300926</v>
       </c>
       <c r="O117" s="3"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>2509014</v>
+        <v>2512542</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>206</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I118" s="3">
-        <v>46044.7250578704</v>
+        <v>46036.5</v>
       </c>
       <c r="J118" s="3">
-        <v>46022.6138541667</v>
+        <v>46024.5900925926</v>
       </c>
       <c r="K118" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L118" s="0" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="M118" s="3">
-        <v>46008.454224537</v>
+        <v>46022.6836342593</v>
       </c>
       <c r="N118" s="3">
-        <v>46045.4708564815</v>
+        <v>46036.5</v>
       </c>
       <c r="O118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>2506714</v>
+        <v>2512541</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>207</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I119" s="3">
-        <v>46038.7073032407</v>
+        <v>46036.5</v>
       </c>
       <c r="J119" s="3">
-        <v>46044.7372337963</v>
+        <v>46022.7128356481</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="M119" s="3">
-        <v>46002.4364699074</v>
+        <v>46022.6762615741</v>
       </c>
       <c r="N119" s="3">
-        <v>46038.7073032407</v>
+        <v>46036.5</v>
       </c>
       <c r="O119" s="3"/>
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <v>2506599</v>
+        <v>2509014</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>208</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I120" s="3">
-        <v>46037.61375</v>
+        <v>46044.7250578704</v>
       </c>
       <c r="J120" s="3">
-        <v>46052.3252083333</v>
+        <v>46022.6138541667</v>
       </c>
       <c r="K120" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L120" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M120" s="3">
-        <v>46002.3429166667</v>
+        <v>46008.454224537</v>
       </c>
       <c r="N120" s="3">
-        <v>46037.61375</v>
+        <v>46045.4708564815</v>
       </c>
       <c r="O120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <v>2506311</v>
+        <v>2506714</v>
       </c>
       <c r="B121" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="C121" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="D121" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="F121" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="G121" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="C121" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="D121" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="E121" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="F121" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="G121" s="0" t="s">
-        <v>210</v>
-      </c>
       <c r="H121" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I121" s="3">
-        <v>46013.7291666667</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="J121" s="3">
-        <v>46013.461875</v>
+        <v>46044.7372337963</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="M121" s="3">
-        <v>46001.5219328704</v>
+        <v>46002.4364699074</v>
       </c>
       <c r="N121" s="3">
-        <v>46013.7291666667</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="O121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <v>2506102</v>
+        <v>2506599</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I122" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I122" s="3">
+        <v>46037.61375</v>
+      </c>
       <c r="J122" s="3">
-        <v>46241.5032638889</v>
+        <v>46052.3252083333</v>
       </c>
       <c r="K122" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L122" s="0" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="M122" s="3">
-        <v>46001.3800578704</v>
-      </c>
-      <c r="N122" s="3"/>
+        <v>46002.3429166667</v>
+      </c>
+      <c r="N122" s="3">
+        <v>46037.61375</v>
+      </c>
       <c r="O122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <v>2502589</v>
+        <v>2506311</v>
       </c>
       <c r="B123" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="C123" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="D123" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="E123" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="F123" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="G123" s="0" t="s">
         <v>212</v>
       </c>
-      <c r="C123" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="D123" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E123" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="F123" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="G123" s="0" t="s">
-        <v>213</v>
-      </c>
       <c r="H123" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I123" s="3">
-        <v>46029.6634375</v>
+        <v>46013.7291666667</v>
       </c>
       <c r="J123" s="3">
-        <v>46014.6931018519</v>
+        <v>46013.461875</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="M123" s="3">
-        <v>45993.3791087963</v>
+        <v>46001.5219328704</v>
       </c>
       <c r="N123" s="3">
-        <v>46029.6634375</v>
+        <v>46013.7291666667</v>
       </c>
       <c r="O123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <v>2502438</v>
+        <v>2506102</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>26</v>
+        <v>144</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I124" s="3">
-        <v>46037.3801388889</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="I124" s="3"/>
       <c r="J124" s="3">
-        <v>45996.4823032407</v>
+        <v>46241.5032638889</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L124" s="0" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="M124" s="3">
-        <v>45992.7134722222</v>
-      </c>
-      <c r="N124" s="3">
-        <v>46037.3801388889</v>
-      </c>
+        <v>46001.3800578704</v>
+      </c>
+      <c r="N124" s="3"/>
       <c r="O124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <v>2501349</v>
+        <v>2502589</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>215</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I125" s="3">
-        <v>46069.7381944444</v>
+        <v>46029.6634375</v>
       </c>
       <c r="J125" s="3">
-        <v>46069.3651388889</v>
+        <v>46014.6931018519</v>
       </c>
       <c r="K125" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="M125" s="3">
-        <v>45989.0365856482</v>
+        <v>45993.3791087963</v>
       </c>
       <c r="N125" s="3">
-        <v>46069.7381944444</v>
+        <v>46029.6634375</v>
       </c>
       <c r="O125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <v>2500635</v>
+        <v>2502438</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>216</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I126" s="3">
-        <v>46024.4633796296</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="J126" s="3">
-        <v>46027.3611111111</v>
+        <v>45996.4823032407</v>
       </c>
       <c r="K126" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="M126" s="3">
-        <v>45987.671712963</v>
+        <v>45992.7134722222</v>
       </c>
       <c r="N126" s="3">
-        <v>46024.4633796296</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="O126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <v>2498066</v>
+        <v>2501349</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>155</v>
+        <v>34</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>217</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I127" s="3">
-        <v>46073.7916666667</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="J127" s="3">
-        <v>46126.6953240741</v>
+        <v>46069.3651388889</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="M127" s="3">
-        <v>45979.750162037</v>
-      </c>
-      <c r="N127" s="3"/>
+        <v>45989.0365856482</v>
+      </c>
+      <c r="N127" s="3">
+        <v>46069.7381944444</v>
+      </c>
       <c r="O127" s="3"/>
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <v>2494282</v>
+        <v>2500635</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D128" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E128" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F128" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="G128" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="E128" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F128" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="G128" s="0" t="s">
-        <v>219</v>
-      </c>
       <c r="H128" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I128" s="3">
-        <v>45986.48125</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="J128" s="3">
-        <v>45988.567025463</v>
+        <v>46027.3611111111</v>
       </c>
       <c r="K128" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L128" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M128" s="3">
-        <v>45971.4792824074</v>
+        <v>45987.671712963</v>
       </c>
       <c r="N128" s="3">
-        <v>45986.4815625</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="O128" s="3"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <v>2494179</v>
+        <v>2498066</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>116</v>
+        <v>181</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>221</v>
+        <v>75</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I129" s="3">
-        <v>46002.675775463</v>
+        <v>46073.7916666667</v>
       </c>
       <c r="J129" s="3">
-        <v>46044.7370486111</v>
+        <v>46126.6953240741</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M129" s="3">
-        <v>45971.4049421296</v>
-      </c>
-      <c r="N129" s="3">
-        <v>46002.675775463</v>
-      </c>
+        <v>45979.750162037</v>
+      </c>
+      <c r="N129" s="3"/>
       <c r="O129" s="3"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <v>2490911</v>
+        <v>2494282</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="I130" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I130" s="3">
+        <v>45986.48125</v>
+      </c>
       <c r="J130" s="3">
-        <v>46182.7633796296</v>
+        <v>45988.567025463</v>
       </c>
       <c r="K130" s="0" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="L130" s="0" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="M130" s="3">
-        <v>45961.5760300926</v>
-      </c>
-      <c r="N130" s="3"/>
+        <v>45971.4792824074</v>
+      </c>
+      <c r="N130" s="3">
+        <v>45986.4815625</v>
+      </c>
       <c r="O130" s="3"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <v>2490185</v>
+        <v>2494179</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>186</v>
+        <v>118</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>187</v>
+        <v>119</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>17</v>
+        <v>222</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>57</v>
+        <v>223</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I131" s="3">
-        <v>46203.7916666667</v>
+        <v>46002.675775463</v>
       </c>
       <c r="J131" s="3">
-        <v>46051.4836111111</v>
+        <v>46044.7370486111</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="M131" s="3">
-        <v>45960.3928819444</v>
-      </c>
-      <c r="N131" s="3"/>
+        <v>45971.4049421296</v>
+      </c>
+      <c r="N131" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="O131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <v>2489016</v>
+        <v>2490911</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>86</v>
+        <v>225</v>
       </c>
       <c r="E132" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F132" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="G132" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="F132" s="0" t="s">
-        <v>221</v>
-      </c>
-      <c r="G132" s="0" t="s">
-        <v>227</v>
-      </c>
       <c r="H132" s="0" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="I132" s="3"/>
       <c r="J132" s="3">
-        <v>45958.3906481481</v>
+        <v>46182.7633796296</v>
       </c>
       <c r="K132" s="0" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="L132" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M132" s="3">
-        <v>45957.7253009259</v>
+        <v>45961.5760300926</v>
       </c>
       <c r="N132" s="3"/>
       <c r="O132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <v>2485386</v>
+        <v>2490185</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="I133" s="3">
-        <v>46386.7916666667</v>
+        <v>46203.7916666667</v>
       </c>
       <c r="J133" s="3">
-        <v>46182.7639236111</v>
+        <v>46051.4836111111</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M133" s="3">
-        <v>45947.7000115741</v>
+        <v>45960.3928819444</v>
       </c>
       <c r="N133" s="3"/>
       <c r="O133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <v>2483420</v>
+        <v>2489016</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D134" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="E134" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="F134" s="0" t="s">
         <v>223</v>
-      </c>
-      <c r="E134" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F134" s="0" t="s">
-        <v>73</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>229</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="I134" s="3"/>
       <c r="J134" s="3">
-        <v>46140.3843518519</v>
+        <v>45958.3906481481</v>
       </c>
       <c r="K134" s="0" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="L134" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M134" s="3">
-        <v>45944.6603819444</v>
+        <v>45957.7253009259</v>
       </c>
       <c r="N134" s="3"/>
       <c r="O134" s="3"/>
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <v>2474606</v>
+        <v>2485386</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>230</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="I135" s="3">
-        <v>45952.4506944444</v>
+        <v>46386.7916666667</v>
       </c>
       <c r="J135" s="3">
-        <v>45966.4450925926</v>
+        <v>46182.7639236111</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="M135" s="3">
-        <v>45924.4486921296</v>
-      </c>
-      <c r="N135" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>45947.7000115741</v>
+      </c>
+      <c r="N135" s="3"/>
       <c r="O135" s="3"/>
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <v>2470122</v>
+        <v>2483420</v>
       </c>
       <c r="B136" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="C136" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D136" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="E136" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F136" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="G136" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="C136" s="0" t="s">
-        <v>231</v>
-      </c>
-      <c r="D136" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="E136" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F136" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G136" s="0" t="s">
-        <v>232</v>
-      </c>
       <c r="H136" s="0" t="s">
-        <v>233</v>
+        <v>109</v>
       </c>
       <c r="I136" s="3"/>
       <c r="J136" s="3">
-        <v>46204.3270601852</v>
+        <v>46140.3843518519</v>
       </c>
       <c r="K136" s="0" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="L136" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M136" s="3">
-        <v>45912.5572222222</v>
+        <v>45944.6603819444</v>
       </c>
       <c r="N136" s="3"/>
       <c r="O136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <v>2463515</v>
+        <v>2474606</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I137" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I137" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="J137" s="3">
-        <v>45910.4755555556</v>
+        <v>45966.4450925926</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="M137" s="3">
-        <v>45897.4218865741</v>
-      </c>
-      <c r="N137" s="3"/>
+        <v>45924.4486921296</v>
+      </c>
+      <c r="N137" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="O137" s="3"/>
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <v>2461703</v>
+        <v>2470122</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I138" s="3"/>
       <c r="J138" s="3">
-        <v>46003.3706828704</v>
+        <v>46204.3270601852</v>
       </c>
       <c r="K138" s="0" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="L138" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M138" s="3">
-        <v>45894.4525347222</v>
+        <v>45912.5572222222</v>
       </c>
       <c r="N138" s="3"/>
       <c r="O138" s="3"/>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>2459339</v>
+        <v>2463515</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>237</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="I139" s="3"/>
       <c r="J139" s="3">
-        <v>46140.3839930556</v>
+        <v>45910.4755555556</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M139" s="3">
-        <v>45887.7442361111</v>
+        <v>45897.4218865741</v>
       </c>
       <c r="N139" s="3"/>
       <c r="O139" s="3"/>
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>2456538</v>
+        <v>2461703</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>86</v>
+        <v>225</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>238</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>53</v>
+        <v>235</v>
       </c>
       <c r="I140" s="3"/>
       <c r="J140" s="3">
-        <v>46126.7428356481</v>
+        <v>46003.3706828704</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="L140" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M140" s="3">
-        <v>45880.6643055556</v>
+        <v>45894.4525347222</v>
       </c>
       <c r="N140" s="3"/>
       <c r="O140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>2449811</v>
+        <v>2459339</v>
       </c>
       <c r="B141" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="C141" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="D141" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="E141" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F141" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="G141" s="0" t="s">
         <v>239</v>
       </c>
-      <c r="C141" s="0" t="s">
-        <v>239</v>
-      </c>
-      <c r="D141" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="E141" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="F141" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="G141" s="0" t="s">
-        <v>240</v>
-      </c>
       <c r="H141" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I141" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="I141" s="3"/>
       <c r="J141" s="3">
-        <v>45870.3628819444</v>
+        <v>46140.3839930556</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="M141" s="3">
-        <v>45862.6188888889</v>
-      </c>
-      <c r="N141" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>45887.7442361111</v>
+      </c>
+      <c r="N141" s="3"/>
       <c r="O141" s="3"/>
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <v>2442028</v>
+        <v>2456538</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>241</v>
+        <v>118</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>241</v>
+        <v>118</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I142" s="3"/>
       <c r="J142" s="3">
-        <v>46126.7431134259</v>
+        <v>46126.7428356481</v>
       </c>
       <c r="K142" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L142" s="0" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M142" s="3">
-        <v>45842.317025463</v>
+        <v>45880.6643055556</v>
       </c>
       <c r="N142" s="3"/>
       <c r="O142" s="3"/>
     </row>
     <row r="143">
       <c r="A143" s="2">
-        <v>2439691</v>
+        <v>2449811</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>116</v>
+        <v>241</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>116</v>
+        <v>241</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>218</v>
+        <v>119</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>31</v>
+        <v>119</v>
+      </c>
+      <c r="F143" s="0" t="s">
+        <v>119</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I143" s="3">
-        <v>45852.3770833333</v>
+        <v>45875.3688888889</v>
       </c>
       <c r="J143" s="3">
-        <v>45838.6211342593</v>
+        <v>45870.3628819444</v>
       </c>
       <c r="K143" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L143" s="0" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="M143" s="3">
-        <v>45838.3761921296</v>
+        <v>45862.6188888889</v>
       </c>
       <c r="N143" s="3">
-        <v>45852.3770833333</v>
+        <v>45875.3688888889</v>
       </c>
       <c r="O143" s="3"/>
     </row>
     <row r="144">
       <c r="A144" s="2">
-        <v>2437239</v>
+        <v>2442028</v>
       </c>
       <c r="B144" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="D144" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F144" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G144" s="0" t="s">
         <v>244</v>
       </c>
-      <c r="C144" s="0" t="s">
-        <v>245</v>
-      </c>
-      <c r="D144" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E144" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="F144" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="G144" s="0" t="s">
-        <v>246</v>
-      </c>
       <c r="H144" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I144" s="3">
-        <v>45870.3600462963</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="I144" s="3"/>
       <c r="J144" s="3">
-        <v>45841.7026091435</v>
+        <v>46126.7431134259</v>
       </c>
       <c r="K144" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L144" s="0" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="M144" s="3">
-        <v>45831.6933796296</v>
-      </c>
-      <c r="N144" s="3">
-        <v>45870.3600462963</v>
-      </c>
+        <v>45842.317025463</v>
+      </c>
+      <c r="N144" s="3"/>
       <c r="O144" s="3"/>
     </row>
     <row r="145">
       <c r="A145" s="2">
-        <v>2436707</v>
+        <v>2439691</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>239</v>
+        <v>118</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>239</v>
+        <v>118</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E145" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="F145" s="0" t="s">
-        <v>26</v>
-      </c>
       <c r="G145" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="H145" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="I145" s="3">
+        <v>45852.3770833333</v>
+      </c>
+      <c r="J145" s="3">
+        <v>45838.6211342593</v>
+      </c>
+      <c r="K145" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="L145" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="M145" s="3">
+        <v>45838.3761921296</v>
+      </c>
+      <c r="N145" s="3">
+        <v>45852.3770833333</v>
+      </c>
+      <c r="O145" s="3"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2">
+        <v>2437239</v>
+      </c>
+      <c r="B146" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C146" s="0" t="s">
         <v>247</v>
       </c>
-      <c r="H145" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="I145" s="3">
+      <c r="D146" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E146" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="F146" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="G146" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="H146" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="I146" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="J146" s="3">
+        <v>45841.7026091435</v>
+      </c>
+      <c r="K146" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="L146" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="M146" s="3">
+        <v>45831.6933796296</v>
+      </c>
+      <c r="N146" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="O146" s="3"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2">
+        <v>2436707</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="C147" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="D147" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F147" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G147" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="H147" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="I147" s="3">
         <v>45835.7284722222</v>
       </c>
-      <c r="J145" s="3">
+      <c r="J147" s="3">
         <v>46126.7436921296</v>
       </c>
-      <c r="K145" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="L145" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="M145" s="3">
+      <c r="K147" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="L147" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="M147" s="3">
         <v>45828.8276273148</v>
       </c>
-      <c r="N145" s="3">
+      <c r="N147" s="3">
         <v>45835.7288773148</v>
       </c>
-      <c r="O145" s="3"/>
+      <c r="O147" s="3"/>
     </row>
   </sheetData>
   <headerFooter/>

--- a/Solicitacoes.xlsx
+++ b/Solicitacoes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
   <si>
     <t>Protocolo</t>
   </si>
@@ -65,6 +65,24 @@
     <t>CORRECAO</t>
   </si>
   <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
+    <t>AG - Erro ao importar Tabela Genérica (Aguardando Processamento)</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Suporte nível II</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>BCON</t>
   </si>
   <si>
@@ -74,15 +92,6 @@
     <t>CON - Impossibilidade adiconar corpo clínico</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
-    <t>Suporte nível II</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>MOBE</t>
   </si>
   <si>
@@ -98,193 +107,193 @@
     <t>ROGERIO.ALMEIDA</t>
   </si>
   <si>
-    <t>AG</t>
-  </si>
-  <si>
     <t>ANS</t>
   </si>
   <si>
     <t>Critica para gerar XML na Rotina Monitoramento TISS</t>
   </si>
   <si>
+    <t>Aguardando Revisão de código</t>
+  </si>
+  <si>
+    <t>Julia Albertim</t>
+  </si>
+  <si>
+    <t>HELPDESK - CUIDAR</t>
+  </si>
+  <si>
+    <t>INSTABILIDADE MÓDULOS</t>
+  </si>
+  <si>
+    <t>Homologando</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Faturamento</t>
+  </si>
+  <si>
+    <t>Guia não disponível para execução de eventos por outros prestadores</t>
+  </si>
+  <si>
+    <t>Plataforma Lean</t>
+  </si>
+  <si>
+    <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
+  </si>
+  <si>
+    <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
+  </si>
+  <si>
+    <t>CONECTA - XML não sai do estado de "Em Processamento"</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
+  </si>
+  <si>
+    <t>ANA.GOLDIM</t>
+  </si>
+  <si>
+    <t>Autorização</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- Conecta- Erro na solicitação dos procedimentos.</t>
+  </si>
+  <si>
+    <t>Agendamentos</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- AG- AGENDAMENTO com erro Módulo de Regulação: Enviar mensagens Lean e Integracao Iris</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>CONECTA - Erro na execução de guias | pop-up e bloqueio por biometria</t>
+  </si>
+  <si>
+    <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
+  </si>
+  <si>
+    <t>Programando</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Prestadores</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO NOME PRESTADOR</t>
+  </si>
+  <si>
+    <t>Liberado para cliente</t>
+  </si>
+  <si>
+    <t>Configurações do Sistema</t>
+  </si>
+  <si>
+    <t>Ajuste no tempo de sessão ativa (timeout) do sistema Lean.</t>
+  </si>
+  <si>
+    <t>ALEXIA.SANTOS</t>
+  </si>
+  <si>
+    <t>Controle Financeiro</t>
+  </si>
+  <si>
+    <t>Correção – CompesaPrev – Erro de Geração do Código de Barras e Linha Digitável</t>
+  </si>
+  <si>
+    <t>COMPESAPREV-CONECTA- Eventos negados, com recibo autorizado</t>
+  </si>
+  <si>
     <t>Verificando</t>
   </si>
   <si>
+    <t>COMPESAPREV.NIECIA</t>
+  </si>
+  <si>
+    <t>Niécia Morais</t>
+  </si>
+  <si>
+    <t>Processamento de Contas</t>
+  </si>
+  <si>
+    <t>Erro no faturamento de pagamentos prestadores</t>
+  </si>
+  <si>
+    <t>Dúvida sobre o local para salvar/exportar a Guia Executada no Portal do Prestador</t>
+  </si>
+  <si>
+    <t>Histórico financeiro sem a informação individual de todos os beneficiários</t>
+  </si>
+  <si>
+    <t>PORTAL</t>
+  </si>
+  <si>
+    <t>Portal não envia e-mails, recuperação de senha e processos parados desde 04/09</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- AG- PROD- Agendamento Regulacao travado</t>
+  </si>
+  <si>
+    <t>Processos</t>
+  </si>
+  <si>
+    <t>Lean / AG (Integração e guias travadas)</t>
+  </si>
+  <si>
+    <t>Beneficiários</t>
+  </si>
+  <si>
+    <t>Erro de divergência de cadastro entre o AG e o LEAN</t>
+  </si>
+  <si>
+    <t>MOBE | Erro no servidor ao tentar logar.</t>
+  </si>
+  <si>
+    <t>Extrato de Utilização com valores de coparticipações sem a limitação de PF e antes do faturamento ser concluído</t>
+  </si>
+  <si>
+    <t>Erro ao buscar documento/relatório na Consulta de Autorizações (App)</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Compesaprev- Conecta- Erro na autorização</t>
+  </si>
+  <si>
+    <t>CENTRAL ATENDIMENTO</t>
+  </si>
+  <si>
+    <t>Transações</t>
+  </si>
+  <si>
+    <t>Falha na integração entre AG Web e Central de Atendimento</t>
+  </si>
+  <si>
+    <t>Ajuste de permissões e perfis de acesso no AG - Papel de Desenvolvedor aplicado a todos os usuários</t>
+  </si>
+  <si>
+    <t>Inconsistência no cálculo do prazo em horas úteis</t>
+  </si>
+  <si>
+    <t>Alinhamento sobre parametrização de críticas/motivos de negação automáticos (AG / Conecta)</t>
+  </si>
+  <si>
+    <t>APOIO DE NEGÓCIO</t>
+  </si>
+  <si>
+    <t>Erro na de geração do “Nosso Número” no boleto</t>
+  </si>
+  <si>
+    <t>Versão futura</t>
+  </si>
+  <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>Julia Albertim</t>
-  </si>
-  <si>
-    <t>HELPDESK - CUIDAR</t>
-  </si>
-  <si>
-    <t>ADM</t>
-  </si>
-  <si>
-    <t>INSTABILIDADE MÓDULOS</t>
-  </si>
-  <si>
-    <t>Homologando</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Faturamento</t>
-  </si>
-  <si>
-    <t>Guia não disponível para execução de eventos por outros prestadores</t>
-  </si>
-  <si>
-    <t>Plataforma Lean</t>
-  </si>
-  <si>
-    <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
-  </si>
-  <si>
-    <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
-  </si>
-  <si>
-    <t>CONECTA - XML não sai do estado de "Em Processamento"</t>
-  </si>
-  <si>
-    <t>Resolvido</t>
-  </si>
-  <si>
-    <t>ANA.GOLDIM</t>
-  </si>
-  <si>
-    <t>Autorização</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- Conecta- Erro na solicitação dos procedimentos.</t>
-  </si>
-  <si>
-    <t>Agendamentos</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- AG- AGENDAMENTO com erro Módulo de Regulação: Enviar mensagens Lean e Integracao Iris</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>CONECTA - Erro na execução de guias | pop-up e bloqueio por biometria</t>
-  </si>
-  <si>
-    <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Prestadores</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO NOME PRESTADOR</t>
-  </si>
-  <si>
-    <t>Liberado para cliente</t>
-  </si>
-  <si>
-    <t>Configurações do Sistema</t>
-  </si>
-  <si>
-    <t>Ajuste no tempo de sessão ativa (timeout) do sistema Lean.</t>
-  </si>
-  <si>
-    <t>ALEXIA.SANTOS</t>
-  </si>
-  <si>
-    <t>Controle Financeiro</t>
-  </si>
-  <si>
-    <t>Correção – CompesaPrev – Erro de Geração do Código de Barras e Linha Digitável</t>
-  </si>
-  <si>
-    <t>COMPESAPREV-CONECTA- Eventos negados, com recibo autorizado</t>
-  </si>
-  <si>
-    <t>COMPESAPREV.NIECIA</t>
-  </si>
-  <si>
-    <t>Niécia Morais</t>
-  </si>
-  <si>
-    <t>Processamento de Contas</t>
-  </si>
-  <si>
-    <t>Erro no faturamento de pagamentos prestadores</t>
-  </si>
-  <si>
-    <t>Dúvida sobre o local para salvar/exportar a Guia Executada no Portal do Prestador</t>
-  </si>
-  <si>
-    <t>Histórico financeiro sem a informação individual de todos os beneficiários</t>
-  </si>
-  <si>
-    <t>PORTAL</t>
-  </si>
-  <si>
-    <t>Portal não envia e-mails, recuperação de senha e processos parados desde 04/09</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- AG- PROD- Agendamento Regulacao travado</t>
-  </si>
-  <si>
-    <t>Processos</t>
-  </si>
-  <si>
-    <t>Lean / AG (Integração e guias travadas)</t>
-  </si>
-  <si>
-    <t>Beneficiários</t>
-  </si>
-  <si>
-    <t>Erro de divergência de cadastro entre o AG e o LEAN</t>
-  </si>
-  <si>
-    <t>MOBE | Erro no servidor ao tentar logar.</t>
-  </si>
-  <si>
-    <t>Extrato de Utilização com valores de coparticipações sem a limitação de PF e antes do faturamento ser concluído</t>
-  </si>
-  <si>
-    <t>Erro ao buscar documento/relatório na Consulta de Autorizações (App)</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Compesaprev- Conecta- Erro na autorização</t>
-  </si>
-  <si>
-    <t>CENTRAL ATENDIMENTO</t>
-  </si>
-  <si>
-    <t>Transações</t>
-  </si>
-  <si>
-    <t>Falha na integração entre AG Web e Central de Atendimento</t>
-  </si>
-  <si>
-    <t>Ajuste de permissões e perfis de acesso no AG - Papel de Desenvolvedor aplicado a todos os usuários</t>
-  </si>
-  <si>
-    <t>Inconsistência no cálculo do prazo em horas úteis</t>
-  </si>
-  <si>
-    <t>Alinhamento sobre parametrização de críticas/motivos de negação automáticos (AG / Conecta)</t>
-  </si>
-  <si>
-    <t>APOIO DE NEGÓCIO</t>
-  </si>
-  <si>
-    <t>Erro na de geração do “Nosso Número” no boleto</t>
-  </si>
-  <si>
-    <t>Versão futura</t>
   </si>
   <si>
     <t>EVIDENCIAS DO PROBLEMA NO RELATORIO DE PREVIA DE PAGAMENTO</t>
@@ -818,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O147"/>
+  <dimension ref="A1:O148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1506990705218" customWidth="1"/>
@@ -828,7 +837,7 @@
     <col min="5" max="5" width="47.7084481375558" customWidth="1"/>
     <col min="6" max="6" width="24.124747140067" customWidth="1"/>
     <col min="7" max="7" width="115.814923967634" customWidth="1"/>
-    <col min="8" max="8" width="27.4691489083426" customWidth="1"/>
+    <col min="8" max="8" width="28.4032069614955" customWidth="1"/>
     <col min="9" max="9" width="17.2691879272461" customWidth="1"/>
     <col min="10" max="10" width="17.2691879272461" customWidth="1"/>
     <col min="11" max="11" width="14.5938720703125" customWidth="1"/>
@@ -887,7 +896,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2618403</v>
+        <v>2618623</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>15</v>
@@ -911,10 +920,10 @@
         <v>20</v>
       </c>
       <c r="I2" s="3">
-        <v>46294.5634259259</v>
+        <v>46294.7106365741</v>
       </c>
       <c r="J2" s="3">
-        <v>46288.6467592593</v>
+        <v>46289.45</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>21</v>
@@ -923,16 +932,16 @@
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>46288.6467592593</v>
+        <v>46289.3773032407</v>
       </c>
       <c r="N2" s="3">
-        <v>46294.5634259259</v>
+        <v>46294.7106365741</v>
       </c>
       <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2618370</v>
+        <v>2618403</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>15</v>
@@ -956,159 +965,163 @@
         <v>20</v>
       </c>
       <c r="I3" s="3">
-        <v>46290.5871296296</v>
+        <v>46294.5634259259</v>
       </c>
       <c r="J3" s="3">
-        <v>46288.6287962963</v>
+        <v>46288.6467592593</v>
       </c>
       <c r="K3" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M3" s="3">
-        <v>46288.6287962963</v>
+        <v>46288.6467592593</v>
       </c>
       <c r="N3" s="3">
-        <v>46290.5871296296</v>
+        <v>46294.5634259259</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2617933</v>
+        <v>2618370</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>30</v>
-      </c>
       <c r="H4" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I4" s="3">
+        <v>46290.5871296296</v>
+      </c>
       <c r="J4" s="3">
-        <v>46288.4902662037</v>
+        <v>46288.6287962963</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M4" s="3">
-        <v>46287.7594097222</v>
-      </c>
-      <c r="N4" s="3"/>
+        <v>46288.6287962963</v>
+      </c>
+      <c r="N4" s="3">
+        <v>46290.5871296296</v>
+      </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>2617538</v>
+        <v>2617933</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C5" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>37</v>
-      </c>
       <c r="I5" s="3">
-        <v>46290.7498263889</v>
+        <v>46293.6666666667</v>
       </c>
       <c r="J5" s="3">
-        <v>46288.4440509259</v>
+        <v>46289.470218669</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L5" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M5" s="3">
-        <v>46287.4164930556</v>
+        <v>46287.7594097222</v>
       </c>
       <c r="N5" s="3">
-        <v>46290.7498263889</v>
+        <v>46293.6666666667</v>
       </c>
       <c r="O5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>2617170</v>
+        <v>2617538</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I6" s="3">
-        <v>46290.4403703704</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="J6" s="3">
-        <v>46286.5862037037</v>
+        <v>46288.4440509259</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L6" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M6" s="3">
-        <v>46286.5862037037</v>
+        <v>46287.4164930556</v>
       </c>
       <c r="N6" s="3">
-        <v>46290.4403703704</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>2617057</v>
+        <v>2617170</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>15</v>
@@ -1120,22 +1133,22 @@
         <v>16</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H7" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="J7" s="3">
-        <v>46286.5879513889</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="K7" s="0" t="s">
         <v>21</v>
@@ -1144,16 +1157,16 @@
         <v>22</v>
       </c>
       <c r="M7" s="3">
-        <v>46286.4877199074</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="N7" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>2615970</v>
+        <v>2617057</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>15</v>
@@ -1162,25 +1175,25 @@
         <v>15</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H8" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I8" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="J8" s="3">
-        <v>46287.3554017708</v>
+        <v>46286.5879513889</v>
       </c>
       <c r="K8" s="0" t="s">
         <v>21</v>
@@ -1189,106 +1202,106 @@
         <v>22</v>
       </c>
       <c r="M8" s="3">
-        <v>46282.5089930556</v>
+        <v>46286.4877199074</v>
       </c>
       <c r="N8" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2615871</v>
+        <v>2615970</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I9" s="3">
-        <v>46286.4024189815</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="J9" s="3">
-        <v>46286.3450115741</v>
+        <v>46287.3554017708</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M9" s="3">
-        <v>46282.4440856481</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="N9" s="3">
-        <v>46286.4024189815</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>2615590</v>
+        <v>2615871</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I10" s="3">
-        <v>46287.5805092593</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="J10" s="3">
-        <v>46281.7496990741</v>
+        <v>46286.3450115741</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M10" s="3">
-        <v>46281.6638425926</v>
+        <v>46282.4440856481</v>
       </c>
       <c r="N10" s="3">
-        <v>46287.5805092593</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>2614686</v>
+        <v>2615590</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>46</v>
@@ -1297,412 +1310,412 @@
         <v>46</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I11" s="3">
-        <v>46321.5908449074</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="J11" s="3">
-        <v>46282.4296635764</v>
+        <v>46281.7496990741</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="M11" s="3">
-        <v>46280.4450115741</v>
+        <v>46281.6638425926</v>
       </c>
       <c r="N11" s="3">
-        <v>46321.5908449074</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>2614334</v>
+        <v>2614686</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I12" s="3">
-        <v>46283.5629166667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="J12" s="3">
-        <v>46283.4291666667</v>
+        <v>46282.4296635764</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="M12" s="3">
-        <v>46279.6749305556</v>
+        <v>46280.4450115741</v>
       </c>
       <c r="N12" s="3">
-        <v>46283.5629166667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>2614135</v>
+        <v>2614334</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="I13" s="3">
-        <v>46289.7291666667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="J13" s="3">
-        <v>46279.6123263889</v>
+        <v>46283.4291666667</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="M13" s="3">
-        <v>46279.5169097222</v>
+        <v>46279.6749305556</v>
       </c>
       <c r="N13" s="3">
-        <v>46289.7291666667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>2613646</v>
+        <v>2614135</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F14" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="3">
+        <v>46289.7291666667</v>
+      </c>
+      <c r="J14" s="3">
+        <v>46288.6498263889</v>
+      </c>
+      <c r="K14" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14" s="3">
-        <v>46289.3876041667</v>
-      </c>
-      <c r="J14" s="3">
-        <v>46283.4346064815</v>
-      </c>
-      <c r="K14" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="L14" s="0" t="s">
-        <v>54</v>
-      </c>
       <c r="M14" s="3">
-        <v>46276.6376041667</v>
+        <v>46279.5169097222</v>
       </c>
       <c r="N14" s="3">
-        <v>46289.3876041667</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2613202</v>
+        <v>2613646</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I15" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="J15" s="3">
-        <v>46283.4707657407</v>
+        <v>46283.4346064815</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M15" s="3">
-        <v>46276.3827546296</v>
+        <v>46276.6376041667</v>
       </c>
       <c r="N15" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>2613026</v>
+        <v>2613202</v>
       </c>
       <c r="B16" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="0" t="s">
-        <v>62</v>
-      </c>
       <c r="H16" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I16" s="3">
-        <v>46281.6747800926</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="J16" s="3">
-        <v>46287.6117592593</v>
+        <v>46283.4707657407</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M16" s="3">
-        <v>46275.6895601852</v>
+        <v>46276.3827546296</v>
       </c>
       <c r="N16" s="3">
-        <v>46281.6747800926</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>2612720</v>
+        <v>2613026</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G17" s="0" t="s">
         <v>63</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I17" s="3">
-        <v>46316.6011689815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="J17" s="3">
-        <v>46279.4816203704</v>
+        <v>46287.6117592593</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="M17" s="3">
-        <v>46275.4553356481</v>
+        <v>46275.6895601852</v>
       </c>
       <c r="N17" s="3">
-        <v>46316.6011689815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>2611881</v>
+        <v>2612720</v>
       </c>
       <c r="B18" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="H18" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>37</v>
-      </c>
       <c r="I18" s="3">
-        <v>46279.6652314815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="J18" s="3">
-        <v>46274.7389930556</v>
+        <v>46279.4816203704</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="M18" s="3">
-        <v>46273.7485648148</v>
+        <v>46275.4553356481</v>
       </c>
       <c r="N18" s="3">
-        <v>46279.6652314815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>2611848</v>
+        <v>2611881</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H19" s="0" t="s">
         <v>37</v>
       </c>
       <c r="I19" s="3">
-        <v>46287.4094675926</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="J19" s="3">
-        <v>46276.5914583333</v>
+        <v>46274.7389930556</v>
       </c>
       <c r="K19" s="0" t="s">
         <v>38</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M19" s="3">
-        <v>46273.7127546296</v>
+        <v>46273.7485648148</v>
       </c>
       <c r="N19" s="3">
-        <v>46287.4094675926</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>2611692</v>
+        <v>2611848</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>23</v>
@@ -1711,181 +1724,181 @@
         <v>24</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I20" s="3">
-        <v>46279.4554861111</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="J20" s="3">
-        <v>46273.637278588</v>
+        <v>46276.5914583333</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M20" s="3">
-        <v>46273.6013194444</v>
+        <v>46273.7127546296</v>
       </c>
       <c r="N20" s="3">
-        <v>46279.4554861111</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>2611552</v>
+        <v>2611692</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G21" s="0" t="s">
         <v>71</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="I21" s="3">
-        <v>46275.4327083333</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="J21" s="3">
-        <v>46273.5743171296</v>
+        <v>46273.637278588</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M21" s="3">
-        <v>46273.474375</v>
+        <v>46273.6013194444</v>
       </c>
       <c r="N21" s="3">
-        <v>46275.4327083333</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2611551</v>
+        <v>2611552</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I22" s="3">
-        <v>46314.6183449074</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="J22" s="3">
-        <v>46274.3603356481</v>
+        <v>46273.5743171296</v>
       </c>
       <c r="K22" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="M22" s="3">
-        <v>46273.4725115741</v>
+        <v>46273.474375</v>
       </c>
       <c r="N22" s="3">
-        <v>46314.6183449074</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>2611539</v>
+        <v>2611551</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="G23" s="0" t="s">
         <v>74</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I23" s="3">
-        <v>46275.4227083333</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="J23" s="3">
-        <v>46274.3607986111</v>
+        <v>46274.3603356481</v>
       </c>
       <c r="K23" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="M23" s="3">
-        <v>46273.464375</v>
+        <v>46273.4725115741</v>
       </c>
       <c r="N23" s="3">
-        <v>46275.4227083333</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>2611521</v>
+        <v>2611539</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>75</v>
@@ -1894,58 +1907,58 @@
         <v>76</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I24" s="3">
-        <v>46279.3705439815</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="J24" s="3">
-        <v>46273.7182003819</v>
+        <v>46274.3607986111</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M24" s="3">
-        <v>46273.4538773148</v>
+        <v>46273.464375</v>
       </c>
       <c r="N24" s="3">
-        <v>46279.3705439815</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>2610876</v>
+        <v>2611521</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I25" s="3">
-        <v>46276.3367592593</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="J25" s="3">
-        <v>46269.4406376505</v>
+        <v>46273.7182003819</v>
       </c>
       <c r="K25" s="0" t="s">
         <v>21</v>
@@ -1954,43 +1967,43 @@
         <v>22</v>
       </c>
       <c r="M25" s="3">
-        <v>46269.4200925926</v>
+        <v>46273.4538773148</v>
       </c>
       <c r="N25" s="3">
-        <v>46276.3367592593</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>2610030</v>
+        <v>2610876</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H26" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I26" s="3">
-        <v>46274.6271990741</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="J26" s="3">
-        <v>46268.3853071412</v>
+        <v>46269.4406376505</v>
       </c>
       <c r="K26" s="0" t="s">
         <v>21</v>
@@ -1999,151 +2012,151 @@
         <v>22</v>
       </c>
       <c r="M26" s="3">
-        <v>46267.7105324074</v>
+        <v>46269.4200925926</v>
       </c>
       <c r="N26" s="3">
-        <v>46274.6271990741</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>2609985</v>
+        <v>2610030</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H27" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I27" s="3">
-        <v>46301.4629166667</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="J27" s="3">
-        <v>46267.6774134606</v>
+        <v>46268.3853071412</v>
       </c>
       <c r="K27" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="M27" s="3">
-        <v>46267.67125</v>
+        <v>46267.7105324074</v>
       </c>
       <c r="N27" s="3">
-        <v>46301.4629166667</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>2609883</v>
+        <v>2609985</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>81</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I28" s="3">
-        <v>46309.7050347222</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="J28" s="3">
-        <v>46280.4030439815</v>
+        <v>46267.6774134606</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="M28" s="3">
-        <v>46267.6217013889</v>
+        <v>46267.67125</v>
       </c>
       <c r="N28" s="3">
-        <v>46309.7050347222</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>2609551</v>
+        <v>2609883</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="F29" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="G29" s="0" t="s">
-        <v>84</v>
-      </c>
       <c r="H29" s="0" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I29" s="3">
-        <v>46273.6887962963</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="J29" s="3">
-        <v>46267.355462963</v>
+        <v>46280.4030439815</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="M29" s="3">
-        <v>46267.355462963</v>
+        <v>46267.6217013889</v>
       </c>
       <c r="N29" s="3">
-        <v>46273.6887962963</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>2609107</v>
+        <v>2609551</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>15</v>
@@ -2152,43 +2165,43 @@
         <v>15</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I30" s="3">
-        <v>46300.3339583333</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="J30" s="3">
-        <v>46268.4380070255</v>
+        <v>46267.355462963</v>
       </c>
       <c r="K30" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="M30" s="3">
-        <v>46266.4797916667</v>
+        <v>46267.355462963</v>
       </c>
       <c r="N30" s="3">
-        <v>46300.3339583333</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>2608731</v>
+        <v>2609107</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>15</v>
@@ -2197,43 +2210,43 @@
         <v>15</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I31" s="3">
-        <v>46279.4280671296</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="J31" s="3">
-        <v>46273.3513888889</v>
+        <v>46289.4408381597</v>
       </c>
       <c r="K31" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="M31" s="3">
-        <v>46265.6780671296</v>
+        <v>46266.4797916667</v>
       </c>
       <c r="N31" s="3">
-        <v>46279.4280671296</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>2608637</v>
+        <v>2608731</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>15</v>
@@ -2242,410 +2255,414 @@
         <v>15</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I32" s="3">
-        <v>46304.6977777778</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="J32" s="3">
-        <v>46287.4125274653</v>
+        <v>46273.3513888889</v>
       </c>
       <c r="K32" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M32" s="3">
-        <v>46265.6144444444</v>
+        <v>46265.6780671296</v>
       </c>
       <c r="N32" s="3">
-        <v>46304.6977777778</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>2607413</v>
+        <v>2608637</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>89</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I33" s="3">
+        <v>46304.6977777778</v>
+      </c>
       <c r="J33" s="3">
-        <v>46266.569212963</v>
+        <v>46287.4125274653</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="M33" s="3">
-        <v>46261.6163888889</v>
-      </c>
-      <c r="N33" s="3"/>
+        <v>46265.6144444444</v>
+      </c>
+      <c r="N33" s="3">
+        <v>46304.6977777778</v>
+      </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>2607198</v>
+        <v>2607413</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>91</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I34" s="3">
-        <v>46267.3546643518</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="I34" s="3"/>
       <c r="J34" s="3">
-        <v>46273.6204976852</v>
+        <v>46266.569212963</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="M34" s="3">
-        <v>46261.4379976852</v>
-      </c>
-      <c r="N34" s="3">
-        <v>46267.3546643518</v>
-      </c>
+        <v>46261.6163888889</v>
+      </c>
+      <c r="N34" s="3"/>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>2606003</v>
+        <v>2607198</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I35" s="3">
-        <v>46265.3599537037</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="J35" s="3">
-        <v>46259.4993506944</v>
+        <v>46273.6204976852</v>
       </c>
       <c r="K35" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L35" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M35" s="3">
-        <v>46259.443287037</v>
+        <v>46261.4379976852</v>
       </c>
       <c r="N35" s="3">
-        <v>46290.75</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="O35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>2604815</v>
+        <v>2606003</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I36" s="3">
-        <v>46296.563587963</v>
+        <v>46265.3599537037</v>
       </c>
       <c r="J36" s="3">
-        <v>46268.6781365741</v>
+        <v>46259.4993506944</v>
       </c>
       <c r="K36" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="M36" s="3">
-        <v>46255.4177546296</v>
+        <v>46259.443287037</v>
       </c>
       <c r="N36" s="3">
-        <v>46296.563587963</v>
+        <v>46290.75</v>
       </c>
       <c r="O36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>2604500</v>
+        <v>2604815</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="I37" s="3">
-        <v>46260.4812268519</v>
+        <v>46296.563587963</v>
       </c>
       <c r="J37" s="3">
-        <v>46258.3485416667</v>
+        <v>46268.6781365741</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="M37" s="3">
-        <v>46254.6270601852</v>
+        <v>46255.4177546296</v>
       </c>
       <c r="N37" s="3">
-        <v>46260.4812268519</v>
+        <v>46296.563587963</v>
       </c>
       <c r="O37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>2603668</v>
+        <v>2604500</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I38" s="3">
-        <v>46259.3446296296</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="J38" s="3">
-        <v>46258.6426851852</v>
+        <v>46258.3485416667</v>
       </c>
       <c r="K38" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L38" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M38" s="3">
-        <v>46253.427962963</v>
+        <v>46254.6270601852</v>
       </c>
       <c r="N38" s="3">
-        <v>46290.75</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="O38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2602388</v>
+        <v>2603668</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="I39" s="3">
-        <v>46255.4166666667</v>
+        <v>46259.3446296296</v>
       </c>
       <c r="J39" s="3">
-        <v>46253.4900231482</v>
+        <v>46258.6426851852</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L39" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M39" s="3">
-        <v>46251.5527777778</v>
+        <v>46253.427962963</v>
       </c>
       <c r="N39" s="3">
-        <v>46255.4166666667</v>
+        <v>46290.75</v>
       </c>
       <c r="O39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>2601999</v>
+        <v>2602388</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="I40" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I40" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="J40" s="3">
-        <v>46266.6188194444</v>
+        <v>46253.4900231482</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M40" s="3">
-        <v>46248.7351273148</v>
-      </c>
-      <c r="N40" s="3"/>
+        <v>46251.5527777778</v>
+      </c>
+      <c r="N40" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="O40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>2600778</v>
+        <v>2601999</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>101</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>102</v>
@@ -2655,338 +2672,334 @@
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3">
-        <v>46274.3780324074</v>
+        <v>46266.6188194444</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M41" s="3">
-        <v>46246.7171759259</v>
+        <v>46248.7351273148</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>2599732</v>
+        <v>2600778</v>
       </c>
       <c r="B42" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>34</v>
-      </c>
       <c r="E42" s="0" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>105</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I42" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="I42" s="3"/>
       <c r="J42" s="3">
-        <v>46248.3419117245</v>
+        <v>46274.3780324074</v>
       </c>
       <c r="K42" s="0" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="M42" s="3">
-        <v>46245.4849537037</v>
-      </c>
-      <c r="N42" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>46246.7171759259</v>
+      </c>
+      <c r="N42" s="3"/>
       <c r="O42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>2598987</v>
+        <v>2599732</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I43" s="3">
-        <v>46254.6856134259</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="J43" s="3">
-        <v>46251.536875</v>
+        <v>46248.3419117245</v>
       </c>
       <c r="K43" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M43" s="3">
-        <v>46244.4564467593</v>
+        <v>46245.4849537037</v>
       </c>
       <c r="N43" s="3">
-        <v>46254.6856134259</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="O43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>2598910</v>
+        <v>2598987</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="I44" s="3">
-        <v>46254.6386574074</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="J44" s="3">
-        <v>46248.4760674769</v>
+        <v>46251.536875</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M44" s="3">
-        <v>46244.4094907407</v>
+        <v>46244.4564467593</v>
       </c>
       <c r="N44" s="3">
-        <v>46261.6103125</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="O44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>2598767</v>
+        <v>2598910</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>111</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="I45" s="3">
-        <v>46247.6666666667</v>
+        <v>46254.6386574074</v>
       </c>
       <c r="J45" s="3">
-        <v>46245.6608564815</v>
+        <v>46248.4760674769</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M45" s="3">
-        <v>46241.757962963</v>
+        <v>46244.4094907407</v>
       </c>
       <c r="N45" s="3">
-        <v>46247.6666666667</v>
+        <v>46261.6103125</v>
       </c>
       <c r="O45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>2597798</v>
+        <v>2598767</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H46" s="0" t="s">
         <v>37</v>
       </c>
       <c r="I46" s="3">
-        <v>46290.75</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="J46" s="3">
-        <v>46273.4412384259</v>
+        <v>46245.6608564815</v>
       </c>
       <c r="K46" s="0" t="s">
         <v>38</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M46" s="3">
-        <v>46240.4508912037</v>
+        <v>46241.757962963</v>
       </c>
       <c r="N46" s="3">
-        <v>46290.75</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="O46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>2597524</v>
+        <v>2597798</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="I47" s="3">
-        <v>46267.0453356481</v>
+        <v>46290.75</v>
       </c>
       <c r="J47" s="3">
-        <v>46259.4158333333</v>
+        <v>46273.4412384259</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M47" s="3">
-        <v>46239.6925347222</v>
+        <v>46240.4508912037</v>
       </c>
       <c r="N47" s="3">
-        <v>46267.0453356481</v>
+        <v>46290.75</v>
       </c>
       <c r="O47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>2597515</v>
+        <v>2597524</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I48" s="3">
-        <v>46266.4759953704</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="J48" s="3">
-        <v>46261.4097453704</v>
+        <v>46259.4158333333</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M48" s="3">
-        <v>46239.6856134259</v>
+        <v>46239.6925347222</v>
       </c>
       <c r="N48" s="3">
-        <v>46266.4759953704</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="O48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>2597495</v>
+        <v>2597515</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>15</v>
@@ -2995,252 +3008,252 @@
         <v>15</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H49" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I49" s="3">
-        <v>46252.3333333333</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="J49" s="3">
-        <v>46241.6523302083</v>
+        <v>46261.4097453704</v>
       </c>
       <c r="K49" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="M49" s="3">
-        <v>46239.6802199074</v>
+        <v>46239.6856134259</v>
       </c>
       <c r="N49" s="3">
-        <v>46245.5968865741</v>
-      </c>
-      <c r="O49" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>46266.4759953704</v>
+      </c>
+      <c r="O49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>2596882</v>
+        <v>2597495</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>120</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="I50" s="3">
-        <v>46280.3775578704</v>
+        <v>46252.3333333333</v>
       </c>
       <c r="J50" s="3">
-        <v>46267.6170023148</v>
+        <v>46241.6523302083</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="M50" s="3">
-        <v>46238.7108912037</v>
+        <v>46239.6802199074</v>
       </c>
       <c r="N50" s="3">
-        <v>46280.3775578704</v>
-      </c>
-      <c r="O50" s="3"/>
+        <v>46245.5968865741</v>
+      </c>
+      <c r="O50" s="3">
+        <v>46252.3333333333</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>2596538</v>
+        <v>2596882</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I51" s="3">
-        <v>46273.960787037</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="J51" s="3">
-        <v>46286.3521412037</v>
+        <v>46267.6170023148</v>
       </c>
       <c r="K51" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M51" s="3">
-        <v>46238.4644791667</v>
+        <v>46238.7108912037</v>
       </c>
       <c r="N51" s="3">
-        <v>46273.960787037</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="O51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>2596407</v>
+        <v>2596538</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I52" s="3">
-        <v>46248.6072106482</v>
+        <v>46273.960787037</v>
       </c>
       <c r="J52" s="3">
-        <v>46267.6164814815</v>
+        <v>46286.3521412037</v>
       </c>
       <c r="K52" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M52" s="3">
-        <v>46238.3780439815</v>
+        <v>46238.4644791667</v>
       </c>
       <c r="N52" s="3">
-        <v>46248.6072106482</v>
+        <v>46273.960787037</v>
       </c>
       <c r="O52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>2595510</v>
+        <v>2596407</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I53" s="3">
-        <v>46240.4984606481</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="J53" s="3">
-        <v>46245.3667592593</v>
+        <v>46267.6164814815</v>
       </c>
       <c r="K53" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M53" s="3">
-        <v>46234.6442939815</v>
+        <v>46238.3780439815</v>
       </c>
       <c r="N53" s="3">
-        <v>46240.4984606481</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="O53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>2595497</v>
+        <v>2595510</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I54" s="3">
-        <v>46240.4978240741</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="J54" s="3">
-        <v>46245.3669444444</v>
+        <v>46245.3667592593</v>
       </c>
       <c r="K54" s="0" t="s">
         <v>45</v>
@@ -3249,239 +3262,239 @@
         <v>22</v>
       </c>
       <c r="M54" s="3">
-        <v>46234.6436574074</v>
+        <v>46234.6442939815</v>
       </c>
       <c r="N54" s="3">
-        <v>46240.4978240741</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="O54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>2593529</v>
+        <v>2595497</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I55" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="J55" s="3">
-        <v>46233.4404570255</v>
+        <v>46245.3669444444</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L55" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M55" s="3">
-        <v>46231.6639930556</v>
+        <v>46234.6436574074</v>
       </c>
       <c r="N55" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="O55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>2593490</v>
+        <v>2593529</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="I56" s="3">
-        <v>46239.6748032407</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="J56" s="3">
-        <v>46253.4905324074</v>
+        <v>46233.4404570255</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M56" s="3">
-        <v>46231.6518865741</v>
+        <v>46231.6639930556</v>
       </c>
       <c r="N56" s="3">
-        <v>46239.6748032407</v>
-      </c>
-      <c r="O56" s="3">
-        <v>46234.48125</v>
-      </c>
+        <v>46237.5806597222</v>
+      </c>
+      <c r="O56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>2593260</v>
+        <v>2593490</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="I57" s="3">
-        <v>46241.6638888889</v>
+        <v>46239.6748032407</v>
       </c>
       <c r="J57" s="3">
-        <v>46267.614525463</v>
+        <v>46253.4905324074</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="M57" s="3">
-        <v>46231.435150463</v>
+        <v>46231.6518865741</v>
       </c>
       <c r="N57" s="3">
-        <v>46241.6638888889</v>
-      </c>
-      <c r="O57" s="3"/>
+        <v>46239.6748032407</v>
+      </c>
+      <c r="O57" s="3">
+        <v>46234.48125</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>2593216</v>
+        <v>2593260</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I58" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="I58" s="3">
+        <v>46241.6638888889</v>
+      </c>
       <c r="J58" s="3">
-        <v>46231.4047453704</v>
+        <v>46267.614525463</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="M58" s="3">
-        <v>46231.4011111111</v>
-      </c>
-      <c r="N58" s="3"/>
+        <v>46231.435150463</v>
+      </c>
+      <c r="N58" s="3">
+        <v>46241.6638888889</v>
+      </c>
       <c r="O58" s="3"/>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>2592878</v>
+        <v>2593216</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I59" s="3">
-        <v>46241.3504282407</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I59" s="3"/>
       <c r="J59" s="3">
-        <v>46230.6675740741</v>
+        <v>46231.4047453704</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="M59" s="3">
-        <v>46230.6004282407</v>
-      </c>
-      <c r="N59" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46231.4011111111</v>
+      </c>
+      <c r="N59" s="3"/>
       <c r="O59" s="3"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2592468</v>
+        <v>2592878</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>46</v>
@@ -3490,264 +3503,264 @@
         <v>46</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H60" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I60" s="3">
-        <v>46237.6038657407</v>
+        <v>46241.3504282407</v>
       </c>
       <c r="J60" s="3">
-        <v>46240.6136738773</v>
+        <v>46230.6675740741</v>
       </c>
       <c r="K60" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M60" s="3">
-        <v>46227.7107060185</v>
+        <v>46230.6004282407</v>
       </c>
       <c r="N60" s="3">
-        <v>46293.6033680556</v>
+        <v>46290.75</v>
       </c>
       <c r="O60" s="3"/>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>2591596</v>
+        <v>2592468</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>126</v>
+        <v>46</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>126</v>
+        <v>46</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H61" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I61" s="3">
-        <v>46238.7083333333</v>
+        <v>46237.6038657407</v>
       </c>
       <c r="J61" s="3">
-        <v>46267.3444803241</v>
+        <v>46240.6136738773</v>
       </c>
       <c r="K61" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M61" s="3">
-        <v>46226.4797916667</v>
+        <v>46227.7107060185</v>
       </c>
       <c r="N61" s="3">
-        <v>46282.6141435185</v>
+        <v>46293.6033680556</v>
       </c>
       <c r="O61" s="3"/>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>2591284</v>
+        <v>2591596</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I62" s="3">
-        <v>46266.3384837963</v>
+        <v>46238.7083333333</v>
       </c>
       <c r="J62" s="3">
-        <v>46225.7002398495</v>
+        <v>46267.3444803241</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M62" s="3">
-        <v>46225.6718171296</v>
+        <v>46226.4797916667</v>
       </c>
       <c r="N62" s="3">
-        <v>46266.3384837963</v>
+        <v>46282.6141435185</v>
       </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>2588490</v>
+        <v>2591284</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H63" s="0" t="s">
         <v>45</v>
       </c>
       <c r="I63" s="3">
-        <v>46230.722037037</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="J63" s="3">
-        <v>46231.4339699074</v>
+        <v>46225.7002398495</v>
       </c>
       <c r="K63" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M63" s="3">
-        <v>46218.4928703704</v>
+        <v>46225.6718171296</v>
       </c>
       <c r="N63" s="3">
-        <v>46230.722037037</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="O63" s="3"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2588025</v>
+        <v>2588490</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="F64" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="G64" s="0" t="s">
-        <v>138</v>
-      </c>
       <c r="H64" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="I64" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="I64" s="3">
+        <v>46230.722037037</v>
+      </c>
       <c r="J64" s="3">
-        <v>46267.5903356482</v>
+        <v>46231.4339699074</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="M64" s="3">
-        <v>46217.612962963</v>
-      </c>
-      <c r="N64" s="3"/>
+        <v>46218.4928703704</v>
+      </c>
+      <c r="N64" s="3">
+        <v>46230.722037037</v>
+      </c>
       <c r="O64" s="3"/>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2587849</v>
+        <v>2588025</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>34</v>
+        <v>138</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I65" s="3">
-        <v>46226.6083796296</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="I65" s="3"/>
       <c r="J65" s="3">
-        <v>46237.9144806713</v>
+        <v>46267.5903356482</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="M65" s="3">
-        <v>46217.4506597222</v>
-      </c>
-      <c r="N65" s="3">
-        <v>46226.6083796296</v>
-      </c>
+        <v>46217.612962963</v>
+      </c>
+      <c r="N65" s="3"/>
       <c r="O65" s="3"/>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>2587713</v>
+        <v>2587849</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>46</v>
@@ -3756,43 +3769,43 @@
         <v>46</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I66" s="3">
-        <v>46218.7408680556</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="J66" s="3">
-        <v>46230.4199074074</v>
+        <v>46237.9144806713</v>
       </c>
       <c r="K66" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M66" s="3">
-        <v>46217.3658680556</v>
+        <v>46217.4506597222</v>
       </c>
       <c r="N66" s="3">
-        <v>46218.7408680556</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>2587585</v>
+        <v>2587713</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>46</v>
@@ -3801,43 +3814,43 @@
         <v>46</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I67" s="3">
-        <v>46220.6264583333</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="J67" s="3">
-        <v>46259.4474884259</v>
+        <v>46230.4199074074</v>
       </c>
       <c r="K67" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M67" s="3">
-        <v>46216.7097916667</v>
+        <v>46217.3658680556</v>
       </c>
       <c r="N67" s="3">
-        <v>46220.6264583333</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="O67" s="3"/>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>2587006</v>
+        <v>2587585</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>46</v>
@@ -3846,219 +3859,223 @@
         <v>46</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I68" s="3">
-        <v>46217.7289699074</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="J68" s="3">
-        <v>46227.4549884259</v>
+        <v>46259.4474884259</v>
       </c>
       <c r="K68" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M68" s="3">
-        <v>46213.7239236111</v>
+        <v>46216.7097916667</v>
       </c>
       <c r="N68" s="3">
-        <v>46217.7289699074</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="O68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>2586984</v>
+        <v>2587006</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I69" s="3">
-        <v>46295.7416550926</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="J69" s="3">
-        <v>46273.4946180556</v>
+        <v>46227.4549884259</v>
       </c>
       <c r="K69" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M69" s="3">
-        <v>46213.6971527778</v>
+        <v>46213.7239236111</v>
       </c>
       <c r="N69" s="3">
-        <v>46295.7416550926</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="O69" s="3"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>2586910</v>
+        <v>2586984</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I70" s="3">
-        <v>46226.5833333333</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="J70" s="3">
-        <v>46230.4194212963</v>
+        <v>46273.4946180556</v>
       </c>
       <c r="K70" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M70" s="3">
-        <v>46213.6245833333</v>
+        <v>46213.6971527778</v>
       </c>
       <c r="N70" s="3">
-        <v>46226.5833333333</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="O70" s="3"/>
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>2586651</v>
+        <v>2586910</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I71" s="3">
-        <v>46218.7157407407</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="J71" s="3">
-        <v>46213.3824074074</v>
+        <v>46230.4194212963</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M71" s="3">
-        <v>46213.3824074074</v>
+        <v>46213.6245833333</v>
       </c>
       <c r="N71" s="3">
-        <v>46218.7157407407</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="O71" s="3"/>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>2586187</v>
+        <v>2586651</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>148</v>
+        <v>35</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I72" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I72" s="3">
+        <v>46218.7157407407</v>
+      </c>
       <c r="J72" s="3">
-        <v>46219.3850231481</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M72" s="3">
-        <v>46211.7697337963</v>
-      </c>
-      <c r="N72" s="3"/>
+        <v>46213.3824074074</v>
+      </c>
+      <c r="N72" s="3">
+        <v>46218.7157407407</v>
+      </c>
       <c r="O72" s="3"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>2585888</v>
+        <v>2586187</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>46</v>
@@ -4067,79 +4084,75 @@
         <v>46</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>34</v>
+        <v>151</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I73" s="3">
-        <v>46217.4119907407</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="I73" s="3"/>
       <c r="J73" s="3">
-        <v>46217.5003587963</v>
+        <v>46219.3850231481</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="M73" s="3">
-        <v>46211.4953240741</v>
-      </c>
-      <c r="N73" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46211.7697337963</v>
+      </c>
+      <c r="N73" s="3"/>
       <c r="O73" s="3"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2585424</v>
+        <v>2585888</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="I74" s="3">
-        <v>46223.3927199074</v>
+        <v>46217.4119907407</v>
       </c>
       <c r="J74" s="3">
-        <v>46234.4964930556</v>
+        <v>46217.5003587963</v>
       </c>
       <c r="K74" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M74" s="3">
-        <v>46210.6427199074</v>
+        <v>46211.4953240741</v>
       </c>
       <c r="N74" s="3">
         <v>46290.75</v>
@@ -4148,52 +4161,52 @@
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2584638</v>
+        <v>2585424</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="I75" s="3">
-        <v>46213.4171527778</v>
+        <v>46223.3927199074</v>
       </c>
       <c r="J75" s="3">
-        <v>46213.4090859607</v>
+        <v>46234.4964930556</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M75" s="3">
-        <v>46209.5016203704</v>
+        <v>46210.6427199074</v>
       </c>
       <c r="N75" s="3">
-        <v>46232.3874884259</v>
+        <v>46290.75</v>
       </c>
       <c r="O75" s="3"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>2584397</v>
+        <v>2584638</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>46</v>
@@ -4202,43 +4215,43 @@
         <v>46</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E76" s="0" t="s">
         <v>41</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="I76" s="3">
-        <v>46212.6757175926</v>
+        <v>46213.4171527778</v>
       </c>
       <c r="J76" s="3">
-        <v>46213.3741550926</v>
+        <v>46213.4090859607</v>
       </c>
       <c r="K76" s="0" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="L76" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M76" s="3">
-        <v>46209.3423842593</v>
+        <v>46209.5016203704</v>
       </c>
       <c r="N76" s="3">
-        <v>46212.6757175926</v>
+        <v>46232.3874884259</v>
       </c>
       <c r="O76" s="3"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>2584167</v>
+        <v>2584397</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>46</v>
@@ -4247,129 +4260,129 @@
         <v>46</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I77" s="3">
-        <v>46246.7216435185</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="J77" s="3">
-        <v>46247.4396759259</v>
+        <v>46213.3741550926</v>
       </c>
       <c r="K77" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="M77" s="3">
-        <v>46206.6383101852</v>
+        <v>46209.3423842593</v>
       </c>
       <c r="N77" s="3">
-        <v>46246.7216435185</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>2583950</v>
+        <v>2584167</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="E78" s="0" t="s">
         <v>23</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I78" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I78" s="3">
+        <v>46246.7216435185</v>
+      </c>
       <c r="J78" s="3">
-        <v>46273.4100925926</v>
+        <v>46247.4396759259</v>
       </c>
       <c r="K78" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="M78" s="3">
-        <v>46206.4623148148</v>
-      </c>
-      <c r="N78" s="3"/>
+        <v>46206.6383101852</v>
+      </c>
+      <c r="N78" s="3">
+        <v>46246.7216435185</v>
+      </c>
       <c r="O78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2583447</v>
+        <v>2583950</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I79" s="3">
-        <v>46205.7916666667</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I79" s="3"/>
       <c r="J79" s="3">
-        <v>46265.3645138889</v>
+        <v>46273.4100925926</v>
       </c>
       <c r="K79" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="M79" s="3">
-        <v>46205.5752083333</v>
-      </c>
-      <c r="N79" s="3">
-        <v>46245.6724189815</v>
-      </c>
+        <v>46206.4623148148</v>
+      </c>
+      <c r="N79" s="3"/>
       <c r="O79" s="3"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>2583382</v>
+        <v>2583447</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>46</v>
@@ -4378,39 +4391,43 @@
         <v>46</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="I80" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I80" s="3">
+        <v>46205.7916666667</v>
+      </c>
       <c r="J80" s="3">
-        <v>46279.4689699074</v>
+        <v>46265.3645138889</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="M80" s="3">
-        <v>46205.4905092593</v>
-      </c>
-      <c r="N80" s="3"/>
+        <v>46205.5752083333</v>
+      </c>
+      <c r="N80" s="3">
+        <v>46245.6724189815</v>
+      </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>2582452</v>
+        <v>2583382</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>46</v>
@@ -4419,43 +4436,39 @@
         <v>46</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I81" s="3">
-        <v>46244.4166666667</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="I81" s="3"/>
       <c r="J81" s="3">
-        <v>46204.7763078704</v>
+        <v>46279.4689699074</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="M81" s="3">
-        <v>46203.8250810185</v>
-      </c>
-      <c r="N81" s="3">
-        <v>46244.4166666667</v>
-      </c>
+        <v>46205.4905092593</v>
+      </c>
+      <c r="N81" s="3"/>
       <c r="O81" s="3"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>2582352</v>
+        <v>2582452</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>46</v>
@@ -4464,25 +4477,25 @@
         <v>46</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I82" s="3">
-        <v>46244.340775463</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="J82" s="3">
-        <v>46204.7761805556</v>
+        <v>46204.7763078704</v>
       </c>
       <c r="K82" s="0" t="s">
         <v>45</v>
@@ -4491,186 +4504,186 @@
         <v>51</v>
       </c>
       <c r="M82" s="3">
-        <v>46203.6741087963</v>
+        <v>46203.8250810185</v>
       </c>
       <c r="N82" s="3">
-        <v>46244.340775463</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>2579299</v>
+        <v>2582352</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>162</v>
+        <v>46</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>162</v>
+        <v>46</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I83" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I83" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="J83" s="3">
-        <v>46204.3277777778</v>
+        <v>46204.7761805556</v>
       </c>
       <c r="K83" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="M83" s="3">
-        <v>46196.4165162037</v>
-      </c>
-      <c r="N83" s="3"/>
+        <v>46203.6741087963</v>
+      </c>
+      <c r="N83" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="O83" s="3"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>2576326</v>
+        <v>2579299</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I84" s="3">
-        <v>46192.7916666667</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I84" s="3"/>
       <c r="J84" s="3">
-        <v>46230.6812731481</v>
+        <v>46204.3277777778</v>
       </c>
       <c r="K84" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M84" s="3">
-        <v>46189.3995833333</v>
+        <v>46196.4165162037</v>
       </c>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>2574153</v>
+        <v>2576326</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I85" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I85" s="3">
+        <v>46192.7916666667</v>
+      </c>
       <c r="J85" s="3">
-        <v>46204.3218402778</v>
+        <v>46230.6812731481</v>
       </c>
       <c r="K85" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M85" s="3">
-        <v>46183.4711226852</v>
+        <v>46189.3995833333</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>2572707</v>
+        <v>2574153</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>166</v>
+        <v>61</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>166</v>
+        <v>61</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>167</v>
+        <v>62</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>168</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I86" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I86" s="3"/>
       <c r="J86" s="3">
-        <v>46188.4629166667</v>
+        <v>46204.3218402778</v>
       </c>
       <c r="K86" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L86" s="0" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="M86" s="3">
-        <v>46178.7298148148</v>
-      </c>
-      <c r="N86" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>46183.4711226852</v>
+      </c>
+      <c r="N86" s="3"/>
       <c r="O86" s="3"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>2570274</v>
+        <v>2572707</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>169</v>
@@ -4679,522 +4692,522 @@
         <v>169</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I87" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I87" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="J87" s="3">
-        <v>46204.3220138889</v>
+        <v>46188.4629166667</v>
       </c>
       <c r="K87" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="M87" s="3">
-        <v>46171.6563773148</v>
-      </c>
-      <c r="N87" s="3"/>
+        <v>46178.7298148148</v>
+      </c>
+      <c r="N87" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>2562116</v>
+        <v>2570274</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I88" s="3"/>
       <c r="J88" s="3">
-        <v>46160.7191666667</v>
+        <v>46204.3220138889</v>
       </c>
       <c r="K88" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M88" s="3">
-        <v>46154.3432638889</v>
+        <v>46171.6563773148</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>2558553</v>
+        <v>2562116</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="E89" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I89" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I89" s="3"/>
       <c r="J89" s="3">
-        <v>46154.5888773148</v>
+        <v>46160.7191666667</v>
       </c>
       <c r="K89" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="M89" s="3">
-        <v>46146.3561805556</v>
-      </c>
-      <c r="N89" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>46154.3432638889</v>
+      </c>
+      <c r="N89" s="3"/>
       <c r="O89" s="3"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2556271</v>
+        <v>2558553</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>173</v>
+        <v>39</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I90" s="3">
-        <v>46141.4297453704</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="J90" s="3">
-        <v>46139.9871412037</v>
+        <v>46154.5888773148</v>
       </c>
       <c r="K90" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M90" s="3">
-        <v>46139.471412037</v>
+        <v>46146.3561805556</v>
       </c>
       <c r="N90" s="3">
-        <v>46141.4901157407</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>2556211</v>
+        <v>2556271</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E91" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>39</v>
+        <v>176</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I91" s="3">
-        <v>46150.6617476852</v>
+        <v>46141.4297453704</v>
       </c>
       <c r="J91" s="3">
-        <v>46146.3663773148</v>
+        <v>46139.9871412037</v>
       </c>
       <c r="K91" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="M91" s="3">
-        <v>46139.4325810185</v>
+        <v>46139.471412037</v>
       </c>
       <c r="N91" s="3">
-        <v>46150.6617476852</v>
+        <v>46141.4901157407</v>
       </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>2556029</v>
+        <v>2556211</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H92" s="0" t="s">
         <v>45</v>
       </c>
       <c r="I92" s="3">
-        <v>46150.5</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="J92" s="3">
-        <v>46146.401875</v>
+        <v>46146.3663773148</v>
       </c>
       <c r="K92" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M92" s="3">
-        <v>46138.757337963</v>
+        <v>46139.4325810185</v>
       </c>
       <c r="N92" s="3">
-        <v>46154.6616087963</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="O92" s="3"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>2554341</v>
+        <v>2556029</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H93" s="0" t="s">
         <v>45</v>
       </c>
       <c r="I93" s="3">
-        <v>46136.3599768519</v>
+        <v>46150.5</v>
       </c>
       <c r="J93" s="3">
-        <v>46135.6585185185</v>
+        <v>46146.401875</v>
       </c>
       <c r="K93" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="M93" s="3">
-        <v>46134.4016435185</v>
+        <v>46138.757337963</v>
       </c>
       <c r="N93" s="3">
-        <v>46136.3599768519</v>
+        <v>46154.6616087963</v>
       </c>
       <c r="O93" s="3"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>2547638</v>
+        <v>2554341</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I94" s="3">
-        <v>46150.3473611111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="J94" s="3">
-        <v>46119.5010069444</v>
+        <v>46135.6585185185</v>
       </c>
       <c r="K94" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L94" s="0" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="M94" s="3">
-        <v>46114.4931944444</v>
+        <v>46134.4016435185</v>
       </c>
       <c r="N94" s="3">
-        <v>46150.3473611111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="O94" s="3"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>2537054</v>
+        <v>2547638</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I95" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="J95" s="3">
-        <v>46090.3698263889</v>
+        <v>46119.5010069444</v>
       </c>
       <c r="K95" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="M95" s="3">
-        <v>46087.5797569444</v>
+        <v>46114.4931944444</v>
       </c>
       <c r="N95" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="O95" s="3"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>2531696</v>
+        <v>2537054</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I96" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I96" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="J96" s="3">
-        <v>46204.3216782407</v>
+        <v>46090.3698263889</v>
       </c>
       <c r="K96" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L96" s="0" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M96" s="3">
-        <v>46076.5833912037</v>
-      </c>
-      <c r="N96" s="3"/>
+        <v>46087.5797569444</v>
+      </c>
+      <c r="N96" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="O96" s="3"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>2530739</v>
+        <v>2531696</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>181</v>
+        <v>61</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>182</v>
+        <v>61</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>183</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="I97" s="3"/>
       <c r="J97" s="3">
-        <v>46218.6914940625</v>
+        <v>46204.3216782407</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M97" s="3">
-        <v>46072.6973148148</v>
+        <v>46076.5833912037</v>
       </c>
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>2529639</v>
+        <v>2530739</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>46</v>
+        <v>184</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>46</v>
+        <v>185</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="E98" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I98" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="I98" s="3"/>
       <c r="J98" s="3">
-        <v>46072.6891666667</v>
+        <v>46218.6914940625</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="M98" s="3">
-        <v>46069.5930902778</v>
-      </c>
-      <c r="N98" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>46072.6973148148</v>
+      </c>
+      <c r="N98" s="3"/>
       <c r="O98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>2529591</v>
+        <v>2529639</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>46</v>
@@ -5203,70 +5216,70 @@
         <v>46</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I99" s="3">
-        <v>46108.5968055556</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="J99" s="3">
-        <v>46126.6875</v>
+        <v>46072.6891666667</v>
       </c>
       <c r="K99" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M99" s="3">
-        <v>46069.4509722222</v>
+        <v>46069.5930902778</v>
       </c>
       <c r="N99" s="3">
-        <v>46108.5968055556</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="O99" s="3"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>2528858</v>
+        <v>2529591</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I100" s="3">
-        <v>46107.3861458333</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="J100" s="3">
-        <v>46087.6277662037</v>
+        <v>46126.6875</v>
       </c>
       <c r="K100" s="0" t="s">
         <v>45</v>
@@ -5275,548 +5288,548 @@
         <v>51</v>
       </c>
       <c r="M100" s="3">
-        <v>46065.7194791667</v>
+        <v>46069.4509722222</v>
       </c>
       <c r="N100" s="3">
-        <v>46107.3861458333</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>2525312</v>
+        <v>2528858</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I101" s="3">
-        <v>46070.5877314815</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="J101" s="3">
-        <v>46062.7587037037</v>
+        <v>46087.6277662037</v>
       </c>
       <c r="K101" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M101" s="3">
-        <v>46058.3585648148</v>
+        <v>46065.7194791667</v>
       </c>
       <c r="N101" s="3">
-        <v>46070.5877314815</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>2525272</v>
+        <v>2525312</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>188</v>
+        <v>46</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>188</v>
+        <v>46</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>189</v>
+        <v>35</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>190</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I102" s="3">
-        <v>46203.7916666667</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="J102" s="3">
-        <v>46126.7441782407</v>
+        <v>46062.7587037037</v>
       </c>
       <c r="K102" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L102" s="0" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="M102" s="3">
-        <v>46058.2883101852</v>
-      </c>
-      <c r="N102" s="3"/>
+        <v>46058.3585648148</v>
+      </c>
+      <c r="N102" s="3">
+        <v>46070.5877314815</v>
+      </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>2524577</v>
+        <v>2525272</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="I103" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I103" s="3">
+        <v>46203.7916666667</v>
+      </c>
       <c r="J103" s="3">
-        <v>46267.4298180903</v>
+        <v>46126.7441782407</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M103" s="3">
-        <v>46056.697349537</v>
+        <v>46058.2883101852</v>
       </c>
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>2524373</v>
+        <v>2524577</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I104" s="3">
-        <v>46087.3854513889</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="I104" s="3"/>
       <c r="J104" s="3">
-        <v>46056.6543865741</v>
+        <v>46267.4298180903</v>
       </c>
       <c r="K104" s="0" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="M104" s="3">
-        <v>46056.5937847222</v>
-      </c>
-      <c r="N104" s="3">
-        <v>46087.3854513889</v>
-      </c>
+        <v>46056.697349537</v>
+      </c>
+      <c r="N104" s="3"/>
       <c r="O104" s="3"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>2524062</v>
+        <v>2524373</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I105" s="3">
-        <v>46057.7412615741</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="J105" s="3">
-        <v>46056.6210300926</v>
+        <v>46056.6543865741</v>
       </c>
       <c r="K105" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="M105" s="3">
-        <v>46056.3662615741</v>
+        <v>46056.5937847222</v>
       </c>
       <c r="N105" s="3">
-        <v>46057.7412615741</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="O105" s="3"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>2523635</v>
+        <v>2524062</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I106" s="3">
-        <v>46059.4164236111</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="J106" s="3">
-        <v>46055.6034837963</v>
+        <v>46056.6210300926</v>
       </c>
       <c r="K106" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L106" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M106" s="3">
-        <v>46055.4997569444</v>
+        <v>46056.3662615741</v>
       </c>
       <c r="N106" s="3">
-        <v>46059.4164236111</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="O106" s="3"/>
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>2523602</v>
+        <v>2523635</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I107" s="3">
-        <v>46093.6246643519</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="J107" s="3">
-        <v>46056.5784027778</v>
+        <v>46055.6034837963</v>
       </c>
       <c r="K107" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="M107" s="3">
-        <v>46055.4788310185</v>
+        <v>46055.4997569444</v>
       </c>
       <c r="N107" s="3">
-        <v>46093.6246643519</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="O107" s="3"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>2521645</v>
+        <v>2523602</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="I108" s="3">
-        <v>46062.5</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="J108" s="3">
-        <v>46050.3426763542</v>
+        <v>46056.5784027778</v>
       </c>
       <c r="K108" s="0" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="L108" s="0" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M108" s="3">
-        <v>46049.7714236111</v>
-      </c>
-      <c r="N108" s="3"/>
+        <v>46055.4788310185</v>
+      </c>
+      <c r="N108" s="3">
+        <v>46093.6246643519</v>
+      </c>
       <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>2521079</v>
+        <v>2521645</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="I109" s="3">
-        <v>46052.6666666667</v>
+        <v>46062.5</v>
       </c>
       <c r="J109" s="3">
-        <v>46056.6197800926</v>
+        <v>46050.3426763542</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M109" s="3">
-        <v>46048.7684490741</v>
-      </c>
-      <c r="N109" s="3">
-        <v>46061.6309722222</v>
-      </c>
+        <v>46049.7714236111</v>
+      </c>
+      <c r="N109" s="3"/>
       <c r="O109" s="3"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>2520048</v>
+        <v>2521079</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>182</v>
+        <v>107</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="F110" s="0" t="s">
         <v>18</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I110" s="3">
-        <v>46057.5</v>
+        <v>46052.6666666667</v>
       </c>
       <c r="J110" s="3">
-        <v>46052.5774305556</v>
+        <v>46056.6197800926</v>
       </c>
       <c r="K110" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L110" s="0" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M110" s="3">
-        <v>46045.3325578704</v>
+        <v>46048.7684490741</v>
       </c>
       <c r="N110" s="3">
-        <v>46057.5</v>
+        <v>46061.6309722222</v>
       </c>
       <c r="O110" s="3"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>2519904</v>
+        <v>2520048</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I111" s="3">
-        <v>46084.7217939815</v>
+        <v>46057.5</v>
       </c>
       <c r="J111" s="3">
-        <v>46044.7413888889</v>
+        <v>46052.5774305556</v>
       </c>
       <c r="K111" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M111" s="3">
-        <v>46044.6384606482</v>
+        <v>46045.3325578704</v>
       </c>
       <c r="N111" s="3">
-        <v>46084.7217939815</v>
+        <v>46057.5</v>
       </c>
       <c r="O111" s="3"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>2519523</v>
+        <v>2519904</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>46</v>
+        <v>185</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I112" s="3">
-        <v>46076.5902777778</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="J112" s="3">
-        <v>46048.4589814815</v>
+        <v>46044.7413888889</v>
       </c>
       <c r="K112" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="M112" s="3">
-        <v>46043.7362847222</v>
+        <v>46044.6384606482</v>
       </c>
       <c r="N112" s="3">
-        <v>46077.380775463</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="O112" s="3"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>2519383</v>
+        <v>2519523</v>
       </c>
       <c r="B113" s="0" t="s">
         <v>46</v>
@@ -5825,304 +5838,304 @@
         <v>46</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E113" s="0" t="s">
         <v>41</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I113" s="3">
-        <v>46076.399224537</v>
+        <v>46076.5902777778</v>
       </c>
       <c r="J113" s="3">
-        <v>46048.4599305556</v>
+        <v>46048.4589814815</v>
       </c>
       <c r="K113" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M113" s="3">
-        <v>46043.6075578704</v>
+        <v>46043.7362847222</v>
       </c>
       <c r="N113" s="3">
-        <v>46076.399224537</v>
+        <v>46077.380775463</v>
       </c>
       <c r="O113" s="3"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>2519284</v>
+        <v>2519383</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I114" s="3">
-        <v>46049.3982986111</v>
+        <v>46076.399224537</v>
       </c>
       <c r="J114" s="3">
-        <v>46043.742337963</v>
+        <v>46048.4599305556</v>
       </c>
       <c r="K114" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L114" s="0" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="M114" s="3">
-        <v>46043.4816319444</v>
+        <v>46043.6075578704</v>
       </c>
       <c r="N114" s="3">
-        <v>46049.3982986111</v>
+        <v>46076.399224537</v>
       </c>
       <c r="O114" s="3"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>2518650</v>
+        <v>2519284</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>182</v>
+        <v>107</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I115" s="3">
-        <v>46072.3536921296</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="J115" s="3">
-        <v>46043.8185648148</v>
+        <v>46043.742337963</v>
       </c>
       <c r="K115" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="M115" s="3">
-        <v>46042.3536921296</v>
+        <v>46043.4816319444</v>
       </c>
       <c r="N115" s="3">
-        <v>46080.437025463</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="O115" s="3"/>
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>2513117</v>
+        <v>2518650</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I116" s="3">
-        <v>46031.4922800926</v>
+        <v>46072.3536921296</v>
       </c>
       <c r="J116" s="3">
-        <v>46028.3500347222</v>
+        <v>46043.8185648148</v>
       </c>
       <c r="K116" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L116" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="M116" s="3">
-        <v>46027.6381134259</v>
+        <v>46042.3536921296</v>
       </c>
       <c r="N116" s="3">
-        <v>46031.4922800926</v>
+        <v>46080.437025463</v>
       </c>
       <c r="O116" s="3"/>
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>2512883</v>
+        <v>2513117</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I117" s="3">
-        <v>46037.6340972222</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="J117" s="3">
-        <v>46129.4199421296</v>
+        <v>46028.3500347222</v>
       </c>
       <c r="K117" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M117" s="3">
-        <v>46027.4049305556</v>
+        <v>46027.6381134259</v>
       </c>
       <c r="N117" s="3">
-        <v>46141.6335300926</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="O117" s="3"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>2512542</v>
+        <v>2512883</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I118" s="3">
-        <v>46036.5</v>
+        <v>46037.6340972222</v>
       </c>
       <c r="J118" s="3">
-        <v>46024.5900925926</v>
+        <v>46129.4199421296</v>
       </c>
       <c r="K118" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L118" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M118" s="3">
-        <v>46022.6836342593</v>
+        <v>46027.4049305556</v>
       </c>
       <c r="N118" s="3">
-        <v>46036.5</v>
+        <v>46141.6335300926</v>
       </c>
       <c r="O118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>2512541</v>
+        <v>2512542</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I119" s="3">
         <v>46036.5</v>
       </c>
       <c r="J119" s="3">
-        <v>46022.7128356481</v>
+        <v>46024.5900925926</v>
       </c>
       <c r="K119" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M119" s="3">
-        <v>46022.6762615741</v>
+        <v>46022.6836342593</v>
       </c>
       <c r="N119" s="3">
         <v>46036.5</v>
@@ -6131,345 +6144,345 @@
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <v>2509014</v>
+        <v>2512541</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I120" s="3">
-        <v>46044.7250578704</v>
+        <v>46036.5</v>
       </c>
       <c r="J120" s="3">
-        <v>46022.6138541667</v>
+        <v>46022.7128356481</v>
       </c>
       <c r="K120" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L120" s="0" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M120" s="3">
-        <v>46008.454224537</v>
+        <v>46022.6762615741</v>
       </c>
       <c r="N120" s="3">
-        <v>46045.4708564815</v>
+        <v>46036.5</v>
       </c>
       <c r="O120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <v>2506714</v>
+        <v>2509014</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I121" s="3">
-        <v>46038.7073032407</v>
+        <v>46044.7250578704</v>
       </c>
       <c r="J121" s="3">
-        <v>46044.7372337963</v>
+        <v>46022.6138541667</v>
       </c>
       <c r="K121" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M121" s="3">
-        <v>46002.4364699074</v>
+        <v>46008.454224537</v>
       </c>
       <c r="N121" s="3">
-        <v>46038.7073032407</v>
+        <v>46045.4708564815</v>
       </c>
       <c r="O121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <v>2506599</v>
+        <v>2506714</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I122" s="3">
-        <v>46037.61375</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="J122" s="3">
-        <v>46052.3252083333</v>
+        <v>46044.7372337963</v>
       </c>
       <c r="K122" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L122" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M122" s="3">
-        <v>46002.3429166667</v>
+        <v>46002.4364699074</v>
       </c>
       <c r="N122" s="3">
-        <v>46037.61375</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="O122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <v>2506311</v>
+        <v>2506599</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>211</v>
+        <v>121</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>211</v>
+        <v>121</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I123" s="3">
-        <v>46013.7291666667</v>
+        <v>46037.61375</v>
       </c>
       <c r="J123" s="3">
-        <v>46013.461875</v>
+        <v>46052.3252083333</v>
       </c>
       <c r="K123" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="M123" s="3">
-        <v>46001.5219328704</v>
+        <v>46002.3429166667</v>
       </c>
       <c r="N123" s="3">
-        <v>46013.7291666667</v>
+        <v>46037.61375</v>
       </c>
       <c r="O123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <v>2506102</v>
+        <v>2506311</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I124" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I124" s="3">
+        <v>46013.7291666667</v>
+      </c>
       <c r="J124" s="3">
-        <v>46241.5032638889</v>
+        <v>46013.461875</v>
       </c>
       <c r="K124" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L124" s="0" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="M124" s="3">
-        <v>46001.3800578704</v>
-      </c>
-      <c r="N124" s="3"/>
+        <v>46001.5219328704</v>
+      </c>
+      <c r="N124" s="3">
+        <v>46013.7291666667</v>
+      </c>
       <c r="O124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <v>2502589</v>
+        <v>2506102</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>214</v>
+        <v>129</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>214</v>
+        <v>129</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="E125" s="0" t="s">
         <v>41</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I125" s="3">
-        <v>46029.6634375</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I125" s="3"/>
       <c r="J125" s="3">
-        <v>46014.6931018519</v>
+        <v>46241.5032638889</v>
       </c>
       <c r="K125" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="M125" s="3">
-        <v>45993.3791087963</v>
-      </c>
-      <c r="N125" s="3">
-        <v>46029.6634375</v>
-      </c>
+        <v>46001.3800578704</v>
+      </c>
+      <c r="N125" s="3"/>
       <c r="O125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <v>2502438</v>
+        <v>2502589</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>104</v>
+        <v>217</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I126" s="3">
-        <v>46037.3801388889</v>
+        <v>46029.6634375</v>
       </c>
       <c r="J126" s="3">
-        <v>45996.4823032407</v>
+        <v>46014.6931018519</v>
       </c>
       <c r="K126" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="M126" s="3">
-        <v>45992.7134722222</v>
+        <v>45993.3791087963</v>
       </c>
       <c r="N126" s="3">
-        <v>46037.3801388889</v>
+        <v>46029.6634375</v>
       </c>
       <c r="O126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <v>2501349</v>
+        <v>2502438</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I127" s="3">
-        <v>46069.7381944444</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="J127" s="3">
-        <v>46069.3651388889</v>
+        <v>45996.4823032407</v>
       </c>
       <c r="K127" s="0" t="s">
         <v>45</v>
@@ -6478,867 +6491,912 @@
         <v>51</v>
       </c>
       <c r="M127" s="3">
-        <v>45989.0365856482</v>
+        <v>45992.7134722222</v>
       </c>
       <c r="N127" s="3">
-        <v>46069.7381944444</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="O127" s="3"/>
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <v>2500635</v>
+        <v>2501349</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I128" s="3">
-        <v>46024.4633796296</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="J128" s="3">
-        <v>46027.3611111111</v>
+        <v>46069.3651388889</v>
       </c>
       <c r="K128" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L128" s="0" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="M128" s="3">
-        <v>45987.671712963</v>
+        <v>45989.0365856482</v>
       </c>
       <c r="N128" s="3">
-        <v>46024.4633796296</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="O128" s="3"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <v>2498066</v>
+        <v>2500635</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>157</v>
+        <v>35</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I129" s="3">
-        <v>46073.7916666667</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="J129" s="3">
-        <v>46126.6953240741</v>
+        <v>46027.3611111111</v>
       </c>
       <c r="K129" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M129" s="3">
-        <v>45979.750162037</v>
-      </c>
-      <c r="N129" s="3"/>
+        <v>45987.671712963</v>
+      </c>
+      <c r="N129" s="3">
+        <v>46024.4633796296</v>
+      </c>
       <c r="O129" s="3"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <v>2494282</v>
+        <v>2498066</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>118</v>
+        <v>185</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I130" s="3">
-        <v>45986.48125</v>
+        <v>46073.7916666667</v>
       </c>
       <c r="J130" s="3">
-        <v>45988.567025463</v>
+        <v>46126.6953240741</v>
       </c>
       <c r="K130" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L130" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M130" s="3">
-        <v>45971.4792824074</v>
-      </c>
-      <c r="N130" s="3">
-        <v>45986.4815625</v>
-      </c>
+        <v>45979.750162037</v>
+      </c>
+      <c r="N130" s="3"/>
       <c r="O130" s="3"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <v>2494179</v>
+        <v>2494282</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>182</v>
+        <v>121</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>119</v>
+        <v>223</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>222</v>
+        <v>17</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>224</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I131" s="3">
-        <v>46002.675775463</v>
+        <v>45986.48125</v>
       </c>
       <c r="J131" s="3">
-        <v>46044.7370486111</v>
+        <v>45988.567025463</v>
       </c>
       <c r="K131" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M131" s="3">
-        <v>45971.4049421296</v>
+        <v>45971.4792824074</v>
       </c>
       <c r="N131" s="3">
-        <v>46002.675775463</v>
+        <v>45986.4815625</v>
       </c>
       <c r="O131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <v>2490911</v>
+        <v>2494179</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="D132" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E132" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="E132" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="F132" s="0" t="s">
-        <v>61</v>
+        <v>226</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="I132" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="I132" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="J132" s="3">
-        <v>46182.7633796296</v>
+        <v>46044.7370486111</v>
       </c>
       <c r="K132" s="0" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="L132" s="0" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="M132" s="3">
-        <v>45961.5760300926</v>
-      </c>
-      <c r="N132" s="3"/>
+        <v>45971.4049421296</v>
+      </c>
+      <c r="N132" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="O132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <v>2490185</v>
+        <v>2490911</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I133" s="3">
-        <v>46203.7916666667</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="I133" s="3"/>
       <c r="J133" s="3">
-        <v>46051.4836111111</v>
+        <v>46182.7633796296</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M133" s="3">
-        <v>45960.3928819444</v>
+        <v>45961.5760300926</v>
       </c>
       <c r="N133" s="3"/>
       <c r="O133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <v>2489016</v>
+        <v>2490185</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>228</v>
+        <v>17</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>223</v>
+        <v>62</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I134" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I134" s="3">
+        <v>46203.7916666667</v>
+      </c>
       <c r="J134" s="3">
-        <v>45958.3906481481</v>
+        <v>46051.4836111111</v>
       </c>
       <c r="K134" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L134" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M134" s="3">
-        <v>45957.7253009259</v>
+        <v>45960.3928819444</v>
       </c>
       <c r="N134" s="3"/>
       <c r="O134" s="3"/>
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <v>2485386</v>
+        <v>2489016</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>225</v>
+        <v>90</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>28</v>
+        <v>231</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>61</v>
+        <v>226</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="I135" s="3">
-        <v>46386.7916666667</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I135" s="3"/>
       <c r="J135" s="3">
-        <v>46182.7639236111</v>
+        <v>45958.3906481481</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M135" s="3">
-        <v>45947.7000115741</v>
+        <v>45957.7253009259</v>
       </c>
       <c r="N135" s="3"/>
       <c r="O135" s="3"/>
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <v>2483420</v>
+        <v>2485386</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="I136" s="3"/>
+        <v>112</v>
+      </c>
+      <c r="I136" s="3">
+        <v>46386.7916666667</v>
+      </c>
       <c r="J136" s="3">
-        <v>46140.3843518519</v>
+        <v>46182.7639236111</v>
       </c>
       <c r="K136" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L136" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M136" s="3">
-        <v>45944.6603819444</v>
+        <v>45947.7000115741</v>
       </c>
       <c r="N136" s="3"/>
       <c r="O136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <v>2474606</v>
+        <v>2483420</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I137" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="I137" s="3"/>
       <c r="J137" s="3">
-        <v>45966.4450925926</v>
+        <v>46140.3843518519</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="M137" s="3">
-        <v>45924.4486921296</v>
-      </c>
-      <c r="N137" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>45944.6603819444</v>
+      </c>
+      <c r="N137" s="3"/>
       <c r="O137" s="3"/>
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <v>2470122</v>
+        <v>2474606</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>233</v>
+        <v>121</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>233</v>
+        <v>121</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="I138" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I138" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="J138" s="3">
-        <v>46204.3270601852</v>
+        <v>45966.4450925926</v>
       </c>
       <c r="K138" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L138" s="0" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="M138" s="3">
-        <v>45912.5572222222</v>
-      </c>
-      <c r="N138" s="3"/>
+        <v>45924.4486921296</v>
+      </c>
+      <c r="N138" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="O138" s="3"/>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>2463515</v>
+        <v>2470122</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>118</v>
+        <v>236</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>118</v>
+        <v>236</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>237</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>57</v>
+        <v>238</v>
       </c>
       <c r="I139" s="3"/>
       <c r="J139" s="3">
-        <v>45910.4755555556</v>
+        <v>46204.3270601852</v>
       </c>
       <c r="K139" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M139" s="3">
-        <v>45897.4218865741</v>
+        <v>45912.5572222222</v>
       </c>
       <c r="N139" s="3"/>
       <c r="O139" s="3"/>
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>2461703</v>
+        <v>2463515</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>235</v>
+        <v>58</v>
       </c>
       <c r="I140" s="3"/>
       <c r="J140" s="3">
-        <v>46003.3706828704</v>
+        <v>45910.4755555556</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="L140" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M140" s="3">
-        <v>45894.4525347222</v>
+        <v>45897.4218865741</v>
       </c>
       <c r="N140" s="3"/>
       <c r="O140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>2459339</v>
+        <v>2461703</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="I141" s="3"/>
       <c r="J141" s="3">
-        <v>46140.3839930556</v>
+        <v>46003.3706828704</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M141" s="3">
-        <v>45887.7442361111</v>
+        <v>45894.4525347222</v>
       </c>
       <c r="N141" s="3"/>
       <c r="O141" s="3"/>
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <v>2456538</v>
+        <v>2459339</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>88</v>
+        <v>228</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="I142" s="3"/>
       <c r="J142" s="3">
-        <v>46126.7428356481</v>
+        <v>46140.3839930556</v>
       </c>
       <c r="K142" s="0" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="L142" s="0" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="M142" s="3">
-        <v>45880.6643055556</v>
+        <v>45887.7442361111</v>
       </c>
       <c r="N142" s="3"/>
       <c r="O142" s="3"/>
     </row>
     <row r="143">
       <c r="A143" s="2">
-        <v>2449811</v>
+        <v>2456538</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I143" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I143" s="3"/>
       <c r="J143" s="3">
-        <v>45870.3628819444</v>
+        <v>46126.7428356481</v>
       </c>
       <c r="K143" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L143" s="0" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="M143" s="3">
-        <v>45862.6188888889</v>
-      </c>
-      <c r="N143" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>45880.6643055556</v>
+      </c>
+      <c r="N143" s="3"/>
       <c r="O143" s="3"/>
     </row>
     <row r="144">
       <c r="A144" s="2">
-        <v>2442028</v>
+        <v>2449811</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="E144" s="0" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I144" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="I144" s="3">
+        <v>45875.3688888889</v>
+      </c>
       <c r="J144" s="3">
-        <v>46126.7431134259</v>
+        <v>45870.3628819444</v>
       </c>
       <c r="K144" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L144" s="0" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="M144" s="3">
-        <v>45842.317025463</v>
-      </c>
-      <c r="N144" s="3"/>
+        <v>45862.6188888889</v>
+      </c>
+      <c r="N144" s="3">
+        <v>45875.3688888889</v>
+      </c>
       <c r="O144" s="3"/>
     </row>
     <row r="145">
       <c r="A145" s="2">
-        <v>2439691</v>
+        <v>2442028</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>118</v>
+        <v>246</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>118</v>
+        <v>246</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E145" s="0" t="s">
         <v>17</v>
       </c>
+      <c r="F145" s="0" t="s">
+        <v>18</v>
+      </c>
       <c r="G145" s="0" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I145" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I145" s="3"/>
       <c r="J145" s="3">
-        <v>45838.6211342593</v>
+        <v>46126.7431134259</v>
       </c>
       <c r="K145" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L145" s="0" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="M145" s="3">
-        <v>45838.3761921296</v>
-      </c>
-      <c r="N145" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>45842.317025463</v>
+      </c>
+      <c r="N145" s="3"/>
       <c r="O145" s="3"/>
     </row>
     <row r="146">
       <c r="A146" s="2">
-        <v>2437239</v>
+        <v>2439691</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>246</v>
+        <v>121</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>247</v>
+        <v>121</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>34</v>
+        <v>223</v>
       </c>
       <c r="E146" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="F146" s="0" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>248</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I146" s="3">
-        <v>45870.3600462963</v>
+        <v>45852.3770833333</v>
       </c>
       <c r="J146" s="3">
-        <v>45841.7026091435</v>
+        <v>45838.6211342593</v>
       </c>
       <c r="K146" s="0" t="s">
         <v>45</v>
       </c>
       <c r="L146" s="0" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="M146" s="3">
-        <v>45831.6933796296</v>
+        <v>45838.3761921296</v>
       </c>
       <c r="N146" s="3">
-        <v>45870.3600462963</v>
+        <v>45852.3770833333</v>
       </c>
       <c r="O146" s="3"/>
     </row>
     <row r="147">
       <c r="A147" s="2">
+        <v>2437239</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="C147" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="D147" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F147" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="G147" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="H147" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="I147" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="J147" s="3">
+        <v>45841.7026091435</v>
+      </c>
+      <c r="K147" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="L147" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="M147" s="3">
+        <v>45831.6933796296</v>
+      </c>
+      <c r="N147" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="O147" s="3"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2">
         <v>2436707</v>
       </c>
-      <c r="B147" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="C147" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="D147" s="0" t="s">
-        <v>220</v>
-      </c>
-      <c r="E147" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="F147" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G147" s="0" t="s">
-        <v>249</v>
-      </c>
-      <c r="H147" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I147" s="3">
+      <c r="B148" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="C148" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G148" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="H148" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="I148" s="3">
         <v>45835.7284722222</v>
       </c>
-      <c r="J147" s="3">
+      <c r="J148" s="3">
         <v>46126.7436921296</v>
       </c>
-      <c r="K147" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="L147" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="M147" s="3">
+      <c r="K148" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="L148" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="M148" s="3">
         <v>45828.8276273148</v>
       </c>
-      <c r="N147" s="3">
+      <c r="N148" s="3">
         <v>45835.7288773148</v>
       </c>
-      <c r="O147" s="3"/>
+      <c r="O148" s="3"/>
     </row>
   </sheetData>
   <headerFooter/>

--- a/Solicitacoes.xlsx
+++ b/Solicitacoes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <si>
     <t>Protocolo</t>
   </si>
@@ -59,25 +59,88 @@
     <t>Prazo desejado</t>
   </si>
   <si>
+    <t>COMPESAPREV.NIECIA</t>
+  </si>
+  <si>
+    <t>CORRECAO</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>Controle Financeiro</t>
+  </si>
+  <si>
+    <t>Erro na geração da limitação de cobrança de PF para o grupo Exames e Terapias</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Suporte nível II</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>ALEXIA.SANTOS</t>
+  </si>
+  <si>
+    <t>HELPDESK - CUIDAR</t>
+  </si>
+  <si>
+    <t>Processamento de Contas</t>
+  </si>
+  <si>
+    <t>Erro genérico no faturamento 210.PagamentoPrestadores</t>
+  </si>
+  <si>
+    <t>Homologando</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Códigos folhas gerados errados com mudança de módulo.</t>
+  </si>
+  <si>
+    <t>MICHEL.HERNANDES</t>
+  </si>
+  <si>
+    <t>Julia Albertim</t>
+  </si>
+  <si>
+    <t>CONFIGURAÇÃO</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>Remover permissão de administrador no web.config para usuários não autorizados</t>
+  </si>
+  <si>
+    <t>Liberado para cliente</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>COMPESAPREV.JULIA</t>
   </si>
   <si>
-    <t>CORRECAO</t>
-  </si>
-  <si>
-    <t>AG</t>
-  </si>
-  <si>
     <t>ADM</t>
   </si>
   <si>
     <t>AG - Erro ao importar Tabela Genérica (Aguardando Processamento)</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
-    <t>Suporte nível II</t>
+    <t>Aguardando detalhamento</t>
   </si>
   <si>
     <t>4</t>
@@ -101,9 +164,6 @@
     <t xml:space="preserve">APP -  Erro no servidor / buscar dados</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>ROGERIO.ALMEIDA</t>
   </si>
   <si>
@@ -113,24 +173,9 @@
     <t>Critica para gerar XML na Rotina Monitoramento TISS</t>
   </si>
   <si>
-    <t>Aguardando Revisão de código</t>
-  </si>
-  <si>
-    <t>Julia Albertim</t>
-  </si>
-  <si>
-    <t>HELPDESK - CUIDAR</t>
-  </si>
-  <si>
     <t>INSTABILIDADE MÓDULOS</t>
   </si>
   <si>
-    <t>Homologando</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
     <t>Faturamento</t>
   </si>
   <si>
@@ -149,9 +194,6 @@
     <t>CONECTA - XML não sai do estado de "Em Processamento"</t>
   </si>
   <si>
-    <t>Resolvido</t>
-  </si>
-  <si>
     <t>ANA.GOLDIM</t>
   </si>
   <si>
@@ -179,30 +221,18 @@
     <t>Programando</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Prestadores</t>
   </si>
   <si>
     <t>ALTERAÇÃO NOME PRESTADOR</t>
   </si>
   <si>
-    <t>Liberado para cliente</t>
-  </si>
-  <si>
     <t>Configurações do Sistema</t>
   </si>
   <si>
     <t>Ajuste no tempo de sessão ativa (timeout) do sistema Lean.</t>
   </si>
   <si>
-    <t>ALEXIA.SANTOS</t>
-  </si>
-  <si>
-    <t>Controle Financeiro</t>
-  </si>
-  <si>
     <t>Correção – CompesaPrev – Erro de Geração do Código de Barras e Linha Digitável</t>
   </si>
   <si>
@@ -212,15 +242,9 @@
     <t>Verificando</t>
   </si>
   <si>
-    <t>COMPESAPREV.NIECIA</t>
-  </si>
-  <si>
     <t>Niécia Morais</t>
   </si>
   <si>
-    <t>Processamento de Contas</t>
-  </si>
-  <si>
     <t>Erro no faturamento de pagamentos prestadores</t>
   </si>
   <si>
@@ -293,9 +317,6 @@
     <t>Versão futura</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>EVIDENCIAS DO PROBLEMA NO RELATORIO DE PREVIA DE PAGAMENTO</t>
   </si>
   <si>
@@ -500,9 +521,6 @@
     <t>COMPESAPREV-AG-PROD- Erro na inclusão de eventos no sistema AG</t>
   </si>
   <si>
-    <t>Aguardando detalhamento</t>
-  </si>
-  <si>
     <t>COMPESAPREV- LEAN- PROD- Agendamento travado</t>
   </si>
   <si>
@@ -540,9 +558,6 @@
   </si>
   <si>
     <t>Erro de execução de query (NHibernate) ao enviar lote de pagamento</t>
-  </si>
-  <si>
-    <t>Web</t>
   </si>
   <si>
     <t>Atualização da BuilderCli</t>
@@ -682,9 +697,6 @@
   </si>
   <si>
     <t>Legenda de campos sobrepostas</t>
-  </si>
-  <si>
-    <t>CONFIGURAÇÃO</t>
   </si>
   <si>
     <t xml:space="preserve">CompesaPrev  - Liberação da ferramenta Central de Atendimento no ambiente de produção</t>
@@ -827,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1506990705218" customWidth="1"/>
@@ -837,7 +849,7 @@
     <col min="5" max="5" width="47.7084481375558" customWidth="1"/>
     <col min="6" max="6" width="24.124747140067" customWidth="1"/>
     <col min="7" max="7" width="115.814923967634" customWidth="1"/>
-    <col min="8" max="8" width="28.4032069614955" customWidth="1"/>
+    <col min="8" max="8" width="27.4691489083426" customWidth="1"/>
     <col min="9" max="9" width="17.2691879272461" customWidth="1"/>
     <col min="10" max="10" width="17.2691879272461" customWidth="1"/>
     <col min="11" max="11" width="14.5938720703125" customWidth="1"/>
@@ -896,7 +908,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2618623</v>
+        <v>2619693</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>15</v>
@@ -920,10 +932,10 @@
         <v>20</v>
       </c>
       <c r="I2" s="3">
-        <v>46294.7106365741</v>
+        <v>46294.6896643518</v>
       </c>
       <c r="J2" s="3">
-        <v>46289.45</v>
+        <v>46290.7313310185</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>21</v>
@@ -932,61 +944,61 @@
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>46289.3773032407</v>
+        <v>46290.7313310185</v>
       </c>
       <c r="N2" s="3">
-        <v>46294.7106365741</v>
+        <v>46294.6896643518</v>
       </c>
       <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2618403</v>
+        <v>2619258</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I3" s="3">
-        <v>46294.5634259259</v>
+        <v>46302.589837963</v>
       </c>
       <c r="J3" s="3">
-        <v>46288.6467592593</v>
+        <v>46293.3487384259</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M3" s="3">
-        <v>46288.6467592593</v>
+        <v>46290.3606712963</v>
       </c>
       <c r="N3" s="3">
-        <v>46294.5634259259</v>
+        <v>46302.589837963</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2618370</v>
+        <v>2619015</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>15</v>
@@ -998,202 +1010,200 @@
         <v>16</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="3">
-        <v>46290.5871296296</v>
+        <v>46293.6019212963</v>
       </c>
       <c r="J4" s="3">
-        <v>46288.6287962963</v>
+        <v>46289.643587963</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M4" s="3">
-        <v>46288.6287962963</v>
+        <v>46289.643587963</v>
       </c>
       <c r="N4" s="3">
-        <v>46290.5871296296</v>
+        <v>46293.6019212963</v>
       </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>2617933</v>
+        <v>2618956</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I5" s="3">
-        <v>46293.6666666667</v>
+        <v>46295.6236574074</v>
       </c>
       <c r="J5" s="3">
-        <v>46289.470218669</v>
+        <v>46293.3764351852</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="M5" s="3">
-        <v>46287.7594097222</v>
-      </c>
-      <c r="N5" s="3">
-        <v>46293.6666666667</v>
-      </c>
+        <v>46289.6236574074</v>
+      </c>
+      <c r="N5" s="3"/>
       <c r="O5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>2617538</v>
+        <v>2618623</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I6" s="3">
-        <v>46290.7498263889</v>
+        <v>46294.7106365741</v>
       </c>
       <c r="J6" s="3">
-        <v>46288.4440509259</v>
+        <v>46290.7337384259</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M6" s="3">
-        <v>46287.4164930556</v>
+        <v>46289.3773032407</v>
       </c>
       <c r="N6" s="3">
-        <v>46290.7498263889</v>
+        <v>46294.7106365741</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>2617170</v>
+        <v>2618403</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H7" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="3">
-        <v>46290.4403703704</v>
+        <v>46294.5634259259</v>
       </c>
       <c r="J7" s="3">
-        <v>46286.5862037037</v>
+        <v>46288.6467592593</v>
       </c>
       <c r="K7" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M7" s="3">
-        <v>46286.5862037037</v>
+        <v>46288.6467592593</v>
       </c>
       <c r="N7" s="3">
-        <v>46290.4403703704</v>
+        <v>46294.5634259259</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>2617057</v>
+        <v>2618370</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H8" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I8" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.5871296296</v>
       </c>
       <c r="J8" s="3">
-        <v>46286.5879513889</v>
+        <v>46289.6879962616</v>
       </c>
       <c r="K8" s="0" t="s">
         <v>21</v>
@@ -1202,1006 +1212,1006 @@
         <v>22</v>
       </c>
       <c r="M8" s="3">
-        <v>46286.4877199074</v>
+        <v>46288.6287962963</v>
       </c>
       <c r="N8" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.5871296296</v>
       </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2615970</v>
+        <v>2617933</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G9" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="3">
+        <v>46290.7916666667</v>
+      </c>
+      <c r="J9" s="3">
+        <v>46290.8786921296</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="3">
-        <v>46288.4166666667</v>
-      </c>
-      <c r="J9" s="3">
-        <v>46287.3554017708</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M9" s="3">
-        <v>46282.5089930556</v>
+        <v>46287.7594097222</v>
       </c>
       <c r="N9" s="3">
-        <v>46288.4166666667</v>
+        <v>46293.6666666667</v>
       </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>2615871</v>
+        <v>2617538</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I10" s="3">
-        <v>46286.4024189815</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="J10" s="3">
-        <v>46286.3450115741</v>
+        <v>46288.4440509259</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="M10" s="3">
-        <v>46282.4440856481</v>
+        <v>46287.4164930556</v>
       </c>
       <c r="N10" s="3">
-        <v>46286.4024189815</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>2615590</v>
+        <v>2617170</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I11" s="3">
-        <v>46287.5805092593</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="J11" s="3">
-        <v>46281.7496990741</v>
+        <v>46289.5649035069</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M11" s="3">
-        <v>46281.6638425926</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="N11" s="3">
-        <v>46287.5805092593</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>2614686</v>
+        <v>2617057</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H12" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="3">
-        <v>46321.5908449074</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="J12" s="3">
-        <v>46282.4296635764</v>
+        <v>46286.5879513889</v>
       </c>
       <c r="K12" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M12" s="3">
-        <v>46280.4450115741</v>
+        <v>46286.4877199074</v>
       </c>
       <c r="N12" s="3">
-        <v>46321.5908449074</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>2614334</v>
+        <v>2615970</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I13" s="3">
-        <v>46283.5629166667</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="J13" s="3">
-        <v>46283.4291666667</v>
+        <v>46287.3554017708</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="M13" s="3">
-        <v>46279.6749305556</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="N13" s="3">
-        <v>46283.5629166667</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>2614135</v>
+        <v>2615871</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="I14" s="3">
-        <v>46289.7291666667</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="J14" s="3">
-        <v>46288.6498263889</v>
+        <v>46286.3450115741</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="M14" s="3">
-        <v>46279.5169097222</v>
+        <v>46282.4440856481</v>
       </c>
       <c r="N14" s="3">
-        <v>46289.7291666667</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2613646</v>
+        <v>2615590</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="I15" s="3">
-        <v>46289.3876041667</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="J15" s="3">
-        <v>46283.4346064815</v>
+        <v>46293.377662037</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M15" s="3">
-        <v>46276.6376041667</v>
+        <v>46281.6638425926</v>
       </c>
       <c r="N15" s="3">
-        <v>46289.3876041667</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>2613202</v>
+        <v>2614686</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="3">
-        <v>46288.6119212963</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="J16" s="3">
-        <v>46283.4707657407</v>
+        <v>46282.4296635764</v>
       </c>
       <c r="K16" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M16" s="3">
-        <v>46276.3827546296</v>
+        <v>46280.4450115741</v>
       </c>
       <c r="N16" s="3">
-        <v>46288.6119212963</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>2613026</v>
+        <v>2614334</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H17" s="0" t="s">
         <v>37</v>
       </c>
       <c r="I17" s="3">
-        <v>46281.6747800926</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="J17" s="3">
-        <v>46287.6117592593</v>
+        <v>46283.4291666667</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L17" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M17" s="3">
-        <v>46275.6895601852</v>
+        <v>46279.6749305556</v>
       </c>
       <c r="N17" s="3">
-        <v>46281.6747800926</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>2612720</v>
+        <v>2614135</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I18" s="3">
-        <v>46316.6011689815</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="J18" s="3">
-        <v>46279.4816203704</v>
+        <v>46293.3668226852</v>
       </c>
       <c r="K18" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="M18" s="3">
-        <v>46275.4553356481</v>
+        <v>46279.5169097222</v>
       </c>
       <c r="N18" s="3">
-        <v>46316.6011689815</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>2611881</v>
+        <v>2613646</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I19" s="3">
-        <v>46279.6652314815</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="J19" s="3">
-        <v>46274.7389930556</v>
+        <v>46283.4346064815</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M19" s="3">
-        <v>46273.7485648148</v>
+        <v>46276.6376041667</v>
       </c>
       <c r="N19" s="3">
-        <v>46279.6652314815</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>2611848</v>
+        <v>2613202</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I20" s="3">
-        <v>46287.4094675926</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="J20" s="3">
-        <v>46276.5914583333</v>
+        <v>46283.4707657407</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="M20" s="3">
-        <v>46273.7127546296</v>
+        <v>46276.3827546296</v>
       </c>
       <c r="N20" s="3">
-        <v>46287.4094675926</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>2611692</v>
+        <v>2613026</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F21" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="I21" s="3">
-        <v>46279.4554861111</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="J21" s="3">
-        <v>46273.637278588</v>
+        <v>46287.6117592593</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M21" s="3">
-        <v>46273.6013194444</v>
+        <v>46275.6895601852</v>
       </c>
       <c r="N21" s="3">
-        <v>46279.4554861111</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2611552</v>
+        <v>2612720</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I22" s="3">
-        <v>46275.4327083333</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="J22" s="3">
-        <v>46273.5743171296</v>
+        <v>46293.3816203704</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="M22" s="3">
-        <v>46273.474375</v>
+        <v>46275.4553356481</v>
       </c>
       <c r="N22" s="3">
-        <v>46275.4327083333</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>2611551</v>
+        <v>2611881</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I23" s="3">
-        <v>46314.6183449074</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="J23" s="3">
-        <v>46274.3603356481</v>
+        <v>46274.7389930556</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M23" s="3">
-        <v>46273.4725115741</v>
+        <v>46273.7485648148</v>
       </c>
       <c r="N23" s="3">
-        <v>46314.6183449074</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>2611539</v>
+        <v>2611848</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I24" s="3">
-        <v>46275.4227083333</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="J24" s="3">
-        <v>46274.3607986111</v>
+        <v>46276.5914583333</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="L24" s="0" t="s">
         <v>29</v>
       </c>
       <c r="M24" s="3">
-        <v>46273.464375</v>
+        <v>46273.7127546296</v>
       </c>
       <c r="N24" s="3">
-        <v>46275.4227083333</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>2611521</v>
+        <v>2611692</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H25" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I25" s="3">
-        <v>46279.3705439815</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="J25" s="3">
-        <v>46273.7182003819</v>
+        <v>46273.637278588</v>
       </c>
       <c r="K25" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M25" s="3">
-        <v>46273.4538773148</v>
+        <v>46273.6013194444</v>
       </c>
       <c r="N25" s="3">
-        <v>46279.3705439815</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>2610876</v>
+        <v>2611552</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I26" s="3">
-        <v>46276.3367592593</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="J26" s="3">
-        <v>46269.4406376505</v>
+        <v>46273.5743171296</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L26" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M26" s="3">
-        <v>46269.4200925926</v>
+        <v>46273.474375</v>
       </c>
       <c r="N26" s="3">
-        <v>46276.3367592593</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>2610030</v>
+        <v>2611551</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I27" s="3">
-        <v>46274.6271990741</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="J27" s="3">
-        <v>46268.3853071412</v>
+        <v>46274.3603356481</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="M27" s="3">
-        <v>46267.7105324074</v>
+        <v>46273.4725115741</v>
       </c>
       <c r="N27" s="3">
-        <v>46274.6271990741</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>2609985</v>
+        <v>2611539</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I28" s="3">
-        <v>46301.4629166667</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="J28" s="3">
-        <v>46267.6774134606</v>
+        <v>46274.3607986111</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="M28" s="3">
-        <v>46267.67125</v>
+        <v>46273.464375</v>
       </c>
       <c r="N28" s="3">
-        <v>46301.4629166667</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>2609883</v>
+        <v>2611521</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I29" s="3">
-        <v>46309.7050347222</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="J29" s="3">
-        <v>46280.4030439815</v>
+        <v>46273.7182003819</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M29" s="3">
-        <v>46267.6217013889</v>
+        <v>46273.4538773148</v>
       </c>
       <c r="N29" s="3">
-        <v>46309.7050347222</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>2609551</v>
+        <v>2610876</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I30" s="3">
-        <v>46273.6887962963</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="J30" s="3">
-        <v>46267.355462963</v>
+        <v>46269.4406376505</v>
       </c>
       <c r="K30" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M30" s="3">
-        <v>46267.355462963</v>
+        <v>46269.4200925926</v>
       </c>
       <c r="N30" s="3">
-        <v>46273.6887962963</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>2609107</v>
+        <v>2610030</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>15</v>
@@ -2210,318 +2220,322 @@
         <v>15</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I31" s="3">
-        <v>46300.3339583333</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="J31" s="3">
-        <v>46289.4408381597</v>
+        <v>46268.3853071412</v>
       </c>
       <c r="K31" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="M31" s="3">
-        <v>46266.4797916667</v>
+        <v>46267.7105324074</v>
       </c>
       <c r="N31" s="3">
-        <v>46300.3339583333</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>2608731</v>
+        <v>2609985</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I32" s="3">
-        <v>46279.4280671296</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="J32" s="3">
-        <v>46273.3513888889</v>
+        <v>46267.6774134606</v>
       </c>
       <c r="K32" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="M32" s="3">
-        <v>46265.6780671296</v>
+        <v>46267.67125</v>
       </c>
       <c r="N32" s="3">
-        <v>46279.4280671296</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>2608637</v>
+        <v>2609883</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I33" s="3">
-        <v>46304.6977777778</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="J33" s="3">
-        <v>46287.4125274653</v>
+        <v>46280.4030439815</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="M33" s="3">
-        <v>46265.6144444444</v>
+        <v>46267.6217013889</v>
       </c>
       <c r="N33" s="3">
-        <v>46304.6977777778</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>2607413</v>
+        <v>2609551</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="I34" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I34" s="3">
+        <v>46273.6887962963</v>
+      </c>
       <c r="J34" s="3">
-        <v>46266.569212963</v>
+        <v>46267.355462963</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="M34" s="3">
-        <v>46261.6163888889</v>
-      </c>
-      <c r="N34" s="3"/>
+        <v>46267.355462963</v>
+      </c>
+      <c r="N34" s="3">
+        <v>46273.6887962963</v>
+      </c>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>2607198</v>
+        <v>2609107</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I35" s="3">
-        <v>46267.3546643518</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="J35" s="3">
-        <v>46273.6204976852</v>
+        <v>46293.378900463</v>
       </c>
       <c r="K35" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="M35" s="3">
-        <v>46261.4379976852</v>
+        <v>46266.4797916667</v>
       </c>
       <c r="N35" s="3">
-        <v>46267.3546643518</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="O35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>2606003</v>
+        <v>2608731</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H36" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I36" s="3">
-        <v>46265.3599537037</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="J36" s="3">
-        <v>46259.4993506944</v>
+        <v>46289.5798690625</v>
       </c>
       <c r="K36" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M36" s="3">
-        <v>46259.443287037</v>
+        <v>46265.6780671296</v>
       </c>
       <c r="N36" s="3">
-        <v>46290.75</v>
+        <v>46293.3554976852</v>
       </c>
       <c r="O36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>2604815</v>
+        <v>2608637</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I37" s="3">
-        <v>46296.563587963</v>
+        <v>46304.6977777778</v>
       </c>
       <c r="J37" s="3">
-        <v>46268.6781365741</v>
+        <v>46287.4125274653</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="M37" s="3">
-        <v>46255.4177546296</v>
+        <v>46265.6144444444</v>
       </c>
       <c r="N37" s="3">
-        <v>46296.563587963</v>
+        <v>46304.6977777778</v>
       </c>
       <c r="O37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>2604500</v>
+        <v>2607413</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>17</v>
@@ -2530,2344 +2544,2348 @@
         <v>18</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I38" s="3">
-        <v>46260.4812268519</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I38" s="3"/>
       <c r="J38" s="3">
-        <v>46258.3485416667</v>
+        <v>46266.569212963</v>
       </c>
       <c r="K38" s="0" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="M38" s="3">
-        <v>46254.6270601852</v>
-      </c>
-      <c r="N38" s="3">
-        <v>46260.4812268519</v>
-      </c>
+        <v>46261.6163888889</v>
+      </c>
+      <c r="N38" s="3"/>
       <c r="O38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2603668</v>
+        <v>2607198</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I39" s="3">
-        <v>46259.3446296296</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="J39" s="3">
-        <v>46258.6426851852</v>
+        <v>46273.6204976852</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M39" s="3">
-        <v>46253.427962963</v>
+        <v>46261.4379976852</v>
       </c>
       <c r="N39" s="3">
-        <v>46290.75</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="O39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>2602388</v>
+        <v>2606003</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="I40" s="3">
-        <v>46255.4166666667</v>
+        <v>46265.3599537037</v>
       </c>
       <c r="J40" s="3">
-        <v>46253.4900231482</v>
+        <v>46259.4993506944</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M40" s="3">
-        <v>46251.5527777778</v>
+        <v>46259.443287037</v>
       </c>
       <c r="N40" s="3">
-        <v>46255.4166666667</v>
+        <v>46290.75</v>
       </c>
       <c r="O40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>2601999</v>
+        <v>2604815</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="I41" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="I41" s="3">
+        <v>46296.563587963</v>
+      </c>
       <c r="J41" s="3">
-        <v>46266.6188194444</v>
+        <v>46268.6781365741</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="M41" s="3">
-        <v>46248.7351273148</v>
-      </c>
-      <c r="N41" s="3"/>
+        <v>46255.4177546296</v>
+      </c>
+      <c r="N41" s="3">
+        <v>46296.563587963</v>
+      </c>
       <c r="O41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>2600778</v>
+        <v>2604500</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="I42" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I42" s="3">
+        <v>46260.4812268519</v>
+      </c>
       <c r="J42" s="3">
-        <v>46274.3780324074</v>
+        <v>46258.3485416667</v>
       </c>
       <c r="K42" s="0" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="M42" s="3">
-        <v>46246.7171759259</v>
-      </c>
-      <c r="N42" s="3"/>
+        <v>46254.6270601852</v>
+      </c>
+      <c r="N42" s="3">
+        <v>46260.4812268519</v>
+      </c>
       <c r="O42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>2599732</v>
+        <v>2603668</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="I43" s="3">
-        <v>46251.4016203704</v>
+        <v>46259.3446296296</v>
       </c>
       <c r="J43" s="3">
-        <v>46248.3419117245</v>
+        <v>46258.6426851852</v>
       </c>
       <c r="K43" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M43" s="3">
-        <v>46245.4849537037</v>
+        <v>46253.427962963</v>
       </c>
       <c r="N43" s="3">
-        <v>46251.4016203704</v>
+        <v>46290.75</v>
       </c>
       <c r="O43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>2598987</v>
+        <v>2602388</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I44" s="3">
-        <v>46254.6856134259</v>
+        <v>46255.4166666667</v>
       </c>
       <c r="J44" s="3">
-        <v>46251.536875</v>
+        <v>46253.4900231482</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M44" s="3">
-        <v>46244.4564467593</v>
+        <v>46251.5527777778</v>
       </c>
       <c r="N44" s="3">
-        <v>46254.6856134259</v>
+        <v>46255.4166666667</v>
       </c>
       <c r="O44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>2598910</v>
+        <v>2601999</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="I45" s="3">
-        <v>46254.6386574074</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="I45" s="3"/>
       <c r="J45" s="3">
-        <v>46248.4760674769</v>
+        <v>46266.6188194444</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M45" s="3">
-        <v>46244.4094907407</v>
-      </c>
-      <c r="N45" s="3">
-        <v>46261.6103125</v>
-      </c>
+        <v>46248.7351273148</v>
+      </c>
+      <c r="N45" s="3"/>
       <c r="O45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>2598767</v>
+        <v>2600778</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="E46" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I46" s="3">
-        <v>46247.6666666667</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="I46" s="3"/>
       <c r="J46" s="3">
-        <v>46245.6608564815</v>
+        <v>46274.3780324074</v>
       </c>
       <c r="K46" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="L46" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="L46" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M46" s="3">
-        <v>46241.757962963</v>
-      </c>
-      <c r="N46" s="3">
-        <v>46247.6666666667</v>
-      </c>
+        <v>46246.7171759259</v>
+      </c>
+      <c r="N46" s="3"/>
       <c r="O46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>2597798</v>
+        <v>2599732</v>
       </c>
       <c r="B47" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G47" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="G47" s="0" t="s">
-        <v>116</v>
-      </c>
       <c r="H47" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I47" s="3">
-        <v>46290.75</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="J47" s="3">
-        <v>46273.4412384259</v>
+        <v>46248.3419117245</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M47" s="3">
-        <v>46240.4508912037</v>
+        <v>46245.4849537037</v>
       </c>
       <c r="N47" s="3">
-        <v>46290.75</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="O47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>2597524</v>
+        <v>2598987</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C48" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="G48" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="D48" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G48" s="0" t="s">
-        <v>118</v>
-      </c>
       <c r="H48" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I48" s="3">
-        <v>46267.0453356481</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="J48" s="3">
-        <v>46259.4158333333</v>
+        <v>46251.536875</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M48" s="3">
-        <v>46239.6925347222</v>
+        <v>46244.4564467593</v>
       </c>
       <c r="N48" s="3">
-        <v>46267.0453356481</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="O48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>2597515</v>
+        <v>2598910</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G49" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="H49" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="H49" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="I49" s="3">
-        <v>46266.4759953704</v>
+        <v>46254.6386574074</v>
       </c>
       <c r="J49" s="3">
-        <v>46261.4097453704</v>
+        <v>46248.4760674769</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="M49" s="3">
-        <v>46239.6856134259</v>
+        <v>46244.4094907407</v>
       </c>
       <c r="N49" s="3">
-        <v>46266.4759953704</v>
+        <v>46261.6103125</v>
       </c>
       <c r="O49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>2597495</v>
+        <v>2598767</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F50" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="H50" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="G50" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="H50" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="I50" s="3">
-        <v>46252.3333333333</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="J50" s="3">
-        <v>46241.6523302083</v>
+        <v>46245.6608564815</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M50" s="3">
-        <v>46239.6802199074</v>
+        <v>46241.757962963</v>
       </c>
       <c r="N50" s="3">
-        <v>46245.5968865741</v>
-      </c>
-      <c r="O50" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>46247.6666666667</v>
+      </c>
+      <c r="O50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>2596882</v>
+        <v>2597798</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>123</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I51" s="3">
-        <v>46280.3775578704</v>
+        <v>46290.75</v>
       </c>
       <c r="J51" s="3">
-        <v>46267.6170023148</v>
+        <v>46273.4412384259</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="M51" s="3">
-        <v>46238.7108912037</v>
+        <v>46240.4508912037</v>
       </c>
       <c r="N51" s="3">
-        <v>46280.3775578704</v>
+        <v>46290.75</v>
       </c>
       <c r="O51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>2596538</v>
+        <v>2597524</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I52" s="3">
-        <v>46273.960787037</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="J52" s="3">
-        <v>46286.3521412037</v>
+        <v>46259.4158333333</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M52" s="3">
-        <v>46238.4644791667</v>
+        <v>46239.6925347222</v>
       </c>
       <c r="N52" s="3">
-        <v>46273.960787037</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="O52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>2596407</v>
+        <v>2597515</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="I53" s="3">
-        <v>46248.6072106482</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="J53" s="3">
-        <v>46267.6164814815</v>
+        <v>46289.7039236111</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M53" s="3">
-        <v>46238.3780439815</v>
+        <v>46239.6856134259</v>
       </c>
       <c r="N53" s="3">
-        <v>46248.6072106482</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="O53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>2595510</v>
+        <v>2597495</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="I54" s="3">
-        <v>46240.4984606481</v>
+        <v>46252.3333333333</v>
       </c>
       <c r="J54" s="3">
-        <v>46245.3667592593</v>
+        <v>46241.6523302083</v>
       </c>
       <c r="K54" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M54" s="3">
-        <v>46234.6442939815</v>
+        <v>46239.6802199074</v>
       </c>
       <c r="N54" s="3">
-        <v>46240.4984606481</v>
-      </c>
-      <c r="O54" s="3"/>
+        <v>46245.5968865741</v>
+      </c>
+      <c r="O54" s="3">
+        <v>46252.3333333333</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>2595497</v>
+        <v>2596882</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I55" s="3">
-        <v>46240.4978240741</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="J55" s="3">
-        <v>46245.3669444444</v>
+        <v>46267.6170023148</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="M55" s="3">
-        <v>46234.6436574074</v>
+        <v>46238.7108912037</v>
       </c>
       <c r="N55" s="3">
-        <v>46240.4978240741</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="O55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>2593529</v>
+        <v>2596538</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>15</v>
+        <v>124</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I56" s="3">
-        <v>46237.5806597222</v>
+        <v>46273.960787037</v>
       </c>
       <c r="J56" s="3">
-        <v>46233.4404570255</v>
+        <v>46286.3521412037</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M56" s="3">
-        <v>46231.6639930556</v>
+        <v>46238.4644791667</v>
       </c>
       <c r="N56" s="3">
-        <v>46237.5806597222</v>
+        <v>46273.960787037</v>
       </c>
       <c r="O56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>2593490</v>
+        <v>2596407</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I57" s="3">
-        <v>46239.6748032407</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="J57" s="3">
-        <v>46253.4905324074</v>
+        <v>46267.6164814815</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L57" s="0" t="s">
         <v>29</v>
       </c>
       <c r="M57" s="3">
-        <v>46231.6518865741</v>
+        <v>46238.3780439815</v>
       </c>
       <c r="N57" s="3">
-        <v>46239.6748032407</v>
-      </c>
-      <c r="O57" s="3">
-        <v>46234.48125</v>
-      </c>
+        <v>46248.6072106482</v>
+      </c>
+      <c r="O57" s="3"/>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>2593260</v>
+        <v>2595510</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I58" s="3">
-        <v>46241.6638888889</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="J58" s="3">
-        <v>46267.614525463</v>
+        <v>46245.3667592593</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M58" s="3">
-        <v>46231.435150463</v>
+        <v>46234.6442939815</v>
       </c>
       <c r="N58" s="3">
-        <v>46241.6638888889</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="O58" s="3"/>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>2593216</v>
+        <v>2595497</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I59" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I59" s="3">
+        <v>46240.4978240741</v>
+      </c>
       <c r="J59" s="3">
-        <v>46231.4047453704</v>
+        <v>46245.3669444444</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="M59" s="3">
-        <v>46231.4011111111</v>
-      </c>
-      <c r="N59" s="3"/>
+        <v>46234.6436574074</v>
+      </c>
+      <c r="N59" s="3">
+        <v>46240.4978240741</v>
+      </c>
       <c r="O59" s="3"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2592878</v>
+        <v>2593529</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H60" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I60" s="3">
-        <v>46241.3504282407</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="J60" s="3">
-        <v>46230.6675740741</v>
+        <v>46233.4404570255</v>
       </c>
       <c r="K60" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M60" s="3">
-        <v>46230.6004282407</v>
+        <v>46231.6639930556</v>
       </c>
       <c r="N60" s="3">
-        <v>46290.75</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="O60" s="3"/>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>2592468</v>
+        <v>2593490</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I61" s="3">
-        <v>46237.6038657407</v>
+        <v>46239.6748032407</v>
       </c>
       <c r="J61" s="3">
-        <v>46240.6136738773</v>
+        <v>46253.4905324074</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L61" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M61" s="3">
-        <v>46227.7107060185</v>
+        <v>46231.6518865741</v>
       </c>
       <c r="N61" s="3">
-        <v>46293.6033680556</v>
-      </c>
-      <c r="O61" s="3"/>
+        <v>46239.6748032407</v>
+      </c>
+      <c r="O61" s="3">
+        <v>46234.48125</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>2591596</v>
+        <v>2593260</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I62" s="3">
-        <v>46238.7083333333</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="J62" s="3">
-        <v>46267.3444803241</v>
+        <v>46267.614525463</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="M62" s="3">
-        <v>46226.4797916667</v>
+        <v>46231.435150463</v>
       </c>
       <c r="N62" s="3">
-        <v>46282.6141435185</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>2591284</v>
+        <v>2593216</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I63" s="3">
-        <v>46266.3384837963</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I63" s="3"/>
       <c r="J63" s="3">
-        <v>46225.7002398495</v>
+        <v>46231.4047453704</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="M63" s="3">
-        <v>46225.6718171296</v>
-      </c>
-      <c r="N63" s="3">
-        <v>46266.3384837963</v>
-      </c>
+        <v>46231.4011111111</v>
+      </c>
+      <c r="N63" s="3"/>
       <c r="O63" s="3"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2588490</v>
+        <v>2592878</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I64" s="3">
-        <v>46230.722037037</v>
+        <v>46241.3504282407</v>
       </c>
       <c r="J64" s="3">
-        <v>46231.4339699074</v>
+        <v>46230.6675740741</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="M64" s="3">
-        <v>46218.4928703704</v>
+        <v>46230.6004282407</v>
       </c>
       <c r="N64" s="3">
-        <v>46230.722037037</v>
+        <v>46290.75</v>
       </c>
       <c r="O64" s="3"/>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2588025</v>
+        <v>2592468</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>139</v>
+        <v>56</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>141</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="I65" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I65" s="3">
+        <v>46237.6038657407</v>
+      </c>
       <c r="J65" s="3">
-        <v>46267.5903356482</v>
+        <v>46240.6136738773</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="M65" s="3">
-        <v>46217.612962963</v>
-      </c>
-      <c r="N65" s="3"/>
+        <v>46227.7107060185</v>
+      </c>
+      <c r="N65" s="3">
+        <v>46293.6033680556</v>
+      </c>
       <c r="O65" s="3"/>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>2587849</v>
+        <v>2591596</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>142</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="I66" s="3">
-        <v>46226.6083796296</v>
+        <v>46238.7083333333</v>
       </c>
       <c r="J66" s="3">
-        <v>46237.9144806713</v>
+        <v>46267.3444803241</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M66" s="3">
-        <v>46217.4506597222</v>
+        <v>46226.4797916667</v>
       </c>
       <c r="N66" s="3">
-        <v>46226.6083796296</v>
+        <v>46282.6141435185</v>
       </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>2587713</v>
+        <v>2591284</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>143</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="I67" s="3">
-        <v>46218.7408680556</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="J67" s="3">
-        <v>46230.4199074074</v>
+        <v>46225.7002398495</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="M67" s="3">
-        <v>46217.3658680556</v>
+        <v>46225.6718171296</v>
       </c>
       <c r="N67" s="3">
-        <v>46218.7408680556</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="O67" s="3"/>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>2587585</v>
+        <v>2588490</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>144</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="I68" s="3">
-        <v>46220.6264583333</v>
+        <v>46230.722037037</v>
       </c>
       <c r="J68" s="3">
-        <v>46259.4474884259</v>
+        <v>46231.4339699074</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M68" s="3">
-        <v>46216.7097916667</v>
+        <v>46218.4928703704</v>
       </c>
       <c r="N68" s="3">
-        <v>46220.6264583333</v>
+        <v>46230.722037037</v>
       </c>
       <c r="O68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>2587006</v>
+        <v>2588025</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I69" s="3">
-        <v>46217.7289699074</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="I69" s="3"/>
       <c r="J69" s="3">
-        <v>46227.4549884259</v>
+        <v>46267.5903356482</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="M69" s="3">
-        <v>46213.7239236111</v>
-      </c>
-      <c r="N69" s="3">
-        <v>46217.7289699074</v>
-      </c>
+        <v>46217.612962963</v>
+      </c>
+      <c r="N69" s="3"/>
       <c r="O69" s="3"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>2586984</v>
+        <v>2587849</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I70" s="3">
-        <v>46295.7416550926</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="J70" s="3">
-        <v>46273.4946180556</v>
+        <v>46237.9144806713</v>
       </c>
       <c r="K70" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M70" s="3">
-        <v>46213.6971527778</v>
+        <v>46217.4506597222</v>
       </c>
       <c r="N70" s="3">
-        <v>46295.7416550926</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="O70" s="3"/>
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>2586910</v>
+        <v>2587713</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I71" s="3">
-        <v>46226.5833333333</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="J71" s="3">
-        <v>46230.4194212963</v>
+        <v>46230.4199074074</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M71" s="3">
-        <v>46213.6245833333</v>
+        <v>46217.3658680556</v>
       </c>
       <c r="N71" s="3">
-        <v>46226.5833333333</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="O71" s="3"/>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>2586651</v>
+        <v>2587585</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I72" s="3">
-        <v>46218.7157407407</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="J72" s="3">
-        <v>46213.3824074074</v>
+        <v>46259.4474884259</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M72" s="3">
-        <v>46213.3824074074</v>
+        <v>46216.7097916667</v>
       </c>
       <c r="N72" s="3">
-        <v>46218.7157407407</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="O72" s="3"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>2586187</v>
+        <v>2587006</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>151</v>
+        <v>24</v>
       </c>
       <c r="E73" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>152</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="I73" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I73" s="3">
+        <v>46217.7289699074</v>
+      </c>
       <c r="J73" s="3">
-        <v>46219.3850231481</v>
+        <v>46227.4549884259</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="M73" s="3">
-        <v>46211.7697337963</v>
-      </c>
-      <c r="N73" s="3"/>
+        <v>46213.7239236111</v>
+      </c>
+      <c r="N73" s="3">
+        <v>46217.7289699074</v>
+      </c>
       <c r="O73" s="3"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2585888</v>
+        <v>2586984</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>153</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I74" s="3">
-        <v>46217.4119907407</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="J74" s="3">
-        <v>46217.5003587963</v>
+        <v>46273.4946180556</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M74" s="3">
-        <v>46211.4953240741</v>
+        <v>46213.6971527778</v>
       </c>
       <c r="N74" s="3">
-        <v>46290.75</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="O74" s="3"/>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2585424</v>
+        <v>2586910</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="I75" s="3">
-        <v>46223.3927199074</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="J75" s="3">
-        <v>46234.4964930556</v>
+        <v>46230.4194212963</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="M75" s="3">
-        <v>46210.6427199074</v>
+        <v>46213.6245833333</v>
       </c>
       <c r="N75" s="3">
-        <v>46290.75</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="O75" s="3"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>2584638</v>
+        <v>2586651</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="I76" s="3">
-        <v>46213.4171527778</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="J76" s="3">
-        <v>46213.4090859607</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="K76" s="0" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M76" s="3">
-        <v>46209.5016203704</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="N76" s="3">
-        <v>46232.3874884259</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="O76" s="3"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>2584397</v>
+        <v>2586187</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I77" s="3">
-        <v>46212.6757175926</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I77" s="3"/>
       <c r="J77" s="3">
-        <v>46213.3741550926</v>
+        <v>46219.3850231481</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="M77" s="3">
-        <v>46209.3423842593</v>
-      </c>
-      <c r="N77" s="3">
-        <v>46212.6757175926</v>
-      </c>
+        <v>46211.7697337963</v>
+      </c>
+      <c r="N77" s="3"/>
       <c r="O77" s="3"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>2584167</v>
+        <v>2585888</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="I78" s="3">
-        <v>46246.7216435185</v>
+        <v>46217.4119907407</v>
       </c>
       <c r="J78" s="3">
-        <v>46247.4396759259</v>
+        <v>46217.5003587963</v>
       </c>
       <c r="K78" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M78" s="3">
-        <v>46206.6383101852</v>
+        <v>46211.4953240741</v>
       </c>
       <c r="N78" s="3">
-        <v>46246.7216435185</v>
+        <v>46290.75</v>
       </c>
       <c r="O78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2583950</v>
+        <v>2585424</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I79" s="3"/>
+        <v>75</v>
+      </c>
+      <c r="I79" s="3">
+        <v>46223.3927199074</v>
+      </c>
       <c r="J79" s="3">
-        <v>46273.4100925926</v>
+        <v>46234.4964930556</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="M79" s="3">
-        <v>46206.4623148148</v>
-      </c>
-      <c r="N79" s="3"/>
+        <v>46210.6427199074</v>
+      </c>
+      <c r="N79" s="3">
+        <v>46290.75</v>
+      </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>2583447</v>
+        <v>2584638</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="I80" s="3">
-        <v>46205.7916666667</v>
+        <v>46213.4171527778</v>
       </c>
       <c r="J80" s="3">
-        <v>46265.3645138889</v>
+        <v>46213.4090859607</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M80" s="3">
-        <v>46205.5752083333</v>
+        <v>46209.5016203704</v>
       </c>
       <c r="N80" s="3">
-        <v>46245.6724189815</v>
+        <v>46232.3874884259</v>
       </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>2583382</v>
+        <v>2584397</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="I81" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I81" s="3">
+        <v>46212.6757175926</v>
+      </c>
       <c r="J81" s="3">
-        <v>46279.4689699074</v>
+        <v>46213.3741550926</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="M81" s="3">
-        <v>46205.4905092593</v>
-      </c>
-      <c r="N81" s="3"/>
+        <v>46209.3423842593</v>
+      </c>
+      <c r="N81" s="3">
+        <v>46212.6757175926</v>
+      </c>
       <c r="O81" s="3"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>2582452</v>
+        <v>2584167</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I82" s="3">
-        <v>46244.4166666667</v>
+        <v>46246.7216435185</v>
       </c>
       <c r="J82" s="3">
-        <v>46204.7763078704</v>
+        <v>46247.4396759259</v>
       </c>
       <c r="K82" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="M82" s="3">
-        <v>46203.8250810185</v>
+        <v>46206.6383101852</v>
       </c>
       <c r="N82" s="3">
-        <v>46244.4166666667</v>
+        <v>46246.7216435185</v>
       </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>2582352</v>
+        <v>2583950</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I83" s="3">
-        <v>46244.340775463</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I83" s="3"/>
       <c r="J83" s="3">
-        <v>46204.7761805556</v>
+        <v>46273.4100925926</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="M83" s="3">
-        <v>46203.6741087963</v>
-      </c>
-      <c r="N83" s="3">
-        <v>46244.340775463</v>
-      </c>
+        <v>46206.4623148148</v>
+      </c>
+      <c r="N83" s="3"/>
       <c r="O83" s="3"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>2579299</v>
+        <v>2583447</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>166</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I84" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I84" s="3">
+        <v>46205.7916666667</v>
+      </c>
       <c r="J84" s="3">
-        <v>46204.3277777778</v>
+        <v>46265.3645138889</v>
       </c>
       <c r="K84" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="M84" s="3">
-        <v>46196.4165162037</v>
-      </c>
-      <c r="N84" s="3"/>
+        <v>46205.5752083333</v>
+      </c>
+      <c r="N84" s="3">
+        <v>46245.6724189815</v>
+      </c>
       <c r="O84" s="3"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>2576326</v>
+        <v>2583382</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="E85" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I85" s="3">
-        <v>46192.7916666667</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I85" s="3"/>
       <c r="J85" s="3">
-        <v>46230.6812731481</v>
+        <v>46293.3798726852</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="M85" s="3">
-        <v>46189.3995833333</v>
+        <v>46205.4905092593</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>2574153</v>
+        <v>2582452</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I86" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I86" s="3">
+        <v>46244.4166666667</v>
+      </c>
       <c r="J86" s="3">
-        <v>46204.3218402778</v>
+        <v>46204.7763078704</v>
       </c>
       <c r="K86" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L86" s="0" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="M86" s="3">
-        <v>46183.4711226852</v>
-      </c>
-      <c r="N86" s="3"/>
+        <v>46203.8250810185</v>
+      </c>
+      <c r="N86" s="3">
+        <v>46244.4166666667</v>
+      </c>
       <c r="O86" s="3"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>2572707</v>
+        <v>2582352</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F87" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G87" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="G87" s="0" t="s">
-        <v>171</v>
-      </c>
       <c r="H87" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I87" s="3">
-        <v>46219.3964814815</v>
+        <v>46244.340775463</v>
       </c>
       <c r="J87" s="3">
-        <v>46188.4629166667</v>
+        <v>46204.7761805556</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="M87" s="3">
-        <v>46178.7298148148</v>
+        <v>46203.6741087963</v>
       </c>
       <c r="N87" s="3">
-        <v>46219.3964814815</v>
+        <v>46244.340775463</v>
       </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>2570274</v>
+        <v>2579299</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E88" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I88" s="3"/>
       <c r="J88" s="3">
-        <v>46204.3220138889</v>
+        <v>46204.3277777778</v>
       </c>
       <c r="K88" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="M88" s="3">
-        <v>46171.6563773148</v>
+        <v>46196.4165162037</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>2562116</v>
+        <v>2576326</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="E89" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I89" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I89" s="3">
+        <v>46192.7916666667</v>
+      </c>
       <c r="J89" s="3">
-        <v>46160.7191666667</v>
+        <v>46230.6812731481</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="M89" s="3">
-        <v>46154.3432638889</v>
+        <v>46189.3995833333</v>
       </c>
       <c r="N89" s="3"/>
       <c r="O89" s="3"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2558553</v>
+        <v>2574153</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I90" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I90" s="3"/>
       <c r="J90" s="3">
-        <v>46154.5888773148</v>
+        <v>46204.3218402778</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="M90" s="3">
-        <v>46146.3561805556</v>
-      </c>
-      <c r="N90" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>46183.4711226852</v>
+      </c>
+      <c r="N90" s="3"/>
       <c r="O90" s="3"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>2556271</v>
+        <v>2572707</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="F91" s="0" t="s">
         <v>176</v>
@@ -4876,704 +4894,702 @@
         <v>177</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I91" s="3">
-        <v>46141.4297453704</v>
+        <v>46219.3964814815</v>
       </c>
       <c r="J91" s="3">
-        <v>46139.9871412037</v>
+        <v>46188.4629166667</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="M91" s="3">
-        <v>46139.471412037</v>
+        <v>46178.7298148148</v>
       </c>
       <c r="N91" s="3">
-        <v>46141.4901157407</v>
+        <v>46219.3964814815</v>
       </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>2556211</v>
+        <v>2570274</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I92" s="3">
-        <v>46150.6617476852</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I92" s="3"/>
       <c r="J92" s="3">
-        <v>46146.3663773148</v>
+        <v>46204.3220138889</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M92" s="3">
-        <v>46139.4325810185</v>
-      </c>
-      <c r="N92" s="3">
-        <v>46150.6617476852</v>
-      </c>
+        <v>46171.6563773148</v>
+      </c>
+      <c r="N92" s="3"/>
       <c r="O92" s="3"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>2556029</v>
+        <v>2562116</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I93" s="3">
-        <v>46150.5</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I93" s="3"/>
       <c r="J93" s="3">
-        <v>46146.401875</v>
+        <v>46160.7191666667</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M93" s="3">
-        <v>46138.757337963</v>
-      </c>
-      <c r="N93" s="3">
-        <v>46154.6616087963</v>
-      </c>
+        <v>46154.3432638889</v>
+      </c>
+      <c r="N93" s="3"/>
       <c r="O93" s="3"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>2554341</v>
+        <v>2558553</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I94" s="3">
-        <v>46136.3599768519</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="J94" s="3">
-        <v>46135.6585185185</v>
+        <v>46154.5888773148</v>
       </c>
       <c r="K94" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L94" s="0" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="M94" s="3">
-        <v>46134.4016435185</v>
+        <v>46146.3561805556</v>
       </c>
       <c r="N94" s="3">
-        <v>46136.3599768519</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="O94" s="3"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>2547638</v>
+        <v>2556271</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E95" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I95" s="3">
-        <v>46150.3473611111</v>
+        <v>46141.4297453704</v>
       </c>
       <c r="J95" s="3">
-        <v>46119.5010069444</v>
+        <v>46139.9871412037</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="M95" s="3">
-        <v>46114.4931944444</v>
+        <v>46139.471412037</v>
       </c>
       <c r="N95" s="3">
-        <v>46150.3473611111</v>
+        <v>46141.4901157407</v>
       </c>
       <c r="O95" s="3"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>2537054</v>
+        <v>2556211</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="I96" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="J96" s="3">
-        <v>46090.3698263889</v>
+        <v>46146.3663773148</v>
       </c>
       <c r="K96" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L96" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M96" s="3">
-        <v>46087.5797569444</v>
+        <v>46139.4325810185</v>
       </c>
       <c r="N96" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="O96" s="3"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>2531696</v>
+        <v>2556029</v>
       </c>
       <c r="B97" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F97" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="C97" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="D97" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="E97" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F97" s="0" t="s">
-        <v>62</v>
-      </c>
       <c r="G97" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I97" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="I97" s="3">
+        <v>46150.5</v>
+      </c>
       <c r="J97" s="3">
-        <v>46204.3216782407</v>
+        <v>46146.401875</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="M97" s="3">
-        <v>46076.5833912037</v>
-      </c>
-      <c r="N97" s="3"/>
+        <v>46138.757337963</v>
+      </c>
+      <c r="N97" s="3">
+        <v>46154.6616087963</v>
+      </c>
       <c r="O97" s="3"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>2530739</v>
+        <v>2554341</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="C98" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F98" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="G98" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="D98" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="E98" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F98" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="G98" s="0" t="s">
-        <v>186</v>
-      </c>
       <c r="H98" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="I98" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="I98" s="3">
+        <v>46136.3599768519</v>
+      </c>
       <c r="J98" s="3">
-        <v>46218.6914940625</v>
+        <v>46135.6585185185</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="M98" s="3">
-        <v>46072.6973148148</v>
-      </c>
-      <c r="N98" s="3"/>
+        <v>46134.4016435185</v>
+      </c>
+      <c r="N98" s="3">
+        <v>46136.3599768519</v>
+      </c>
       <c r="O98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>2529639</v>
+        <v>2547638</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I99" s="3">
-        <v>46083.3430902778</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="J99" s="3">
-        <v>46072.6891666667</v>
+        <v>46119.5010069444</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="M99" s="3">
-        <v>46069.5930902778</v>
+        <v>46114.4931944444</v>
       </c>
       <c r="N99" s="3">
-        <v>46083.3430902778</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="O99" s="3"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>2529591</v>
+        <v>2537054</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I100" s="3">
-        <v>46108.5968055556</v>
+        <v>46093.4339236111</v>
       </c>
       <c r="J100" s="3">
-        <v>46126.6875</v>
+        <v>46090.3698263889</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L100" s="0" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M100" s="3">
-        <v>46069.4509722222</v>
+        <v>46087.5797569444</v>
       </c>
       <c r="N100" s="3">
-        <v>46108.5968055556</v>
+        <v>46093.4339236111</v>
       </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>2528858</v>
+        <v>2531696</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F101" s="0" t="s">
         <v>18</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I101" s="3">
-        <v>46107.3861458333</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I101" s="3"/>
       <c r="J101" s="3">
-        <v>46087.6277662037</v>
+        <v>46204.3216782407</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="M101" s="3">
-        <v>46065.7194791667</v>
-      </c>
-      <c r="N101" s="3">
-        <v>46107.3861458333</v>
-      </c>
+        <v>46076.5833912037</v>
+      </c>
+      <c r="N101" s="3"/>
       <c r="O101" s="3"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>2525312</v>
+        <v>2530739</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>46</v>
+        <v>189</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I102" s="3">
-        <v>46070.5877314815</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="I102" s="3"/>
       <c r="J102" s="3">
-        <v>46062.7587037037</v>
+        <v>46218.6914940625</v>
       </c>
       <c r="K102" s="0" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="L102" s="0" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M102" s="3">
-        <v>46058.3585648148</v>
-      </c>
-      <c r="N102" s="3">
-        <v>46070.5877314815</v>
-      </c>
+        <v>46072.6973148148</v>
+      </c>
+      <c r="N102" s="3"/>
       <c r="O102" s="3"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>2525272</v>
+        <v>2529639</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>191</v>
+        <v>60</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>191</v>
+        <v>60</v>
       </c>
       <c r="D103" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F103" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="G103" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="E103" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F103" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="G103" s="0" t="s">
-        <v>193</v>
-      </c>
       <c r="H103" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I103" s="3">
-        <v>46203.7916666667</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="J103" s="3">
-        <v>46126.7441782407</v>
+        <v>46072.6891666667</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="M103" s="3">
-        <v>46058.2883101852</v>
-      </c>
-      <c r="N103" s="3"/>
+        <v>46069.5930902778</v>
+      </c>
+      <c r="N103" s="3">
+        <v>46083.3430902778</v>
+      </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>2524577</v>
+        <v>2529591</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="I104" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I104" s="3">
+        <v>46108.5968055556</v>
+      </c>
       <c r="J104" s="3">
-        <v>46267.4298180903</v>
+        <v>46126.6875</v>
       </c>
       <c r="K104" s="0" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="M104" s="3">
-        <v>46056.697349537</v>
-      </c>
-      <c r="N104" s="3"/>
+        <v>46069.4509722222</v>
+      </c>
+      <c r="N104" s="3">
+        <v>46108.5968055556</v>
+      </c>
       <c r="O104" s="3"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>2524373</v>
+        <v>2528858</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I105" s="3">
-        <v>46087.3854513889</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="J105" s="3">
-        <v>46056.6543865741</v>
+        <v>46087.6277662037</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="M105" s="3">
-        <v>46056.5937847222</v>
+        <v>46065.7194791667</v>
       </c>
       <c r="N105" s="3">
-        <v>46087.3854513889</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="O105" s="3"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>2524062</v>
+        <v>2525312</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I106" s="3">
-        <v>46057.7412615741</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="J106" s="3">
-        <v>46056.6210300926</v>
+        <v>46062.7587037037</v>
       </c>
       <c r="K106" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L106" s="0" t="s">
         <v>29</v>
       </c>
       <c r="M106" s="3">
-        <v>46056.3662615741</v>
+        <v>46058.3585648148</v>
       </c>
       <c r="N106" s="3">
-        <v>46057.7412615741</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="O106" s="3"/>
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>2523635</v>
+        <v>2525272</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>35</v>
+        <v>197</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F107" s="0" t="s">
         <v>18</v>
@@ -5582,1452 +5598,1456 @@
         <v>198</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I107" s="3">
-        <v>46059.4164236111</v>
+        <v>46203.7916666667</v>
       </c>
       <c r="J107" s="3">
-        <v>46055.6034837963</v>
+        <v>46126.7441782407</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="M107" s="3">
-        <v>46055.4997569444</v>
-      </c>
-      <c r="N107" s="3">
-        <v>46059.4164236111</v>
-      </c>
+        <v>46058.2883101852</v>
+      </c>
+      <c r="N107" s="3"/>
       <c r="O107" s="3"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>2523602</v>
+        <v>2524577</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>199</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I108" s="3">
-        <v>46093.6246643519</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="I108" s="3"/>
       <c r="J108" s="3">
-        <v>46056.5784027778</v>
+        <v>46267.4298180903</v>
       </c>
       <c r="K108" s="0" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="L108" s="0" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="M108" s="3">
-        <v>46055.4788310185</v>
-      </c>
-      <c r="N108" s="3">
-        <v>46093.6246643519</v>
-      </c>
+        <v>46056.697349537</v>
+      </c>
+      <c r="N108" s="3"/>
       <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>2521645</v>
+        <v>2524373</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="I109" s="3">
-        <v>46062.5</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="J109" s="3">
-        <v>46050.3426763542</v>
+        <v>46056.6543865741</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="M109" s="3">
-        <v>46049.7714236111</v>
-      </c>
-      <c r="N109" s="3"/>
+        <v>46056.5937847222</v>
+      </c>
+      <c r="N109" s="3">
+        <v>46087.3854513889</v>
+      </c>
       <c r="O109" s="3"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>2521079</v>
+        <v>2524062</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I110" s="3">
-        <v>46052.6666666667</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="J110" s="3">
-        <v>46056.6197800926</v>
+        <v>46056.6210300926</v>
       </c>
       <c r="K110" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L110" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M110" s="3">
-        <v>46048.7684490741</v>
+        <v>46056.3662615741</v>
       </c>
       <c r="N110" s="3">
-        <v>46061.6309722222</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="O110" s="3"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>2520048</v>
+        <v>2523635</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I111" s="3">
-        <v>46057.5</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="J111" s="3">
-        <v>46052.5774305556</v>
+        <v>46055.6034837963</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M111" s="3">
-        <v>46045.3325578704</v>
+        <v>46055.4997569444</v>
       </c>
       <c r="N111" s="3">
-        <v>46057.5</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="O111" s="3"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>2519904</v>
+        <v>2523602</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I112" s="3">
-        <v>46084.7217939815</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="J112" s="3">
-        <v>46044.7413888889</v>
+        <v>46056.5784027778</v>
       </c>
       <c r="K112" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="M112" s="3">
-        <v>46044.6384606482</v>
+        <v>46055.4788310185</v>
       </c>
       <c r="N112" s="3">
-        <v>46084.7217939815</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="O112" s="3"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>2519523</v>
+        <v>2521645</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="I113" s="3">
-        <v>46076.5902777778</v>
+        <v>46062.5</v>
       </c>
       <c r="J113" s="3">
-        <v>46048.4589814815</v>
+        <v>46050.3426763542</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="M113" s="3">
-        <v>46043.7362847222</v>
-      </c>
-      <c r="N113" s="3">
-        <v>46077.380775463</v>
-      </c>
+        <v>46049.7714236111</v>
+      </c>
+      <c r="N113" s="3"/>
       <c r="O113" s="3"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>2519383</v>
+        <v>2521079</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I114" s="3">
-        <v>46076.399224537</v>
+        <v>46052.6666666667</v>
       </c>
       <c r="J114" s="3">
-        <v>46048.4599305556</v>
+        <v>46056.6197800926</v>
       </c>
       <c r="K114" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L114" s="0" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="M114" s="3">
-        <v>46043.6075578704</v>
+        <v>46048.7684490741</v>
       </c>
       <c r="N114" s="3">
-        <v>46076.399224537</v>
+        <v>46061.6309722222</v>
       </c>
       <c r="O114" s="3"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>2519284</v>
+        <v>2520048</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="I115" s="3">
-        <v>46049.3982986111</v>
+        <v>46057.5</v>
       </c>
       <c r="J115" s="3">
-        <v>46043.742337963</v>
+        <v>46052.5774305556</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M115" s="3">
-        <v>46043.4816319444</v>
+        <v>46045.3325578704</v>
       </c>
       <c r="N115" s="3">
-        <v>46049.3982986111</v>
+        <v>46057.5</v>
       </c>
       <c r="O115" s="3"/>
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>2518650</v>
+        <v>2519904</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E116" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I116" s="3">
-        <v>46072.3536921296</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="J116" s="3">
-        <v>46043.8185648148</v>
+        <v>46044.7413888889</v>
       </c>
       <c r="K116" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L116" s="0" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="M116" s="3">
-        <v>46042.3536921296</v>
+        <v>46044.6384606482</v>
       </c>
       <c r="N116" s="3">
-        <v>46080.437025463</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="O116" s="3"/>
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>2513117</v>
+        <v>2519523</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>176</v>
+        <v>71</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I117" s="3">
-        <v>46031.4922800926</v>
+        <v>46076.5902777778</v>
       </c>
       <c r="J117" s="3">
-        <v>46028.3500347222</v>
+        <v>46048.4589814815</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="M117" s="3">
-        <v>46027.6381134259</v>
+        <v>46043.7362847222</v>
       </c>
       <c r="N117" s="3">
-        <v>46031.4922800926</v>
+        <v>46077.380775463</v>
       </c>
       <c r="O117" s="3"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>2512883</v>
+        <v>2519383</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I118" s="3">
-        <v>46037.6340972222</v>
+        <v>46076.399224537</v>
       </c>
       <c r="J118" s="3">
-        <v>46129.4199421296</v>
+        <v>46048.4599305556</v>
       </c>
       <c r="K118" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L118" s="0" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="M118" s="3">
-        <v>46027.4049305556</v>
+        <v>46043.6075578704</v>
       </c>
       <c r="N118" s="3">
-        <v>46141.6335300926</v>
+        <v>46076.399224537</v>
       </c>
       <c r="O118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>2512542</v>
+        <v>2519284</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I119" s="3">
-        <v>46036.5</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="J119" s="3">
-        <v>46024.5900925926</v>
+        <v>46043.742337963</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M119" s="3">
-        <v>46022.6836342593</v>
+        <v>46043.4816319444</v>
       </c>
       <c r="N119" s="3">
-        <v>46036.5</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="O119" s="3"/>
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <v>2512541</v>
+        <v>2518650</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I120" s="3">
-        <v>46036.5</v>
+        <v>46072.3536921296</v>
       </c>
       <c r="J120" s="3">
-        <v>46022.7128356481</v>
+        <v>46043.8185648148</v>
       </c>
       <c r="K120" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L120" s="0" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M120" s="3">
-        <v>46022.6762615741</v>
+        <v>46042.3536921296</v>
       </c>
       <c r="N120" s="3">
-        <v>46036.5</v>
+        <v>46080.437025463</v>
       </c>
       <c r="O120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <v>2509014</v>
+        <v>2513117</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I121" s="3">
-        <v>46044.7250578704</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="J121" s="3">
-        <v>46022.6138541667</v>
+        <v>46028.3500347222</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="M121" s="3">
-        <v>46008.454224537</v>
+        <v>46027.6381134259</v>
       </c>
       <c r="N121" s="3">
-        <v>46045.4708564815</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="O121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <v>2506714</v>
+        <v>2512883</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I122" s="3">
-        <v>46038.7073032407</v>
+        <v>46037.6340972222</v>
       </c>
       <c r="J122" s="3">
-        <v>46044.7372337963</v>
+        <v>46129.4199421296</v>
       </c>
       <c r="K122" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L122" s="0" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="M122" s="3">
-        <v>46002.4364699074</v>
+        <v>46027.4049305556</v>
       </c>
       <c r="N122" s="3">
-        <v>46038.7073032407</v>
+        <v>46141.6335300926</v>
       </c>
       <c r="O122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <v>2506599</v>
+        <v>2512542</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I123" s="3">
-        <v>46037.61375</v>
+        <v>46036.5</v>
       </c>
       <c r="J123" s="3">
-        <v>46052.3252083333</v>
+        <v>46024.5900925926</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="M123" s="3">
-        <v>46002.3429166667</v>
+        <v>46022.6836342593</v>
       </c>
       <c r="N123" s="3">
-        <v>46037.61375</v>
+        <v>46036.5</v>
       </c>
       <c r="O123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <v>2506311</v>
+        <v>2512541</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>214</v>
+        <v>114</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>214</v>
+        <v>114</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>215</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I124" s="3">
-        <v>46013.7291666667</v>
+        <v>46036.5</v>
       </c>
       <c r="J124" s="3">
-        <v>46013.461875</v>
+        <v>46022.7128356481</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L124" s="0" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="M124" s="3">
-        <v>46001.5219328704</v>
+        <v>46022.6762615741</v>
       </c>
       <c r="N124" s="3">
-        <v>46013.7291666667</v>
+        <v>46036.5</v>
       </c>
       <c r="O124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <v>2506102</v>
+        <v>2509014</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>216</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I125" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I125" s="3">
+        <v>46044.7250578704</v>
+      </c>
       <c r="J125" s="3">
-        <v>46241.5032638889</v>
+        <v>46022.6138541667</v>
       </c>
       <c r="K125" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M125" s="3">
-        <v>46001.3800578704</v>
-      </c>
-      <c r="N125" s="3"/>
+        <v>46008.454224537</v>
+      </c>
+      <c r="N125" s="3">
+        <v>46045.4708564815</v>
+      </c>
       <c r="O125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <v>2502589</v>
+        <v>2506714</v>
       </c>
       <c r="B126" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="C126" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D126" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="E126" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="F126" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="G126" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="C126" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="D126" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="E126" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="F126" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="G126" s="0" t="s">
-        <v>218</v>
-      </c>
       <c r="H126" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I126" s="3">
-        <v>46029.6634375</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="J126" s="3">
-        <v>46014.6931018519</v>
+        <v>46044.7372337963</v>
       </c>
       <c r="K126" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="M126" s="3">
-        <v>45993.3791087963</v>
+        <v>46002.4364699074</v>
       </c>
       <c r="N126" s="3">
-        <v>46029.6634375</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="O126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <v>2502438</v>
+        <v>2506599</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>185</v>
+        <v>128</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I127" s="3">
-        <v>46037.3801388889</v>
+        <v>46037.61375</v>
       </c>
       <c r="J127" s="3">
-        <v>45996.4823032407</v>
+        <v>46052.3252083333</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="M127" s="3">
-        <v>45992.7134722222</v>
+        <v>46002.3429166667</v>
       </c>
       <c r="N127" s="3">
-        <v>46037.3801388889</v>
+        <v>46037.61375</v>
       </c>
       <c r="O127" s="3"/>
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <v>2501349</v>
+        <v>2506311</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>220</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I128" s="3">
-        <v>46069.7381944444</v>
+        <v>46013.7291666667</v>
       </c>
       <c r="J128" s="3">
-        <v>46069.3651388889</v>
+        <v>46013.461875</v>
       </c>
       <c r="K128" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L128" s="0" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="M128" s="3">
-        <v>45989.0365856482</v>
+        <v>46001.5219328704</v>
       </c>
       <c r="N128" s="3">
-        <v>46069.7381944444</v>
+        <v>46013.7291666667</v>
       </c>
       <c r="O128" s="3"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <v>2500635</v>
+        <v>2506102</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>221</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I129" s="3">
-        <v>46024.4633796296</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I129" s="3"/>
       <c r="J129" s="3">
-        <v>46027.3611111111</v>
+        <v>46241.5032638889</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="M129" s="3">
-        <v>45987.671712963</v>
-      </c>
-      <c r="N129" s="3">
-        <v>46024.4633796296</v>
-      </c>
+        <v>46001.3800578704</v>
+      </c>
+      <c r="N129" s="3"/>
       <c r="O129" s="3"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <v>2498066</v>
+        <v>2502589</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I130" s="3">
-        <v>46073.7916666667</v>
+        <v>46029.6634375</v>
       </c>
       <c r="J130" s="3">
-        <v>46126.6953240741</v>
+        <v>46014.6931018519</v>
       </c>
       <c r="K130" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L130" s="0" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="M130" s="3">
-        <v>45979.750162037</v>
-      </c>
-      <c r="N130" s="3"/>
+        <v>45993.3791087963</v>
+      </c>
+      <c r="N130" s="3">
+        <v>46029.6634375</v>
+      </c>
       <c r="O130" s="3"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <v>2494282</v>
+        <v>2502438</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>223</v>
+        <v>24</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>224</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I131" s="3">
-        <v>45986.48125</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="J131" s="3">
-        <v>45988.567025463</v>
+        <v>45996.4823032407</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="M131" s="3">
-        <v>45971.4792824074</v>
+        <v>45992.7134722222</v>
       </c>
       <c r="N131" s="3">
-        <v>45986.4815625</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="O131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <v>2494179</v>
+        <v>2501349</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="E132" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="G132" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="F132" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="G132" s="0" t="s">
-        <v>227</v>
-      </c>
       <c r="H132" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I132" s="3">
-        <v>46002.675775463</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="J132" s="3">
-        <v>46044.7370486111</v>
+        <v>46069.3651388889</v>
       </c>
       <c r="K132" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L132" s="0" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="M132" s="3">
-        <v>45971.4049421296</v>
+        <v>45989.0365856482</v>
       </c>
       <c r="N132" s="3">
-        <v>46002.675775463</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="O132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <v>2490911</v>
+        <v>2500635</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>228</v>
+        <v>24</v>
       </c>
       <c r="E133" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="I133" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I133" s="3">
+        <v>46024.4633796296</v>
+      </c>
       <c r="J133" s="3">
-        <v>46182.7633796296</v>
+        <v>46027.3611111111</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M133" s="3">
-        <v>45961.5760300926</v>
-      </c>
-      <c r="N133" s="3"/>
+        <v>45987.671712963</v>
+      </c>
+      <c r="N133" s="3">
+        <v>46024.4633796296</v>
+      </c>
       <c r="O133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <v>2490185</v>
+        <v>2498066</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="E134" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I134" s="3">
-        <v>46203.7916666667</v>
+        <v>46073.7916666667</v>
       </c>
       <c r="J134" s="3">
-        <v>46051.4836111111</v>
+        <v>46126.6953240741</v>
       </c>
       <c r="K134" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L134" s="0" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M134" s="3">
-        <v>45960.3928819444</v>
+        <v>45979.750162037</v>
       </c>
       <c r="N134" s="3"/>
       <c r="O134" s="3"/>
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <v>2489016</v>
+        <v>2494282</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D135" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E135" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F135" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="G135" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="H135" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I135" s="3">
+        <v>45986.48125</v>
+      </c>
+      <c r="J135" s="3">
+        <v>45988.567025463</v>
+      </c>
+      <c r="K135" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="L135" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="E135" s="0" t="s">
-        <v>231</v>
-      </c>
-      <c r="F135" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="G135" s="0" t="s">
-        <v>232</v>
-      </c>
-      <c r="H135" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I135" s="3"/>
-      <c r="J135" s="3">
-        <v>45958.3906481481</v>
-      </c>
-      <c r="K135" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="L135" s="0" t="s">
-        <v>93</v>
-      </c>
       <c r="M135" s="3">
-        <v>45957.7253009259</v>
-      </c>
-      <c r="N135" s="3"/>
+        <v>45971.4792824074</v>
+      </c>
+      <c r="N135" s="3">
+        <v>45986.4815625</v>
+      </c>
       <c r="O135" s="3"/>
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <v>2485386</v>
+        <v>2494179</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>228</v>
+        <v>129</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>62</v>
+        <v>230</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="I136" s="3">
-        <v>46386.7916666667</v>
+        <v>46002.675775463</v>
       </c>
       <c r="J136" s="3">
-        <v>46182.7639236111</v>
+        <v>46044.7370486111</v>
       </c>
       <c r="K136" s="0" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="L136" s="0" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M136" s="3">
-        <v>45947.7000115741</v>
-      </c>
-      <c r="N136" s="3"/>
+        <v>45971.4049421296</v>
+      </c>
+      <c r="N136" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="O136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <v>2483420</v>
+        <v>2490911</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E137" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="I137" s="3"/>
       <c r="J137" s="3">
-        <v>46140.3843518519</v>
+        <v>46182.7633796296</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="M137" s="3">
-        <v>45944.6603819444</v>
+        <v>45961.5760300926</v>
       </c>
       <c r="N137" s="3"/>
       <c r="O137" s="3"/>
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <v>2474606</v>
+        <v>2490185</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>121</v>
+        <v>196</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>121</v>
+        <v>196</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="E138" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I138" s="3">
-        <v>45952.4506944444</v>
+        <v>46203.7916666667</v>
       </c>
       <c r="J138" s="3">
-        <v>45966.4450925926</v>
+        <v>46051.4836111111</v>
       </c>
       <c r="K138" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L138" s="0" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="M138" s="3">
-        <v>45924.4486921296</v>
-      </c>
-      <c r="N138" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>45960.3928819444</v>
+      </c>
+      <c r="N138" s="3"/>
       <c r="O138" s="3"/>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>2470122</v>
+        <v>2489016</v>
       </c>
       <c r="B139" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D139" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E139" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="F139" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="G139" s="0" t="s">
         <v>236</v>
       </c>
-      <c r="C139" s="0" t="s">
-        <v>236</v>
-      </c>
-      <c r="D139" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="E139" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F139" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="G139" s="0" t="s">
-        <v>237</v>
-      </c>
       <c r="H139" s="0" t="s">
-        <v>238</v>
+        <v>36</v>
       </c>
       <c r="I139" s="3"/>
       <c r="J139" s="3">
-        <v>46204.3270601852</v>
+        <v>45958.3906481481</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="M139" s="3">
-        <v>45912.5572222222</v>
+        <v>45957.7253009259</v>
       </c>
       <c r="N139" s="3"/>
       <c r="O139" s="3"/>
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>2463515</v>
+        <v>2485386</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E140" s="0" t="s">
         <v>17</v>
@@ -7036,367 +7056,537 @@
         <v>18</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I140" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="I140" s="3">
+        <v>46386.7916666667</v>
+      </c>
       <c r="J140" s="3">
-        <v>45910.4755555556</v>
+        <v>46182.7639236111</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="L140" s="0" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="M140" s="3">
-        <v>45897.4218865741</v>
+        <v>45947.7000115741</v>
       </c>
       <c r="N140" s="3"/>
       <c r="O140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>2461703</v>
+        <v>2483420</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>238</v>
+        <v>119</v>
       </c>
       <c r="I141" s="3"/>
       <c r="J141" s="3">
-        <v>46003.3706828704</v>
+        <v>46140.3843518519</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="M141" s="3">
-        <v>45894.4525347222</v>
+        <v>45944.6603819444</v>
       </c>
       <c r="N141" s="3"/>
       <c r="O141" s="3"/>
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <v>2459339</v>
+        <v>2474606</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>228</v>
+        <v>33</v>
       </c>
       <c r="E142" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="I142" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="I142" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="J142" s="3">
-        <v>46140.3839930556</v>
+        <v>45966.4450925926</v>
       </c>
       <c r="K142" s="0" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="L142" s="0" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="M142" s="3">
-        <v>45887.7442361111</v>
-      </c>
-      <c r="N142" s="3"/>
+        <v>45924.4486921296</v>
+      </c>
+      <c r="N142" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="O142" s="3"/>
     </row>
     <row r="143">
       <c r="A143" s="2">
-        <v>2456538</v>
+        <v>2470122</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>121</v>
+        <v>240</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>121</v>
+        <v>240</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>90</v>
+        <v>232</v>
       </c>
       <c r="E143" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>58</v>
+        <v>242</v>
       </c>
       <c r="I143" s="3"/>
       <c r="J143" s="3">
-        <v>46126.7428356481</v>
+        <v>46204.3270601852</v>
       </c>
       <c r="K143" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L143" s="0" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="M143" s="3">
-        <v>45880.6643055556</v>
+        <v>45912.5572222222</v>
       </c>
       <c r="N143" s="3"/>
       <c r="O143" s="3"/>
     </row>
     <row r="144">
       <c r="A144" s="2">
-        <v>2449811</v>
+        <v>2463515</v>
       </c>
       <c r="B144" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D144" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F144" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G144" s="0" t="s">
         <v>244</v>
       </c>
-      <c r="C144" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="D144" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="E144" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="F144" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="G144" s="0" t="s">
-        <v>245</v>
-      </c>
       <c r="H144" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I144" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I144" s="3"/>
       <c r="J144" s="3">
-        <v>45870.3628819444</v>
+        <v>45910.4755555556</v>
       </c>
       <c r="K144" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L144" s="0" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M144" s="3">
-        <v>45862.6188888889</v>
-      </c>
-      <c r="N144" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>45897.4218865741</v>
+      </c>
+      <c r="N144" s="3"/>
       <c r="O144" s="3"/>
     </row>
     <row r="145">
       <c r="A145" s="2">
-        <v>2442028</v>
+        <v>2461703</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>90</v>
+        <v>232</v>
       </c>
       <c r="E145" s="0" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>58</v>
+        <v>242</v>
       </c>
       <c r="I145" s="3"/>
       <c r="J145" s="3">
-        <v>46126.7431134259</v>
+        <v>46003.3706828704</v>
       </c>
       <c r="K145" s="0" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="L145" s="0" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="M145" s="3">
-        <v>45842.317025463</v>
+        <v>45894.4525347222</v>
       </c>
       <c r="N145" s="3"/>
       <c r="O145" s="3"/>
     </row>
     <row r="146">
       <c r="A146" s="2">
-        <v>2439691</v>
+        <v>2459339</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="E146" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="F146" s="0" t="s">
+        <v>139</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I146" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="I146" s="3"/>
       <c r="J146" s="3">
-        <v>45838.6211342593</v>
+        <v>46140.3839930556</v>
       </c>
       <c r="K146" s="0" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="L146" s="0" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="M146" s="3">
-        <v>45838.3761921296</v>
-      </c>
-      <c r="N146" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>45887.7442361111</v>
+      </c>
+      <c r="N146" s="3"/>
       <c r="O146" s="3"/>
     </row>
     <row r="147">
       <c r="A147" s="2">
-        <v>2437239</v>
+        <v>2456538</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>249</v>
+        <v>128</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>250</v>
+        <v>128</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I147" s="3">
-        <v>45870.3600462963</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I147" s="3"/>
       <c r="J147" s="3">
-        <v>45841.7026091435</v>
+        <v>46126.7428356481</v>
       </c>
       <c r="K147" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L147" s="0" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="M147" s="3">
-        <v>45831.6933796296</v>
-      </c>
-      <c r="N147" s="3">
-        <v>45870.3600462963</v>
-      </c>
+        <v>45880.6643055556</v>
+      </c>
+      <c r="N147" s="3"/>
       <c r="O147" s="3"/>
     </row>
     <row r="148">
       <c r="A148" s="2">
+        <v>2449811</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="C148" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="G148" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="H148" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I148" s="3">
+        <v>45875.3688888889</v>
+      </c>
+      <c r="J148" s="3">
+        <v>45870.3628819444</v>
+      </c>
+      <c r="K148" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="L148" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M148" s="3">
+        <v>45862.6188888889</v>
+      </c>
+      <c r="N148" s="3">
+        <v>45875.3688888889</v>
+      </c>
+      <c r="O148" s="3"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2">
+        <v>2442028</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="C149" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="D149" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E149" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F149" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G149" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="H149" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I149" s="3"/>
+      <c r="J149" s="3">
+        <v>46126.7431134259</v>
+      </c>
+      <c r="K149" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="L149" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M149" s="3">
+        <v>45842.317025463</v>
+      </c>
+      <c r="N149" s="3"/>
+      <c r="O149" s="3"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2">
+        <v>2439691</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="C150" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D150" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E150" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="G150" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="H150" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I150" s="3">
+        <v>45852.3770833333</v>
+      </c>
+      <c r="J150" s="3">
+        <v>45838.6211342593</v>
+      </c>
+      <c r="K150" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="L150" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="M150" s="3">
+        <v>45838.3761921296</v>
+      </c>
+      <c r="N150" s="3">
+        <v>45852.3770833333</v>
+      </c>
+      <c r="O150" s="3"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2">
+        <v>2437239</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="C151" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="D151" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E151" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="F151" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="G151" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="H151" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I151" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="J151" s="3">
+        <v>45841.7026091435</v>
+      </c>
+      <c r="K151" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="L151" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="M151" s="3">
+        <v>45831.6933796296</v>
+      </c>
+      <c r="N151" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="O151" s="3"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2">
         <v>2436707</v>
       </c>
-      <c r="B148" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="C148" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="D148" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="E148" s="0" t="s">
+      <c r="B152" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="C152" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="D152" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E152" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="F148" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G148" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="H148" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I148" s="3">
+      <c r="F152" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G152" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="H152" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I152" s="3">
         <v>45835.7284722222</v>
       </c>
-      <c r="J148" s="3">
+      <c r="J152" s="3">
         <v>46126.7436921296</v>
       </c>
-      <c r="K148" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="L148" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="M148" s="3">
+      <c r="K152" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="L152" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M152" s="3">
         <v>45828.8276273148</v>
       </c>
-      <c r="N148" s="3">
+      <c r="N152" s="3">
         <v>45835.7288773148</v>
       </c>
-      <c r="O148" s="3"/>
+      <c r="O152" s="3"/>
     </row>
   </sheetData>
   <headerFooter/>

--- a/Solicitacoes.xlsx
+++ b/Solicitacoes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
   <si>
     <t>Protocolo</t>
   </si>
@@ -59,36 +59,66 @@
     <t>Prazo desejado</t>
   </si>
   <si>
+    <t>COMPESAPREV.JULIA</t>
+  </si>
+  <si>
+    <t>CORRECAO</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
+    <t>HOMOLOGAÇÃO - Atualização do ambiente de homologação para a release 3.65.26</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Suporte nível II</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>HELPDESK - CUIDAR</t>
+  </si>
+  <si>
+    <t>Atendimento</t>
+  </si>
+  <si>
+    <t>E-mail para beneficiário sem detalhamento.</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>BCON</t>
+  </si>
+  <si>
+    <t>Autorização</t>
+  </si>
+  <si>
+    <t>Eventos autorizados automaticamente ficam "Em análise" no Conecta até finalizar a regulação.</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>COMPESAPREV.NIECIA</t>
   </si>
   <si>
-    <t>CORRECAO</t>
-  </si>
-  <si>
-    <t>AG</t>
-  </si>
-  <si>
     <t>Controle Financeiro</t>
   </si>
   <si>
     <t>Erro na geração da limitação de cobrança de PF para o grupo Exames e Terapias</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
-    <t>Suporte nível II</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>ALEXIA.SANTOS</t>
   </si>
   <si>
-    <t>HELPDESK - CUIDAR</t>
-  </si>
-  <si>
     <t>Processamento de Contas</t>
   </si>
   <si>
@@ -101,7 +131,7 @@
     <t>Cliente</t>
   </si>
   <si>
-    <t>3</t>
+    <t>Niécia Morais</t>
   </si>
   <si>
     <t>Códigos folhas gerados errados com mudança de módulo.</t>
@@ -131,270 +161,252 @@
     <t>6</t>
   </si>
   <si>
-    <t>COMPESAPREV.JULIA</t>
-  </si>
-  <si>
-    <t>ADM</t>
-  </si>
-  <si>
     <t>AG - Erro ao importar Tabela Genérica (Aguardando Processamento)</t>
   </si>
   <si>
+    <t>Adm Operadora</t>
+  </si>
+  <si>
+    <t>CON - Impossibilidade adiconar corpo clínico</t>
+  </si>
+  <si>
+    <t>MOBE</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APP -  Erro no servidor / buscar dados</t>
+  </si>
+  <si>
+    <t>ROGERIO.ALMEIDA</t>
+  </si>
+  <si>
+    <t>ANS</t>
+  </si>
+  <si>
+    <t>Critica para gerar XML na Rotina Monitoramento TISS</t>
+  </si>
+  <si>
+    <t>INSTABILIDADE MÓDULOS</t>
+  </si>
+  <si>
+    <t>Faturamento</t>
+  </si>
+  <si>
+    <t>Guia não disponível para execução de eventos por outros prestadores</t>
+  </si>
+  <si>
+    <t>Plataforma Lean</t>
+  </si>
+  <si>
+    <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
+  </si>
+  <si>
+    <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
+  </si>
+  <si>
+    <t>CONECTA - XML não sai do estado de "Em Processamento"</t>
+  </si>
+  <si>
+    <t>ANA.GOLDIM</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- Conecta- Erro na solicitação dos procedimentos.</t>
+  </si>
+  <si>
+    <t>Agendamentos</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- AG- AGENDAMENTO com erro Módulo de Regulação: Enviar mensagens Lean e Integracao Iris</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>CONECTA - Erro na execução de guias | pop-up e bloqueio por biometria</t>
+  </si>
+  <si>
+    <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
+  </si>
+  <si>
+    <t>Aguardando Revisão de código</t>
+  </si>
+  <si>
+    <t>Prestadores</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO NOME PRESTADOR</t>
+  </si>
+  <si>
+    <t>Configurações do Sistema</t>
+  </si>
+  <si>
+    <t>Ajuste no tempo de sessão ativa (timeout) do sistema Lean.</t>
+  </si>
+  <si>
+    <t>Correção – CompesaPrev – Erro de Geração do Código de Barras e Linha Digitável</t>
+  </si>
+  <si>
+    <t>COMPESAPREV-CONECTA- Eventos negados, com recibo autorizado</t>
+  </si>
+  <si>
+    <t>Erro no faturamento de pagamentos prestadores</t>
+  </si>
+  <si>
+    <t>Dúvida sobre o local para salvar/exportar a Guia Executada no Portal do Prestador</t>
+  </si>
+  <si>
+    <t>Histórico financeiro sem a informação individual de todos os beneficiários</t>
+  </si>
+  <si>
+    <t>PORTAL</t>
+  </si>
+  <si>
+    <t>Portal não envia e-mails, recuperação de senha e processos parados desde 04/09</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- AG- PROD- Agendamento Regulacao travado</t>
+  </si>
+  <si>
+    <t>Processos</t>
+  </si>
+  <si>
+    <t>Lean / AG (Integração e guias travadas)</t>
+  </si>
+  <si>
+    <t>Beneficiários</t>
+  </si>
+  <si>
+    <t>Erro de divergência de cadastro entre o AG e o LEAN</t>
+  </si>
+  <si>
+    <t>MOBE | Erro no servidor ao tentar logar.</t>
+  </si>
+  <si>
+    <t>Extrato de Utilização com valores de coparticipações sem a limitação de PF e antes do faturamento ser concluído</t>
+  </si>
+  <si>
+    <t>Erro ao buscar documento/relatório na Consulta de Autorizações (App)</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Compesaprev- Conecta- Erro na autorização</t>
+  </si>
+  <si>
+    <t>CENTRAL ATENDIMENTO</t>
+  </si>
+  <si>
+    <t>Transações</t>
+  </si>
+  <si>
+    <t>Falha na integração entre AG Web e Central de Atendimento</t>
+  </si>
+  <si>
+    <t>Ajuste de permissões e perfis de acesso no AG - Papel de Desenvolvedor aplicado a todos os usuários</t>
+  </si>
+  <si>
+    <t>Inconsistência no cálculo do prazo em horas úteis</t>
+  </si>
+  <si>
+    <t>Alinhamento sobre parametrização de críticas/motivos de negação automáticos (AG / Conecta)</t>
+  </si>
+  <si>
+    <t>APOIO DE NEGÓCIO</t>
+  </si>
+  <si>
+    <t>Erro na de geração do “Nosso Número” no boleto</t>
+  </si>
+  <si>
+    <t>Verificando</t>
+  </si>
+  <si>
+    <t>Versão futura</t>
+  </si>
+  <si>
+    <t>EVIDENCIAS DO PROBLEMA NO RELATORIO DE PREVIA DE PAGAMENTO</t>
+  </si>
+  <si>
+    <t>COMPESAPREV – AG: Duplicidade dos eventos solicitados no e-mail do Beneficiario</t>
+  </si>
+  <si>
+    <t>Impossibilidade de Auditoria Geral de Biometria na Execução de Eventos (Exigência de Filtro por Prestador)</t>
+  </si>
+  <si>
+    <t>Atualização do AG em Produção - Release 3.65.19 (Ambiente e WTS)</t>
+  </si>
+  <si>
+    <t>Regulação Médica</t>
+  </si>
+  <si>
+    <t>COMPESAPREV- LEAN- RELATORIO- Regulações Vencidas</t>
+  </si>
+  <si>
+    <t>Esqueci minha senha APP</t>
+  </si>
+  <si>
+    <t>MELHORIA</t>
+  </si>
+  <si>
+    <t>CompesaPrev – Erro na Emissão de Boleto</t>
+  </si>
+  <si>
+    <t>Aguardando análise (negócio)</t>
+  </si>
+  <si>
+    <t>IMPL NAO COBRADA</t>
+  </si>
+  <si>
+    <t>Compesaprev - Complemento II SMS 2531696 – Regra para cálculo de coparticipação</t>
+  </si>
+  <si>
+    <t>Analisando (negócio)</t>
+  </si>
+  <si>
+    <t>ANA.BRASILEIRO</t>
+  </si>
+  <si>
+    <t>COMPESAPREV_Painel de sincronização - PLANOS</t>
+  </si>
+  <si>
+    <t>Históricos Atendimentos</t>
+  </si>
+  <si>
+    <t>Não está sendo possível SOLUCIONAR DEMANDAS</t>
+  </si>
+  <si>
+    <t>Compesaprev- Lean- Erro log integração</t>
+  </si>
+  <si>
+    <t>Cancelado</t>
+  </si>
+  <si>
+    <t>Daniel Serafim</t>
+  </si>
+  <si>
+    <t>COMPESAPREV - SISTEMA NÃO ESTÁ CONSIDERANDO LIMITADOR PF PARA REEMBOLSO</t>
+  </si>
+  <si>
+    <t>COMPESAPREV.DANIEL</t>
+  </si>
+  <si>
+    <t>COMPESPREV - Arquivo retorno com erro na importação</t>
+  </si>
+  <si>
+    <t>Julia Flora Ferreira de Albertim</t>
+  </si>
+  <si>
+    <t>Não consigo vizualizar o que estão pedindo para ALTERAR quando solicitam alteração cadastral de E-MAIL</t>
+  </si>
+  <si>
+    <t>Os detalhes da CARTEIRINHA não está aparecendo para alguns beneficiários</t>
+  </si>
+  <si>
     <t>Aguardando detalhamento</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>BCON</t>
-  </si>
-  <si>
-    <t>Adm Operadora</t>
-  </si>
-  <si>
-    <t>CON - Impossibilidade adiconar corpo clínico</t>
-  </si>
-  <si>
-    <t>MOBE</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APP -  Erro no servidor / buscar dados</t>
-  </si>
-  <si>
-    <t>ROGERIO.ALMEIDA</t>
-  </si>
-  <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Critica para gerar XML na Rotina Monitoramento TISS</t>
-  </si>
-  <si>
-    <t>INSTABILIDADE MÓDULOS</t>
-  </si>
-  <si>
-    <t>Faturamento</t>
-  </si>
-  <si>
-    <t>Guia não disponível para execução de eventos por outros prestadores</t>
-  </si>
-  <si>
-    <t>Plataforma Lean</t>
-  </si>
-  <si>
-    <t>LEAN - Mensagens de prestadores não são exibidas no Lean</t>
-  </si>
-  <si>
-    <t>Erro 504 Gateway Time-out no AG e na Central de Atendimento</t>
-  </si>
-  <si>
-    <t>CONECTA - XML não sai do estado de "Em Processamento"</t>
-  </si>
-  <si>
-    <t>ANA.GOLDIM</t>
-  </si>
-  <si>
-    <t>Autorização</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- Conecta- Erro na solicitação dos procedimentos.</t>
-  </si>
-  <si>
-    <t>Agendamentos</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- AG- AGENDAMENTO com erro Módulo de Regulação: Enviar mensagens Lean e Integracao Iris</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>CONECTA - Erro na execução de guias | pop-up e bloqueio por biometria</t>
-  </si>
-  <si>
-    <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
-  </si>
-  <si>
-    <t>Programando</t>
-  </si>
-  <si>
-    <t>Prestadores</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO NOME PRESTADOR</t>
-  </si>
-  <si>
-    <t>Configurações do Sistema</t>
-  </si>
-  <si>
-    <t>Ajuste no tempo de sessão ativa (timeout) do sistema Lean.</t>
-  </si>
-  <si>
-    <t>Correção – CompesaPrev – Erro de Geração do Código de Barras e Linha Digitável</t>
-  </si>
-  <si>
-    <t>COMPESAPREV-CONECTA- Eventos negados, com recibo autorizado</t>
-  </si>
-  <si>
-    <t>Verificando</t>
-  </si>
-  <si>
-    <t>Niécia Morais</t>
-  </si>
-  <si>
-    <t>Erro no faturamento de pagamentos prestadores</t>
-  </si>
-  <si>
-    <t>Dúvida sobre o local para salvar/exportar a Guia Executada no Portal do Prestador</t>
-  </si>
-  <si>
-    <t>Histórico financeiro sem a informação individual de todos os beneficiários</t>
-  </si>
-  <si>
-    <t>PORTAL</t>
-  </si>
-  <si>
-    <t>Portal não envia e-mails, recuperação de senha e processos parados desde 04/09</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- AG- PROD- Agendamento Regulacao travado</t>
-  </si>
-  <si>
-    <t>Processos</t>
-  </si>
-  <si>
-    <t>Lean / AG (Integração e guias travadas)</t>
-  </si>
-  <si>
-    <t>Beneficiários</t>
-  </si>
-  <si>
-    <t>Erro de divergência de cadastro entre o AG e o LEAN</t>
-  </si>
-  <si>
-    <t>MOBE | Erro no servidor ao tentar logar.</t>
-  </si>
-  <si>
-    <t>Extrato de Utilização com valores de coparticipações sem a limitação de PF e antes do faturamento ser concluído</t>
-  </si>
-  <si>
-    <t>Erro ao buscar documento/relatório na Consulta de Autorizações (App)</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Compesaprev- Conecta- Erro na autorização</t>
-  </si>
-  <si>
-    <t>CENTRAL ATENDIMENTO</t>
-  </si>
-  <si>
-    <t>Transações</t>
-  </si>
-  <si>
-    <t>Falha na integração entre AG Web e Central de Atendimento</t>
-  </si>
-  <si>
-    <t>Ajuste de permissões e perfis de acesso no AG - Papel de Desenvolvedor aplicado a todos os usuários</t>
-  </si>
-  <si>
-    <t>Inconsistência no cálculo do prazo em horas úteis</t>
-  </si>
-  <si>
-    <t>Alinhamento sobre parametrização de críticas/motivos de negação automáticos (AG / Conecta)</t>
-  </si>
-  <si>
-    <t>APOIO DE NEGÓCIO</t>
-  </si>
-  <si>
-    <t>Erro na de geração do “Nosso Número” no boleto</t>
-  </si>
-  <si>
-    <t>Versão futura</t>
-  </si>
-  <si>
-    <t>EVIDENCIAS DO PROBLEMA NO RELATORIO DE PREVIA DE PAGAMENTO</t>
-  </si>
-  <si>
-    <t>COMPESAPREV – AG: Duplicidade dos eventos solicitados no e-mail do Beneficiario</t>
-  </si>
-  <si>
-    <t>Impossibilidade de Auditoria Geral de Biometria na Execução de Eventos (Exigência de Filtro por Prestador)</t>
-  </si>
-  <si>
-    <t>Atualização do AG em Produção - Release 3.65.19 (Ambiente e WTS)</t>
-  </si>
-  <si>
-    <t>Regulação Médica</t>
-  </si>
-  <si>
-    <t>COMPESAPREV- LEAN- RELATORIO- Regulações Vencidas</t>
-  </si>
-  <si>
-    <t>Esqueci minha senha APP</t>
-  </si>
-  <si>
-    <t>MELHORIA</t>
-  </si>
-  <si>
-    <t>CompesaPrev – Erro na Emissão de Boleto</t>
-  </si>
-  <si>
-    <t>Aguardando análise (negócio)</t>
-  </si>
-  <si>
-    <t>IMPL NAO COBRADA</t>
-  </si>
-  <si>
-    <t>Compesaprev - Complemento II SMS 2531696 – Regra para cálculo de coparticipação</t>
-  </si>
-  <si>
-    <t>Analisando (negócio)</t>
-  </si>
-  <si>
-    <t>ANA.BRASILEIRO</t>
-  </si>
-  <si>
-    <t>COMPESAPREV_Painel de sincronização - PLANOS</t>
-  </si>
-  <si>
-    <t>Históricos Atendimentos</t>
-  </si>
-  <si>
-    <t>Não está sendo possível SOLUCIONAR DEMANDAS</t>
-  </si>
-  <si>
-    <t>Compesaprev- Lean- Erro log integração</t>
-  </si>
-  <si>
-    <t>Cancelado</t>
-  </si>
-  <si>
-    <t>Daniel Serafim</t>
-  </si>
-  <si>
-    <t>COMPESAPREV - SISTEMA NÃO ESTÁ CONSIDERANDO LIMITADOR PF PARA REEMBOLSO</t>
-  </si>
-  <si>
-    <t>COMPESAPREV.DANIEL</t>
-  </si>
-  <si>
-    <t>COMPESPREV - Arquivo retorno com erro na importação</t>
-  </si>
-  <si>
-    <t>Julia Flora Ferreira de Albertim</t>
-  </si>
-  <si>
-    <t>Não consigo vizualizar o que estão pedindo para ALTERAR quando solicitam alteração cadastral de E-MAIL</t>
-  </si>
-  <si>
-    <t>Os detalhes da CARTEIRINHA não está aparecendo para alguns beneficiários</t>
-  </si>
-  <si>
     <t>Acesso rede credenciada com perfil de DEPENDENTE não traz resultados.</t>
   </si>
   <si>
@@ -429,9 +441,6 @@
   </si>
   <si>
     <t>COMPREPREV_ PROBLEMA RELACIONADO A REDE DE ATENDIMENTO</t>
-  </si>
-  <si>
-    <t>Atendimento</t>
   </si>
   <si>
     <t>Compesaprev- AG-Produção: Erro na autorização</t>
@@ -839,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O152"/>
+  <dimension ref="A1:O155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1506990705218" customWidth="1"/>
@@ -849,7 +858,7 @@
     <col min="5" max="5" width="47.7084481375558" customWidth="1"/>
     <col min="6" max="6" width="24.124747140067" customWidth="1"/>
     <col min="7" max="7" width="115.814923967634" customWidth="1"/>
-    <col min="8" max="8" width="27.4691489083426" customWidth="1"/>
+    <col min="8" max="8" width="28.4032069614955" customWidth="1"/>
     <col min="9" max="9" width="17.2691879272461" customWidth="1"/>
     <col min="10" max="10" width="17.2691879272461" customWidth="1"/>
     <col min="11" max="11" width="14.5938720703125" customWidth="1"/>
@@ -908,7 +917,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2619693</v>
+        <v>2620239</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>15</v>
@@ -932,10 +941,10 @@
         <v>20</v>
       </c>
       <c r="I2" s="3">
-        <v>46294.6896643518</v>
+        <v>46297.626712963</v>
       </c>
       <c r="J2" s="3">
-        <v>46290.7313310185</v>
+        <v>46293.7100462963</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>21</v>
@@ -944,61 +953,61 @@
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>46290.7313310185</v>
+        <v>46293.7100462963</v>
       </c>
       <c r="N2" s="3">
-        <v>46294.6896643518</v>
+        <v>46297.626712963</v>
       </c>
       <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2619258</v>
+        <v>2619954</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="H3" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3">
+        <v>46303.7183912037</v>
+      </c>
+      <c r="J3" s="3">
+        <v>46293.489224537</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="3">
-        <v>46302.589837963</v>
-      </c>
-      <c r="J3" s="3">
-        <v>46293.3487384259</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>29</v>
-      </c>
       <c r="M3" s="3">
-        <v>46290.3606712963</v>
+        <v>46293.489224537</v>
       </c>
       <c r="N3" s="3">
-        <v>46302.589837963</v>
+        <v>46303.7183912037</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2619015</v>
+        <v>2619927</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>15</v>
@@ -1010,1532 +1019,1534 @@
         <v>16</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="3">
-        <v>46293.6019212963</v>
+        <v>46295.42625</v>
       </c>
       <c r="J4" s="3">
-        <v>46289.643587963</v>
+        <v>46293.4679166667</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M4" s="3">
-        <v>46289.643587963</v>
+        <v>46293.4679166667</v>
       </c>
       <c r="N4" s="3">
-        <v>46293.6019212963</v>
+        <v>46295.42625</v>
       </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>2618956</v>
+        <v>2619693</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I5" s="3">
-        <v>46295.6236574074</v>
+        <v>46294.75</v>
       </c>
       <c r="J5" s="3">
-        <v>46293.3764351852</v>
+        <v>46293.4025881944</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="M5" s="3">
-        <v>46289.6236574074</v>
-      </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+        <v>46290.7313310185</v>
+      </c>
+      <c r="N5" s="3">
+        <v>46296.6479976852</v>
+      </c>
+      <c r="O5" s="3">
+        <v>46294.75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>2618623</v>
+        <v>2619258</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I6" s="3">
-        <v>46294.7106365741</v>
+        <v>46302.589837963</v>
       </c>
       <c r="J6" s="3">
-        <v>46290.7337384259</v>
+        <v>46293.3487384259</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M6" s="3">
-        <v>46289.3773032407</v>
+        <v>46290.3606712963</v>
       </c>
       <c r="N6" s="3">
-        <v>46294.7106365741</v>
+        <v>46302.589837963</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>2618403</v>
+        <v>2619015</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>39</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I7" s="3">
-        <v>46294.5634259259</v>
+        <v>46295.4977546296</v>
       </c>
       <c r="J7" s="3">
-        <v>46288.6467592593</v>
+        <v>46293.7032986111</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M7" s="3">
-        <v>46288.6467592593</v>
+        <v>46289.643587963</v>
       </c>
       <c r="N7" s="3">
-        <v>46294.5634259259</v>
+        <v>46295.4977546296</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>2618370</v>
+        <v>2618956</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F8" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="3">
+        <v>46295.6236574074</v>
+      </c>
+      <c r="J8" s="3">
+        <v>46293.3764351852</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="3">
-        <v>46290.5871296296</v>
-      </c>
-      <c r="J8" s="3">
-        <v>46289.6879962616</v>
-      </c>
-      <c r="K8" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M8" s="3">
-        <v>46288.6287962963</v>
-      </c>
-      <c r="N8" s="3">
-        <v>46290.5871296296</v>
-      </c>
+        <v>46289.6236574074</v>
+      </c>
+      <c r="N8" s="3"/>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2617933</v>
+        <v>2618623</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I9" s="3">
-        <v>46290.7916666667</v>
+        <v>46294.7106365741</v>
       </c>
       <c r="J9" s="3">
-        <v>46290.8786921296</v>
+        <v>46293.385684375</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M9" s="3">
-        <v>46287.7594097222</v>
+        <v>46289.3773032407</v>
       </c>
       <c r="N9" s="3">
-        <v>46293.6666666667</v>
+        <v>46295.3625810185</v>
       </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>2617538</v>
+        <v>2618403</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I10" s="3">
-        <v>46290.7498263889</v>
+        <v>46294.5634259259</v>
       </c>
       <c r="J10" s="3">
-        <v>46288.4440509259</v>
+        <v>46293.749640544</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M10" s="3">
-        <v>46287.4164930556</v>
+        <v>46288.6467592593</v>
       </c>
       <c r="N10" s="3">
-        <v>46290.7498263889</v>
+        <v>46294.5634259259</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>2617170</v>
+        <v>2618370</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F11" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="0" t="s">
         <v>54</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>55</v>
       </c>
       <c r="H11" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I11" s="3">
-        <v>46290.4403703704</v>
+        <v>46290.5871296296</v>
       </c>
       <c r="J11" s="3">
-        <v>46289.5649035069</v>
+        <v>46289.6879962616</v>
       </c>
       <c r="K11" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M11" s="3">
-        <v>46286.5862037037</v>
+        <v>46288.6287962963</v>
       </c>
       <c r="N11" s="3">
-        <v>46290.4403703704</v>
+        <v>46290.5871296296</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>2617057</v>
+        <v>2617933</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="0" t="s">
         <v>56</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>40</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>57</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I12" s="3">
-        <v>46290.4043865741</v>
+        <v>46293.6666666667</v>
       </c>
       <c r="J12" s="3">
-        <v>46286.5879513889</v>
+        <v>46293.3910300926</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M12" s="3">
-        <v>46286.4877199074</v>
+        <v>46287.7594097222</v>
       </c>
       <c r="N12" s="3">
-        <v>46290.4043865741</v>
+        <v>46293.6666666667</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>2615970</v>
+        <v>2617538</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>58</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I13" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="J13" s="3">
-        <v>46287.3554017708</v>
+        <v>46288.4440509259</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M13" s="3">
-        <v>46282.5089930556</v>
+        <v>46287.4164930556</v>
       </c>
       <c r="N13" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>2615871</v>
+        <v>2617170</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I14" s="3">
-        <v>46286.4024189815</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="J14" s="3">
-        <v>46286.3450115741</v>
+        <v>46289.5649035069</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L14" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M14" s="3">
-        <v>46282.4440856481</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="N14" s="3">
-        <v>46286.4024189815</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2615590</v>
+        <v>2617057</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I15" s="3">
-        <v>46287.5805092593</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="J15" s="3">
-        <v>46293.377662037</v>
+        <v>46286.5879513889</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M15" s="3">
-        <v>46281.6638425926</v>
+        <v>46286.4877199074</v>
       </c>
       <c r="N15" s="3">
-        <v>46287.5805092593</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>2614686</v>
+        <v>2615970</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="0" t="s">
         <v>63</v>
-      </c>
-      <c r="G16" s="0" t="s">
-        <v>64</v>
       </c>
       <c r="H16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="3">
-        <v>46321.5908449074</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="J16" s="3">
-        <v>46282.4296635764</v>
+        <v>46287.3554017708</v>
       </c>
       <c r="K16" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="M16" s="3">
-        <v>46280.4450115741</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="N16" s="3">
-        <v>46321.5908449074</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>2614334</v>
+        <v>2615871</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I17" s="3">
-        <v>46283.5629166667</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="J17" s="3">
-        <v>46283.4291666667</v>
+        <v>46286.3450115741</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M17" s="3">
-        <v>46279.6749305556</v>
+        <v>46282.4440856481</v>
       </c>
       <c r="N17" s="3">
-        <v>46283.5629166667</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>2614135</v>
+        <v>2615590</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="I18" s="3">
-        <v>46289.7291666667</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="J18" s="3">
-        <v>46293.3668226852</v>
+        <v>46293.377662037</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M18" s="3">
-        <v>46279.5169097222</v>
+        <v>46281.6638425926</v>
       </c>
       <c r="N18" s="3">
-        <v>46289.7291666667</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>2613646</v>
+        <v>2614686</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="3">
+        <v>46321.5908449074</v>
+      </c>
+      <c r="J19" s="3">
+        <v>46282.4296635764</v>
+      </c>
+      <c r="K19" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="G19" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="3">
-        <v>46289.3876041667</v>
-      </c>
-      <c r="J19" s="3">
-        <v>46283.4346064815</v>
-      </c>
-      <c r="K19" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="L19" s="0" t="s">
-        <v>29</v>
-      </c>
       <c r="M19" s="3">
-        <v>46276.6376041667</v>
+        <v>46280.4450115741</v>
       </c>
       <c r="N19" s="3">
-        <v>46289.3876041667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>2613202</v>
+        <v>2614334</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I20" s="3">
-        <v>46288.6119212963</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="J20" s="3">
-        <v>46283.4707657407</v>
+        <v>46283.4291666667</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M20" s="3">
-        <v>46276.3827546296</v>
+        <v>46279.6749305556</v>
       </c>
       <c r="N20" s="3">
-        <v>46288.6119212963</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>2613026</v>
+        <v>2614135</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="I21" s="3">
-        <v>46281.6747800926</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="J21" s="3">
-        <v>46287.6117592593</v>
+        <v>46293.6142361111</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M21" s="3">
-        <v>46275.6895601852</v>
+        <v>46279.5169097222</v>
       </c>
       <c r="N21" s="3">
-        <v>46281.6747800926</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2612720</v>
+        <v>2613646</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>74</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="I22" s="3">
-        <v>46316.6011689815</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="J22" s="3">
-        <v>46293.3816203704</v>
+        <v>46283.4346064815</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="M22" s="3">
-        <v>46275.4553356481</v>
+        <v>46276.6376041667</v>
       </c>
       <c r="N22" s="3">
-        <v>46316.6011689815</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>2611881</v>
+        <v>2613202</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="0" t="s">
-        <v>77</v>
-      </c>
       <c r="H23" s="0" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I23" s="3">
-        <v>46279.6652314815</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="J23" s="3">
-        <v>46274.7389930556</v>
+        <v>46283.4707657407</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M23" s="3">
-        <v>46273.7485648148</v>
+        <v>46276.3827546296</v>
       </c>
       <c r="N23" s="3">
-        <v>46279.6652314815</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>2611848</v>
+        <v>2613026</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C24" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>45</v>
-      </c>
       <c r="G24" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I24" s="3">
-        <v>46287.4094675926</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="J24" s="3">
-        <v>46276.5914583333</v>
+        <v>46287.6117592593</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M24" s="3">
-        <v>46273.7127546296</v>
+        <v>46275.6895601852</v>
       </c>
       <c r="N24" s="3">
-        <v>46287.4094675926</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>2611692</v>
+        <v>2612720</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H25" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I25" s="3">
-        <v>46279.4554861111</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="J25" s="3">
-        <v>46273.637278588</v>
+        <v>46279.4816185532</v>
       </c>
       <c r="K25" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="M25" s="3">
-        <v>46273.6013194444</v>
+        <v>46275.4553356481</v>
       </c>
       <c r="N25" s="3">
-        <v>46279.4554861111</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>2611552</v>
+        <v>2611881</v>
       </c>
       <c r="B26" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>32</v>
-      </c>
       <c r="D26" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I26" s="3">
-        <v>46275.4327083333</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="J26" s="3">
-        <v>46273.5743171296</v>
+        <v>46274.7389930556</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L26" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M26" s="3">
-        <v>46273.474375</v>
+        <v>46273.7485648148</v>
       </c>
       <c r="N26" s="3">
-        <v>46275.4327083333</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>2611551</v>
+        <v>2611848</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I27" s="3">
-        <v>46314.6183449074</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="J27" s="3">
-        <v>46274.3603356481</v>
+        <v>46276.5914583333</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="M27" s="3">
-        <v>46273.4725115741</v>
+        <v>46273.7127546296</v>
       </c>
       <c r="N27" s="3">
-        <v>46314.6183449074</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>2611539</v>
+        <v>2611692</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I28" s="3">
-        <v>46275.4227083333</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="J28" s="3">
-        <v>46274.3607986111</v>
+        <v>46273.637278588</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L28" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M28" s="3">
-        <v>46273.464375</v>
+        <v>46273.6013194444</v>
       </c>
       <c r="N28" s="3">
-        <v>46275.4227083333</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>2611521</v>
+        <v>2611552</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I29" s="3">
-        <v>46279.3705439815</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="J29" s="3">
-        <v>46273.7182003819</v>
+        <v>46273.5743171296</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M29" s="3">
-        <v>46273.4538773148</v>
+        <v>46273.474375</v>
       </c>
       <c r="N29" s="3">
-        <v>46279.3705439815</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>2610876</v>
+        <v>2611551</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I30" s="3">
-        <v>46276.3367592593</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="J30" s="3">
-        <v>46269.4406376505</v>
+        <v>46274.3603356481</v>
       </c>
       <c r="K30" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="M30" s="3">
-        <v>46269.4200925926</v>
+        <v>46273.4725115741</v>
       </c>
       <c r="N30" s="3">
-        <v>46276.3367592593</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>2610030</v>
+        <v>2611539</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I31" s="3">
-        <v>46274.6271990741</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="J31" s="3">
-        <v>46268.3853071412</v>
+        <v>46274.3607986111</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M31" s="3">
-        <v>46267.7105324074</v>
+        <v>46273.464375</v>
       </c>
       <c r="N31" s="3">
-        <v>46274.6271990741</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>2609985</v>
+        <v>2611521</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H32" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I32" s="3">
-        <v>46301.4629166667</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="J32" s="3">
-        <v>46267.6774134606</v>
+        <v>46273.7182003819</v>
       </c>
       <c r="K32" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="M32" s="3">
-        <v>46267.67125</v>
+        <v>46273.4538773148</v>
       </c>
       <c r="N32" s="3">
-        <v>46301.4629166667</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>2609883</v>
+        <v>2610876</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I33" s="3">
-        <v>46309.7050347222</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="J33" s="3">
-        <v>46280.4030439815</v>
+        <v>46269.4406376505</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="M33" s="3">
-        <v>46267.6217013889</v>
+        <v>46269.4200925926</v>
       </c>
       <c r="N33" s="3">
-        <v>46309.7050347222</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>2609551</v>
+        <v>2610030</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H34" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I34" s="3">
-        <v>46273.6887962963</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="J34" s="3">
-        <v>46267.355462963</v>
+        <v>46268.3853071412</v>
       </c>
       <c r="K34" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M34" s="3">
-        <v>46267.355462963</v>
+        <v>46267.7105324074</v>
       </c>
       <c r="N34" s="3">
-        <v>46273.6887962963</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>2609107</v>
+        <v>2609985</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I35" s="3">
-        <v>46300.3339583333</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="J35" s="3">
-        <v>46293.378900463</v>
+        <v>46267.6774134606</v>
       </c>
       <c r="K35" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M35" s="3">
-        <v>46266.4797916667</v>
+        <v>46267.67125</v>
       </c>
       <c r="N35" s="3">
-        <v>46300.3339583333</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="O35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>2608731</v>
+        <v>2609883</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I36" s="3">
-        <v>46279.4280671296</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="J36" s="3">
-        <v>46289.5798690625</v>
+        <v>46280.4030439815</v>
       </c>
       <c r="K36" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="M36" s="3">
-        <v>46265.6780671296</v>
+        <v>46267.6217013889</v>
       </c>
       <c r="N36" s="3">
-        <v>46293.3554976852</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="O36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>2608637</v>
+        <v>2609551</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H37" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I37" s="3">
-        <v>46304.6977777778</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="J37" s="3">
-        <v>46287.4125274653</v>
+        <v>46267.355462963</v>
       </c>
       <c r="K37" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="M37" s="3">
-        <v>46265.6144444444</v>
+        <v>46267.355462963</v>
       </c>
       <c r="N37" s="3">
-        <v>46304.6977777778</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="O37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>2607413</v>
+        <v>2609107</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>17</v>
@@ -2544,246 +2555,246 @@
         <v>18</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="I38" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I38" s="3">
+        <v>46300.3339583333</v>
+      </c>
       <c r="J38" s="3">
-        <v>46266.569212963</v>
+        <v>46293.378900463</v>
       </c>
       <c r="K38" s="0" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="M38" s="3">
-        <v>46261.6163888889</v>
-      </c>
-      <c r="N38" s="3"/>
+        <v>46266.4797916667</v>
+      </c>
+      <c r="N38" s="3">
+        <v>46300.3339583333</v>
+      </c>
       <c r="O38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2607198</v>
+        <v>2608731</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I39" s="3">
-        <v>46267.3546643518</v>
+        <v>46279.4280671296</v>
       </c>
       <c r="J39" s="3">
-        <v>46273.6204976852</v>
+        <v>46289.5798690625</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M39" s="3">
-        <v>46261.4379976852</v>
+        <v>46265.6780671296</v>
       </c>
       <c r="N39" s="3">
-        <v>46267.3546643518</v>
+        <v>46298.2756365741</v>
       </c>
       <c r="O39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>2606003</v>
+        <v>2608637</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E40" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I40" s="3">
-        <v>46265.3599537037</v>
+        <v>46304.6977777778</v>
       </c>
       <c r="J40" s="3">
-        <v>46259.4993506944</v>
+        <v>46293.6437731481</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="M40" s="3">
-        <v>46259.443287037</v>
+        <v>46265.6144444444</v>
       </c>
       <c r="N40" s="3">
-        <v>46290.75</v>
+        <v>46304.6977777778</v>
       </c>
       <c r="O40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>2604815</v>
+        <v>2607413</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C41" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>45</v>
-      </c>
       <c r="G41" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="H41" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3">
+        <v>46266.569212963</v>
+      </c>
+      <c r="K41" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="H41" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="I41" s="3">
-        <v>46296.563587963</v>
-      </c>
-      <c r="J41" s="3">
-        <v>46268.6781365741</v>
-      </c>
-      <c r="K41" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="L41" s="0" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M41" s="3">
-        <v>46255.4177546296</v>
-      </c>
-      <c r="N41" s="3">
-        <v>46296.563587963</v>
-      </c>
+        <v>46261.6163888889</v>
+      </c>
+      <c r="N41" s="3"/>
       <c r="O41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>2604500</v>
+        <v>2607198</v>
       </c>
       <c r="B42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="0" t="s">
-        <v>32</v>
-      </c>
       <c r="D42" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>104</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I42" s="3">
-        <v>46260.4812268519</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="J42" s="3">
-        <v>46258.3485416667</v>
+        <v>46273.6204976852</v>
       </c>
       <c r="K42" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M42" s="3">
-        <v>46254.6270601852</v>
+        <v>46261.4379976852</v>
       </c>
       <c r="N42" s="3">
-        <v>46260.4812268519</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="O42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>2603668</v>
+        <v>2606003</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F43" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="G43" s="0" t="s">
         <v>105</v>
-      </c>
-      <c r="G43" s="0" t="s">
-        <v>106</v>
       </c>
       <c r="H43" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I43" s="3">
-        <v>46259.3446296296</v>
+        <v>46265.3599537037</v>
       </c>
       <c r="J43" s="3">
-        <v>46258.6426851852</v>
+        <v>46259.4993506944</v>
       </c>
       <c r="K43" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M43" s="3">
-        <v>46253.427962963</v>
+        <v>46259.443287037</v>
       </c>
       <c r="N43" s="3">
         <v>46290.75</v>
@@ -2792,2056 +2803,2062 @@
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>2602388</v>
+        <v>2604815</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I44" s="3">
-        <v>46255.4166666667</v>
+        <v>46296.563587963</v>
       </c>
       <c r="J44" s="3">
-        <v>46253.4900231482</v>
+        <v>46268.6781365741</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="M44" s="3">
-        <v>46251.5527777778</v>
+        <v>46255.4177546296</v>
       </c>
       <c r="N44" s="3">
-        <v>46255.4166666667</v>
+        <v>46296.563587963</v>
       </c>
       <c r="O44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>2601999</v>
+        <v>2604500</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="E45" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="I45" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I45" s="3">
+        <v>46260.4812268519</v>
+      </c>
       <c r="J45" s="3">
-        <v>46266.6188194444</v>
+        <v>46258.3485416667</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="M45" s="3">
-        <v>46248.7351273148</v>
-      </c>
-      <c r="N45" s="3"/>
+        <v>46254.6270601852</v>
+      </c>
+      <c r="N45" s="3">
+        <v>46260.4812268519</v>
+      </c>
       <c r="O45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>2600778</v>
+        <v>2603668</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="I46" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I46" s="3">
+        <v>46259.3446296296</v>
+      </c>
       <c r="J46" s="3">
-        <v>46274.3780324074</v>
+        <v>46258.6426851852</v>
       </c>
       <c r="K46" s="0" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="M46" s="3">
-        <v>46246.7171759259</v>
-      </c>
-      <c r="N46" s="3"/>
+        <v>46253.427962963</v>
+      </c>
+      <c r="N46" s="3">
+        <v>46290.75</v>
+      </c>
       <c r="O46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>2599732</v>
+        <v>2602388</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I47" s="3">
-        <v>46251.4016203704</v>
+        <v>46255.4166666667</v>
       </c>
       <c r="J47" s="3">
-        <v>46248.3419117245</v>
+        <v>46253.4900231482</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M47" s="3">
-        <v>46245.4849537037</v>
+        <v>46251.5527777778</v>
       </c>
       <c r="N47" s="3">
-        <v>46251.4016203704</v>
+        <v>46255.4166666667</v>
       </c>
       <c r="O47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>2598987</v>
+        <v>2601999</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I48" s="3">
-        <v>46254.6856134259</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="I48" s="3"/>
       <c r="J48" s="3">
-        <v>46251.536875</v>
+        <v>46266.6188194444</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="M48" s="3">
-        <v>46244.4564467593</v>
-      </c>
-      <c r="N48" s="3">
-        <v>46254.6856134259</v>
-      </c>
+        <v>46248.7351273148</v>
+      </c>
+      <c r="N48" s="3"/>
       <c r="O48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>2598910</v>
+        <v>2600778</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="I49" s="3">
-        <v>46254.6386574074</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="I49" s="3"/>
       <c r="J49" s="3">
-        <v>46248.4760674769</v>
+        <v>46274.3780324074</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="M49" s="3">
-        <v>46244.4094907407</v>
-      </c>
-      <c r="N49" s="3">
-        <v>46261.6103125</v>
-      </c>
+        <v>46246.7171759259</v>
+      </c>
+      <c r="N49" s="3"/>
       <c r="O49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>2598767</v>
+        <v>2599732</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I50" s="3">
-        <v>46247.6666666667</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="J50" s="3">
-        <v>46245.6608564815</v>
+        <v>46248.3419117245</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M50" s="3">
-        <v>46241.757962963</v>
+        <v>46245.4849537037</v>
       </c>
       <c r="N50" s="3">
-        <v>46247.6666666667</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="O50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>2597798</v>
+        <v>2598987</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="C51" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="G51" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="D51" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G51" s="0" t="s">
-        <v>123</v>
-      </c>
       <c r="H51" s="0" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I51" s="3">
-        <v>46290.75</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="J51" s="3">
-        <v>46273.4412384259</v>
+        <v>46251.536875</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M51" s="3">
-        <v>46240.4508912037</v>
+        <v>46244.4564467593</v>
       </c>
       <c r="N51" s="3">
-        <v>46290.75</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="O51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>2597524</v>
+        <v>2598910</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F52" s="0" t="s">
         <v>85</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="I52" s="3">
-        <v>46267.0453356481</v>
+        <v>46254.6386574074</v>
       </c>
       <c r="J52" s="3">
-        <v>46259.4158333333</v>
+        <v>46248.4760674769</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M52" s="3">
-        <v>46239.6925347222</v>
+        <v>46244.4094907407</v>
       </c>
       <c r="N52" s="3">
-        <v>46267.0453356481</v>
+        <v>46261.6103125</v>
       </c>
       <c r="O52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>2597515</v>
+        <v>2598767</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C53" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G53" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="D53" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="F53" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="G53" s="0" t="s">
-        <v>126</v>
-      </c>
       <c r="H53" s="0" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I53" s="3">
-        <v>46266.4759953704</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="J53" s="3">
-        <v>46289.7039236111</v>
+        <v>46245.6608564815</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="M53" s="3">
-        <v>46239.6856134259</v>
+        <v>46241.757962963</v>
       </c>
       <c r="N53" s="3">
-        <v>46266.4759953704</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="O53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>2597495</v>
+        <v>2597798</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I54" s="3">
-        <v>46252.3333333333</v>
+        <v>46290.75</v>
       </c>
       <c r="J54" s="3">
-        <v>46241.6523302083</v>
+        <v>46273.4412384259</v>
       </c>
       <c r="K54" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M54" s="3">
-        <v>46239.6802199074</v>
+        <v>46240.4508912037</v>
       </c>
       <c r="N54" s="3">
-        <v>46245.5968865741</v>
-      </c>
-      <c r="O54" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>46290.75</v>
+      </c>
+      <c r="O54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>2596882</v>
+        <v>2597524</v>
       </c>
       <c r="B55" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="G55" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="C55" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="F55" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="G55" s="0" t="s">
-        <v>130</v>
-      </c>
       <c r="H55" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I55" s="3">
-        <v>46280.3775578704</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="J55" s="3">
-        <v>46267.6170023148</v>
+        <v>46259.4158333333</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="M55" s="3">
-        <v>46238.7108912037</v>
+        <v>46239.6925347222</v>
       </c>
       <c r="N55" s="3">
-        <v>46280.3775578704</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="O55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>2596538</v>
+        <v>2597515</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="I56" s="3">
-        <v>46273.960787037</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="J56" s="3">
-        <v>46286.3521412037</v>
+        <v>46289.7039236111</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="M56" s="3">
-        <v>46238.4644791667</v>
+        <v>46239.6856134259</v>
       </c>
       <c r="N56" s="3">
-        <v>46273.960787037</v>
+        <v>46266.4759953704</v>
       </c>
       <c r="O56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>2596407</v>
+        <v>2597495</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I57" s="3">
-        <v>46248.6072106482</v>
+        <v>46252.3333333333</v>
       </c>
       <c r="J57" s="3">
-        <v>46267.6164814815</v>
+        <v>46241.6523302083</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M57" s="3">
-        <v>46238.3780439815</v>
+        <v>46239.6802199074</v>
       </c>
       <c r="N57" s="3">
-        <v>46248.6072106482</v>
-      </c>
-      <c r="O57" s="3"/>
+        <v>46245.5968865741</v>
+      </c>
+      <c r="O57" s="3">
+        <v>46252.3333333333</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>2595510</v>
+        <v>2596882</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I58" s="3">
-        <v>46240.4984606481</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="J58" s="3">
-        <v>46245.3667592593</v>
+        <v>46267.6170023148</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="M58" s="3">
-        <v>46234.6442939815</v>
+        <v>46238.7108912037</v>
       </c>
       <c r="N58" s="3">
-        <v>46240.4984606481</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="O58" s="3"/>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>2595497</v>
+        <v>2596538</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I59" s="3">
-        <v>46240.4978240741</v>
+        <v>46273.960787037</v>
       </c>
       <c r="J59" s="3">
-        <v>46245.3669444444</v>
+        <v>46286.3521412037</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M59" s="3">
-        <v>46234.6436574074</v>
+        <v>46238.4644791667</v>
       </c>
       <c r="N59" s="3">
-        <v>46240.4978240741</v>
+        <v>46273.960787037</v>
       </c>
       <c r="O59" s="3"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2593529</v>
+        <v>2596407</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I60" s="3">
-        <v>46237.5806597222</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="J60" s="3">
-        <v>46233.4404570255</v>
+        <v>46267.6164814815</v>
       </c>
       <c r="K60" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M60" s="3">
-        <v>46231.6639930556</v>
+        <v>46238.3780439815</v>
       </c>
       <c r="N60" s="3">
-        <v>46237.5806597222</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="O60" s="3"/>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>2593490</v>
+        <v>2595510</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I61" s="3">
-        <v>46239.6748032407</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="J61" s="3">
-        <v>46253.4905324074</v>
+        <v>46245.3667592593</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L61" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M61" s="3">
-        <v>46231.6518865741</v>
+        <v>46234.6442939815</v>
       </c>
       <c r="N61" s="3">
-        <v>46239.6748032407</v>
-      </c>
-      <c r="O61" s="3">
-        <v>46234.48125</v>
-      </c>
+        <v>46240.4984606481</v>
+      </c>
+      <c r="O61" s="3"/>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>2593260</v>
+        <v>2595497</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I62" s="3">
-        <v>46241.6638888889</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="J62" s="3">
-        <v>46267.614525463</v>
+        <v>46245.3669444444</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M62" s="3">
-        <v>46231.435150463</v>
+        <v>46234.6436574074</v>
       </c>
       <c r="N62" s="3">
-        <v>46241.6638888889</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>2593216</v>
+        <v>2593529</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I63" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I63" s="3">
+        <v>46237.5806597222</v>
+      </c>
       <c r="J63" s="3">
-        <v>46231.4047453704</v>
+        <v>46233.4404570255</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="M63" s="3">
-        <v>46231.4011111111</v>
-      </c>
-      <c r="N63" s="3"/>
+        <v>46231.6639930556</v>
+      </c>
+      <c r="N63" s="3">
+        <v>46237.5806597222</v>
+      </c>
       <c r="O63" s="3"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2592878</v>
+        <v>2593490</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I64" s="3">
-        <v>46241.3504282407</v>
+        <v>46239.6748032407</v>
       </c>
       <c r="J64" s="3">
-        <v>46230.6675740741</v>
+        <v>46253.4905324074</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M64" s="3">
-        <v>46230.6004282407</v>
+        <v>46231.6518865741</v>
       </c>
       <c r="N64" s="3">
-        <v>46290.75</v>
-      </c>
-      <c r="O64" s="3"/>
+        <v>46239.6748032407</v>
+      </c>
+      <c r="O64" s="3">
+        <v>46234.48125</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2592468</v>
+        <v>2593260</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>141</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I65" s="3">
-        <v>46237.6038657407</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="J65" s="3">
-        <v>46240.6136738773</v>
+        <v>46267.614525463</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M65" s="3">
-        <v>46227.7107060185</v>
+        <v>46231.435150463</v>
       </c>
       <c r="N65" s="3">
-        <v>46293.6033680556</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="O65" s="3"/>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>2591596</v>
+        <v>2593216</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>142</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I66" s="3">
-        <v>46238.7083333333</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I66" s="3"/>
       <c r="J66" s="3">
-        <v>46267.3444803241</v>
+        <v>46231.4047453704</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="M66" s="3">
-        <v>46226.4797916667</v>
-      </c>
-      <c r="N66" s="3">
-        <v>46282.6141435185</v>
-      </c>
+        <v>46231.4011111111</v>
+      </c>
+      <c r="N66" s="3"/>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>2591284</v>
+        <v>2592878</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>143</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I67" s="3">
-        <v>46266.3384837963</v>
+        <v>46241.3504282407</v>
       </c>
       <c r="J67" s="3">
-        <v>46225.7002398495</v>
+        <v>46230.6675740741</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="M67" s="3">
-        <v>46225.6718171296</v>
+        <v>46230.6004282407</v>
       </c>
       <c r="N67" s="3">
-        <v>46266.3384837963</v>
+        <v>46290.75</v>
       </c>
       <c r="O67" s="3"/>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>2588490</v>
+        <v>2592468</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>144</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I68" s="3">
-        <v>46230.722037037</v>
+        <v>46237.6038657407</v>
       </c>
       <c r="J68" s="3">
-        <v>46231.4339699074</v>
+        <v>46240.6136738773</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M68" s="3">
-        <v>46218.4928703704</v>
+        <v>46227.7107060185</v>
       </c>
       <c r="N68" s="3">
-        <v>46230.722037037</v>
+        <v>46293.6033680556</v>
       </c>
       <c r="O68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>2588025</v>
+        <v>2591596</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D69" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G69" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="E69" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="F69" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="G69" s="0" t="s">
-        <v>148</v>
-      </c>
       <c r="H69" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="I69" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I69" s="3">
+        <v>46238.7083333333</v>
+      </c>
       <c r="J69" s="3">
-        <v>46267.5903356482</v>
+        <v>46267.3444803241</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M69" s="3">
-        <v>46217.612962963</v>
-      </c>
-      <c r="N69" s="3"/>
+        <v>46226.4797916667</v>
+      </c>
+      <c r="N69" s="3">
+        <v>46282.6141435185</v>
+      </c>
       <c r="O69" s="3"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>2587849</v>
+        <v>2591284</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I70" s="3">
-        <v>46226.6083796296</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="J70" s="3">
-        <v>46237.9144806713</v>
+        <v>46225.7002398495</v>
       </c>
       <c r="K70" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="M70" s="3">
-        <v>46217.4506597222</v>
+        <v>46225.6718171296</v>
       </c>
       <c r="N70" s="3">
-        <v>46226.6083796296</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="O70" s="3"/>
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>2587713</v>
+        <v>2588490</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I71" s="3">
-        <v>46218.7408680556</v>
+        <v>46230.722037037</v>
       </c>
       <c r="J71" s="3">
-        <v>46230.4199074074</v>
+        <v>46231.4339699074</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M71" s="3">
-        <v>46217.3658680556</v>
+        <v>46218.4928703704</v>
       </c>
       <c r="N71" s="3">
-        <v>46218.7408680556</v>
+        <v>46230.722037037</v>
       </c>
       <c r="O71" s="3"/>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>2587585</v>
+        <v>2588025</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>44</v>
+        <v>149</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>151</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I72" s="3">
-        <v>46220.6264583333</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="I72" s="3"/>
       <c r="J72" s="3">
-        <v>46259.4474884259</v>
+        <v>46267.5903356482</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M72" s="3">
-        <v>46216.7097916667</v>
-      </c>
-      <c r="N72" s="3">
-        <v>46220.6264583333</v>
-      </c>
+        <v>46217.612962963</v>
+      </c>
+      <c r="N72" s="3"/>
       <c r="O72" s="3"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>2587006</v>
+        <v>2587849</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E73" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>152</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I73" s="3">
-        <v>46217.7289699074</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="J73" s="3">
-        <v>46227.4549884259</v>
+        <v>46237.9144806713</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L73" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M73" s="3">
-        <v>46213.7239236111</v>
+        <v>46217.4506597222</v>
       </c>
       <c r="N73" s="3">
-        <v>46217.7289699074</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="O73" s="3"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2586984</v>
+        <v>2587713</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>153</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I74" s="3">
-        <v>46295.7416550926</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="J74" s="3">
-        <v>46273.4946180556</v>
+        <v>46230.4199074074</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M74" s="3">
-        <v>46213.6971527778</v>
+        <v>46217.3658680556</v>
       </c>
       <c r="N74" s="3">
-        <v>46295.7416550926</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="O74" s="3"/>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2586910</v>
+        <v>2587585</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F75" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G75" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="G75" s="0" t="s">
-        <v>155</v>
-      </c>
       <c r="H75" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I75" s="3">
-        <v>46226.5833333333</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="J75" s="3">
-        <v>46230.4194212963</v>
+        <v>46259.4474884259</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L75" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M75" s="3">
-        <v>46213.6245833333</v>
+        <v>46216.7097916667</v>
       </c>
       <c r="N75" s="3">
-        <v>46226.5833333333</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="O75" s="3"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>2586651</v>
+        <v>2587006</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I76" s="3">
-        <v>46218.7157407407</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="J76" s="3">
-        <v>46213.3824074074</v>
+        <v>46227.4549884259</v>
       </c>
       <c r="K76" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M76" s="3">
-        <v>46213.3824074074</v>
+        <v>46213.7239236111</v>
       </c>
       <c r="N76" s="3">
-        <v>46218.7157407407</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="O76" s="3"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>2586187</v>
+        <v>2586984</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="I77" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I77" s="3">
+        <v>46295.7416550926</v>
+      </c>
       <c r="J77" s="3">
-        <v>46219.3850231481</v>
+        <v>46273.4946180556</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="M77" s="3">
-        <v>46211.7697337963</v>
-      </c>
-      <c r="N77" s="3"/>
+        <v>46213.6971527778</v>
+      </c>
+      <c r="N77" s="3">
+        <v>46295.7416550926</v>
+      </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>2585888</v>
+        <v>2586910</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I78" s="3">
-        <v>46217.4119907407</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="J78" s="3">
-        <v>46217.5003587963</v>
+        <v>46230.4194212963</v>
       </c>
       <c r="K78" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M78" s="3">
-        <v>46211.4953240741</v>
+        <v>46213.6245833333</v>
       </c>
       <c r="N78" s="3">
-        <v>46290.75</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="O78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2585424</v>
+        <v>2586651</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I79" s="3">
-        <v>46223.3927199074</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="J79" s="3">
-        <v>46234.4964930556</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="K79" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M79" s="3">
-        <v>46210.6427199074</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="N79" s="3">
-        <v>46290.75</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>2584638</v>
+        <v>2586187</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>162</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="I80" s="3">
-        <v>46213.4171527778</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I80" s="3"/>
       <c r="J80" s="3">
-        <v>46213.4090859607</v>
+        <v>46219.3850231481</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M80" s="3">
-        <v>46209.5016203704</v>
-      </c>
-      <c r="N80" s="3">
-        <v>46232.3874884259</v>
-      </c>
+        <v>46211.7697337963</v>
+      </c>
+      <c r="N80" s="3"/>
       <c r="O80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>2584397</v>
+        <v>2585888</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>40</v>
+        <v>157</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>163</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I81" s="3">
-        <v>46212.6757175926</v>
+        <v>46217.4119907407</v>
       </c>
       <c r="J81" s="3">
-        <v>46213.3741550926</v>
+        <v>46217.5003587963</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M81" s="3">
-        <v>46209.3423842593</v>
+        <v>46211.4953240741</v>
       </c>
       <c r="N81" s="3">
-        <v>46212.6757175926</v>
+        <v>46290.75</v>
       </c>
       <c r="O81" s="3"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>2584167</v>
+        <v>2585424</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>164</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="I82" s="3">
-        <v>46246.7216435185</v>
+        <v>46223.3927199074</v>
       </c>
       <c r="J82" s="3">
-        <v>46247.4396759259</v>
+        <v>46234.4964930556</v>
       </c>
       <c r="K82" s="0" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="M82" s="3">
-        <v>46206.6383101852</v>
+        <v>46210.6427199074</v>
       </c>
       <c r="N82" s="3">
-        <v>46246.7216435185</v>
+        <v>46290.75</v>
       </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>2583950</v>
+        <v>2584638</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>165</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I83" s="3"/>
+        <v>122</v>
+      </c>
+      <c r="I83" s="3">
+        <v>46213.4171527778</v>
+      </c>
       <c r="J83" s="3">
-        <v>46273.4100925926</v>
+        <v>46213.4090859607</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="M83" s="3">
-        <v>46206.4623148148</v>
-      </c>
-      <c r="N83" s="3"/>
+        <v>46209.5016203704</v>
+      </c>
+      <c r="N83" s="3">
+        <v>46232.3874884259</v>
+      </c>
       <c r="O83" s="3"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>2583447</v>
+        <v>2584397</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>166</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I84" s="3">
-        <v>46205.7916666667</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="J84" s="3">
-        <v>46265.3645138889</v>
+        <v>46213.3741550926</v>
       </c>
       <c r="K84" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="M84" s="3">
-        <v>46205.5752083333</v>
+        <v>46209.3423842593</v>
       </c>
       <c r="N84" s="3">
-        <v>46245.6724189815</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="O84" s="3"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>2583382</v>
+        <v>2584167</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D85" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F85" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G85" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="E85" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F85" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="G85" s="0" t="s">
-        <v>168</v>
-      </c>
       <c r="H85" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I85" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I85" s="3">
+        <v>46246.7216435185</v>
+      </c>
       <c r="J85" s="3">
-        <v>46293.3798726852</v>
+        <v>46247.4396759259</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="M85" s="3">
-        <v>46205.4905092593</v>
-      </c>
-      <c r="N85" s="3"/>
+        <v>46206.6383101852</v>
+      </c>
+      <c r="N85" s="3">
+        <v>46246.7216435185</v>
+      </c>
       <c r="O85" s="3"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>2582452</v>
+        <v>2583950</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I86" s="3">
-        <v>46244.4166666667</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I86" s="3"/>
       <c r="J86" s="3">
-        <v>46204.7763078704</v>
+        <v>46273.4100925926</v>
       </c>
       <c r="K86" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L86" s="0" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M86" s="3">
-        <v>46203.8250810185</v>
-      </c>
-      <c r="N86" s="3">
-        <v>46244.4166666667</v>
-      </c>
+        <v>46206.4623148148</v>
+      </c>
+      <c r="N86" s="3"/>
       <c r="O86" s="3"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>2582352</v>
+        <v>2583447</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I87" s="3">
-        <v>46244.340775463</v>
+        <v>46205.7916666667</v>
       </c>
       <c r="J87" s="3">
-        <v>46204.7761805556</v>
+        <v>46265.3645138889</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M87" s="3">
-        <v>46203.6741087963</v>
+        <v>46205.5752083333</v>
       </c>
       <c r="N87" s="3">
-        <v>46244.340775463</v>
+        <v>46245.6724189815</v>
       </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>2579299</v>
+        <v>2583382</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>171</v>
+        <v>65</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>171</v>
+        <v>65</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="E88" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I88" s="3"/>
       <c r="J88" s="3">
-        <v>46204.3277777778</v>
+        <v>46293.3798726852</v>
       </c>
       <c r="K88" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M88" s="3">
-        <v>46196.4165162037</v>
+        <v>46205.4905092593</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>2576326</v>
+        <v>2582452</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F89" s="0" t="s">
         <v>85</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I89" s="3">
-        <v>46192.7916666667</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="J89" s="3">
-        <v>46230.6812731481</v>
+        <v>46204.7763078704</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="M89" s="3">
-        <v>46189.3995833333</v>
-      </c>
-      <c r="N89" s="3"/>
+        <v>46203.8250810185</v>
+      </c>
+      <c r="N89" s="3">
+        <v>46244.4166666667</v>
+      </c>
       <c r="O89" s="3"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2574153</v>
+        <v>2582352</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="E90" s="0" t="s">
         <v>17</v>
@@ -4850,2743 +4867,2872 @@
         <v>18</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I90" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I90" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="J90" s="3">
-        <v>46204.3218402778</v>
+        <v>46204.7761805556</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="M90" s="3">
-        <v>46183.4711226852</v>
-      </c>
-      <c r="N90" s="3"/>
+        <v>46203.6741087963</v>
+      </c>
+      <c r="N90" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>2572707</v>
+        <v>2579299</v>
       </c>
       <c r="B91" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="G91" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="C91" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="D91" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E91" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="F91" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="G91" s="0" t="s">
-        <v>177</v>
-      </c>
       <c r="H91" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I91" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I91" s="3"/>
       <c r="J91" s="3">
-        <v>46188.4629166667</v>
+        <v>46204.3277777778</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M91" s="3">
-        <v>46178.7298148148</v>
-      </c>
-      <c r="N91" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>46196.4165162037</v>
+      </c>
+      <c r="N91" s="3"/>
       <c r="O91" s="3"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>2570274</v>
+        <v>2576326</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E92" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I92" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I92" s="3">
+        <v>46192.7916666667</v>
+      </c>
       <c r="J92" s="3">
-        <v>46204.3220138889</v>
+        <v>46230.6812731481</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M92" s="3">
-        <v>46171.6563773148</v>
+        <v>46189.3995833333</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>2562116</v>
+        <v>2574153</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>128</v>
+        <v>34</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>128</v>
+        <v>34</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E93" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I93" s="3"/>
       <c r="J93" s="3">
-        <v>46160.7191666667</v>
+        <v>46204.3218402778</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M93" s="3">
-        <v>46154.3432638889</v>
+        <v>46183.4711226852</v>
       </c>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>2558553</v>
+        <v>2572707</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>54</v>
+        <v>179</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I94" s="3">
-        <v>46149.6895138889</v>
+        <v>46219.3964814815</v>
       </c>
       <c r="J94" s="3">
-        <v>46154.5888773148</v>
+        <v>46188.4629166667</v>
       </c>
       <c r="K94" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L94" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="M94" s="3">
-        <v>46146.3561805556</v>
+        <v>46178.7298148148</v>
       </c>
       <c r="N94" s="3">
-        <v>46149.6895138889</v>
+        <v>46219.3964814815</v>
       </c>
       <c r="O94" s="3"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>2556271</v>
+        <v>2570274</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>120</v>
+        <v>181</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="E95" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>182</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I95" s="3">
-        <v>46141.4297453704</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I95" s="3"/>
       <c r="J95" s="3">
-        <v>46139.9871412037</v>
+        <v>46204.3220138889</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="M95" s="3">
-        <v>46139.471412037</v>
-      </c>
-      <c r="N95" s="3">
-        <v>46141.4901157407</v>
-      </c>
+        <v>46171.6563773148</v>
+      </c>
+      <c r="N95" s="3"/>
       <c r="O95" s="3"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>2556211</v>
+        <v>2562116</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>183</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I96" s="3">
-        <v>46150.6617476852</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I96" s="3"/>
       <c r="J96" s="3">
-        <v>46146.3663773148</v>
+        <v>46160.7191666667</v>
       </c>
       <c r="K96" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L96" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="M96" s="3">
-        <v>46139.4325810185</v>
-      </c>
-      <c r="N96" s="3">
-        <v>46150.6617476852</v>
-      </c>
+        <v>46154.3432638889</v>
+      </c>
+      <c r="N96" s="3"/>
       <c r="O96" s="3"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>2556029</v>
+        <v>2558553</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>184</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I97" s="3">
-        <v>46150.5</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="J97" s="3">
-        <v>46146.401875</v>
+        <v>46154.5888773148</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M97" s="3">
-        <v>46138.757337963</v>
+        <v>46146.3561805556</v>
       </c>
       <c r="N97" s="3">
-        <v>46154.6616087963</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="O97" s="3"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>2554341</v>
+        <v>2556271</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E98" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="0" t="s">
         <v>44</v>
-      </c>
-      <c r="F98" s="0" t="s">
-        <v>45</v>
       </c>
       <c r="G98" s="0" t="s">
         <v>185</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I98" s="3">
-        <v>46136.3599768519</v>
+        <v>46141.4297453704</v>
       </c>
       <c r="J98" s="3">
-        <v>46135.6585185185</v>
+        <v>46139.9871412037</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M98" s="3">
-        <v>46134.4016435185</v>
+        <v>46139.471412037</v>
       </c>
       <c r="N98" s="3">
-        <v>46136.3599768519</v>
+        <v>46141.4901157407</v>
       </c>
       <c r="O98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>2547638</v>
+        <v>2556211</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>186</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I99" s="3">
-        <v>46150.3473611111</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="J99" s="3">
-        <v>46119.5010069444</v>
+        <v>46146.3663773148</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="M99" s="3">
-        <v>46114.4931944444</v>
+        <v>46139.4325810185</v>
       </c>
       <c r="N99" s="3">
-        <v>46150.3473611111</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="O99" s="3"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>2537054</v>
+        <v>2556029</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>187</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I100" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.5</v>
       </c>
       <c r="J100" s="3">
-        <v>46090.3698263889</v>
+        <v>46146.401875</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L100" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M100" s="3">
-        <v>46087.5797569444</v>
+        <v>46138.757337963</v>
       </c>
       <c r="N100" s="3">
-        <v>46093.4339236111</v>
+        <v>46154.6616087963</v>
       </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>2531696</v>
+        <v>2554341</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>188</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I101" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I101" s="3">
+        <v>46136.3599768519</v>
+      </c>
       <c r="J101" s="3">
-        <v>46204.3216782407</v>
+        <v>46135.6585185185</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M101" s="3">
-        <v>46076.5833912037</v>
-      </c>
-      <c r="N101" s="3"/>
+        <v>46134.4016435185</v>
+      </c>
+      <c r="N101" s="3">
+        <v>46136.3599768519</v>
+      </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>2530739</v>
+        <v>2547638</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>189</v>
+        <v>125</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>190</v>
+        <v>123</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="E102" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="I102" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I102" s="3">
+        <v>46150.3473611111</v>
+      </c>
       <c r="J102" s="3">
-        <v>46218.6914940625</v>
+        <v>46119.5010069444</v>
       </c>
       <c r="K102" s="0" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="L102" s="0" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="M102" s="3">
-        <v>46072.6973148148</v>
-      </c>
-      <c r="N102" s="3"/>
+        <v>46114.4931944444</v>
+      </c>
+      <c r="N102" s="3">
+        <v>46150.3473611111</v>
+      </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>2529639</v>
+        <v>2537054</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I103" s="3">
-        <v>46083.3430902778</v>
+        <v>46093.4339236111</v>
       </c>
       <c r="J103" s="3">
-        <v>46072.6891666667</v>
+        <v>46090.3698263889</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M103" s="3">
-        <v>46069.5930902778</v>
+        <v>46087.5797569444</v>
       </c>
       <c r="N103" s="3">
-        <v>46083.3430902778</v>
+        <v>46093.4339236111</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>2529591</v>
+        <v>2531696</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I104" s="3">
-        <v>46108.5968055556</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I104" s="3"/>
       <c r="J104" s="3">
-        <v>46126.6875</v>
+        <v>46204.3216782407</v>
       </c>
       <c r="K104" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M104" s="3">
-        <v>46069.4509722222</v>
-      </c>
-      <c r="N104" s="3">
-        <v>46108.5968055556</v>
-      </c>
+        <v>46076.5833912037</v>
+      </c>
+      <c r="N104" s="3"/>
       <c r="O104" s="3"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>2528858</v>
+        <v>2530739</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>194</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I105" s="3">
-        <v>46107.3861458333</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="I105" s="3"/>
       <c r="J105" s="3">
-        <v>46087.6277662037</v>
+        <v>46218.6914940625</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M105" s="3">
-        <v>46065.7194791667</v>
-      </c>
-      <c r="N105" s="3">
-        <v>46107.3861458333</v>
-      </c>
+        <v>46072.6973148148</v>
+      </c>
+      <c r="N105" s="3"/>
       <c r="O105" s="3"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>2525312</v>
+        <v>2529639</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>195</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I106" s="3">
-        <v>46070.5877314815</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="J106" s="3">
-        <v>46062.7587037037</v>
+        <v>46072.6891666667</v>
       </c>
       <c r="K106" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L106" s="0" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M106" s="3">
-        <v>46058.3585648148</v>
+        <v>46069.5930902778</v>
       </c>
       <c r="N106" s="3">
-        <v>46070.5877314815</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="O106" s="3"/>
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>2525272</v>
+        <v>2529591</v>
       </c>
       <c r="B107" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C107" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="D107" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E107" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F107" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G107" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="C107" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="D107" s="0" t="s">
-        <v>197</v>
-      </c>
-      <c r="E107" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F107" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G107" s="0" t="s">
-        <v>198</v>
-      </c>
       <c r="H107" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I107" s="3">
-        <v>46203.7916666667</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="J107" s="3">
-        <v>46126.7441782407</v>
+        <v>46126.6875</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="M107" s="3">
-        <v>46058.2883101852</v>
-      </c>
-      <c r="N107" s="3"/>
+        <v>46069.4509722222</v>
+      </c>
+      <c r="N107" s="3">
+        <v>46108.5968055556</v>
+      </c>
       <c r="O107" s="3"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>2524577</v>
+        <v>2528858</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="I108" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I108" s="3">
+        <v>46107.3861458333</v>
+      </c>
       <c r="J108" s="3">
-        <v>46267.4298180903</v>
+        <v>46087.6277662037</v>
       </c>
       <c r="K108" s="0" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="L108" s="0" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="M108" s="3">
-        <v>46056.697349537</v>
-      </c>
-      <c r="N108" s="3"/>
+        <v>46065.7194791667</v>
+      </c>
+      <c r="N108" s="3">
+        <v>46107.3861458333</v>
+      </c>
       <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>2524373</v>
+        <v>2525312</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I109" s="3">
-        <v>46087.3854513889</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="J109" s="3">
-        <v>46056.6543865741</v>
+        <v>46062.7587037037</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="M109" s="3">
-        <v>46056.5937847222</v>
+        <v>46058.3585648148</v>
       </c>
       <c r="N109" s="3">
-        <v>46087.3854513889</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="O109" s="3"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>2524062</v>
+        <v>2525272</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I110" s="3">
-        <v>46057.7412615741</v>
+        <v>46203.7916666667</v>
       </c>
       <c r="J110" s="3">
-        <v>46056.6210300926</v>
+        <v>46126.7441782407</v>
       </c>
       <c r="K110" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L110" s="0" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="M110" s="3">
-        <v>46056.3662615741</v>
-      </c>
-      <c r="N110" s="3">
-        <v>46057.7412615741</v>
-      </c>
+        <v>46058.2883101852</v>
+      </c>
+      <c r="N110" s="3"/>
       <c r="O110" s="3"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>2523635</v>
+        <v>2524577</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="G111" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="H111" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="H111" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I111" s="3">
-        <v>46059.4164236111</v>
-      </c>
+      <c r="I111" s="3"/>
       <c r="J111" s="3">
-        <v>46055.6034837963</v>
+        <v>46267.4298180903</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M111" s="3">
-        <v>46055.4997569444</v>
-      </c>
-      <c r="N111" s="3">
-        <v>46059.4164236111</v>
-      </c>
+        <v>46056.697349537</v>
+      </c>
+      <c r="N111" s="3"/>
       <c r="O111" s="3"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>2523602</v>
+        <v>2524373</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>204</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I112" s="3">
-        <v>46093.6246643519</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="J112" s="3">
-        <v>46056.5784027778</v>
+        <v>46056.6543865741</v>
       </c>
       <c r="K112" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="M112" s="3">
-        <v>46055.4788310185</v>
+        <v>46056.5937847222</v>
       </c>
       <c r="N112" s="3">
-        <v>46093.6246643519</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="O112" s="3"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>2521645</v>
+        <v>2524062</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>205</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="I113" s="3">
-        <v>46062.5</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="J113" s="3">
-        <v>46050.3426763542</v>
+        <v>46056.6210300926</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M113" s="3">
-        <v>46049.7714236111</v>
-      </c>
-      <c r="N113" s="3"/>
+        <v>46056.3662615741</v>
+      </c>
+      <c r="N113" s="3">
+        <v>46057.7412615741</v>
+      </c>
       <c r="O113" s="3"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>2521079</v>
+        <v>2523635</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>206</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I114" s="3">
-        <v>46052.6666666667</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="J114" s="3">
-        <v>46056.6197800926</v>
+        <v>46055.6034837963</v>
       </c>
       <c r="K114" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L114" s="0" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="M114" s="3">
-        <v>46048.7684490741</v>
+        <v>46055.4997569444</v>
       </c>
       <c r="N114" s="3">
-        <v>46061.6309722222</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="O114" s="3"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>2520048</v>
+        <v>2523602</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>207</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I115" s="3">
-        <v>46057.5</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="J115" s="3">
-        <v>46052.5774305556</v>
+        <v>46056.5784027778</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="M115" s="3">
-        <v>46045.3325578704</v>
+        <v>46055.4788310185</v>
       </c>
       <c r="N115" s="3">
-        <v>46057.5</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="O115" s="3"/>
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>2519904</v>
+        <v>2521645</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>208</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="I116" s="3">
-        <v>46084.7217939815</v>
+        <v>46062.5</v>
       </c>
       <c r="J116" s="3">
-        <v>46044.7413888889</v>
+        <v>46050.3426763542</v>
       </c>
       <c r="K116" s="0" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="L116" s="0" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="M116" s="3">
-        <v>46044.6384606482</v>
-      </c>
-      <c r="N116" s="3">
-        <v>46084.7217939815</v>
-      </c>
+        <v>46049.7714236111</v>
+      </c>
+      <c r="N116" s="3"/>
       <c r="O116" s="3"/>
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>2519523</v>
+        <v>2521079</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>209</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I117" s="3">
-        <v>46076.5902777778</v>
+        <v>46052.6666666667</v>
       </c>
       <c r="J117" s="3">
-        <v>46048.4589814815</v>
+        <v>46056.6197800926</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="M117" s="3">
-        <v>46043.7362847222</v>
+        <v>46048.7684490741</v>
       </c>
       <c r="N117" s="3">
-        <v>46077.380775463</v>
+        <v>46061.6309722222</v>
       </c>
       <c r="O117" s="3"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>2519383</v>
+        <v>2520048</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>210</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I118" s="3">
-        <v>46076.399224537</v>
+        <v>46057.5</v>
       </c>
       <c r="J118" s="3">
-        <v>46048.4599305556</v>
+        <v>46052.5774305556</v>
       </c>
       <c r="K118" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L118" s="0" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="M118" s="3">
-        <v>46043.6075578704</v>
+        <v>46045.3325578704</v>
       </c>
       <c r="N118" s="3">
-        <v>46076.399224537</v>
+        <v>46057.5</v>
       </c>
       <c r="O118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>2519284</v>
+        <v>2519904</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I119" s="3">
-        <v>46049.3982986111</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="J119" s="3">
-        <v>46043.742337963</v>
+        <v>46044.7413888889</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="M119" s="3">
-        <v>46043.4816319444</v>
+        <v>46044.6384606482</v>
       </c>
       <c r="N119" s="3">
-        <v>46049.3982986111</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="O119" s="3"/>
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <v>2518650</v>
+        <v>2519523</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I120" s="3">
-        <v>46072.3536921296</v>
+        <v>46076.5902777778</v>
       </c>
       <c r="J120" s="3">
-        <v>46043.8185648148</v>
+        <v>46048.4589814815</v>
       </c>
       <c r="K120" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L120" s="0" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="M120" s="3">
-        <v>46042.3536921296</v>
+        <v>46043.7362847222</v>
       </c>
       <c r="N120" s="3">
-        <v>46080.437025463</v>
+        <v>46077.380775463</v>
       </c>
       <c r="O120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <v>2513117</v>
+        <v>2519383</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I121" s="3">
-        <v>46031.4922800926</v>
+        <v>46076.399224537</v>
       </c>
       <c r="J121" s="3">
-        <v>46028.3500347222</v>
+        <v>46048.4599305556</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="M121" s="3">
-        <v>46027.6381134259</v>
+        <v>46043.6075578704</v>
       </c>
       <c r="N121" s="3">
-        <v>46031.4922800926</v>
+        <v>46076.399224537</v>
       </c>
       <c r="O121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <v>2512883</v>
+        <v>2519284</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I122" s="3">
-        <v>46037.6340972222</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="J122" s="3">
-        <v>46129.4199421296</v>
+        <v>46043.742337963</v>
       </c>
       <c r="K122" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L122" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M122" s="3">
-        <v>46027.4049305556</v>
+        <v>46043.4816319444</v>
       </c>
       <c r="N122" s="3">
-        <v>46141.6335300926</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="O122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <v>2512542</v>
+        <v>2518650</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>214</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I123" s="3">
-        <v>46036.5</v>
+        <v>46072.3536921296</v>
       </c>
       <c r="J123" s="3">
-        <v>46024.5900925926</v>
+        <v>46043.8185648148</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="M123" s="3">
-        <v>46022.6836342593</v>
+        <v>46042.3536921296</v>
       </c>
       <c r="N123" s="3">
-        <v>46036.5</v>
+        <v>46080.437025463</v>
       </c>
       <c r="O123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <v>2512541</v>
+        <v>2513117</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>215</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I124" s="3">
-        <v>46036.5</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="J124" s="3">
-        <v>46022.7128356481</v>
+        <v>46028.3500347222</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L124" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M124" s="3">
-        <v>46022.6762615741</v>
+        <v>46027.6381134259</v>
       </c>
       <c r="N124" s="3">
-        <v>46036.5</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="O124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <v>2509014</v>
+        <v>2512883</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>216</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I125" s="3">
-        <v>46044.7250578704</v>
+        <v>46037.6340972222</v>
       </c>
       <c r="J125" s="3">
-        <v>46022.6138541667</v>
+        <v>46129.4199421296</v>
       </c>
       <c r="K125" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="M125" s="3">
-        <v>46008.454224537</v>
+        <v>46027.4049305556</v>
       </c>
       <c r="N125" s="3">
-        <v>46045.4708564815</v>
+        <v>46141.6335300926</v>
       </c>
       <c r="O125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <v>2506714</v>
+        <v>2512542</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>217</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I126" s="3">
-        <v>46038.7073032407</v>
+        <v>46036.5</v>
       </c>
       <c r="J126" s="3">
-        <v>46044.7372337963</v>
+        <v>46024.5900925926</v>
       </c>
       <c r="K126" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="M126" s="3">
-        <v>46002.4364699074</v>
+        <v>46022.6836342593</v>
       </c>
       <c r="N126" s="3">
-        <v>46038.7073032407</v>
+        <v>46036.5</v>
       </c>
       <c r="O126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <v>2506599</v>
+        <v>2512541</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>218</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I127" s="3">
-        <v>46037.61375</v>
+        <v>46036.5</v>
       </c>
       <c r="J127" s="3">
-        <v>46052.3252083333</v>
+        <v>46022.7128356481</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="M127" s="3">
-        <v>46002.3429166667</v>
+        <v>46022.6762615741</v>
       </c>
       <c r="N127" s="3">
-        <v>46037.61375</v>
+        <v>46036.5</v>
       </c>
       <c r="O127" s="3"/>
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <v>2506311</v>
+        <v>2509014</v>
       </c>
       <c r="B128" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C128" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="D128" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="F128" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G128" s="0" t="s">
         <v>219</v>
       </c>
-      <c r="C128" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D128" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="E128" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="F128" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="G128" s="0" t="s">
-        <v>220</v>
-      </c>
       <c r="H128" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I128" s="3">
-        <v>46013.7291666667</v>
+        <v>46044.7250578704</v>
       </c>
       <c r="J128" s="3">
-        <v>46013.461875</v>
+        <v>46022.6138541667</v>
       </c>
       <c r="K128" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L128" s="0" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="M128" s="3">
-        <v>46001.5219328704</v>
+        <v>46008.454224537</v>
       </c>
       <c r="N128" s="3">
-        <v>46013.7291666667</v>
+        <v>46045.4708564815</v>
       </c>
       <c r="O128" s="3"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <v>2506102</v>
+        <v>2506714</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I129" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I129" s="3">
+        <v>46038.7073032407</v>
+      </c>
       <c r="J129" s="3">
-        <v>46241.5032638889</v>
+        <v>46044.7372337963</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="M129" s="3">
-        <v>46001.3800578704</v>
-      </c>
-      <c r="N129" s="3"/>
+        <v>46002.4364699074</v>
+      </c>
+      <c r="N129" s="3">
+        <v>46038.7073032407</v>
+      </c>
       <c r="O129" s="3"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <v>2502589</v>
+        <v>2506599</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I130" s="3">
-        <v>46029.6634375</v>
+        <v>46037.61375</v>
       </c>
       <c r="J130" s="3">
-        <v>46014.6931018519</v>
+        <v>46052.3252083333</v>
       </c>
       <c r="K130" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L130" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M130" s="3">
-        <v>45993.3791087963</v>
+        <v>46002.3429166667</v>
       </c>
       <c r="N130" s="3">
-        <v>46029.6634375</v>
+        <v>46037.61375</v>
       </c>
       <c r="O130" s="3"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <v>2502438</v>
+        <v>2506311</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>114</v>
+        <v>222</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I131" s="3">
-        <v>46037.3801388889</v>
+        <v>46013.7291666667</v>
       </c>
       <c r="J131" s="3">
-        <v>45996.4823032407</v>
+        <v>46013.461875</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="M131" s="3">
-        <v>45992.7134722222</v>
+        <v>46001.5219328704</v>
       </c>
       <c r="N131" s="3">
-        <v>46037.3801388889</v>
+        <v>46013.7291666667</v>
       </c>
       <c r="O131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <v>2501349</v>
+        <v>2506102</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I132" s="3">
-        <v>46069.7381944444</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I132" s="3"/>
       <c r="J132" s="3">
-        <v>46069.3651388889</v>
+        <v>46241.5032638889</v>
       </c>
       <c r="K132" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L132" s="0" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M132" s="3">
-        <v>45989.0365856482</v>
-      </c>
-      <c r="N132" s="3">
-        <v>46069.7381944444</v>
-      </c>
+        <v>46001.3800578704</v>
+      </c>
+      <c r="N132" s="3"/>
       <c r="O132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <v>2500635</v>
+        <v>2502589</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>226</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I133" s="3">
-        <v>46024.4633796296</v>
+        <v>46029.6634375</v>
       </c>
       <c r="J133" s="3">
-        <v>46027.3611111111</v>
+        <v>46014.6931018519</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M133" s="3">
-        <v>45987.671712963</v>
+        <v>45993.3791087963</v>
       </c>
       <c r="N133" s="3">
-        <v>46024.4633796296</v>
+        <v>46029.6634375</v>
       </c>
       <c r="O133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <v>2498066</v>
+        <v>2502438</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>189</v>
+        <v>117</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>227</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I134" s="3">
-        <v>46073.7916666667</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="J134" s="3">
-        <v>46126.6953240741</v>
+        <v>45996.4823032407</v>
       </c>
       <c r="K134" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L134" s="0" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M134" s="3">
-        <v>45979.750162037</v>
-      </c>
-      <c r="N134" s="3"/>
+        <v>45992.7134722222</v>
+      </c>
+      <c r="N134" s="3">
+        <v>46037.3801388889</v>
+      </c>
       <c r="O134" s="3"/>
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <v>2494282</v>
+        <v>2501349</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>128</v>
+        <v>193</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E135" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>228</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I135" s="3">
-        <v>45986.48125</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="J135" s="3">
-        <v>45988.567025463</v>
+        <v>46069.3651388889</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M135" s="3">
-        <v>45971.4792824074</v>
+        <v>45989.0365856482</v>
       </c>
       <c r="N135" s="3">
-        <v>45986.4815625</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="O135" s="3"/>
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <v>2494179</v>
+        <v>2500635</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="E136" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F136" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G136" s="0" t="s">
         <v>229</v>
       </c>
-      <c r="F136" s="0" t="s">
-        <v>230</v>
-      </c>
-      <c r="G136" s="0" t="s">
-        <v>231</v>
-      </c>
       <c r="H136" s="0" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I136" s="3">
-        <v>46002.675775463</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="J136" s="3">
-        <v>46044.7370486111</v>
+        <v>46027.3611111111</v>
       </c>
       <c r="K136" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L136" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M136" s="3">
-        <v>45971.4049421296</v>
+        <v>45987.671712963</v>
       </c>
       <c r="N136" s="3">
-        <v>46002.675775463</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="O136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <v>2490911</v>
+        <v>2498066</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="E137" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="I137" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I137" s="3">
+        <v>46073.7916666667</v>
+      </c>
       <c r="J137" s="3">
-        <v>46182.7633796296</v>
+        <v>46126.6953240741</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="M137" s="3">
-        <v>45961.5760300926</v>
+        <v>45979.750162037</v>
       </c>
       <c r="N137" s="3"/>
       <c r="O137" s="3"/>
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <v>2490185</v>
+        <v>2494282</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
       <c r="E138" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I138" s="3">
-        <v>46203.7916666667</v>
+        <v>45986.48125</v>
       </c>
       <c r="J138" s="3">
-        <v>46051.4836111111</v>
+        <v>45988.567025463</v>
       </c>
       <c r="K138" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L138" s="0" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="M138" s="3">
-        <v>45960.3928819444</v>
-      </c>
-      <c r="N138" s="3"/>
+        <v>45971.4792824074</v>
+      </c>
+      <c r="N138" s="3">
+        <v>45986.4815625</v>
+      </c>
       <c r="O138" s="3"/>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>2489016</v>
+        <v>2494179</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>128</v>
+        <v>193</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I139" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I139" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="J139" s="3">
-        <v>45958.3906481481</v>
+        <v>46044.7370486111</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="M139" s="3">
-        <v>45957.7253009259</v>
-      </c>
-      <c r="N139" s="3"/>
+        <v>45971.4049421296</v>
+      </c>
+      <c r="N139" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="O139" s="3"/>
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>2485386</v>
+        <v>2490911</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E140" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="I140" s="3">
-        <v>46386.7916666667</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="I140" s="3"/>
       <c r="J140" s="3">
-        <v>46182.7639236111</v>
+        <v>46182.7633796296</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L140" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M140" s="3">
-        <v>45947.7000115741</v>
+        <v>45961.5760300926</v>
       </c>
       <c r="N140" s="3"/>
       <c r="O140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>2483420</v>
+        <v>2490185</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="E141" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="I141" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I141" s="3">
+        <v>46203.7916666667</v>
+      </c>
       <c r="J141" s="3">
-        <v>46140.3843518519</v>
+        <v>46051.4836111111</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M141" s="3">
-        <v>45944.6603819444</v>
+        <v>45960.3928819444</v>
       </c>
       <c r="N141" s="3"/>
       <c r="O141" s="3"/>
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <v>2474606</v>
+        <v>2489016</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>17</v>
+        <v>238</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>239</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I142" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I142" s="3"/>
       <c r="J142" s="3">
-        <v>45966.4450925926</v>
+        <v>45958.3906481481</v>
       </c>
       <c r="K142" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L142" s="0" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M142" s="3">
-        <v>45924.4486921296</v>
-      </c>
-      <c r="N142" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>45957.7253009259</v>
+      </c>
+      <c r="N142" s="3"/>
       <c r="O142" s="3"/>
     </row>
     <row r="143">
       <c r="A143" s="2">
-        <v>2470122</v>
+        <v>2485386</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>240</v>
+        <v>117</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>240</v>
+        <v>117</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E143" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="I143" s="3"/>
+        <v>122</v>
+      </c>
+      <c r="I143" s="3">
+        <v>46386.7916666667</v>
+      </c>
       <c r="J143" s="3">
-        <v>46204.3270601852</v>
+        <v>46182.7639236111</v>
       </c>
       <c r="K143" s="0" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="L143" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M143" s="3">
-        <v>45912.5572222222</v>
+        <v>45947.7000115741</v>
       </c>
       <c r="N143" s="3"/>
       <c r="O143" s="3"/>
     </row>
     <row r="144">
       <c r="A144" s="2">
-        <v>2463515</v>
+        <v>2483420</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E144" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="I144" s="3"/>
       <c r="J144" s="3">
-        <v>45910.4755555556</v>
+        <v>46140.3843518519</v>
       </c>
       <c r="K144" s="0" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="L144" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M144" s="3">
-        <v>45897.4218865741</v>
+        <v>45944.6603819444</v>
       </c>
       <c r="N144" s="3"/>
       <c r="O144" s="3"/>
     </row>
     <row r="145">
       <c r="A145" s="2">
-        <v>2461703</v>
+        <v>2474606</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>232</v>
+        <v>43</v>
       </c>
       <c r="E145" s="0" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="I145" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="I145" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="J145" s="3">
-        <v>46003.3706828704</v>
+        <v>45966.4450925926</v>
       </c>
       <c r="K145" s="0" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="L145" s="0" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="M145" s="3">
-        <v>45894.4525347222</v>
-      </c>
-      <c r="N145" s="3"/>
+        <v>45924.4486921296</v>
+      </c>
+      <c r="N145" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="O145" s="3"/>
     </row>
     <row r="146">
       <c r="A146" s="2">
-        <v>2459339</v>
+        <v>2470122</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>128</v>
+        <v>243</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>128</v>
+        <v>243</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E146" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>139</v>
+        <v>32</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>119</v>
+        <v>245</v>
       </c>
       <c r="I146" s="3"/>
       <c r="J146" s="3">
-        <v>46140.3839930556</v>
+        <v>46204.3270601852</v>
       </c>
       <c r="K146" s="0" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="L146" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M146" s="3">
-        <v>45887.7442361111</v>
+        <v>45912.5572222222</v>
       </c>
       <c r="N146" s="3"/>
       <c r="O146" s="3"/>
     </row>
     <row r="147">
       <c r="A147" s="2">
-        <v>2456538</v>
+        <v>2463515</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>98</v>
+        <v>246</v>
       </c>
       <c r="E147" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>247</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I147" s="3"/>
       <c r="J147" s="3">
-        <v>46126.7428356481</v>
+        <v>45910.4755555556</v>
       </c>
       <c r="K147" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L147" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M147" s="3">
-        <v>45880.6643055556</v>
+        <v>45897.4218865741</v>
       </c>
       <c r="N147" s="3"/>
       <c r="O147" s="3"/>
     </row>
     <row r="148">
       <c r="A148" s="2">
-        <v>2449811</v>
+        <v>2461703</v>
       </c>
       <c r="B148" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C148" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G148" s="0" t="s">
         <v>248</v>
       </c>
-      <c r="C148" s="0" t="s">
-        <v>248</v>
-      </c>
-      <c r="D148" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="E148" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="F148" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="G148" s="0" t="s">
-        <v>249</v>
-      </c>
       <c r="H148" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I148" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="I148" s="3"/>
       <c r="J148" s="3">
-        <v>45870.3628819444</v>
+        <v>46003.3706828704</v>
       </c>
       <c r="K148" s="0" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="L148" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="M148" s="3">
-        <v>45862.6188888889</v>
-      </c>
-      <c r="N148" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>45894.4525347222</v>
+      </c>
+      <c r="N148" s="3"/>
       <c r="O148" s="3"/>
     </row>
     <row r="149">
       <c r="A149" s="2">
-        <v>2442028</v>
+        <v>2459339</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="E149" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="I149" s="3"/>
       <c r="J149" s="3">
-        <v>46126.7431134259</v>
+        <v>46140.3839930556</v>
       </c>
       <c r="K149" s="0" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="L149" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M149" s="3">
-        <v>45842.317025463</v>
+        <v>45887.7442361111</v>
       </c>
       <c r="N149" s="3"/>
       <c r="O149" s="3"/>
     </row>
     <row r="150">
       <c r="A150" s="2">
-        <v>2439691</v>
+        <v>2456538</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>44</v>
+        <v>17</v>
+      </c>
+      <c r="F150" s="0" t="s">
+        <v>87</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I150" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I150" s="3"/>
       <c r="J150" s="3">
-        <v>45838.6211342593</v>
+        <v>46126.7428356481</v>
       </c>
       <c r="K150" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L150" s="0" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="M150" s="3">
-        <v>45838.3761921296</v>
-      </c>
-      <c r="N150" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>45880.6643055556</v>
+      </c>
+      <c r="N150" s="3"/>
       <c r="O150" s="3"/>
     </row>
     <row r="151">
       <c r="A151" s="2">
-        <v>2437239</v>
+        <v>2449811</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I151" s="3">
-        <v>45870.3600462963</v>
+        <v>45875.3688888889</v>
       </c>
       <c r="J151" s="3">
-        <v>45841.7026091435</v>
+        <v>45870.3628819444</v>
       </c>
       <c r="K151" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L151" s="0" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="M151" s="3">
-        <v>45831.6933796296</v>
+        <v>45862.6188888889</v>
       </c>
       <c r="N151" s="3">
-        <v>45870.3600462963</v>
+        <v>45875.3688888889</v>
       </c>
       <c r="O151" s="3"/>
     </row>
     <row r="152">
       <c r="A152" s="2">
-        <v>2436707</v>
+        <v>2442028</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E152" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G152" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="H152" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="I152" s="3"/>
+      <c r="J152" s="3">
+        <v>46126.7431134259</v>
+      </c>
+      <c r="K152" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="L152" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="M152" s="3">
+        <v>45842.317025463</v>
+      </c>
+      <c r="N152" s="3"/>
+      <c r="O152" s="3"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2">
+        <v>2439691</v>
+      </c>
+      <c r="B153" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="C153" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D153" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E153" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G153" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="H153" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="I153" s="3">
+        <v>45852.3770833333</v>
+      </c>
+      <c r="J153" s="3">
+        <v>45838.6211342593</v>
+      </c>
+      <c r="K153" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="L153" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="M153" s="3">
+        <v>45838.3761921296</v>
+      </c>
+      <c r="N153" s="3">
+        <v>45852.3770833333</v>
+      </c>
+      <c r="O153" s="3"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2">
+        <v>2437239</v>
+      </c>
+      <c r="B154" s="0" t="s">
         <v>256</v>
       </c>
-      <c r="H152" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I152" s="3">
+      <c r="C154" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="D154" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E154" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="F154" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="G154" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="H154" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="I154" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="J154" s="3">
+        <v>45841.7026091435</v>
+      </c>
+      <c r="K154" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="L154" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="M154" s="3">
+        <v>45831.6933796296</v>
+      </c>
+      <c r="N154" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="O154" s="3"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2">
+        <v>2436707</v>
+      </c>
+      <c r="B155" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="C155" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="D155" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F155" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G155" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="H155" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="I155" s="3">
         <v>45835.7284722222</v>
       </c>
-      <c r="J152" s="3">
+      <c r="J155" s="3">
         <v>46126.7436921296</v>
       </c>
-      <c r="K152" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="L152" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="M152" s="3">
+      <c r="K155" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="L155" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="M155" s="3">
         <v>45828.8276273148</v>
       </c>
-      <c r="N152" s="3">
+      <c r="N155" s="3">
         <v>45835.7288773148</v>
       </c>
-      <c r="O152" s="3"/>
+      <c r="O155" s="3"/>
     </row>
   </sheetData>
   <headerFooter/>

--- a/Solicitacoes.xlsx
+++ b/Solicitacoes.xlsx
@@ -59,30 +59,39 @@
     <t>Prazo desejado</t>
   </si>
   <si>
+    <t>COMPESAPREV.NIECIA</t>
+  </si>
+  <si>
+    <t>CORRECAO</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>Controle Financeiro</t>
+  </si>
+  <si>
+    <t>Calculo da mensalidade sem redistribuição entre o grupo familiar</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Suporte nível II</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>COMPESAPREV.JULIA</t>
   </si>
   <si>
-    <t>CORRECAO</t>
-  </si>
-  <si>
-    <t>AG</t>
-  </si>
-  <si>
     <t>ADM</t>
   </si>
   <si>
     <t>HOMOLOGAÇÃO - Atualização do ambiente de homologação para a release 3.65.26</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
-    <t>Suporte nível II</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>HELPDESK - CUIDAR</t>
   </si>
   <si>
@@ -104,81 +113,78 @@
     <t>Eventos autorizados automaticamente ficam "Em análise" no Conecta até finalizar a regulação.</t>
   </si>
   <si>
+    <t>Niécia Morais</t>
+  </si>
+  <si>
+    <t>Erro na geração da limitação de cobrança de PF para o grupo Exames e Terapias</t>
+  </si>
+  <si>
+    <t>Verificando</t>
+  </si>
+  <si>
+    <t>ALEXIA.SANTOS</t>
+  </si>
+  <si>
+    <t>Processamento de Contas</t>
+  </si>
+  <si>
+    <t>Erro genérico no faturamento 210.PagamentoPrestadores</t>
+  </si>
+  <si>
+    <t>Homologando</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Códigos folhas gerados errados com mudança de módulo.</t>
+  </si>
+  <si>
+    <t>MICHEL.HERNANDES</t>
+  </si>
+  <si>
+    <t>Julia Albertim</t>
+  </si>
+  <si>
+    <t>CONFIGURAÇÃO</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>Remover permissão de administrador no web.config para usuários não autorizados</t>
+  </si>
+  <si>
+    <t>Liberado para cliente</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>AG - Erro ao importar Tabela Genérica (Aguardando Processamento)</t>
+  </si>
+  <si>
+    <t>Adm Operadora</t>
+  </si>
+  <si>
+    <t>CON - Impossibilidade adiconar corpo clínico</t>
+  </si>
+  <si>
+    <t>MOBE</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APP -  Erro no servidor / buscar dados</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>COMPESAPREV.NIECIA</t>
-  </si>
-  <si>
-    <t>Controle Financeiro</t>
-  </si>
-  <si>
-    <t>Erro na geração da limitação de cobrança de PF para o grupo Exames e Terapias</t>
-  </si>
-  <si>
-    <t>ALEXIA.SANTOS</t>
-  </si>
-  <si>
-    <t>Processamento de Contas</t>
-  </si>
-  <si>
-    <t>Erro genérico no faturamento 210.PagamentoPrestadores</t>
-  </si>
-  <si>
-    <t>Homologando</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Niécia Morais</t>
-  </si>
-  <si>
-    <t>Códigos folhas gerados errados com mudança de módulo.</t>
-  </si>
-  <si>
-    <t>MICHEL.HERNANDES</t>
-  </si>
-  <si>
-    <t>Julia Albertim</t>
-  </si>
-  <si>
-    <t>CONFIGURAÇÃO</t>
-  </si>
-  <si>
-    <t>Web</t>
-  </si>
-  <si>
-    <t>Remover permissão de administrador no web.config para usuários não autorizados</t>
-  </si>
-  <si>
-    <t>Liberado para cliente</t>
-  </si>
-  <si>
-    <t>Resolvido</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>AG - Erro ao importar Tabela Genérica (Aguardando Processamento)</t>
-  </si>
-  <si>
-    <t>Adm Operadora</t>
-  </si>
-  <si>
-    <t>CON - Impossibilidade adiconar corpo clínico</t>
-  </si>
-  <si>
-    <t>MOBE</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APP -  Erro no servidor / buscar dados</t>
-  </si>
-  <si>
     <t>ROGERIO.ALMEIDA</t>
   </si>
   <si>
@@ -230,7 +236,7 @@
     <t>INFORMATIVOS CONECTA - Como vincular imagem</t>
   </si>
   <si>
-    <t>Aguardando Revisão de código</t>
+    <t>Revisando</t>
   </si>
   <si>
     <t>Prestadores</t>
@@ -320,9 +326,6 @@
     <t>Erro na de geração do “Nosso Número” no boleto</t>
   </si>
   <si>
-    <t>Verificando</t>
-  </si>
-  <si>
     <t>Versão futura</t>
   </si>
   <si>
@@ -402,9 +405,6 @@
   </si>
   <si>
     <t>Os detalhes da CARTEIRINHA não está aparecendo para alguns beneficiários</t>
-  </si>
-  <si>
-    <t>Aguardando detalhamento</t>
   </si>
   <si>
     <t>Acesso rede credenciada com perfil de DEPENDENTE não traz resultados.</t>
@@ -848,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O155"/>
+  <dimension ref="A1:O156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1506990705218" customWidth="1"/>
@@ -858,7 +858,7 @@
     <col min="5" max="5" width="47.7084481375558" customWidth="1"/>
     <col min="6" max="6" width="24.124747140067" customWidth="1"/>
     <col min="7" max="7" width="115.814923967634" customWidth="1"/>
-    <col min="8" max="8" width="28.4032069614955" customWidth="1"/>
+    <col min="8" max="8" width="27.4691489083426" customWidth="1"/>
     <col min="9" max="9" width="17.2691879272461" customWidth="1"/>
     <col min="10" max="10" width="17.2691879272461" customWidth="1"/>
     <col min="11" max="11" width="14.5938720703125" customWidth="1"/>
@@ -917,7 +917,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2620239</v>
+        <v>2620853</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>15</v>
@@ -941,10 +941,10 @@
         <v>20</v>
       </c>
       <c r="I2" s="3">
-        <v>46297.626712963</v>
+        <v>46300.6124768518</v>
       </c>
       <c r="J2" s="3">
-        <v>46293.7100462963</v>
+        <v>46294.6958101852</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>21</v>
@@ -953,25 +953,25 @@
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>46293.7100462963</v>
+        <v>46294.6958101852</v>
       </c>
       <c r="N2" s="3">
-        <v>46297.626712963</v>
+        <v>46300.6124768518</v>
       </c>
       <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2619954</v>
+        <v>2620239</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>17</v>
@@ -986,538 +986,536 @@
         <v>20</v>
       </c>
       <c r="I3" s="3">
-        <v>46303.7183912037</v>
+        <v>46297.626712963</v>
       </c>
       <c r="J3" s="3">
-        <v>46293.489224537</v>
+        <v>46293.7100462963</v>
       </c>
       <c r="K3" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M3" s="3">
-        <v>46293.489224537</v>
+        <v>46293.7100462963</v>
       </c>
       <c r="N3" s="3">
-        <v>46303.7183912037</v>
+        <v>46297.626712963</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2619927</v>
+        <v>2619954</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="G4" s="0" t="s">
         <v>28</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>29</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="3">
-        <v>46295.42625</v>
+        <v>46303.7183912037</v>
       </c>
       <c r="J4" s="3">
-        <v>46293.4679166667</v>
+        <v>46293.489224537</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M4" s="3">
-        <v>46293.4679166667</v>
+        <v>46293.489224537</v>
       </c>
       <c r="N4" s="3">
-        <v>46295.42625</v>
+        <v>46303.7183912037</v>
       </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>2619693</v>
+        <v>2619927</v>
       </c>
       <c r="B5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="0" t="s">
+      <c r="G5" s="0" t="s">
         <v>32</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>33</v>
       </c>
       <c r="H5" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="3">
-        <v>46294.75</v>
+        <v>46303.6970833333</v>
       </c>
       <c r="J5" s="3">
-        <v>46293.4025881944</v>
+        <v>46294.7248677083</v>
       </c>
       <c r="K5" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M5" s="3">
-        <v>46290.7313310185</v>
+        <v>46293.4679166667</v>
       </c>
       <c r="N5" s="3">
-        <v>46296.6479976852</v>
-      </c>
-      <c r="O5" s="3">
-        <v>46294.75</v>
-      </c>
+        <v>46303.6970833333</v>
+      </c>
+      <c r="O5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>2619258</v>
+        <v>2619693</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>37</v>
-      </c>
       <c r="I6" s="3">
-        <v>46302.589837963</v>
+        <v>46296.6479976852</v>
       </c>
       <c r="J6" s="3">
-        <v>46293.3487384259</v>
+        <v>46294.5493055556</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M6" s="3">
-        <v>46290.3606712963</v>
+        <v>46290.7313310185</v>
       </c>
       <c r="N6" s="3">
-        <v>46302.589837963</v>
+        <v>46296.6479976852</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>2619015</v>
+        <v>2619258</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G7" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="3">
+        <v>46302.589837963</v>
+      </c>
+      <c r="J7" s="3">
+        <v>46293.3487384259</v>
+      </c>
+      <c r="K7" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="3">
-        <v>46295.4977546296</v>
-      </c>
-      <c r="J7" s="3">
-        <v>46293.7032986111</v>
-      </c>
-      <c r="K7" s="0" t="s">
-        <v>38</v>
-      </c>
       <c r="L7" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M7" s="3">
-        <v>46289.643587963</v>
+        <v>46290.3606712963</v>
       </c>
       <c r="N7" s="3">
-        <v>46295.4977546296</v>
+        <v>46302.589837963</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>2618956</v>
+        <v>2619015</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I8" s="3">
-        <v>46295.6236574074</v>
+        <v>46295.4977546296</v>
       </c>
       <c r="J8" s="3">
-        <v>46293.3764351852</v>
+        <v>46293.7032986111</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="M8" s="3">
-        <v>46289.6236574074</v>
-      </c>
-      <c r="N8" s="3"/>
+        <v>46289.643587963</v>
+      </c>
+      <c r="N8" s="3">
+        <v>46295.4977546296</v>
+      </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2618623</v>
+        <v>2618956</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G9" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="3">
+        <v>46295.6236574074</v>
+      </c>
+      <c r="J9" s="3">
+        <v>46293.3764351852</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="3">
-        <v>46294.7106365741</v>
-      </c>
-      <c r="J9" s="3">
-        <v>46293.385684375</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M9" s="3">
-        <v>46289.3773032407</v>
-      </c>
-      <c r="N9" s="3">
-        <v>46295.3625810185</v>
-      </c>
+        <v>46289.6236574074</v>
+      </c>
+      <c r="N9" s="3"/>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>2618403</v>
+        <v>2618623</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F10" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="H10" s="0" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I10" s="3">
-        <v>46294.5634259259</v>
+        <v>46295.3625810185</v>
       </c>
       <c r="J10" s="3">
-        <v>46293.749640544</v>
+        <v>46294.668900463</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="L10" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M10" s="3">
-        <v>46288.6467592593</v>
+        <v>46289.3773032407</v>
       </c>
       <c r="N10" s="3">
-        <v>46294.5634259259</v>
+        <v>46295.3625810185</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>2618370</v>
+        <v>2618403</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E11" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="0" t="s">
         <v>52</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>54</v>
       </c>
       <c r="H11" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I11" s="3">
-        <v>46290.5871296296</v>
+        <v>46294.5634259259</v>
       </c>
       <c r="J11" s="3">
-        <v>46289.6879962616</v>
+        <v>46293.749640544</v>
       </c>
       <c r="K11" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M11" s="3">
-        <v>46288.6287962963</v>
+        <v>46288.6467592593</v>
       </c>
       <c r="N11" s="3">
-        <v>46290.5871296296</v>
+        <v>46294.5634259259</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>2617933</v>
+        <v>2618370</v>
       </c>
       <c r="B12" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="0" t="s">
+      <c r="H12" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="3">
+        <v>46290.5871296296</v>
+      </c>
+      <c r="J12" s="3">
+        <v>46289.6879962616</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I12" s="3">
-        <v>46293.6666666667</v>
-      </c>
-      <c r="J12" s="3">
-        <v>46293.3910300926</v>
-      </c>
-      <c r="K12" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="L12" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M12" s="3">
-        <v>46287.7594097222</v>
+        <v>46288.6287962963</v>
       </c>
       <c r="N12" s="3">
-        <v>46293.6666666667</v>
+        <v>46290.5871296296</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>2617538</v>
+        <v>2617933</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I13" s="3">
-        <v>46290.7498263889</v>
+        <v>46293.6666666667</v>
       </c>
       <c r="J13" s="3">
-        <v>46288.4440509259</v>
+        <v>46293.3910300926</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L13" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M13" s="3">
-        <v>46287.4164930556</v>
+        <v>46287.7594097222</v>
       </c>
       <c r="N13" s="3">
-        <v>46290.7498263889</v>
+        <v>46293.6666666667</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>2617170</v>
+        <v>2617538</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>60</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I14" s="3">
-        <v>46290.4403703704</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="J14" s="3">
-        <v>46289.5649035069</v>
+        <v>46288.4440509259</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="L14" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M14" s="3">
-        <v>46286.5862037037</v>
+        <v>46287.4164930556</v>
       </c>
       <c r="N14" s="3">
-        <v>46290.4403703704</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2617057</v>
+        <v>2617170</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E15" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="0" t="s">
         <v>61</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>18</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>62</v>
@@ -1526,10 +1524,10 @@
         <v>20</v>
       </c>
       <c r="I15" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="J15" s="3">
-        <v>46286.5879513889</v>
+        <v>46289.5649035069</v>
       </c>
       <c r="K15" s="0" t="s">
         <v>21</v>
@@ -1538,43 +1536,43 @@
         <v>22</v>
       </c>
       <c r="M15" s="3">
-        <v>46286.4877199074</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="N15" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>2615970</v>
+        <v>2617057</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H16" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="J16" s="3">
-        <v>46287.3554017708</v>
+        <v>46286.5879513889</v>
       </c>
       <c r="K16" s="0" t="s">
         <v>21</v>
@@ -1583,298 +1581,298 @@
         <v>22</v>
       </c>
       <c r="M16" s="3">
-        <v>46282.5089930556</v>
+        <v>46286.4877199074</v>
       </c>
       <c r="N16" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>2615871</v>
+        <v>2615970</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I17" s="3">
-        <v>46286.4024189815</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="J17" s="3">
-        <v>46286.3450115741</v>
+        <v>46287.3554017708</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M17" s="3">
-        <v>46282.4440856481</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="N17" s="3">
-        <v>46286.4024189815</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>2615590</v>
+        <v>2615871</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>66</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I18" s="3">
-        <v>46287.5805092593</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="J18" s="3">
-        <v>46293.377662037</v>
+        <v>46286.3450115741</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="M18" s="3">
-        <v>46281.6638425926</v>
+        <v>46282.4440856481</v>
       </c>
       <c r="N18" s="3">
-        <v>46287.5805092593</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>2614686</v>
+        <v>2615590</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="G19" s="0" t="s">
         <v>68</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I19" s="3">
-        <v>46321.5908449074</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="J19" s="3">
-        <v>46282.4296635764</v>
+        <v>46293.377662037</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="M19" s="3">
-        <v>46280.4450115741</v>
+        <v>46281.6638425926</v>
       </c>
       <c r="N19" s="3">
-        <v>46321.5908449074</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>2614334</v>
+        <v>2614686</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G20" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I20" s="3">
-        <v>46283.5629166667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="J20" s="3">
-        <v>46283.4291666667</v>
+        <v>46282.4296635764</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="M20" s="3">
-        <v>46279.6749305556</v>
+        <v>46280.4450115741</v>
       </c>
       <c r="N20" s="3">
-        <v>46283.5629166667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>2614135</v>
+        <v>2614334</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="I21" s="3">
-        <v>46289.7291666667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="J21" s="3">
-        <v>46293.6142361111</v>
+        <v>46283.4291666667</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="M21" s="3">
-        <v>46279.5169097222</v>
+        <v>46279.6749305556</v>
       </c>
       <c r="N21" s="3">
-        <v>46289.7291666667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2613646</v>
+        <v>2614135</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F22" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="H22" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="I22" s="3">
-        <v>46289.3876041667</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="J22" s="3">
-        <v>46283.4346064815</v>
+        <v>46294.3620486111</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M22" s="3">
-        <v>46276.6376041667</v>
+        <v>46279.5169097222</v>
       </c>
       <c r="N22" s="3">
-        <v>46289.3876041667</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>2613202</v>
+        <v>2613646</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>75</v>
@@ -1883,403 +1881,403 @@
         <v>76</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I23" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="J23" s="3">
-        <v>46283.4707657407</v>
+        <v>46283.4346064815</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M23" s="3">
-        <v>46276.3827546296</v>
+        <v>46276.6376041667</v>
       </c>
       <c r="N23" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>2613026</v>
+        <v>2613202</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I24" s="3">
-        <v>46281.6747800926</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="J24" s="3">
-        <v>46287.6117592593</v>
+        <v>46283.4707657407</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M24" s="3">
-        <v>46275.6895601852</v>
+        <v>46276.3827546296</v>
       </c>
       <c r="N24" s="3">
-        <v>46281.6747800926</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>2612720</v>
+        <v>2613026</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I25" s="3">
-        <v>46316.6011689815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="J25" s="3">
-        <v>46279.4816185532</v>
+        <v>46287.6117592593</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="M25" s="3">
-        <v>46275.4553356481</v>
+        <v>46275.6895601852</v>
       </c>
       <c r="N25" s="3">
-        <v>46316.6011689815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>2611881</v>
+        <v>2612720</v>
       </c>
       <c r="B26" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="0" t="s">
-        <v>35</v>
-      </c>
       <c r="G26" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I26" s="3">
-        <v>46279.6652314815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="J26" s="3">
-        <v>46274.7389930556</v>
+        <v>46279.4816185532</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="M26" s="3">
-        <v>46273.7485648148</v>
+        <v>46275.4553356481</v>
       </c>
       <c r="N26" s="3">
-        <v>46279.6652314815</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>2611848</v>
+        <v>2611881</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I27" s="3">
-        <v>46287.4094675926</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="J27" s="3">
-        <v>46276.5914583333</v>
+        <v>46274.7389930556</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M27" s="3">
-        <v>46273.7127546296</v>
+        <v>46273.7485648148</v>
       </c>
       <c r="N27" s="3">
-        <v>46287.4094675926</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>2611692</v>
+        <v>2611848</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I28" s="3">
-        <v>46279.4554861111</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="J28" s="3">
-        <v>46273.637278588</v>
+        <v>46276.5914583333</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M28" s="3">
-        <v>46273.6013194444</v>
+        <v>46273.7127546296</v>
       </c>
       <c r="N28" s="3">
-        <v>46279.4554861111</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>2611552</v>
+        <v>2611692</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>83</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="I29" s="3">
-        <v>46275.4327083333</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="J29" s="3">
-        <v>46273.5743171296</v>
+        <v>46294.8010955671</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M29" s="3">
-        <v>46273.474375</v>
+        <v>46273.6013194444</v>
       </c>
       <c r="N29" s="3">
-        <v>46275.4327083333</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>2611551</v>
+        <v>2611552</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I30" s="3">
-        <v>46314.6183449074</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="J30" s="3">
-        <v>46274.3603356481</v>
+        <v>46273.5743171296</v>
       </c>
       <c r="K30" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="M30" s="3">
-        <v>46273.4725115741</v>
+        <v>46273.474375</v>
       </c>
       <c r="N30" s="3">
-        <v>46314.6183449074</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>2611539</v>
+        <v>2611551</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>86</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I31" s="3">
-        <v>46275.4227083333</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="J31" s="3">
-        <v>46274.3607986111</v>
+        <v>46274.3603356481</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="M31" s="3">
-        <v>46273.464375</v>
+        <v>46273.4725115741</v>
       </c>
       <c r="N31" s="3">
-        <v>46275.4227083333</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>2611521</v>
+        <v>2611539</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F32" s="0" t="s">
         <v>87</v>
@@ -2288,31 +2286,31 @@
         <v>88</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I32" s="3">
-        <v>46279.3705439815</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="J32" s="3">
-        <v>46273.7182003819</v>
+        <v>46274.3607986111</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="M32" s="3">
-        <v>46273.4538773148</v>
+        <v>46273.464375</v>
       </c>
       <c r="N32" s="3">
-        <v>46279.3705439815</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>2610876</v>
+        <v>2611521</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>15</v>
@@ -2321,25 +2319,25 @@
         <v>15</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H33" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I33" s="3">
-        <v>46276.3367592593</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="J33" s="3">
-        <v>46269.4406376505</v>
+        <v>46273.7182003819</v>
       </c>
       <c r="K33" s="0" t="s">
         <v>21</v>
@@ -2348,43 +2346,43 @@
         <v>22</v>
       </c>
       <c r="M33" s="3">
-        <v>46269.4200925926</v>
+        <v>46273.4538773148</v>
       </c>
       <c r="N33" s="3">
-        <v>46276.3367592593</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>2610030</v>
+        <v>2610876</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H34" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I34" s="3">
-        <v>46274.6271990741</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="J34" s="3">
-        <v>46268.3853071412</v>
+        <v>46269.4406376505</v>
       </c>
       <c r="K34" s="0" t="s">
         <v>21</v>
@@ -2393,16 +2391,16 @@
         <v>22</v>
       </c>
       <c r="M34" s="3">
-        <v>46267.7105324074</v>
+        <v>46269.4200925926</v>
       </c>
       <c r="N34" s="3">
-        <v>46274.6271990741</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>2609985</v>
+        <v>2610030</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>15</v>
@@ -2411,1561 +2409,1561 @@
         <v>15</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H35" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I35" s="3">
-        <v>46301.4629166667</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="J35" s="3">
-        <v>46267.6774134606</v>
+        <v>46268.3853071412</v>
       </c>
       <c r="K35" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="M35" s="3">
-        <v>46267.67125</v>
+        <v>46267.7105324074</v>
       </c>
       <c r="N35" s="3">
-        <v>46301.4629166667</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="O35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>2609883</v>
+        <v>2609985</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>93</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I36" s="3">
-        <v>46309.7050347222</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="J36" s="3">
-        <v>46280.4030439815</v>
+        <v>46267.6774134606</v>
       </c>
       <c r="K36" s="0" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="M36" s="3">
-        <v>46267.6217013889</v>
+        <v>46267.67125</v>
       </c>
       <c r="N36" s="3">
-        <v>46309.7050347222</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="O36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>2609551</v>
+        <v>2609883</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="F37" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="G37" s="0" t="s">
-        <v>96</v>
-      </c>
       <c r="H37" s="0" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I37" s="3">
-        <v>46273.6887962963</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="J37" s="3">
-        <v>46267.355462963</v>
+        <v>46280.4030439815</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="M37" s="3">
-        <v>46267.355462963</v>
+        <v>46267.6217013889</v>
       </c>
       <c r="N37" s="3">
-        <v>46273.6887962963</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="O37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>2609107</v>
+        <v>2609551</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="I38" s="3">
-        <v>46300.3339583333</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="J38" s="3">
-        <v>46293.378900463</v>
+        <v>46267.355462963</v>
       </c>
       <c r="K38" s="0" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="M38" s="3">
-        <v>46266.4797916667</v>
+        <v>46267.355462963</v>
       </c>
       <c r="N38" s="3">
-        <v>46300.3339583333</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="O38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2608731</v>
+        <v>2609107</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I39" s="3">
-        <v>46279.4280671296</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="J39" s="3">
-        <v>46289.5798690625</v>
+        <v>46293.378900463</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="M39" s="3">
-        <v>46265.6780671296</v>
+        <v>46266.4797916667</v>
       </c>
       <c r="N39" s="3">
-        <v>46298.2756365741</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="O39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>2608637</v>
+        <v>2608731</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I40" s="3">
-        <v>46304.6977777778</v>
+        <v>46298.2938888889</v>
       </c>
       <c r="J40" s="3">
-        <v>46293.6437731481</v>
+        <v>46294.5490856481</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="M40" s="3">
-        <v>46265.6144444444</v>
+        <v>46265.6780671296</v>
       </c>
       <c r="N40" s="3">
-        <v>46304.6977777778</v>
+        <v>46298.2938888889</v>
       </c>
       <c r="O40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>2607413</v>
+        <v>2608637</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>101</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="I41" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="I41" s="3">
+        <v>46304.6977777778</v>
+      </c>
       <c r="J41" s="3">
-        <v>46266.569212963</v>
+        <v>46293.6437731481</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="M41" s="3">
-        <v>46261.6163888889</v>
-      </c>
-      <c r="N41" s="3"/>
+        <v>46265.6144444444</v>
+      </c>
+      <c r="N41" s="3">
+        <v>46304.6977777778</v>
+      </c>
       <c r="O41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>2607198</v>
+        <v>2607413</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F42" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="H42" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="I42" s="3"/>
+      <c r="J42" s="3">
+        <v>46266.569212963</v>
+      </c>
+      <c r="K42" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="H42" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" s="3">
-        <v>46267.3546643518</v>
-      </c>
-      <c r="J42" s="3">
-        <v>46273.6204976852</v>
-      </c>
-      <c r="K42" s="0" t="s">
-        <v>47</v>
-      </c>
       <c r="L42" s="0" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="M42" s="3">
-        <v>46261.4379976852</v>
-      </c>
-      <c r="N42" s="3">
-        <v>46267.3546643518</v>
-      </c>
+        <v>46261.6163888889</v>
+      </c>
+      <c r="N42" s="3"/>
       <c r="O42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>2606003</v>
+        <v>2607198</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E43" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>105</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I43" s="3">
-        <v>46265.3599537037</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="J43" s="3">
-        <v>46259.4993506944</v>
+        <v>46273.6204976852</v>
       </c>
       <c r="K43" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L43" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M43" s="3">
-        <v>46259.443287037</v>
+        <v>46261.4379976852</v>
       </c>
       <c r="N43" s="3">
-        <v>46290.75</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="O43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>2604815</v>
+        <v>2606003</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>106</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I44" s="3">
-        <v>46296.563587963</v>
+        <v>46265.3599537037</v>
       </c>
       <c r="J44" s="3">
-        <v>46268.6781365741</v>
+        <v>46259.4993506944</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="M44" s="3">
-        <v>46255.4177546296</v>
+        <v>46259.443287037</v>
       </c>
       <c r="N44" s="3">
-        <v>46296.563587963</v>
+        <v>46290.75</v>
       </c>
       <c r="O44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>2604500</v>
+        <v>2604815</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>107</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I45" s="3">
-        <v>46260.4812268519</v>
+        <v>46296.563587963</v>
       </c>
       <c r="J45" s="3">
-        <v>46258.3485416667</v>
+        <v>46268.6781365741</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="M45" s="3">
-        <v>46254.6270601852</v>
+        <v>46255.4177546296</v>
       </c>
       <c r="N45" s="3">
-        <v>46260.4812268519</v>
+        <v>46296.563587963</v>
       </c>
       <c r="O45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>2603668</v>
+        <v>2604500</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F46" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="G46" s="0" t="s">
-        <v>109</v>
-      </c>
       <c r="H46" s="0" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I46" s="3">
-        <v>46259.3446296296</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="J46" s="3">
-        <v>46258.6426851852</v>
+        <v>46258.3485416667</v>
       </c>
       <c r="K46" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L46" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M46" s="3">
-        <v>46253.427962963</v>
+        <v>46254.6270601852</v>
       </c>
       <c r="N46" s="3">
-        <v>46290.75</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="O46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>2602388</v>
+        <v>2603668</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>110</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="I47" s="3">
-        <v>46255.4166666667</v>
+        <v>46259.3446296296</v>
       </c>
       <c r="J47" s="3">
-        <v>46253.4900231482</v>
+        <v>46258.6426851852</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L47" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M47" s="3">
-        <v>46251.5527777778</v>
+        <v>46253.427962963</v>
       </c>
       <c r="N47" s="3">
-        <v>46255.4166666667</v>
+        <v>46290.75</v>
       </c>
       <c r="O47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>2601999</v>
+        <v>2602388</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D48" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G48" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="E48" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="G48" s="0" t="s">
-        <v>112</v>
-      </c>
       <c r="H48" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="I48" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I48" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="J48" s="3">
-        <v>46266.6188194444</v>
+        <v>46253.4900231482</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="M48" s="3">
-        <v>46248.7351273148</v>
-      </c>
-      <c r="N48" s="3"/>
+        <v>46251.5527777778</v>
+      </c>
+      <c r="N48" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="O48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>2600778</v>
+        <v>2601999</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E49" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3">
-        <v>46274.3780324074</v>
+        <v>46266.6188194444</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M49" s="3">
-        <v>46246.7171759259</v>
+        <v>46248.7351273148</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>2599732</v>
+        <v>2600778</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="F50" s="0" t="s">
         <v>18</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I50" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="I50" s="3"/>
       <c r="J50" s="3">
-        <v>46248.3419117245</v>
+        <v>46274.3780324074</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="M50" s="3">
-        <v>46245.4849537037</v>
-      </c>
-      <c r="N50" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>46246.7171759259</v>
+      </c>
+      <c r="N50" s="3"/>
       <c r="O50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>2598987</v>
+        <v>2599732</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F51" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G51" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="G51" s="0" t="s">
-        <v>120</v>
-      </c>
       <c r="H51" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I51" s="3">
-        <v>46254.6856134259</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="J51" s="3">
-        <v>46251.536875</v>
+        <v>46248.3419117245</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M51" s="3">
-        <v>46244.4564467593</v>
+        <v>46245.4849537037</v>
       </c>
       <c r="N51" s="3">
-        <v>46254.6856134259</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="O51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>2598910</v>
+        <v>2598987</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>121</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="I52" s="3">
-        <v>46254.6386574074</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="J52" s="3">
-        <v>46248.4760674769</v>
+        <v>46251.536875</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M52" s="3">
-        <v>46244.4094907407</v>
+        <v>46244.4564467593</v>
       </c>
       <c r="N52" s="3">
-        <v>46261.6103125</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="O52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>2598767</v>
+        <v>2598910</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C53" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="G53" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="H53" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="D53" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G53" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="H53" s="0" t="s">
-        <v>37</v>
-      </c>
       <c r="I53" s="3">
-        <v>46247.6666666667</v>
+        <v>46254.6386574074</v>
       </c>
       <c r="J53" s="3">
-        <v>46245.6608564815</v>
+        <v>46248.4760674769</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M53" s="3">
-        <v>46241.757962963</v>
+        <v>46244.4094907407</v>
       </c>
       <c r="N53" s="3">
-        <v>46247.6666666667</v>
+        <v>46261.6103125</v>
       </c>
       <c r="O53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>2597798</v>
+        <v>2598767</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E54" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I54" s="3">
-        <v>46290.75</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="J54" s="3">
-        <v>46273.4412384259</v>
+        <v>46245.6608564815</v>
       </c>
       <c r="K54" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M54" s="3">
-        <v>46240.4508912037</v>
+        <v>46241.757962963</v>
       </c>
       <c r="N54" s="3">
-        <v>46290.75</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="O54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>2597524</v>
+        <v>2597798</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E55" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I55" s="3">
-        <v>46267.0453356481</v>
+        <v>46290.75</v>
       </c>
       <c r="J55" s="3">
-        <v>46259.4158333333</v>
+        <v>46273.4412384259</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M55" s="3">
-        <v>46239.6925347222</v>
+        <v>46240.4508912037</v>
       </c>
       <c r="N55" s="3">
-        <v>46267.0453356481</v>
+        <v>46290.75</v>
       </c>
       <c r="O55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>2597515</v>
+        <v>2597524</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>129</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="I56" s="3">
-        <v>46266.4759953704</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="J56" s="3">
-        <v>46289.7039236111</v>
+        <v>46259.4158333333</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="M56" s="3">
-        <v>46239.6856134259</v>
+        <v>46239.6925347222</v>
       </c>
       <c r="N56" s="3">
-        <v>46266.4759953704</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="O56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>2597495</v>
+        <v>2597515</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H57" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I57" s="3">
-        <v>46252.3333333333</v>
+        <v>46271.3406597222</v>
       </c>
       <c r="J57" s="3">
-        <v>46241.6523302083</v>
+        <v>46294.7045655093</v>
       </c>
       <c r="K57" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="M57" s="3">
-        <v>46239.6802199074</v>
+        <v>46239.6856134259</v>
       </c>
       <c r="N57" s="3">
-        <v>46245.5968865741</v>
-      </c>
-      <c r="O57" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>46271.3406597222</v>
+      </c>
+      <c r="O57" s="3"/>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>2596882</v>
+        <v>2597495</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="I58" s="3">
-        <v>46280.3775578704</v>
+        <v>46252.3333333333</v>
       </c>
       <c r="J58" s="3">
-        <v>46267.6170023148</v>
+        <v>46241.6523302083</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="M58" s="3">
-        <v>46238.7108912037</v>
+        <v>46239.6802199074</v>
       </c>
       <c r="N58" s="3">
-        <v>46280.3775578704</v>
-      </c>
-      <c r="O58" s="3"/>
+        <v>46245.5968865741</v>
+      </c>
+      <c r="O58" s="3">
+        <v>46252.3333333333</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>2596538</v>
+        <v>2596882</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H59" s="0" t="s">
         <v>47</v>
       </c>
       <c r="I59" s="3">
-        <v>46273.960787037</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="J59" s="3">
-        <v>46286.3521412037</v>
+        <v>46267.6170023148</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="M59" s="3">
-        <v>46238.4644791667</v>
+        <v>46238.7108912037</v>
       </c>
       <c r="N59" s="3">
-        <v>46273.960787037</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="O59" s="3"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2596407</v>
+        <v>2596538</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I60" s="3">
-        <v>46248.6072106482</v>
+        <v>46273.960787037</v>
       </c>
       <c r="J60" s="3">
-        <v>46267.6164814815</v>
+        <v>46286.3521412037</v>
       </c>
       <c r="K60" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M60" s="3">
-        <v>46238.3780439815</v>
+        <v>46238.4644791667</v>
       </c>
       <c r="N60" s="3">
-        <v>46248.6072106482</v>
+        <v>46273.960787037</v>
       </c>
       <c r="O60" s="3"/>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>2595510</v>
+        <v>2596407</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I61" s="3">
-        <v>46240.4984606481</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="J61" s="3">
-        <v>46245.3667592593</v>
+        <v>46267.6164814815</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M61" s="3">
-        <v>46234.6442939815</v>
+        <v>46238.3780439815</v>
       </c>
       <c r="N61" s="3">
-        <v>46240.4984606481</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="O61" s="3"/>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>2595497</v>
+        <v>2595510</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I62" s="3">
-        <v>46240.4978240741</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="J62" s="3">
-        <v>46245.3669444444</v>
+        <v>46245.3667592593</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L62" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M62" s="3">
-        <v>46234.6436574074</v>
+        <v>46234.6442939815</v>
       </c>
       <c r="N62" s="3">
-        <v>46240.4978240741</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>2593529</v>
+        <v>2595497</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I63" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="J63" s="3">
-        <v>46233.4404570255</v>
+        <v>46245.3669444444</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L63" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M63" s="3">
-        <v>46231.6639930556</v>
+        <v>46234.6436574074</v>
       </c>
       <c r="N63" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="O63" s="3"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2593490</v>
+        <v>2593529</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I64" s="3">
-        <v>46239.6748032407</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="J64" s="3">
-        <v>46253.4905324074</v>
+        <v>46294.7638078704</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M64" s="3">
-        <v>46231.6518865741</v>
+        <v>46231.6639930556</v>
       </c>
       <c r="N64" s="3">
-        <v>46239.6748032407</v>
-      </c>
-      <c r="O64" s="3">
-        <v>46234.48125</v>
-      </c>
+        <v>46237.5806597222</v>
+      </c>
+      <c r="O64" s="3"/>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2593260</v>
+        <v>2593490</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I65" s="3">
-        <v>46241.6638888889</v>
+        <v>46239.6748032407</v>
       </c>
       <c r="J65" s="3">
-        <v>46267.614525463</v>
+        <v>46253.4905324074</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="M65" s="3">
-        <v>46231.435150463</v>
+        <v>46231.6518865741</v>
       </c>
       <c r="N65" s="3">
-        <v>46241.6638888889</v>
-      </c>
-      <c r="O65" s="3"/>
+        <v>46239.6748032407</v>
+      </c>
+      <c r="O65" s="3">
+        <v>46234.48125</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>2593216</v>
+        <v>2593260</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I66" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="I66" s="3">
+        <v>46241.6638888889</v>
+      </c>
       <c r="J66" s="3">
-        <v>46231.4047453704</v>
+        <v>46267.614525463</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="M66" s="3">
-        <v>46231.4011111111</v>
-      </c>
-      <c r="N66" s="3"/>
+        <v>46231.435150463</v>
+      </c>
+      <c r="N66" s="3">
+        <v>46241.6638888889</v>
+      </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>2592878</v>
+        <v>2593216</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F67" s="0" t="s">
         <v>24</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I67" s="3">
-        <v>46241.3504282407</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I67" s="3"/>
       <c r="J67" s="3">
-        <v>46230.6675740741</v>
+        <v>46231.4047453704</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="M67" s="3">
-        <v>46230.6004282407</v>
-      </c>
-      <c r="N67" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46231.4011111111</v>
+      </c>
+      <c r="N67" s="3"/>
       <c r="O67" s="3"/>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>2592468</v>
+        <v>2592878</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I68" s="3">
-        <v>46237.6038657407</v>
+        <v>46290.75</v>
       </c>
       <c r="J68" s="3">
-        <v>46240.6136738773</v>
+        <v>46294.7411689815</v>
       </c>
       <c r="K68" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M68" s="3">
-        <v>46227.7107060185</v>
+        <v>46230.6004282407</v>
       </c>
       <c r="N68" s="3">
-        <v>46293.6033680556</v>
+        <v>46290.75</v>
       </c>
       <c r="O68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>2591596</v>
+        <v>2592468</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H69" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I69" s="3">
-        <v>46238.7083333333</v>
+        <v>46237.6038657407</v>
       </c>
       <c r="J69" s="3">
-        <v>46267.3444803241</v>
+        <v>46240.6136738773</v>
       </c>
       <c r="K69" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M69" s="3">
-        <v>46226.4797916667</v>
+        <v>46227.7107060185</v>
       </c>
       <c r="N69" s="3">
-        <v>46282.6141435185</v>
+        <v>46293.6033680556</v>
       </c>
       <c r="O69" s="3"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>2591284</v>
+        <v>2591596</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>140</v>
@@ -3974,43 +3972,43 @@
         <v>140</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I70" s="3">
-        <v>46266.3384837963</v>
+        <v>46238.7083333333</v>
       </c>
       <c r="J70" s="3">
-        <v>46225.7002398495</v>
+        <v>46267.3444803241</v>
       </c>
       <c r="K70" s="0" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="M70" s="3">
-        <v>46225.6718171296</v>
+        <v>46226.4797916667</v>
       </c>
       <c r="N70" s="3">
-        <v>46266.3384837963</v>
+        <v>46282.6141435185</v>
       </c>
       <c r="O70" s="3"/>
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>2588490</v>
+        <v>2591284</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>140</v>
@@ -4019,521 +4017,521 @@
         <v>140</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I71" s="3">
-        <v>46230.722037037</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="J71" s="3">
-        <v>46231.4339699074</v>
+        <v>46225.7002398495</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="M71" s="3">
-        <v>46218.4928703704</v>
+        <v>46225.6718171296</v>
       </c>
       <c r="N71" s="3">
-        <v>46230.722037037</v>
+        <v>46266.3384837963</v>
       </c>
       <c r="O71" s="3"/>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>2588025</v>
+        <v>2588490</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="I72" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I72" s="3">
+        <v>46230.722037037</v>
+      </c>
       <c r="J72" s="3">
-        <v>46267.5903356482</v>
+        <v>46231.4339699074</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="M72" s="3">
-        <v>46217.612962963</v>
-      </c>
-      <c r="N72" s="3"/>
+        <v>46218.4928703704</v>
+      </c>
+      <c r="N72" s="3">
+        <v>46230.722037037</v>
+      </c>
       <c r="O72" s="3"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>2587849</v>
+        <v>2588025</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>17</v>
+        <v>149</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I73" s="3">
-        <v>46226.6083796296</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="I73" s="3"/>
       <c r="J73" s="3">
-        <v>46237.9144806713</v>
+        <v>46267.5903356482</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="M73" s="3">
-        <v>46217.4506597222</v>
-      </c>
-      <c r="N73" s="3">
-        <v>46226.6083796296</v>
-      </c>
+        <v>46217.612962963</v>
+      </c>
+      <c r="N73" s="3"/>
       <c r="O73" s="3"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2587713</v>
+        <v>2587849</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I74" s="3">
-        <v>46218.7408680556</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="J74" s="3">
-        <v>46230.4199074074</v>
+        <v>46237.9144806713</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M74" s="3">
-        <v>46217.3658680556</v>
+        <v>46217.4506597222</v>
       </c>
       <c r="N74" s="3">
-        <v>46218.7408680556</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="O74" s="3"/>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2587585</v>
+        <v>2587713</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I75" s="3">
-        <v>46220.6264583333</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="J75" s="3">
-        <v>46259.4474884259</v>
+        <v>46230.4199074074</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="M75" s="3">
-        <v>46216.7097916667</v>
+        <v>46217.3658680556</v>
       </c>
       <c r="N75" s="3">
-        <v>46220.6264583333</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="O75" s="3"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>2587006</v>
+        <v>2587585</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I76" s="3">
-        <v>46217.7289699074</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="J76" s="3">
-        <v>46227.4549884259</v>
+        <v>46259.4474884259</v>
       </c>
       <c r="K76" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M76" s="3">
-        <v>46213.7239236111</v>
+        <v>46216.7097916667</v>
       </c>
       <c r="N76" s="3">
-        <v>46217.7289699074</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="O76" s="3"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>2586984</v>
+        <v>2587006</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I77" s="3">
-        <v>46295.7416550926</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="J77" s="3">
-        <v>46273.4946180556</v>
+        <v>46227.4549884259</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="M77" s="3">
-        <v>46213.6971527778</v>
+        <v>46213.7239236111</v>
       </c>
       <c r="N77" s="3">
-        <v>46295.7416550926</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>2586910</v>
+        <v>2586984</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>157</v>
+        <v>24</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I78" s="3">
-        <v>46226.5833333333</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="J78" s="3">
-        <v>46230.4194212963</v>
+        <v>46273.4946180556</v>
       </c>
       <c r="K78" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M78" s="3">
-        <v>46213.6245833333</v>
+        <v>46213.6971527778</v>
       </c>
       <c r="N78" s="3">
-        <v>46226.5833333333</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="O78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2586651</v>
+        <v>2586910</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I79" s="3">
-        <v>46218.7157407407</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="J79" s="3">
-        <v>46213.3824074074</v>
+        <v>46230.4194212963</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="M79" s="3">
-        <v>46213.3824074074</v>
+        <v>46213.6245833333</v>
       </c>
       <c r="N79" s="3">
-        <v>46218.7157407407</v>
+        <v>46226.5833333333</v>
       </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>2586187</v>
+        <v>2586651</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>161</v>
+        <v>26</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="I80" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I80" s="3">
+        <v>46218.7157407407</v>
+      </c>
       <c r="J80" s="3">
-        <v>46219.3850231481</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="M80" s="3">
-        <v>46211.7697337963</v>
-      </c>
-      <c r="N80" s="3"/>
+        <v>46213.3824074074</v>
+      </c>
+      <c r="N80" s="3">
+        <v>46218.7157407407</v>
+      </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>2585888</v>
+        <v>2586187</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>157</v>
+        <v>69</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I81" s="3">
-        <v>46217.4119907407</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="I81" s="3"/>
       <c r="J81" s="3">
-        <v>46217.5003587963</v>
+        <v>46219.3850231481</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="M81" s="3">
-        <v>46211.4953240741</v>
-      </c>
-      <c r="N81" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46211.7697337963</v>
+      </c>
+      <c r="N81" s="3"/>
       <c r="O81" s="3"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>2585424</v>
+        <v>2585888</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="I82" s="3">
-        <v>46223.3927199074</v>
+        <v>46217.4119907407</v>
       </c>
       <c r="J82" s="3">
-        <v>46234.4964930556</v>
+        <v>46217.5003587963</v>
       </c>
       <c r="K82" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M82" s="3">
-        <v>46210.6427199074</v>
+        <v>46211.4953240741</v>
       </c>
       <c r="N82" s="3">
         <v>46290.75</v>
@@ -4542,746 +4540,746 @@
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>2584638</v>
+        <v>2585424</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="I83" s="3">
-        <v>46213.4171527778</v>
+        <v>46223.3927199074</v>
       </c>
       <c r="J83" s="3">
-        <v>46213.4090859607</v>
+        <v>46234.4964930556</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M83" s="3">
-        <v>46209.5016203704</v>
+        <v>46210.6427199074</v>
       </c>
       <c r="N83" s="3">
-        <v>46232.3874884259</v>
+        <v>46290.75</v>
       </c>
       <c r="O83" s="3"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>2584397</v>
+        <v>2584638</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="I84" s="3">
-        <v>46212.6757175926</v>
+        <v>46213.4171527778</v>
       </c>
       <c r="J84" s="3">
-        <v>46213.3741550926</v>
+        <v>46213.4090859607</v>
       </c>
       <c r="K84" s="0" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="L84" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M84" s="3">
-        <v>46209.3423842593</v>
+        <v>46209.5016203704</v>
       </c>
       <c r="N84" s="3">
-        <v>46212.6757175926</v>
+        <v>46232.3874884259</v>
       </c>
       <c r="O84" s="3"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>2584167</v>
+        <v>2584397</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I85" s="3">
-        <v>46246.7216435185</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="J85" s="3">
-        <v>46247.4396759259</v>
+        <v>46213.3741550926</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="M85" s="3">
-        <v>46206.6383101852</v>
+        <v>46209.3423842593</v>
       </c>
       <c r="N85" s="3">
-        <v>46246.7216435185</v>
+        <v>46212.6757175926</v>
       </c>
       <c r="O85" s="3"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>2583950</v>
+        <v>2584167</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I86" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I86" s="3">
+        <v>46246.7216435185</v>
+      </c>
       <c r="J86" s="3">
-        <v>46273.4100925926</v>
+        <v>46247.4396759259</v>
       </c>
       <c r="K86" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L86" s="0" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="M86" s="3">
-        <v>46206.4623148148</v>
-      </c>
-      <c r="N86" s="3"/>
+        <v>46206.6383101852</v>
+      </c>
+      <c r="N86" s="3">
+        <v>46246.7216435185</v>
+      </c>
       <c r="O86" s="3"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>2583447</v>
+        <v>2583950</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I87" s="3">
-        <v>46205.7916666667</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I87" s="3"/>
       <c r="J87" s="3">
-        <v>46265.3645138889</v>
+        <v>46273.4100925926</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="M87" s="3">
-        <v>46205.5752083333</v>
-      </c>
-      <c r="N87" s="3">
-        <v>46245.6724189815</v>
-      </c>
+        <v>46206.4623148148</v>
+      </c>
+      <c r="N87" s="3"/>
       <c r="O87" s="3"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>2583382</v>
+        <v>2583447</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I88" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I88" s="3">
+        <v>46205.7916666667</v>
+      </c>
       <c r="J88" s="3">
-        <v>46293.3798726852</v>
+        <v>46265.3645138889</v>
       </c>
       <c r="K88" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="M88" s="3">
-        <v>46205.4905092593</v>
-      </c>
-      <c r="N88" s="3"/>
+        <v>46205.5752083333</v>
+      </c>
+      <c r="N88" s="3">
+        <v>46245.6724189815</v>
+      </c>
       <c r="O88" s="3"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>2582452</v>
+        <v>2583382</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>23</v>
+        <v>170</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I89" s="3">
-        <v>46244.4166666667</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I89" s="3"/>
       <c r="J89" s="3">
-        <v>46204.7763078704</v>
+        <v>46293.3798726852</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="M89" s="3">
-        <v>46203.8250810185</v>
-      </c>
-      <c r="N89" s="3">
-        <v>46244.4166666667</v>
-      </c>
+        <v>46205.4905092593</v>
+      </c>
+      <c r="N89" s="3"/>
       <c r="O89" s="3"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2582352</v>
+        <v>2582452</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I90" s="3">
-        <v>46244.340775463</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="J90" s="3">
-        <v>46204.7761805556</v>
+        <v>46204.7763078704</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M90" s="3">
-        <v>46203.6741087963</v>
+        <v>46203.8250810185</v>
       </c>
       <c r="N90" s="3">
-        <v>46244.340775463</v>
+        <v>46244.4166666667</v>
       </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>2579299</v>
+        <v>2582352</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="E91" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I91" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I91" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="J91" s="3">
-        <v>46204.3277777778</v>
+        <v>46204.7761805556</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="M91" s="3">
-        <v>46196.4165162037</v>
-      </c>
-      <c r="N91" s="3"/>
+        <v>46203.6741087963</v>
+      </c>
+      <c r="N91" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>2576326</v>
+        <v>2579299</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>34</v>
+        <v>174</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>34</v>
+        <v>174</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E92" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I92" s="3">
-        <v>46192.7916666667</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I92" s="3"/>
       <c r="J92" s="3">
-        <v>46230.6812731481</v>
+        <v>46204.3277777778</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M92" s="3">
-        <v>46189.3995833333</v>
+        <v>46196.4165162037</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>2574153</v>
+        <v>2576326</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E93" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I93" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I93" s="3">
+        <v>46192.7916666667</v>
+      </c>
       <c r="J93" s="3">
-        <v>46204.3218402778</v>
+        <v>46230.6812731481</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M93" s="3">
-        <v>46183.4711226852</v>
+        <v>46189.3995833333</v>
       </c>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>2572707</v>
+        <v>2574153</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I94" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I94" s="3"/>
       <c r="J94" s="3">
-        <v>46188.4629166667</v>
+        <v>46204.3218402778</v>
       </c>
       <c r="K94" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L94" s="0" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="M94" s="3">
-        <v>46178.7298148148</v>
-      </c>
-      <c r="N94" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>46183.4711226852</v>
+      </c>
+      <c r="N94" s="3"/>
       <c r="O94" s="3"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>2570274</v>
+        <v>2572707</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>32</v>
+        <v>179</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I95" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I95" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="J95" s="3">
-        <v>46204.3220138889</v>
+        <v>46188.4629166667</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="M95" s="3">
-        <v>46171.6563773148</v>
-      </c>
-      <c r="N95" s="3"/>
+        <v>46178.7298148148</v>
+      </c>
+      <c r="N95" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="O95" s="3"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>2562116</v>
+        <v>2570274</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E96" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I96" s="3"/>
       <c r="J96" s="3">
-        <v>46160.7191666667</v>
+        <v>46204.3220138889</v>
       </c>
       <c r="K96" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L96" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M96" s="3">
-        <v>46154.3432638889</v>
+        <v>46171.6563773148</v>
       </c>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>2558553</v>
+        <v>2562116</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H97" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="I97" s="3">
-        <v>46149.6895138889</v>
-      </c>
+      <c r="I97" s="3"/>
       <c r="J97" s="3">
-        <v>46154.5888773148</v>
+        <v>46160.7191666667</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="M97" s="3">
-        <v>46146.3561805556</v>
-      </c>
-      <c r="N97" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>46154.3432638889</v>
+      </c>
+      <c r="N97" s="3"/>
       <c r="O97" s="3"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>2556271</v>
+        <v>2558553</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I98" s="3">
-        <v>46141.4297453704</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="J98" s="3">
-        <v>46139.9871412037</v>
+        <v>46154.5888773148</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M98" s="3">
-        <v>46139.471412037</v>
+        <v>46146.3561805556</v>
       </c>
       <c r="N98" s="3">
-        <v>46141.4901157407</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="O98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>2556211</v>
+        <v>2556271</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H99" s="0" t="s">
         <v>47</v>
       </c>
       <c r="I99" s="3">
-        <v>46150.6617476852</v>
+        <v>46141.4297453704</v>
       </c>
       <c r="J99" s="3">
-        <v>46146.3663773148</v>
+        <v>46139.9871412037</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="M99" s="3">
-        <v>46139.4325810185</v>
+        <v>46139.471412037</v>
       </c>
       <c r="N99" s="3">
-        <v>46150.6617476852</v>
+        <v>46141.4901157407</v>
       </c>
       <c r="O99" s="3"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>2556029</v>
+        <v>2556211</v>
       </c>
       <c r="B100" s="0" t="s">
         <v>140</v>
@@ -5290,43 +5288,43 @@
         <v>140</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I100" s="3">
-        <v>46150.5</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="J100" s="3">
-        <v>46146.401875</v>
+        <v>46146.3663773148</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L100" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M100" s="3">
-        <v>46138.757337963</v>
+        <v>46139.4325810185</v>
       </c>
       <c r="N100" s="3">
-        <v>46154.6616087963</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>2554341</v>
+        <v>2556029</v>
       </c>
       <c r="B101" s="0" t="s">
         <v>140</v>
@@ -5335,792 +5333,792 @@
         <v>140</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I101" s="3">
-        <v>46136.3599768519</v>
+        <v>46150.5</v>
       </c>
       <c r="J101" s="3">
-        <v>46135.6585185185</v>
+        <v>46146.401875</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M101" s="3">
-        <v>46134.4016435185</v>
+        <v>46138.757337963</v>
       </c>
       <c r="N101" s="3">
-        <v>46136.3599768519</v>
+        <v>46154.6616087963</v>
       </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>2547638</v>
+        <v>2554341</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I102" s="3">
-        <v>46150.3473611111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="J102" s="3">
-        <v>46119.5010069444</v>
+        <v>46135.6585185185</v>
       </c>
       <c r="K102" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L102" s="0" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="M102" s="3">
-        <v>46114.4931944444</v>
+        <v>46134.4016435185</v>
       </c>
       <c r="N102" s="3">
-        <v>46150.3473611111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>2537054</v>
+        <v>2547638</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E103" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I103" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="J103" s="3">
-        <v>46090.3698263889</v>
+        <v>46119.5010069444</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="M103" s="3">
-        <v>46087.5797569444</v>
+        <v>46114.4931944444</v>
       </c>
       <c r="N103" s="3">
-        <v>46093.4339236111</v>
+        <v>46150.3473611111</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>2531696</v>
+        <v>2537054</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="E104" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I104" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I104" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="J104" s="3">
-        <v>46204.3216782407</v>
+        <v>46090.3698263889</v>
       </c>
       <c r="K104" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="M104" s="3">
-        <v>46076.5833912037</v>
-      </c>
-      <c r="N104" s="3"/>
+        <v>46087.5797569444</v>
+      </c>
+      <c r="N104" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="O104" s="3"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>2530739</v>
+        <v>2531696</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E105" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="I105" s="3"/>
       <c r="J105" s="3">
-        <v>46218.6914940625</v>
+        <v>46204.3216782407</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M105" s="3">
-        <v>46072.6973148148</v>
+        <v>46076.5833912037</v>
       </c>
       <c r="N105" s="3"/>
       <c r="O105" s="3"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>2529639</v>
+        <v>2530739</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>65</v>
+        <v>192</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>65</v>
+        <v>193</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I106" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="I106" s="3"/>
       <c r="J106" s="3">
-        <v>46072.6891666667</v>
+        <v>46218.6914940625</v>
       </c>
       <c r="K106" s="0" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="L106" s="0" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="M106" s="3">
-        <v>46069.5930902778</v>
-      </c>
-      <c r="N106" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>46072.6973148148</v>
+      </c>
+      <c r="N106" s="3"/>
       <c r="O106" s="3"/>
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>2529591</v>
+        <v>2529639</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I107" s="3">
-        <v>46108.5968055556</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="J107" s="3">
-        <v>46126.6875</v>
+        <v>46072.6891666667</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="M107" s="3">
-        <v>46069.4509722222</v>
+        <v>46069.5930902778</v>
       </c>
       <c r="N107" s="3">
-        <v>46108.5968055556</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="O107" s="3"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>2528858</v>
+        <v>2529591</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I108" s="3">
-        <v>46107.3861458333</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="J108" s="3">
-        <v>46087.6277662037</v>
+        <v>46126.6875</v>
       </c>
       <c r="K108" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L108" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M108" s="3">
-        <v>46065.7194791667</v>
+        <v>46069.4509722222</v>
       </c>
       <c r="N108" s="3">
-        <v>46107.3861458333</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>2525312</v>
+        <v>2528858</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I109" s="3">
-        <v>46070.5877314815</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="J109" s="3">
-        <v>46062.7587037037</v>
+        <v>46087.6277662037</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="M109" s="3">
-        <v>46058.3585648148</v>
+        <v>46065.7194791667</v>
       </c>
       <c r="N109" s="3">
-        <v>46070.5877314815</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="O109" s="3"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>2525272</v>
+        <v>2525312</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>199</v>
+        <v>67</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>199</v>
+        <v>67</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I110" s="3">
-        <v>46203.7916666667</v>
+        <v>46070.5877314815</v>
       </c>
       <c r="J110" s="3">
-        <v>46126.7441782407</v>
+        <v>46062.7587037037</v>
       </c>
       <c r="K110" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L110" s="0" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="M110" s="3">
-        <v>46058.2883101852</v>
-      </c>
-      <c r="N110" s="3"/>
+        <v>46058.3585648148</v>
+      </c>
+      <c r="N110" s="3">
+        <v>46070.5877314815</v>
+      </c>
       <c r="O110" s="3"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>2524577</v>
+        <v>2525272</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="I111" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I111" s="3">
+        <v>46203.7916666667</v>
+      </c>
       <c r="J111" s="3">
-        <v>46267.4298180903</v>
+        <v>46126.7441782407</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M111" s="3">
-        <v>46056.697349537</v>
+        <v>46058.2883101852</v>
       </c>
       <c r="N111" s="3"/>
       <c r="O111" s="3"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>2524373</v>
+        <v>2524577</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I112" s="3">
-        <v>46087.3854513889</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="I112" s="3"/>
       <c r="J112" s="3">
-        <v>46056.6543865741</v>
+        <v>46267.4298180903</v>
       </c>
       <c r="K112" s="0" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="M112" s="3">
-        <v>46056.5937847222</v>
-      </c>
-      <c r="N112" s="3">
-        <v>46087.3854513889</v>
-      </c>
+        <v>46056.697349537</v>
+      </c>
+      <c r="N112" s="3"/>
       <c r="O112" s="3"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>2524062</v>
+        <v>2524373</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I113" s="3">
-        <v>46057.7412615741</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="J113" s="3">
-        <v>46056.6210300926</v>
+        <v>46056.6543865741</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="M113" s="3">
-        <v>46056.3662615741</v>
+        <v>46056.5937847222</v>
       </c>
       <c r="N113" s="3">
-        <v>46057.7412615741</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="O113" s="3"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>2523635</v>
+        <v>2524062</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I114" s="3">
-        <v>46059.4164236111</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="J114" s="3">
-        <v>46055.6034837963</v>
+        <v>46056.6210300926</v>
       </c>
       <c r="K114" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L114" s="0" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="M114" s="3">
-        <v>46055.4997569444</v>
+        <v>46056.3662615741</v>
       </c>
       <c r="N114" s="3">
-        <v>46059.4164236111</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="O114" s="3"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>2523602</v>
+        <v>2523635</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I115" s="3">
-        <v>46093.6246643519</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="J115" s="3">
-        <v>46056.5784027778</v>
+        <v>46055.6034837963</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="M115" s="3">
-        <v>46055.4788310185</v>
+        <v>46055.4997569444</v>
       </c>
       <c r="N115" s="3">
-        <v>46093.6246643519</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="O115" s="3"/>
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>2521645</v>
+        <v>2523602</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="I116" s="3">
-        <v>46062.5</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="J116" s="3">
-        <v>46050.3426763542</v>
+        <v>46056.5784027778</v>
       </c>
       <c r="K116" s="0" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="L116" s="0" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="M116" s="3">
-        <v>46049.7714236111</v>
-      </c>
-      <c r="N116" s="3"/>
+        <v>46055.4788310185</v>
+      </c>
+      <c r="N116" s="3">
+        <v>46093.6246643519</v>
+      </c>
       <c r="O116" s="3"/>
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>2521079</v>
+        <v>2521645</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="I117" s="3">
-        <v>46052.6666666667</v>
+        <v>46062.5</v>
       </c>
       <c r="J117" s="3">
-        <v>46056.6197800926</v>
+        <v>46050.3426763542</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M117" s="3">
-        <v>46048.7684490741</v>
-      </c>
-      <c r="N117" s="3">
-        <v>46061.6309722222</v>
-      </c>
+        <v>46049.7714236111</v>
+      </c>
+      <c r="N117" s="3"/>
       <c r="O117" s="3"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>2520048</v>
+        <v>2521079</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>193</v>
+        <v>118</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H118" s="0" t="s">
         <v>47</v>
       </c>
       <c r="I118" s="3">
-        <v>46057.5</v>
+        <v>46052.6666666667</v>
       </c>
       <c r="J118" s="3">
-        <v>46052.5774305556</v>
+        <v>46056.6197800926</v>
       </c>
       <c r="K118" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L118" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M118" s="3">
-        <v>46045.3325578704</v>
+        <v>46048.7684490741</v>
       </c>
       <c r="N118" s="3">
-        <v>46057.5</v>
+        <v>46061.6309722222</v>
       </c>
       <c r="O118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>2519904</v>
+        <v>2520048</v>
       </c>
       <c r="B119" s="0" t="s">
         <v>132</v>
@@ -6129,394 +6127,394 @@
         <v>193</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I119" s="3">
-        <v>46084.7217939815</v>
+        <v>46057.5</v>
       </c>
       <c r="J119" s="3">
-        <v>46044.7413888889</v>
+        <v>46052.5774305556</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="M119" s="3">
-        <v>46044.6384606482</v>
+        <v>46045.3325578704</v>
       </c>
       <c r="N119" s="3">
-        <v>46084.7217939815</v>
+        <v>46057.5</v>
       </c>
       <c r="O119" s="3"/>
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <v>2519523</v>
+        <v>2519904</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>65</v>
+        <v>193</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I120" s="3">
-        <v>46076.5902777778</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="J120" s="3">
-        <v>46048.4589814815</v>
+        <v>46044.7413888889</v>
       </c>
       <c r="K120" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L120" s="0" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="M120" s="3">
-        <v>46043.7362847222</v>
+        <v>46044.6384606482</v>
       </c>
       <c r="N120" s="3">
-        <v>46077.380775463</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="O120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <v>2519383</v>
+        <v>2519523</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I121" s="3">
-        <v>46076.399224537</v>
+        <v>46076.5902777778</v>
       </c>
       <c r="J121" s="3">
-        <v>46048.4599305556</v>
+        <v>46048.4589814815</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M121" s="3">
-        <v>46043.6075578704</v>
+        <v>46043.7362847222</v>
       </c>
       <c r="N121" s="3">
-        <v>46076.399224537</v>
+        <v>46077.380775463</v>
       </c>
       <c r="O121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <v>2519284</v>
+        <v>2519383</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I122" s="3">
-        <v>46049.3982986111</v>
+        <v>46076.399224537</v>
       </c>
       <c r="J122" s="3">
-        <v>46043.742337963</v>
+        <v>46048.4599305556</v>
       </c>
       <c r="K122" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L122" s="0" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="M122" s="3">
-        <v>46043.4816319444</v>
+        <v>46043.6075578704</v>
       </c>
       <c r="N122" s="3">
-        <v>46049.3982986111</v>
+        <v>46076.399224537</v>
       </c>
       <c r="O122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <v>2518650</v>
+        <v>2519284</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>193</v>
+        <v>118</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I123" s="3">
-        <v>46072.3536921296</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="J123" s="3">
-        <v>46043.8185648148</v>
+        <v>46043.742337963</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="M123" s="3">
-        <v>46042.3536921296</v>
+        <v>46043.4816319444</v>
       </c>
       <c r="N123" s="3">
-        <v>46080.437025463</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="O123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <v>2513117</v>
+        <v>2518650</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E124" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I124" s="3">
-        <v>46031.4922800926</v>
+        <v>46072.3536921296</v>
       </c>
       <c r="J124" s="3">
-        <v>46028.3500347222</v>
+        <v>46043.8185648148</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L124" s="0" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="M124" s="3">
-        <v>46027.6381134259</v>
+        <v>46042.3536921296</v>
       </c>
       <c r="N124" s="3">
-        <v>46031.4922800926</v>
+        <v>46080.437025463</v>
       </c>
       <c r="O124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <v>2512883</v>
+        <v>2513117</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I125" s="3">
-        <v>46037.6340972222</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="J125" s="3">
-        <v>46129.4199421296</v>
+        <v>46028.3500347222</v>
       </c>
       <c r="K125" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M125" s="3">
-        <v>46027.4049305556</v>
+        <v>46027.6381134259</v>
       </c>
       <c r="N125" s="3">
-        <v>46141.6335300926</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="O125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <v>2512542</v>
+        <v>2512883</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I126" s="3">
-        <v>46036.5</v>
+        <v>46037.6340972222</v>
       </c>
       <c r="J126" s="3">
-        <v>46024.5900925926</v>
+        <v>46129.4199421296</v>
       </c>
       <c r="K126" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M126" s="3">
-        <v>46022.6836342593</v>
+        <v>46027.4049305556</v>
       </c>
       <c r="N126" s="3">
-        <v>46036.5</v>
+        <v>46141.6335300926</v>
       </c>
       <c r="O126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <v>2512541</v>
+        <v>2512542</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I127" s="3">
         <v>46036.5</v>
       </c>
       <c r="J127" s="3">
-        <v>46022.7128356481</v>
+        <v>46024.5900925926</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M127" s="3">
-        <v>46022.6762615741</v>
+        <v>46022.6836342593</v>
       </c>
       <c r="N127" s="3">
         <v>46036.5</v>
@@ -6525,97 +6523,97 @@
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <v>2509014</v>
+        <v>2512541</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I128" s="3">
-        <v>46044.7250578704</v>
+        <v>46036.5</v>
       </c>
       <c r="J128" s="3">
-        <v>46022.6138541667</v>
+        <v>46022.7128356481</v>
       </c>
       <c r="K128" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L128" s="0" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="M128" s="3">
-        <v>46008.454224537</v>
+        <v>46022.6762615741</v>
       </c>
       <c r="N128" s="3">
-        <v>46045.4708564815</v>
+        <v>46036.5</v>
       </c>
       <c r="O128" s="3"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <v>2506714</v>
+        <v>2509014</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I129" s="3">
-        <v>46038.7073032407</v>
+        <v>46044.7250578704</v>
       </c>
       <c r="J129" s="3">
-        <v>46044.7372337963</v>
+        <v>46022.6138541667</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M129" s="3">
-        <v>46002.4364699074</v>
+        <v>46008.454224537</v>
       </c>
       <c r="N129" s="3">
-        <v>46038.7073032407</v>
+        <v>46045.4708564815</v>
       </c>
       <c r="O129" s="3"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <v>2506599</v>
+        <v>2506714</v>
       </c>
       <c r="B130" s="0" t="s">
         <v>132</v>
@@ -6624,7 +6622,7 @@
         <v>132</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="E130" s="0" t="s">
         <v>133</v>
@@ -6633,43 +6631,43 @@
         <v>133</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I130" s="3">
-        <v>46037.61375</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="J130" s="3">
-        <v>46052.3252083333</v>
+        <v>46044.7372337963</v>
       </c>
       <c r="K130" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L130" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M130" s="3">
-        <v>46002.3429166667</v>
+        <v>46002.4364699074</v>
       </c>
       <c r="N130" s="3">
-        <v>46037.61375</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="O130" s="3"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <v>2506311</v>
+        <v>2506599</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="E131" s="0" t="s">
         <v>133</v>
@@ -6678,562 +6676,564 @@
         <v>133</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I131" s="3">
-        <v>46013.7291666667</v>
+        <v>46037.61375</v>
       </c>
       <c r="J131" s="3">
-        <v>46013.461875</v>
+        <v>46052.3252083333</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="M131" s="3">
-        <v>46001.5219328704</v>
+        <v>46002.3429166667</v>
       </c>
       <c r="N131" s="3">
-        <v>46013.7291666667</v>
+        <v>46037.61375</v>
       </c>
       <c r="O131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <v>2506102</v>
+        <v>2506311</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>140</v>
+        <v>222</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>140</v>
+        <v>222</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I132" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I132" s="3">
+        <v>46013.7291666667</v>
+      </c>
       <c r="J132" s="3">
-        <v>46241.5032638889</v>
+        <v>46013.461875</v>
       </c>
       <c r="K132" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L132" s="0" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="M132" s="3">
-        <v>46001.3800578704</v>
-      </c>
-      <c r="N132" s="3"/>
+        <v>46001.5219328704</v>
+      </c>
+      <c r="N132" s="3">
+        <v>46013.7291666667</v>
+      </c>
       <c r="O132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <v>2502589</v>
+        <v>2506102</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>225</v>
+        <v>140</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>225</v>
+        <v>140</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I133" s="3">
-        <v>46029.6634375</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I133" s="3"/>
       <c r="J133" s="3">
-        <v>46014.6931018519</v>
+        <v>46241.5032638889</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="M133" s="3">
-        <v>45993.3791087963</v>
-      </c>
-      <c r="N133" s="3">
-        <v>46029.6634375</v>
-      </c>
+        <v>46001.3800578704</v>
+      </c>
+      <c r="N133" s="3"/>
       <c r="O133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <v>2502438</v>
+        <v>2502589</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>117</v>
+        <v>225</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I134" s="3">
-        <v>46037.3801388889</v>
+        <v>46029.6634375</v>
       </c>
       <c r="J134" s="3">
-        <v>45996.4823032407</v>
+        <v>46014.6931018519</v>
       </c>
       <c r="K134" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L134" s="0" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="M134" s="3">
-        <v>45992.7134722222</v>
+        <v>45993.3791087963</v>
       </c>
       <c r="N134" s="3">
-        <v>46037.3801388889</v>
+        <v>46029.6634375</v>
       </c>
       <c r="O134" s="3"/>
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <v>2501349</v>
+        <v>2502438</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="C135" s="0" t="s">
         <v>193</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I135" s="3">
-        <v>46069.7381944444</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="J135" s="3">
-        <v>46069.3651388889</v>
+        <v>45996.4823032407</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M135" s="3">
-        <v>45989.0365856482</v>
+        <v>45992.7134722222</v>
       </c>
       <c r="N135" s="3">
-        <v>46069.7381944444</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="O135" s="3"/>
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <v>2500635</v>
+        <v>2501349</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E136" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I136" s="3">
-        <v>46024.4633796296</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="J136" s="3">
-        <v>46027.3611111111</v>
+        <v>46069.3651388889</v>
       </c>
       <c r="K136" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L136" s="0" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="M136" s="3">
-        <v>45987.671712963</v>
+        <v>45989.0365856482</v>
       </c>
       <c r="N136" s="3">
-        <v>46024.4633796296</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="O136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <v>2498066</v>
+        <v>2500635</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="E137" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I137" s="3">
-        <v>46073.7916666667</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="J137" s="3">
-        <v>46126.6953240741</v>
+        <v>46027.3611111111</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M137" s="3">
-        <v>45979.750162037</v>
-      </c>
-      <c r="N137" s="3"/>
+        <v>45987.671712963</v>
+      </c>
+      <c r="N137" s="3">
+        <v>46024.4633796296</v>
+      </c>
       <c r="O137" s="3"/>
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <v>2494282</v>
+        <v>2498066</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="E138" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I138" s="3">
-        <v>45986.48125</v>
+        <v>46073.7916666667</v>
       </c>
       <c r="J138" s="3">
-        <v>45988.567025463</v>
+        <v>46126.6953240741</v>
       </c>
       <c r="K138" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L138" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M138" s="3">
-        <v>45971.4792824074</v>
-      </c>
-      <c r="N138" s="3">
-        <v>45986.4815625</v>
-      </c>
+        <v>45979.750162037</v>
+      </c>
+      <c r="N138" s="3"/>
       <c r="O138" s="3"/>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>2494179</v>
+        <v>2494282</v>
       </c>
       <c r="B139" s="0" t="s">
         <v>132</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H139" s="0" t="s">
         <v>47</v>
       </c>
       <c r="I139" s="3">
-        <v>46002.675775463</v>
+        <v>45986.48125</v>
       </c>
       <c r="J139" s="3">
-        <v>46044.7370486111</v>
+        <v>45988.567025463</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M139" s="3">
-        <v>45971.4049421296</v>
+        <v>45971.4792824074</v>
       </c>
       <c r="N139" s="3">
-        <v>46002.675775463</v>
+        <v>45986.4815625</v>
       </c>
       <c r="O139" s="3"/>
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>2490911</v>
+        <v>2494179</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>235</v>
+        <v>133</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>17</v>
+        <v>232</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>32</v>
+        <v>233</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="I140" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="I140" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="J140" s="3">
-        <v>46182.7633796296</v>
+        <v>46044.7370486111</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="L140" s="0" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="M140" s="3">
-        <v>45961.5760300926</v>
-      </c>
-      <c r="N140" s="3"/>
+        <v>45971.4049421296</v>
+      </c>
+      <c r="N140" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="O140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>2490185</v>
+        <v>2490911</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="E141" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I141" s="3">
-        <v>46203.7916666667</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="I141" s="3"/>
       <c r="J141" s="3">
-        <v>46051.4836111111</v>
+        <v>46182.7633796296</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M141" s="3">
-        <v>45960.3928819444</v>
+        <v>45961.5760300926</v>
       </c>
       <c r="N141" s="3"/>
       <c r="O141" s="3"/>
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <v>2489016</v>
+        <v>2490185</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>238</v>
+        <v>17</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I142" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I142" s="3">
+        <v>46203.7916666667</v>
+      </c>
       <c r="J142" s="3">
-        <v>45958.3906481481</v>
+        <v>46051.4836111111</v>
       </c>
       <c r="K142" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L142" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M142" s="3">
-        <v>45957.7253009259</v>
+        <v>45960.3928819444</v>
       </c>
       <c r="N142" s="3"/>
       <c r="O142" s="3"/>
     </row>
     <row r="143">
       <c r="A143" s="2">
-        <v>2485386</v>
+        <v>2489016</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>235</v>
+        <v>102</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>17</v>
+        <v>238</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>32</v>
+        <v>233</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="I143" s="3">
-        <v>46386.7916666667</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I143" s="3"/>
       <c r="J143" s="3">
-        <v>46182.7639236111</v>
+        <v>45958.3906481481</v>
       </c>
       <c r="K143" s="0" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="L143" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M143" s="3">
-        <v>45947.7000115741</v>
+        <v>45957.7253009259</v>
       </c>
       <c r="N143" s="3"/>
       <c r="O143" s="3"/>
     </row>
     <row r="144">
       <c r="A144" s="2">
-        <v>2483420</v>
+        <v>2485386</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D144" s="0" t="s">
         <v>235</v>
@@ -7242,128 +7242,130 @@
         <v>17</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="I144" s="3"/>
+        <v>123</v>
+      </c>
+      <c r="I144" s="3">
+        <v>46386.7916666667</v>
+      </c>
       <c r="J144" s="3">
-        <v>46140.3843518519</v>
+        <v>46182.7639236111</v>
       </c>
       <c r="K144" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L144" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M144" s="3">
-        <v>45944.6603819444</v>
+        <v>45947.7000115741</v>
       </c>
       <c r="N144" s="3"/>
       <c r="O144" s="3"/>
     </row>
     <row r="145">
       <c r="A145" s="2">
-        <v>2474606</v>
+        <v>2483420</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>43</v>
+        <v>235</v>
       </c>
       <c r="E145" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I145" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="I145" s="3"/>
       <c r="J145" s="3">
-        <v>45966.4450925926</v>
+        <v>46140.3843518519</v>
       </c>
       <c r="K145" s="0" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="L145" s="0" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="M145" s="3">
-        <v>45924.4486921296</v>
-      </c>
-      <c r="N145" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>45944.6603819444</v>
+      </c>
+      <c r="N145" s="3"/>
       <c r="O145" s="3"/>
     </row>
     <row r="146">
       <c r="A146" s="2">
-        <v>2470122</v>
+        <v>2474606</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>235</v>
+        <v>44</v>
       </c>
       <c r="E146" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>245</v>
-      </c>
-      <c r="I146" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I146" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="J146" s="3">
-        <v>46204.3270601852</v>
+        <v>45966.4450925926</v>
       </c>
       <c r="K146" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L146" s="0" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="M146" s="3">
-        <v>45912.5572222222</v>
-      </c>
-      <c r="N146" s="3"/>
+        <v>45924.4486921296</v>
+      </c>
+      <c r="N146" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="O146" s="3"/>
     </row>
     <row r="147">
       <c r="A147" s="2">
-        <v>2463515</v>
+        <v>2470122</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E147" s="0" t="s">
         <v>17</v>
@@ -7372,112 +7374,112 @@
         <v>18</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>46</v>
+        <v>245</v>
       </c>
       <c r="I147" s="3"/>
       <c r="J147" s="3">
-        <v>45910.4755555556</v>
+        <v>46204.3270601852</v>
       </c>
       <c r="K147" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L147" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M147" s="3">
-        <v>45897.4218865741</v>
+        <v>45912.5572222222</v>
       </c>
       <c r="N147" s="3"/>
       <c r="O147" s="3"/>
     </row>
     <row r="148">
       <c r="A148" s="2">
-        <v>2461703</v>
+        <v>2463515</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="I148" s="3"/>
       <c r="J148" s="3">
-        <v>46003.3706828704</v>
+        <v>45910.4755555556</v>
       </c>
       <c r="K148" s="0" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="L148" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M148" s="3">
-        <v>45894.4525347222</v>
+        <v>45897.4218865741</v>
       </c>
       <c r="N148" s="3"/>
       <c r="O148" s="3"/>
     </row>
     <row r="149">
       <c r="A149" s="2">
-        <v>2459339</v>
+        <v>2461703</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="D149" s="0" t="s">
         <v>235</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>122</v>
+        <v>245</v>
       </c>
       <c r="I149" s="3"/>
       <c r="J149" s="3">
-        <v>46140.3839930556</v>
+        <v>46003.3706828704</v>
       </c>
       <c r="K149" s="0" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="L149" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M149" s="3">
-        <v>45887.7442361111</v>
+        <v>45894.4525347222</v>
       </c>
       <c r="N149" s="3"/>
       <c r="O149" s="3"/>
     </row>
     <row r="150">
       <c r="A150" s="2">
-        <v>2456538</v>
+        <v>2459339</v>
       </c>
       <c r="B150" s="0" t="s">
         <v>132</v>
@@ -7486,253 +7488,294 @@
         <v>132</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>100</v>
+        <v>235</v>
       </c>
       <c r="E150" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="I150" s="3"/>
       <c r="J150" s="3">
-        <v>46126.7428356481</v>
+        <v>46140.3839930556</v>
       </c>
       <c r="K150" s="0" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="L150" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M150" s="3">
-        <v>45880.6643055556</v>
+        <v>45887.7442361111</v>
       </c>
       <c r="N150" s="3"/>
       <c r="O150" s="3"/>
     </row>
     <row r="151">
       <c r="A151" s="2">
-        <v>2449811</v>
+        <v>2456538</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>251</v>
+        <v>132</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>251</v>
+        <v>132</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I151" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I151" s="3"/>
       <c r="J151" s="3">
-        <v>45870.3628819444</v>
+        <v>46126.7428356481</v>
       </c>
       <c r="K151" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L151" s="0" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="M151" s="3">
-        <v>45862.6188888889</v>
-      </c>
-      <c r="N151" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>45880.6643055556</v>
+      </c>
+      <c r="N151" s="3"/>
       <c r="O151" s="3"/>
     </row>
     <row r="152">
       <c r="A152" s="2">
-        <v>2442028</v>
+        <v>2449811</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I152" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="I152" s="3">
+        <v>45875.3688888889</v>
+      </c>
       <c r="J152" s="3">
-        <v>46126.7431134259</v>
+        <v>45870.3628819444</v>
       </c>
       <c r="K152" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L152" s="0" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="M152" s="3">
-        <v>45842.317025463</v>
-      </c>
-      <c r="N152" s="3"/>
+        <v>45862.6188888889</v>
+      </c>
+      <c r="N152" s="3">
+        <v>45875.3688888889</v>
+      </c>
       <c r="O152" s="3"/>
     </row>
     <row r="153">
       <c r="A153" s="2">
-        <v>2439691</v>
+        <v>2442028</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>132</v>
+        <v>253</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>132</v>
+        <v>253</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
+      </c>
+      <c r="F153" s="0" t="s">
+        <v>24</v>
       </c>
       <c r="G153" s="0" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I153" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I153" s="3"/>
       <c r="J153" s="3">
-        <v>45838.6211342593</v>
+        <v>46126.7431134259</v>
       </c>
       <c r="K153" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L153" s="0" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="M153" s="3">
-        <v>45838.3761921296</v>
-      </c>
-      <c r="N153" s="3">
-        <v>45852.3770833333</v>
-      </c>
+        <v>45842.317025463</v>
+      </c>
+      <c r="N153" s="3"/>
       <c r="O153" s="3"/>
     </row>
     <row r="154">
       <c r="A154" s="2">
-        <v>2437239</v>
+        <v>2439691</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>257</v>
+        <v>132</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="F154" s="0" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I154" s="3">
-        <v>45870.3600462963</v>
+        <v>45852.3770833333</v>
       </c>
       <c r="J154" s="3">
-        <v>45841.7026091435</v>
+        <v>45838.6211342593</v>
       </c>
       <c r="K154" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L154" s="0" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="M154" s="3">
-        <v>45831.6933796296</v>
+        <v>45838.3761921296</v>
       </c>
       <c r="N154" s="3">
-        <v>45870.3600462963</v>
+        <v>45852.3770833333</v>
       </c>
       <c r="O154" s="3"/>
     </row>
     <row r="155">
       <c r="A155" s="2">
+        <v>2437239</v>
+      </c>
+      <c r="B155" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="C155" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="D155" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="F155" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="G155" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="H155" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="I155" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="J155" s="3">
+        <v>45841.7026091435</v>
+      </c>
+      <c r="K155" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="L155" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="M155" s="3">
+        <v>45831.6933796296</v>
+      </c>
+      <c r="N155" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="O155" s="3"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2">
         <v>2436707</v>
       </c>
-      <c r="B155" s="0" t="s">
+      <c r="B156" s="0" t="s">
         <v>251</v>
       </c>
-      <c r="C155" s="0" t="s">
+      <c r="C156" s="0" t="s">
         <v>251</v>
       </c>
-      <c r="D155" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="E155" s="0" t="s">
+      <c r="D156" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E156" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="F155" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G155" s="0" t="s">
+      <c r="F156" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G156" s="0" t="s">
         <v>259</v>
       </c>
-      <c r="H155" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I155" s="3">
+      <c r="H156" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="I156" s="3">
         <v>45835.7284722222</v>
       </c>
-      <c r="J155" s="3">
+      <c r="J156" s="3">
         <v>46126.7436921296</v>
       </c>
-      <c r="K155" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="L155" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="M155" s="3">
+      <c r="K156" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="L156" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M156" s="3">
         <v>45828.8276273148</v>
       </c>
-      <c r="N155" s="3">
+      <c r="N156" s="3">
         <v>45835.7288773148</v>
       </c>
-      <c r="O155" s="3"/>
+      <c r="O156" s="3"/>
     </row>
   </sheetData>
   <headerFooter/>

--- a/Solicitacoes.xlsx
+++ b/Solicitacoes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
   <si>
     <t>Protocolo</t>
   </si>
@@ -59,12 +59,36 @@
     <t>Prazo desejado</t>
   </si>
   <si>
+    <t>COMPESAPREV.JULIA</t>
+  </si>
+  <si>
+    <t>CORRECAO</t>
+  </si>
+  <si>
+    <t>MOBE</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>MOBE - Beneficiário não consegue logar pelo app há mais de um mês</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Suporte nível II</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>MOBE - Não foi possível carregar a carteirinha</t>
+  </si>
+  <si>
     <t>COMPESAPREV.NIECIA</t>
   </si>
   <si>
-    <t>CORRECAO</t>
-  </si>
-  <si>
     <t>AG</t>
   </si>
   <si>
@@ -74,18 +98,6 @@
     <t>Calculo da mensalidade sem redistribuição entre o grupo familiar</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
-    <t>Suporte nível II</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>COMPESAPREV.JULIA</t>
-  </si>
-  <si>
     <t>ADM</t>
   </si>
   <si>
@@ -173,12 +185,6 @@
     <t>CON - Impossibilidade adiconar corpo clínico</t>
   </si>
   <si>
-    <t>MOBE</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
     <t xml:space="preserve">APP -  Erro no servidor / buscar dados</t>
   </si>
   <si>
@@ -504,6 +510,9 @@
   </si>
   <si>
     <t>COMPESAPREV-LEAN-PROD- Erro ao substituir diária — Enum inválido (TissTabelaProcedimentos)</t>
+  </si>
+  <si>
+    <t>Aguardando detalhamento</t>
   </si>
   <si>
     <t>CompesaPrev - Cadastro de Cooperados</t>
@@ -848,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O156"/>
+  <dimension ref="A1:O158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1506990705218" customWidth="1"/>
@@ -917,7 +926,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2620853</v>
+        <v>2621321</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>15</v>
@@ -941,10 +950,10 @@
         <v>20</v>
       </c>
       <c r="I2" s="3">
-        <v>46300.6124768518</v>
+        <v>46301.467037037</v>
       </c>
       <c r="J2" s="3">
-        <v>46294.6958101852</v>
+        <v>46295.6128703704</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>21</v>
@@ -953,22 +962,22 @@
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>46294.6958101852</v>
+        <v>46295.6128703704</v>
       </c>
       <c r="N2" s="3">
-        <v>46300.6124768518</v>
+        <v>46301.467037037</v>
       </c>
       <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2620239</v>
+        <v>2621118</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>16</v>
@@ -977,19 +986,19 @@
         <v>17</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H3" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I3" s="3">
-        <v>46297.626712963</v>
+        <v>46301.3640856482</v>
       </c>
       <c r="J3" s="3">
-        <v>46293.7100462963</v>
+        <v>46295.4474189815</v>
       </c>
       <c r="K3" s="0" t="s">
         <v>21</v>
@@ -998,626 +1007,626 @@
         <v>22</v>
       </c>
       <c r="M3" s="3">
-        <v>46293.7100462963</v>
+        <v>46295.4474189815</v>
       </c>
       <c r="N3" s="3">
-        <v>46297.626712963</v>
+        <v>46301.3640856482</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>2619954</v>
+        <v>2620853</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="0" t="s">
+      <c r="G4" s="0" t="s">
         <v>27</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>28</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="3">
-        <v>46303.7183912037</v>
+        <v>46300.6124768518</v>
       </c>
       <c r="J4" s="3">
-        <v>46293.489224537</v>
+        <v>46294.6958101852</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M4" s="3">
-        <v>46293.489224537</v>
+        <v>46294.6958101852</v>
       </c>
       <c r="N4" s="3">
-        <v>46303.7183912037</v>
+        <v>46300.6124768518</v>
       </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>2619927</v>
+        <v>2620239</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H5" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="3">
-        <v>46303.6970833333</v>
+        <v>46297.626712963</v>
       </c>
       <c r="J5" s="3">
-        <v>46294.7248677083</v>
+        <v>46293.7100462963</v>
       </c>
       <c r="K5" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M5" s="3">
-        <v>46293.4679166667</v>
+        <v>46293.7100462963</v>
       </c>
       <c r="N5" s="3">
-        <v>46303.6970833333</v>
+        <v>46297.626712963</v>
       </c>
       <c r="O5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>2619693</v>
+        <v>2619954</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I6" s="3">
-        <v>46296.6479976852</v>
+        <v>46303.7183912037</v>
       </c>
       <c r="J6" s="3">
-        <v>46294.5493055556</v>
+        <v>46293.489224537</v>
       </c>
       <c r="K6" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M6" s="3">
-        <v>46290.7313310185</v>
+        <v>46293.489224537</v>
       </c>
       <c r="N6" s="3">
-        <v>46296.6479976852</v>
+        <v>46303.7183912037</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>2619258</v>
+        <v>2619927</v>
       </c>
       <c r="B7" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>38</v>
-      </c>
       <c r="H7" s="0" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I7" s="3">
-        <v>46302.589837963</v>
+        <v>46303.6970833333</v>
       </c>
       <c r="J7" s="3">
-        <v>46293.3487384259</v>
+        <v>46294.7248677083</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M7" s="3">
-        <v>46290.3606712963</v>
+        <v>46293.4679166667</v>
       </c>
       <c r="N7" s="3">
-        <v>46302.589837963</v>
+        <v>46303.6970833333</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>2619015</v>
+        <v>2619693</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D8" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="G8" s="0" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H8" s="0" t="s">
         <v>39</v>
       </c>
       <c r="I8" s="3">
-        <v>46295.4977546296</v>
+        <v>46296.6479976852</v>
       </c>
       <c r="J8" s="3">
-        <v>46293.7032986111</v>
+        <v>46294.5493055556</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L8" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M8" s="3">
-        <v>46289.643587963</v>
+        <v>46290.7313310185</v>
       </c>
       <c r="N8" s="3">
-        <v>46295.4977546296</v>
+        <v>46296.6479976852</v>
       </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>2618956</v>
+        <v>2619258</v>
       </c>
       <c r="B9" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="H9" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="I9" s="3">
+        <v>46302.589837963</v>
+      </c>
+      <c r="J9" s="3">
+        <v>46293.3487384259</v>
+      </c>
+      <c r="K9" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="3">
-        <v>46295.6236574074</v>
-      </c>
-      <c r="J9" s="3">
-        <v>46293.3764351852</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>48</v>
-      </c>
       <c r="L9" s="0" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="M9" s="3">
-        <v>46289.6236574074</v>
-      </c>
-      <c r="N9" s="3"/>
+        <v>46290.3606712963</v>
+      </c>
+      <c r="N9" s="3">
+        <v>46302.589837963</v>
+      </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>2618623</v>
+        <v>2619015</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>39</v>
-      </c>
       <c r="I10" s="3">
-        <v>46295.3625810185</v>
+        <v>46295.4977546296</v>
       </c>
       <c r="J10" s="3">
-        <v>46294.668900463</v>
+        <v>46293.7032986111</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L10" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M10" s="3">
-        <v>46289.3773032407</v>
+        <v>46289.643587963</v>
       </c>
       <c r="N10" s="3">
-        <v>46295.3625810185</v>
+        <v>46295.4977546296</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>2618403</v>
+        <v>2618956</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I11" s="3">
-        <v>46294.5634259259</v>
+        <v>46295.6236574074</v>
       </c>
       <c r="J11" s="3">
-        <v>46293.749640544</v>
+        <v>46293.3764351852</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="M11" s="3">
-        <v>46288.6467592593</v>
-      </c>
-      <c r="N11" s="3">
-        <v>46294.5634259259</v>
-      </c>
+        <v>46289.6236574074</v>
+      </c>
+      <c r="N11" s="3"/>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>2618370</v>
+        <v>2618623</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F12" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="0" t="s">
-        <v>55</v>
-      </c>
       <c r="H12" s="0" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I12" s="3">
-        <v>46290.5871296296</v>
+        <v>46295.3625810185</v>
       </c>
       <c r="J12" s="3">
-        <v>46289.6879962616</v>
+        <v>46294.668900463</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="M12" s="3">
-        <v>46288.6287962963</v>
+        <v>46289.3773032407</v>
       </c>
       <c r="N12" s="3">
-        <v>46290.5871296296</v>
+        <v>46295.3625810185</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>2617933</v>
+        <v>2618403</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I13" s="3">
-        <v>46293.6666666667</v>
+        <v>46294.5634259259</v>
       </c>
       <c r="J13" s="3">
-        <v>46293.3910300926</v>
+        <v>46293.749640544</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L13" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M13" s="3">
-        <v>46287.7594097222</v>
+        <v>46288.6467592593</v>
       </c>
       <c r="N13" s="3">
-        <v>46293.6666666667</v>
+        <v>46294.5634259259</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>2617538</v>
+        <v>2618370</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I14" s="3">
-        <v>46290.7498263889</v>
+        <v>46290.5871296296</v>
       </c>
       <c r="J14" s="3">
-        <v>46288.4440509259</v>
+        <v>46289.6879962616</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="M14" s="3">
-        <v>46287.4164930556</v>
+        <v>46288.6287962963</v>
       </c>
       <c r="N14" s="3">
-        <v>46290.7498263889</v>
+        <v>46290.5871296296</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2617170</v>
+        <v>2617933</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F15" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="G15" s="0" t="s">
-        <v>62</v>
-      </c>
       <c r="H15" s="0" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I15" s="3">
-        <v>46290.4403703704</v>
+        <v>46293.6666666667</v>
       </c>
       <c r="J15" s="3">
-        <v>46289.5649035069</v>
+        <v>46293.3910300926</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L15" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M15" s="3">
-        <v>46286.5862037037</v>
+        <v>46287.7594097222</v>
       </c>
       <c r="N15" s="3">
-        <v>46290.4403703704</v>
+        <v>46293.6666666667</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>2617057</v>
+        <v>2617538</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I16" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="J16" s="3">
-        <v>46286.5879513889</v>
+        <v>46288.4440509259</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L16" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M16" s="3">
-        <v>46286.4877199074</v>
+        <v>46287.4164930556</v>
       </c>
       <c r="N16" s="3">
-        <v>46290.4043865741</v>
+        <v>46290.7498263889</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>2615970</v>
+        <v>2617170</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H17" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I17" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="J17" s="3">
-        <v>46287.3554017708</v>
+        <v>46289.5649035069</v>
       </c>
       <c r="K17" s="0" t="s">
         <v>21</v>
@@ -1626,391 +1635,391 @@
         <v>22</v>
       </c>
       <c r="M17" s="3">
-        <v>46282.5089930556</v>
+        <v>46286.5862037037</v>
       </c>
       <c r="N17" s="3">
-        <v>46288.4166666667</v>
+        <v>46290.4403703704</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>2615871</v>
+        <v>2617057</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>66</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I18" s="3">
-        <v>46286.4024189815</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="J18" s="3">
-        <v>46286.3450115741</v>
+        <v>46286.5879513889</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="M18" s="3">
-        <v>46282.4440856481</v>
+        <v>46286.4877199074</v>
       </c>
       <c r="N18" s="3">
-        <v>46286.4024189815</v>
+        <v>46290.4043865741</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>2615590</v>
+        <v>2615970</v>
       </c>
       <c r="B19" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="0" t="s">
-        <v>68</v>
-      </c>
       <c r="H19" s="0" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I19" s="3">
-        <v>46287.5805092593</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="J19" s="3">
-        <v>46293.377662037</v>
+        <v>46287.3554017708</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L19" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M19" s="3">
-        <v>46281.6638425926</v>
+        <v>46282.5089930556</v>
       </c>
       <c r="N19" s="3">
-        <v>46287.5805092593</v>
+        <v>46288.4166666667</v>
       </c>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>2614686</v>
+        <v>2615871</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="I20" s="3">
-        <v>46321.5908449074</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="J20" s="3">
-        <v>46282.4296635764</v>
+        <v>46286.3450115741</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="M20" s="3">
-        <v>46280.4450115741</v>
+        <v>46282.4440856481</v>
       </c>
       <c r="N20" s="3">
-        <v>46321.5908449074</v>
+        <v>46286.4024189815</v>
       </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>2614334</v>
+        <v>2615590</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I21" s="3">
-        <v>46283.5629166667</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="J21" s="3">
-        <v>46283.4291666667</v>
+        <v>46293.377662037</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="M21" s="3">
-        <v>46279.6749305556</v>
+        <v>46281.6638425926</v>
       </c>
       <c r="N21" s="3">
-        <v>46283.5629166667</v>
+        <v>46287.5805092593</v>
       </c>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>2614135</v>
+        <v>2614686</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="I22" s="3">
-        <v>46289.7291666667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="J22" s="3">
-        <v>46294.3620486111</v>
+        <v>46282.4296635764</v>
       </c>
       <c r="K22" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="M22" s="3">
-        <v>46279.5169097222</v>
+        <v>46280.4450115741</v>
       </c>
       <c r="N22" s="3">
-        <v>46289.7291666667</v>
+        <v>46321.5908449074</v>
       </c>
       <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>2613646</v>
+        <v>2614334</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I23" s="3">
-        <v>46289.3876041667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="J23" s="3">
-        <v>46283.4346064815</v>
+        <v>46283.4291666667</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="M23" s="3">
-        <v>46276.6376041667</v>
+        <v>46279.6749305556</v>
       </c>
       <c r="N23" s="3">
-        <v>46289.3876041667</v>
+        <v>46283.5629166667</v>
       </c>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>2613202</v>
+        <v>2614135</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="I24" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="J24" s="3">
-        <v>46283.4707657407</v>
+        <v>46294.3620486111</v>
       </c>
       <c r="K24" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M24" s="3">
-        <v>46276.3827546296</v>
+        <v>46279.5169097222</v>
       </c>
       <c r="N24" s="3">
-        <v>46288.6119212963</v>
+        <v>46289.7291666667</v>
       </c>
       <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>2613026</v>
+        <v>2613646</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I25" s="3">
-        <v>46281.6747800926</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="J25" s="3">
-        <v>46287.6117592593</v>
+        <v>46283.4346064815</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M25" s="3">
-        <v>46275.6895601852</v>
+        <v>46276.6376041667</v>
       </c>
       <c r="N25" s="3">
-        <v>46281.6747800926</v>
+        <v>46289.3876041667</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>2612720</v>
+        <v>2613202</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>80</v>
@@ -2019,403 +2028,403 @@
         <v>20</v>
       </c>
       <c r="I26" s="3">
-        <v>46316.6011689815</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="J26" s="3">
-        <v>46279.4816185532</v>
+        <v>46283.4707657407</v>
       </c>
       <c r="K26" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="M26" s="3">
-        <v>46275.4553356481</v>
+        <v>46276.3827546296</v>
       </c>
       <c r="N26" s="3">
-        <v>46316.6011689815</v>
+        <v>46288.6119212963</v>
       </c>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>2611881</v>
+        <v>2613026</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D27" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="0" t="s">
-        <v>37</v>
       </c>
       <c r="G27" s="0" t="s">
         <v>81</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I27" s="3">
-        <v>46279.6652314815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="J27" s="3">
-        <v>46274.7389930556</v>
+        <v>46287.6117592593</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L27" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M27" s="3">
-        <v>46273.7485648148</v>
+        <v>46275.6895601852</v>
       </c>
       <c r="N27" s="3">
-        <v>46279.6652314815</v>
+        <v>46281.6747800926</v>
       </c>
       <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>2611848</v>
+        <v>2612720</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>82</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I28" s="3">
-        <v>46287.4094675926</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="J28" s="3">
-        <v>46276.5914583333</v>
+        <v>46279.4816185532</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="M28" s="3">
-        <v>46273.7127546296</v>
+        <v>46275.4553356481</v>
       </c>
       <c r="N28" s="3">
-        <v>46287.4094675926</v>
+        <v>46316.6011689815</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>2611692</v>
+        <v>2611881</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>83</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I29" s="3">
-        <v>46279.4554861111</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="J29" s="3">
-        <v>46294.8010955671</v>
+        <v>46274.7389930556</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L29" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M29" s="3">
-        <v>46273.6013194444</v>
+        <v>46273.7485648148</v>
       </c>
       <c r="N29" s="3">
-        <v>46279.4554861111</v>
+        <v>46279.6652314815</v>
       </c>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>2611552</v>
+        <v>2611848</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C30" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="F30" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="H30" s="0" t="s">
-        <v>47</v>
-      </c>
       <c r="I30" s="3">
-        <v>46275.4327083333</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="J30" s="3">
-        <v>46273.5743171296</v>
+        <v>46276.5914583333</v>
       </c>
       <c r="K30" s="0" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="M30" s="3">
-        <v>46273.474375</v>
+        <v>46273.7127546296</v>
       </c>
       <c r="N30" s="3">
-        <v>46275.4327083333</v>
+        <v>46287.4094675926</v>
       </c>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>2611551</v>
+        <v>2611692</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I31" s="3">
-        <v>46314.6183449074</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="J31" s="3">
-        <v>46274.3603356481</v>
+        <v>46294.8010955671</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="M31" s="3">
-        <v>46273.4725115741</v>
+        <v>46273.6013194444</v>
       </c>
       <c r="N31" s="3">
-        <v>46314.6183449074</v>
+        <v>46279.4554861111</v>
       </c>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>2611539</v>
+        <v>2611552</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F32" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="0" t="s">
-        <v>88</v>
-      </c>
       <c r="H32" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I32" s="3">
-        <v>46275.4227083333</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="J32" s="3">
-        <v>46274.3607986111</v>
+        <v>46273.5743171296</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M32" s="3">
-        <v>46273.464375</v>
+        <v>46273.474375</v>
       </c>
       <c r="N32" s="3">
-        <v>46275.4227083333</v>
+        <v>46275.4327083333</v>
       </c>
       <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>2611521</v>
+        <v>2611551</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I33" s="3">
-        <v>46279.3705439815</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="J33" s="3">
-        <v>46273.7182003819</v>
+        <v>46274.3603356481</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="M33" s="3">
-        <v>46273.4538773148</v>
+        <v>46273.4725115741</v>
       </c>
       <c r="N33" s="3">
-        <v>46279.3705439815</v>
+        <v>46314.6183449074</v>
       </c>
       <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>2610876</v>
+        <v>2611539</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I34" s="3">
-        <v>46276.3367592593</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="J34" s="3">
-        <v>46269.4406376505</v>
+        <v>46274.3607986111</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="M34" s="3">
-        <v>46269.4200925926</v>
+        <v>46273.464375</v>
       </c>
       <c r="N34" s="3">
-        <v>46276.3367592593</v>
+        <v>46275.4227083333</v>
       </c>
       <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>2610030</v>
+        <v>2611521</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>92</v>
@@ -2424,10 +2433,10 @@
         <v>20</v>
       </c>
       <c r="I35" s="3">
-        <v>46274.6271990741</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="J35" s="3">
-        <v>46268.3853071412</v>
+        <v>46273.7182003819</v>
       </c>
       <c r="K35" s="0" t="s">
         <v>21</v>
@@ -2436,31 +2445,31 @@
         <v>22</v>
       </c>
       <c r="M35" s="3">
-        <v>46267.7105324074</v>
+        <v>46273.4538773148</v>
       </c>
       <c r="N35" s="3">
-        <v>46274.6271990741</v>
+        <v>46279.3705439815</v>
       </c>
       <c r="O35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>2609985</v>
+        <v>2610876</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>93</v>
@@ -2469,614 +2478,618 @@
         <v>20</v>
       </c>
       <c r="I36" s="3">
-        <v>46301.4629166667</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="J36" s="3">
-        <v>46267.6774134606</v>
+        <v>46269.4406376505</v>
       </c>
       <c r="K36" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="M36" s="3">
-        <v>46267.67125</v>
+        <v>46269.4200925926</v>
       </c>
       <c r="N36" s="3">
-        <v>46301.4629166667</v>
+        <v>46276.3367592593</v>
       </c>
       <c r="O36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>2609883</v>
+        <v>2610030</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I37" s="3">
-        <v>46309.7050347222</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="J37" s="3">
-        <v>46280.4030439815</v>
+        <v>46268.3853071412</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="M37" s="3">
-        <v>46267.6217013889</v>
+        <v>46267.7105324074</v>
       </c>
       <c r="N37" s="3">
-        <v>46309.7050347222</v>
+        <v>46274.6271990741</v>
       </c>
       <c r="O37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>2609551</v>
+        <v>2609985</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H38" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I38" s="3">
-        <v>46273.6887962963</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="J38" s="3">
-        <v>46267.355462963</v>
+        <v>46267.6774134606</v>
       </c>
       <c r="K38" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="M38" s="3">
-        <v>46267.355462963</v>
+        <v>46267.67125</v>
       </c>
       <c r="N38" s="3">
-        <v>46273.6887962963</v>
+        <v>46301.4629166667</v>
       </c>
       <c r="O38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>2609107</v>
+        <v>2609883</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I39" s="3">
-        <v>46300.3339583333</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="J39" s="3">
-        <v>46293.378900463</v>
+        <v>46280.4030439815</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="M39" s="3">
-        <v>46266.4797916667</v>
+        <v>46267.6217013889</v>
       </c>
       <c r="N39" s="3">
-        <v>46300.3339583333</v>
+        <v>46309.7050347222</v>
       </c>
       <c r="O39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>2608731</v>
+        <v>2609551</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>100</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I40" s="3">
-        <v>46298.2938888889</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="J40" s="3">
-        <v>46294.5490856481</v>
+        <v>46267.355462963</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M40" s="3">
-        <v>46265.6780671296</v>
+        <v>46267.355462963</v>
       </c>
       <c r="N40" s="3">
-        <v>46298.2938888889</v>
+        <v>46273.6887962963</v>
       </c>
       <c r="O40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>2608637</v>
+        <v>2609107</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>101</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I41" s="3">
-        <v>46304.6977777778</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="J41" s="3">
-        <v>46293.6437731481</v>
+        <v>46293.378900463</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="M41" s="3">
-        <v>46265.6144444444</v>
+        <v>46266.4797916667</v>
       </c>
       <c r="N41" s="3">
-        <v>46304.6977777778</v>
+        <v>46300.3339583333</v>
       </c>
       <c r="O41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>2607413</v>
+        <v>2608731</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D42" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="G42" s="0" t="s">
         <v>102</v>
       </c>
-      <c r="E42" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G42" s="0" t="s">
-        <v>103</v>
-      </c>
       <c r="H42" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="I42" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I42" s="3">
+        <v>46298.2938888889</v>
+      </c>
       <c r="J42" s="3">
-        <v>46266.569212963</v>
+        <v>46294.5490856481</v>
       </c>
       <c r="K42" s="0" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="M42" s="3">
-        <v>46261.6163888889</v>
-      </c>
-      <c r="N42" s="3"/>
+        <v>46265.6780671296</v>
+      </c>
+      <c r="N42" s="3">
+        <v>46298.2938888889</v>
+      </c>
       <c r="O42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>2607198</v>
+        <v>2608637</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I43" s="3">
-        <v>46267.3546643518</v>
+        <v>46304.6977777778</v>
       </c>
       <c r="J43" s="3">
-        <v>46273.6204976852</v>
+        <v>46293.6437731481</v>
       </c>
       <c r="K43" s="0" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="M43" s="3">
-        <v>46261.4379976852</v>
+        <v>46265.6144444444</v>
       </c>
       <c r="N43" s="3">
-        <v>46267.3546643518</v>
+        <v>46304.6977777778</v>
       </c>
       <c r="O43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>2606003</v>
+        <v>2607413</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D44" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E44" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="0" t="s">
-        <v>89</v>
-      </c>
       <c r="G44" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="H44" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3">
+        <v>46266.569212963</v>
+      </c>
+      <c r="K44" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="H44" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I44" s="3">
-        <v>46265.3599537037</v>
-      </c>
-      <c r="J44" s="3">
-        <v>46259.4993506944</v>
-      </c>
-      <c r="K44" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="L44" s="0" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="M44" s="3">
-        <v>46259.443287037</v>
-      </c>
-      <c r="N44" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46261.6163888889</v>
+      </c>
+      <c r="N44" s="3"/>
       <c r="O44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>2604815</v>
+        <v>2607198</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>107</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I45" s="3">
-        <v>46296.563587963</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="J45" s="3">
-        <v>46268.6781365741</v>
+        <v>46273.6204976852</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="M45" s="3">
-        <v>46255.4177546296</v>
+        <v>46261.4379976852</v>
       </c>
       <c r="N45" s="3">
-        <v>46296.563587963</v>
+        <v>46267.3546643518</v>
       </c>
       <c r="O45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>2604500</v>
+        <v>2606003</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>108</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I46" s="3">
-        <v>46260.4812268519</v>
+        <v>46265.3599537037</v>
       </c>
       <c r="J46" s="3">
-        <v>46258.3485416667</v>
+        <v>46259.4993506944</v>
       </c>
       <c r="K46" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L46" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M46" s="3">
-        <v>46254.6270601852</v>
+        <v>46259.443287037</v>
       </c>
       <c r="N46" s="3">
-        <v>46260.4812268519</v>
+        <v>46290.75</v>
       </c>
       <c r="O46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>2603668</v>
+        <v>2604815</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="F47" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="G47" s="0" t="s">
-        <v>110</v>
-      </c>
       <c r="H47" s="0" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I47" s="3">
-        <v>46259.3446296296</v>
+        <v>46296.563587963</v>
       </c>
       <c r="J47" s="3">
-        <v>46258.6426851852</v>
+        <v>46268.6781365741</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="M47" s="3">
-        <v>46253.427962963</v>
+        <v>46255.4177546296</v>
       </c>
       <c r="N47" s="3">
-        <v>46290.75</v>
+        <v>46296.563587963</v>
       </c>
       <c r="O47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>2602388</v>
+        <v>2604500</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I48" s="3">
-        <v>46255.4166666667</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="J48" s="3">
-        <v>46253.4900231482</v>
+        <v>46258.3485416667</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L48" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M48" s="3">
-        <v>46251.5527777778</v>
+        <v>46254.6270601852</v>
       </c>
       <c r="N48" s="3">
-        <v>46255.4166666667</v>
+        <v>46260.4812268519</v>
       </c>
       <c r="O48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>2601999</v>
+        <v>2603668</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D49" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="G49" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="E49" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="G49" s="0" t="s">
-        <v>113</v>
-      </c>
       <c r="H49" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="I49" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="I49" s="3">
+        <v>46259.3446296296</v>
+      </c>
       <c r="J49" s="3">
-        <v>46266.6188194444</v>
+        <v>46258.6426851852</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M49" s="3">
-        <v>46248.7351273148</v>
-      </c>
-      <c r="N49" s="3"/>
+        <v>46253.427962963</v>
+      </c>
+      <c r="N49" s="3">
+        <v>46290.75</v>
+      </c>
       <c r="O49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>2600778</v>
+        <v>2602388</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="E50" s="0" t="s">
         <v>17</v>
@@ -3085,897 +3098,893 @@
         <v>18</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="I50" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I50" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="J50" s="3">
-        <v>46274.3780324074</v>
+        <v>46253.4900231482</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M50" s="3">
-        <v>46246.7171759259</v>
-      </c>
-      <c r="N50" s="3"/>
+        <v>46251.5527777778</v>
+      </c>
+      <c r="N50" s="3">
+        <v>46255.4166666667</v>
+      </c>
       <c r="O50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>2599732</v>
+        <v>2601999</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I51" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="I51" s="3"/>
       <c r="J51" s="3">
-        <v>46248.3419117245</v>
+        <v>46266.6188194444</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="M51" s="3">
-        <v>46245.4849537037</v>
-      </c>
-      <c r="N51" s="3">
-        <v>46251.4016203704</v>
-      </c>
+        <v>46248.7351273148</v>
+      </c>
+      <c r="N51" s="3"/>
       <c r="O51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>2598987</v>
+        <v>2600778</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D52" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E52" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="F52" s="0" t="s">
-        <v>120</v>
-      </c>
       <c r="G52" s="0" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I52" s="3">
-        <v>46254.6856134259</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="I52" s="3"/>
       <c r="J52" s="3">
-        <v>46251.536875</v>
+        <v>46274.3780324074</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="M52" s="3">
-        <v>46244.4564467593</v>
-      </c>
-      <c r="N52" s="3">
-        <v>46254.6856134259</v>
-      </c>
+        <v>46246.7171759259</v>
+      </c>
+      <c r="N52" s="3"/>
       <c r="O52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>2598910</v>
+        <v>2599732</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="I53" s="3">
-        <v>46254.6386574074</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="J53" s="3">
-        <v>46248.4760674769</v>
+        <v>46248.3419117245</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M53" s="3">
-        <v>46244.4094907407</v>
+        <v>46245.4849537037</v>
       </c>
       <c r="N53" s="3">
-        <v>46261.6103125</v>
+        <v>46251.4016203704</v>
       </c>
       <c r="O53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>2598767</v>
+        <v>2598987</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I54" s="3">
-        <v>46247.6666666667</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="J54" s="3">
-        <v>46245.6608564815</v>
+        <v>46251.536875</v>
       </c>
       <c r="K54" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M54" s="3">
-        <v>46241.757962963</v>
+        <v>46244.4564467593</v>
       </c>
       <c r="N54" s="3">
-        <v>46247.6666666667</v>
+        <v>46254.6856134259</v>
       </c>
       <c r="O54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>2597798</v>
+        <v>2598910</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="C55" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="G55" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="D55" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G55" s="0" t="s">
-        <v>127</v>
-      </c>
       <c r="H55" s="0" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="I55" s="3">
-        <v>46290.75</v>
+        <v>46254.6386574074</v>
       </c>
       <c r="J55" s="3">
-        <v>46273.4412384259</v>
+        <v>46248.4760674769</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M55" s="3">
-        <v>46240.4508912037</v>
+        <v>46244.4094907407</v>
       </c>
       <c r="N55" s="3">
-        <v>46290.75</v>
+        <v>46261.6103125</v>
       </c>
       <c r="O55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>2597524</v>
+        <v>2598767</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I56" s="3">
-        <v>46267.0453356481</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="J56" s="3">
-        <v>46259.4158333333</v>
+        <v>46245.6608564815</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L56" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M56" s="3">
-        <v>46239.6925347222</v>
+        <v>46241.757962963</v>
       </c>
       <c r="N56" s="3">
-        <v>46267.0453356481</v>
+        <v>46247.6666666667</v>
       </c>
       <c r="O56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>2597515</v>
+        <v>2597798</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="D57" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="F57" s="0" t="s">
-        <v>89</v>
-      </c>
       <c r="G57" s="0" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I57" s="3">
-        <v>46271.3406597222</v>
+        <v>46290.75</v>
       </c>
       <c r="J57" s="3">
-        <v>46294.7045655093</v>
+        <v>46273.4412384259</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="M57" s="3">
-        <v>46239.6856134259</v>
+        <v>46240.4508912037</v>
       </c>
       <c r="N57" s="3">
-        <v>46271.3406597222</v>
+        <v>46290.75</v>
       </c>
       <c r="O57" s="3"/>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>2597495</v>
+        <v>2597524</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>131</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I58" s="3">
-        <v>46252.3333333333</v>
+        <v>46267.0453356481</v>
       </c>
       <c r="J58" s="3">
-        <v>46241.6523302083</v>
+        <v>46259.4158333333</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="L58" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M58" s="3">
-        <v>46239.6802199074</v>
+        <v>46239.6925347222</v>
       </c>
       <c r="N58" s="3">
-        <v>46245.5968865741</v>
-      </c>
-      <c r="O58" s="3">
-        <v>46252.3333333333</v>
-      </c>
+        <v>46267.0453356481</v>
+      </c>
+      <c r="O58" s="3"/>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>2596882</v>
+        <v>2597515</v>
       </c>
       <c r="B59" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="G59" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="C59" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="D59" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E59" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="F59" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="G59" s="0" t="s">
-        <v>134</v>
-      </c>
       <c r="H59" s="0" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I59" s="3">
-        <v>46280.3775578704</v>
+        <v>46271.3406597222</v>
       </c>
       <c r="J59" s="3">
-        <v>46267.6170023148</v>
+        <v>46294.7045655093</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="M59" s="3">
-        <v>46238.7108912037</v>
+        <v>46239.6856134259</v>
       </c>
       <c r="N59" s="3">
-        <v>46280.3775578704</v>
+        <v>46271.3406597222</v>
       </c>
       <c r="O59" s="3"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2596538</v>
+        <v>2597495</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I60" s="3">
-        <v>46273.960787037</v>
+        <v>46252.3333333333</v>
       </c>
       <c r="J60" s="3">
-        <v>46286.3521412037</v>
+        <v>46241.6523302083</v>
       </c>
       <c r="K60" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M60" s="3">
-        <v>46238.4644791667</v>
+        <v>46239.6802199074</v>
       </c>
       <c r="N60" s="3">
-        <v>46273.960787037</v>
-      </c>
-      <c r="O60" s="3"/>
+        <v>46245.5968865741</v>
+      </c>
+      <c r="O60" s="3">
+        <v>46252.3333333333</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>2596407</v>
+        <v>2596882</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>136</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I61" s="3">
-        <v>46248.6072106482</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="J61" s="3">
-        <v>46267.6164814815</v>
+        <v>46267.6170023148</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="M61" s="3">
-        <v>46238.3780439815</v>
+        <v>46238.7108912037</v>
       </c>
       <c r="N61" s="3">
-        <v>46248.6072106482</v>
+        <v>46280.3775578704</v>
       </c>
       <c r="O61" s="3"/>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>2595510</v>
+        <v>2596538</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>137</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I62" s="3">
-        <v>46240.4984606481</v>
+        <v>46273.960787037</v>
       </c>
       <c r="J62" s="3">
-        <v>46245.3667592593</v>
+        <v>46286.3521412037</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M62" s="3">
-        <v>46234.6442939815</v>
+        <v>46238.4644791667</v>
       </c>
       <c r="N62" s="3">
-        <v>46240.4984606481</v>
+        <v>46273.960787037</v>
       </c>
       <c r="O62" s="3"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>2595497</v>
+        <v>2596407</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>138</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I63" s="3">
-        <v>46240.4978240741</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="J63" s="3">
-        <v>46245.3669444444</v>
+        <v>46267.6164814815</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M63" s="3">
-        <v>46234.6436574074</v>
+        <v>46238.3780439815</v>
       </c>
       <c r="N63" s="3">
-        <v>46240.4978240741</v>
+        <v>46248.6072106482</v>
       </c>
       <c r="O63" s="3"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2593529</v>
+        <v>2595510</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>139</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I64" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="J64" s="3">
-        <v>46294.7638078704</v>
+        <v>46245.3667592593</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="L64" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M64" s="3">
-        <v>46231.6639930556</v>
+        <v>46234.6442939815</v>
       </c>
       <c r="N64" s="3">
-        <v>46237.5806597222</v>
+        <v>46240.4984606481</v>
       </c>
       <c r="O64" s="3"/>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2593490</v>
+        <v>2595497</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I65" s="3">
-        <v>46239.6748032407</v>
+        <v>46240.4978240741</v>
       </c>
       <c r="J65" s="3">
-        <v>46253.4905324074</v>
+        <v>46245.3669444444</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="M65" s="3">
-        <v>46231.6518865741</v>
+        <v>46234.6436574074</v>
       </c>
       <c r="N65" s="3">
-        <v>46239.6748032407</v>
-      </c>
-      <c r="O65" s="3">
-        <v>46234.48125</v>
-      </c>
+        <v>46240.4978240741</v>
+      </c>
+      <c r="O65" s="3"/>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>2593260</v>
+        <v>2593529</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>141</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I66" s="3">
-        <v>46241.6638888889</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="J66" s="3">
-        <v>46267.614525463</v>
+        <v>46294.7638078704</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M66" s="3">
-        <v>46231.435150463</v>
+        <v>46231.6639930556</v>
       </c>
       <c r="N66" s="3">
-        <v>46241.6638888889</v>
+        <v>46237.5806597222</v>
       </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>2593216</v>
+        <v>2593490</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I67" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I67" s="3">
+        <v>46239.6748032407</v>
+      </c>
       <c r="J67" s="3">
-        <v>46231.4047453704</v>
+        <v>46253.4905324074</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M67" s="3">
-        <v>46231.4011111111</v>
-      </c>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
+        <v>46231.6518865741</v>
+      </c>
+      <c r="N67" s="3">
+        <v>46239.6748032407</v>
+      </c>
+      <c r="O67" s="3">
+        <v>46234.48125</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>2592878</v>
+        <v>2593260</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>143</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I68" s="3">
-        <v>46290.75</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="J68" s="3">
-        <v>46294.7411689815</v>
+        <v>46267.614525463</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M68" s="3">
-        <v>46230.6004282407</v>
+        <v>46231.435150463</v>
       </c>
       <c r="N68" s="3">
-        <v>46290.75</v>
+        <v>46241.6638888889</v>
       </c>
       <c r="O68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>2592468</v>
+        <v>2593216</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>144</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I69" s="3">
-        <v>46237.6038657407</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I69" s="3"/>
       <c r="J69" s="3">
-        <v>46240.6136738773</v>
+        <v>46231.4047453704</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="M69" s="3">
-        <v>46227.7107060185</v>
-      </c>
-      <c r="N69" s="3">
-        <v>46293.6033680556</v>
-      </c>
+        <v>46231.4011111111</v>
+      </c>
+      <c r="N69" s="3"/>
       <c r="O69" s="3"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>2591596</v>
+        <v>2592878</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F70" s="0" t="s">
         <v>31</v>
@@ -3984,545 +3993,549 @@
         <v>145</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I70" s="3">
-        <v>46238.7083333333</v>
+        <v>46290.75</v>
       </c>
       <c r="J70" s="3">
-        <v>46267.3444803241</v>
+        <v>46295.5935300926</v>
       </c>
       <c r="K70" s="0" t="s">
         <v>21</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M70" s="3">
-        <v>46226.4797916667</v>
+        <v>46230.6004282407</v>
       </c>
       <c r="N70" s="3">
-        <v>46282.6141435185</v>
+        <v>46290.75</v>
       </c>
       <c r="O70" s="3"/>
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>2591284</v>
+        <v>2592468</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="G71" s="0" t="s">
         <v>146</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I71" s="3">
-        <v>46266.3384837963</v>
+        <v>46237.6038657407</v>
       </c>
       <c r="J71" s="3">
-        <v>46225.7002398495</v>
+        <v>46240.6136738773</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="M71" s="3">
-        <v>46225.6718171296</v>
+        <v>46227.7107060185</v>
       </c>
       <c r="N71" s="3">
-        <v>46266.3384837963</v>
+        <v>46293.6033680556</v>
       </c>
       <c r="O71" s="3"/>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>2588490</v>
+        <v>2591596</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>147</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I72" s="3">
-        <v>46230.722037037</v>
+        <v>46238.7083333333</v>
       </c>
       <c r="J72" s="3">
-        <v>46231.4339699074</v>
+        <v>46267.3444803241</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M72" s="3">
-        <v>46218.4928703704</v>
+        <v>46226.4797916667</v>
       </c>
       <c r="N72" s="3">
-        <v>46230.722037037</v>
+        <v>46282.6141435185</v>
       </c>
       <c r="O72" s="3"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>2588025</v>
+        <v>2591284</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D73" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F73" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="G73" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="E73" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="F73" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="G73" s="0" t="s">
-        <v>151</v>
-      </c>
       <c r="H73" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="I73" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="I73" s="3">
+        <v>46266.3384837963</v>
+      </c>
       <c r="J73" s="3">
-        <v>46267.5903356482</v>
+        <v>46225.7002398495</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M73" s="3">
-        <v>46217.612962963</v>
-      </c>
-      <c r="N73" s="3"/>
+        <v>46225.6718171296</v>
+      </c>
+      <c r="N73" s="3">
+        <v>46266.3384837963</v>
+      </c>
       <c r="O73" s="3"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2587849</v>
+        <v>2588490</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I74" s="3">
-        <v>46226.6083796296</v>
+        <v>46230.722037037</v>
       </c>
       <c r="J74" s="3">
-        <v>46237.9144806713</v>
+        <v>46231.4339699074</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M74" s="3">
-        <v>46217.4506597222</v>
+        <v>46218.4928703704</v>
       </c>
       <c r="N74" s="3">
-        <v>46226.6083796296</v>
+        <v>46230.722037037</v>
       </c>
       <c r="O74" s="3"/>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2587713</v>
+        <v>2588025</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>26</v>
+        <v>150</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>153</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I75" s="3">
-        <v>46218.7408680556</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="I75" s="3"/>
       <c r="J75" s="3">
-        <v>46230.4199074074</v>
+        <v>46267.5903356482</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M75" s="3">
-        <v>46217.3658680556</v>
-      </c>
-      <c r="N75" s="3">
-        <v>46218.7408680556</v>
-      </c>
+        <v>46217.612962963</v>
+      </c>
+      <c r="N75" s="3"/>
       <c r="O75" s="3"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>2587585</v>
+        <v>2587849</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>154</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I76" s="3">
-        <v>46220.6264583333</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="J76" s="3">
-        <v>46259.4474884259</v>
+        <v>46237.9144806713</v>
       </c>
       <c r="K76" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L76" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M76" s="3">
-        <v>46216.7097916667</v>
+        <v>46217.4506597222</v>
       </c>
       <c r="N76" s="3">
-        <v>46220.6264583333</v>
+        <v>46226.6083796296</v>
       </c>
       <c r="O76" s="3"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>2587006</v>
+        <v>2587713</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>155</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I77" s="3">
-        <v>46217.7289699074</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="J77" s="3">
-        <v>46227.4549884259</v>
+        <v>46230.4199074074</v>
       </c>
       <c r="K77" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M77" s="3">
-        <v>46213.7239236111</v>
+        <v>46217.3658680556</v>
       </c>
       <c r="N77" s="3">
-        <v>46217.7289699074</v>
+        <v>46218.7408680556</v>
       </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>2586984</v>
+        <v>2587585</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>156</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I78" s="3">
-        <v>46295.7416550926</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="J78" s="3">
-        <v>46273.4946180556</v>
+        <v>46259.4474884259</v>
       </c>
       <c r="K78" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L78" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M78" s="3">
-        <v>46213.6971527778</v>
+        <v>46216.7097916667</v>
       </c>
       <c r="N78" s="3">
-        <v>46295.7416550926</v>
+        <v>46220.6264583333</v>
       </c>
       <c r="O78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2586910</v>
+        <v>2587006</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F79" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="G79" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="G79" s="0" t="s">
-        <v>158</v>
-      </c>
       <c r="H79" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I79" s="3">
-        <v>46226.5833333333</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="J79" s="3">
-        <v>46230.4194212963</v>
+        <v>46227.4549884259</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M79" s="3">
-        <v>46213.6245833333</v>
+        <v>46213.7239236111</v>
       </c>
       <c r="N79" s="3">
-        <v>46226.5833333333</v>
+        <v>46217.7289699074</v>
       </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>2586651</v>
+        <v>2586984</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>159</v>
+        <v>28</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I80" s="3">
-        <v>46218.7157407407</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="J80" s="3">
-        <v>46213.3824074074</v>
+        <v>46273.4946180556</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="L80" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M80" s="3">
-        <v>46213.3824074074</v>
+        <v>46213.6971527778</v>
       </c>
       <c r="N80" s="3">
-        <v>46218.7157407407</v>
+        <v>46295.7416550926</v>
       </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>2586187</v>
+        <v>2586910</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="I81" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I81" s="3">
+        <v>46226.5833333333</v>
+      </c>
       <c r="J81" s="3">
-        <v>46219.3850231481</v>
+        <v>46230.4194212963</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M81" s="3">
-        <v>46211.7697337963</v>
-      </c>
-      <c r="N81" s="3"/>
+        <v>46213.6245833333</v>
+      </c>
+      <c r="N81" s="3">
+        <v>46226.5833333333</v>
+      </c>
       <c r="O81" s="3"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>2585888</v>
+        <v>2586651</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H82" s="0" t="s">
         <v>20</v>
       </c>
       <c r="I82" s="3">
-        <v>46217.4119907407</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="J82" s="3">
-        <v>46217.5003587963</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="K82" s="0" t="s">
         <v>21</v>
@@ -4531,425 +4544,421 @@
         <v>22</v>
       </c>
       <c r="M82" s="3">
-        <v>46211.4953240741</v>
+        <v>46213.3824074074</v>
       </c>
       <c r="N82" s="3">
-        <v>46290.75</v>
+        <v>46218.7157407407</v>
       </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>2585424</v>
+        <v>2586187</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>164</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="I83" s="3">
-        <v>46223.3927199074</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I83" s="3"/>
       <c r="J83" s="3">
-        <v>46234.4964930556</v>
+        <v>46219.3850231481</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="M83" s="3">
-        <v>46210.6427199074</v>
-      </c>
-      <c r="N83" s="3">
-        <v>46290.75</v>
-      </c>
+        <v>46211.7697337963</v>
+      </c>
+      <c r="N83" s="3"/>
       <c r="O83" s="3"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>2584638</v>
+        <v>2585888</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>165</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="I84" s="3">
-        <v>46213.4171527778</v>
+        <v>46217.4119907407</v>
       </c>
       <c r="J84" s="3">
-        <v>46213.4090859607</v>
+        <v>46295.4495486111</v>
       </c>
       <c r="K84" s="0" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="L84" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M84" s="3">
-        <v>46209.5016203704</v>
+        <v>46211.4953240741</v>
       </c>
       <c r="N84" s="3">
-        <v>46232.3874884259</v>
+        <v>46290.75</v>
       </c>
       <c r="O84" s="3"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>2584397</v>
+        <v>2585424</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="I85" s="3">
-        <v>46212.6757175926</v>
+        <v>46223.3927199074</v>
       </c>
       <c r="J85" s="3">
-        <v>46213.3741550926</v>
+        <v>46234.4964930556</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M85" s="3">
-        <v>46209.3423842593</v>
+        <v>46210.6427199074</v>
       </c>
       <c r="N85" s="3">
-        <v>46212.6757175926</v>
+        <v>46290.75</v>
       </c>
       <c r="O85" s="3"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>2584167</v>
+        <v>2584638</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="I86" s="3">
-        <v>46246.7216435185</v>
+        <v>46213.4171527778</v>
       </c>
       <c r="J86" s="3">
-        <v>46247.4396759259</v>
+        <v>46213.4090859607</v>
       </c>
       <c r="K86" s="0" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="L86" s="0" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="M86" s="3">
-        <v>46206.6383101852</v>
+        <v>46209.5016203704</v>
       </c>
       <c r="N86" s="3">
-        <v>46246.7216435185</v>
+        <v>46232.3874884259</v>
       </c>
       <c r="O86" s="3"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>2583950</v>
+        <v>2584397</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I87" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I87" s="3">
+        <v>46212.6757175926</v>
+      </c>
       <c r="J87" s="3">
-        <v>46273.4100925926</v>
+        <v>46213.3741550926</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M87" s="3">
-        <v>46206.4623148148</v>
-      </c>
-      <c r="N87" s="3"/>
+        <v>46209.3423842593</v>
+      </c>
+      <c r="N87" s="3">
+        <v>46212.6757175926</v>
+      </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>2583447</v>
+        <v>2584167</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I88" s="3">
-        <v>46205.7916666667</v>
+        <v>46246.7216435185</v>
       </c>
       <c r="J88" s="3">
-        <v>46265.3645138889</v>
+        <v>46247.4396759259</v>
       </c>
       <c r="K88" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M88" s="3">
-        <v>46205.5752083333</v>
+        <v>46206.6383101852</v>
       </c>
       <c r="N88" s="3">
-        <v>46245.6724189815</v>
+        <v>46246.7216435185</v>
       </c>
       <c r="O88" s="3"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>2583382</v>
+        <v>2583950</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="E89" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>171</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I89" s="3"/>
       <c r="J89" s="3">
-        <v>46293.3798726852</v>
+        <v>46273.4100925926</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M89" s="3">
-        <v>46205.4905092593</v>
+        <v>46206.4623148148</v>
       </c>
       <c r="N89" s="3"/>
       <c r="O89" s="3"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2582452</v>
+        <v>2583447</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>172</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I90" s="3">
-        <v>46244.4166666667</v>
+        <v>46205.7916666667</v>
       </c>
       <c r="J90" s="3">
-        <v>46204.7763078704</v>
+        <v>46265.3645138889</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M90" s="3">
-        <v>46203.8250810185</v>
+        <v>46205.5752083333</v>
       </c>
       <c r="N90" s="3">
-        <v>46244.4166666667</v>
+        <v>46245.6724189815</v>
       </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>2582352</v>
+        <v>2583382</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I91" s="3">
-        <v>46244.340775463</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I91" s="3"/>
       <c r="J91" s="3">
-        <v>46204.7761805556</v>
+        <v>46293.3798726852</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="M91" s="3">
-        <v>46203.6741087963</v>
-      </c>
-      <c r="N91" s="3">
-        <v>46244.340775463</v>
-      </c>
+        <v>46205.4905092593</v>
+      </c>
+      <c r="N91" s="3"/>
       <c r="O91" s="3"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>2579299</v>
+        <v>2582452</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F92" s="0" t="s">
         <v>89</v>
@@ -4958,1838 +4967,1842 @@
         <v>175</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I92" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I92" s="3">
+        <v>46244.4166666667</v>
+      </c>
       <c r="J92" s="3">
-        <v>46204.3277777778</v>
+        <v>46204.7763078704</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M92" s="3">
-        <v>46196.4165162037</v>
-      </c>
-      <c r="N92" s="3"/>
+        <v>46203.8250810185</v>
+      </c>
+      <c r="N92" s="3">
+        <v>46244.4166666667</v>
+      </c>
       <c r="O92" s="3"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>2576326</v>
+        <v>2582352</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>176</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I93" s="3">
-        <v>46192.7916666667</v>
+        <v>46244.340775463</v>
       </c>
       <c r="J93" s="3">
-        <v>46230.6812731481</v>
+        <v>46204.7761805556</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M93" s="3">
-        <v>46189.3995833333</v>
-      </c>
-      <c r="N93" s="3"/>
+        <v>46203.6741087963</v>
+      </c>
+      <c r="N93" s="3">
+        <v>46244.340775463</v>
+      </c>
       <c r="O93" s="3"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>2574153</v>
+        <v>2579299</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I94" s="3"/>
       <c r="J94" s="3">
-        <v>46204.3218402778</v>
+        <v>46204.3277777778</v>
       </c>
       <c r="K94" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L94" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M94" s="3">
-        <v>46183.4711226852</v>
+        <v>46196.4165162037</v>
       </c>
       <c r="N94" s="3"/>
       <c r="O94" s="3"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>2572707</v>
+        <v>2576326</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>178</v>
+        <v>40</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>178</v>
+        <v>40</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="F95" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="G95" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="G95" s="0" t="s">
-        <v>180</v>
-      </c>
       <c r="H95" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I95" s="3">
-        <v>46219.3964814815</v>
+        <v>46192.7916666667</v>
       </c>
       <c r="J95" s="3">
-        <v>46188.4629166667</v>
+        <v>46230.6812731481</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="M95" s="3">
-        <v>46178.7298148148</v>
-      </c>
-      <c r="N95" s="3">
-        <v>46219.3964814815</v>
-      </c>
+        <v>46189.3995833333</v>
+      </c>
+      <c r="N95" s="3"/>
       <c r="O95" s="3"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>2570274</v>
+        <v>2574153</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>181</v>
+        <v>40</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>181</v>
+        <v>40</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I96" s="3"/>
       <c r="J96" s="3">
-        <v>46204.3220138889</v>
+        <v>46204.3218402778</v>
       </c>
       <c r="K96" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L96" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M96" s="3">
-        <v>46171.6563773148</v>
+        <v>46183.4711226852</v>
       </c>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>2562116</v>
+        <v>2572707</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>69</v>
+        <v>182</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>183</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I97" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I97" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="J97" s="3">
-        <v>46160.7191666667</v>
+        <v>46188.4629166667</v>
       </c>
       <c r="K97" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M97" s="3">
-        <v>46154.3432638889</v>
-      </c>
-      <c r="N97" s="3"/>
+        <v>46178.7298148148</v>
+      </c>
+      <c r="N97" s="3">
+        <v>46219.3964814815</v>
+      </c>
       <c r="O97" s="3"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>2558553</v>
+        <v>2570274</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="D98" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E98" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="F98" s="0" t="s">
-        <v>61</v>
-      </c>
       <c r="G98" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I98" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I98" s="3"/>
       <c r="J98" s="3">
-        <v>46154.5888773148</v>
+        <v>46204.3220138889</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="M98" s="3">
-        <v>46146.3561805556</v>
-      </c>
-      <c r="N98" s="3">
-        <v>46149.6895138889</v>
-      </c>
+        <v>46171.6563773148</v>
+      </c>
+      <c r="N98" s="3"/>
       <c r="O98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>2556271</v>
+        <v>2562116</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I99" s="3">
-        <v>46141.4297453704</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I99" s="3"/>
       <c r="J99" s="3">
-        <v>46139.9871412037</v>
+        <v>46160.7191666667</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M99" s="3">
-        <v>46139.471412037</v>
-      </c>
-      <c r="N99" s="3">
-        <v>46141.4901157407</v>
-      </c>
+        <v>46154.3432638889</v>
+      </c>
+      <c r="N99" s="3"/>
       <c r="O99" s="3"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>2556211</v>
+        <v>2558553</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I100" s="3">
-        <v>46150.6617476852</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="J100" s="3">
-        <v>46146.3663773148</v>
+        <v>46154.5888773148</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L100" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M100" s="3">
-        <v>46139.4325810185</v>
+        <v>46146.3561805556</v>
       </c>
       <c r="N100" s="3">
-        <v>46150.6617476852</v>
+        <v>46149.6895138889</v>
       </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>2556029</v>
+        <v>2556271</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I101" s="3">
-        <v>46150.5</v>
+        <v>46141.4297453704</v>
       </c>
       <c r="J101" s="3">
-        <v>46146.401875</v>
+        <v>46139.9871412037</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="M101" s="3">
-        <v>46138.757337963</v>
+        <v>46139.471412037</v>
       </c>
       <c r="N101" s="3">
-        <v>46154.6616087963</v>
+        <v>46141.4901157407</v>
       </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>2554341</v>
+        <v>2556211</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I102" s="3">
-        <v>46136.3599768519</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="J102" s="3">
-        <v>46135.6585185185</v>
+        <v>46146.3663773148</v>
       </c>
       <c r="K102" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L102" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="M102" s="3">
-        <v>46134.4016435185</v>
+        <v>46139.4325810185</v>
       </c>
       <c r="N102" s="3">
-        <v>46136.3599768519</v>
+        <v>46150.6617476852</v>
       </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>2547638</v>
+        <v>2556029</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I103" s="3">
-        <v>46150.3473611111</v>
+        <v>46150.5</v>
       </c>
       <c r="J103" s="3">
-        <v>46119.5010069444</v>
+        <v>46146.401875</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="M103" s="3">
-        <v>46114.4931944444</v>
+        <v>46138.757337963</v>
       </c>
       <c r="N103" s="3">
-        <v>46150.3473611111</v>
+        <v>46154.6616087963</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>2537054</v>
+        <v>2554341</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I104" s="3">
-        <v>46093.4339236111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="J104" s="3">
-        <v>46090.3698263889</v>
+        <v>46135.6585185185</v>
       </c>
       <c r="K104" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="M104" s="3">
-        <v>46087.5797569444</v>
+        <v>46134.4016435185</v>
       </c>
       <c r="N104" s="3">
-        <v>46093.4339236111</v>
+        <v>46136.3599768519</v>
       </c>
       <c r="O104" s="3"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>2531696</v>
+        <v>2547638</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I105" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I105" s="3">
+        <v>46150.3473611111</v>
+      </c>
       <c r="J105" s="3">
-        <v>46204.3216782407</v>
+        <v>46119.5010069444</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="M105" s="3">
-        <v>46076.5833912037</v>
-      </c>
-      <c r="N105" s="3"/>
+        <v>46114.4931944444</v>
+      </c>
+      <c r="N105" s="3">
+        <v>46150.3473611111</v>
+      </c>
       <c r="O105" s="3"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>2530739</v>
+        <v>2537054</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="C106" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G106" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="D106" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="E106" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F106" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="G106" s="0" t="s">
-        <v>194</v>
-      </c>
       <c r="H106" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="I106" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I106" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="J106" s="3">
-        <v>46218.6914940625</v>
+        <v>46090.3698263889</v>
       </c>
       <c r="K106" s="0" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="L106" s="0" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M106" s="3">
-        <v>46072.6973148148</v>
-      </c>
-      <c r="N106" s="3"/>
+        <v>46087.5797569444</v>
+      </c>
+      <c r="N106" s="3">
+        <v>46093.4339236111</v>
+      </c>
       <c r="O106" s="3"/>
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>2529639</v>
+        <v>2531696</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D107" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="E107" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E107" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="F107" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="G107" s="0" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I107" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I107" s="3"/>
       <c r="J107" s="3">
-        <v>46072.6891666667</v>
+        <v>46204.3216782407</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="M107" s="3">
-        <v>46069.5930902778</v>
-      </c>
-      <c r="N107" s="3">
-        <v>46083.3430902778</v>
-      </c>
+        <v>46076.5833912037</v>
+      </c>
+      <c r="N107" s="3"/>
       <c r="O107" s="3"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>2529591</v>
+        <v>2530739</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>67</v>
+        <v>196</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I108" s="3">
-        <v>46108.5968055556</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="I108" s="3"/>
       <c r="J108" s="3">
-        <v>46126.6875</v>
+        <v>46218.6914940625</v>
       </c>
       <c r="K108" s="0" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="L108" s="0" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="M108" s="3">
-        <v>46069.4509722222</v>
-      </c>
-      <c r="N108" s="3">
-        <v>46108.5968055556</v>
-      </c>
+        <v>46072.6973148148</v>
+      </c>
+      <c r="N108" s="3"/>
       <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>2528858</v>
+        <v>2529639</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I109" s="3">
-        <v>46107.3861458333</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="J109" s="3">
-        <v>46087.6277662037</v>
+        <v>46072.6891666667</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="M109" s="3">
-        <v>46065.7194791667</v>
+        <v>46069.5930902778</v>
       </c>
       <c r="N109" s="3">
-        <v>46107.3861458333</v>
+        <v>46083.3430902778</v>
       </c>
       <c r="O109" s="3"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>2525312</v>
+        <v>2529591</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I110" s="3">
-        <v>46070.5877314815</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="J110" s="3">
-        <v>46062.7587037037</v>
+        <v>46126.6875</v>
       </c>
       <c r="K110" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L110" s="0" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="M110" s="3">
-        <v>46058.3585648148</v>
+        <v>46069.4509722222</v>
       </c>
       <c r="N110" s="3">
-        <v>46070.5877314815</v>
+        <v>46108.5968055556</v>
       </c>
       <c r="O110" s="3"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>2525272</v>
+        <v>2528858</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>199</v>
+        <v>120</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>199</v>
+        <v>120</v>
       </c>
       <c r="D111" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="F111" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G111" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="E111" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F111" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G111" s="0" t="s">
-        <v>201</v>
-      </c>
       <c r="H111" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I111" s="3">
-        <v>46203.7916666667</v>
+        <v>46107.3861458333</v>
       </c>
       <c r="J111" s="3">
-        <v>46126.7441782407</v>
+        <v>46087.6277662037</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M111" s="3">
-        <v>46058.2883101852</v>
-      </c>
-      <c r="N111" s="3"/>
+        <v>46065.7194791667</v>
+      </c>
+      <c r="N111" s="3">
+        <v>46107.3861458333</v>
+      </c>
       <c r="O111" s="3"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>2524577</v>
+        <v>2525312</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="I112" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I112" s="3">
+        <v>46070.5877314815</v>
+      </c>
       <c r="J112" s="3">
-        <v>46267.4298180903</v>
+        <v>46062.7587037037</v>
       </c>
       <c r="K112" s="0" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="M112" s="3">
-        <v>46056.697349537</v>
-      </c>
-      <c r="N112" s="3"/>
+        <v>46058.3585648148</v>
+      </c>
+      <c r="N112" s="3">
+        <v>46070.5877314815</v>
+      </c>
       <c r="O112" s="3"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>2524373</v>
+        <v>2525272</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="D113" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="E113" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F113" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="E113" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="F113" s="0" t="s">
-        <v>77</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>204</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I113" s="3">
-        <v>46087.3854513889</v>
+        <v>46203.7916666667</v>
       </c>
       <c r="J113" s="3">
-        <v>46056.6543865741</v>
+        <v>46126.7441782407</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="M113" s="3">
-        <v>46056.5937847222</v>
-      </c>
-      <c r="N113" s="3">
-        <v>46087.3854513889</v>
-      </c>
+        <v>46058.2883101852</v>
+      </c>
+      <c r="N113" s="3"/>
       <c r="O113" s="3"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>2524062</v>
+        <v>2524577</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>205</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I114" s="3">
-        <v>46057.7412615741</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="I114" s="3"/>
       <c r="J114" s="3">
-        <v>46056.6210300926</v>
+        <v>46267.4298180903</v>
       </c>
       <c r="K114" s="0" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="L114" s="0" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M114" s="3">
-        <v>46056.3662615741</v>
-      </c>
-      <c r="N114" s="3">
-        <v>46057.7412615741</v>
-      </c>
+        <v>46056.697349537</v>
+      </c>
+      <c r="N114" s="3"/>
       <c r="O114" s="3"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>2523635</v>
+        <v>2524373</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I115" s="3">
-        <v>46059.4164236111</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="J115" s="3">
-        <v>46055.6034837963</v>
+        <v>46056.6543865741</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="M115" s="3">
-        <v>46055.4997569444</v>
+        <v>46056.5937847222</v>
       </c>
       <c r="N115" s="3">
-        <v>46059.4164236111</v>
+        <v>46087.3854513889</v>
       </c>
       <c r="O115" s="3"/>
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>2523602</v>
+        <v>2524062</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I116" s="3">
-        <v>46093.6246643519</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="J116" s="3">
-        <v>46056.5784027778</v>
+        <v>46056.6210300926</v>
       </c>
       <c r="K116" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L116" s="0" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="M116" s="3">
-        <v>46055.4788310185</v>
+        <v>46056.3662615741</v>
       </c>
       <c r="N116" s="3">
-        <v>46093.6246643519</v>
+        <v>46057.7412615741</v>
       </c>
       <c r="O116" s="3"/>
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>2521645</v>
+        <v>2523635</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="I117" s="3">
-        <v>46062.5</v>
+        <v>46059.4164236111</v>
       </c>
       <c r="J117" s="3">
-        <v>46050.3426763542</v>
+        <v>46055.6034837963</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M117" s="3">
-        <v>46049.7714236111</v>
-      </c>
-      <c r="N117" s="3"/>
+        <v>46055.4997569444</v>
+      </c>
+      <c r="N117" s="3">
+        <v>46059.4164236111</v>
+      </c>
       <c r="O117" s="3"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>2521079</v>
+        <v>2523602</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I118" s="3">
-        <v>46052.6666666667</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="J118" s="3">
-        <v>46056.6197800926</v>
+        <v>46056.5784027778</v>
       </c>
       <c r="K118" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L118" s="0" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="M118" s="3">
-        <v>46048.7684490741</v>
+        <v>46055.4788310185</v>
       </c>
       <c r="N118" s="3">
-        <v>46061.6309722222</v>
+        <v>46093.6246643519</v>
       </c>
       <c r="O118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>2520048</v>
+        <v>2521645</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="I119" s="3">
-        <v>46057.5</v>
+        <v>46062.5</v>
       </c>
       <c r="J119" s="3">
-        <v>46052.5774305556</v>
+        <v>46050.3426763542</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M119" s="3">
-        <v>46045.3325578704</v>
-      </c>
-      <c r="N119" s="3">
-        <v>46057.5</v>
-      </c>
+        <v>46049.7714236111</v>
+      </c>
+      <c r="N119" s="3"/>
       <c r="O119" s="3"/>
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <v>2519904</v>
+        <v>2521079</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I120" s="3">
-        <v>46084.7217939815</v>
+        <v>46052.6666666667</v>
       </c>
       <c r="J120" s="3">
-        <v>46044.7413888889</v>
+        <v>46056.6197800926</v>
       </c>
       <c r="K120" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L120" s="0" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="M120" s="3">
-        <v>46044.6384606482</v>
+        <v>46048.7684490741</v>
       </c>
       <c r="N120" s="3">
-        <v>46084.7217939815</v>
+        <v>46061.6309722222</v>
       </c>
       <c r="O120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <v>2519523</v>
+        <v>2520048</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>67</v>
+        <v>196</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I121" s="3">
-        <v>46076.5902777778</v>
+        <v>46057.5</v>
       </c>
       <c r="J121" s="3">
-        <v>46048.4589814815</v>
+        <v>46052.5774305556</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L121" s="0" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="M121" s="3">
-        <v>46043.7362847222</v>
+        <v>46045.3325578704</v>
       </c>
       <c r="N121" s="3">
-        <v>46077.380775463</v>
+        <v>46057.5</v>
       </c>
       <c r="O121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <v>2519383</v>
+        <v>2519904</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>67</v>
+        <v>196</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I122" s="3">
-        <v>46076.399224537</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="J122" s="3">
-        <v>46048.4599305556</v>
+        <v>46044.7413888889</v>
       </c>
       <c r="K122" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L122" s="0" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="M122" s="3">
-        <v>46043.6075578704</v>
+        <v>46044.6384606482</v>
       </c>
       <c r="N122" s="3">
-        <v>46076.399224537</v>
+        <v>46084.7217939815</v>
       </c>
       <c r="O122" s="3"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <v>2519284</v>
+        <v>2519523</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I123" s="3">
-        <v>46049.3982986111</v>
+        <v>46076.5902777778</v>
       </c>
       <c r="J123" s="3">
-        <v>46043.742337963</v>
+        <v>46048.4589814815</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="M123" s="3">
-        <v>46043.4816319444</v>
+        <v>46043.7362847222</v>
       </c>
       <c r="N123" s="3">
-        <v>46049.3982986111</v>
+        <v>46077.380775463</v>
       </c>
       <c r="O123" s="3"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <v>2518650</v>
+        <v>2519383</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I124" s="3">
-        <v>46072.3536921296</v>
+        <v>46076.399224537</v>
       </c>
       <c r="J124" s="3">
-        <v>46043.8185648148</v>
+        <v>46048.4599305556</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L124" s="0" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="M124" s="3">
-        <v>46042.3536921296</v>
+        <v>46043.6075578704</v>
       </c>
       <c r="N124" s="3">
-        <v>46080.437025463</v>
+        <v>46076.399224537</v>
       </c>
       <c r="O124" s="3"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <v>2513117</v>
+        <v>2519284</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I125" s="3">
-        <v>46031.4922800926</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="J125" s="3">
-        <v>46028.3500347222</v>
+        <v>46043.742337963</v>
       </c>
       <c r="K125" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L125" s="0" t="s">
         <v>22</v>
       </c>
       <c r="M125" s="3">
-        <v>46027.6381134259</v>
+        <v>46043.4816319444</v>
       </c>
       <c r="N125" s="3">
-        <v>46031.4922800926</v>
+        <v>46049.3982986111</v>
       </c>
       <c r="O125" s="3"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <v>2512883</v>
+        <v>2518650</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>118</v>
+        <v>196</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I126" s="3">
-        <v>46037.6340972222</v>
+        <v>46072.3536921296</v>
       </c>
       <c r="J126" s="3">
-        <v>46129.4199421296</v>
+        <v>46043.8185648148</v>
       </c>
       <c r="K126" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="M126" s="3">
-        <v>46027.4049305556</v>
+        <v>46042.3536921296</v>
       </c>
       <c r="N126" s="3">
-        <v>46141.6335300926</v>
+        <v>46080.437025463</v>
       </c>
       <c r="O126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <v>2512542</v>
+        <v>2513117</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I127" s="3">
-        <v>46036.5</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="J127" s="3">
-        <v>46024.5900925926</v>
+        <v>46028.3500347222</v>
       </c>
       <c r="K127" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M127" s="3">
-        <v>46022.6836342593</v>
+        <v>46027.6381134259</v>
       </c>
       <c r="N127" s="3">
-        <v>46036.5</v>
+        <v>46031.4922800926</v>
       </c>
       <c r="O127" s="3"/>
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <v>2512541</v>
+        <v>2512883</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I128" s="3">
-        <v>46036.5</v>
+        <v>46037.6340972222</v>
       </c>
       <c r="J128" s="3">
-        <v>46022.7128356481</v>
+        <v>46129.4199421296</v>
       </c>
       <c r="K128" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L128" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M128" s="3">
-        <v>46022.6762615741</v>
+        <v>46027.4049305556</v>
       </c>
       <c r="N128" s="3">
-        <v>46036.5</v>
+        <v>46141.6335300926</v>
       </c>
       <c r="O128" s="3"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <v>2509014</v>
+        <v>2512542</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I129" s="3">
-        <v>46044.7250578704</v>
+        <v>46036.5</v>
       </c>
       <c r="J129" s="3">
-        <v>46022.6138541667</v>
+        <v>46024.5900925926</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="M129" s="3">
-        <v>46008.454224537</v>
+        <v>46022.6836342593</v>
       </c>
       <c r="N129" s="3">
-        <v>46045.4708564815</v>
+        <v>46036.5</v>
       </c>
       <c r="O129" s="3"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <v>2506714</v>
+        <v>2512541</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I130" s="3">
-        <v>46038.7073032407</v>
+        <v>46036.5</v>
       </c>
       <c r="J130" s="3">
-        <v>46044.7372337963</v>
+        <v>46022.7128356481</v>
       </c>
       <c r="K130" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L130" s="0" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="M130" s="3">
-        <v>46002.4364699074</v>
+        <v>46022.6762615741</v>
       </c>
       <c r="N130" s="3">
-        <v>46038.7073032407</v>
+        <v>46036.5</v>
       </c>
       <c r="O130" s="3"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <v>2506599</v>
+        <v>2509014</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I131" s="3">
-        <v>46037.61375</v>
+        <v>46044.7250578704</v>
       </c>
       <c r="J131" s="3">
-        <v>46052.3252083333</v>
+        <v>46022.6138541667</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M131" s="3">
-        <v>46002.3429166667</v>
+        <v>46008.454224537</v>
       </c>
       <c r="N131" s="3">
-        <v>46037.61375</v>
+        <v>46045.4708564815</v>
       </c>
       <c r="O131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <v>2506311</v>
+        <v>2506714</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>222</v>
+        <v>134</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>222</v>
+        <v>134</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>223</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I132" s="3">
-        <v>46013.7291666667</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="J132" s="3">
-        <v>46013.461875</v>
+        <v>46044.7372337963</v>
       </c>
       <c r="K132" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L132" s="0" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="M132" s="3">
-        <v>46001.5219328704</v>
+        <v>46002.4364699074</v>
       </c>
       <c r="N132" s="3">
-        <v>46013.7291666667</v>
+        <v>46038.7073032407</v>
       </c>
       <c r="O132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <v>2506102</v>
+        <v>2506599</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>224</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I133" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I133" s="3">
+        <v>46037.61375</v>
+      </c>
       <c r="J133" s="3">
-        <v>46241.5032638889</v>
+        <v>46052.3252083333</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="M133" s="3">
-        <v>46001.3800578704</v>
-      </c>
-      <c r="N133" s="3"/>
+        <v>46002.3429166667</v>
+      </c>
+      <c r="N133" s="3">
+        <v>46037.61375</v>
+      </c>
       <c r="O133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <v>2502589</v>
+        <v>2506311</v>
       </c>
       <c r="B134" s="0" t="s">
         <v>225</v>
@@ -6798,984 +6811,1070 @@
         <v>225</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>226</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I134" s="3">
-        <v>46029.6634375</v>
+        <v>46013.7291666667</v>
       </c>
       <c r="J134" s="3">
-        <v>46014.6931018519</v>
+        <v>46013.461875</v>
       </c>
       <c r="K134" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L134" s="0" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="M134" s="3">
-        <v>45993.3791087963</v>
+        <v>46001.5219328704</v>
       </c>
       <c r="N134" s="3">
-        <v>46029.6634375</v>
+        <v>46013.7291666667</v>
       </c>
       <c r="O134" s="3"/>
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <v>2502438</v>
+        <v>2506102</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>193</v>
+        <v>142</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>24</v>
+        <v>159</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>227</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I135" s="3">
-        <v>46037.3801388889</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I135" s="3"/>
       <c r="J135" s="3">
-        <v>45996.4823032407</v>
+        <v>46241.5032638889</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="M135" s="3">
-        <v>45992.7134722222</v>
-      </c>
-      <c r="N135" s="3">
-        <v>46037.3801388889</v>
-      </c>
+        <v>46001.3800578704</v>
+      </c>
+      <c r="N135" s="3"/>
       <c r="O135" s="3"/>
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <v>2501349</v>
+        <v>2502589</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I136" s="3">
-        <v>46069.7381944444</v>
+        <v>46029.6634375</v>
       </c>
       <c r="J136" s="3">
-        <v>46069.3651388889</v>
+        <v>46014.6931018519</v>
       </c>
       <c r="K136" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L136" s="0" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="M136" s="3">
-        <v>45989.0365856482</v>
+        <v>45993.3791087963</v>
       </c>
       <c r="N136" s="3">
-        <v>46069.7381944444</v>
+        <v>46029.6634375</v>
       </c>
       <c r="O136" s="3"/>
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <v>2500635</v>
+        <v>2502438</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I137" s="3">
-        <v>46024.4633796296</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="J137" s="3">
-        <v>46027.3611111111</v>
+        <v>45996.4823032407</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="M137" s="3">
-        <v>45987.671712963</v>
+        <v>45992.7134722222</v>
       </c>
       <c r="N137" s="3">
-        <v>46024.4633796296</v>
+        <v>46037.3801388889</v>
       </c>
       <c r="O137" s="3"/>
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <v>2498066</v>
+        <v>2501349</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>170</v>
+        <v>30</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I138" s="3">
-        <v>46073.7916666667</v>
+        <v>46069.7381944444</v>
       </c>
       <c r="J138" s="3">
-        <v>46126.6953240741</v>
+        <v>46069.3651388889</v>
       </c>
       <c r="K138" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L138" s="0" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="M138" s="3">
-        <v>45979.750162037</v>
-      </c>
-      <c r="N138" s="3"/>
+        <v>45989.0365856482</v>
+      </c>
+      <c r="N138" s="3">
+        <v>46069.7381944444</v>
+      </c>
       <c r="O138" s="3"/>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>2494282</v>
+        <v>2500635</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I139" s="3">
-        <v>45986.48125</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="J139" s="3">
-        <v>45988.567025463</v>
+        <v>46027.3611111111</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M139" s="3">
-        <v>45971.4792824074</v>
+        <v>45987.671712963</v>
       </c>
       <c r="N139" s="3">
-        <v>45986.4815625</v>
+        <v>46024.4633796296</v>
       </c>
       <c r="O139" s="3"/>
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>2494179</v>
+        <v>2498066</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>232</v>
+        <v>25</v>
       </c>
       <c r="F140" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="G140" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="G140" s="0" t="s">
-        <v>234</v>
-      </c>
       <c r="H140" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I140" s="3">
-        <v>46002.675775463</v>
+        <v>46073.7916666667</v>
       </c>
       <c r="J140" s="3">
-        <v>46044.7370486111</v>
+        <v>46126.6953240741</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L140" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M140" s="3">
-        <v>45971.4049421296</v>
-      </c>
-      <c r="N140" s="3">
-        <v>46002.675775463</v>
-      </c>
+        <v>45979.750162037</v>
+      </c>
+      <c r="N140" s="3"/>
       <c r="O140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>2490911</v>
+        <v>2494282</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>235</v>
+        <v>48</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="I141" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I141" s="3">
+        <v>45986.48125</v>
+      </c>
       <c r="J141" s="3">
-        <v>46182.7633796296</v>
+        <v>45988.567025463</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="M141" s="3">
-        <v>45961.5760300926</v>
-      </c>
-      <c r="N141" s="3"/>
+        <v>45971.4792824074</v>
+      </c>
+      <c r="N141" s="3">
+        <v>45986.4815625</v>
+      </c>
       <c r="O141" s="3"/>
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <v>2490185</v>
+        <v>2494179</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>17</v>
+        <v>235</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>237</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I142" s="3">
-        <v>46203.7916666667</v>
+        <v>46002.675775463</v>
       </c>
       <c r="J142" s="3">
-        <v>46051.4836111111</v>
+        <v>46044.7370486111</v>
       </c>
       <c r="K142" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L142" s="0" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="M142" s="3">
-        <v>45960.3928819444</v>
-      </c>
-      <c r="N142" s="3"/>
+        <v>45971.4049421296</v>
+      </c>
+      <c r="N142" s="3">
+        <v>46002.675775463</v>
+      </c>
       <c r="O142" s="3"/>
     </row>
     <row r="143">
       <c r="A143" s="2">
-        <v>2489016</v>
+        <v>2490911</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>102</v>
+        <v>238</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>238</v>
+        <v>25</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>239</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="I143" s="3"/>
       <c r="J143" s="3">
-        <v>45958.3906481481</v>
+        <v>46182.7633796296</v>
       </c>
       <c r="K143" s="0" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="L143" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M143" s="3">
-        <v>45957.7253009259</v>
+        <v>45961.5760300926</v>
       </c>
       <c r="N143" s="3"/>
       <c r="O143" s="3"/>
     </row>
     <row r="144">
       <c r="A144" s="2">
-        <v>2485386</v>
+        <v>2490185</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="E144" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>240</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="I144" s="3">
-        <v>46386.7916666667</v>
+        <v>46203.7916666667</v>
       </c>
       <c r="J144" s="3">
-        <v>46182.7639236111</v>
+        <v>46051.4836111111</v>
       </c>
       <c r="K144" s="0" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="L144" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M144" s="3">
-        <v>45947.7000115741</v>
+        <v>45960.3928819444</v>
       </c>
       <c r="N144" s="3"/>
       <c r="O144" s="3"/>
     </row>
     <row r="145">
       <c r="A145" s="2">
-        <v>2483420</v>
+        <v>2489016</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="E145" s="0" t="s">
-        <v>17</v>
+        <v>241</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>89</v>
+        <v>236</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="I145" s="3"/>
       <c r="J145" s="3">
-        <v>46140.3843518519</v>
+        <v>45958.3906481481</v>
       </c>
       <c r="K145" s="0" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="L145" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M145" s="3">
-        <v>45944.6603819444</v>
+        <v>45957.7253009259</v>
       </c>
       <c r="N145" s="3"/>
       <c r="O145" s="3"/>
     </row>
     <row r="146">
       <c r="A146" s="2">
-        <v>2474606</v>
+        <v>2485386</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>44</v>
+        <v>238</v>
       </c>
       <c r="E146" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="I146" s="3">
-        <v>45952.4506944444</v>
+        <v>46386.7916666667</v>
       </c>
       <c r="J146" s="3">
-        <v>45966.4450925926</v>
+        <v>46182.7639236111</v>
       </c>
       <c r="K146" s="0" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="L146" s="0" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="M146" s="3">
-        <v>45924.4486921296</v>
-      </c>
-      <c r="N146" s="3">
-        <v>45952.4506944444</v>
-      </c>
+        <v>45947.7000115741</v>
+      </c>
+      <c r="N146" s="3"/>
       <c r="O146" s="3"/>
     </row>
     <row r="147">
       <c r="A147" s="2">
-        <v>2470122</v>
+        <v>2483420</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>243</v>
+        <v>120</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>243</v>
+        <v>120</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>244</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>245</v>
+        <v>125</v>
       </c>
       <c r="I147" s="3"/>
       <c r="J147" s="3">
-        <v>46204.3270601852</v>
+        <v>46140.3843518519</v>
       </c>
       <c r="K147" s="0" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="L147" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M147" s="3">
-        <v>45912.5572222222</v>
+        <v>45944.6603819444</v>
       </c>
       <c r="N147" s="3"/>
       <c r="O147" s="3"/>
     </row>
     <row r="148">
       <c r="A148" s="2">
-        <v>2463515</v>
+        <v>2474606</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>246</v>
+        <v>48</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I148" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I148" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="J148" s="3">
-        <v>45910.4755555556</v>
+        <v>45966.4450925926</v>
       </c>
       <c r="K148" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L148" s="0" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M148" s="3">
-        <v>45897.4218865741</v>
-      </c>
-      <c r="N148" s="3"/>
+        <v>45924.4486921296</v>
+      </c>
+      <c r="N148" s="3">
+        <v>45952.4506944444</v>
+      </c>
       <c r="O148" s="3"/>
     </row>
     <row r="149">
       <c r="A149" s="2">
-        <v>2461703</v>
+        <v>2470122</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G149" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="H149" s="0" t="s">
         <v>248</v>
-      </c>
-      <c r="H149" s="0" t="s">
-        <v>245</v>
       </c>
       <c r="I149" s="3"/>
       <c r="J149" s="3">
-        <v>46003.3706828704</v>
+        <v>46204.3270601852</v>
       </c>
       <c r="K149" s="0" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="L149" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M149" s="3">
-        <v>45894.4525347222</v>
+        <v>45912.5572222222</v>
       </c>
       <c r="N149" s="3"/>
       <c r="O149" s="3"/>
     </row>
     <row r="150">
       <c r="A150" s="2">
-        <v>2459339</v>
+        <v>2463515</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="I150" s="3"/>
       <c r="J150" s="3">
-        <v>46140.3839930556</v>
+        <v>45910.4755555556</v>
       </c>
       <c r="K150" s="0" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="L150" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M150" s="3">
-        <v>45887.7442361111</v>
+        <v>45897.4218865741</v>
       </c>
       <c r="N150" s="3"/>
       <c r="O150" s="3"/>
     </row>
     <row r="151">
       <c r="A151" s="2">
-        <v>2456538</v>
+        <v>2461703</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>102</v>
+        <v>238</v>
       </c>
       <c r="E151" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="I151" s="3"/>
       <c r="J151" s="3">
-        <v>46126.7428356481</v>
+        <v>46003.3706828704</v>
       </c>
       <c r="K151" s="0" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="L151" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M151" s="3">
-        <v>45880.6643055556</v>
+        <v>45894.4525347222</v>
       </c>
       <c r="N151" s="3"/>
       <c r="O151" s="3"/>
     </row>
     <row r="152">
       <c r="A152" s="2">
-        <v>2449811</v>
+        <v>2459339</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>251</v>
+        <v>134</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>251</v>
+        <v>134</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>133</v>
+        <v>238</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>252</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I152" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="I152" s="3"/>
       <c r="J152" s="3">
-        <v>45870.3628819444</v>
+        <v>46140.3839930556</v>
       </c>
       <c r="K152" s="0" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="L152" s="0" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="M152" s="3">
-        <v>45862.6188888889</v>
-      </c>
-      <c r="N152" s="3">
-        <v>45875.3688888889</v>
-      </c>
+        <v>45887.7442361111</v>
+      </c>
+      <c r="N152" s="3"/>
       <c r="O152" s="3"/>
     </row>
     <row r="153">
       <c r="A153" s="2">
-        <v>2442028</v>
+        <v>2456538</v>
       </c>
       <c r="B153" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C153" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="D153" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="E153" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F153" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="G153" s="0" t="s">
         <v>253</v>
       </c>
-      <c r="C153" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="D153" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="E153" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F153" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G153" s="0" t="s">
-        <v>254</v>
-      </c>
       <c r="H153" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I153" s="3"/>
       <c r="J153" s="3">
-        <v>46126.7431134259</v>
+        <v>46126.7428356481</v>
       </c>
       <c r="K153" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L153" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M153" s="3">
-        <v>45842.317025463</v>
+        <v>45880.6643055556</v>
       </c>
       <c r="N153" s="3"/>
       <c r="O153" s="3"/>
     </row>
     <row r="154">
       <c r="A154" s="2">
-        <v>2439691</v>
+        <v>2449811</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>132</v>
+        <v>254</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>132</v>
+        <v>254</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>30</v>
+        <v>135</v>
+      </c>
+      <c r="F154" s="0" t="s">
+        <v>135</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>255</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I154" s="3">
-        <v>45852.3770833333</v>
+        <v>45875.3688888889</v>
       </c>
       <c r="J154" s="3">
-        <v>45838.6211342593</v>
+        <v>45870.3628819444</v>
       </c>
       <c r="K154" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L154" s="0" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="M154" s="3">
-        <v>45838.3761921296</v>
+        <v>45862.6188888889</v>
       </c>
       <c r="N154" s="3">
-        <v>45852.3770833333</v>
+        <v>45875.3688888889</v>
       </c>
       <c r="O154" s="3"/>
     </row>
     <row r="155">
       <c r="A155" s="2">
-        <v>2437239</v>
+        <v>2442028</v>
       </c>
       <c r="B155" s="0" t="s">
         <v>256</v>
       </c>
       <c r="C155" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="D155" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F155" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G155" s="0" t="s">
         <v>257</v>
       </c>
-      <c r="D155" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E155" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="F155" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="G155" s="0" t="s">
-        <v>258</v>
-      </c>
       <c r="H155" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I155" s="3">
-        <v>45870.3600462963</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I155" s="3"/>
       <c r="J155" s="3">
-        <v>45841.7026091435</v>
+        <v>46126.7431134259</v>
       </c>
       <c r="K155" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L155" s="0" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="M155" s="3">
-        <v>45831.6933796296</v>
-      </c>
-      <c r="N155" s="3">
-        <v>45870.3600462963</v>
-      </c>
+        <v>45842.317025463</v>
+      </c>
+      <c r="N155" s="3"/>
       <c r="O155" s="3"/>
     </row>
     <row r="156">
       <c r="A156" s="2">
+        <v>2439691</v>
+      </c>
+      <c r="B156" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C156" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="D156" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="E156" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G156" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="H156" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="I156" s="3">
+        <v>45852.3770833333</v>
+      </c>
+      <c r="J156" s="3">
+        <v>45838.6211342593</v>
+      </c>
+      <c r="K156" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="L156" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="M156" s="3">
+        <v>45838.3761921296</v>
+      </c>
+      <c r="N156" s="3">
+        <v>45852.3770833333</v>
+      </c>
+      <c r="O156" s="3"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2">
+        <v>2437239</v>
+      </c>
+      <c r="B157" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="C157" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="D157" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E157" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="F157" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="G157" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="H157" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="I157" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="J157" s="3">
+        <v>45841.7026091435</v>
+      </c>
+      <c r="K157" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="L157" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="M157" s="3">
+        <v>45831.6933796296</v>
+      </c>
+      <c r="N157" s="3">
+        <v>45870.3600462963</v>
+      </c>
+      <c r="O157" s="3"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2">
         <v>2436707</v>
       </c>
-      <c r="B156" s="0" t="s">
-        <v>251</v>
-      </c>
-      <c r="C156" s="0" t="s">
-        <v>251</v>
-      </c>
-      <c r="D156" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="E156" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F156" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G156" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="H156" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I156" s="3">
+      <c r="B158" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="C158" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="D158" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="E158" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F158" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G158" s="0" t="s">
+        <v>262</v